--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G30" s="39" t="n"/>
       <c r="H30" s="40" t="n">
-        <v>6578.98</v>
+        <v>6623.98</v>
       </c>
       <c r="I30" s="41">
         <f>IFERROR(F30-H30,0)</f>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="G31" s="51" t="n"/>
       <c r="H31" s="52" t="n">
-        <v>1089.81</v>
+        <v>1341.81</v>
       </c>
       <c r="I31" s="53">
         <f>IFERROR(F31-H31,0)</f>
@@ -8239,17 +8239,46 @@
       <c r="Q31" s="56" t="n"/>
     </row>
     <row r="32" ht="16.5" customHeight="1" s="274">
-      <c r="B32" s="34" t="n"/>
-      <c r="C32" s="35" t="n"/>
-      <c r="D32" s="36" t="n"/>
-      <c r="E32" s="37" t="n"/>
-      <c r="F32" s="38" t="n"/>
-      <c r="G32" s="39" t="n"/>
-      <c r="H32" s="40" t="n"/>
-      <c r="I32" s="41" t="n"/>
-      <c r="J32" s="42" t="n"/>
+      <c r="B32" s="34" t="inlineStr">
+        <is>
+          <t>11-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C32" s="35" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D32" s="36" t="n">
+        <v>2075</v>
+      </c>
+      <c r="E32" s="37" t="n">
+        <v>2091</v>
+      </c>
+      <c r="F32" s="38">
+        <f>IFERROR(D32+E32+G32,0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="40" t="n">
+        <v>4044</v>
+      </c>
+      <c r="I32" s="41">
+        <f>IFERROR(F32-H32,0)</f>
+        <v/>
+      </c>
+      <c r="J32" s="42">
+        <f>IFERROR(I32/F32,0)</f>
+        <v/>
+      </c>
       <c r="K32" s="43" t="n"/>
-      <c r="L32" s="9" t="n"/>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>Cierre 11 Jun + receipts</t>
+        </is>
+      </c>
       <c r="M32" s="12" t="n"/>
       <c r="N32" s="44" t="n"/>
       <c r="O32" s="45" t="n"/>
@@ -14378,9 +14407,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -24203,64 +24232,262 @@
       </c>
     </row>
     <row r="240">
-      <c r="B240" s="64" t="n"/>
-      <c r="C240" s="65" t="n"/>
-      <c r="D240" s="66" t="n"/>
-      <c r="E240" s="65" t="n"/>
-      <c r="F240" s="67" t="n"/>
-      <c r="G240" s="14" t="n"/>
-      <c r="H240" s="14" t="n"/>
-      <c r="I240" s="43" t="n"/>
+      <c r="B240" s="64" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C240" s="65" t="inlineStr">
+        <is>
+          <t>Costillas de Cerdo $315 + Bistec de Cerdo $190 + Carne Molida $409</t>
+        </is>
+      </c>
+      <c r="D240" s="66" t="inlineStr">
+        <is>
+          <t>Miscelánea LC La Cruz</t>
+        </is>
+      </c>
+      <c r="E240" s="65" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F240" s="67" t="n">
+        <v>914</v>
+      </c>
+      <c r="G240" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H240" s="14" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I240" s="43" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>Getnet slip $914 · ML debit MC · Aut 291606 · 08:59</t>
+        </is>
+      </c>
     </row>
     <row r="241">
-      <c r="B241" s="64" t="n"/>
-      <c r="C241" s="69" t="n"/>
-      <c r="D241" s="68" t="n"/>
-      <c r="E241" s="69" t="n"/>
-      <c r="F241" s="70" t="n"/>
-      <c r="G241" s="23" t="n"/>
-      <c r="H241" s="23" t="n"/>
-      <c r="I241" s="55" t="n"/>
+      <c r="B241" s="64" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C241" s="69" t="inlineStr">
+        <is>
+          <t>Ala de Pollo $975 + Papa Harvest 13.62kg $690 + Boneless Freskecito $1,200</t>
+        </is>
+      </c>
+      <c r="D241" s="68" t="inlineStr">
+        <is>
+          <t>ALICO (Cerro de las Campanas)</t>
+        </is>
+      </c>
+      <c r="E241" s="69" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F241" s="70" t="n">
+        <v>2865</v>
+      </c>
+      <c r="G241" s="23" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H241" s="23" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I241" s="55" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Paid cash exact $2,865 · 08:22 AM</t>
+        </is>
+      </c>
     </row>
     <row r="242">
-      <c r="B242" s="64" t="n"/>
-      <c r="C242" s="65" t="n"/>
-      <c r="D242" s="66" t="n"/>
-      <c r="E242" s="65" t="n"/>
-      <c r="F242" s="67" t="n"/>
-      <c r="G242" s="14" t="n"/>
-      <c r="H242" s="14" t="n"/>
-      <c r="I242" s="43" t="n"/>
+      <c r="B242" s="64" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C242" s="65" t="inlineStr">
+        <is>
+          <t>Muslo de Pollo 4.70 kg @ $50</t>
+        </is>
+      </c>
+      <c r="D242" s="66" t="inlineStr">
+        <is>
+          <t>Pollería (nota de remisión)</t>
+        </is>
+      </c>
+      <c r="E242" s="65" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F242" s="67" t="n">
+        <v>235</v>
+      </c>
+      <c r="G242" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H242" s="14" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I242" s="43" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Pink nota "Oh Lele" · marked Cobrado</t>
+        </is>
+      </c>
     </row>
     <row r="243">
-      <c r="B243" s="64" t="n"/>
-      <c r="C243" s="69" t="n"/>
-      <c r="D243" s="68" t="n"/>
-      <c r="E243" s="69" t="n"/>
-      <c r="F243" s="70" t="n"/>
-      <c r="G243" s="23" t="n"/>
-      <c r="H243" s="23" t="n"/>
-      <c r="I243" s="55" t="n"/>
+      <c r="B243" s="64" t="n">
+        <v>46182</v>
+      </c>
+      <c r="C243" s="69" t="inlineStr">
+        <is>
+          <t>Agua Natural — 3 bottles</t>
+        </is>
+      </c>
+      <c r="D243" s="68" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E243" s="69" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F243" s="70" t="n">
+        <v>45</v>
+      </c>
+      <c r="G243" s="23" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H243" s="23" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I243" s="55" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Logged retroactively (no receipt)</t>
+        </is>
+      </c>
     </row>
     <row r="244">
-      <c r="B244" s="64" t="n"/>
-      <c r="C244" s="65" t="n"/>
-      <c r="D244" s="66" t="n"/>
-      <c r="E244" s="65" t="n"/>
-      <c r="F244" s="67" t="n"/>
-      <c r="G244" s="14" t="n"/>
-      <c r="H244" s="14" t="n"/>
-      <c r="I244" s="43" t="n"/>
+      <c r="B244" s="64" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C244" s="65" t="inlineStr">
+        <is>
+          <t>Agua Natural — 2 bottles</t>
+        </is>
+      </c>
+      <c r="D244" s="66" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E244" s="65" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F244" s="67" t="n">
+        <v>30</v>
+      </c>
+      <c r="G244" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H244" s="14" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I244" s="43" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Logged retroactively (no receipt)</t>
+        </is>
+      </c>
     </row>
     <row r="245">
-      <c r="B245" s="64" t="n"/>
-      <c r="C245" s="69" t="n"/>
-      <c r="D245" s="68" t="n"/>
-      <c r="E245" s="69" t="n"/>
-      <c r="F245" s="70" t="n"/>
-      <c r="G245" s="23" t="n"/>
-      <c r="H245" s="23" t="n"/>
-      <c r="I245" s="55" t="n"/>
+      <c r="B245" s="64" t="n">
+        <v>46183</v>
+      </c>
+      <c r="C245" s="69" t="inlineStr">
+        <is>
+          <t>Pasta (caracol, codo, fusilli) + Roma detergent 1kg</t>
+        </is>
+      </c>
+      <c r="D245" s="68" t="inlineStr">
+        <is>
+          <t>Tiendas 3B (La Pradera)</t>
+        </is>
+      </c>
+      <c r="E245" s="69" t="inlineStr">
+        <is>
+          <t>Supermarket / General</t>
+        </is>
+      </c>
+      <c r="F245" s="70" t="n">
+        <v>252</v>
+      </c>
+      <c r="G245" s="23" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H245" s="23" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I245" s="55" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Ticket 188 · 19:25 · card Banco Plata **2684 · logged 11 Jun</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="B246" s="64" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -25,7 +25,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ ddd"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
@@ -36,6 +36,7 @@
     <numFmt numFmtId="171" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="172" formatCode="#,##0.##;\(#,##0.##\);&quot;-&quot;"/>
     <numFmt numFmtId="173" formatCode="#,##0;\-#,##0;\-"/>
+    <numFmt numFmtId="174" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="86">
     <font>
@@ -8286,17 +8287,46 @@
       <c r="Q32" s="44" t="n"/>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="274">
-      <c r="B33" s="34" t="n"/>
-      <c r="C33" s="47" t="n"/>
-      <c r="D33" s="48" t="n"/>
-      <c r="E33" s="49" t="n"/>
-      <c r="F33" s="50" t="n"/>
-      <c r="G33" s="51" t="n"/>
-      <c r="H33" s="52" t="n"/>
-      <c r="I33" s="53" t="n"/>
-      <c r="J33" s="54" t="n"/>
+      <c r="B33" s="34" t="inlineStr">
+        <is>
+          <t>12-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C33" s="47" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D33" s="48" t="n">
+        <v>2635</v>
+      </c>
+      <c r="E33" s="49" t="n">
+        <v>3435</v>
+      </c>
+      <c r="F33" s="50">
+        <f>IFERROR(D33+E33+G33,0)</f>
+        <v/>
+      </c>
+      <c r="G33" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="52" t="n">
+        <v>901.8</v>
+      </c>
+      <c r="I33" s="53">
+        <f>IFERROR(F33-H33,0)</f>
+        <v/>
+      </c>
+      <c r="J33" s="54">
+        <f>IFERROR(I33/F33,0)</f>
+        <v/>
+      </c>
       <c r="K33" s="55" t="n"/>
-      <c r="L33" s="18" t="n"/>
+      <c r="L33" s="18" t="inlineStr">
+        <is>
+          <t>Cierre 12 Jun + receipts</t>
+        </is>
+      </c>
       <c r="M33" s="21" t="n"/>
       <c r="N33" s="56" t="n"/>
       <c r="O33" s="57" t="n"/>
@@ -8304,17 +8334,46 @@
       <c r="Q33" s="56" t="n"/>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="274">
-      <c r="B34" s="34" t="n"/>
-      <c r="C34" s="35" t="n"/>
-      <c r="D34" s="36" t="n"/>
-      <c r="E34" s="37" t="n"/>
-      <c r="F34" s="38" t="n"/>
-      <c r="G34" s="39" t="n"/>
-      <c r="H34" s="40" t="n"/>
-      <c r="I34" s="41" t="n"/>
-      <c r="J34" s="42" t="n"/>
+      <c r="B34" s="34" t="inlineStr">
+        <is>
+          <t>13-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C34" s="35" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D34" s="36" t="n">
+        <v>1005</v>
+      </c>
+      <c r="E34" s="37" t="n">
+        <v>806</v>
+      </c>
+      <c r="F34" s="38">
+        <f>IFERROR(D34+E34+G34,0)</f>
+        <v/>
+      </c>
+      <c r="G34" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="40" t="n">
+        <v>778.16</v>
+      </c>
+      <c r="I34" s="41">
+        <f>IFERROR(F34-H34,0)</f>
+        <v/>
+      </c>
+      <c r="J34" s="42">
+        <f>IFERROR(I34/F34,0)</f>
+        <v/>
+      </c>
       <c r="K34" s="43" t="n"/>
-      <c r="L34" s="9" t="n"/>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>Cierre 13 Jun + receipts</t>
+        </is>
+      </c>
       <c r="M34" s="12" t="n"/>
       <c r="N34" s="44" t="n"/>
       <c r="O34" s="45" t="n"/>
@@ -14407,9 +14466,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -24298,7 +24357,7 @@
       </c>
       <c r="G241" s="23" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Lohith (Personal)</t>
         </is>
       </c>
       <c r="H241" s="23" t="inlineStr">
@@ -24313,7 +24372,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Paid cash exact $2,865 · 08:22 AM</t>
+          <t>Paid cash exact $2,865 · 08:22 AM | Paid personally by Lohith (transfer) — reimburse</t>
         </is>
       </c>
     </row>
@@ -24341,7 +24400,7 @@
       </c>
       <c r="G242" s="14" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Lohith (Personal)</t>
         </is>
       </c>
       <c r="H242" s="14" t="inlineStr">
@@ -24356,7 +24415,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Pink nota "Oh Lele" · marked Cobrado</t>
+          <t>Pink nota "Oh Lele" · marked Cobrado | Paid personally by Lohith (transfer) — reimburse</t>
         </is>
       </c>
     </row>
@@ -24490,74 +24549,305 @@
       </c>
     </row>
     <row r="246">
-      <c r="B246" s="64" t="n"/>
-      <c r="C246" s="65" t="n"/>
-      <c r="D246" s="66" t="n"/>
-      <c r="E246" s="65" t="n"/>
-      <c r="F246" s="67" t="n"/>
-      <c r="G246" s="14" t="n"/>
-      <c r="H246" s="14" t="n"/>
-      <c r="I246" s="43" t="n"/>
+      <c r="B246" s="64" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C246" s="65" t="inlineStr">
+        <is>
+          <t>Leche PL UHT Nutri 1LT (2 pcs)</t>
+        </is>
+      </c>
+      <c r="D246" s="66" t="inlineStr">
+        <is>
+          <t>OXXO Acueducto</t>
+        </is>
+      </c>
+      <c r="E246" s="65" t="inlineStr">
+        <is>
+          <t>Ingredients - Dairy</t>
+        </is>
+      </c>
+      <c r="F246" s="67" t="n">
+        <v>42</v>
+      </c>
+      <c r="G246" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H246" s="14" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I246" s="43" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>ML debit **3982 · Aut 324051 · 10:13</t>
+        </is>
+      </c>
     </row>
     <row r="247">
-      <c r="B247" s="64" t="n"/>
-      <c r="C247" s="69" t="n"/>
-      <c r="D247" s="68" t="n"/>
-      <c r="E247" s="69" t="n"/>
-      <c r="F247" s="70" t="n"/>
-      <c r="G247" s="23" t="n"/>
-      <c r="H247" s="23" t="n"/>
-      <c r="I247" s="55" t="n"/>
+      <c r="B247" s="64" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C247" s="69" t="inlineStr">
+        <is>
+          <t>Pan hamburguesa ajonjolí (36) + Chapata grande (24)</t>
+        </is>
+      </c>
+      <c r="D247" s="68" t="inlineStr">
+        <is>
+          <t>Productos Real (La Cruz)</t>
+        </is>
+      </c>
+      <c r="E247" s="69" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F247" s="70" t="n">
+        <v>546</v>
+      </c>
+      <c r="G247" s="23" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H247" s="23" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I247" s="55" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Folio 4251 · debit · 09:38</t>
+        </is>
+      </c>
     </row>
     <row r="248">
-      <c r="B248" s="64" t="n"/>
-      <c r="C248" s="65" t="n"/>
-      <c r="D248" s="66" t="n"/>
-      <c r="E248" s="65" t="n"/>
-      <c r="F248" s="67" t="n"/>
-      <c r="G248" s="14" t="n"/>
-      <c r="H248" s="14" t="n"/>
-      <c r="I248" s="43" t="n"/>
+      <c r="B248" s="64" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C248" s="65" t="inlineStr">
+        <is>
+          <t>Aceite Vegetal La Posada 800 (2 pcs)</t>
+        </is>
+      </c>
+      <c r="D248" s="66" t="inlineStr">
+        <is>
+          <t>OXXO Pathe</t>
+        </is>
+      </c>
+      <c r="E248" s="65" t="inlineStr">
+        <is>
+          <t>Ingredients - Other</t>
+        </is>
+      </c>
+      <c r="F248" s="67" t="n">
+        <v>104</v>
+      </c>
+      <c r="G248" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H248" s="14" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I248" s="43" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>ML debit **3982 · Aut 468013 · 09:22</t>
+        </is>
+      </c>
     </row>
     <row r="249">
-      <c r="B249" s="64" t="n"/>
-      <c r="C249" s="69" t="n"/>
-      <c r="D249" s="68" t="n"/>
-      <c r="E249" s="69" t="n"/>
-      <c r="F249" s="70" t="n"/>
-      <c r="G249" s="23" t="n"/>
-      <c r="H249" s="23" t="n"/>
-      <c r="I249" s="55" t="n"/>
+      <c r="B249" s="64" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C249" s="69" t="inlineStr">
+        <is>
+          <t>Plátano + Tortillas Blancas + Rosca Marmoleada</t>
+        </is>
+      </c>
+      <c r="D249" s="68" t="inlineStr">
+        <is>
+          <t>Chedraui Paseo</t>
+        </is>
+      </c>
+      <c r="E249" s="69" t="inlineStr">
+        <is>
+          <t>Supermarket / General</t>
+        </is>
+      </c>
+      <c r="F249" s="70" t="n">
+        <v>161.8</v>
+      </c>
+      <c r="G249" s="23" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H249" s="23" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I249" s="55" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Debit BBVA **3982 · Aut 200580 · 09:02</t>
+        </is>
+      </c>
     </row>
     <row r="250">
-      <c r="B250" s="64" t="n"/>
-      <c r="C250" s="65" t="n"/>
-      <c r="D250" s="66" t="n"/>
-      <c r="E250" s="65" t="n"/>
-      <c r="F250" s="67" t="n"/>
-      <c r="G250" s="14" t="n"/>
-      <c r="H250" s="14" t="n"/>
-      <c r="I250" s="43" t="n"/>
+      <c r="B250" s="64" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C250" s="65" t="inlineStr">
+        <is>
+          <t>Lechugas (lettuce)</t>
+        </is>
+      </c>
+      <c r="D250" s="66" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E250" s="65" t="inlineStr">
+        <is>
+          <t>Ingredients - Produce</t>
+        </is>
+      </c>
+      <c r="F250" s="67" t="n">
+        <v>48</v>
+      </c>
+      <c r="G250" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H250" s="14" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I250" s="43" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>No receipt — logged manually</t>
+        </is>
+      </c>
     </row>
     <row r="251">
-      <c r="B251" s="64" t="n"/>
-      <c r="C251" s="69" t="n"/>
-      <c r="D251" s="68" t="n"/>
-      <c r="E251" s="69" t="n"/>
-      <c r="F251" s="70" t="n"/>
-      <c r="G251" s="23" t="n"/>
-      <c r="H251" s="23" t="n"/>
-      <c r="I251" s="55" t="n"/>
+      <c r="B251" s="64" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C251" s="69" t="inlineStr">
+        <is>
+          <t>Empanizador Bimbo, especias, tomate, pimiento verde, papa, mole, tortillas (14 art.)</t>
+        </is>
+      </c>
+      <c r="D251" s="68" t="inlineStr">
+        <is>
+          <t>Chedraui Paseo</t>
+        </is>
+      </c>
+      <c r="E251" s="69" t="inlineStr">
+        <is>
+          <t>Supermarket / General</t>
+        </is>
+      </c>
+      <c r="F251" s="70" t="n">
+        <v>468.16</v>
+      </c>
+      <c r="G251" s="23" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H251" s="23" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I251" s="55" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>Debit BBVA **3982 · Aut 641502 · 09:19 · Folio 2606-1309-1901</t>
+        </is>
+      </c>
     </row>
     <row r="252">
-      <c r="B252" s="64" t="n"/>
-      <c r="C252" s="65" t="n"/>
-      <c r="D252" s="66" t="n"/>
-      <c r="E252" s="65" t="n"/>
-      <c r="F252" s="67" t="n"/>
-      <c r="G252" s="14" t="n"/>
-      <c r="H252" s="14" t="n"/>
-      <c r="I252" s="43" t="n"/>
+      <c r="B252" s="64" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C252" s="65" t="inlineStr">
+        <is>
+          <t>Bistec de Cerdo 1.66 kg</t>
+        </is>
+      </c>
+      <c r="D252" s="66" t="inlineStr">
+        <is>
+          <t>Carnicería (nota de remisión)</t>
+        </is>
+      </c>
+      <c r="E252" s="65" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F252" s="67" t="n">
+        <v>310</v>
+      </c>
+      <c r="G252" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H252" s="14" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I252" s="43" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>Handwritten remisión · 1.66 kg · total $310</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="B253" s="64" t="n"/>
@@ -30742,7 +31032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="18.33203125" customWidth="1" style="274" min="1" max="1"/>
@@ -32441,62 +32731,99 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="226" t="inlineStr">
+      <c r="A74" s="265" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B74" s="266" t="inlineStr">
+        <is>
+          <t>ALICO — Ala de Pollo, Papa Harvest 13.62kg, Boneless Freskecito</t>
+        </is>
+      </c>
+      <c r="C74" s="267" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D74" s="268" t="n">
+        <v>2865</v>
+      </c>
+      <c r="F74" s="269">
+        <f>IFERROR(F73+D74-E74,0)</f>
+        <v/>
+      </c>
+      <c r="G74" s="266" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H74" s="242" t="inlineStr">
+        <is>
+          <t>Restaurant ingredients paid personally by Lohith (transfer) — 11 Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="265" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B75" s="266" t="inlineStr">
+        <is>
+          <t>Pollería — Muslo de Pollo 4.70 kg</t>
+        </is>
+      </c>
+      <c r="C75" s="267" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D75" s="268" t="n">
+        <v>235</v>
+      </c>
+      <c r="F75" s="269">
+        <f>IFERROR(F74+D75-E75,0)</f>
+        <v/>
+      </c>
+      <c r="G75" s="266" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H75" s="242" t="inlineStr">
+        <is>
+          <t>Restaurant ingredients paid personally by Lohith (transfer) — 11 Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="226" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B74" s="219" t="n"/>
-      <c r="C74" s="219" t="n"/>
-      <c r="D74" s="256">
-        <f>SUM(D63:D73)</f>
-        <v/>
-      </c>
-      <c r="E74" s="257">
-        <f>SUM(E63:E73)</f>
-        <v/>
-      </c>
-      <c r="F74" s="258">
-        <f>F73</f>
-        <v/>
-      </c>
-      <c r="G74" s="226">
-        <f>IF(F73&gt;0,"⏳ Restaurant owes Lohith $"&amp;TEXT(F73,"#,##0"),IF(F73&lt;0,"💵 Lohith holds $"&amp;TEXT(ABS(F73),"#,##0"),"✅ Zero balance"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="242" t="inlineStr">
-        <is>
-          <t>HOW TO USE:</t>
-        </is>
-      </c>
-      <c r="B76" s="242" t="n"/>
-      <c r="C76" s="242" t="n"/>
-      <c r="D76" s="242" t="n"/>
-      <c r="E76" s="242" t="n"/>
-      <c r="F76" s="242" t="n"/>
-      <c r="G76" s="242" t="n"/>
-      <c r="H76" s="242" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="242" t="inlineStr">
-        <is>
-          <t>Add new rows above TOTALS. Spent by Lohith = restaurant expenses he paid personally.</t>
-        </is>
-      </c>
-      <c r="B77" s="242" t="n"/>
-      <c r="C77" s="242" t="n"/>
-      <c r="D77" s="242" t="n"/>
-      <c r="E77" s="242" t="n"/>
-      <c r="F77" s="242" t="n"/>
-      <c r="G77" s="242" t="n"/>
-      <c r="H77" s="242" t="n"/>
-    </row>
+      <c r="B76" s="219" t="n"/>
+      <c r="C76" s="219" t="n"/>
+      <c r="D76" s="256">
+        <f>SUM(D63:D75)</f>
+        <v/>
+      </c>
+      <c r="E76" s="257">
+        <f>SUM(E63:E75)</f>
+        <v/>
+      </c>
+      <c r="F76" s="258">
+        <f>F75</f>
+        <v/>
+      </c>
+      <c r="G76" s="226">
+        <f>IF(F75&gt;0,"⏳ Restaurant owes Lohith $"&amp;TEXT(F75,"#,##0"),IF(F75&lt;0,"💵 Lohith holds $"&amp;TEXT(ABS(F75),"#,##0"),"✅ Zero balance"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77"/>
     <row r="78">
       <c r="A78" s="242" t="inlineStr">
         <is>
-          <t>Transferred to Lohith = customer bank transfers received in his personal account.</t>
+          <t>HOW TO USE:</t>
         </is>
       </c>
       <c r="B78" s="242" t="n"/>
@@ -32510,7 +32837,7 @@
     <row r="79">
       <c r="A79" s="242" t="inlineStr">
         <is>
-          <t>Positive balance = restaurant owes Lohith. Negative = Lohith holds restaurant funds.</t>
+          <t>Add new rows above TOTALS. Spent by Lohith = restaurant expenses he paid personally.</t>
         </is>
       </c>
       <c r="B79" s="242" t="n"/>
@@ -32520,6 +32847,34 @@
       <c r="F79" s="242" t="n"/>
       <c r="G79" s="242" t="n"/>
       <c r="H79" s="242" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="242" t="inlineStr">
+        <is>
+          <t>Transferred to Lohith = customer bank transfers received in his personal account.</t>
+        </is>
+      </c>
+      <c r="B80" s="242" t="n"/>
+      <c r="C80" s="242" t="n"/>
+      <c r="D80" s="242" t="n"/>
+      <c r="E80" s="242" t="n"/>
+      <c r="F80" s="242" t="n"/>
+      <c r="G80" s="242" t="n"/>
+      <c r="H80" s="242" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="242" t="inlineStr">
+        <is>
+          <t>Positive balance = restaurant owes Lohith. Negative = Lohith holds restaurant funds.</t>
+        </is>
+      </c>
+      <c r="B81" s="242" t="n"/>
+      <c r="C81" s="242" t="n"/>
+      <c r="D81" s="242" t="n"/>
+      <c r="E81" s="242" t="n"/>
+      <c r="F81" s="242" t="n"/>
+      <c r="G81" s="242" t="n"/>
+      <c r="H81" s="242" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -17,6 +17,7 @@
     <sheet name="📈 Monthly P&amp;L" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="📥 Pending Income" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="📊 Weekly Closing" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="💰 Owner Ledger" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -38,7 +39,7 @@
     <numFmt numFmtId="173" formatCode="#,##0;\-#,##0;\-"/>
     <numFmt numFmtId="174" formatCode="dd-mmm-yyyy"/>
   </numFmts>
-  <fonts count="86">
+  <fonts count="90">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -586,8 +587,25 @@
       <color rgb="FF555555"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="52">
+  <fills count="55">
     <fill>
       <patternFill/>
     </fill>
@@ -881,8 +899,23 @@
         <fgColor rgb="FFFFCDD2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000D2818"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E2C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F0E8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1100,11 +1133,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="356">
+  <cellXfs count="365">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2005,6 +2066,21 @@
     <xf numFmtId="174" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="37" fillId="19" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="53" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="54" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="88" fillId="54" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5212,6 +5288,796 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="274" min="1" max="1"/>
+    <col width="46" customWidth="1" style="274" min="2" max="2"/>
+    <col width="18" customWidth="1" style="274" min="3" max="3"/>
+    <col width="18" customWidth="1" style="274" min="4" max="4"/>
+    <col width="22" customWidth="1" style="274" min="5" max="5"/>
+    <col width="18" customWidth="1" style="274" min="6" max="6"/>
+    <col width="22" customWidth="1" style="274" min="7" max="7"/>
+    <col width="40" customWidth="1" style="274" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" s="274">
+      <c r="A1" s="357" t="inlineStr">
+        <is>
+          <t>LOHITH — OWNER LEDGER &amp; PERSONAL BALANCE TRACKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="274">
+      <c r="A3" s="358" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B3" s="358" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C3" s="358" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D3" s="358" t="inlineStr">
+        <is>
+          <t>Spent by Lohith ($)</t>
+        </is>
+      </c>
+      <c r="E3" s="358" t="inlineStr">
+        <is>
+          <t>Transferred to Lohith ($)</t>
+        </is>
+      </c>
+      <c r="F3" s="358" t="inlineStr">
+        <is>
+          <t>Running Balance ($)</t>
+        </is>
+      </c>
+      <c r="G3" s="358" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H3" s="358" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="359" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B4" s="360" t="inlineStr">
+        <is>
+          <t>Telmex Internet Bill (Mayo)</t>
+        </is>
+      </c>
+      <c r="C4" s="360" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D4" s="361" t="n">
+        <v>349</v>
+      </c>
+      <c r="E4" s="360" t="n"/>
+      <c r="F4" s="361">
+        <f>IFERROR(D4-E4,0)</f>
+        <v/>
+      </c>
+      <c r="G4" s="360" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H4" s="360" t="inlineStr">
+        <is>
+          <t>Paid by Lohith — ⏳ Reimburse</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="359" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B5" s="360" t="inlineStr">
+        <is>
+          <t>Customer Transfer — Jun 1</t>
+        </is>
+      </c>
+      <c r="C5" s="360" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D5" s="360" t="n"/>
+      <c r="E5" s="361" t="n">
+        <v>310</v>
+      </c>
+      <c r="F5" s="361">
+        <f>IFERROR(F4+D5-E5,0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="360" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H5" s="360" t="inlineStr">
+        <is>
+          <t>✅ Received in Lohith account</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="359" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B6" s="360" t="inlineStr">
+        <is>
+          <t>Customer Transfer — Jun 2</t>
+        </is>
+      </c>
+      <c r="C6" s="360" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D6" s="360" t="n"/>
+      <c r="E6" s="361" t="n">
+        <v>283</v>
+      </c>
+      <c r="F6" s="361">
+        <f>IFERROR(F5+D6-E6,0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="360" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H6" s="360" t="inlineStr">
+        <is>
+          <t>✅ Received in Lohith account</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="359" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B7" s="360" t="inlineStr">
+        <is>
+          <t>Customer Transfer — Jun 3</t>
+        </is>
+      </c>
+      <c r="C7" s="360" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D7" s="360" t="n"/>
+      <c r="E7" s="361" t="n">
+        <v>120</v>
+      </c>
+      <c r="F7" s="361">
+        <f>IFERROR(F6+D7-E7,0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="360" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H7" s="360" t="inlineStr">
+        <is>
+          <t>✅ Received in Lohith account</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="359" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B8" s="360" t="inlineStr">
+        <is>
+          <t>Personal expenses — Huevos, Ajonjoli, Verduras</t>
+        </is>
+      </c>
+      <c r="C8" s="360" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D8" s="361" t="n">
+        <v>358</v>
+      </c>
+      <c r="E8" s="360" t="n"/>
+      <c r="F8" s="361">
+        <f>IFERROR(F7+D8-E8,0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="360" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H8" s="360" t="inlineStr">
+        <is>
+          <t>$69 Huevos + $44 Ajonjoli Blanco + $45 Ajonjoli Negro + $200 Verduras</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="359" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B9" s="360" t="inlineStr">
+        <is>
+          <t>Cash settlement — $6 added to restaurant</t>
+        </is>
+      </c>
+      <c r="C9" s="360" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D9" s="361" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="360" t="n"/>
+      <c r="F9" s="361">
+        <f>IFERROR(F8+D9-E9,0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="360" t="inlineStr">
+        <is>
+          <t>✅ Settled</t>
+        </is>
+      </c>
+      <c r="H9" s="360" t="inlineStr">
+        <is>
+          <t>Lohith added $6 cash to restaurant — balance now ZERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="359" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B10" s="360" t="inlineStr">
+        <is>
+          <t>Customer Transfer — Jun 5</t>
+        </is>
+      </c>
+      <c r="C10" s="360" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D10" s="360" t="n"/>
+      <c r="E10" s="361" t="n">
+        <v>135</v>
+      </c>
+      <c r="F10" s="361">
+        <f>IFERROR(F9+D10-E10,0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="360" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H10" s="360" t="inlineStr">
+        <is>
+          <t>✅ Received in Lohith account — Jun 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="359" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B11" s="360" t="inlineStr">
+        <is>
+          <t>Renta + Mantenimiento Junio 2026</t>
+        </is>
+      </c>
+      <c r="C11" s="360" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D11" s="361" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E11" s="360" t="n"/>
+      <c r="F11" s="361">
+        <f>IFERROR(F10+D11-E11,0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="360" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H11" s="360" t="inlineStr">
+        <is>
+          <t>Rent $15,000 + Maintenance $5,000 — paid personally by Lohith on 4 Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="359" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B12" s="360" t="inlineStr">
+        <is>
+          <t>Customer Transfer — Jun 8</t>
+        </is>
+      </c>
+      <c r="C12" s="360" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D12" s="360" t="n"/>
+      <c r="E12" s="361" t="n">
+        <v>99</v>
+      </c>
+      <c r="F12" s="361">
+        <f>IFERROR(F11+D12-E12,0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="360" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H12" s="360" t="inlineStr">
+        <is>
+          <t>✅ Received in Lohith account — Jun 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="359" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B13" s="360" t="inlineStr">
+        <is>
+          <t>Chedraui Paseo — Groceries (elote, chile, tomate, tortillas, bolillo)</t>
+        </is>
+      </c>
+      <c r="C13" s="360" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D13" s="361" t="n">
+        <v>236.81</v>
+      </c>
+      <c r="E13" s="360" t="n"/>
+      <c r="F13" s="361">
+        <f>IFERROR(F12+D13-E13,0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="360" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H13" s="360" t="inlineStr">
+        <is>
+          <t>Paid personally by Lohith — HSBC **5543</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="359" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B14" s="360" t="inlineStr">
+        <is>
+          <t>Office Depot — Comanda Restaurante</t>
+        </is>
+      </c>
+      <c r="C14" s="360" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D14" s="361" t="n">
+        <v>59</v>
+      </c>
+      <c r="E14" s="360" t="n"/>
+      <c r="F14" s="361">
+        <f>IFERROR(F13+D14-E14,0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="360" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H14" s="360" t="inlineStr">
+        <is>
+          <t>Paid personally by Lohith — MC **5543</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="359" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B15" s="360" t="inlineStr">
+        <is>
+          <t>ALICO — Ala de Pollo, Papa Harvest 13.62kg, Boneless Freskecito</t>
+        </is>
+      </c>
+      <c r="C15" s="360" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D15" s="361" t="n">
+        <v>2865</v>
+      </c>
+      <c r="E15" s="360" t="n"/>
+      <c r="F15" s="361">
+        <f>IFERROR(F14+D15-E15,0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="360" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H15" s="360" t="inlineStr">
+        <is>
+          <t>Restaurant ingredients paid personally by Lohith (transfer) — 11 Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="359" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B16" s="360" t="inlineStr">
+        <is>
+          <t>Pollería — Muslo de Pollo 4.70 kg</t>
+        </is>
+      </c>
+      <c r="C16" s="360" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D16" s="361" t="n">
+        <v>235</v>
+      </c>
+      <c r="E16" s="360" t="n"/>
+      <c r="F16" s="361">
+        <f>IFERROR(F15+D16-E16,0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="360" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H16" s="360" t="inlineStr">
+        <is>
+          <t>Restaurant ingredients paid personally by Lohith (transfer) — 11 Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="359" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B17" s="360" t="inlineStr">
+        <is>
+          <t>Chedraui — Tortillas, Bolillo, Rosca de Nuez</t>
+        </is>
+      </c>
+      <c r="C17" s="360" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D17" s="361" t="n">
+        <v>160.33</v>
+      </c>
+      <c r="E17" s="360" t="n"/>
+      <c r="F17" s="361">
+        <f>IFERROR(F16+D17-E17,0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="360" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H17" s="360" t="inlineStr">
+        <is>
+          <t>HSBC **5543 — paid by Lohith 15 Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="359" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B18" s="360" t="inlineStr">
+        <is>
+          <t>OXXO Pathe — Aceite Vegetal (2)</t>
+        </is>
+      </c>
+      <c r="C18" s="360" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D18" s="361" t="n">
+        <v>104</v>
+      </c>
+      <c r="E18" s="360" t="n"/>
+      <c r="F18" s="361">
+        <f>IFERROR(F17+D18-E18,0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="360" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H18" s="360" t="inlineStr">
+        <is>
+          <t>HSBC **5543 — paid by Lohith 15 Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="359" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B19" s="360" t="inlineStr">
+        <is>
+          <t>Miscelánea LC — Ribeye, Chuleta, Bistec</t>
+        </is>
+      </c>
+      <c r="C19" s="360" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D19" s="361" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E19" s="360" t="n"/>
+      <c r="F19" s="361">
+        <f>IFERROR(F18+D19-E19,0)</f>
+        <v/>
+      </c>
+      <c r="G19" s="360" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H19" s="360" t="inlineStr">
+        <is>
+          <t>HSBC **5543 — paid by Lohith 15 Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="359" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B20" s="360" t="inlineStr">
+        <is>
+          <t>Transfer from Restaurant account</t>
+        </is>
+      </c>
+      <c r="C20" s="360" t="inlineStr">
+        <is>
+          <t>Reimbursement</t>
+        </is>
+      </c>
+      <c r="D20" s="360" t="n"/>
+      <c r="E20" s="361" t="n">
+        <v>3162</v>
+      </c>
+      <c r="F20" s="361">
+        <f>IFERROR(F19+D20-E20,0)</f>
+        <v/>
+      </c>
+      <c r="G20" s="360" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H20" s="360" t="inlineStr">
+        <is>
+          <t>Bank transfer to Lohith</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="359" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B21" s="360" t="inlineStr">
+        <is>
+          <t>15 Jun card expenses reimbursed (Chedraui+OXXO+Miscelánea)</t>
+        </is>
+      </c>
+      <c r="C21" s="360" t="inlineStr">
+        <is>
+          <t>Reimbursement</t>
+        </is>
+      </c>
+      <c r="D21" s="360" t="n"/>
+      <c r="E21" s="361" t="n">
+        <v>1279.33</v>
+      </c>
+      <c r="F21" s="361">
+        <f>IFERROR(F20+D21-E21,0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="360" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H21" s="360" t="inlineStr">
+        <is>
+          <t>HSBC **5543 items repaid same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="359" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B22" s="360" t="inlineStr">
+        <is>
+          <t>OXXO Pathe — Leche Lala UHT (2)</t>
+        </is>
+      </c>
+      <c r="C22" s="360" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D22" s="361" t="n">
+        <v>93</v>
+      </c>
+      <c r="E22" s="360" t="n"/>
+      <c r="F22" s="361">
+        <f>IFERROR(F21+D22-E22,0)</f>
+        <v/>
+      </c>
+      <c r="G22" s="360" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H22" s="360" t="inlineStr">
+        <is>
+          <t>HSBC **5543 — paid by Lohith 16 Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="359" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B23" s="360" t="inlineStr">
+        <is>
+          <t>16 Jun OXXO card expense reimbursed</t>
+        </is>
+      </c>
+      <c r="C23" s="360" t="inlineStr">
+        <is>
+          <t>Reimbursement</t>
+        </is>
+      </c>
+      <c r="D23" s="360" t="n"/>
+      <c r="E23" s="361" t="n">
+        <v>93</v>
+      </c>
+      <c r="F23" s="361">
+        <f>IFERROR(F22+D23-E23,0)</f>
+        <v/>
+      </c>
+      <c r="G23" s="360" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H23" s="360" t="inlineStr">
+        <is>
+          <t>HSBC **5543 item repaid same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="362" t="inlineStr">
+        <is>
+          <t>TOTALS &amp; CURRENT BALANCE</t>
+        </is>
+      </c>
+      <c r="B24" s="362" t="n"/>
+      <c r="C24" s="362" t="n"/>
+      <c r="D24" s="363">
+        <f>SUM(D4:D23)</f>
+        <v/>
+      </c>
+      <c r="E24" s="363">
+        <f>SUM(E4:E23)</f>
+        <v/>
+      </c>
+      <c r="F24" s="363">
+        <f>F23</f>
+        <v/>
+      </c>
+      <c r="G24" s="362">
+        <f>IF(F23&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F23,"#,##0"),IF(F23&lt;0,"Lohith holds $"&amp;TEXT(ABS(F23),"#,##0"),"Zero balance"))</f>
+        <v/>
+      </c>
+      <c r="H24" s="362" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="364" t="inlineStr">
+        <is>
+          <t>HOW TO USE:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Add new rows ABOVE the TOTALS row. Spent by Lohith = restaurant costs he paid personally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Transferred to Lohith = transfers/reimbursements received in his account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Positive balance = restaurant owes Lohith. This sheet is the single source for the owner balance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7156,10 +8022,8 @@
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" s="274">
-      <c r="B8" s="34" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
+      <c r="B8" s="356" t="n">
+        <v>46160</v>
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
@@ -7177,8 +8041,9 @@
         <v/>
       </c>
       <c r="G8" s="39" t="n"/>
-      <c r="H8" s="40" t="n">
-        <v>2629</v>
+      <c r="H8" s="40">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B8,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B8+1))</f>
+        <v/>
       </c>
       <c r="I8" s="41">
         <f>IFERROR(F8-H8,0)</f>
@@ -7201,10 +8066,8 @@
       <c r="Q8" s="44" t="n"/>
     </row>
     <row r="9" ht="16.5" customHeight="1" s="274">
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
+      <c r="B9" s="356" t="n">
+        <v>46161</v>
       </c>
       <c r="C9" s="47" t="inlineStr">
         <is>
@@ -7222,8 +8085,9 @@
         <v/>
       </c>
       <c r="G9" s="51" t="n"/>
-      <c r="H9" s="52" t="n">
-        <v>30</v>
+      <c r="H9" s="52">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B9,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B9+1))</f>
+        <v/>
       </c>
       <c r="I9" s="53">
         <f>IFERROR(F9-H9,0)</f>
@@ -7246,10 +8110,8 @@
       <c r="Q9" s="56" t="n"/>
     </row>
     <row r="10" ht="16.5" customHeight="1" s="274">
-      <c r="B10" s="34" t="inlineStr">
-        <is>
-          <t>20-May-2026</t>
-        </is>
+      <c r="B10" s="356" t="n">
+        <v>46162</v>
       </c>
       <c r="C10" s="35" t="inlineStr">
         <is>
@@ -7267,8 +8129,9 @@
         <v/>
       </c>
       <c r="G10" s="39" t="n"/>
-      <c r="H10" s="40" t="n">
-        <v>3777</v>
+      <c r="H10" s="40">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B10,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B10+1))</f>
+        <v/>
       </c>
       <c r="I10" s="41">
         <f>IFERROR(F10-H10,0)</f>
@@ -7291,10 +8154,8 @@
       <c r="Q10" s="44" t="n"/>
     </row>
     <row r="11" ht="16.5" customHeight="1" s="274">
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>21-May-2026</t>
-        </is>
+      <c r="B11" s="356" t="n">
+        <v>46163</v>
       </c>
       <c r="C11" s="47" t="inlineStr">
         <is>
@@ -7312,8 +8173,9 @@
         <v/>
       </c>
       <c r="G11" s="51" t="n"/>
-      <c r="H11" s="52" t="n">
-        <v>2434</v>
+      <c r="H11" s="52">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B11,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B11+1))</f>
+        <v/>
       </c>
       <c r="I11" s="53">
         <f>IFERROR(F11-H11,0)</f>
@@ -7336,10 +8198,8 @@
       <c r="Q11" s="56" t="n"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="274">
-      <c r="B12" s="34" t="inlineStr">
-        <is>
-          <t>22-May-2026</t>
-        </is>
+      <c r="B12" s="356" t="n">
+        <v>46164</v>
       </c>
       <c r="C12" s="35" t="inlineStr">
         <is>
@@ -7357,8 +8217,9 @@
         <v/>
       </c>
       <c r="G12" s="39" t="n"/>
-      <c r="H12" s="40" t="n">
-        <v>1457</v>
+      <c r="H12" s="40">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B12,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B12+1))</f>
+        <v/>
       </c>
       <c r="I12" s="41">
         <f>IFERROR(F12-H12,0)</f>
@@ -7381,10 +8242,8 @@
       <c r="Q12" s="44" t="n"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="274">
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>23-May-2026</t>
-        </is>
+      <c r="B13" s="356" t="n">
+        <v>46165</v>
       </c>
       <c r="C13" s="47" t="inlineStr">
         <is>
@@ -7402,8 +8261,9 @@
         <v/>
       </c>
       <c r="G13" s="51" t="n"/>
-      <c r="H13" s="52" t="n">
-        <v>7755.43</v>
+      <c r="H13" s="52">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B13,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B13+1))</f>
+        <v/>
       </c>
       <c r="I13" s="53">
         <f>IFERROR(F13-H13,0)</f>
@@ -7430,10 +8290,8 @@
       <c r="Q13" s="56" t="n"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="274">
-      <c r="B14" s="34" t="inlineStr">
-        <is>
-          <t>24-May-2026</t>
-        </is>
+      <c r="B14" s="356" t="n">
+        <v>46166</v>
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
@@ -7449,8 +8307,9 @@
         <v/>
       </c>
       <c r="G14" s="39" t="n"/>
-      <c r="H14" s="40" t="n">
-        <v>1076</v>
+      <c r="H14" s="40">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B14,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B14+1))</f>
+        <v/>
       </c>
       <c r="I14" s="41">
         <f>IFERROR(F14-H14,0)</f>
@@ -7477,10 +8336,8 @@
       <c r="Q14" s="44" t="n"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="274">
-      <c r="B15" s="34" t="inlineStr">
-        <is>
-          <t>25-May-2026</t>
-        </is>
+      <c r="B15" s="356" t="n">
+        <v>46167</v>
       </c>
       <c r="C15" s="47" t="inlineStr">
         <is>
@@ -7498,8 +8355,9 @@
         <v/>
       </c>
       <c r="G15" s="51" t="n"/>
-      <c r="H15" s="52" t="n">
-        <v>3021.45</v>
+      <c r="H15" s="52">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B15,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B15+1))</f>
+        <v/>
       </c>
       <c r="I15" s="53">
         <f>IFERROR(F15-H15,0)</f>
@@ -7522,10 +8380,8 @@
       <c r="Q15" s="56" t="n"/>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="274">
-      <c r="B16" s="34" t="inlineStr">
-        <is>
-          <t>26-May-2026</t>
-        </is>
+      <c r="B16" s="356" t="n">
+        <v>46168</v>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
@@ -7543,8 +8399,9 @@
         <v/>
       </c>
       <c r="G16" s="39" t="n"/>
-      <c r="H16" s="40" t="n">
-        <v>1191.6</v>
+      <c r="H16" s="40">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B16,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B16+1))</f>
+        <v/>
       </c>
       <c r="I16" s="41">
         <f>IFERROR(F16-H16,0)</f>
@@ -7567,10 +8424,8 @@
       <c r="Q16" s="44" t="n"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="274">
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>27-May-2026</t>
-        </is>
+      <c r="B17" s="356" t="n">
+        <v>46169</v>
       </c>
       <c r="C17" s="47" t="inlineStr">
         <is>
@@ -7588,8 +8443,9 @@
         <v/>
       </c>
       <c r="G17" s="51" t="n"/>
-      <c r="H17" s="52" t="n">
-        <v>1073.22</v>
+      <c r="H17" s="52">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B17,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B17+1))</f>
+        <v/>
       </c>
       <c r="I17" s="53">
         <f>IFERROR(F17-H17,0)</f>
@@ -7612,10 +8468,8 @@
       <c r="Q17" s="56" t="n"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="274">
-      <c r="B18" s="34" t="inlineStr">
-        <is>
-          <t>28-May-2026</t>
-        </is>
+      <c r="B18" s="356" t="n">
+        <v>46170</v>
       </c>
       <c r="C18" s="35" t="inlineStr">
         <is>
@@ -7633,8 +8487,9 @@
         <v/>
       </c>
       <c r="G18" s="39" t="n"/>
-      <c r="H18" s="40" t="n">
-        <v>1931.34</v>
+      <c r="H18" s="40">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B18,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B18+1))</f>
+        <v/>
       </c>
       <c r="I18" s="41">
         <f>IFERROR(F18-H18,0)</f>
@@ -7657,10 +8512,8 @@
       <c r="Q18" s="44" t="n"/>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="274">
-      <c r="B19" s="34" t="inlineStr">
-        <is>
-          <t>29-May-2026</t>
-        </is>
+      <c r="B19" s="356" t="n">
+        <v>46171</v>
       </c>
       <c r="C19" s="47" t="inlineStr">
         <is>
@@ -7678,8 +8531,9 @@
         <v/>
       </c>
       <c r="G19" s="51" t="n"/>
-      <c r="H19" s="52" t="n">
-        <v>257.29</v>
+      <c r="H19" s="52">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B19,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B19+1))</f>
+        <v/>
       </c>
       <c r="I19" s="53">
         <f>IFERROR(F19-H19,0)</f>
@@ -7702,10 +8556,8 @@
       <c r="Q19" s="56" t="n"/>
     </row>
     <row r="20" ht="16.5" customHeight="1" s="274">
-      <c r="B20" s="34" t="inlineStr">
-        <is>
-          <t>30-May-2026</t>
-        </is>
+      <c r="B20" s="356" t="n">
+        <v>46172</v>
       </c>
       <c r="C20" s="35" t="inlineStr">
         <is>
@@ -7723,8 +8575,9 @@
         <v/>
       </c>
       <c r="G20" s="39" t="n"/>
-      <c r="H20" s="40" t="n">
-        <v>5974.3</v>
+      <c r="H20" s="40">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B20,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B20+1))</f>
+        <v/>
       </c>
       <c r="I20" s="41">
         <f>IFERROR(F20-H20,0)</f>
@@ -7747,10 +8600,8 @@
       <c r="Q20" s="44" t="n"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="274">
-      <c r="B21" s="34" t="inlineStr">
-        <is>
-          <t>31-May-2026</t>
-        </is>
+      <c r="B21" s="356" t="n">
+        <v>46173</v>
       </c>
       <c r="C21" s="47" t="inlineStr">
         <is>
@@ -7766,8 +8617,9 @@
         <v/>
       </c>
       <c r="G21" s="51" t="n"/>
-      <c r="H21" s="52" t="n">
-        <v>312</v>
+      <c r="H21" s="52">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B21,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B21+1))</f>
+        <v/>
       </c>
       <c r="I21" s="53">
         <f>IFERROR(F21-H21,0)</f>
@@ -7790,10 +8642,8 @@
       <c r="Q21" s="56" t="n"/>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="274">
-      <c r="B22" s="34" t="inlineStr">
-        <is>
-          <t>01-Jun-2026</t>
-        </is>
+      <c r="B22" s="356" t="n">
+        <v>46174</v>
       </c>
       <c r="C22" s="35" t="inlineStr">
         <is>
@@ -7813,8 +8663,9 @@
       <c r="G22" s="39" t="n">
         <v>310</v>
       </c>
-      <c r="H22" s="40" t="n">
-        <v>5329.64</v>
+      <c r="H22" s="40">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B22,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B22+1))</f>
+        <v/>
       </c>
       <c r="I22" s="41">
         <f>IFERROR(F22-H22,0)</f>
@@ -7837,10 +8688,8 @@
       <c r="Q22" s="44" t="n"/>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="274">
-      <c r="B23" s="34" t="inlineStr">
-        <is>
-          <t>02-Jun-2026</t>
-        </is>
+      <c r="B23" s="356" t="n">
+        <v>46175</v>
       </c>
       <c r="C23" s="47" t="inlineStr">
         <is>
@@ -7860,8 +8709,9 @@
       <c r="G23" s="51" t="n">
         <v>283</v>
       </c>
-      <c r="H23" s="52" t="n">
-        <v>2379.11</v>
+      <c r="H23" s="52">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B23,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B23+1))</f>
+        <v/>
       </c>
       <c r="I23" s="53">
         <f>IFERROR(F23-H23,0)</f>
@@ -7884,10 +8734,8 @@
       <c r="Q23" s="56" t="n"/>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="274">
-      <c r="B24" s="34" t="inlineStr">
-        <is>
-          <t>03-Jun-2026</t>
-        </is>
+      <c r="B24" s="356" t="n">
+        <v>46176</v>
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
@@ -7907,8 +8755,9 @@
       <c r="G24" s="39" t="n">
         <v>120</v>
       </c>
-      <c r="H24" s="40" t="n">
-        <v>4033.86</v>
+      <c r="H24" s="40">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B24,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B24+1))</f>
+        <v/>
       </c>
       <c r="I24" s="41">
         <f>IFERROR(F24-H24,0)</f>
@@ -7931,10 +8780,8 @@
       <c r="Q24" s="44" t="n"/>
     </row>
     <row r="25" ht="16.5" customHeight="1" s="274">
-      <c r="B25" s="34" t="inlineStr">
-        <is>
-          <t>04-Jun-2026</t>
-        </is>
+      <c r="B25" s="356" t="n">
+        <v>46177</v>
       </c>
       <c r="C25" s="47" t="inlineStr">
         <is>
@@ -7952,8 +8799,9 @@
         <v/>
       </c>
       <c r="G25" s="51" t="n"/>
-      <c r="H25" s="52" t="n">
-        <v>20959.96</v>
+      <c r="H25" s="52">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B25,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B25+1))</f>
+        <v/>
       </c>
       <c r="I25" s="53">
         <f>IFERROR(F25-H25,0)</f>
@@ -7976,10 +8824,8 @@
       <c r="Q25" s="56" t="n"/>
     </row>
     <row r="26" ht="16.5" customHeight="1" s="274">
-      <c r="B26" s="34" t="inlineStr">
-        <is>
-          <t>05-Jun-2026</t>
-        </is>
+      <c r="B26" s="356" t="n">
+        <v>46178</v>
       </c>
       <c r="C26" s="35" t="inlineStr">
         <is>
@@ -7999,8 +8845,9 @@
       <c r="G26" s="39" t="n">
         <v>135</v>
       </c>
-      <c r="H26" s="40" t="n">
-        <v>878.0599999999999</v>
+      <c r="H26" s="40">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B26,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B26+1))</f>
+        <v/>
       </c>
       <c r="I26" s="41">
         <f>IFERROR(F26-H26,0)</f>
@@ -8023,10 +8870,8 @@
       <c r="Q26" s="44" t="n"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" s="274">
-      <c r="B27" s="34" t="inlineStr">
-        <is>
-          <t>06-Jun-2026</t>
-        </is>
+      <c r="B27" s="356" t="n">
+        <v>46179</v>
       </c>
       <c r="C27" s="47" t="inlineStr">
         <is>
@@ -8044,8 +8889,9 @@
         <v/>
       </c>
       <c r="G27" s="51" t="n"/>
-      <c r="H27" s="52" t="n">
-        <v>5414</v>
+      <c r="H27" s="52">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B27,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B27+1))</f>
+        <v/>
       </c>
       <c r="I27" s="53">
         <f>IFERROR(F27-H27,0)</f>
@@ -8068,10 +8914,8 @@
       <c r="Q27" s="56" t="n"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="274">
-      <c r="B28" s="34" t="inlineStr">
-        <is>
-          <t>07-Jun-2026</t>
-        </is>
+      <c r="B28" s="356" t="n">
+        <v>46180</v>
       </c>
       <c r="C28" s="35" t="inlineStr">
         <is>
@@ -8085,8 +8929,9 @@
         <v/>
       </c>
       <c r="G28" s="39" t="n"/>
-      <c r="H28" s="40" t="n">
-        <v>1671</v>
+      <c r="H28" s="40">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B28,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B28+1))</f>
+        <v/>
       </c>
       <c r="I28" s="41">
         <f>IFERROR(F28-H28,0)</f>
@@ -8106,10 +8951,8 @@
       <c r="Q28" s="44" t="n"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" s="274">
-      <c r="B29" s="34" t="inlineStr">
-        <is>
-          <t>08-Jun-2026</t>
-        </is>
+      <c r="B29" s="356" t="n">
+        <v>46181</v>
       </c>
       <c r="C29" s="47" t="inlineStr">
         <is>
@@ -8129,8 +8972,9 @@
       <c r="G29" s="51" t="n">
         <v>99</v>
       </c>
-      <c r="H29" s="52" t="n">
-        <v>3187.11</v>
+      <c r="H29" s="52">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B29,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B29+1))</f>
+        <v/>
       </c>
       <c r="I29" s="53">
         <f>IFERROR(F29-H29,0)</f>
@@ -8153,10 +8997,8 @@
       <c r="Q29" s="56" t="n"/>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="274">
-      <c r="B30" s="34" t="inlineStr">
-        <is>
-          <t>09-Jun-2026</t>
-        </is>
+      <c r="B30" s="356" t="n">
+        <v>46182</v>
       </c>
       <c r="C30" s="35" t="inlineStr">
         <is>
@@ -8174,8 +9016,9 @@
         <v/>
       </c>
       <c r="G30" s="39" t="n"/>
-      <c r="H30" s="40" t="n">
-        <v>6623.98</v>
+      <c r="H30" s="40">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B30,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B30+1))</f>
+        <v/>
       </c>
       <c r="I30" s="41">
         <f>IFERROR(F30-H30,0)</f>
@@ -8198,10 +9041,8 @@
       <c r="Q30" s="44" t="n"/>
     </row>
     <row r="31" ht="16.5" customHeight="1" s="274">
-      <c r="B31" s="34" t="inlineStr">
-        <is>
-          <t>10-Jun-2026</t>
-        </is>
+      <c r="B31" s="356" t="n">
+        <v>46183</v>
       </c>
       <c r="C31" s="47" t="inlineStr">
         <is>
@@ -8219,8 +9060,9 @@
         <v/>
       </c>
       <c r="G31" s="51" t="n"/>
-      <c r="H31" s="52" t="n">
-        <v>1341.81</v>
+      <c r="H31" s="52">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B31,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B31+1))</f>
+        <v/>
       </c>
       <c r="I31" s="53">
         <f>IFERROR(F31-H31,0)</f>
@@ -8243,10 +9085,8 @@
       <c r="Q31" s="56" t="n"/>
     </row>
     <row r="32" ht="16.5" customHeight="1" s="274">
-      <c r="B32" s="34" t="inlineStr">
-        <is>
-          <t>11-Jun-2026</t>
-        </is>
+      <c r="B32" s="356" t="n">
+        <v>46184</v>
       </c>
       <c r="C32" s="35" t="inlineStr">
         <is>
@@ -8266,8 +9106,9 @@
       <c r="G32" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="40" t="n">
-        <v>4044</v>
+      <c r="H32" s="40">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B32,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B32+1))</f>
+        <v/>
       </c>
       <c r="I32" s="41">
         <f>IFERROR(F32-H32,0)</f>
@@ -8290,10 +9131,8 @@
       <c r="Q32" s="44" t="n"/>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="274">
-      <c r="B33" s="34" t="inlineStr">
-        <is>
-          <t>12-Jun-2026</t>
-        </is>
+      <c r="B33" s="356" t="n">
+        <v>46185</v>
       </c>
       <c r="C33" s="47" t="inlineStr">
         <is>
@@ -8313,8 +9152,9 @@
       <c r="G33" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="52" t="n">
-        <v>901.8</v>
+      <c r="H33" s="52">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B33,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B33+1))</f>
+        <v/>
       </c>
       <c r="I33" s="53">
         <f>IFERROR(F33-H33,0)</f>
@@ -8337,10 +9177,8 @@
       <c r="Q33" s="56" t="n"/>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="274">
-      <c r="B34" s="34" t="inlineStr">
-        <is>
-          <t>13-Jun-2026</t>
-        </is>
+      <c r="B34" s="356" t="n">
+        <v>46186</v>
       </c>
       <c r="C34" s="35" t="inlineStr">
         <is>
@@ -8360,8 +9198,9 @@
       <c r="G34" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="40" t="n">
-        <v>8084.16</v>
+      <c r="H34" s="40">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B34,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B34+1))</f>
+        <v/>
       </c>
       <c r="I34" s="41">
         <f>IFERROR(F34-H34,0)</f>
@@ -8384,10 +9223,8 @@
       <c r="Q34" s="44" t="n"/>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="274">
-      <c r="B35" s="34" t="inlineStr">
-        <is>
-          <t>14-Jun-2026</t>
-        </is>
+      <c r="B35" s="356" t="n">
+        <v>46187</v>
       </c>
       <c r="C35" s="47" t="inlineStr">
         <is>
@@ -8407,8 +9244,9 @@
       <c r="G35" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="52" t="n">
-        <v>1526.18</v>
+      <c r="H35" s="52">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B35,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B35+1))</f>
+        <v/>
       </c>
       <c r="I35" s="53">
         <f>IFERROR(F35-H35,0)</f>
@@ -8431,10 +9269,8 @@
       <c r="Q35" s="56" t="n"/>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="274">
-      <c r="B36" s="34" t="inlineStr">
-        <is>
-          <t>15-Jun-2026</t>
-        </is>
+      <c r="B36" s="356" t="n">
+        <v>46188</v>
       </c>
       <c r="C36" s="35" t="inlineStr">
         <is>
@@ -8454,8 +9290,9 @@
       <c r="G36" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="40" t="n">
-        <v>2578.08</v>
+      <c r="H36" s="40">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B36,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B36+1))</f>
+        <v/>
       </c>
       <c r="I36" s="41">
         <f>IFERROR(F36-H36,0)</f>
@@ -8478,17 +9315,39 @@
       <c r="Q36" s="44" t="n"/>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="274">
-      <c r="B37" s="34" t="n"/>
-      <c r="C37" s="47" t="n"/>
+      <c r="B37" s="356" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C37" s="47" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
       <c r="D37" s="48" t="n"/>
       <c r="E37" s="49" t="n"/>
-      <c r="F37" s="50" t="n"/>
+      <c r="F37" s="50">
+        <f>IFERROR(D37+E37+G37,0)</f>
+        <v/>
+      </c>
       <c r="G37" s="51" t="n"/>
-      <c r="H37" s="52" t="n"/>
-      <c r="I37" s="53" t="n"/>
-      <c r="J37" s="54" t="n"/>
+      <c r="H37" s="52">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B37,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B37+1))</f>
+        <v/>
+      </c>
+      <c r="I37" s="53">
+        <f>IFERROR(F37-H37,0)</f>
+        <v/>
+      </c>
+      <c r="J37" s="54">
+        <f>IFERROR(I37/F37,0)</f>
+        <v/>
+      </c>
       <c r="K37" s="55" t="n"/>
-      <c r="L37" s="18" t="n"/>
+      <c r="L37" s="18" t="inlineStr">
+        <is>
+          <t>Expenses logged — revenue pending</t>
+        </is>
+      </c>
       <c r="M37" s="21" t="n"/>
       <c r="N37" s="56" t="n"/>
       <c r="O37" s="57" t="n"/>
@@ -14527,9 +15386,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I2:P2"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B5:P5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:P2"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -25728,64 +26587,262 @@
       </c>
     </row>
     <row r="272">
-      <c r="B272" s="64" t="n"/>
-      <c r="C272" s="69" t="n"/>
-      <c r="D272" s="68" t="n"/>
-      <c r="E272" s="69" t="n"/>
-      <c r="F272" s="70" t="n"/>
-      <c r="G272" s="23" t="n"/>
-      <c r="H272" s="23" t="n"/>
-      <c r="I272" s="55" t="n"/>
+      <c r="B272" s="64" t="n">
+        <v>46188</v>
+      </c>
+      <c r="C272" s="69" t="inlineStr">
+        <is>
+          <t>Le Croz Paste</t>
+        </is>
+      </c>
+      <c r="D272" s="68" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E272" s="69" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F272" s="70" t="n">
+        <v>180</v>
+      </c>
+      <c r="G272" s="23" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H272" s="23" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I272" s="55" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>No receipt — logged manually</t>
+        </is>
+      </c>
     </row>
     <row r="273">
-      <c r="B273" s="64" t="n"/>
-      <c r="C273" s="65" t="n"/>
-      <c r="D273" s="66" t="n"/>
-      <c r="E273" s="65" t="n"/>
-      <c r="F273" s="67" t="n"/>
-      <c r="G273" s="14" t="n"/>
-      <c r="H273" s="14" t="n"/>
-      <c r="I273" s="43" t="n"/>
+      <c r="B273" s="64" t="n">
+        <v>46188</v>
+      </c>
+      <c r="C273" s="65" t="inlineStr">
+        <is>
+          <t>Hielo (ice)</t>
+        </is>
+      </c>
+      <c r="D273" s="66" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E273" s="65" t="inlineStr">
+        <is>
+          <t>Supplies / Other</t>
+        </is>
+      </c>
+      <c r="F273" s="67" t="n">
+        <v>100</v>
+      </c>
+      <c r="G273" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H273" s="14" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I273" s="43" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>No receipt — logged manually</t>
+        </is>
+      </c>
     </row>
     <row r="274">
-      <c r="B274" s="64" t="n"/>
-      <c r="C274" s="69" t="n"/>
-      <c r="D274" s="68" t="n"/>
-      <c r="E274" s="69" t="n"/>
-      <c r="F274" s="70" t="n"/>
-      <c r="G274" s="23" t="n"/>
-      <c r="H274" s="23" t="n"/>
-      <c r="I274" s="55" t="n"/>
+      <c r="B274" s="64" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C274" s="69" t="inlineStr">
+        <is>
+          <t>Filete de Mojarra 3.245 kg @ $130</t>
+        </is>
+      </c>
+      <c r="D274" s="68" t="inlineStr">
+        <is>
+          <t>Brisa del Mar</t>
+        </is>
+      </c>
+      <c r="E274" s="69" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat &amp; Fish</t>
+        </is>
+      </c>
+      <c r="F274" s="70" t="n">
+        <v>421.9</v>
+      </c>
+      <c r="G274" s="23" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H274" s="23" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I274" s="55" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Pescados y Mariscos · 09:26</t>
+        </is>
+      </c>
     </row>
     <row r="275">
-      <c r="B275" s="64" t="n"/>
-      <c r="C275" s="65" t="n"/>
-      <c r="D275" s="66" t="n"/>
-      <c r="E275" s="65" t="n"/>
-      <c r="F275" s="67" t="n"/>
-      <c r="G275" s="14" t="n"/>
-      <c r="H275" s="14" t="n"/>
-      <c r="I275" s="43" t="n"/>
+      <c r="B275" s="64" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C275" s="65" t="inlineStr">
+        <is>
+          <t>Leche Lala UHT Entera 1.5L (2 pcs)</t>
+        </is>
+      </c>
+      <c r="D275" s="66" t="inlineStr">
+        <is>
+          <t>OXXO Pathe</t>
+        </is>
+      </c>
+      <c r="E275" s="65" t="inlineStr">
+        <is>
+          <t>Ingredients - Dairy</t>
+        </is>
+      </c>
+      <c r="F275" s="67" t="n">
+        <v>93</v>
+      </c>
+      <c r="G275" s="14" t="inlineStr">
+        <is>
+          <t>Lohith (Personal)</t>
+        </is>
+      </c>
+      <c r="H275" s="14" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I275" s="43" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>HSBC **5543 · Aut 920308 · paid by Lohith (reimburse)</t>
+        </is>
+      </c>
     </row>
     <row r="276">
-      <c r="B276" s="64" t="n"/>
-      <c r="C276" s="69" t="n"/>
-      <c r="D276" s="68" t="n"/>
-      <c r="E276" s="69" t="n"/>
-      <c r="F276" s="70" t="n"/>
-      <c r="G276" s="23" t="n"/>
-      <c r="H276" s="23" t="n"/>
-      <c r="I276" s="55" t="n"/>
+      <c r="B276" s="64" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C276" s="69" t="inlineStr">
+        <is>
+          <t>Pechuga 4.15kg @ $115 + Muslo 4.13kg @ $50</t>
+        </is>
+      </c>
+      <c r="D276" s="68" t="inlineStr">
+        <is>
+          <t>Oh lele (poultry)</t>
+        </is>
+      </c>
+      <c r="E276" s="69" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F276" s="70" t="n">
+        <v>685</v>
+      </c>
+      <c r="G276" s="23" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H276" s="23" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I276" s="55" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Nota de remisión · 478+207</t>
+        </is>
+      </c>
     </row>
     <row r="277">
-      <c r="B277" s="64" t="n"/>
-      <c r="C277" s="65" t="n"/>
-      <c r="D277" s="66" t="n"/>
-      <c r="E277" s="65" t="n"/>
-      <c r="F277" s="67" t="n"/>
-      <c r="G277" s="14" t="n"/>
-      <c r="H277" s="14" t="n"/>
-      <c r="I277" s="43" t="n"/>
+      <c r="B277" s="64" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C277" s="65" t="inlineStr">
+        <is>
+          <t>Azúcar, Leche Entera, Crema Ácida, Arroz Morelos (7 art.)</t>
+        </is>
+      </c>
+      <c r="D277" s="66" t="inlineStr">
+        <is>
+          <t>Sam’s Club</t>
+        </is>
+      </c>
+      <c r="E277" s="65" t="inlineStr">
+        <is>
+          <t>Supermarket / General</t>
+        </is>
+      </c>
+      <c r="F277" s="67" t="n">
+        <v>1342</v>
+      </c>
+      <c r="G277" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H277" s="14" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I277" s="43" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Visa Débito **29 · Aut 070287</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="B278" s="64" t="n"/>
@@ -31630,7 +32687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="18.33203125" customWidth="1" style="274" min="1" max="1"/>
@@ -32910,915 +33967,193 @@
     </row>
     <row r="59" ht="15.6" customHeight="1" s="274"/>
     <row r="61" ht="15.6" customHeight="1" s="274">
-      <c r="A61" s="218" t="inlineStr">
-        <is>
-          <t>── LOHITH PERSONAL LEDGER — OWNER BALANCE TRACKER ──</t>
-        </is>
-      </c>
-      <c r="B61" s="218" t="n"/>
-      <c r="C61" s="218" t="n"/>
-      <c r="D61" s="218" t="n"/>
-      <c r="E61" s="218" t="n"/>
-      <c r="F61" s="218" t="n"/>
-      <c r="G61" s="218" t="n"/>
-      <c r="H61" s="218" t="n"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>── PROPINAS / TIPS PASS-THROUGH (NOT income, NOT expense) ──</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="219" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B62" s="219" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C62" s="219" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D62" s="219" t="inlineStr">
-        <is>
-          <t>Spent by Lohith ($)</t>
-        </is>
-      </c>
-      <c r="E62" s="219" t="inlineStr">
-        <is>
-          <t>Transferred to Lohith ($)</t>
-        </is>
-      </c>
-      <c r="F62" s="219" t="inlineStr">
-        <is>
-          <t>Running Balance ($)</t>
-        </is>
-      </c>
-      <c r="G62" s="219" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H62" s="219" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Paid To</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Amount</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="243" t="n">
+      <c r="A63" s="355" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>John (6 dias)</t>
+        </is>
+      </c>
+      <c r="D63" s="354" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="355" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Debi (6 dias)</t>
+        </is>
+      </c>
+      <c r="D64" s="354" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="355" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Victor (2 dias)</t>
+        </is>
+      </c>
+      <c r="D65" s="354" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="355" t="n">
         <v>46174</v>
       </c>
-      <c r="B63" s="244" t="inlineStr">
-        <is>
-          <t>Telmex Internet Bill (Mayo)</t>
-        </is>
-      </c>
-      <c r="C63" s="245" t="inlineStr">
-        <is>
-          <t>Expense - Personal</t>
-        </is>
-      </c>
-      <c r="D63" s="246" t="n">
-        <v>349</v>
-      </c>
-      <c r="E63" s="247" t="n"/>
-      <c r="F63" s="248">
-        <f>IFERROR(D63-E63,0)</f>
-        <v/>
-      </c>
-      <c r="G63" s="244" t="inlineStr">
-        <is>
-          <t>⏳ Reimburse</t>
-        </is>
-      </c>
-      <c r="H63" s="249" t="inlineStr">
-        <is>
-          <t>Paid by Lohith — ⏳ Reimburse</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="250" t="n">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>John (Week 2)</t>
+        </is>
+      </c>
+      <c r="D66" s="354" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="355" t="n">
         <v>46174</v>
       </c>
-      <c r="B64" s="227" t="inlineStr">
-        <is>
-          <t>Customer Transfer — Jun 1</t>
-        </is>
-      </c>
-      <c r="C64" s="251" t="inlineStr">
-        <is>
-          <t>Transfer Received</t>
-        </is>
-      </c>
-      <c r="D64" s="231" t="n"/>
-      <c r="E64" s="230" t="n">
-        <v>310</v>
-      </c>
-      <c r="F64" s="228">
-        <f>IFERROR(F63+D64-E64,0)</f>
-        <v/>
-      </c>
-      <c r="G64" s="227" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H64" s="252" t="inlineStr">
-        <is>
-          <t>✅ Received in Lohith account</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="250" t="n">
-        <v>46175</v>
-      </c>
-      <c r="B65" s="227" t="inlineStr">
-        <is>
-          <t>Customer Transfer — Jun 2</t>
-        </is>
-      </c>
-      <c r="C65" s="251" t="inlineStr">
-        <is>
-          <t>Transfer Received</t>
-        </is>
-      </c>
-      <c r="D65" s="231" t="n"/>
-      <c r="E65" s="230" t="n">
-        <v>283</v>
-      </c>
-      <c r="F65" s="228">
-        <f>IFERROR(F64+D65-E65,0)</f>
-        <v/>
-      </c>
-      <c r="G65" s="227" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H65" s="252" t="inlineStr">
-        <is>
-          <t>✅ Received in Lohith account</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="250" t="n">
-        <v>46176</v>
-      </c>
-      <c r="B66" s="227" t="inlineStr">
-        <is>
-          <t>Customer Transfer — Jun 3</t>
-        </is>
-      </c>
-      <c r="C66" s="251" t="inlineStr">
-        <is>
-          <t>Transfer Received</t>
-        </is>
-      </c>
-      <c r="D66" s="231" t="n"/>
-      <c r="E66" s="230" t="n">
-        <v>120</v>
-      </c>
-      <c r="F66" s="228">
-        <f>IFERROR(F65+D66-E66,0)</f>
-        <v/>
-      </c>
-      <c r="G66" s="227" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H66" s="252" t="inlineStr">
-        <is>
-          <t>✅ Received in Lohith account</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="243" t="n">
-        <v>46177</v>
-      </c>
-      <c r="B67" s="244" t="inlineStr">
-        <is>
-          <t>Personal expenses — Huevos, Ajonjoli, Verduras</t>
-        </is>
-      </c>
-      <c r="C67" s="245" t="inlineStr">
-        <is>
-          <t>Expense - Personal</t>
-        </is>
-      </c>
-      <c r="D67" s="246" t="n">
-        <v>358</v>
-      </c>
-      <c r="E67" s="247" t="n"/>
-      <c r="F67" s="248">
-        <f>IFERROR(F66+D67-E67,0)</f>
-        <v/>
-      </c>
-      <c r="G67" s="244" t="inlineStr">
-        <is>
-          <t>⏳ Reimburse</t>
-        </is>
-      </c>
-      <c r="H67" s="249" t="inlineStr">
-        <is>
-          <t>$69 Huevos + $44 Ajonjoli Blanco + $45 Ajonjoli Negro + $200 Verduras</t>
-        </is>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Duvi/Debi (Week 2)</t>
+        </is>
+      </c>
+      <c r="D67" s="354" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="253" t="n">
-        <v>46177</v>
-      </c>
-      <c r="B68" s="232" t="inlineStr">
-        <is>
-          <t>Cash settlement — $6 added to restaurant</t>
-        </is>
-      </c>
-      <c r="C68" s="254" t="inlineStr">
-        <is>
-          <t>Expense - Personal</t>
-        </is>
-      </c>
-      <c r="D68" s="236" t="n">
-        <v>6</v>
-      </c>
-      <c r="E68" s="235" t="n"/>
-      <c r="F68" s="233">
-        <f>IFERROR(F67+D68-E68,0)</f>
-        <v/>
-      </c>
-      <c r="G68" s="232" t="inlineStr">
-        <is>
-          <t>✅ Settled</t>
-        </is>
-      </c>
-      <c r="H68" s="255" t="inlineStr">
-        <is>
-          <t>Lohith added $6 cash to restaurant — balance now ZERO</t>
-        </is>
+      <c r="A68" s="355" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>John (Week 4)</t>
+        </is>
+      </c>
+      <c r="D68" s="354" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="250" t="n">
-        <v>46178</v>
-      </c>
-      <c r="B69" s="227" t="inlineStr">
-        <is>
-          <t>Customer Transfer — Jun 5</t>
-        </is>
-      </c>
-      <c r="C69" s="251" t="inlineStr">
-        <is>
-          <t>Transfer Received</t>
-        </is>
-      </c>
-      <c r="D69" s="231" t="n"/>
-      <c r="E69" s="230" t="n">
-        <v>135</v>
-      </c>
-      <c r="F69" s="228">
-        <f>IFERROR(F68+D69-E69,0)</f>
-        <v/>
-      </c>
-      <c r="G69" s="227" t="inlineStr">
-        <is>
-          <t>✅ Received</t>
-        </is>
-      </c>
-      <c r="H69" s="252" t="inlineStr">
-        <is>
-          <t>✅ Received in Lohith account — Jun 5</t>
-        </is>
+      <c r="A69" s="355" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Duvi/Debi (Week 4)</t>
+        </is>
+      </c>
+      <c r="D69" s="354" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="243" t="n">
-        <v>46177</v>
-      </c>
-      <c r="B70" s="244" t="inlineStr">
-        <is>
-          <t>Renta + Mantenimiento Junio 2026</t>
-        </is>
-      </c>
-      <c r="C70" s="245" t="inlineStr">
-        <is>
-          <t>Expense - Personal</t>
-        </is>
-      </c>
-      <c r="D70" s="246" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E70" s="247" t="n"/>
-      <c r="F70" s="248">
-        <f>IFERROR(F69+D70-E70,0)</f>
-        <v/>
-      </c>
-      <c r="G70" s="244" t="inlineStr">
-        <is>
-          <t>⏳ Reimburse</t>
-        </is>
-      </c>
-      <c r="H70" s="249" t="inlineStr">
-        <is>
-          <t>Rent $15,000 + Maintenance $5,000 — paid personally by Lohith on 4 Jun</t>
-        </is>
+      <c r="A70" s="355" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Cesar (Week 4)</t>
+        </is>
+      </c>
+      <c r="D70" s="354" t="n">
+        <v>126</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="250" t="n">
-        <v>46181</v>
-      </c>
-      <c r="B71" s="227" t="inlineStr">
-        <is>
-          <t>Customer Transfer — Jun 8</t>
-        </is>
-      </c>
-      <c r="C71" s="251" t="inlineStr">
-        <is>
-          <t>Transfer Received</t>
-        </is>
-      </c>
-      <c r="D71" s="231" t="n"/>
-      <c r="E71" s="230" t="n">
-        <v>99</v>
-      </c>
-      <c r="F71" s="228">
-        <f>IFERROR(F70+D71-E71,0)</f>
-        <v/>
-      </c>
-      <c r="G71" s="227" t="inlineStr">
-        <is>
-          <t>✅ Received</t>
-        </is>
-      </c>
-      <c r="H71" s="252" t="inlineStr">
-        <is>
-          <t>✅ Received in Lohith account — Jun 8</t>
-        </is>
+      <c r="A71" s="355" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Samu (Week 4)</t>
+        </is>
+      </c>
+      <c r="D71" s="354" t="n">
+        <v>126</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="265" t="n">
-        <v>46183</v>
-      </c>
-      <c r="B72" s="266" t="inlineStr">
-        <is>
-          <t>Chedraui Paseo — Groceries (elote, chile, tomate, tortillas, bolillo)</t>
-        </is>
-      </c>
-      <c r="C72" s="267" t="inlineStr">
-        <is>
-          <t>Expense - Personal</t>
-        </is>
-      </c>
-      <c r="D72" s="268" t="n">
-        <v>236.81</v>
-      </c>
-      <c r="F72" s="269">
-        <f>IFERROR(F71+D72-E72,0)</f>
-        <v/>
-      </c>
-      <c r="G72" s="266" t="inlineStr">
-        <is>
-          <t>⏳ Reimburse</t>
-        </is>
-      </c>
-      <c r="H72" s="242" t="inlineStr">
-        <is>
-          <t>Paid personally by Lohith — HSBC **5543</t>
-        </is>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>TOTAL TIPS PASSED THROUGH</t>
+        </is>
+      </c>
+      <c r="D72" s="354">
+        <f>SUM(D63:D71)</f>
+        <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="265" t="n">
-        <v>46183</v>
-      </c>
-      <c r="B73" s="266" t="inlineStr">
-        <is>
-          <t>Office Depot — Comanda Restaurante</t>
-        </is>
-      </c>
-      <c r="C73" s="267" t="inlineStr">
-        <is>
-          <t>Expense - Personal</t>
-        </is>
-      </c>
-      <c r="D73" s="268" t="n">
-        <v>59</v>
-      </c>
-      <c r="F73" s="269">
-        <f>IFERROR(F72+D73-E73,0)</f>
-        <v/>
-      </c>
-      <c r="G73" s="266" t="inlineStr">
-        <is>
-          <t>⏳ Reimburse</t>
-        </is>
-      </c>
-      <c r="H73" s="242" t="inlineStr">
-        <is>
-          <t>Paid personally by Lohith — MC **5543</t>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Customer tips collected &amp; handed to staff. Excluded from P&amp;L — nets to zero (received = paid).</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="265" t="n">
-        <v>46184</v>
-      </c>
-      <c r="B74" s="266" t="inlineStr">
-        <is>
-          <t>ALICO — Ala de Pollo, Papa Harvest 13.62kg, Boneless Freskecito</t>
-        </is>
-      </c>
-      <c r="C74" s="267" t="inlineStr">
-        <is>
-          <t>Expense - Personal</t>
-        </is>
-      </c>
-      <c r="D74" s="268" t="n">
-        <v>2865</v>
-      </c>
-      <c r="F74" s="269">
-        <f>IFERROR(F73+D74-E74,0)</f>
-        <v/>
-      </c>
-      <c r="G74" s="266" t="inlineStr">
-        <is>
-          <t>⏳ Reimburse</t>
-        </is>
-      </c>
-      <c r="H74" s="242" t="inlineStr">
-        <is>
-          <t>Restaurant ingredients paid personally by Lohith (transfer) — 11 Jun</t>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>── CASH RECONCILIATION (15 Jun 2026) ──</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="265" t="n">
-        <v>46184</v>
-      </c>
-      <c r="B75" s="266" t="inlineStr">
-        <is>
-          <t>Pollería — Muslo de Pollo 4.70 kg</t>
-        </is>
-      </c>
-      <c r="C75" s="267" t="inlineStr">
-        <is>
-          <t>Expense - Personal</t>
-        </is>
-      </c>
-      <c r="D75" s="268" t="n">
-        <v>235</v>
-      </c>
-      <c r="F75" s="269">
-        <f>IFERROR(F74+D75-E75,0)</f>
-        <v/>
-      </c>
-      <c r="G75" s="266" t="inlineStr">
-        <is>
-          <t>⏳ Reimburse</t>
-        </is>
-      </c>
-      <c r="H75" s="242" t="inlineStr">
-        <is>
-          <t>Restaurant ingredients paid personally by Lohith (transfer) — 11 Jun</t>
-        </is>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Actual restaurant cash on hand</t>
+        </is>
+      </c>
+      <c r="D75" s="354" t="n">
+        <v>20283</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="265" t="n">
-        <v>46188</v>
-      </c>
-      <c r="B76" s="266" t="inlineStr">
-        <is>
-          <t>Chedraui — Tortillas, Bolillo, Rosca de Nuez</t>
-        </is>
-      </c>
-      <c r="C76" s="267" t="inlineStr">
-        <is>
-          <t>Expense - Personal</t>
-        </is>
-      </c>
-      <c r="D76" s="268" t="n">
-        <v>160.33</v>
-      </c>
-      <c r="F76" s="269">
-        <f>IFERROR(F75+D76-E76,0)</f>
-        <v/>
-      </c>
-      <c r="G76" s="266" t="inlineStr">
-        <is>
-          <t>⏳ Reimburse</t>
-        </is>
-      </c>
-      <c r="H76" s="242" t="inlineStr">
-        <is>
-          <t>HSBC **5543 — paid by Lohith 15 Jun</t>
-        </is>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Adjustment: restaurant cash added to tips + Mercado Pago commission (vs running estimate)</t>
+        </is>
+      </c>
+      <c r="D76" s="354" t="n">
+        <v>-165</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="265" t="n">
-        <v>46188</v>
-      </c>
-      <c r="B77" s="266" t="inlineStr">
-        <is>
-          <t>OXXO Pathe — Aceite Vegetal (2)</t>
-        </is>
-      </c>
-      <c r="C77" s="267" t="inlineStr">
-        <is>
-          <t>Expense - Personal</t>
-        </is>
-      </c>
-      <c r="D77" s="268" t="n">
-        <v>104</v>
-      </c>
-      <c r="F77" s="269">
-        <f>IFERROR(F76+D77-E77,0)</f>
-        <v/>
-      </c>
-      <c r="G77" s="266" t="inlineStr">
-        <is>
-          <t>⏳ Reimburse</t>
-        </is>
-      </c>
-      <c r="H77" s="242" t="inlineStr">
-        <is>
-          <t>HSBC **5543 — paid by Lohith 15 Jun</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="265" t="n">
-        <v>46188</v>
-      </c>
-      <c r="B78" s="266" t="inlineStr">
-        <is>
-          <t>Miscelánea LC — Ribeye, Chuleta, Bistec</t>
-        </is>
-      </c>
-      <c r="C78" s="267" t="inlineStr">
-        <is>
-          <t>Expense - Personal</t>
-        </is>
-      </c>
-      <c r="D78" s="268" t="n">
-        <v>1015</v>
-      </c>
-      <c r="F78" s="269">
-        <f>IFERROR(F77+D78-E78,0)</f>
-        <v/>
-      </c>
-      <c r="G78" s="266" t="inlineStr">
-        <is>
-          <t>⏳ Reimburse</t>
-        </is>
-      </c>
-      <c r="H78" s="242" t="inlineStr">
-        <is>
-          <t>HSBC **5543 — paid by Lohith 15 Jun</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="265" t="n">
-        <v>46188</v>
-      </c>
-      <c r="B79" s="266" t="inlineStr">
-        <is>
-          <t>Transfer from Restaurant account</t>
-        </is>
-      </c>
-      <c r="C79" s="267" t="inlineStr">
-        <is>
-          <t>Reimbursement</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>3162</v>
-      </c>
-      <c r="F79" s="269">
-        <f>IFERROR(F78+D79-E79,0)</f>
-        <v/>
-      </c>
-      <c r="G79" s="266" t="inlineStr">
-        <is>
-          <t>✅ Received</t>
-        </is>
-      </c>
-      <c r="H79" s="242" t="inlineStr">
-        <is>
-          <t>Bank transfer to Lohith</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="265" t="n">
-        <v>46188</v>
-      </c>
-      <c r="B80" s="266" t="inlineStr">
-        <is>
-          <t>15 Jun card expenses reimbursed (Chedraui+OXXO+Miscelánea)</t>
-        </is>
-      </c>
-      <c r="C80" s="267" t="inlineStr">
-        <is>
-          <t>Reimbursement</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>1279.33</v>
-      </c>
-      <c r="F80" s="269">
-        <f>IFERROR(F79+D80-E80,0)</f>
-        <v/>
-      </c>
-      <c r="G80" s="266" t="inlineStr">
-        <is>
-          <t>✅ Received</t>
-        </is>
-      </c>
-      <c r="H80" s="242" t="inlineStr">
-        <is>
-          <t>HSBC **5543 items repaid same day</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="226" t="inlineStr">
-        <is>
-          <t>TOTALS &amp; CURRENT BALANCE</t>
-        </is>
-      </c>
-      <c r="B81" s="219" t="n"/>
-      <c r="C81" s="219" t="n"/>
-      <c r="D81" s="256">
-        <f>SUM(D63:D80)</f>
-        <v/>
-      </c>
-      <c r="E81" s="257">
-        <f>SUM(E63:E80)</f>
-        <v/>
-      </c>
-      <c r="F81" s="258">
-        <f>F80</f>
-        <v/>
-      </c>
-      <c r="G81" s="226">
-        <f>IF(F80&gt;0,"⏳ Restaurant owes Lohith $"&amp;TEXT(F80,"#,##0"),IF(F80&lt;0,"💵 Lohith holds $"&amp;TEXT(ABS(F80),"#,##0"),"✅ Zero balance"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="242" t="inlineStr">
-        <is>
-          <t>HOW TO USE:</t>
-        </is>
-      </c>
-      <c r="B83" s="242" t="n"/>
-      <c r="C83" s="242" t="n"/>
-      <c r="D83" s="242" t="n"/>
-      <c r="E83" s="242" t="n"/>
-      <c r="F83" s="242" t="n"/>
-      <c r="G83" s="242" t="n"/>
-      <c r="H83" s="242" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="242" t="inlineStr">
-        <is>
-          <t>Add new rows above TOTALS. Spent by Lohith = restaurant expenses he paid personally.</t>
-        </is>
-      </c>
-      <c r="B84" s="242" t="n"/>
-      <c r="C84" s="242" t="n"/>
-      <c r="D84" s="242" t="n"/>
-      <c r="E84" s="242" t="n"/>
-      <c r="F84" s="242" t="n"/>
-      <c r="G84" s="242" t="n"/>
-      <c r="H84" s="242" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="242" t="inlineStr">
-        <is>
-          <t>Transferred to Lohith = customer bank transfers received in his personal account.</t>
-        </is>
-      </c>
-      <c r="B85" s="242" t="n"/>
-      <c r="C85" s="242" t="n"/>
-      <c r="D85" s="242" t="n"/>
-      <c r="E85" s="242" t="n"/>
-      <c r="F85" s="242" t="n"/>
-      <c r="G85" s="242" t="n"/>
-      <c r="H85" s="242" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="242" t="inlineStr">
-        <is>
-          <t>Positive balance = restaurant owes Lohith. Negative = Lohith holds restaurant funds.</t>
-        </is>
-      </c>
-      <c r="B86" s="242" t="n"/>
-      <c r="C86" s="242" t="n"/>
-      <c r="D86" s="242" t="n"/>
-      <c r="E86" s="242" t="n"/>
-      <c r="F86" s="242" t="n"/>
-      <c r="G86" s="242" t="n"/>
-      <c r="H86" s="242" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>── PROPINAS / TIPS PASS-THROUGH (NOT income, NOT expense) ──</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Paid To</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="355" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>John (6 dias)</t>
-        </is>
-      </c>
-      <c r="D91" s="354" t="n">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="355" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Debi (6 dias)</t>
-        </is>
-      </c>
-      <c r="D92" s="354" t="n">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="355" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Victor (2 dias)</t>
-        </is>
-      </c>
-      <c r="D93" s="354" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="355" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>John (Week 2)</t>
-        </is>
-      </c>
-      <c r="D94" s="354" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="355" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Duvi/Debi (Week 2)</t>
-        </is>
-      </c>
-      <c r="D95" s="354" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="355" t="n">
-        <v>46186</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>John (Week 4)</t>
-        </is>
-      </c>
-      <c r="D96" s="354" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="355" t="n">
-        <v>46186</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Duvi/Debi (Week 4)</t>
-        </is>
-      </c>
-      <c r="D97" s="354" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="355" t="n">
-        <v>46186</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Cesar (Week 4)</t>
-        </is>
-      </c>
-      <c r="D98" s="354" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="355" t="n">
-        <v>46186</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Samu (Week 4)</t>
-        </is>
-      </c>
-      <c r="D99" s="354" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>TOTAL TIPS PASSED THROUGH</t>
-        </is>
-      </c>
-      <c r="D100" s="354">
-        <f>SUM(D91:D99)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Customer tips collected &amp; handed to staff. Excluded from P&amp;L — nets to zero (received = paid).</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>── CASH RECONCILIATION (15 Jun 2026) ──</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Actual restaurant cash on hand</t>
-        </is>
-      </c>
-      <c r="D103" s="354" t="n">
-        <v>20283</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Adjustment: restaurant cash added to tips + Mercado Pago commission (vs running estimate)</t>
-        </is>
-      </c>
-      <c r="D104" s="354" t="n">
-        <v>-165</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>Reconciled to physical count provided by Reddy. $20,283 is net of MP % deductions.</t>
         </is>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -15386,9 +15386,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -33725,11 +33725,11 @@
     <row r="45" ht="15.6" customHeight="1" s="274">
       <c r="A45" s="226" t="inlineStr">
         <is>
-          <t>With Cesar + Samu (✅ ACTIVE from 9 Jun)</t>
+          <t>Current roster: John + Debi + Samu (no mesero)</t>
         </is>
       </c>
       <c r="B45" s="227" t="n">
-        <v>14050</v>
+        <v>12050</v>
       </c>
       <c r="C45" s="227" t="n">
         <v>23750</v>
@@ -33738,16 +33738,16 @@
         <v>24550</v>
       </c>
       <c r="E45" s="227" t="n">
-        <v>4092</v>
+        <v>3758</v>
       </c>
       <c r="F45" s="227" t="inlineStr">
         <is>
-          <t>✅ NOW ACTIVE — current avg $4,011/day vs break-even $3,959/day</t>
+          <t>Cesar resigned — fixed costs down $2,000/wk</t>
         </is>
       </c>
       <c r="G45" s="227" t="inlineStr">
         <is>
-          <t>✅ Cesar $2,000 + Samu $800 — break-even $4,092/day</t>
+          <t>Break-even ≈ $3,758/day (fixed $12,050 + variable $10,500, ÷6 days)</t>
         </is>
       </c>
       <c r="H45" s="227" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -9323,13 +9323,19 @@
           <t>Tue</t>
         </is>
       </c>
-      <c r="D37" s="48" t="n"/>
-      <c r="E37" s="49" t="n"/>
+      <c r="D37" s="48" t="n">
+        <v>1841</v>
+      </c>
+      <c r="E37" s="49" t="n">
+        <v>945</v>
+      </c>
       <c r="F37" s="50">
         <f>IFERROR(D37+E37+G37,0)</f>
         <v/>
       </c>
-      <c r="G37" s="51" t="n"/>
+      <c r="G37" s="51" t="n">
+        <v>0</v>
+      </c>
       <c r="H37" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B37,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B37+1))</f>
         <v/>
@@ -9345,7 +9351,7 @@
       <c r="K37" s="55" t="n"/>
       <c r="L37" s="18" t="inlineStr">
         <is>
-          <t>Expenses logged — revenue pending</t>
+          <t>Cierre 16 Jun + receipts</t>
         </is>
       </c>
       <c r="M37" s="21" t="n"/>
@@ -15386,9 +15392,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -39,7 +39,7 @@
     <numFmt numFmtId="173" formatCode="#,##0;\-#,##0;\-"/>
     <numFmt numFmtId="174" formatCode="dd-mmm-yyyy"/>
   </numFmts>
-  <fonts count="90">
+  <fonts count="91">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -604,6 +604,10 @@
       <b val="1"/>
       <i val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
   <fills count="55">
     <fill>
@@ -1165,7 +1169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="365">
+  <cellXfs count="393">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2081,6 +2085,86 @@
     <xf numFmtId="0" fontId="88" fillId="54" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="88" fillId="54" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="53" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="53" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="88" fillId="13" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="88" fillId="19" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="10" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="53" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="90" fillId="53" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="10" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="42" fillId="20" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="37" fillId="20" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="42" fillId="19" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="37" fillId="19" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="43" fillId="18" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="67" fillId="18" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="72" fillId="17" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="68" fillId="17" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="40" fillId="16" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="51" fillId="16" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="51" fillId="16" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="37" fillId="16" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="64" fillId="14" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="43" fillId="14" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="62" fillId="19" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="62" fillId="20" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="62" fillId="20" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="88" fillId="19" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15392,8 +15476,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I2:P2"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:P2"/>
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
@@ -38202,20 +38286,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:O209"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
-    <col width="4" customWidth="1" style="274" min="1" max="1"/>
-    <col width="30" customWidth="1" style="274" min="2" max="2"/>
-    <col width="16" customWidth="1" style="274" min="3" max="8"/>
+    <col width="30" customWidth="1" style="274" min="1" max="1"/>
+    <col width="15" customWidth="1" style="274" min="2" max="2"/>
+    <col width="15" customWidth="1" style="274" min="3" max="8"/>
     <col width="18" customWidth="1" style="274" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="4.5" customHeight="1" s="274">
-      <c r="A1" s="5" t="n"/>
-      <c r="B1" s="5" t="n"/>
-      <c r="C1" s="5" t="n"/>
-      <c r="D1" s="5" t="n"/>
+    <row r="1" ht="24" customHeight="1" s="274">
+      <c r="A1" s="365" t="inlineStr">
+        <is>
+          <t>LOKA — MONTHLY P&amp;L  (auto-summary by month)</t>
+        </is>
+      </c>
       <c r="E1" s="5" t="n"/>
       <c r="F1" s="5" t="n"/>
       <c r="G1" s="5" t="n"/>
@@ -38223,40 +38308,90 @@
       <c r="I1" s="5" t="n"/>
     </row>
     <row r="2" ht="37.5" customHeight="1" s="274">
-      <c r="A2" s="340" t="inlineStr">
-        <is>
-          <t>📈  LOKA — MONTHLY P&amp;L</t>
-        </is>
-      </c>
-      <c r="E2" s="313" t="inlineStr">
-        <is>
-          <t>Revenue &amp; Expense summary — fill monthly totals from Daily Log &amp; Expenses</t>
-        </is>
-      </c>
+      <c r="A2" s="340" t="n"/>
+      <c r="E2" s="313" t="n"/>
     </row>
     <row r="3" ht="3.75" customHeight="1" s="274">
-      <c r="A3" s="323" t="n"/>
-    </row>
-    <row r="4" ht="7.5" customHeight="1" s="274"/>
-    <row r="5" ht="9.75" customHeight="1" s="274"/>
+      <c r="A3" s="366" t="inlineStr">
+        <is>
+          <t>SUMMARY</t>
+        </is>
+      </c>
+      <c r="B3" s="367" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C3" s="367" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="7.5" customHeight="1" s="274">
+      <c r="A4" s="360" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="B4" s="361" t="n">
+        <v>52949</v>
+      </c>
+      <c r="C4" s="361" t="n">
+        <v>53931</v>
+      </c>
+    </row>
+    <row r="5" ht="9.75" customHeight="1" s="274">
+      <c r="A5" s="360" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="B5" s="361" t="n">
+        <v>32919.63</v>
+      </c>
+      <c r="C5" s="361" t="n">
+        <v>71774.64999999999</v>
+      </c>
+    </row>
     <row r="6" ht="21.75" customHeight="1" s="274">
-      <c r="B6" s="133" t="inlineStr">
-        <is>
-          <t>YEAR:</t>
-        </is>
-      </c>
-      <c r="C6" s="134" t="n">
-        <v>2025</v>
+      <c r="A6" s="368" t="inlineStr">
+        <is>
+          <t>NET PROFIT / LOSS</t>
+        </is>
+      </c>
+      <c r="B6" s="369" t="n">
+        <v>20029.37</v>
+      </c>
+      <c r="C6" s="370" t="n">
+        <v>-17843.65</v>
       </c>
     </row>
     <row r="7" ht="7.5" customHeight="1" s="274">
-      <c r="C7" t="n">
-        <v>2026</v>
+      <c r="A7" s="360" t="inlineStr">
+        <is>
+          <t>Trading Days</t>
+        </is>
+      </c>
+      <c r="B7" s="361" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" s="361" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="8" ht="27.75" customHeight="1" s="274">
-      <c r="B8" s="279" t="n"/>
-      <c r="C8" s="279" t="n"/>
+      <c r="A8" s="360" t="inlineStr">
+        <is>
+          <t>Avg Income / Day</t>
+        </is>
+      </c>
+      <c r="B8" s="371" t="n">
+        <v>3782.07</v>
+      </c>
+      <c r="C8" s="371" t="n">
+        <v>3852.21</v>
+      </c>
       <c r="D8" s="279" t="n"/>
       <c r="E8" s="279" t="n"/>
       <c r="F8" s="279" t="n"/>
@@ -38266,17 +38401,23 @@
     </row>
     <row r="9" ht="19.5" customHeight="1" s="274">
       <c r="B9" s="298" t="n"/>
-      <c r="C9" s="299" t="n"/>
-      <c r="D9" s="299" t="n"/>
-      <c r="E9" s="299" t="n"/>
-      <c r="F9" s="299" t="n"/>
-      <c r="G9" s="299" t="n"/>
-      <c r="H9" s="299" t="n"/>
-      <c r="I9" s="299" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1" s="274">
-      <c r="B10" s="135" t="n"/>
-      <c r="C10" s="93" t="n"/>
+      <c r="A10" s="367" t="inlineStr">
+        <is>
+          <t>INCOME BY TYPE</t>
+        </is>
+      </c>
+      <c r="B10" s="372" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C10" s="373" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
       <c r="D10" s="93" t="n"/>
       <c r="E10" s="93" t="n"/>
       <c r="F10" s="93" t="n"/>
@@ -38285,18 +38426,30 @@
       <c r="I10" s="116" t="n"/>
     </row>
     <row r="11" ht="19.5" customHeight="1" s="274">
-      <c r="B11" s="298" t="n"/>
-      <c r="C11" s="299" t="n"/>
-      <c r="D11" s="299" t="n"/>
-      <c r="E11" s="299" t="n"/>
-      <c r="F11" s="299" t="n"/>
-      <c r="G11" s="299" t="n"/>
-      <c r="H11" s="299" t="n"/>
-      <c r="I11" s="299" t="n"/>
+      <c r="A11" s="360" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="B11" s="374" t="n">
+        <v>26684</v>
+      </c>
+      <c r="C11" s="361" t="n">
+        <v>27158</v>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1" s="274">
-      <c r="B12" s="136" t="n"/>
-      <c r="C12" s="93" t="n"/>
+      <c r="A12" s="360" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="B12" s="375" t="n">
+        <v>26265</v>
+      </c>
+      <c r="C12" s="376" t="n">
+        <v>25826</v>
+      </c>
       <c r="D12" s="93" t="n"/>
       <c r="E12" s="93" t="n"/>
       <c r="F12" s="93" t="n"/>
@@ -38305,8 +38458,17 @@
       <c r="I12" s="137" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="274">
-      <c r="B13" s="138" t="n"/>
-      <c r="C13" s="86" t="n"/>
+      <c r="A13" s="360" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="B13" s="377" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="378" t="n">
+        <v>947</v>
+      </c>
       <c r="D13" s="86" t="n"/>
       <c r="E13" s="86" t="n"/>
       <c r="F13" s="86" t="n"/>
@@ -38325,8 +38487,21 @@
       <c r="I14" s="114" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="274">
-      <c r="B15" s="141" t="n"/>
-      <c r="C15" s="112" t="n"/>
+      <c r="A15" s="367" t="inlineStr">
+        <is>
+          <t>EXPENSES BY CATEGORY</t>
+        </is>
+      </c>
+      <c r="B15" s="372" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C15" s="373" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
       <c r="D15" s="112" t="n"/>
       <c r="E15" s="112" t="n"/>
       <c r="F15" s="112" t="n"/>
@@ -38335,8 +38510,17 @@
       <c r="I15" s="112" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1" s="274">
-      <c r="B16" s="142" t="n"/>
-      <c r="C16" s="143" t="n"/>
+      <c r="A16" s="360" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="B16" s="379" t="n">
+        <v>905.23</v>
+      </c>
+      <c r="C16" s="380" t="n">
+        <v>5567.39</v>
+      </c>
       <c r="D16" s="143" t="n"/>
       <c r="E16" s="143" t="n"/>
       <c r="F16" s="143" t="n"/>
@@ -38345,18 +38529,30 @@
       <c r="I16" s="143" t="n"/>
     </row>
     <row r="17" ht="19.5" customHeight="1" s="274">
-      <c r="B17" s="298" t="n"/>
-      <c r="C17" s="299" t="n"/>
-      <c r="D17" s="299" t="n"/>
-      <c r="E17" s="299" t="n"/>
-      <c r="F17" s="299" t="n"/>
-      <c r="G17" s="299" t="n"/>
-      <c r="H17" s="299" t="n"/>
-      <c r="I17" s="299" t="n"/>
+      <c r="A17" s="360" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="B17" s="374" t="n">
+        <v>1976.5</v>
+      </c>
+      <c r="C17" s="361" t="n">
+        <v>972.54</v>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1" s="274">
-      <c r="B18" s="136" t="n"/>
-      <c r="C18" s="93" t="n"/>
+      <c r="A18" s="360" t="inlineStr">
+        <is>
+          <t>Ingredients - Dairy</t>
+        </is>
+      </c>
+      <c r="B18" s="375" t="n">
+        <v>2388.12</v>
+      </c>
+      <c r="C18" s="376" t="n">
+        <v>2732.39</v>
+      </c>
       <c r="D18" s="93" t="n"/>
       <c r="E18" s="93" t="n"/>
       <c r="F18" s="93" t="n"/>
@@ -38365,8 +38561,17 @@
       <c r="I18" s="137" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="274">
-      <c r="B19" s="138" t="n"/>
-      <c r="C19" s="86" t="n"/>
+      <c r="A19" s="360" t="inlineStr">
+        <is>
+          <t>Ingredients - Desserts</t>
+        </is>
+      </c>
+      <c r="B19" s="377" t="n">
+        <v>260</v>
+      </c>
+      <c r="C19" s="378" t="n">
+        <v>0</v>
+      </c>
       <c r="D19" s="86" t="n"/>
       <c r="E19" s="86" t="n"/>
       <c r="F19" s="86" t="n"/>
@@ -38375,8 +38580,17 @@
       <c r="I19" s="139" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1" s="274">
-      <c r="B20" s="136" t="n"/>
-      <c r="C20" s="93" t="n"/>
+      <c r="A20" s="360" t="inlineStr">
+        <is>
+          <t>Ingredients - Fruit</t>
+        </is>
+      </c>
+      <c r="B20" s="375" t="n">
+        <v>794.0599999999999</v>
+      </c>
+      <c r="C20" s="376" t="n">
+        <v>1043.79</v>
+      </c>
       <c r="D20" s="93" t="n"/>
       <c r="E20" s="93" t="n"/>
       <c r="F20" s="93" t="n"/>
@@ -38385,8 +38599,17 @@
       <c r="I20" s="137" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1" s="274">
-      <c r="B21" s="138" t="n"/>
-      <c r="C21" s="86" t="n"/>
+      <c r="A21" s="360" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="B21" s="377" t="n">
+        <v>5617.49</v>
+      </c>
+      <c r="C21" s="378" t="n">
+        <v>12947.35</v>
+      </c>
       <c r="D21" s="86" t="n"/>
       <c r="E21" s="86" t="n"/>
       <c r="F21" s="86" t="n"/>
@@ -38395,8 +38618,17 @@
       <c r="I21" s="139" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1" s="274">
-      <c r="B22" s="136" t="n"/>
-      <c r="C22" s="93" t="n"/>
+      <c r="A22" s="360" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat &amp; Fish</t>
+        </is>
+      </c>
+      <c r="B22" s="375" t="n">
+        <v>1540.7</v>
+      </c>
+      <c r="C22" s="376" t="n">
+        <v>901.4</v>
+      </c>
       <c r="D22" s="93" t="n"/>
       <c r="E22" s="93" t="n"/>
       <c r="F22" s="93" t="n"/>
@@ -38405,8 +38637,17 @@
       <c r="I22" s="137" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1" s="274">
-      <c r="B23" s="140" t="n"/>
-      <c r="C23" s="114" t="n"/>
+      <c r="A23" s="360" t="inlineStr">
+        <is>
+          <t>Ingredients - Other</t>
+        </is>
+      </c>
+      <c r="B23" s="381" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="382" t="n">
+        <v>608</v>
+      </c>
       <c r="D23" s="114" t="n"/>
       <c r="E23" s="114" t="n"/>
       <c r="F23" s="114" t="n"/>
@@ -38415,8 +38656,17 @@
       <c r="I23" s="114" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1" s="274">
-      <c r="B24" s="144" t="n"/>
-      <c r="C24" s="145" t="n"/>
+      <c r="A24" s="360" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="B24" s="383" t="n">
+        <v>3505.54</v>
+      </c>
+      <c r="C24" s="384" t="n">
+        <v>2729.76</v>
+      </c>
       <c r="D24" s="145" t="n"/>
       <c r="E24" s="145" t="n"/>
       <c r="F24" s="145" t="n"/>
@@ -38425,8 +38675,17 @@
       <c r="I24" s="145" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1" s="274">
-      <c r="B25" s="146" t="n"/>
-      <c r="C25" s="147" t="n"/>
+      <c r="A25" s="360" t="inlineStr">
+        <is>
+          <t>Ingredients - Produce</t>
+        </is>
+      </c>
+      <c r="B25" s="385" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="386" t="n">
+        <v>48</v>
+      </c>
       <c r="D25" s="147" t="n"/>
       <c r="E25" s="147" t="n"/>
       <c r="F25" s="147" t="n"/>
@@ -38435,8 +38694,17 @@
       <c r="I25" s="147" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="274">
-      <c r="B26" s="136" t="n"/>
-      <c r="C26" s="93" t="n"/>
+      <c r="A26" s="360" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="B26" s="375" t="n">
+        <v>3439.79</v>
+      </c>
+      <c r="C26" s="376" t="n">
+        <v>3208.63</v>
+      </c>
       <c r="D26" s="93" t="n"/>
       <c r="E26" s="93" t="n"/>
       <c r="F26" s="93" t="n"/>
@@ -38445,8 +38713,17 @@
       <c r="I26" s="137" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="274">
-      <c r="B27" s="138" t="n"/>
-      <c r="C27" s="86" t="n"/>
+      <c r="A27" s="360" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B27" s="377" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="378" t="n">
+        <v>5000</v>
+      </c>
       <c r="D27" s="86" t="n"/>
       <c r="E27" s="86" t="n"/>
       <c r="F27" s="86" t="n"/>
@@ -38455,8 +38732,17 @@
       <c r="I27" s="139" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="274">
-      <c r="B28" s="141" t="n"/>
-      <c r="C28" s="112" t="n"/>
+      <c r="A28" s="360" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="B28" s="387" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="388" t="n">
+        <v>15000</v>
+      </c>
       <c r="D28" s="112" t="n"/>
       <c r="E28" s="112" t="n"/>
       <c r="F28" s="112" t="n"/>
@@ -38465,8 +38751,17 @@
       <c r="I28" s="112" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="274">
-      <c r="B29" s="142" t="n"/>
-      <c r="C29" s="143" t="n"/>
+      <c r="A29" s="360" t="inlineStr">
+        <is>
+          <t>Staff - Advance</t>
+        </is>
+      </c>
+      <c r="B29" s="379" t="n">
+        <v>500</v>
+      </c>
+      <c r="C29" s="380" t="n">
+        <v>0</v>
+      </c>
       <c r="D29" s="143" t="n"/>
       <c r="E29" s="143" t="n"/>
       <c r="F29" s="143" t="n"/>
@@ -38475,18 +38770,30 @@
       <c r="I29" s="143" t="n"/>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="274">
-      <c r="B30" s="298" t="n"/>
-      <c r="C30" s="299" t="n"/>
-      <c r="D30" s="299" t="n"/>
-      <c r="E30" s="299" t="n"/>
-      <c r="F30" s="299" t="n"/>
-      <c r="G30" s="299" t="n"/>
-      <c r="H30" s="299" t="n"/>
-      <c r="I30" s="299" t="n"/>
+      <c r="A30" s="360" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="B30" s="374" t="n">
+        <v>10666</v>
+      </c>
+      <c r="C30" s="361" t="n">
+        <v>14956.65</v>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="274">
-      <c r="B31" s="109" t="n"/>
-      <c r="C31" s="111" t="n"/>
+      <c r="A31" s="360" t="inlineStr">
+        <is>
+          <t>Supermarket / General</t>
+        </is>
+      </c>
+      <c r="B31" s="389" t="n">
+        <v>698</v>
+      </c>
+      <c r="C31" s="378" t="n">
+        <v>2621.1</v>
+      </c>
       <c r="D31" s="111" t="n"/>
       <c r="E31" s="111" t="n"/>
       <c r="F31" s="111" t="n"/>
@@ -38495,8 +38802,17 @@
       <c r="I31" s="148" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="274">
-      <c r="B32" s="115" t="n"/>
-      <c r="C32" s="149" t="n"/>
+      <c r="A32" s="360" t="inlineStr">
+        <is>
+          <t>Supplies / Other</t>
+        </is>
+      </c>
+      <c r="B32" s="390" t="n">
+        <v>628.2</v>
+      </c>
+      <c r="C32" s="391" t="n">
+        <v>3437.65</v>
+      </c>
       <c r="D32" s="149" t="n"/>
       <c r="E32" s="149" t="n"/>
       <c r="F32" s="149" t="n"/>
@@ -38505,8 +38821,17 @@
       <c r="I32" s="149" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="274">
-      <c r="B33" s="109" t="n"/>
-      <c r="C33" s="111" t="n"/>
+      <c r="A33" s="368" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="B33" s="392" t="n">
+        <v>32919.63</v>
+      </c>
+      <c r="C33" s="370" t="n">
+        <v>71774.64999999999</v>
+      </c>
       <c r="D33" s="111" t="n"/>
       <c r="E33" s="111" t="n"/>
       <c r="F33" s="111" t="n"/>
@@ -38527,13 +38852,6 @@
     <row r="35" ht="7.5" customHeight="1" s="274"/>
     <row r="36" ht="19.5" customHeight="1" s="274">
       <c r="B36" s="298" t="n"/>
-      <c r="C36" s="299" t="n"/>
-      <c r="D36" s="299" t="n"/>
-      <c r="E36" s="299" t="n"/>
-      <c r="F36" s="299" t="n"/>
-      <c r="G36" s="299" t="n"/>
-      <c r="H36" s="299" t="n"/>
-      <c r="I36" s="299" t="n"/>
     </row>
     <row r="37" ht="27.75" customHeight="1" s="274">
       <c r="B37" s="279" t="n"/>
@@ -38765,16 +39083,159 @@
       <c r="H59" s="93" t="n"/>
       <c r="I59" s="93" t="n"/>
     </row>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B17:I17"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -9445,17 +9445,39 @@
       <c r="Q37" s="56" t="n"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="274">
-      <c r="B38" s="34" t="n"/>
-      <c r="C38" s="35" t="n"/>
+      <c r="B38" s="356" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C38" s="35" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
       <c r="D38" s="36" t="n"/>
       <c r="E38" s="37" t="n"/>
-      <c r="F38" s="38" t="n"/>
+      <c r="F38" s="38">
+        <f>IFERROR(D38+E38+G38,0)</f>
+        <v/>
+      </c>
       <c r="G38" s="39" t="n"/>
-      <c r="H38" s="40" t="n"/>
-      <c r="I38" s="41" t="n"/>
-      <c r="J38" s="42" t="n"/>
+      <c r="H38" s="40">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B38,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B38+1))</f>
+        <v/>
+      </c>
+      <c r="I38" s="41">
+        <f>IFERROR(F38-H38,0)</f>
+        <v/>
+      </c>
+      <c r="J38" s="42">
+        <f>IFERROR(I38/F38,0)</f>
+        <v/>
+      </c>
       <c r="K38" s="43" t="n"/>
-      <c r="L38" s="9" t="n"/>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>Expenses logged — revenue pending</t>
+        </is>
+      </c>
       <c r="M38" s="12" t="n"/>
       <c r="N38" s="44" t="n"/>
       <c r="O38" s="45" t="n"/>
@@ -15476,8 +15498,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
@@ -26935,54 +26957,219 @@
       </c>
     </row>
     <row r="278">
-      <c r="B278" s="64" t="n"/>
-      <c r="C278" s="69" t="n"/>
-      <c r="D278" s="68" t="n"/>
-      <c r="E278" s="69" t="n"/>
-      <c r="F278" s="70" t="n"/>
-      <c r="G278" s="23" t="n"/>
-      <c r="H278" s="23" t="n"/>
-      <c r="I278" s="55" t="n"/>
+      <c r="B278" s="64" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C278" s="69" t="inlineStr">
+        <is>
+          <t>Jamaica 1LT (6) + Té Fresco 1LT (6) — 12 pzas</t>
+        </is>
+      </c>
+      <c r="D278" s="68" t="inlineStr">
+        <is>
+          <t>Casa Reca</t>
+        </is>
+      </c>
+      <c r="E278" s="69" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F278" s="70" t="n">
+        <v>300</v>
+      </c>
+      <c r="G278" s="23" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H278" s="23" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I278" s="55" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Nota QR-3 · Café Oh lele</t>
+        </is>
+      </c>
     </row>
     <row r="279">
-      <c r="B279" s="64" t="n"/>
-      <c r="C279" s="65" t="n"/>
-      <c r="D279" s="66" t="n"/>
-      <c r="E279" s="65" t="n"/>
-      <c r="F279" s="67" t="n"/>
-      <c r="G279" s="14" t="n"/>
-      <c r="H279" s="14" t="n"/>
-      <c r="I279" s="43" t="n"/>
+      <c r="B279" s="64" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C279" s="65" t="inlineStr">
+        <is>
+          <t>Bolsas papel #5/#6, Vasos plást. 4CH, Tapas</t>
+        </is>
+      </c>
+      <c r="D279" s="66" t="inlineStr">
+        <is>
+          <t>Guimar Polietilenos</t>
+        </is>
+      </c>
+      <c r="E279" s="65" t="inlineStr">
+        <is>
+          <t>Supplies / Other</t>
+        </is>
+      </c>
+      <c r="F279" s="67" t="n">
+        <v>173</v>
+      </c>
+      <c r="G279" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H279" s="14" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I279" s="43" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Débito **28 · Folio XCC37437</t>
+        </is>
+      </c>
     </row>
     <row r="280">
-      <c r="B280" s="64" t="n"/>
-      <c r="C280" s="69" t="n"/>
-      <c r="D280" s="68" t="n"/>
-      <c r="E280" s="69" t="n"/>
-      <c r="F280" s="70" t="n"/>
-      <c r="G280" s="23" t="n"/>
-      <c r="H280" s="23" t="n"/>
-      <c r="I280" s="55" t="n"/>
+      <c r="B280" s="64" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C280" s="69" t="inlineStr">
+        <is>
+          <t>Bistec</t>
+        </is>
+      </c>
+      <c r="D280" s="68" t="inlineStr">
+        <is>
+          <t>Miscelánea LC La Cruz</t>
+        </is>
+      </c>
+      <c r="E280" s="69" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F280" s="70" t="n">
+        <v>285</v>
+      </c>
+      <c r="G280" s="23" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H280" s="23" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I280" s="55" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Getnet **3982 · Aut 354977</t>
+        </is>
+      </c>
     </row>
     <row r="281">
-      <c r="B281" s="64" t="n"/>
-      <c r="C281" s="65" t="n"/>
-      <c r="D281" s="66" t="n"/>
-      <c r="E281" s="65" t="n"/>
-      <c r="F281" s="67" t="n"/>
-      <c r="G281" s="14" t="n"/>
-      <c r="H281" s="14" t="n"/>
-      <c r="I281" s="43" t="n"/>
+      <c r="B281" s="64" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C281" s="65" t="inlineStr">
+        <is>
+          <t>Tortillas Blancas</t>
+        </is>
+      </c>
+      <c r="D281" s="66" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E281" s="65" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F281" s="67" t="n">
+        <v>52</v>
+      </c>
+      <c r="G281" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H281" s="14" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I281" s="43" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>No receipt</t>
+        </is>
+      </c>
     </row>
     <row r="282">
-      <c r="B282" s="64" t="n"/>
-      <c r="C282" s="69" t="n"/>
-      <c r="D282" s="68" t="n"/>
-      <c r="E282" s="69" t="n"/>
-      <c r="F282" s="70" t="n"/>
-      <c r="G282" s="23" t="n"/>
-      <c r="H282" s="23" t="n"/>
-      <c r="I282" s="55" t="n"/>
+      <c r="B282" s="64" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C282" s="69" t="inlineStr">
+        <is>
+          <t>Leche Descremada, Jumex (2), Coca-Cola, CC Sin Azúcar, Crema (6 art.)</t>
+        </is>
+      </c>
+      <c r="D282" s="68" t="inlineStr">
+        <is>
+          <t>Sam’s Club</t>
+        </is>
+      </c>
+      <c r="E282" s="69" t="inlineStr">
+        <is>
+          <t>Supermarket / General</t>
+        </is>
+      </c>
+      <c r="F282" s="70" t="n">
+        <v>1386</v>
+      </c>
+      <c r="G282" s="23" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H282" s="23" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I282" s="55" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Debit MC **82 · Aut 135301 · 12:46</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="B283" s="64" t="n"/>
@@ -38286,7 +38473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O209"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="30" customWidth="1" style="274" min="1" max="1"/>
@@ -39083,156 +39270,6 @@
       <c r="H59" s="93" t="n"/>
       <c r="I59" s="93" t="n"/>
     </row>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -9453,13 +9453,19 @@
           <t>Wed</t>
         </is>
       </c>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="37" t="n"/>
+      <c r="D38" s="36" t="n">
+        <v>2123</v>
+      </c>
+      <c r="E38" s="37" t="n">
+        <v>2281</v>
+      </c>
       <c r="F38" s="38">
         <f>IFERROR(D38+E38+G38,0)</f>
         <v/>
       </c>
-      <c r="G38" s="39" t="n"/>
+      <c r="G38" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="H38" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B38,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B38+1))</f>
         <v/>
@@ -9475,7 +9481,7 @@
       <c r="K38" s="43" t="n"/>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>Expenses logged — revenue pending</t>
+          <t>Cierre 17 Jun + receipts</t>
         </is>
       </c>
       <c r="M38" s="12" t="n"/>
@@ -15498,9 +15504,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -38473,10 +38479,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:O209"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
-    <col width="30" customWidth="1" style="274" min="1" max="1"/>
+    <col width="32" customWidth="1" style="274" min="1" max="1"/>
     <col width="15" customWidth="1" style="274" min="2" max="2"/>
     <col width="15" customWidth="1" style="274" min="3" max="8"/>
     <col width="18" customWidth="1" style="274" min="9" max="9"/>
@@ -38525,7 +38531,7 @@
         <v>52949</v>
       </c>
       <c r="C4" s="361" t="n">
-        <v>53931</v>
+        <v>58335</v>
       </c>
     </row>
     <row r="5" ht="9.75" customHeight="1" s="274">
@@ -38538,7 +38544,7 @@
         <v>32919.63</v>
       </c>
       <c r="C5" s="361" t="n">
-        <v>71774.64999999999</v>
+        <v>73970.64999999999</v>
       </c>
     </row>
     <row r="6" ht="21.75" customHeight="1" s="274">
@@ -38551,7 +38557,7 @@
         <v>20029.37</v>
       </c>
       <c r="C6" s="370" t="n">
-        <v>-17843.65</v>
+        <v>-15635.65</v>
       </c>
     </row>
     <row r="7" ht="7.5" customHeight="1" s="274">
@@ -38564,7 +38570,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="361" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" ht="27.75" customHeight="1" s="274">
@@ -38577,7 +38583,7 @@
         <v>3782.07</v>
       </c>
       <c r="C8" s="371" t="n">
-        <v>3852.21</v>
+        <v>3889</v>
       </c>
       <c r="D8" s="279" t="n"/>
       <c r="E8" s="279" t="n"/>
@@ -38622,7 +38628,7 @@
         <v>26684</v>
       </c>
       <c r="C11" s="361" t="n">
-        <v>27158</v>
+        <v>29281</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" s="274">
@@ -38635,7 +38641,7 @@
         <v>26265</v>
       </c>
       <c r="C12" s="376" t="n">
-        <v>25826</v>
+        <v>28107</v>
       </c>
       <c r="D12" s="93" t="n"/>
       <c r="E12" s="93" t="n"/>
@@ -38676,7 +38682,7 @@
     <row r="15" ht="18" customHeight="1" s="274">
       <c r="A15" s="367" t="inlineStr">
         <is>
-          <t>EXPENSES BY CATEGORY</t>
+          <t>EXPENSES BY CATEGORY (high to low)</t>
         </is>
       </c>
       <c r="B15" s="372" t="inlineStr">
@@ -38699,14 +38705,14 @@
     <row r="16" ht="18" customHeight="1" s="274">
       <c r="A16" s="360" t="inlineStr">
         <is>
-          <t>Ingredients - Beverages</t>
+          <t>Staff - Salary</t>
         </is>
       </c>
       <c r="B16" s="379" t="n">
-        <v>905.23</v>
+        <v>10666</v>
       </c>
       <c r="C16" s="380" t="n">
-        <v>5567.39</v>
+        <v>14956.65</v>
       </c>
       <c r="D16" s="143" t="n"/>
       <c r="E16" s="143" t="n"/>
@@ -38718,27 +38724,27 @@
     <row r="17" ht="19.5" customHeight="1" s="274">
       <c r="A17" s="360" t="inlineStr">
         <is>
-          <t>Ingredients - Bread</t>
+          <t>Ingredients - Meat</t>
         </is>
       </c>
       <c r="B17" s="374" t="n">
-        <v>1976.5</v>
+        <v>5617.49</v>
       </c>
       <c r="C17" s="361" t="n">
-        <v>972.54</v>
+        <v>13232.35</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" s="274">
       <c r="A18" s="360" t="inlineStr">
         <is>
-          <t>Ingredients - Dairy</t>
+          <t>Rent</t>
         </is>
       </c>
       <c r="B18" s="375" t="n">
-        <v>2388.12</v>
+        <v>0</v>
       </c>
       <c r="C18" s="376" t="n">
-        <v>2732.39</v>
+        <v>15000</v>
       </c>
       <c r="D18" s="93" t="n"/>
       <c r="E18" s="93" t="n"/>
@@ -38750,14 +38756,14 @@
     <row r="19" ht="18" customHeight="1" s="274">
       <c r="A19" s="360" t="inlineStr">
         <is>
-          <t>Ingredients - Desserts</t>
+          <t>Ingredients - Beverages</t>
         </is>
       </c>
       <c r="B19" s="377" t="n">
-        <v>260</v>
+        <v>905.23</v>
       </c>
       <c r="C19" s="378" t="n">
-        <v>0</v>
+        <v>5867.39</v>
       </c>
       <c r="D19" s="86" t="n"/>
       <c r="E19" s="86" t="n"/>
@@ -38769,14 +38775,14 @@
     <row r="20" ht="18" customHeight="1" s="274">
       <c r="A20" s="360" t="inlineStr">
         <is>
-          <t>Ingredients - Fruit</t>
+          <t>Ingredients - Vegetables</t>
         </is>
       </c>
       <c r="B20" s="375" t="n">
-        <v>794.0599999999999</v>
+        <v>3439.79</v>
       </c>
       <c r="C20" s="376" t="n">
-        <v>1043.79</v>
+        <v>3208.63</v>
       </c>
       <c r="D20" s="93" t="n"/>
       <c r="E20" s="93" t="n"/>
@@ -38788,14 +38794,14 @@
     <row r="21" ht="18" customHeight="1" s="274">
       <c r="A21" s="360" t="inlineStr">
         <is>
-          <t>Ingredients - Meat</t>
+          <t>Ingredients - Pantry</t>
         </is>
       </c>
       <c r="B21" s="377" t="n">
-        <v>5617.49</v>
+        <v>3505.54</v>
       </c>
       <c r="C21" s="378" t="n">
-        <v>12947.35</v>
+        <v>2729.76</v>
       </c>
       <c r="D21" s="86" t="n"/>
       <c r="E21" s="86" t="n"/>
@@ -38807,14 +38813,14 @@
     <row r="22" ht="18" customHeight="1" s="274">
       <c r="A22" s="360" t="inlineStr">
         <is>
-          <t>Ingredients - Meat &amp; Fish</t>
+          <t>Ingredients - Dairy</t>
         </is>
       </c>
       <c r="B22" s="375" t="n">
-        <v>1540.7</v>
+        <v>2388.12</v>
       </c>
       <c r="C22" s="376" t="n">
-        <v>901.4</v>
+        <v>2732.39</v>
       </c>
       <c r="D22" s="93" t="n"/>
       <c r="E22" s="93" t="n"/>
@@ -38826,14 +38832,14 @@
     <row r="23" ht="18" customHeight="1" s="274">
       <c r="A23" s="360" t="inlineStr">
         <is>
-          <t>Ingredients - Other</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B23" s="381" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="382" t="n">
-        <v>608</v>
+        <v>5000</v>
       </c>
       <c r="D23" s="114" t="n"/>
       <c r="E23" s="114" t="n"/>
@@ -38845,14 +38851,14 @@
     <row r="24" ht="18" customHeight="1" s="274">
       <c r="A24" s="360" t="inlineStr">
         <is>
-          <t>Ingredients - Pantry</t>
+          <t>Supermarket / General</t>
         </is>
       </c>
       <c r="B24" s="383" t="n">
-        <v>3505.54</v>
+        <v>698</v>
       </c>
       <c r="C24" s="384" t="n">
-        <v>2729.76</v>
+        <v>4007.1</v>
       </c>
       <c r="D24" s="145" t="n"/>
       <c r="E24" s="145" t="n"/>
@@ -38864,14 +38870,14 @@
     <row r="25" ht="18" customHeight="1" s="274">
       <c r="A25" s="360" t="inlineStr">
         <is>
-          <t>Ingredients - Produce</t>
+          <t>Supplies / Other</t>
         </is>
       </c>
       <c r="B25" s="385" t="n">
-        <v>0</v>
+        <v>628.2</v>
       </c>
       <c r="C25" s="386" t="n">
-        <v>48</v>
+        <v>3610.65</v>
       </c>
       <c r="D25" s="147" t="n"/>
       <c r="E25" s="147" t="n"/>
@@ -38883,14 +38889,14 @@
     <row r="26" ht="18" customHeight="1" s="274">
       <c r="A26" s="360" t="inlineStr">
         <is>
-          <t>Ingredients - Vegetables</t>
+          <t>Ingredients - Bread</t>
         </is>
       </c>
       <c r="B26" s="375" t="n">
-        <v>3439.79</v>
+        <v>1976.5</v>
       </c>
       <c r="C26" s="376" t="n">
-        <v>3208.63</v>
+        <v>1024.54</v>
       </c>
       <c r="D26" s="93" t="n"/>
       <c r="E26" s="93" t="n"/>
@@ -38902,14 +38908,14 @@
     <row r="27" ht="18" customHeight="1" s="274">
       <c r="A27" s="360" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Ingredients - Meat &amp; Fish</t>
         </is>
       </c>
       <c r="B27" s="377" t="n">
-        <v>0</v>
+        <v>1540.7</v>
       </c>
       <c r="C27" s="378" t="n">
-        <v>5000</v>
+        <v>901.4</v>
       </c>
       <c r="D27" s="86" t="n"/>
       <c r="E27" s="86" t="n"/>
@@ -38921,14 +38927,14 @@
     <row r="28" ht="18" customHeight="1" s="274">
       <c r="A28" s="360" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Ingredients - Fruit</t>
         </is>
       </c>
       <c r="B28" s="387" t="n">
-        <v>0</v>
+        <v>794.0599999999999</v>
       </c>
       <c r="C28" s="388" t="n">
-        <v>15000</v>
+        <v>1043.79</v>
       </c>
       <c r="D28" s="112" t="n"/>
       <c r="E28" s="112" t="n"/>
@@ -38940,14 +38946,14 @@
     <row r="29" ht="18" customHeight="1" s="274">
       <c r="A29" s="360" t="inlineStr">
         <is>
-          <t>Staff - Advance</t>
+          <t>Ingredients - Other</t>
         </is>
       </c>
       <c r="B29" s="379" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="C29" s="380" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="D29" s="143" t="n"/>
       <c r="E29" s="143" t="n"/>
@@ -38959,27 +38965,27 @@
     <row r="30" ht="19.5" customHeight="1" s="274">
       <c r="A30" s="360" t="inlineStr">
         <is>
-          <t>Staff - Salary</t>
+          <t>Staff - Advance</t>
         </is>
       </c>
       <c r="B30" s="374" t="n">
-        <v>10666</v>
+        <v>500</v>
       </c>
       <c r="C30" s="361" t="n">
-        <v>14956.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="274">
       <c r="A31" s="360" t="inlineStr">
         <is>
-          <t>Supermarket / General</t>
+          <t>Ingredients - Desserts</t>
         </is>
       </c>
       <c r="B31" s="389" t="n">
-        <v>698</v>
+        <v>260</v>
       </c>
       <c r="C31" s="378" t="n">
-        <v>2621.1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="111" t="n"/>
       <c r="E31" s="111" t="n"/>
@@ -38991,14 +38997,14 @@
     <row r="32" ht="18" customHeight="1" s="274">
       <c r="A32" s="360" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Ingredients - Produce</t>
         </is>
       </c>
       <c r="B32" s="390" t="n">
-        <v>628.2</v>
+        <v>0</v>
       </c>
       <c r="C32" s="391" t="n">
-        <v>3437.65</v>
+        <v>48</v>
       </c>
       <c r="D32" s="149" t="n"/>
       <c r="E32" s="149" t="n"/>
@@ -39017,7 +39023,7 @@
         <v>32919.63</v>
       </c>
       <c r="C33" s="370" t="n">
-        <v>71774.64999999999</v>
+        <v>73970.64999999999</v>
       </c>
       <c r="D33" s="111" t="n"/>
       <c r="E33" s="111" t="n"/>
@@ -39270,6 +39276,156 @@
       <c r="H59" s="93" t="n"/>
       <c r="I59" s="93" t="n"/>
     </row>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -1169,7 +1169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="393">
+  <cellXfs count="397">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2165,6 +2165,18 @@
     <xf numFmtId="4" fontId="88" fillId="19" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="174" fontId="73" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="73" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="74" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2629,7 +2641,7 @@
     <row r="2" ht="24" customHeight="1" s="274">
       <c r="B2" s="276" t="inlineStr">
         <is>
-          <t>Last updated: 10 Jun 2026  |  Capital, Acquisition, Pre-Opening &amp; Renovation CapEx</t>
+          <t>Last updated: 17 Jun 2026  |  Capital, Acquisition, Pre-Opening &amp; Renovation CapEx</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2842,7 @@
       </c>
       <c r="F13" s="160" t="inlineStr">
         <is>
-          <t>⚠️ PARTIALLY PAID — $134,500 remaining</t>
+          <t>⚠️ PARTIALLY PAID — $118,970 remaining</t>
         </is>
       </c>
       <c r="G13" s="160" t="inlineStr">
@@ -3097,7 +3109,7 @@
       </c>
       <c r="C23" s="172" t="n"/>
       <c r="D23" s="180">
-        <f>D13-SUM(D14:D22)</f>
+        <f>D13-SUM(D14:D22)-D24</f>
         <v/>
       </c>
       <c r="E23" s="172" t="inlineStr">
@@ -3112,11 +3124,38 @@
       </c>
       <c r="G23" s="172" t="inlineStr">
         <is>
-          <t>$390,000 − $255,500 paid = $134,500 remaining</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="25.95" customHeight="1" s="274"/>
+          <t>$390,000 − $255,500 paid − $15,530 electricity offset = $118,970 remaining</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="25.95" customHeight="1" s="274">
+      <c r="B24" s="212" t="inlineStr">
+        <is>
+          <t>Electricity Bill (Mar–May CFE) — paid by Lohith for Previous Owners</t>
+        </is>
+      </c>
+      <c r="C24" s="393" t="n">
+        <v>46190</v>
+      </c>
+      <c r="D24" s="214" t="n">
+        <v>15530</v>
+      </c>
+      <c r="E24" s="213" t="inlineStr">
+        <is>
+          <t>Lohith Reddy</t>
+        </is>
+      </c>
+      <c r="F24" s="213" t="inlineStr">
+        <is>
+          <t>✅ OFFSET vs balance</t>
+        </is>
+      </c>
+      <c r="G24" s="212" t="inlineStr">
+        <is>
+          <t>Prev owners’ liability (pre-handover). Deducted from acquisition balance owed to them.</t>
+        </is>
+      </c>
+    </row>
     <row r="25" ht="22.05" customHeight="1" s="274">
       <c r="B25" s="173" t="inlineStr">
         <is>
@@ -3647,12 +3686,32 @@
       </c>
     </row>
     <row r="50" ht="22.05" customHeight="1" s="274">
-      <c r="B50" s="159" t="n"/>
-      <c r="C50" s="184" t="n"/>
-      <c r="D50" s="184" t="n"/>
-      <c r="E50" s="184" t="n"/>
-      <c r="F50" s="184" t="n"/>
-      <c r="G50" s="282" t="n"/>
+      <c r="B50" s="394" t="inlineStr">
+        <is>
+          <t>Alejandra — License Costs</t>
+        </is>
+      </c>
+      <c r="C50" s="393" t="n">
+        <v>46190</v>
+      </c>
+      <c r="D50" s="214" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E50" s="213" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="F50" s="213" t="inlineStr">
+        <is>
+          <t>Legal / License</t>
+        </is>
+      </c>
+      <c r="G50" s="212" t="inlineStr">
+        <is>
+          <t>License costs — paid by Lohith 17 Jun</t>
+        </is>
+      </c>
       <c r="H50" s="278" t="n"/>
     </row>
     <row r="51" ht="19.95" customHeight="1" s="274">
@@ -3934,12 +3993,32 @@
       </c>
     </row>
     <row r="66" ht="19.95" customHeight="1" s="274">
-      <c r="B66" s="159" t="n"/>
-      <c r="C66" s="159" t="n"/>
-      <c r="D66" s="185" t="n"/>
-      <c r="E66" s="159" t="n"/>
-      <c r="F66" s="159" t="n"/>
-      <c r="G66" s="159" t="n"/>
+      <c r="B66" s="394" t="inlineStr">
+        <is>
+          <t>Letrero 3-D Retroiluminado (illuminated sign)</t>
+        </is>
+      </c>
+      <c r="C66" s="395" t="n">
+        <v>46190</v>
+      </c>
+      <c r="D66" s="396" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E66" s="394" t="inlineStr">
+        <is>
+          <t>POPA Publicidad</t>
+        </is>
+      </c>
+      <c r="F66" s="394" t="inlineStr">
+        <is>
+          <t>Branding / Signage</t>
+        </is>
+      </c>
+      <c r="G66" s="394" t="inlineStr">
+        <is>
+          <t>3D backlit sign + "CAFE RESTAURANT &amp; BAR" letters — paid by Shashirekha · Cotización A0626-560</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="19.95" customHeight="1" s="274">
       <c r="B67" s="212" t="n"/>
@@ -4621,10 +4700,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B24:H24"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B11:H11"/>
   </mergeCells>
@@ -27178,14 +27256,47 @@
       </c>
     </row>
     <row r="283">
-      <c r="B283" s="64" t="n"/>
-      <c r="C283" s="65" t="n"/>
-      <c r="D283" s="66" t="n"/>
-      <c r="E283" s="65" t="n"/>
-      <c r="F283" s="67" t="n"/>
-      <c r="G283" s="14" t="n"/>
-      <c r="H283" s="14" t="n"/>
-      <c r="I283" s="43" t="n"/>
+      <c r="B283" s="64" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C283" s="65" t="inlineStr">
+        <is>
+          <t>Detergente Roma 2kg + Blanqueador Clorox 5.8L</t>
+        </is>
+      </c>
+      <c r="D283" s="66" t="inlineStr">
+        <is>
+          <t>Chedraui Paseo</t>
+        </is>
+      </c>
+      <c r="E283" s="65" t="inlineStr">
+        <is>
+          <t>Supplies / Other</t>
+        </is>
+      </c>
+      <c r="F283" s="67" t="n">
+        <v>157</v>
+      </c>
+      <c r="G283" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H283" s="14" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I283" s="43" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>Débito **3982 · Aut 161026 · cleaning supplies</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="B284" s="64" t="n"/>
@@ -38479,7 +38590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O209"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="32" customWidth="1" style="274" min="1" max="1"/>
@@ -39276,156 +39387,6 @@
       <c r="H59" s="93" t="n"/>
       <c r="I59" s="93" t="n"/>
     </row>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -26,7 +26,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ ddd"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
@@ -38,8 +38,9 @@
     <numFmt numFmtId="172" formatCode="#,##0.##;\(#,##0.##\);&quot;-&quot;"/>
     <numFmt numFmtId="173" formatCode="#,##0;\-#,##0;\-"/>
     <numFmt numFmtId="174" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="175" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="91">
+  <fonts count="92">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -608,6 +609,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="55">
     <fill>
@@ -1169,7 +1175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="397">
+  <cellXfs count="405">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2177,6 +2183,18 @@
     <xf numFmtId="172" fontId="74" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="91" fillId="52" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="88" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="90" fillId="53" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="88" fillId="20" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="88" fillId="20" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="54" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="54" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2620,11 +2638,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H116"/>
+  <dimension ref="B1:H125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="3" customWidth="1" style="274" min="1" max="1"/>
-    <col width="36" customWidth="1" style="274" min="2" max="2"/>
+    <col width="48" customWidth="1" style="274" min="2" max="2"/>
     <col width="18" customWidth="1" style="273" min="3" max="3"/>
     <col width="20" customWidth="1" style="273" min="4" max="6"/>
     <col width="24" customWidth="1" style="274" min="7" max="7"/>
@@ -4697,6 +4715,88 @@
         <is>
           <t>Log renovation/equipment here with Paid By for partner settlement. If also logged in 💸 Expenses, tag category "Capital Expense — …" so it stays OUT of Daily Log operating costs.</t>
         </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  J.  LOHITH — CASH POSITION  (funds managed: own budget + partner transfers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="360" t="inlineStr">
+        <is>
+          <t>My Total Budget</t>
+        </is>
+      </c>
+      <c r="D119" s="361">
+        <f>D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="360" t="inlineStr">
+        <is>
+          <t>+ Kashigoud Transferred to Me</t>
+        </is>
+      </c>
+      <c r="D120" s="361">
+        <f>D34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="360" t="inlineStr">
+        <is>
+          <t>+ Shashirekha Transferred to Me</t>
+        </is>
+      </c>
+      <c r="D121" s="361">
+        <f>D59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="368">
+        <f> Total Funds In</f>
+        <v/>
+      </c>
+      <c r="D122" s="398">
+        <f>D119+D120+D121</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="360" t="inlineStr">
+        <is>
+          <t>− Pre-Opening Expenses (excl. $5k advance)</t>
+        </is>
+      </c>
+      <c r="D123" s="361">
+        <f>D55-D46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="360" t="inlineStr">
+        <is>
+          <t>− Paid to Previous Owners (incl. $15,530 electricity)</t>
+        </is>
+      </c>
+      <c r="D124" s="361">
+        <f>SUM(D14:D22)+D24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="367">
+        <f> REMAINING WITH ME</f>
+        <v/>
+      </c>
+      <c r="D125" s="399">
+        <f>D122-D123-D124</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -6179,30 +6279,63 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="362" t="inlineStr">
+      <c r="A24" s="402" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B24" s="403" t="inlineStr">
+        <is>
+          <t>Customer Transfer — Jun 18 (revenue paid into Lohith account)</t>
+        </is>
+      </c>
+      <c r="C24" s="403" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D24" s="403" t="n"/>
+      <c r="E24" s="404" t="n">
+        <v>400</v>
+      </c>
+      <c r="F24" s="404">
+        <f>IFERROR(F23+D24-E24,0)</f>
+        <v/>
+      </c>
+      <c r="G24" s="403" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H24" s="403" t="inlineStr">
+        <is>
+          <t>Customer paid $400 by transfer into Lohith account — counts against balance owed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="362" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B24" s="362" t="n"/>
-      <c r="C24" s="362" t="n"/>
-      <c r="D24" s="363">
-        <f>SUM(D4:D23)</f>
-        <v/>
-      </c>
-      <c r="E24" s="363">
-        <f>SUM(E4:E23)</f>
-        <v/>
-      </c>
-      <c r="F24" s="363">
-        <f>F23</f>
-        <v/>
-      </c>
-      <c r="G24" s="362">
-        <f>IF(F23&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F23,"#,##0"),IF(F23&lt;0,"Lohith holds $"&amp;TEXT(ABS(F23),"#,##0"),"Zero balance"))</f>
-        <v/>
-      </c>
-      <c r="H24" s="362" t="n"/>
+      <c r="B25" s="362" t="n"/>
+      <c r="C25" s="362" t="n"/>
+      <c r="D25" s="363">
+        <f>SUM(D4:D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="363">
+        <f>SUM(E4:E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="363">
+        <f>F24</f>
+        <v/>
+      </c>
+      <c r="G25" s="362">
+        <f>IF(F24&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F24,"#,##0"),IF(F24&lt;0,"Lohith holds $"&amp;TEXT(ABS(F24),"#,##0"),"Zero balance"))</f>
+        <v/>
+      </c>
+      <c r="H25" s="362" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="364" t="inlineStr">
@@ -9569,17 +9702,45 @@
       <c r="Q38" s="44" t="n"/>
     </row>
     <row r="39" ht="16.5" customHeight="1" s="274">
-      <c r="B39" s="34" t="n"/>
-      <c r="C39" s="47" t="n"/>
-      <c r="D39" s="48" t="n"/>
-      <c r="E39" s="49" t="n"/>
-      <c r="F39" s="50" t="n"/>
-      <c r="G39" s="51" t="n"/>
-      <c r="H39" s="52" t="n"/>
-      <c r="I39" s="53" t="n"/>
-      <c r="J39" s="54" t="n"/>
+      <c r="B39" s="356" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C39" s="47" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D39" s="48" t="n">
+        <v>2211</v>
+      </c>
+      <c r="E39" s="49" t="n">
+        <v>1554</v>
+      </c>
+      <c r="F39" s="50">
+        <f>IFERROR(D39+E39+G39,0)</f>
+        <v/>
+      </c>
+      <c r="G39" s="51" t="n">
+        <v>400</v>
+      </c>
+      <c r="H39" s="52">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B39,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B39+1))</f>
+        <v/>
+      </c>
+      <c r="I39" s="53">
+        <f>IFERROR(F39-H39,0)</f>
+        <v/>
+      </c>
+      <c r="J39" s="54">
+        <f>IFERROR(I39/F39,0)</f>
+        <v/>
+      </c>
       <c r="K39" s="55" t="n"/>
-      <c r="L39" s="18" t="n"/>
+      <c r="L39" s="18" t="inlineStr">
+        <is>
+          <t>Cierre 18 Jun + receipts</t>
+        </is>
+      </c>
       <c r="M39" s="21" t="n"/>
       <c r="N39" s="56" t="n"/>
       <c r="O39" s="57" t="n"/>
@@ -15582,9 +15743,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I2:P2"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B5:P5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:P2"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -27299,74 +27460,305 @@
       </c>
     </row>
     <row r="284">
-      <c r="B284" s="64" t="n"/>
-      <c r="C284" s="69" t="n"/>
-      <c r="D284" s="68" t="n"/>
-      <c r="E284" s="69" t="n"/>
-      <c r="F284" s="70" t="n"/>
-      <c r="G284" s="23" t="n"/>
-      <c r="H284" s="23" t="n"/>
-      <c r="I284" s="55" t="n"/>
+      <c r="B284" s="64" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C284" s="69" t="inlineStr">
+        <is>
+          <t>Yogurt Yalpura 1kg, Tortillas, Bolillo</t>
+        </is>
+      </c>
+      <c r="D284" s="68" t="inlineStr">
+        <is>
+          <t>Chedraui Paseo</t>
+        </is>
+      </c>
+      <c r="E284" s="69" t="inlineStr">
+        <is>
+          <t>Supermarket / General</t>
+        </is>
+      </c>
+      <c r="F284" s="70" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="G284" s="23" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H284" s="23" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I284" s="55" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>Débito BBVA **3982 · Aut 411221</t>
+        </is>
+      </c>
     </row>
     <row r="285">
-      <c r="B285" s="64" t="n"/>
-      <c r="C285" s="65" t="n"/>
-      <c r="D285" s="66" t="n"/>
-      <c r="E285" s="65" t="n"/>
-      <c r="F285" s="67" t="n"/>
-      <c r="G285" s="14" t="n"/>
-      <c r="H285" s="14" t="n"/>
-      <c r="I285" s="43" t="n"/>
+      <c r="B285" s="64" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C285" s="65" t="inlineStr">
+        <is>
+          <t>2 H de Sirloin + Papa Harvest 13.62 kg</t>
+        </is>
+      </c>
+      <c r="D285" s="66" t="inlineStr">
+        <is>
+          <t>ALICO</t>
+        </is>
+      </c>
+      <c r="E285" s="65" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F285" s="67" t="n">
+        <v>1450</v>
+      </c>
+      <c r="G285" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H285" s="14" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I285" s="43" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>Sirloin $760 + Papa $690</t>
+        </is>
+      </c>
     </row>
     <row r="286">
-      <c r="B286" s="64" t="n"/>
-      <c r="C286" s="69" t="n"/>
-      <c r="D286" s="68" t="n"/>
-      <c r="E286" s="69" t="n"/>
-      <c r="F286" s="70" t="n"/>
-      <c r="G286" s="23" t="n"/>
-      <c r="H286" s="23" t="n"/>
-      <c r="I286" s="55" t="n"/>
+      <c r="B286" s="64" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C286" s="69" t="inlineStr">
+        <is>
+          <t>Jamón Pierna, Queso Mozzarella, Chiles Rodajas</t>
+        </is>
+      </c>
+      <c r="D286" s="68" t="inlineStr">
+        <is>
+          <t>San Juan Salchichonerías</t>
+        </is>
+      </c>
+      <c r="E286" s="69" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F286" s="70" t="n">
+        <v>298.13</v>
+      </c>
+      <c r="G286" s="23" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H286" s="23" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I286" s="55" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>Débito MC **3982 · Ticket 0250950</t>
+        </is>
+      </c>
     </row>
     <row r="287">
-      <c r="B287" s="64" t="n"/>
-      <c r="C287" s="65" t="n"/>
-      <c r="D287" s="66" t="n"/>
-      <c r="E287" s="65" t="n"/>
-      <c r="F287" s="67" t="n"/>
-      <c r="G287" s="14" t="n"/>
-      <c r="H287" s="14" t="n"/>
-      <c r="I287" s="43" t="n"/>
+      <c r="B287" s="64" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C287" s="65" t="inlineStr">
+        <is>
+          <t>Costilla $267 + Bistec $96 + Tocino $237</t>
+        </is>
+      </c>
+      <c r="D287" s="66" t="inlineStr">
+        <is>
+          <t>Miscelánea LC La Cruz</t>
+        </is>
+      </c>
+      <c r="E287" s="65" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F287" s="67" t="n">
+        <v>600</v>
+      </c>
+      <c r="G287" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H287" s="14" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I287" s="43" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>Getnet **3982 · Aut 349371</t>
+        </is>
+      </c>
     </row>
     <row r="288">
-      <c r="B288" s="64" t="n"/>
-      <c r="C288" s="69" t="n"/>
-      <c r="D288" s="68" t="n"/>
-      <c r="E288" s="69" t="n"/>
-      <c r="F288" s="70" t="n"/>
-      <c r="G288" s="23" t="n"/>
-      <c r="H288" s="23" t="n"/>
-      <c r="I288" s="55" t="n"/>
+      <c r="B288" s="64" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C288" s="69" t="inlineStr">
+        <is>
+          <t>Lechuga</t>
+        </is>
+      </c>
+      <c r="D288" s="68" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E288" s="69" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F288" s="70" t="n">
+        <v>40</v>
+      </c>
+      <c r="G288" s="23" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H288" s="23" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I288" s="55" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>No receipt</t>
+        </is>
+      </c>
     </row>
     <row r="289">
-      <c r="B289" s="64" t="n"/>
-      <c r="C289" s="65" t="n"/>
-      <c r="D289" s="66" t="n"/>
-      <c r="E289" s="65" t="n"/>
-      <c r="F289" s="67" t="n"/>
-      <c r="G289" s="14" t="n"/>
-      <c r="H289" s="14" t="n"/>
-      <c r="I289" s="43" t="n"/>
+      <c r="B289" s="64" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C289" s="65" t="inlineStr">
+        <is>
+          <t>Telmex Internet (monthly)</t>
+        </is>
+      </c>
+      <c r="D289" s="66" t="inlineStr">
+        <is>
+          <t>Telmex</t>
+        </is>
+      </c>
+      <c r="E289" s="65" t="inlineStr">
+        <is>
+          <t>Utilities / Internet</t>
+        </is>
+      </c>
+      <c r="F289" s="67" t="n">
+        <v>349</v>
+      </c>
+      <c r="G289" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H289" s="14" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="I289" s="43" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>No receipt — internet service</t>
+        </is>
+      </c>
     </row>
     <row r="290">
-      <c r="B290" s="64" t="n"/>
-      <c r="C290" s="69" t="n"/>
-      <c r="D290" s="68" t="n"/>
-      <c r="E290" s="69" t="n"/>
-      <c r="F290" s="70" t="n"/>
-      <c r="G290" s="23" t="n"/>
-      <c r="H290" s="23" t="n"/>
-      <c r="I290" s="55" t="n"/>
+      <c r="B290" s="64" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C290" s="69" t="inlineStr">
+        <is>
+          <t>Aceite La Posada 800 (x4)</t>
+        </is>
+      </c>
+      <c r="D290" s="68" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E290" s="69" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F290" s="70" t="n">
+        <v>104</v>
+      </c>
+      <c r="G290" s="23" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H290" s="23" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I290" s="55" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>Folio 177330 · oil</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="B291" s="64" t="n"/>
@@ -38642,7 +39034,7 @@
         <v>52949</v>
       </c>
       <c r="C4" s="361" t="n">
-        <v>58335</v>
+        <v>62500</v>
       </c>
     </row>
     <row r="5" ht="9.75" customHeight="1" s="274">
@@ -38655,7 +39047,7 @@
         <v>32919.63</v>
       </c>
       <c r="C5" s="361" t="n">
-        <v>73970.64999999999</v>
+        <v>77086.48</v>
       </c>
     </row>
     <row r="6" ht="21.75" customHeight="1" s="274">
@@ -38668,7 +39060,7 @@
         <v>20029.37</v>
       </c>
       <c r="C6" s="370" t="n">
-        <v>-15635.65</v>
+        <v>-14586.48</v>
       </c>
     </row>
     <row r="7" ht="7.5" customHeight="1" s="274">
@@ -38681,7 +39073,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="361" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" ht="27.75" customHeight="1" s="274">
@@ -38694,7 +39086,7 @@
         <v>3782.07</v>
       </c>
       <c r="C8" s="371" t="n">
-        <v>3889</v>
+        <v>3906.25</v>
       </c>
       <c r="D8" s="279" t="n"/>
       <c r="E8" s="279" t="n"/>
@@ -38739,7 +39131,7 @@
         <v>26684</v>
       </c>
       <c r="C11" s="361" t="n">
-        <v>29281</v>
+        <v>31492</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" s="274">
@@ -38752,7 +39144,7 @@
         <v>26265</v>
       </c>
       <c r="C12" s="376" t="n">
-        <v>28107</v>
+        <v>29661</v>
       </c>
       <c r="D12" s="93" t="n"/>
       <c r="E12" s="93" t="n"/>
@@ -38771,7 +39163,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="378" t="n">
-        <v>947</v>
+        <v>1347</v>
       </c>
       <c r="D13" s="86" t="n"/>
       <c r="E13" s="86" t="n"/>
@@ -38842,7 +39234,7 @@
         <v>5617.49</v>
       </c>
       <c r="C17" s="361" t="n">
-        <v>13232.35</v>
+        <v>15580.48</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" s="274">
@@ -38893,7 +39285,7 @@
         <v>3439.79</v>
       </c>
       <c r="C20" s="376" t="n">
-        <v>3208.63</v>
+        <v>3248.63</v>
       </c>
       <c r="D20" s="93" t="n"/>
       <c r="E20" s="93" t="n"/>
@@ -38912,7 +39304,7 @@
         <v>3505.54</v>
       </c>
       <c r="C21" s="378" t="n">
-        <v>2729.76</v>
+        <v>2833.76</v>
       </c>
       <c r="D21" s="86" t="n"/>
       <c r="E21" s="86" t="n"/>
@@ -38969,7 +39361,7 @@
         <v>698</v>
       </c>
       <c r="C24" s="384" t="n">
-        <v>4007.1</v>
+        <v>4124.8</v>
       </c>
       <c r="D24" s="145" t="n"/>
       <c r="E24" s="145" t="n"/>
@@ -38988,7 +39380,7 @@
         <v>628.2</v>
       </c>
       <c r="C25" s="386" t="n">
-        <v>3610.65</v>
+        <v>3767.65</v>
       </c>
       <c r="D25" s="147" t="n"/>
       <c r="E25" s="147" t="n"/>
@@ -39089,14 +39481,14 @@
     <row r="31" ht="18" customHeight="1" s="274">
       <c r="A31" s="360" t="inlineStr">
         <is>
-          <t>Ingredients - Desserts</t>
+          <t>Utilities / Internet</t>
         </is>
       </c>
       <c r="B31" s="389" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="C31" s="378" t="n">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="D31" s="111" t="n"/>
       <c r="E31" s="111" t="n"/>
@@ -39108,14 +39500,14 @@
     <row r="32" ht="18" customHeight="1" s="274">
       <c r="A32" s="360" t="inlineStr">
         <is>
-          <t>Ingredients - Produce</t>
+          <t>Ingredients - Desserts</t>
         </is>
       </c>
       <c r="B32" s="390" t="n">
+        <v>260</v>
+      </c>
+      <c r="C32" s="391" t="n">
         <v>0</v>
-      </c>
-      <c r="C32" s="391" t="n">
-        <v>48</v>
       </c>
       <c r="D32" s="149" t="n"/>
       <c r="E32" s="149" t="n"/>
@@ -39127,14 +39519,14 @@
     <row r="33" ht="18" customHeight="1" s="274">
       <c r="A33" s="368" t="inlineStr">
         <is>
-          <t>TOTAL EXPENSES</t>
+          <t>Ingredients - Produce</t>
         </is>
       </c>
       <c r="B33" s="392" t="n">
-        <v>32919.63</v>
+        <v>0</v>
       </c>
       <c r="C33" s="370" t="n">
-        <v>73970.64999999999</v>
+        <v>48</v>
       </c>
       <c r="D33" s="111" t="n"/>
       <c r="E33" s="111" t="n"/>
@@ -39144,8 +39536,17 @@
       <c r="I33" s="148" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="274">
-      <c r="B34" s="115" t="n"/>
-      <c r="C34" s="149" t="n"/>
+      <c r="A34" s="368" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="B34" s="400" t="n">
+        <v>32919.63</v>
+      </c>
+      <c r="C34" s="401" t="n">
+        <v>77086.48</v>
+      </c>
       <c r="D34" s="149" t="n"/>
       <c r="E34" s="149" t="n"/>
       <c r="F34" s="149" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -25,7 +25,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="12">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ ddd"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
@@ -38,6 +38,7 @@
     <numFmt numFmtId="173" formatCode="#,##0;\-#,##0;\-"/>
     <numFmt numFmtId="174" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="175" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="176" formatCode="dd-mmm-yyyy"/>
   </numFmts>
   <fonts count="98">
     <font>
@@ -976,7 +977,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1283,11 +1284,15 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <right/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19"/>
   </cellStyleXfs>
-  <cellXfs count="382">
+  <cellXfs count="393">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2272,6 +2277,37 @@
     <xf numFmtId="3" fontId="94" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="176" fontId="51" fillId="19" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="95" fillId="57" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="37" fillId="19" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="19" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="19" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="41" fillId="19" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="17" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="43" fillId="19" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="44" fillId="19" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="19" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9518,17 +9554,45 @@
       <c r="Q41" s="56" t="n"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="278">
-      <c r="B42" s="34" t="n"/>
-      <c r="C42" s="35" t="n"/>
-      <c r="D42" s="36" t="n"/>
-      <c r="E42" s="37" t="n"/>
-      <c r="F42" s="38" t="n"/>
-      <c r="G42" s="39" t="n"/>
-      <c r="H42" s="40" t="n"/>
-      <c r="I42" s="41" t="n"/>
-      <c r="J42" s="42" t="n"/>
-      <c r="K42" s="43" t="n"/>
-      <c r="L42" s="9" t="n"/>
+      <c r="B42" s="385" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C42" s="386" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="D42" s="387" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="38">
+        <f>IFERROR(D42+E42+G42,0)</f>
+        <v/>
+      </c>
+      <c r="G42" s="388" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="389">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B42,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B42+1))</f>
+        <v/>
+      </c>
+      <c r="I42" s="390">
+        <f>IFERROR(F42-H42,0)</f>
+        <v/>
+      </c>
+      <c r="J42" s="391">
+        <f>IFERROR(I42/F42,0)</f>
+        <v/>
+      </c>
+      <c r="K42" s="251" t="n"/>
+      <c r="L42" s="392" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
       <c r="M42" s="12" t="n"/>
       <c r="N42" s="44" t="n"/>
       <c r="O42" s="45" t="n"/>
@@ -15477,8 +15541,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I2:P2"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:P2"/>
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
@@ -28140,184 +28204,762 @@
       </c>
     </row>
     <row r="306">
-      <c r="B306" s="64" t="n"/>
-      <c r="C306" s="69" t="n"/>
-      <c r="D306" s="68" t="n"/>
-      <c r="E306" s="69" t="n"/>
-      <c r="F306" s="70" t="n"/>
-      <c r="G306" s="23" t="n"/>
-      <c r="H306" s="23" t="n"/>
-      <c r="I306" s="55" t="n"/>
+      <c r="B306" s="382" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C306" s="252" t="inlineStr">
+        <is>
+          <t>Cuchara de Moka 6pcs 10.5cm (x2)</t>
+        </is>
+      </c>
+      <c r="D306" s="253" t="inlineStr">
+        <is>
+          <t>Small China</t>
+        </is>
+      </c>
+      <c r="E306" s="252" t="inlineStr">
+        <is>
+          <t>Kitchen Supplies</t>
+        </is>
+      </c>
+      <c r="F306" s="70" t="n">
+        <v>178</v>
+      </c>
+      <c r="G306" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H306" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I306" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J306" s="383" t="inlineStr">
+        <is>
+          <t>Tarjeta crédito · serial D2606031530065 (back-dated 3 Jun)</t>
+        </is>
+      </c>
     </row>
     <row r="307">
-      <c r="B307" s="64" t="n"/>
-      <c r="C307" s="65" t="n"/>
-      <c r="D307" s="66" t="n"/>
-      <c r="E307" s="65" t="n"/>
-      <c r="F307" s="67" t="n"/>
-      <c r="G307" s="14" t="n"/>
-      <c r="H307" s="14" t="n"/>
-      <c r="I307" s="43" t="n"/>
+      <c r="B307" s="382" t="n">
+        <v>46193</v>
+      </c>
+      <c r="C307" s="248" t="inlineStr">
+        <is>
+          <t>Topo Chico (2 packs)</t>
+        </is>
+      </c>
+      <c r="D307" s="249" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="E307" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F307" s="67" t="n">
+        <v>464</v>
+      </c>
+      <c r="G307" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H307" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I307" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J307" s="383" t="inlineStr">
+        <is>
+          <t>No receipt</t>
+        </is>
+      </c>
     </row>
     <row r="308">
-      <c r="B308" s="64" t="n"/>
-      <c r="C308" s="69" t="n"/>
-      <c r="D308" s="68" t="n"/>
-      <c r="E308" s="69" t="n"/>
-      <c r="F308" s="70" t="n"/>
-      <c r="G308" s="23" t="n"/>
-      <c r="H308" s="23" t="n"/>
-      <c r="I308" s="55" t="n"/>
+      <c r="B308" s="382" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C308" s="252" t="inlineStr">
+        <is>
+          <t>Soft Restaurant — POS app subscription</t>
+        </is>
+      </c>
+      <c r="D308" s="253" t="inlineStr">
+        <is>
+          <t>Soft Restaurant</t>
+        </is>
+      </c>
+      <c r="E308" s="252" t="inlineStr">
+        <is>
+          <t>Software / Subscription</t>
+        </is>
+      </c>
+      <c r="F308" s="70" t="n">
+        <v>810</v>
+      </c>
+      <c r="G308" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H308" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I308" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J308" s="383" t="inlineStr">
+        <is>
+          <t>No receipt · POS software subscription</t>
+        </is>
+      </c>
     </row>
     <row r="309">
-      <c r="B309" s="64" t="n"/>
-      <c r="C309" s="65" t="n"/>
-      <c r="D309" s="66" t="n"/>
-      <c r="E309" s="65" t="n"/>
-      <c r="F309" s="67" t="n"/>
-      <c r="G309" s="14" t="n"/>
-      <c r="H309" s="14" t="n"/>
-      <c r="I309" s="43" t="n"/>
+      <c r="B309" s="382" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C309" s="248" t="inlineStr">
+        <is>
+          <t>Morrón surtido, espinaca, betabel</t>
+        </is>
+      </c>
+      <c r="D309" s="249" t="inlineStr">
+        <is>
+          <t>Verduras Selectas Oscar</t>
+        </is>
+      </c>
+      <c r="E309" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F309" s="67" t="n">
+        <v>84</v>
+      </c>
+      <c r="G309" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H309" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I309" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J309" s="383" t="inlineStr">
+        <is>
+          <t>Mercado de Abastos</t>
+        </is>
+      </c>
     </row>
     <row r="310">
-      <c r="B310" s="64" t="n"/>
-      <c r="C310" s="69" t="n"/>
-      <c r="D310" s="68" t="n"/>
-      <c r="E310" s="69" t="n"/>
-      <c r="F310" s="70" t="n"/>
-      <c r="G310" s="23" t="n"/>
-      <c r="H310" s="23" t="n"/>
-      <c r="I310" s="55" t="n"/>
+      <c r="B310" s="382" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C310" s="252" t="inlineStr">
+        <is>
+          <t>Champiñón 1.02kg + Manzana Mexicana 1.13kg</t>
+        </is>
+      </c>
+      <c r="D310" s="253" t="inlineStr">
+        <is>
+          <t>Mercado de Abastos</t>
+        </is>
+      </c>
+      <c r="E310" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F310" s="70" t="n">
+        <v>153.62</v>
+      </c>
+      <c r="G310" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H310" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I310" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J310" s="383" t="inlineStr">
+        <is>
+          <t>Ticket 26351 (incl. apple)</t>
+        </is>
+      </c>
     </row>
     <row r="311">
-      <c r="B311" s="64" t="n"/>
-      <c r="C311" s="65" t="n"/>
-      <c r="D311" s="66" t="n"/>
-      <c r="E311" s="65" t="n"/>
-      <c r="F311" s="67" t="n"/>
-      <c r="G311" s="14" t="n"/>
-      <c r="H311" s="14" t="n"/>
-      <c r="I311" s="43" t="n"/>
+      <c r="B311" s="382" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C311" s="248" t="inlineStr">
+        <is>
+          <t>Huevo (2 conos)</t>
+        </is>
+      </c>
+      <c r="D311" s="249" t="inlineStr">
+        <is>
+          <t>Jaime (Mercado Abastos)</t>
+        </is>
+      </c>
+      <c r="E311" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Eggs</t>
+        </is>
+      </c>
+      <c r="F311" s="67" t="n">
+        <v>102</v>
+      </c>
+      <c r="G311" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H311" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I311" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J311" s="383" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="B312" s="64" t="n"/>
-      <c r="C312" s="69" t="n"/>
-      <c r="D312" s="68" t="n"/>
-      <c r="E312" s="69" t="n"/>
-      <c r="F312" s="70" t="n"/>
-      <c r="G312" s="23" t="n"/>
-      <c r="H312" s="23" t="n"/>
-      <c r="I312" s="55" t="n"/>
+      <c r="B312" s="382" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C312" s="252" t="inlineStr">
+        <is>
+          <t>Zanahoria, jalapeño, serrano, cebolla</t>
+        </is>
+      </c>
+      <c r="D312" s="253" t="inlineStr">
+        <is>
+          <t>Mi Joven</t>
+        </is>
+      </c>
+      <c r="E312" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F312" s="70" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="G312" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H312" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I312" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J312" s="383" t="inlineStr">
+        <is>
+          <t>Folio 19465</t>
+        </is>
+      </c>
     </row>
     <row r="313">
-      <c r="B313" s="64" t="n"/>
-      <c r="C313" s="65" t="n"/>
-      <c r="D313" s="66" t="n"/>
-      <c r="E313" s="65" t="n"/>
-      <c r="F313" s="67" t="n"/>
-      <c r="G313" s="14" t="n"/>
-      <c r="H313" s="14" t="n"/>
-      <c r="I313" s="43" t="n"/>
+      <c r="B313" s="382" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C313" s="248" t="inlineStr">
+        <is>
+          <t>Calabaza 1.7kg</t>
+        </is>
+      </c>
+      <c r="D313" s="249" t="inlineStr">
+        <is>
+          <t>Mi Joven</t>
+        </is>
+      </c>
+      <c r="E313" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F313" s="67" t="n">
+        <v>34</v>
+      </c>
+      <c r="G313" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H313" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I313" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J313" s="383" t="inlineStr">
+        <is>
+          <t>Folio 19466</t>
+        </is>
+      </c>
     </row>
     <row r="314">
-      <c r="B314" s="64" t="n"/>
-      <c r="C314" s="69" t="n"/>
-      <c r="D314" s="68" t="n"/>
-      <c r="E314" s="69" t="n"/>
-      <c r="F314" s="70" t="n"/>
-      <c r="G314" s="23" t="n"/>
-      <c r="H314" s="23" t="n"/>
-      <c r="I314" s="55" t="n"/>
+      <c r="B314" s="382" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C314" s="252" t="inlineStr">
+        <is>
+          <t>Tomate, limón, pepino, jícama</t>
+        </is>
+      </c>
+      <c r="D314" s="253" t="inlineStr">
+        <is>
+          <t>Mercado de Abastos</t>
+        </is>
+      </c>
+      <c r="E314" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F314" s="70" t="n">
+        <v>240</v>
+      </c>
+      <c r="G314" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H314" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I314" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J314" s="383" t="inlineStr">
+        <is>
+          <t>Handwritten note</t>
+        </is>
+      </c>
     </row>
     <row r="315">
-      <c r="B315" s="64" t="n"/>
-      <c r="C315" s="65" t="n"/>
-      <c r="D315" s="66" t="n"/>
-      <c r="E315" s="65" t="n"/>
-      <c r="F315" s="67" t="n"/>
-      <c r="G315" s="14" t="n"/>
-      <c r="H315" s="14" t="n"/>
-      <c r="I315" s="43" t="n"/>
+      <c r="B315" s="382" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C315" s="248" t="inlineStr">
+        <is>
+          <t>Jitomate 7kg</t>
+        </is>
+      </c>
+      <c r="D315" s="249" t="inlineStr">
+        <is>
+          <t>Frutas Finas Ana Pao</t>
+        </is>
+      </c>
+      <c r="E315" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F315" s="67" t="n">
+        <v>105</v>
+      </c>
+      <c r="G315" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H315" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I315" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J315" s="383" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="B316" s="64" t="n"/>
-      <c r="C316" s="69" t="n"/>
-      <c r="D316" s="68" t="n"/>
-      <c r="E316" s="69" t="n"/>
-      <c r="F316" s="70" t="n"/>
-      <c r="G316" s="23" t="n"/>
-      <c r="H316" s="23" t="n"/>
-      <c r="I316" s="55" t="n"/>
+      <c r="B316" s="382" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C316" s="252" t="inlineStr">
+        <is>
+          <t>Sandía, papaya, plátano, melón</t>
+        </is>
+      </c>
+      <c r="D316" s="253" t="inlineStr">
+        <is>
+          <t>Mercado de Abastos</t>
+        </is>
+      </c>
+      <c r="E316" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Fruit</t>
+        </is>
+      </c>
+      <c r="F316" s="70" t="n">
+        <v>208</v>
+      </c>
+      <c r="G316" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H316" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I316" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J316" s="383" t="inlineStr">
+        <is>
+          <t>Handwritten note</t>
+        </is>
+      </c>
     </row>
     <row r="317">
-      <c r="B317" s="64" t="n"/>
-      <c r="C317" s="65" t="n"/>
-      <c r="D317" s="66" t="n"/>
-      <c r="E317" s="65" t="n"/>
-      <c r="F317" s="67" t="n"/>
-      <c r="G317" s="14" t="n"/>
-      <c r="H317" s="14" t="n"/>
-      <c r="I317" s="43" t="n"/>
+      <c r="B317" s="382" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C317" s="248" t="inlineStr">
+        <is>
+          <t>Papa (3 x $35)</t>
+        </is>
+      </c>
+      <c r="D317" s="249" t="inlineStr">
+        <is>
+          <t>Papas San Miguel</t>
+        </is>
+      </c>
+      <c r="E317" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F317" s="67" t="n">
+        <v>105</v>
+      </c>
+      <c r="G317" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H317" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I317" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J317" s="383" t="inlineStr"/>
     </row>
     <row r="318">
-      <c r="B318" s="64" t="n"/>
-      <c r="C318" s="69" t="n"/>
-      <c r="D318" s="68" t="n"/>
-      <c r="E318" s="69" t="n"/>
-      <c r="F318" s="70" t="n"/>
-      <c r="G318" s="23" t="n"/>
-      <c r="H318" s="23" t="n"/>
-      <c r="I318" s="55" t="n"/>
+      <c r="B318" s="382" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C318" s="252" t="inlineStr">
+        <is>
+          <t>Aguacate Hass + habanero</t>
+        </is>
+      </c>
+      <c r="D318" s="253" t="inlineStr">
+        <is>
+          <t>Rey Tacamba</t>
+        </is>
+      </c>
+      <c r="E318" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F318" s="70" t="n">
+        <v>214</v>
+      </c>
+      <c r="G318" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H318" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I318" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J318" s="383" t="inlineStr">
+        <is>
+          <t>Hass $94 + habanero $120</t>
+        </is>
+      </c>
     </row>
     <row r="319">
-      <c r="B319" s="64" t="n"/>
-      <c r="C319" s="65" t="n"/>
-      <c r="D319" s="66" t="n"/>
-      <c r="E319" s="65" t="n"/>
-      <c r="F319" s="67" t="n"/>
-      <c r="G319" s="14" t="n"/>
-      <c r="H319" s="14" t="n"/>
-      <c r="I319" s="43" t="n"/>
+      <c r="B319" s="382" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C319" s="248" t="inlineStr">
+        <is>
+          <t>Chicharrón (1 hoja)</t>
+        </is>
+      </c>
+      <c r="D319" s="249" t="inlineStr">
+        <is>
+          <t>Chicharronería San Nicolás</t>
+        </is>
+      </c>
+      <c r="E319" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F319" s="67" t="n">
+        <v>89</v>
+      </c>
+      <c r="G319" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H319" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I319" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J319" s="383" t="inlineStr">
+        <is>
+          <t>Corrected to \ per Reddy (was read as 899)</t>
+        </is>
+      </c>
     </row>
     <row r="320">
-      <c r="B320" s="64" t="n"/>
-      <c r="C320" s="69" t="n"/>
-      <c r="D320" s="68" t="n"/>
-      <c r="E320" s="69" t="n"/>
-      <c r="F320" s="70" t="n"/>
-      <c r="G320" s="23" t="n"/>
-      <c r="H320" s="23" t="n"/>
-      <c r="I320" s="55" t="n"/>
+      <c r="B320" s="382" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C320" s="252" t="inlineStr">
+        <is>
+          <t>Vasos, tapas, cucharas, biocup vaso papel</t>
+        </is>
+      </c>
+      <c r="D320" s="253" t="inlineStr">
+        <is>
+          <t>MPPD - Materias Primas Plasticos</t>
+        </is>
+      </c>
+      <c r="E320" s="252" t="inlineStr">
+        <is>
+          <t>Packaging / Disposables</t>
+        </is>
+      </c>
+      <c r="F320" s="70" t="n">
+        <v>295.73</v>
+      </c>
+      <c r="G320" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H320" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I320" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J320" s="383" t="inlineStr">
+        <is>
+          <t>Folio 381088</t>
+        </is>
+      </c>
     </row>
     <row r="321">
-      <c r="B321" s="64" t="n"/>
-      <c r="C321" s="65" t="n"/>
-      <c r="D321" s="66" t="n"/>
-      <c r="E321" s="65" t="n"/>
-      <c r="F321" s="67" t="n"/>
-      <c r="G321" s="14" t="n"/>
-      <c r="H321" s="14" t="n"/>
-      <c r="I321" s="43" t="n"/>
+      <c r="B321" s="382" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C321" s="248" t="inlineStr">
+        <is>
+          <t>Cilantro, hierbabuena, lechuga italiana</t>
+        </is>
+      </c>
+      <c r="D321" s="249" t="inlineStr">
+        <is>
+          <t>Hnos. Labra's</t>
+        </is>
+      </c>
+      <c r="E321" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F321" s="67" t="n">
+        <v>215</v>
+      </c>
+      <c r="G321" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H321" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I321" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J321" s="383" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="B322" s="64" t="n"/>
-      <c r="C322" s="69" t="n"/>
-      <c r="D322" s="68" t="n"/>
-      <c r="E322" s="69" t="n"/>
-      <c r="F322" s="70" t="n"/>
-      <c r="G322" s="23" t="n"/>
-      <c r="H322" s="23" t="n"/>
-      <c r="I322" s="55" t="n"/>
+      <c r="B322" s="382" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C322" s="252" t="inlineStr">
+        <is>
+          <t>Pens (office/stationery)</t>
+        </is>
+      </c>
+      <c r="D322" s="253" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E322" s="252" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F322" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="G322" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H322" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I322" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J322" s="383" t="inlineStr">
+        <is>
+          <t>No receipt</t>
+        </is>
+      </c>
     </row>
     <row r="323">
-      <c r="B323" s="64" t="n"/>
-      <c r="C323" s="65" t="n"/>
-      <c r="D323" s="66" t="n"/>
-      <c r="E323" s="65" t="n"/>
-      <c r="F323" s="67" t="n"/>
-      <c r="G323" s="14" t="n"/>
-      <c r="H323" s="14" t="n"/>
-      <c r="I323" s="43" t="n"/>
+      <c r="B323" s="382" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C323" s="248" t="inlineStr">
+        <is>
+          <t>Restaurant Command booklet (comandas)</t>
+        </is>
+      </c>
+      <c r="D323" s="249" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E323" s="248" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F323" s="67" t="n">
+        <v>59</v>
+      </c>
+      <c r="G323" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H323" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I323" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J323" s="383" t="inlineStr">
+        <is>
+          <t>No receipt — order pads</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="B324" s="64" t="n"/>
@@ -39855,7 +40497,7 @@
     <row r="21">
       <c r="A21" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Pantry</t>
+          <t>Ingredients - Beverages</t>
         </is>
       </c>
       <c r="B21" s="378">
@@ -39879,7 +40521,7 @@
     <row r="22">
       <c r="A22" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Beverages</t>
+          <t>Ingredients - Pantry</t>
         </is>
       </c>
       <c r="B22" s="378">
@@ -40071,7 +40713,7 @@
     <row r="30">
       <c r="A30" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Other</t>
+          <t>Software / Subscription</t>
         </is>
       </c>
       <c r="B30" s="378">
@@ -40095,7 +40737,7 @@
     <row r="31">
       <c r="A31" s="380" t="inlineStr">
         <is>
-          <t>Staff - Advance</t>
+          <t>Ingredients - Other</t>
         </is>
       </c>
       <c r="B31" s="378">
@@ -40119,7 +40761,7 @@
     <row r="32">
       <c r="A32" s="380" t="inlineStr">
         <is>
-          <t>Utilities / Internet</t>
+          <t>Staff - Advance</t>
         </is>
       </c>
       <c r="B32" s="378">
@@ -40143,7 +40785,7 @@
     <row r="33">
       <c r="A33" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Desserts</t>
+          <t>Utilities / Internet</t>
         </is>
       </c>
       <c r="B33" s="378">
@@ -40167,7 +40809,7 @@
     <row r="34">
       <c r="A34" s="380" t="inlineStr">
         <is>
-          <t>Staff - Propinas</t>
+          <t>Packaging / Disposables</t>
         </is>
       </c>
       <c r="B34" s="378">
@@ -40191,7 +40833,7 @@
     <row r="35">
       <c r="A35" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Produce</t>
+          <t>Ingredients - Desserts</t>
         </is>
       </c>
       <c r="B35" s="378">
@@ -40213,17 +40855,17 @@
       <c r="L35" s="374" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="377" t="inlineStr">
-        <is>
-          <t>TOTAL EXPENSES</t>
-        </is>
-      </c>
-      <c r="B36" s="379">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
-        <v/>
-      </c>
-      <c r="C36" s="379">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+      <c r="A36" s="380" t="inlineStr">
+        <is>
+          <t>Kitchen Supplies</t>
+        </is>
+      </c>
+      <c r="B36" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A36,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <v/>
+      </c>
+      <c r="C36" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A36,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D36" s="374" t="n"/>
@@ -40237,17 +40879,17 @@
       <c r="L36" s="374" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="377" t="inlineStr">
-        <is>
-          <t>NET PROFIT / LOSS</t>
-        </is>
-      </c>
-      <c r="B37" s="379">
-        <f>B4-B36</f>
-        <v/>
-      </c>
-      <c r="C37" s="379">
-        <f>C4-C36</f>
+      <c r="A37" s="380" t="inlineStr">
+        <is>
+          <t>Staff - Propinas</t>
+        </is>
+      </c>
+      <c r="B37" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A37,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <v/>
+      </c>
+      <c r="C37" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A37,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D37" s="374" t="n"/>
@@ -40261,9 +40903,19 @@
       <c r="L37" s="374" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="374" t="n"/>
-      <c r="B38" s="374" t="n"/>
-      <c r="C38" s="374" t="n"/>
+      <c r="A38" s="380" t="inlineStr">
+        <is>
+          <t>Ingredients - Eggs</t>
+        </is>
+      </c>
+      <c r="B38" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A38,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <v/>
+      </c>
+      <c r="C38" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A38,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <v/>
+      </c>
       <c r="D38" s="374" t="n"/>
       <c r="E38" s="374" t="n"/>
       <c r="F38" s="374" t="n"/>
@@ -40275,9 +40927,19 @@
       <c r="L38" s="374" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="374" t="n"/>
-      <c r="B39" s="374" t="n"/>
-      <c r="C39" s="374" t="n"/>
+      <c r="A39" s="380" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="B39" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A39,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <v/>
+      </c>
+      <c r="C39" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A39,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <v/>
+      </c>
       <c r="D39" s="374" t="n"/>
       <c r="E39" s="374" t="n"/>
       <c r="F39" s="374" t="n"/>
@@ -40289,9 +40951,19 @@
       <c r="L39" s="374" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="374" t="n"/>
-      <c r="B40" s="374" t="n"/>
-      <c r="C40" s="374" t="n"/>
+      <c r="A40" s="380" t="inlineStr">
+        <is>
+          <t>Ingredients - Produce</t>
+        </is>
+      </c>
+      <c r="B40" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A40,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <v/>
+      </c>
+      <c r="C40" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A40,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <v/>
+      </c>
       <c r="D40" s="374" t="n"/>
       <c r="E40" s="374" t="n"/>
       <c r="F40" s="374" t="n"/>
@@ -40303,9 +40975,19 @@
       <c r="L40" s="374" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="374" t="n"/>
-      <c r="B41" s="374" t="n"/>
-      <c r="C41" s="374" t="n"/>
+      <c r="A41" s="377" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="B41" s="379">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <v/>
+      </c>
+      <c r="C41" s="379">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <v/>
+      </c>
       <c r="D41" s="374" t="n"/>
       <c r="E41" s="374" t="n"/>
       <c r="F41" s="374" t="n"/>
@@ -40317,9 +40999,19 @@
       <c r="L41" s="374" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="374" t="n"/>
-      <c r="B42" s="374" t="n"/>
-      <c r="C42" s="374" t="n"/>
+      <c r="A42" s="377" t="inlineStr">
+        <is>
+          <t>NET PROFIT / LOSS</t>
+        </is>
+      </c>
+      <c r="B42" s="379">
+        <f>B4-B41</f>
+        <v/>
+      </c>
+      <c r="C42" s="379">
+        <f>C4-C41</f>
+        <v/>
+      </c>
       <c r="D42" s="374" t="n"/>
       <c r="E42" s="374" t="n"/>
       <c r="F42" s="374" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -15541,9 +15541,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -1292,7 +1292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19"/>
   </cellStyleXfs>
-  <cellXfs count="393">
+  <cellXfs count="397">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2308,6 +2308,16 @@
     <xf numFmtId="166" fontId="19" fillId="19" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="72" fillId="40" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="72" fillId="40" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="73" fillId="40" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="40" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2751,7 +2761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H144"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="3" customWidth="1" style="278" min="1" max="1"/>
@@ -2973,7 +2983,7 @@
       </c>
       <c r="F13" s="138" t="inlineStr">
         <is>
-          <t>⚠️ PARTIALLY PAID — $68,235 remaining</t>
+          <t>⚠️ PARTIALLY PAID — $8,235 remaining</t>
         </is>
       </c>
       <c r="G13" s="138" t="inlineStr">
@@ -3317,12 +3327,33 @@
       </c>
     </row>
     <row r="26" ht="19.95" customHeight="1" s="278">
-      <c r="B26" s="149" t="n"/>
-      <c r="C26" s="180" t="n"/>
-      <c r="D26" s="157" t="n"/>
-      <c r="E26" s="172" t="n"/>
-      <c r="F26" s="172" t="n"/>
-      <c r="G26" s="149" t="n"/>
+      <c r="A26" s="383" t="n"/>
+      <c r="B26" s="393" t="inlineStr">
+        <is>
+          <t>Payment to Previous Owners — Jun 22</t>
+        </is>
+      </c>
+      <c r="C26" s="394" t="n">
+        <v>46195</v>
+      </c>
+      <c r="D26" s="395" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E26" s="396" t="inlineStr">
+        <is>
+          <t>Lohith Reddy</t>
+        </is>
+      </c>
+      <c r="F26" s="396" t="inlineStr">
+        <is>
+          <t>✅ PAID</t>
+        </is>
+      </c>
+      <c r="G26" s="393" t="inlineStr">
+        <is>
+          <t>Capital payment to previous owners — 22 Jun 2026</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="19.95" customHeight="1" s="278">
       <c r="B27" s="149" t="n"/>
@@ -3379,7 +3410,7 @@
       </c>
       <c r="G31" s="150" t="inlineStr">
         <is>
-          <t>$390,000 − $306,235 paid (Jun 3-19) − $15,530 electricity offset = $68,235 remaining</t>
+          <t>$390,000 − $366,235 paid (Jun 3–22) − $15,530 electricity offset = $8,235 remaining</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4741,7 @@
     <row r="104" ht="15.6" customHeight="1" s="278">
       <c r="B104" s="144" t="inlineStr">
         <is>
-          <t xml:space="preserve">  H.  ACQUISITION PAYMENT — SPLIT BY OWNERSHIP SHARE  ($385,000 BALANCE DUE)</t>
+          <t xml:space="preserve">  H.  ACQUISITION PAYMENT — SPLIT BY OWNERSHIP SHARE  (50% / 30% / 20%)</t>
         </is>
       </c>
       <c r="C104" s="143" t="n"/>
@@ -4738,12 +4769,12 @@
       </c>
       <c r="E105" s="170" t="inlineStr">
         <is>
-          <t>Advance Credited ($)</t>
+          <t>Paid So Far — by Share ($)</t>
         </is>
       </c>
       <c r="F105" s="170" t="inlineStr">
         <is>
-          <t>Balance Owed to Prev. Owners ($)</t>
+          <t>Share of Balance Remaining ($)</t>
         </is>
       </c>
       <c r="G105" s="154" t="inlineStr">
@@ -4767,17 +4798,16 @@
         <v/>
       </c>
       <c r="E106" s="161">
-        <f>D14</f>
+        <f>C106*$D$138</f>
         <v/>
       </c>
       <c r="F106" s="161">
         <f>D106-E106</f>
         <v/>
       </c>
-      <c r="G106" s="139" t="inlineStr">
-        <is>
-          <t>⏳ Pending — $134,500 balance outstanding</t>
-        </is>
+      <c r="G106" s="139">
+        <f>IF(F106&lt;1,"✅ Share fully paid","⏳ $"&amp;TEXT(F106,"#,##0")&amp;" of share remaining")</f>
+        <v/>
       </c>
     </row>
     <row r="107">
@@ -4794,17 +4824,17 @@
         <f>C107*D13</f>
         <v/>
       </c>
-      <c r="E107" s="163" t="n">
-        <v>0</v>
+      <c r="E107" s="163">
+        <f>C107*$D$138</f>
+        <v/>
       </c>
       <c r="F107" s="163">
         <f>D107-E107</f>
         <v/>
       </c>
-      <c r="G107" s="141" t="inlineStr">
-        <is>
-          <t>⏳ Pending — $134,500 balance outstanding</t>
-        </is>
+      <c r="G107" s="141">
+        <f>IF(F107&lt;1,"✅ Share fully paid","⏳ $"&amp;TEXT(F107,"#,##0")&amp;" of share remaining")</f>
+        <v/>
       </c>
     </row>
     <row r="108">
@@ -4821,17 +4851,17 @@
         <f>C108*D13</f>
         <v/>
       </c>
-      <c r="E108" s="161" t="n">
-        <v>0</v>
+      <c r="E108" s="161">
+        <f>C108*$D$138</f>
+        <v/>
       </c>
       <c r="F108" s="161">
         <f>D108-E108</f>
         <v/>
       </c>
-      <c r="G108" s="139" t="inlineStr">
-        <is>
-          <t>⏳ Pending — $134,500 balance outstanding</t>
-        </is>
+      <c r="G108" s="139">
+        <f>IF(F108&lt;1,"✅ Share fully paid","⏳ $"&amp;TEXT(F108,"#,##0")&amp;" of share remaining")</f>
+        <v/>
       </c>
     </row>
     <row r="109">
@@ -5046,7 +5076,7 @@
     <row r="138">
       <c r="B138" s="232" t="inlineStr">
         <is>
-          <t>− Paid to Previous Owners (incl. $15,530 electricity + Jun 19 $50,735)</t>
+          <t>− Paid to Previous Owners (incl. $15,530 electricity offset)</t>
         </is>
       </c>
       <c r="D138" s="233">
@@ -9600,17 +9630,45 @@
       <c r="Q42" s="44" t="n"/>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="278">
-      <c r="B43" s="34" t="n"/>
-      <c r="C43" s="47" t="n"/>
-      <c r="D43" s="48" t="n"/>
-      <c r="E43" s="49" t="n"/>
-      <c r="F43" s="50" t="n"/>
-      <c r="G43" s="51" t="n"/>
-      <c r="H43" s="52" t="n"/>
-      <c r="I43" s="53" t="n"/>
-      <c r="J43" s="54" t="n"/>
-      <c r="K43" s="55" t="n"/>
-      <c r="L43" s="18" t="n"/>
+      <c r="B43" s="385" t="n">
+        <v>46195</v>
+      </c>
+      <c r="C43" s="256" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D43" s="257" t="n">
+        <v>2459</v>
+      </c>
+      <c r="E43" s="49" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F43" s="50">
+        <f>IFERROR(D43+E43+G43,0)</f>
+        <v/>
+      </c>
+      <c r="G43" s="258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="259">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B43,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B43+1))</f>
+        <v/>
+      </c>
+      <c r="I43" s="260">
+        <f>IFERROR(F43-H43,0)</f>
+        <v/>
+      </c>
+      <c r="J43" s="261">
+        <f>IFERROR(I43/F43,0)</f>
+        <v/>
+      </c>
+      <c r="K43" s="255" t="n"/>
+      <c r="L43" s="262" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
       <c r="M43" s="21" t="n"/>
       <c r="N43" s="56" t="n"/>
       <c r="O43" s="57" t="n"/>
@@ -15541,9 +15599,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I2:P2"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B5:P5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:P2"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -28962,74 +29020,305 @@
       </c>
     </row>
     <row r="324">
-      <c r="B324" s="64" t="n"/>
-      <c r="C324" s="69" t="n"/>
-      <c r="D324" s="68" t="n"/>
-      <c r="E324" s="69" t="n"/>
-      <c r="F324" s="70" t="n"/>
-      <c r="G324" s="23" t="n"/>
-      <c r="H324" s="23" t="n"/>
-      <c r="I324" s="55" t="n"/>
+      <c r="B324" s="382" t="n">
+        <v>46195</v>
+      </c>
+      <c r="C324" s="252" t="inlineStr">
+        <is>
+          <t>Pollo: muslo 4.95kg, pechuga 3.32kg, milanesa 1.64kg, ala 1.74kg</t>
+        </is>
+      </c>
+      <c r="D324" s="253" t="inlineStr">
+        <is>
+          <t>Polleria local</t>
+        </is>
+      </c>
+      <c r="E324" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F324" s="70" t="n">
+        <v>940</v>
+      </c>
+      <c r="G324" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H324" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I324" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J324" s="383" t="inlineStr">
+        <is>
+          <t>Nota remision LOKA Cafe</t>
+        </is>
+      </c>
     </row>
     <row r="325">
-      <c r="B325" s="64" t="n"/>
-      <c r="C325" s="65" t="n"/>
-      <c r="D325" s="66" t="n"/>
-      <c r="E325" s="65" t="n"/>
-      <c r="F325" s="67" t="n"/>
-      <c r="G325" s="14" t="n"/>
-      <c r="H325" s="14" t="n"/>
-      <c r="I325" s="43" t="n"/>
+      <c r="B325" s="382" t="n">
+        <v>46195</v>
+      </c>
+      <c r="C325" s="248" t="inlineStr">
+        <is>
+          <t>Carne ~3 kg</t>
+        </is>
+      </c>
+      <c r="D325" s="249" t="inlineStr">
+        <is>
+          <t>Miscelanea LC La Cruz</t>
+        </is>
+      </c>
+      <c r="E325" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F325" s="67" t="n">
+        <v>291</v>
+      </c>
+      <c r="G325" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H325" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I325" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J325" s="383" t="inlineStr">
+        <is>
+          <t>Getnet 3982 Aut 358593</t>
+        </is>
+      </c>
     </row>
     <row r="326">
-      <c r="B326" s="64" t="n"/>
-      <c r="C326" s="69" t="n"/>
-      <c r="D326" s="68" t="n"/>
-      <c r="E326" s="69" t="n"/>
-      <c r="F326" s="70" t="n"/>
-      <c r="G326" s="23" t="n"/>
-      <c r="H326" s="23" t="n"/>
-      <c r="I326" s="55" t="n"/>
+      <c r="B326" s="382" t="n">
+        <v>46195</v>
+      </c>
+      <c r="C326" s="252" t="inlineStr">
+        <is>
+          <t>Agua natural</t>
+        </is>
+      </c>
+      <c r="D326" s="253" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E326" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F326" s="70" t="n">
+        <v>60</v>
+      </c>
+      <c r="G326" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H326" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I326" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J326" s="383" t="inlineStr">
+        <is>
+          <t>No receipt</t>
+        </is>
+      </c>
     </row>
     <row r="327">
-      <c r="B327" s="64" t="n"/>
-      <c r="C327" s="65" t="n"/>
-      <c r="D327" s="66" t="n"/>
-      <c r="E327" s="65" t="n"/>
-      <c r="F327" s="67" t="n"/>
-      <c r="G327" s="14" t="n"/>
-      <c r="H327" s="14" t="n"/>
-      <c r="I327" s="43" t="n"/>
+      <c r="B327" s="382" t="n">
+        <v>46195</v>
+      </c>
+      <c r="C327" s="248" t="inlineStr">
+        <is>
+          <t>Tortillas</t>
+        </is>
+      </c>
+      <c r="D327" s="249" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E327" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F327" s="67" t="n">
+        <v>26</v>
+      </c>
+      <c r="G327" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H327" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I327" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J327" s="383" t="inlineStr">
+        <is>
+          <t>No receipt</t>
+        </is>
+      </c>
     </row>
     <row r="328">
-      <c r="B328" s="64" t="n"/>
-      <c r="C328" s="69" t="n"/>
-      <c r="D328" s="68" t="n"/>
-      <c r="E328" s="69" t="n"/>
-      <c r="F328" s="70" t="n"/>
-      <c r="G328" s="23" t="n"/>
-      <c r="H328" s="23" t="n"/>
-      <c r="I328" s="55" t="n"/>
+      <c r="B328" s="382" t="n">
+        <v>46195</v>
+      </c>
+      <c r="C328" s="252" t="inlineStr">
+        <is>
+          <t>Pan dulces</t>
+        </is>
+      </c>
+      <c r="D328" s="253" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E328" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F328" s="70" t="n">
+        <v>134</v>
+      </c>
+      <c r="G328" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H328" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I328" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J328" s="383" t="inlineStr">
+        <is>
+          <t>No receipt</t>
+        </is>
+      </c>
     </row>
     <row r="329">
-      <c r="B329" s="64" t="n"/>
-      <c r="C329" s="65" t="n"/>
-      <c r="D329" s="66" t="n"/>
-      <c r="E329" s="65" t="n"/>
-      <c r="F329" s="67" t="n"/>
-      <c r="G329" s="14" t="n"/>
-      <c r="H329" s="14" t="n"/>
-      <c r="I329" s="43" t="n"/>
+      <c r="B329" s="382" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C329" s="248" t="inlineStr">
+        <is>
+          <t>Panko (x2)</t>
+        </is>
+      </c>
+      <c r="D329" s="249" t="inlineStr">
+        <is>
+          <t>Molino y Condimentos La Cruz</t>
+        </is>
+      </c>
+      <c r="E329" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F329" s="67" t="n">
+        <v>196</v>
+      </c>
+      <c r="G329" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H329" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I329" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J329" s="383" t="inlineStr">
+        <is>
+          <t>Nota 202067 back-dated 19 Jun; paid by another person, reimbursed by Lohith 22-Jun</t>
+        </is>
+      </c>
     </row>
     <row r="330">
-      <c r="B330" s="64" t="n"/>
-      <c r="C330" s="69" t="n"/>
-      <c r="D330" s="68" t="n"/>
-      <c r="E330" s="69" t="n"/>
-      <c r="F330" s="70" t="n"/>
-      <c r="G330" s="23" t="n"/>
-      <c r="H330" s="23" t="n"/>
-      <c r="I330" s="55" t="n"/>
+      <c r="B330" s="382" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C330" s="252" t="inlineStr">
+        <is>
+          <t>Papel alimenticio (food paper)</t>
+        </is>
+      </c>
+      <c r="D330" s="253" t="inlineStr">
+        <is>
+          <t>Guimar Polietilenos</t>
+        </is>
+      </c>
+      <c r="E330" s="252" t="inlineStr">
+        <is>
+          <t>Packaging / Disposables</t>
+        </is>
+      </c>
+      <c r="F330" s="70" t="n">
+        <v>35</v>
+      </c>
+      <c r="G330" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H330" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I330" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J330" s="383" t="inlineStr">
+        <is>
+          <t>Folio XCC37706 back-dated 19 Jun; paid by another person, reimbursed by Lohith 22-Jun</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="B331" s="64" t="n"/>
@@ -40045,13 +40334,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="278">
-      <c r="A1" s="372" t="inlineStr">
+      <c r="A1" s="384" t="inlineStr">
         <is>
           <t>LOKA — MONTHLY P&amp;L   (live formulas — auto-updates from Daily Log &amp; Expenses)</t>
         </is>
       </c>
-      <c r="B1" s="373" t="n"/>
-      <c r="C1" s="373" t="n"/>
+      <c r="B1" s="383" t="n"/>
+      <c r="C1" s="383" t="n"/>
       <c r="D1" s="374" t="n"/>
       <c r="E1" s="374" t="n"/>
       <c r="F1" s="374" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -9676,17 +9676,45 @@
       <c r="Q43" s="56" t="n"/>
     </row>
     <row r="44" ht="16.5" customHeight="1" s="278">
-      <c r="B44" s="34" t="n"/>
-      <c r="C44" s="35" t="n"/>
-      <c r="D44" s="36" t="n"/>
-      <c r="E44" s="37" t="n"/>
-      <c r="F44" s="38" t="n"/>
-      <c r="G44" s="39" t="n"/>
-      <c r="H44" s="40" t="n"/>
-      <c r="I44" s="41" t="n"/>
-      <c r="J44" s="42" t="n"/>
-      <c r="K44" s="43" t="n"/>
-      <c r="L44" s="9" t="n"/>
+      <c r="B44" s="385" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C44" s="386" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D44" s="387" t="n">
+        <v>1452</v>
+      </c>
+      <c r="E44" s="37" t="n">
+        <v>1515</v>
+      </c>
+      <c r="F44" s="38">
+        <f>IFERROR(D44+E44+G44,0)</f>
+        <v/>
+      </c>
+      <c r="G44" s="388" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="389">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B44,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B44+1))</f>
+        <v/>
+      </c>
+      <c r="I44" s="390">
+        <f>IFERROR(F44-H44,0)</f>
+        <v/>
+      </c>
+      <c r="J44" s="391">
+        <f>IFERROR(I44/F44,0)</f>
+        <v/>
+      </c>
+      <c r="K44" s="251" t="n"/>
+      <c r="L44" s="392" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
       <c r="M44" s="12" t="n"/>
       <c r="N44" s="44" t="n"/>
       <c r="O44" s="45" t="n"/>
@@ -29321,54 +29349,219 @@
       </c>
     </row>
     <row r="331">
-      <c r="B331" s="64" t="n"/>
-      <c r="C331" s="65" t="n"/>
-      <c r="D331" s="66" t="n"/>
-      <c r="E331" s="65" t="n"/>
-      <c r="F331" s="67" t="n"/>
-      <c r="G331" s="14" t="n"/>
-      <c r="H331" s="14" t="n"/>
-      <c r="I331" s="43" t="n"/>
+      <c r="B331" s="382" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C331" s="248" t="inlineStr">
+        <is>
+          <t>Sushi ingredients: arroz para sushi + alga nori</t>
+        </is>
+      </c>
+      <c r="D331" s="249" t="inlineStr">
+        <is>
+          <t>H-E-B</t>
+        </is>
+      </c>
+      <c r="E331" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F331" s="67" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="G331" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H331" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I331" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J331" s="383" t="inlineStr">
+        <is>
+          <t>CB PROSA 3982 Aut 766296 (part of 366 ticket)</t>
+        </is>
+      </c>
     </row>
     <row r="332">
-      <c r="B332" s="64" t="n"/>
-      <c r="C332" s="69" t="n"/>
-      <c r="D332" s="68" t="n"/>
-      <c r="E332" s="69" t="n"/>
-      <c r="F332" s="70" t="n"/>
-      <c r="G332" s="23" t="n"/>
-      <c r="H332" s="23" t="n"/>
-      <c r="I332" s="55" t="n"/>
+      <c r="B332" s="382" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C332" s="252" t="inlineStr">
+        <is>
+          <t>Sushi supplies: makisu mat + palillos</t>
+        </is>
+      </c>
+      <c r="D332" s="253" t="inlineStr">
+        <is>
+          <t>H-E-B</t>
+        </is>
+      </c>
+      <c r="E332" s="252" t="inlineStr">
+        <is>
+          <t>Kitchen Supplies</t>
+        </is>
+      </c>
+      <c r="F332" s="70" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="G332" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H332" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I332" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J332" s="383" t="inlineStr">
+        <is>
+          <t>Part of 366 H-E-B ticket</t>
+        </is>
+      </c>
     </row>
     <row r="333">
-      <c r="B333" s="64" t="n"/>
-      <c r="C333" s="65" t="n"/>
-      <c r="D333" s="66" t="n"/>
-      <c r="E333" s="65" t="n"/>
-      <c r="F333" s="67" t="n"/>
-      <c r="G333" s="14" t="n"/>
-      <c r="H333" s="14" t="n"/>
-      <c r="I333" s="43" t="n"/>
+      <c r="B333" s="382" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C333" s="248" t="inlineStr">
+        <is>
+          <t>Carne / meat (handwritten remision)</t>
+        </is>
+      </c>
+      <c r="D333" s="249" t="inlineStr">
+        <is>
+          <t>Miscelanea LC La Cruz</t>
+        </is>
+      </c>
+      <c r="E333" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F333" s="67" t="n">
+        <v>151</v>
+      </c>
+      <c r="G333" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H333" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I333" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J333" s="383" t="inlineStr">
+        <is>
+          <t>Getnet 3982 Aut 993325</t>
+        </is>
+      </c>
     </row>
     <row r="334">
-      <c r="B334" s="64" t="n"/>
-      <c r="C334" s="69" t="n"/>
-      <c r="D334" s="68" t="n"/>
-      <c r="E334" s="69" t="n"/>
-      <c r="F334" s="70" t="n"/>
-      <c r="G334" s="23" t="n"/>
-      <c r="H334" s="23" t="n"/>
-      <c r="I334" s="55" t="n"/>
+      <c r="B334" s="382" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C334" s="252" t="inlineStr">
+        <is>
+          <t>Hielo (ice)</t>
+        </is>
+      </c>
+      <c r="D334" s="253" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E334" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F334" s="70" t="n">
+        <v>150</v>
+      </c>
+      <c r="G334" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H334" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I334" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J334" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="335">
-      <c r="B335" s="64" t="n"/>
-      <c r="C335" s="65" t="n"/>
-      <c r="D335" s="66" t="n"/>
-      <c r="E335" s="65" t="n"/>
-      <c r="F335" s="67" t="n"/>
-      <c r="G335" s="14" t="n"/>
-      <c r="H335" s="14" t="n"/>
-      <c r="I335" s="43" t="n"/>
+      <c r="B335" s="382" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C335" s="248" t="inlineStr">
+        <is>
+          <t>Pan molido (breadcrumbs)</t>
+        </is>
+      </c>
+      <c r="D335" s="249" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E335" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F335" s="67" t="n">
+        <v>46</v>
+      </c>
+      <c r="G335" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H335" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I335" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J335" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="B336" s="64" t="n"/>
@@ -40334,13 +40527,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="278">
-      <c r="A1" s="384" t="inlineStr">
+      <c r="A1" s="372" t="inlineStr">
         <is>
           <t>LOKA — MONTHLY P&amp;L   (live formulas — auto-updates from Daily Log &amp; Expenses)</t>
         </is>
       </c>
-      <c r="B1" s="383" t="n"/>
-      <c r="C1" s="383" t="n"/>
+      <c r="B1" s="373" t="n"/>
+      <c r="C1" s="373" t="n"/>
       <c r="D1" s="374" t="n"/>
       <c r="E1" s="374" t="n"/>
       <c r="F1" s="374" t="n"/>
@@ -41122,7 +41315,7 @@
     <row r="35">
       <c r="A35" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Desserts</t>
+          <t>Kitchen Supplies</t>
         </is>
       </c>
       <c r="B35" s="378">
@@ -41146,7 +41339,7 @@
     <row r="36">
       <c r="A36" s="380" t="inlineStr">
         <is>
-          <t>Kitchen Supplies</t>
+          <t>Ingredients - Desserts</t>
         </is>
       </c>
       <c r="B36" s="378">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -15627,8 +15627,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
@@ -29564,14 +29564,47 @@
       </c>
     </row>
     <row r="336">
-      <c r="B336" s="64" t="n"/>
-      <c r="C336" s="69" t="n"/>
-      <c r="D336" s="68" t="n"/>
-      <c r="E336" s="69" t="n"/>
-      <c r="F336" s="70" t="n"/>
-      <c r="G336" s="23" t="n"/>
-      <c r="H336" s="23" t="n"/>
-      <c r="I336" s="55" t="n"/>
+      <c r="B336" s="382" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C336" s="252" t="inlineStr">
+        <is>
+          <t>Tortillas blanca 3.395 kg</t>
+        </is>
+      </c>
+      <c r="D336" s="253" t="inlineStr">
+        <is>
+          <t>Chedraui Selecto</t>
+        </is>
+      </c>
+      <c r="E336" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F336" s="70" t="n">
+        <v>44.13</v>
+      </c>
+      <c r="G336" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H336" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I336" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J336" s="383" t="inlineStr">
+        <is>
+          <t>Debito BBVA 3982 Aut 651338 Folio 2606230937026818</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="B337" s="64" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -9722,17 +9722,45 @@
       <c r="Q44" s="44" t="n"/>
     </row>
     <row r="45" ht="16.5" customHeight="1" s="278">
-      <c r="B45" s="34" t="n"/>
-      <c r="C45" s="47" t="n"/>
-      <c r="D45" s="48" t="n"/>
-      <c r="E45" s="49" t="n"/>
-      <c r="F45" s="50" t="n"/>
-      <c r="G45" s="51" t="n"/>
-      <c r="H45" s="52" t="n"/>
-      <c r="I45" s="53" t="n"/>
-      <c r="J45" s="54" t="n"/>
-      <c r="K45" s="55" t="n"/>
-      <c r="L45" s="18" t="n"/>
+      <c r="B45" s="385" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C45" s="256" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D45" s="257" t="n">
+        <v>1064</v>
+      </c>
+      <c r="E45" s="49" t="n">
+        <v>2525</v>
+      </c>
+      <c r="F45" s="50">
+        <f>IFERROR(D45+E45+G45,0)</f>
+        <v/>
+      </c>
+      <c r="G45" s="258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="259">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B45,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B45+1))</f>
+        <v/>
+      </c>
+      <c r="I45" s="260">
+        <f>IFERROR(F45-H45,0)</f>
+        <v/>
+      </c>
+      <c r="J45" s="261">
+        <f>IFERROR(I45/F45,0)</f>
+        <v/>
+      </c>
+      <c r="K45" s="255" t="n"/>
+      <c r="L45" s="262" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
       <c r="M45" s="21" t="n"/>
       <c r="N45" s="56" t="n"/>
       <c r="O45" s="57" t="n"/>
@@ -15627,9 +15655,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -29607,84 +29635,348 @@
       </c>
     </row>
     <row r="337">
-      <c r="B337" s="64" t="n"/>
-      <c r="C337" s="65" t="n"/>
-      <c r="D337" s="66" t="n"/>
-      <c r="E337" s="65" t="n"/>
-      <c r="F337" s="67" t="n"/>
-      <c r="G337" s="14" t="n"/>
-      <c r="H337" s="14" t="n"/>
-      <c r="I337" s="43" t="n"/>
+      <c r="B337" s="382" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C337" s="248" t="inlineStr">
+        <is>
+          <t>Queso crema Lala 190g x2</t>
+        </is>
+      </c>
+      <c r="D337" s="249" t="inlineStr">
+        <is>
+          <t>Chedraui Paseo</t>
+        </is>
+      </c>
+      <c r="E337" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Dairy</t>
+        </is>
+      </c>
+      <c r="F337" s="67" t="n">
+        <v>72</v>
+      </c>
+      <c r="G337" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H337" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I337" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J337" s="383" t="inlineStr">
+        <is>
+          <t>Debito BBVA 3982; Chedraui Paseo ticket total 126.33 (crema+tortillas), dairy portion</t>
+        </is>
+      </c>
     </row>
     <row r="338">
-      <c r="B338" s="64" t="n"/>
-      <c r="C338" s="69" t="n"/>
-      <c r="D338" s="68" t="n"/>
-      <c r="E338" s="69" t="n"/>
-      <c r="F338" s="70" t="n"/>
-      <c r="G338" s="23" t="n"/>
-      <c r="H338" s="23" t="n"/>
-      <c r="I338" s="55" t="n"/>
+      <c r="B338" s="382" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C338" s="252" t="inlineStr">
+        <is>
+          <t>Tortillas blancas x2</t>
+        </is>
+      </c>
+      <c r="D338" s="253" t="inlineStr">
+        <is>
+          <t>Chedraui Paseo</t>
+        </is>
+      </c>
+      <c r="E338" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F338" s="70" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="G338" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H338" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I338" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J338" s="383" t="inlineStr">
+        <is>
+          <t>Debito BBVA 3982; same Chedraui ticket, bread portion</t>
+        </is>
+      </c>
     </row>
     <row r="339">
-      <c r="B339" s="64" t="n"/>
-      <c r="C339" s="65" t="n"/>
-      <c r="D339" s="66" t="n"/>
-      <c r="E339" s="65" t="n"/>
-      <c r="F339" s="67" t="n"/>
-      <c r="G339" s="14" t="n"/>
-      <c r="H339" s="14" t="n"/>
-      <c r="I339" s="43" t="n"/>
+      <c r="B339" s="382" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C339" s="248" t="inlineStr">
+        <is>
+          <t>Crema acida x2</t>
+        </is>
+      </c>
+      <c r="D339" s="249" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="E339" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Dairy</t>
+        </is>
+      </c>
+      <c r="F339" s="67" t="n">
+        <v>479.84</v>
+      </c>
+      <c r="G339" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H339" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I339" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J339" s="383" t="inlineStr">
+        <is>
+          <t>Debito Mastercard **82; Sam's ticket 1512.00 net of cuponera -32.73 + descuento -34.77; dairy portion of split</t>
+        </is>
+      </c>
     </row>
     <row r="340">
-      <c r="B340" s="64" t="n"/>
-      <c r="C340" s="69" t="n"/>
-      <c r="D340" s="68" t="n"/>
-      <c r="E340" s="69" t="n"/>
-      <c r="F340" s="70" t="n"/>
-      <c r="G340" s="23" t="n"/>
-      <c r="H340" s="23" t="n"/>
-      <c r="I340" s="55" t="n"/>
+      <c r="B340" s="382" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C340" s="252" t="inlineStr">
+        <is>
+          <t>Condimix 3.6, Mayo Real, Arroz Morel</t>
+        </is>
+      </c>
+      <c r="D340" s="253" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="E340" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F340" s="70" t="n">
+        <v>1032.16</v>
+      </c>
+      <c r="G340" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H340" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I340" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J340" s="383" t="inlineStr">
+        <is>
+          <t>Debito Mastercard **82; pantry portion of 1512.00 Sam's ticket</t>
+        </is>
+      </c>
     </row>
     <row r="341">
-      <c r="B341" s="64" t="n"/>
-      <c r="C341" s="65" t="n"/>
-      <c r="D341" s="66" t="n"/>
-      <c r="E341" s="65" t="n"/>
-      <c r="F341" s="67" t="n"/>
-      <c r="G341" s="14" t="n"/>
-      <c r="H341" s="14" t="n"/>
-      <c r="I341" s="43" t="n"/>
+      <c r="B341" s="382" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C341" s="248" t="inlineStr">
+        <is>
+          <t>Gas LP</t>
+        </is>
+      </c>
+      <c r="D341" s="249" t="inlineStr">
+        <is>
+          <t>Gas Tomza de Mexico</t>
+        </is>
+      </c>
+      <c r="E341" s="248" t="inlineStr">
+        <is>
+          <t>Utilities / Gas</t>
+        </is>
+      </c>
+      <c r="F341" s="67" t="n">
+        <v>1499.52</v>
+      </c>
+      <c r="G341" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H341" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I341" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J341" s="383" t="inlineStr">
+        <is>
+          <t>Remision 8900 @ $10.58/L IVA incl; pague antes 25/06; paid cash</t>
+        </is>
+      </c>
     </row>
     <row r="342">
-      <c r="B342" s="64" t="n"/>
-      <c r="C342" s="69" t="n"/>
-      <c r="D342" s="68" t="n"/>
-      <c r="E342" s="69" t="n"/>
-      <c r="F342" s="70" t="n"/>
-      <c r="G342" s="23" t="n"/>
-      <c r="H342" s="23" t="n"/>
-      <c r="I342" s="55" t="n"/>
+      <c r="B342" s="382" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C342" s="252" t="inlineStr">
+        <is>
+          <t>Filete de salmon 1.03 kg @ 350/kg</t>
+        </is>
+      </c>
+      <c r="D342" s="253" t="inlineStr">
+        <is>
+          <t>Brisa del Mar</t>
+        </is>
+      </c>
+      <c r="E342" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat &amp; Fish</t>
+        </is>
+      </c>
+      <c r="F342" s="70" t="n">
+        <v>360.5</v>
+      </c>
+      <c r="G342" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H342" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I342" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J342" s="383" t="inlineStr">
+        <is>
+          <t>Contado; NT 027672</t>
+        </is>
+      </c>
     </row>
     <row r="343">
-      <c r="B343" s="64" t="n"/>
-      <c r="C343" s="65" t="n"/>
-      <c r="D343" s="66" t="n"/>
-      <c r="E343" s="65" t="n"/>
-      <c r="F343" s="67" t="n"/>
-      <c r="G343" s="14" t="n"/>
-      <c r="H343" s="14" t="n"/>
-      <c r="I343" s="43" t="n"/>
+      <c r="B343" s="382" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C343" s="248" t="inlineStr">
+        <is>
+          <t>Naranjada 1L x6</t>
+        </is>
+      </c>
+      <c r="D343" s="249" t="inlineStr">
+        <is>
+          <t>Casa Reca</t>
+        </is>
+      </c>
+      <c r="E343" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F343" s="67" t="n">
+        <v>150</v>
+      </c>
+      <c r="G343" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H343" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I343" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J343" s="383" t="inlineStr">
+        <is>
+          <t>Nota QR-37; 6 pzas; canje CJ-4 (horchata/naranjada/tamarindo) $0; paid cash</t>
+        </is>
+      </c>
     </row>
     <row r="344">
-      <c r="B344" s="64" t="n"/>
-      <c r="C344" s="69" t="n"/>
-      <c r="D344" s="68" t="n"/>
-      <c r="E344" s="69" t="n"/>
-      <c r="F344" s="70" t="n"/>
-      <c r="G344" s="23" t="n"/>
-      <c r="H344" s="23" t="n"/>
-      <c r="I344" s="55" t="n"/>
+      <c r="B344" s="382" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C344" s="252" t="inlineStr">
+        <is>
+          <t>Papas (potatoes)</t>
+        </is>
+      </c>
+      <c r="D344" s="253" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E344" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F344" s="70" t="n">
+        <v>133</v>
+      </c>
+      <c r="G344" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H344" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I344" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J344" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="B345" s="64" t="n"/>
@@ -40988,7 +41280,7 @@
     <row r="20">
       <c r="A20" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Vegetables</t>
+          <t>Ingredients - Pantry</t>
         </is>
       </c>
       <c r="B20" s="378">
@@ -41012,7 +41304,7 @@
     <row r="21">
       <c r="A21" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Beverages</t>
+          <t>Ingredients - Vegetables</t>
         </is>
       </c>
       <c r="B21" s="378">
@@ -41036,7 +41328,7 @@
     <row r="22">
       <c r="A22" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Pantry</t>
+          <t>Ingredients - Beverages</t>
         </is>
       </c>
       <c r="B22" s="378">
@@ -41228,7 +41520,7 @@
     <row r="30">
       <c r="A30" s="380" t="inlineStr">
         <is>
-          <t>Software / Subscription</t>
+          <t>Utilities / Gas</t>
         </is>
       </c>
       <c r="B30" s="378">
@@ -41252,7 +41544,7 @@
     <row r="31">
       <c r="A31" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Other</t>
+          <t>Software / Subscription</t>
         </is>
       </c>
       <c r="B31" s="378">
@@ -41276,7 +41568,7 @@
     <row r="32">
       <c r="A32" s="380" t="inlineStr">
         <is>
-          <t>Staff - Advance</t>
+          <t>Ingredients - Other</t>
         </is>
       </c>
       <c r="B32" s="378">
@@ -41300,7 +41592,7 @@
     <row r="33">
       <c r="A33" s="380" t="inlineStr">
         <is>
-          <t>Utilities / Internet</t>
+          <t>Staff - Advance</t>
         </is>
       </c>
       <c r="B33" s="378">
@@ -41324,7 +41616,7 @@
     <row r="34">
       <c r="A34" s="380" t="inlineStr">
         <is>
-          <t>Packaging / Disposables</t>
+          <t>Utilities / Internet</t>
         </is>
       </c>
       <c r="B34" s="378">
@@ -41348,7 +41640,7 @@
     <row r="35">
       <c r="A35" s="380" t="inlineStr">
         <is>
-          <t>Kitchen Supplies</t>
+          <t>Packaging / Disposables</t>
         </is>
       </c>
       <c r="B35" s="378">
@@ -41372,7 +41664,7 @@
     <row r="36">
       <c r="A36" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Desserts</t>
+          <t>Kitchen Supplies</t>
         </is>
       </c>
       <c r="B36" s="378">
@@ -41396,7 +41688,7 @@
     <row r="37">
       <c r="A37" s="380" t="inlineStr">
         <is>
-          <t>Staff - Propinas</t>
+          <t>Ingredients - Desserts</t>
         </is>
       </c>
       <c r="B37" s="378">
@@ -41420,7 +41712,7 @@
     <row r="38">
       <c r="A38" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Eggs</t>
+          <t>Staff - Propinas</t>
         </is>
       </c>
       <c r="B38" s="378">
@@ -41444,7 +41736,7 @@
     <row r="39">
       <c r="A39" s="380" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Ingredients - Eggs</t>
         </is>
       </c>
       <c r="B39" s="378">
@@ -41468,7 +41760,7 @@
     <row r="40">
       <c r="A40" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Produce</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="B40" s="378">
@@ -41490,17 +41782,17 @@
       <c r="L40" s="374" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="377" t="inlineStr">
-        <is>
-          <t>TOTAL EXPENSES</t>
-        </is>
-      </c>
-      <c r="B41" s="379">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
-        <v/>
-      </c>
-      <c r="C41" s="379">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+      <c r="A41" s="380" t="inlineStr">
+        <is>
+          <t>Ingredients - Produce</t>
+        </is>
+      </c>
+      <c r="B41" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A41,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <v/>
+      </c>
+      <c r="C41" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A41,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D41" s="374" t="n"/>
@@ -41516,15 +41808,15 @@
     <row r="42">
       <c r="A42" s="377" t="inlineStr">
         <is>
-          <t>NET PROFIT / LOSS</t>
+          <t>TOTAL EXPENSES</t>
         </is>
       </c>
       <c r="B42" s="379">
-        <f>B4-B41</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C42" s="379">
-        <f>C4-C41</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D42" s="374" t="n"/>
@@ -41538,9 +41830,19 @@
       <c r="L42" s="374" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="374" t="n"/>
-      <c r="B43" s="374" t="n"/>
-      <c r="C43" s="374" t="n"/>
+      <c r="A43" s="377" t="inlineStr">
+        <is>
+          <t>NET PROFIT / LOSS</t>
+        </is>
+      </c>
+      <c r="B43" s="379">
+        <f>B4-B42</f>
+        <v/>
+      </c>
+      <c r="C43" s="379">
+        <f>C4-C42</f>
+        <v/>
+      </c>
       <c r="D43" s="374" t="n"/>
       <c r="E43" s="374" t="n"/>
       <c r="F43" s="374" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -9768,17 +9768,45 @@
       <c r="Q45" s="56" t="n"/>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="278">
-      <c r="B46" s="34" t="n"/>
-      <c r="C46" s="35" t="n"/>
-      <c r="D46" s="36" t="n"/>
-      <c r="E46" s="37" t="n"/>
-      <c r="F46" s="38" t="n"/>
-      <c r="G46" s="39" t="n"/>
-      <c r="H46" s="40" t="n"/>
-      <c r="I46" s="41" t="n"/>
-      <c r="J46" s="42" t="n"/>
-      <c r="K46" s="43" t="n"/>
-      <c r="L46" s="9" t="n"/>
+      <c r="B46" s="385" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C46" s="386" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D46" s="387" t="n">
+        <v>1735</v>
+      </c>
+      <c r="E46" s="37" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F46" s="38">
+        <f>IFERROR(D46+E46+G46,0)</f>
+        <v/>
+      </c>
+      <c r="G46" s="388" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="389">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B46,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B46+1))</f>
+        <v/>
+      </c>
+      <c r="I46" s="390">
+        <f>IFERROR(F46-H46,0)</f>
+        <v/>
+      </c>
+      <c r="J46" s="391">
+        <f>IFERROR(I46/F46,0)</f>
+        <v/>
+      </c>
+      <c r="K46" s="251" t="n"/>
+      <c r="L46" s="392" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
       <c r="M46" s="12" t="n"/>
       <c r="N46" s="44" t="n"/>
       <c r="O46" s="45" t="n"/>
@@ -15655,9 +15683,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I2:P2"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B5:P5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:P2"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -29979,74 +30007,305 @@
       </c>
     </row>
     <row r="345">
-      <c r="B345" s="64" t="n"/>
-      <c r="C345" s="65" t="n"/>
-      <c r="D345" s="66" t="n"/>
-      <c r="E345" s="65" t="n"/>
-      <c r="F345" s="67" t="n"/>
-      <c r="G345" s="14" t="n"/>
-      <c r="H345" s="14" t="n"/>
-      <c r="I345" s="43" t="n"/>
+      <c r="B345" s="382" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C345" s="248" t="inlineStr">
+        <is>
+          <t>Muslo (chicken thigh) ~12.3 kg @ $50/kg</t>
+        </is>
+      </c>
+      <c r="D345" s="249" t="inlineStr">
+        <is>
+          <t>Oh lele / Local</t>
+        </is>
+      </c>
+      <c r="E345" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F345" s="67" t="n">
+        <v>615</v>
+      </c>
+      <c r="G345" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H345" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I345" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J345" s="383" t="inlineStr">
+        <is>
+          <t>Nota de remision (handwritten, Loka Cafe); total $615; cash</t>
+        </is>
+      </c>
     </row>
     <row r="346">
-      <c r="B346" s="64" t="n"/>
-      <c r="C346" s="69" t="n"/>
-      <c r="D346" s="68" t="n"/>
-      <c r="E346" s="69" t="n"/>
-      <c r="F346" s="70" t="n"/>
-      <c r="G346" s="23" t="n"/>
-      <c r="H346" s="23" t="n"/>
-      <c r="I346" s="55" t="n"/>
+      <c r="B346" s="382" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C346" s="252" t="inlineStr">
+        <is>
+          <t>Costilla cd (pork ribs) 3.15 kg @ ~$103/kg</t>
+        </is>
+      </c>
+      <c r="D346" s="253" t="inlineStr">
+        <is>
+          <t>Miscelanea LC La Cruz</t>
+        </is>
+      </c>
+      <c r="E346" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F346" s="70" t="n">
+        <v>318</v>
+      </c>
+      <c r="G346" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H346" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I346" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J346" s="383" t="inlineStr">
+        <is>
+          <t>Remision ~319 handwritten; Getnet card charge 318.00; card **3982 Aut 298095; LC remision partly illegible</t>
+        </is>
+      </c>
     </row>
     <row r="347">
-      <c r="B347" s="64" t="n"/>
-      <c r="C347" s="65" t="n"/>
-      <c r="D347" s="66" t="n"/>
-      <c r="E347" s="65" t="n"/>
-      <c r="F347" s="67" t="n"/>
-      <c r="G347" s="14" t="n"/>
-      <c r="H347" s="14" t="n"/>
-      <c r="I347" s="43" t="n"/>
+      <c r="B347" s="382" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C347" s="248" t="inlineStr">
+        <is>
+          <t>Papas (potatoes)</t>
+        </is>
+      </c>
+      <c r="D347" s="249" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E347" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F347" s="67" t="n">
+        <v>64</v>
+      </c>
+      <c r="G347" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H347" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I347" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J347" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="348">
-      <c r="B348" s="64" t="n"/>
-      <c r="C348" s="69" t="n"/>
-      <c r="D348" s="68" t="n"/>
-      <c r="E348" s="69" t="n"/>
-      <c r="F348" s="70" t="n"/>
-      <c r="G348" s="23" t="n"/>
-      <c r="H348" s="23" t="n"/>
-      <c r="I348" s="55" t="n"/>
+      <c r="B348" s="382" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C348" s="252" t="inlineStr">
+        <is>
+          <t>Pan dulces</t>
+        </is>
+      </c>
+      <c r="D348" s="253" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E348" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F348" s="70" t="n">
+        <v>96</v>
+      </c>
+      <c r="G348" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H348" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I348" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J348" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="349">
-      <c r="B349" s="64" t="n"/>
-      <c r="C349" s="65" t="n"/>
-      <c r="D349" s="66" t="n"/>
-      <c r="E349" s="65" t="n"/>
-      <c r="F349" s="67" t="n"/>
-      <c r="G349" s="14" t="n"/>
-      <c r="H349" s="14" t="n"/>
-      <c r="I349" s="43" t="n"/>
+      <c r="B349" s="382" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C349" s="248" t="inlineStr">
+        <is>
+          <t>Agua natural</t>
+        </is>
+      </c>
+      <c r="D349" s="249" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E349" s="248" t="inlineStr">
+        <is>
+          <t>Supplies / Other</t>
+        </is>
+      </c>
+      <c r="F349" s="67" t="n">
+        <v>60</v>
+      </c>
+      <c r="G349" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H349" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I349" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J349" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="350">
-      <c r="B350" s="64" t="n"/>
-      <c r="C350" s="69" t="n"/>
-      <c r="D350" s="68" t="n"/>
-      <c r="E350" s="69" t="n"/>
-      <c r="F350" s="70" t="n"/>
-      <c r="G350" s="23" t="n"/>
-      <c r="H350" s="23" t="n"/>
-      <c r="I350" s="55" t="n"/>
+      <c r="B350" s="382" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C350" s="252" t="inlineStr">
+        <is>
+          <t>Frigadora (kitchenware)</t>
+        </is>
+      </c>
+      <c r="D350" s="253" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E350" s="252" t="inlineStr">
+        <is>
+          <t>Kitchen Supplies</t>
+        </is>
+      </c>
+      <c r="F350" s="70" t="n">
+        <v>45</v>
+      </c>
+      <c r="G350" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H350" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I350" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J350" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="351">
-      <c r="B351" s="64" t="n"/>
-      <c r="C351" s="65" t="n"/>
-      <c r="D351" s="66" t="n"/>
-      <c r="E351" s="65" t="n"/>
-      <c r="F351" s="67" t="n"/>
-      <c r="G351" s="14" t="n"/>
-      <c r="H351" s="14" t="n"/>
-      <c r="I351" s="43" t="n"/>
+      <c r="B351" s="382" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C351" s="248" t="inlineStr">
+        <is>
+          <t>Gancho (hook)</t>
+        </is>
+      </c>
+      <c r="D351" s="249" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E351" s="248" t="inlineStr">
+        <is>
+          <t>Supplies / Other</t>
+        </is>
+      </c>
+      <c r="F351" s="67" t="n">
+        <v>30</v>
+      </c>
+      <c r="G351" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H351" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I351" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J351" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="B352" s="64" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -1292,7 +1292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19"/>
   </cellStyleXfs>
-  <cellXfs count="397">
+  <cellXfs count="398">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2318,6 +2318,7 @@
     <xf numFmtId="0" fontId="72" fillId="40" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6063,37 +6064,63 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="231" t="inlineStr">
+      <c r="A26" s="397" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B26" s="232" t="inlineStr">
+        <is>
+          <t>Customer Transfer - Jun 26 (revenue paid into Lohith account)</t>
+        </is>
+      </c>
+      <c r="C26" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D26" s="232" t="n"/>
+      <c r="E26" s="233" t="n">
+        <v>165</v>
+      </c>
+      <c r="F26" s="233">
+        <f>IFERROR(F25+D26-E26,0)</f>
+        <v/>
+      </c>
+      <c r="G26" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H26" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid $165 by transfer into Lohith account - counts against balance owed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="397" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B26" s="232" t="n"/>
-      <c r="C26" s="232" t="n"/>
-      <c r="D26" s="232">
-        <f>SUM(D4:D25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="233">
-        <f>SUM(E4:E25)</f>
-        <v/>
-      </c>
-      <c r="F26" s="233">
-        <f>F25</f>
-        <v/>
-      </c>
-      <c r="G26" s="232">
-        <f>IF(F25&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F25,"#,##0"),IF(F25&lt;0,"Lohith holds $"&amp;TEXT(ABS(F25),"#,##0"),"Zero balance"))</f>
-        <v/>
-      </c>
-      <c r="H26" s="232" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Add new rows ABOVE the TOTALS row. Spent by Lohith = restaurant costs he paid personally.</t>
-        </is>
-      </c>
+      <c r="B27" s="232" t="n"/>
+      <c r="C27" s="232" t="n"/>
+      <c r="D27" s="232">
+        <f>SUM(D4:D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="233">
+        <f>SUM(E4:E26)</f>
+        <v/>
+      </c>
+      <c r="F27" s="233">
+        <f>F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="232">
+        <f>IF(F26&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F26,"#,##0"),IF(F26&lt;0,"Lohith holds $"&amp;TEXT(ABS(F26),"#,##0"),"Zero balance"))</f>
+        <v/>
+      </c>
+      <c r="H27" s="232" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9814,17 +9841,45 @@
       <c r="Q46" s="44" t="n"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="278">
-      <c r="B47" s="34" t="n"/>
-      <c r="C47" s="47" t="n"/>
-      <c r="D47" s="48" t="n"/>
-      <c r="E47" s="49" t="n"/>
-      <c r="F47" s="50" t="n"/>
-      <c r="G47" s="51" t="n"/>
-      <c r="H47" s="52" t="n"/>
-      <c r="I47" s="53" t="n"/>
-      <c r="J47" s="54" t="n"/>
-      <c r="K47" s="55" t="n"/>
-      <c r="L47" s="18" t="n"/>
+      <c r="B47" s="385" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C47" s="256" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D47" s="257" t="n">
+        <v>1719</v>
+      </c>
+      <c r="E47" s="49" t="n">
+        <v>2593</v>
+      </c>
+      <c r="F47" s="50">
+        <f>IFERROR(D47+E47+G47,0)</f>
+        <v/>
+      </c>
+      <c r="G47" s="258" t="n">
+        <v>165</v>
+      </c>
+      <c r="H47" s="259">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B47,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B47+1))</f>
+        <v/>
+      </c>
+      <c r="I47" s="260">
+        <f>IFERROR(F47-H47,0)</f>
+        <v/>
+      </c>
+      <c r="J47" s="261">
+        <f>IFERROR(I47/F47,0)</f>
+        <v/>
+      </c>
+      <c r="K47" s="255" t="n"/>
+      <c r="L47" s="262" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
       <c r="M47" s="21" t="n"/>
       <c r="N47" s="56" t="n"/>
       <c r="O47" s="57" t="n"/>
@@ -9832,17 +9887,45 @@
       <c r="Q47" s="56" t="n"/>
     </row>
     <row r="48" ht="16.5" customHeight="1" s="278">
-      <c r="B48" s="34" t="n"/>
-      <c r="C48" s="35" t="n"/>
-      <c r="D48" s="36" t="n"/>
-      <c r="E48" s="37" t="n"/>
-      <c r="F48" s="38" t="n"/>
-      <c r="G48" s="39" t="n"/>
-      <c r="H48" s="40" t="n"/>
-      <c r="I48" s="41" t="n"/>
-      <c r="J48" s="42" t="n"/>
-      <c r="K48" s="43" t="n"/>
-      <c r="L48" s="9" t="n"/>
+      <c r="B48" s="385" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C48" s="386" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D48" s="387" t="n">
+        <v>175</v>
+      </c>
+      <c r="E48" s="37" t="n">
+        <v>1854</v>
+      </c>
+      <c r="F48" s="38">
+        <f>IFERROR(D48+E48+G48,0)</f>
+        <v/>
+      </c>
+      <c r="G48" s="388" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="389">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B48,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B48+1))</f>
+        <v/>
+      </c>
+      <c r="I48" s="390">
+        <f>IFERROR(F48-H48,0)</f>
+        <v/>
+      </c>
+      <c r="J48" s="391">
+        <f>IFERROR(I48/F48,0)</f>
+        <v/>
+      </c>
+      <c r="K48" s="251" t="n"/>
+      <c r="L48" s="392" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
       <c r="M48" s="12" t="n"/>
       <c r="N48" s="44" t="n"/>
       <c r="O48" s="45" t="n"/>
@@ -9850,17 +9933,45 @@
       <c r="Q48" s="44" t="n"/>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="278">
-      <c r="B49" s="34" t="n"/>
-      <c r="C49" s="47" t="n"/>
-      <c r="D49" s="48" t="n"/>
-      <c r="E49" s="49" t="n"/>
-      <c r="F49" s="50" t="n"/>
-      <c r="G49" s="51" t="n"/>
-      <c r="H49" s="52" t="n"/>
-      <c r="I49" s="53" t="n"/>
-      <c r="J49" s="54" t="n"/>
-      <c r="K49" s="55" t="n"/>
-      <c r="L49" s="18" t="n"/>
+      <c r="B49" s="385" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C49" s="256" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="D49" s="257" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="50">
+        <f>IFERROR(D49+E49+G49,0)</f>
+        <v/>
+      </c>
+      <c r="G49" s="258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="259">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B49,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B49+1))</f>
+        <v/>
+      </c>
+      <c r="I49" s="260">
+        <f>IFERROR(F49-H49,0)</f>
+        <v/>
+      </c>
+      <c r="J49" s="261">
+        <f>IFERROR(I49/F49,0)</f>
+        <v/>
+      </c>
+      <c r="K49" s="255" t="n"/>
+      <c r="L49" s="262" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
       <c r="M49" s="21" t="n"/>
       <c r="N49" s="56" t="n"/>
       <c r="O49" s="57" t="n"/>
@@ -30308,274 +30419,1165 @@
       </c>
     </row>
     <row r="352">
-      <c r="B352" s="64" t="n"/>
-      <c r="C352" s="69" t="n"/>
-      <c r="D352" s="68" t="n"/>
-      <c r="E352" s="69" t="n"/>
-      <c r="F352" s="70" t="n"/>
-      <c r="G352" s="23" t="n"/>
-      <c r="H352" s="23" t="n"/>
-      <c r="I352" s="55" t="n"/>
+      <c r="B352" s="382" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C352" s="252" t="inlineStr">
+        <is>
+          <t>Zanahoria, cilantro, tomate (granel)</t>
+        </is>
+      </c>
+      <c r="D352" s="253" t="inlineStr">
+        <is>
+          <t>Chedraui Paseo</t>
+        </is>
+      </c>
+      <c r="E352" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F352" s="70" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="G352" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H352" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I352" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J352" s="383" t="inlineStr">
+        <is>
+          <t>Debito BBVA 3982; Chedraui ticket total 99.53 (veg+tortillas), veg portion</t>
+        </is>
+      </c>
     </row>
     <row r="353">
-      <c r="B353" s="64" t="n"/>
-      <c r="C353" s="65" t="n"/>
-      <c r="D353" s="66" t="n"/>
-      <c r="E353" s="65" t="n"/>
-      <c r="F353" s="67" t="n"/>
-      <c r="G353" s="14" t="n"/>
-      <c r="H353" s="14" t="n"/>
-      <c r="I353" s="43" t="n"/>
+      <c r="B353" s="382" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C353" s="248" t="inlineStr">
+        <is>
+          <t>Tortillas blancas x2</t>
+        </is>
+      </c>
+      <c r="D353" s="249" t="inlineStr">
+        <is>
+          <t>Chedraui Paseo</t>
+        </is>
+      </c>
+      <c r="E353" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F353" s="67" t="n">
+        <v>53.79</v>
+      </c>
+      <c r="G353" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H353" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I353" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J353" s="383" t="inlineStr">
+        <is>
+          <t>Debito BBVA 3982; same Chedraui ticket, bread portion</t>
+        </is>
+      </c>
     </row>
     <row r="354">
-      <c r="B354" s="64" t="n"/>
-      <c r="C354" s="69" t="n"/>
-      <c r="D354" s="68" t="n"/>
-      <c r="E354" s="69" t="n"/>
-      <c r="F354" s="70" t="n"/>
-      <c r="G354" s="23" t="n"/>
-      <c r="H354" s="23" t="n"/>
-      <c r="I354" s="55" t="n"/>
+      <c r="B354" s="382" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C354" s="252" t="inlineStr">
+        <is>
+          <t>Curcuma (turmeric) 70g</t>
+        </is>
+      </c>
+      <c r="D354" s="253" t="inlineStr">
+        <is>
+          <t>H-E-B</t>
+        </is>
+      </c>
+      <c r="E354" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F354" s="70" t="n">
+        <v>14</v>
+      </c>
+      <c r="G354" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H354" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I354" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J354" s="383" t="inlineStr">
+        <is>
+          <t>Efectivo; ticket 215/07/02997</t>
+        </is>
+      </c>
     </row>
     <row r="355">
-      <c r="B355" s="64" t="n"/>
-      <c r="C355" s="65" t="n"/>
-      <c r="D355" s="66" t="n"/>
-      <c r="E355" s="65" t="n"/>
-      <c r="F355" s="67" t="n"/>
-      <c r="G355" s="14" t="n"/>
-      <c r="H355" s="14" t="n"/>
-      <c r="I355" s="43" t="n"/>
+      <c r="B355" s="382" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C355" s="248" t="inlineStr">
+        <is>
+          <t>Lechugas (lettuce)</t>
+        </is>
+      </c>
+      <c r="D355" s="249" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E355" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F355" s="67" t="n">
+        <v>40</v>
+      </c>
+      <c r="G355" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H355" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I355" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J355" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="356">
-      <c r="B356" s="64" t="n"/>
-      <c r="C356" s="69" t="n"/>
-      <c r="D356" s="68" t="n"/>
-      <c r="E356" s="69" t="n"/>
-      <c r="F356" s="70" t="n"/>
-      <c r="G356" s="23" t="n"/>
-      <c r="H356" s="23" t="n"/>
-      <c r="I356" s="55" t="n"/>
+      <c r="B356" s="382" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C356" s="252" t="inlineStr">
+        <is>
+          <t>Queso Panela</t>
+        </is>
+      </c>
+      <c r="D356" s="253" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E356" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Dairy</t>
+        </is>
+      </c>
+      <c r="F356" s="70" t="n">
+        <v>592</v>
+      </c>
+      <c r="G356" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H356" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I356" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J356" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="357">
-      <c r="B357" s="64" t="n"/>
-      <c r="C357" s="65" t="n"/>
-      <c r="D357" s="66" t="n"/>
-      <c r="E357" s="65" t="n"/>
-      <c r="F357" s="67" t="n"/>
-      <c r="G357" s="14" t="n"/>
-      <c r="H357" s="14" t="n"/>
-      <c r="I357" s="43" t="n"/>
+      <c r="B357" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C357" s="248" t="inlineStr">
+        <is>
+          <t>Mi Huevo Blanco (white eggs) 5.59 kg @ $24/kg</t>
+        </is>
+      </c>
+      <c r="D357" s="249" t="inlineStr">
+        <is>
+          <t>Delgado Semillas y Especias</t>
+        </is>
+      </c>
+      <c r="E357" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Eggs</t>
+        </is>
+      </c>
+      <c r="F357" s="67" t="n">
+        <v>134.16</v>
+      </c>
+      <c r="G357" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H357" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I357" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J357" s="383" t="inlineStr">
+        <is>
+          <t>Folio 134837; efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="358">
-      <c r="B358" s="64" t="n"/>
-      <c r="C358" s="69" t="n"/>
-      <c r="D358" s="68" t="n"/>
-      <c r="E358" s="69" t="n"/>
-      <c r="F358" s="70" t="n"/>
-      <c r="G358" s="23" t="n"/>
-      <c r="H358" s="23" t="n"/>
-      <c r="I358" s="55" t="n"/>
+      <c r="B358" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C358" s="252" t="inlineStr">
+        <is>
+          <t>Dart lids 10oz + Dart cups 10 + aluminum foil 45cm</t>
+        </is>
+      </c>
+      <c r="D358" s="253" t="inlineStr">
+        <is>
+          <t>Basicos en Alimentos</t>
+        </is>
+      </c>
+      <c r="E358" s="252" t="inlineStr">
+        <is>
+          <t>Supplies / Other</t>
+        </is>
+      </c>
+      <c r="F358" s="70" t="n">
+        <v>395</v>
+      </c>
+      <c r="G358" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H358" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I358" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J358" s="383" t="inlineStr">
+        <is>
+          <t>Ticket Sec 93; 403.72 less desc 8.72; tarjeta debito</t>
+        </is>
+      </c>
     </row>
     <row r="359">
-      <c r="B359" s="64" t="n"/>
-      <c r="C359" s="65" t="n"/>
-      <c r="D359" s="66" t="n"/>
-      <c r="E359" s="65" t="n"/>
-      <c r="F359" s="67" t="n"/>
-      <c r="G359" s="14" t="n"/>
-      <c r="H359" s="14" t="n"/>
-      <c r="I359" s="43" t="n"/>
+      <c r="B359" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C359" s="248" t="inlineStr">
+        <is>
+          <t>Fajilla de papel economica 1000pz</t>
+        </is>
+      </c>
+      <c r="D359" s="249" t="inlineStr">
+        <is>
+          <t>Guimar Polietilenos</t>
+        </is>
+      </c>
+      <c r="E359" s="248" t="inlineStr">
+        <is>
+          <t>Supplies / Other</t>
+        </is>
+      </c>
+      <c r="F359" s="67" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="G359" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H359" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I359" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J359" s="383" t="inlineStr">
+        <is>
+          <t>Folio AK89660; tarjeta debito</t>
+        </is>
+      </c>
     </row>
     <row r="360">
-      <c r="B360" s="64" t="n"/>
-      <c r="C360" s="69" t="n"/>
-      <c r="D360" s="68" t="n"/>
-      <c r="E360" s="69" t="n"/>
-      <c r="F360" s="70" t="n"/>
-      <c r="G360" s="23" t="n"/>
-      <c r="H360" s="23" t="n"/>
-      <c r="I360" s="55" t="n"/>
+      <c r="B360" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C360" s="252" t="inlineStr">
+        <is>
+          <t>Vaso plastico 4CH Reyma 20/50 + Tapa vaso 20/50</t>
+        </is>
+      </c>
+      <c r="D360" s="253" t="inlineStr">
+        <is>
+          <t>Guimar Polietilenos</t>
+        </is>
+      </c>
+      <c r="E360" s="252" t="inlineStr">
+        <is>
+          <t>Supplies / Other</t>
+        </is>
+      </c>
+      <c r="F360" s="70" t="n">
+        <v>828</v>
+      </c>
+      <c r="G360" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H360" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I360" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J360" s="383" t="inlineStr">
+        <is>
+          <t>Folio AK89656; ahorro 92; tarjeta debito</t>
+        </is>
+      </c>
     </row>
     <row r="361">
-      <c r="B361" s="64" t="n"/>
-      <c r="C361" s="65" t="n"/>
-      <c r="D361" s="66" t="n"/>
-      <c r="E361" s="65" t="n"/>
-      <c r="F361" s="67" t="n"/>
-      <c r="G361" s="14" t="n"/>
-      <c r="H361" s="14" t="n"/>
-      <c r="I361" s="43" t="n"/>
+      <c r="B361" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C361" s="248" t="inlineStr">
+        <is>
+          <t>Gelatina D'Gari (durazno, fresa, pina) 120g</t>
+        </is>
+      </c>
+      <c r="D361" s="249" t="inlineStr">
+        <is>
+          <t>Basicos en Alimentos</t>
+        </is>
+      </c>
+      <c r="E361" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F361" s="67" t="n">
+        <v>96</v>
+      </c>
+      <c r="G361" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H361" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I361" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J361" s="383" t="inlineStr">
+        <is>
+          <t>Ticket Sec 77; dessert gelatin</t>
+        </is>
+      </c>
     </row>
     <row r="362">
-      <c r="B362" s="64" t="n"/>
-      <c r="C362" s="69" t="n"/>
-      <c r="D362" s="68" t="n"/>
-      <c r="E362" s="69" t="n"/>
-      <c r="F362" s="70" t="n"/>
-      <c r="G362" s="23" t="n"/>
-      <c r="H362" s="23" t="n"/>
-      <c r="I362" s="55" t="n"/>
+      <c r="B362" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C362" s="252" t="inlineStr">
+        <is>
+          <t>Clorox King 5.8L + Detergente Roma 5kg</t>
+        </is>
+      </c>
+      <c r="D362" s="253" t="inlineStr">
+        <is>
+          <t>Basicos en Alimentos</t>
+        </is>
+      </c>
+      <c r="E362" s="252" t="inlineStr">
+        <is>
+          <t>Supplies / Other</t>
+        </is>
+      </c>
+      <c r="F362" s="70" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="G362" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H362" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I362" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J362" s="383" t="inlineStr">
+        <is>
+          <t>Ticket Sec 77; cleaning</t>
+        </is>
+      </c>
     </row>
     <row r="363">
-      <c r="B363" s="64" t="n"/>
-      <c r="C363" s="65" t="n"/>
-      <c r="D363" s="66" t="n"/>
-      <c r="E363" s="65" t="n"/>
-      <c r="F363" s="67" t="n"/>
-      <c r="G363" s="14" t="n"/>
-      <c r="H363" s="14" t="n"/>
-      <c r="I363" s="43" t="n"/>
+      <c r="B363" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C363" s="248" t="inlineStr">
+        <is>
+          <t>Servilleta Maxima cuadrada 500pz x8</t>
+        </is>
+      </c>
+      <c r="D363" s="249" t="inlineStr">
+        <is>
+          <t>Basicos en Alimentos</t>
+        </is>
+      </c>
+      <c r="E363" s="248" t="inlineStr">
+        <is>
+          <t>Supplies / Other</t>
+        </is>
+      </c>
+      <c r="F363" s="67" t="n">
+        <v>340</v>
+      </c>
+      <c r="G363" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H363" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I363" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J363" s="383" t="inlineStr">
+        <is>
+          <t>Ticket Sec 77; napkins</t>
+        </is>
+      </c>
     </row>
     <row r="364">
-      <c r="B364" s="64" t="n"/>
-      <c r="C364" s="69" t="n"/>
-      <c r="D364" s="68" t="n"/>
-      <c r="E364" s="69" t="n"/>
-      <c r="F364" s="70" t="n"/>
-      <c r="G364" s="23" t="n"/>
-      <c r="H364" s="23" t="n"/>
-      <c r="I364" s="55" t="n"/>
+      <c r="B364" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C364" s="252" t="inlineStr">
+        <is>
+          <t>Manzana (apple)</t>
+        </is>
+      </c>
+      <c r="D364" s="253" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E364" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Fruit</t>
+        </is>
+      </c>
+      <c r="F364" s="70" t="n">
+        <v>89</v>
+      </c>
+      <c r="G364" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H364" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I364" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J364" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="365">
-      <c r="B365" s="64" t="n"/>
-      <c r="C365" s="65" t="n"/>
-      <c r="D365" s="66" t="n"/>
-      <c r="E365" s="65" t="n"/>
-      <c r="F365" s="67" t="n"/>
-      <c r="G365" s="14" t="n"/>
-      <c r="H365" s="14" t="n"/>
-      <c r="I365" s="43" t="n"/>
+      <c r="B365" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C365" s="248" t="inlineStr">
+        <is>
+          <t>Pepino (cucumber)</t>
+        </is>
+      </c>
+      <c r="D365" s="249" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E365" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F365" s="67" t="n">
+        <v>80</v>
+      </c>
+      <c r="G365" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H365" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I365" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J365" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="366">
-      <c r="B366" s="64" t="n"/>
-      <c r="C366" s="69" t="n"/>
-      <c r="D366" s="68" t="n"/>
-      <c r="E366" s="69" t="n"/>
-      <c r="F366" s="70" t="n"/>
-      <c r="G366" s="23" t="n"/>
-      <c r="H366" s="23" t="n"/>
-      <c r="I366" s="55" t="n"/>
+      <c r="B366" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C366" s="252" t="inlineStr">
+        <is>
+          <t>Tomate verde (tomatillo)</t>
+        </is>
+      </c>
+      <c r="D366" s="253" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E366" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F366" s="70" t="n">
+        <v>80</v>
+      </c>
+      <c r="G366" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H366" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I366" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J366" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="367">
-      <c r="B367" s="64" t="n"/>
-      <c r="C367" s="65" t="n"/>
-      <c r="D367" s="66" t="n"/>
-      <c r="E367" s="65" t="n"/>
-      <c r="F367" s="67" t="n"/>
-      <c r="G367" s="14" t="n"/>
-      <c r="H367" s="14" t="n"/>
-      <c r="I367" s="43" t="n"/>
+      <c r="B367" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C367" s="248" t="inlineStr">
+        <is>
+          <t>Papas (potatoes)</t>
+        </is>
+      </c>
+      <c r="D367" s="249" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E367" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F367" s="67" t="n">
+        <v>195</v>
+      </c>
+      <c r="G367" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H367" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I367" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J367" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="368">
-      <c r="B368" s="64" t="n"/>
-      <c r="C368" s="69" t="n"/>
-      <c r="D368" s="68" t="n"/>
-      <c r="E368" s="69" t="n"/>
-      <c r="F368" s="70" t="n"/>
-      <c r="G368" s="23" t="n"/>
-      <c r="H368" s="23" t="n"/>
-      <c r="I368" s="55" t="n"/>
+      <c r="B368" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C368" s="252" t="inlineStr">
+        <is>
+          <t>Guayaba (guava)</t>
+        </is>
+      </c>
+      <c r="D368" s="253" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E368" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Fruit</t>
+        </is>
+      </c>
+      <c r="F368" s="70" t="n">
+        <v>100</v>
+      </c>
+      <c r="G368" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H368" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I368" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J368" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="369">
-      <c r="B369" s="64" t="n"/>
-      <c r="C369" s="65" t="n"/>
-      <c r="D369" s="66" t="n"/>
-      <c r="E369" s="65" t="n"/>
-      <c r="F369" s="67" t="n"/>
-      <c r="G369" s="14" t="n"/>
-      <c r="H369" s="14" t="n"/>
-      <c r="I369" s="43" t="n"/>
+      <c r="B369" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C369" s="248" t="inlineStr">
+        <is>
+          <t>Platano (banana)</t>
+        </is>
+      </c>
+      <c r="D369" s="249" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E369" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Fruit</t>
+        </is>
+      </c>
+      <c r="F369" s="67" t="n">
+        <v>54</v>
+      </c>
+      <c r="G369" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H369" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I369" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J369" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="370">
-      <c r="B370" s="64" t="n"/>
-      <c r="C370" s="69" t="n"/>
-      <c r="D370" s="68" t="n"/>
-      <c r="E370" s="69" t="n"/>
-      <c r="F370" s="70" t="n"/>
-      <c r="G370" s="23" t="n"/>
-      <c r="H370" s="23" t="n"/>
-      <c r="I370" s="55" t="n"/>
+      <c r="B370" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C370" s="252" t="inlineStr">
+        <is>
+          <t>Betabel (beet)</t>
+        </is>
+      </c>
+      <c r="D370" s="253" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E370" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F370" s="70" t="n">
+        <v>80</v>
+      </c>
+      <c r="G370" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H370" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I370" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J370" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="371">
-      <c r="B371" s="64" t="n"/>
-      <c r="C371" s="65" t="n"/>
-      <c r="D371" s="66" t="n"/>
-      <c r="E371" s="65" t="n"/>
-      <c r="F371" s="67" t="n"/>
-      <c r="G371" s="14" t="n"/>
-      <c r="H371" s="14" t="n"/>
-      <c r="I371" s="43" t="n"/>
+      <c r="B371" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C371" s="248" t="inlineStr">
+        <is>
+          <t>Cilantro</t>
+        </is>
+      </c>
+      <c r="D371" s="249" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E371" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F371" s="67" t="n">
+        <v>60</v>
+      </c>
+      <c r="G371" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H371" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I371" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J371" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="372">
-      <c r="B372" s="64" t="n"/>
-      <c r="C372" s="69" t="n"/>
-      <c r="D372" s="68" t="n"/>
-      <c r="E372" s="69" t="n"/>
-      <c r="F372" s="70" t="n"/>
-      <c r="G372" s="23" t="n"/>
-      <c r="H372" s="23" t="n"/>
-      <c r="I372" s="55" t="n"/>
+      <c r="B372" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C372" s="252" t="inlineStr">
+        <is>
+          <t>Nopal (cactus)</t>
+        </is>
+      </c>
+      <c r="D372" s="253" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E372" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F372" s="70" t="n">
+        <v>50</v>
+      </c>
+      <c r="G372" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H372" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I372" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J372" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="373">
-      <c r="B373" s="64" t="n"/>
-      <c r="C373" s="65" t="n"/>
-      <c r="D373" s="66" t="n"/>
-      <c r="E373" s="65" t="n"/>
-      <c r="F373" s="67" t="n"/>
-      <c r="G373" s="14" t="n"/>
-      <c r="H373" s="14" t="n"/>
-      <c r="I373" s="43" t="n"/>
+      <c r="B373" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C373" s="248" t="inlineStr">
+        <is>
+          <t>Jitomate (tomato)</t>
+        </is>
+      </c>
+      <c r="D373" s="249" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E373" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F373" s="67" t="n">
+        <v>80</v>
+      </c>
+      <c r="G373" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H373" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I373" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J373" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="374">
-      <c r="B374" s="64" t="n"/>
-      <c r="C374" s="69" t="n"/>
-      <c r="D374" s="68" t="n"/>
-      <c r="E374" s="69" t="n"/>
-      <c r="F374" s="70" t="n"/>
-      <c r="G374" s="23" t="n"/>
-      <c r="H374" s="23" t="n"/>
-      <c r="I374" s="55" t="n"/>
+      <c r="B374" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C374" s="252" t="inlineStr">
+        <is>
+          <t>Lechuga italiana</t>
+        </is>
+      </c>
+      <c r="D374" s="253" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E374" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F374" s="70" t="n">
+        <v>148</v>
+      </c>
+      <c r="G374" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H374" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I374" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J374" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="375">
-      <c r="B375" s="64" t="n"/>
-      <c r="C375" s="65" t="n"/>
-      <c r="D375" s="66" t="n"/>
-      <c r="E375" s="65" t="n"/>
-      <c r="F375" s="67" t="n"/>
-      <c r="G375" s="14" t="n"/>
-      <c r="H375" s="14" t="n"/>
-      <c r="I375" s="43" t="n"/>
+      <c r="B375" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C375" s="248" t="inlineStr">
+        <is>
+          <t>Espinaca (spinach)</t>
+        </is>
+      </c>
+      <c r="D375" s="249" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E375" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F375" s="67" t="n">
+        <v>30</v>
+      </c>
+      <c r="G375" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H375" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I375" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J375" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="376">
-      <c r="B376" s="64" t="n"/>
-      <c r="C376" s="69" t="n"/>
-      <c r="D376" s="68" t="n"/>
-      <c r="E376" s="69" t="n"/>
-      <c r="F376" s="70" t="n"/>
-      <c r="G376" s="23" t="n"/>
-      <c r="H376" s="23" t="n"/>
-      <c r="I376" s="55" t="n"/>
+      <c r="B376" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C376" s="252" t="inlineStr">
+        <is>
+          <t>Limones (limes)</t>
+        </is>
+      </c>
+      <c r="D376" s="253" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E376" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Fruit</t>
+        </is>
+      </c>
+      <c r="F376" s="70" t="n">
+        <v>20</v>
+      </c>
+      <c r="G376" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H376" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I376" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J376" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="377">
-      <c r="B377" s="64" t="n"/>
-      <c r="C377" s="65" t="n"/>
-      <c r="D377" s="66" t="n"/>
-      <c r="E377" s="65" t="n"/>
-      <c r="F377" s="67" t="n"/>
-      <c r="G377" s="14" t="n"/>
-      <c r="H377" s="14" t="n"/>
-      <c r="I377" s="43" t="n"/>
+      <c r="B377" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C377" s="248" t="inlineStr">
+        <is>
+          <t>Verduras variadas (vegetables)</t>
+        </is>
+      </c>
+      <c r="D377" s="249" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E377" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F377" s="67" t="n">
+        <v>211</v>
+      </c>
+      <c r="G377" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H377" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I377" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J377" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="378">
-      <c r="B378" s="64" t="n"/>
-      <c r="C378" s="69" t="n"/>
-      <c r="D378" s="68" t="n"/>
-      <c r="E378" s="69" t="n"/>
-      <c r="F378" s="70" t="n"/>
-      <c r="G378" s="23" t="n"/>
-      <c r="H378" s="23" t="n"/>
-      <c r="I378" s="55" t="n"/>
+      <c r="B378" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C378" s="252" t="inlineStr">
+        <is>
+          <t>Frutas variadas (fruit)</t>
+        </is>
+      </c>
+      <c r="D378" s="253" t="inlineStr">
+        <is>
+          <t>Local purchase</t>
+        </is>
+      </c>
+      <c r="E378" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Fruit</t>
+        </is>
+      </c>
+      <c r="F378" s="70" t="n">
+        <v>324</v>
+      </c>
+      <c r="G378" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H378" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I378" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J378" s="383" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="B379" s="64" t="n"/>
@@ -41539,7 +42541,7 @@
     <row r="20">
       <c r="A20" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Pantry</t>
+          <t>Ingredients - Vegetables</t>
         </is>
       </c>
       <c r="B20" s="378">
@@ -41563,7 +42565,7 @@
     <row r="21">
       <c r="A21" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Vegetables</t>
+          <t>Ingredients - Pantry</t>
         </is>
       </c>
       <c r="B21" s="378">
@@ -41635,7 +42637,7 @@
     <row r="24">
       <c r="A24" s="380" t="inlineStr">
         <is>
-          <t>Supermarket / General</t>
+          <t>Supplies / Other</t>
         </is>
       </c>
       <c r="B24" s="378">
@@ -41659,7 +42661,7 @@
     <row r="25">
       <c r="A25" s="380" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Supermarket / General</t>
         </is>
       </c>
       <c r="B25" s="378">
@@ -41683,7 +42685,7 @@
     <row r="26">
       <c r="A26" s="380" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B26" s="378">
@@ -41971,7 +42973,7 @@
     <row r="38">
       <c r="A38" s="380" t="inlineStr">
         <is>
-          <t>Staff - Propinas</t>
+          <t>Ingredients - Eggs</t>
         </is>
       </c>
       <c r="B38" s="378">
@@ -41995,7 +42997,7 @@
     <row r="39">
       <c r="A39" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Eggs</t>
+          <t>Staff - Propinas</t>
         </is>
       </c>
       <c r="B39" s="378">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -31580,34 +31580,133 @@
       </c>
     </row>
     <row r="379">
-      <c r="B379" s="64" t="n"/>
-      <c r="C379" s="65" t="n"/>
-      <c r="D379" s="66" t="n"/>
-      <c r="E379" s="65" t="n"/>
-      <c r="F379" s="67" t="n"/>
-      <c r="G379" s="14" t="n"/>
-      <c r="H379" s="14" t="n"/>
-      <c r="I379" s="43" t="n"/>
+      <c r="B379" s="382" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C379" s="248" t="inlineStr">
+        <is>
+          <t>Samu — Ayudante Week 6</t>
+        </is>
+      </c>
+      <c r="D379" s="249" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E379" s="248" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F379" s="67" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G379" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H379" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I379" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J379" s="383" t="inlineStr">
+        <is>
+          <t>Week 6 salary, paid Friday</t>
+        </is>
+      </c>
     </row>
     <row r="380">
-      <c r="B380" s="64" t="n"/>
-      <c r="C380" s="69" t="n"/>
-      <c r="D380" s="68" t="n"/>
-      <c r="E380" s="69" t="n"/>
-      <c r="F380" s="70" t="n"/>
-      <c r="G380" s="23" t="n"/>
-      <c r="H380" s="23" t="n"/>
-      <c r="I380" s="55" t="n"/>
+      <c r="B380" s="382" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C380" s="252" t="inlineStr">
+        <is>
+          <t>John — Head Chef Week 6 (full week)</t>
+        </is>
+      </c>
+      <c r="D380" s="253" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E380" s="252" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F380" s="70" t="n">
+        <v>3750</v>
+      </c>
+      <c r="G380" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H380" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I380" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J380" s="383" t="inlineStr">
+        <is>
+          <t>Week 6 salary, paid Saturday</t>
+        </is>
+      </c>
     </row>
     <row r="381">
-      <c r="B381" s="64" t="n"/>
-      <c r="C381" s="65" t="n"/>
-      <c r="D381" s="66" t="n"/>
-      <c r="E381" s="65" t="n"/>
-      <c r="F381" s="67" t="n"/>
-      <c r="G381" s="14" t="n"/>
-      <c r="H381" s="14" t="n"/>
-      <c r="I381" s="43" t="n"/>
+      <c r="B381" s="382" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C381" s="248" t="inlineStr">
+        <is>
+          <t>Duvi/Debi — Limpieza Week 6</t>
+        </is>
+      </c>
+      <c r="D381" s="249" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E381" s="248" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F381" s="67" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G381" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H381" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I381" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J381" s="383" t="inlineStr">
+        <is>
+          <t>Week 6 salary, paid Saturday</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="B382" s="64" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -15794,9 +15794,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -6097,37 +6097,63 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="397" t="inlineStr">
+      <c r="A27" s="397" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B27" s="232" t="inlineStr">
+        <is>
+          <t>Cash withdrawal by Lohith from restaurant (partial repayment of balance owed)</t>
+        </is>
+      </c>
+      <c r="C27" s="232" t="inlineStr">
+        <is>
+          <t>Cash Withdrawal</t>
+        </is>
+      </c>
+      <c r="D27" s="232" t="n"/>
+      <c r="E27" s="233" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F27" s="233">
+        <f>IFERROR(F26+D27-E27,0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="232" t="inlineStr">
+        <is>
+          <t>✅ Taken</t>
+        </is>
+      </c>
+      <c r="H27" s="232" t="inlineStr">
+        <is>
+          <t>Took $10,000 cash from restaurant till; deducted from balance owed and from restaurant cash on hand</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="397" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B27" s="232" t="n"/>
-      <c r="C27" s="232" t="n"/>
-      <c r="D27" s="232">
-        <f>SUM(D4:D26)</f>
-        <v/>
-      </c>
-      <c r="E27" s="233">
-        <f>SUM(E4:E26)</f>
-        <v/>
-      </c>
-      <c r="F27" s="233">
-        <f>F26</f>
-        <v/>
-      </c>
-      <c r="G27" s="232">
-        <f>IF(F26&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F26,"#,##0"),IF(F26&lt;0,"Lohith holds $"&amp;TEXT(ABS(F26),"#,##0"),"Zero balance"))</f>
-        <v/>
-      </c>
-      <c r="H27" s="232" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Transferred to Lohith = transfers/reimbursements received in his account.</t>
-        </is>
-      </c>
+      <c r="B28" s="232" t="n"/>
+      <c r="C28" s="232" t="n"/>
+      <c r="D28" s="232">
+        <f>SUM(D4:D27)</f>
+        <v/>
+      </c>
+      <c r="E28" s="233">
+        <f>SUM(E4:E27)</f>
+        <v/>
+      </c>
+      <c r="F28" s="233">
+        <f>F27</f>
+        <v/>
+      </c>
+      <c r="G28" s="232">
+        <f>IF(F27&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F27,"#,##0"),IF(F27&lt;0,"Lohith holds $"&amp;TEXT(ABS(F27),"#,##0"),"Zero balance"))</f>
+        <v/>
+      </c>
+      <c r="H28" s="232" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15794,9 +15820,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -31709,14 +31735,47 @@
       </c>
     </row>
     <row r="382">
-      <c r="B382" s="64" t="n"/>
-      <c r="C382" s="69" t="n"/>
-      <c r="D382" s="68" t="n"/>
-      <c r="E382" s="69" t="n"/>
-      <c r="F382" s="70" t="n"/>
-      <c r="G382" s="23" t="n"/>
-      <c r="H382" s="23" t="n"/>
-      <c r="I382" s="55" t="n"/>
+      <c r="B382" s="382" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C382" s="252" t="inlineStr">
+        <is>
+          <t>Towel (kitchen)</t>
+        </is>
+      </c>
+      <c r="D382" s="253" t="inlineStr">
+        <is>
+          <t>Tienda China (variety store)</t>
+        </is>
+      </c>
+      <c r="E382" s="252" t="inlineStr">
+        <is>
+          <t>Kitchen Supplies</t>
+        </is>
+      </c>
+      <c r="F382" s="70" t="n">
+        <v>69</v>
+      </c>
+      <c r="G382" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H382" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I382" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J382" s="383" t="inlineStr">
+        <is>
+          <t>No bill; bought from small china/variety store</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="B383" s="64" t="n"/>
@@ -42976,7 +43035,7 @@
     <row r="34">
       <c r="A34" s="380" t="inlineStr">
         <is>
-          <t>Utilities / Internet</t>
+          <t>Kitchen Supplies</t>
         </is>
       </c>
       <c r="B34" s="378">
@@ -43000,7 +43059,7 @@
     <row r="35">
       <c r="A35" s="380" t="inlineStr">
         <is>
-          <t>Packaging / Disposables</t>
+          <t>Utilities / Internet</t>
         </is>
       </c>
       <c r="B35" s="378">
@@ -43024,7 +43083,7 @@
     <row r="36">
       <c r="A36" s="380" t="inlineStr">
         <is>
-          <t>Kitchen Supplies</t>
+          <t>Packaging / Disposables</t>
         </is>
       </c>
       <c r="B36" s="378">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -10005,17 +10005,45 @@
       <c r="Q49" s="56" t="n"/>
     </row>
     <row r="50" ht="16.5" customHeight="1" s="278">
-      <c r="B50" s="34" t="n"/>
-      <c r="C50" s="35" t="n"/>
-      <c r="D50" s="36" t="n"/>
-      <c r="E50" s="37" t="n"/>
-      <c r="F50" s="38" t="n"/>
-      <c r="G50" s="39" t="n"/>
-      <c r="H50" s="40" t="n"/>
-      <c r="I50" s="41" t="n"/>
-      <c r="J50" s="42" t="n"/>
-      <c r="K50" s="43" t="n"/>
-      <c r="L50" s="9" t="n"/>
+      <c r="B50" s="385" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C50" s="386" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D50" s="387" t="n">
+        <v>1814</v>
+      </c>
+      <c r="E50" s="37" t="n">
+        <v>1575</v>
+      </c>
+      <c r="F50" s="38">
+        <f>IFERROR(D50+E50+G50,0)</f>
+        <v/>
+      </c>
+      <c r="G50" s="388" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="389">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B50,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B50+1))</f>
+        <v/>
+      </c>
+      <c r="I50" s="390">
+        <f>IFERROR(F50-H50,0)</f>
+        <v/>
+      </c>
+      <c r="J50" s="391">
+        <f>IFERROR(I50/F50,0)</f>
+        <v/>
+      </c>
+      <c r="K50" s="251" t="n"/>
+      <c r="L50" s="392" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
       <c r="M50" s="12" t="n"/>
       <c r="N50" s="44" t="n"/>
       <c r="O50" s="45" t="n"/>
@@ -15820,9 +15848,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -31778,84 +31806,348 @@
       </c>
     </row>
     <row r="383">
-      <c r="B383" s="64" t="n"/>
-      <c r="C383" s="65" t="n"/>
-      <c r="D383" s="66" t="n"/>
-      <c r="E383" s="65" t="n"/>
-      <c r="F383" s="67" t="n"/>
-      <c r="G383" s="14" t="n"/>
-      <c r="H383" s="14" t="n"/>
-      <c r="I383" s="43" t="n"/>
+      <c r="B383" s="382" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C383" s="248" t="inlineStr">
+        <is>
+          <t>Tortillas blancas 3.965kg + Rosca de nuez</t>
+        </is>
+      </c>
+      <c r="D383" s="249" t="inlineStr">
+        <is>
+          <t>Chedraui Paseo</t>
+        </is>
+      </c>
+      <c r="E383" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F383" s="67" t="n">
+        <v>144.51</v>
+      </c>
+      <c r="G383" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H383" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I383" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J383" s="383" t="inlineStr">
+        <is>
+          <t>Debito BBVA 3982; digital ticket FOLIO ...0050; IEPS 8% on rosca</t>
+        </is>
+      </c>
     </row>
     <row r="384">
-      <c r="B384" s="64" t="n"/>
-      <c r="C384" s="69" t="n"/>
-      <c r="D384" s="68" t="n"/>
-      <c r="E384" s="69" t="n"/>
-      <c r="F384" s="70" t="n"/>
-      <c r="G384" s="23" t="n"/>
-      <c r="H384" s="23" t="n"/>
-      <c r="I384" s="55" t="n"/>
+      <c r="B384" s="382" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C384" s="252" t="inlineStr">
+        <is>
+          <t>Pechuga (chicken breast) ~4.29kg @ $115/kg</t>
+        </is>
+      </c>
+      <c r="D384" s="253" t="inlineStr">
+        <is>
+          <t>Oh lele / Local</t>
+        </is>
+      </c>
+      <c r="E384" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F384" s="70" t="n">
+        <v>493</v>
+      </c>
+      <c r="G384" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H384" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I384" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J384" s="383" t="inlineStr">
+        <is>
+          <t>Nota de remision (Loka Cafe); ticket total 967 (pechuga+milanesa)</t>
+        </is>
+      </c>
     </row>
     <row r="385">
-      <c r="B385" s="64" t="n"/>
-      <c r="C385" s="65" t="n"/>
-      <c r="D385" s="66" t="n"/>
-      <c r="E385" s="65" t="n"/>
-      <c r="F385" s="67" t="n"/>
-      <c r="G385" s="14" t="n"/>
-      <c r="H385" s="14" t="n"/>
-      <c r="I385" s="43" t="n"/>
+      <c r="B385" s="382" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C385" s="248" t="inlineStr">
+        <is>
+          <t>Milanesa ~3.79kg @ $125/kg</t>
+        </is>
+      </c>
+      <c r="D385" s="249" t="inlineStr">
+        <is>
+          <t>Oh lele / Local</t>
+        </is>
+      </c>
+      <c r="E385" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F385" s="67" t="n">
+        <v>474</v>
+      </c>
+      <c r="G385" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H385" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I385" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J385" s="383" t="inlineStr">
+        <is>
+          <t>Nota de remision (Loka Cafe); same ticket</t>
+        </is>
+      </c>
     </row>
     <row r="386">
-      <c r="B386" s="64" t="n"/>
-      <c r="C386" s="69" t="n"/>
-      <c r="D386" s="68" t="n"/>
-      <c r="E386" s="69" t="n"/>
-      <c r="F386" s="70" t="n"/>
-      <c r="G386" s="23" t="n"/>
-      <c r="H386" s="23" t="n"/>
-      <c r="I386" s="55" t="n"/>
+      <c r="B386" s="382" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C386" s="252" t="inlineStr">
+        <is>
+          <t>Frijol pinto a granel x2</t>
+        </is>
+      </c>
+      <c r="D386" s="253" t="inlineStr">
+        <is>
+          <t>Molino y Condimentos La Cruz</t>
+        </is>
+      </c>
+      <c r="E386" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F386" s="70" t="n">
+        <v>56</v>
+      </c>
+      <c r="G386" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H386" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I386" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J386" s="383" t="inlineStr">
+        <is>
+          <t>Nota 203548; efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="387">
-      <c r="B387" s="64" t="n"/>
-      <c r="C387" s="65" t="n"/>
-      <c r="D387" s="66" t="n"/>
-      <c r="E387" s="65" t="n"/>
-      <c r="F387" s="67" t="n"/>
-      <c r="G387" s="14" t="n"/>
-      <c r="H387" s="14" t="n"/>
-      <c r="I387" s="43" t="n"/>
+      <c r="B387" s="382" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C387" s="248" t="inlineStr">
+        <is>
+          <t>Jamon Americano San Antonio 2.055kg @ $86.50/kg</t>
+        </is>
+      </c>
+      <c r="D387" s="249" t="inlineStr">
+        <is>
+          <t>San Juan Salchichonerias</t>
+        </is>
+      </c>
+      <c r="E387" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F387" s="67" t="n">
+        <v>177.76</v>
+      </c>
+      <c r="G387" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H387" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I387" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J387" s="383" t="inlineStr">
+        <is>
+          <t>Debito Mastercard 3982; ticket 0254555; net of 17.47 desc</t>
+        </is>
+      </c>
     </row>
     <row r="388">
-      <c r="B388" s="64" t="n"/>
-      <c r="C388" s="69" t="n"/>
-      <c r="D388" s="68" t="n"/>
-      <c r="E388" s="69" t="n"/>
-      <c r="F388" s="70" t="n"/>
-      <c r="G388" s="23" t="n"/>
-      <c r="H388" s="23" t="n"/>
-      <c r="I388" s="55" t="n"/>
+      <c r="B388" s="382" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C388" s="252" t="inlineStr">
+        <is>
+          <t>Arrachera 1.05kg @ $270/kg</t>
+        </is>
+      </c>
+      <c r="D388" s="253" t="inlineStr">
+        <is>
+          <t>Kamy Karnes</t>
+        </is>
+      </c>
+      <c r="E388" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F388" s="70" t="n">
+        <v>284</v>
+      </c>
+      <c r="G388" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H388" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I388" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J388" s="383" t="inlineStr">
+        <is>
+          <t>Nota de venta 0971; method assumed Cash -- CONFIRM if card</t>
+        </is>
+      </c>
     </row>
     <row r="389">
-      <c r="B389" s="64" t="n"/>
-      <c r="C389" s="65" t="n"/>
-      <c r="D389" s="66" t="n"/>
-      <c r="E389" s="65" t="n"/>
-      <c r="F389" s="67" t="n"/>
-      <c r="G389" s="14" t="n"/>
-      <c r="H389" s="14" t="n"/>
-      <c r="I389" s="43" t="n"/>
+      <c r="B389" s="382" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C389" s="248" t="inlineStr">
+        <is>
+          <t>Bistec + tocino</t>
+        </is>
+      </c>
+      <c r="D389" s="249" t="inlineStr">
+        <is>
+          <t>Miscelanea LC La Cruz</t>
+        </is>
+      </c>
+      <c r="E389" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F389" s="67" t="n">
+        <v>415</v>
+      </c>
+      <c r="G389" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H389" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I389" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J389" s="383" t="inlineStr">
+        <is>
+          <t>Meat portion of Getnet card charge 1054.00 (Aut 236713, **3982): bistec ~292 + tocino ~123; papas portion logged separately</t>
+        </is>
+      </c>
     </row>
     <row r="390">
-      <c r="B390" s="64" t="n"/>
-      <c r="C390" s="69" t="n"/>
-      <c r="D390" s="68" t="n"/>
-      <c r="E390" s="69" t="n"/>
-      <c r="F390" s="70" t="n"/>
-      <c r="G390" s="23" t="n"/>
-      <c r="H390" s="23" t="n"/>
-      <c r="I390" s="55" t="n"/>
+      <c r="B390" s="382" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C390" s="252" t="inlineStr">
+        <is>
+          <t>Papas a la francesa (frozen French fries)</t>
+        </is>
+      </c>
+      <c r="D390" s="253" t="inlineStr">
+        <is>
+          <t>Miscelanea LC La Cruz</t>
+        </is>
+      </c>
+      <c r="E390" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F390" s="70" t="n">
+        <v>639</v>
+      </c>
+      <c r="G390" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H390" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I390" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J390" s="383" t="inlineStr">
+        <is>
+          <t>Frozen French fries; portion of Getnet card charge 1054.00 (Aut 236713, **3982); the ~639 item on the LC remision</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="B391" s="64" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -40,7 +40,7 @@
     <numFmt numFmtId="175" formatCode="$#,##0.00"/>
     <numFmt numFmtId="176" formatCode="dd-mmm-yyyy"/>
   </numFmts>
-  <fonts count="98">
+  <fonts count="101">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -644,6 +644,20 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="59">
@@ -1292,7 +1306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19"/>
   </cellStyleXfs>
-  <cellXfs count="398">
+  <cellXfs count="411">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2319,6 +2333,27 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="98" fillId="57" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="57" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="72" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="97" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2762,7 +2797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="3" customWidth="1" style="278" min="1" max="1"/>
@@ -2783,7 +2818,7 @@
     <row r="2" ht="24" customHeight="1" s="278">
       <c r="B2" s="362" t="inlineStr">
         <is>
-          <t>Last updated: 17 Jun 2026  |  Capital, Acquisition, Pre-Opening &amp; Renovation CapEx</t>
+          <t>Last updated: 1 Jul 2026  |  Capital, Acquisition, Pre-Opening, Renovation CapEx &amp; Operations↔Capital</t>
         </is>
       </c>
     </row>
@@ -2984,7 +3019,7 @@
       </c>
       <c r="F13" s="138" t="inlineStr">
         <is>
-          <t>⚠️ PARTIALLY PAID — $8,235 remaining</t>
+          <t>⚠️ PARTIALLY PAID — $2,235 remaining</t>
         </is>
       </c>
       <c r="G13" s="138" t="inlineStr">
@@ -3357,12 +3392,32 @@
       </c>
     </row>
     <row r="27" ht="19.95" customHeight="1" s="278">
-      <c r="B27" s="149" t="n"/>
-      <c r="C27" s="180" t="n"/>
-      <c r="D27" s="157" t="n"/>
-      <c r="E27" s="172" t="n"/>
-      <c r="F27" s="172" t="n"/>
-      <c r="G27" s="149" t="n"/>
+      <c r="B27" s="149" t="inlineStr">
+        <is>
+          <t>Additional Payment to Previous Owners — Jun 30</t>
+        </is>
+      </c>
+      <c r="C27" s="180" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D27" s="157" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E27" s="172" t="inlineStr">
+        <is>
+          <t>Lohith Reddy</t>
+        </is>
+      </c>
+      <c r="F27" s="172" t="inlineStr">
+        <is>
+          <t>✅ PAID</t>
+        </is>
+      </c>
+      <c r="G27" s="149" t="inlineStr">
+        <is>
+          <t>Additional capital payment to previous owners — 30 Jun 2026 (part of $16k transfer; rent portion logged separately)</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="19.95" customHeight="1" s="278">
       <c r="B28" s="149" t="n"/>
@@ -3411,7 +3466,7 @@
       </c>
       <c r="G31" s="150" t="inlineStr">
         <is>
-          <t>$390,000 − $366,235 paid (Jun 3–22) − $15,530 electricity offset = $8,235 remaining</t>
+          <t>$390,000 − $372,235 paid (Jun 3–30) − $15,530 electricity offset = $2,235 remaining</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3691,7 @@
       </c>
       <c r="C42" s="138" t="n"/>
       <c r="D42" s="146" t="n">
-        <v>125000</v>
+        <v>145000</v>
       </c>
       <c r="E42" s="138" t="inlineStr">
         <is>
@@ -3650,7 +3705,7 @@
       </c>
       <c r="G42" s="138" t="inlineStr">
         <is>
-          <t>For acquisition &amp; expenses</t>
+          <t>For acquisition &amp; expenses; $125,000 initial + $20,000 transferred 29 Jun 2026 = $145,000</t>
         </is>
       </c>
     </row>
@@ -5086,37 +5141,111 @@
       </c>
     </row>
     <row r="139">
-      <c r="B139" s="234">
-        <f>REMAINING WITH ME</f>
-        <v/>
-      </c>
-      <c r="D139" s="242">
-        <f>D136-D137-D138</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="B142" s="247" t="n"/>
+      <c r="B139" s="234" t="inlineStr">
+        <is>
+          <t>− Owner ledger balance settled from budget (rent + fronted items)</t>
+        </is>
+      </c>
+      <c r="D139" s="242" t="n">
+        <v>19314.81</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140">
+        <f>REMAINING WITH ME (budget left with Lohith)</f>
+        <v/>
+      </c>
+      <c r="D140">
+        <f>D136-D137-D138-D139</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142" ht="22" customHeight="1" s="278">
+      <c r="B142" s="398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K.  OPERATIONS ↔ CAPITAL  —  RUNNING POSITION</t>
+        </is>
+      </c>
     </row>
     <row r="143">
-      <c r="B143" s="189" t="n"/>
-      <c r="C143" s="236" t="n"/>
+      <c r="B143" s="400" t="inlineStr">
+        <is>
+          <t>Operating Income (all-time, from Daily Log)</t>
+        </is>
+      </c>
+      <c r="C143" s="401">
+        <f>SUM('📅 Daily Log'!D8:D500)+SUM('📅 Daily Log'!E8:E500)+SUM('📅 Daily Log'!G8:G500)</f>
+        <v/>
+      </c>
       <c r="D143" s="191" t="n"/>
       <c r="E143" s="190" t="n"/>
       <c r="F143" s="190" t="n"/>
       <c r="G143" s="189" t="n"/>
     </row>
     <row r="144">
-      <c r="B144" s="189" t="n"/>
-      <c r="C144" s="236" t="n"/>
+      <c r="B144" s="400" t="inlineStr">
+        <is>
+          <t>Operating Expenses (all-time, from Expenses)</t>
+        </is>
+      </c>
+      <c r="C144" s="401">
+        <f>SUM('💸 Expenses'!F8:F500)</f>
+        <v/>
+      </c>
       <c r="D144" s="191" t="n"/>
       <c r="E144" s="190" t="n"/>
       <c r="F144" s="190" t="n"/>
       <c r="G144" s="189" t="n"/>
     </row>
+    <row r="145">
+      <c r="B145" s="400" t="inlineStr">
+        <is>
+          <t>MP Commission (auto: card × 4.06%)</t>
+        </is>
+      </c>
+      <c r="C145" s="379">
+        <f>SUM('📅 Daily Log'!R8:R500)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="402" t="inlineStr">
+        <is>
+          <t>OPERATING RESULT  (income − expenses − commission)</t>
+        </is>
+      </c>
+      <c r="C146" s="379">
+        <f>C143-C144-C145</f>
+        <v/>
+      </c>
+      <c r="E146" s="403" t="n"/>
+    </row>
+    <row r="147">
+      <c r="B147" s="377" t="inlineStr">
+        <is>
+          <t>ADVANCE OWED by Operations to Capital</t>
+        </is>
+      </c>
+      <c r="C147" s="379" t="n">
+        <v>19314.81</v>
+      </c>
+      <c r="E147" s="405" t="inlineStr">
+        <is>
+          <t>Rent + fronted operating items funded from capital budget (settled 30 Jun). Add future capital-funded operating costs here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="406" t="inlineStr">
+        <is>
+          <t>MP commission now auto-calculated per day in Daily Log (col R) at the rate in T7; feeds this result and Cash-on-Hand automatically.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B148:H148"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B11:H11"/>
@@ -5276,7 +5405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="278" min="1" max="1"/>
@@ -6130,37 +6259,129 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="397" t="inlineStr">
+      <c r="A28" s="397" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B28" s="232" t="inlineStr">
+        <is>
+          <t>Renta media mensualidad Mayo 2026 (duenos anteriores) - paid by Lohith</t>
+        </is>
+      </c>
+      <c r="C28" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D28" s="232" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E28" s="233" t="n"/>
+      <c r="F28" s="233">
+        <f>IFERROR(F27+D28-E28,0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H28" s="232" t="inlineStr">
+        <is>
+          <t>May half-month rent fronted by Lohith; reimbursable</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="397" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B29" s="232" t="inlineStr">
+        <is>
+          <t>Owner balance settled from restaurant capital budget (paid from Remaining-with-Lohith)</t>
+        </is>
+      </c>
+      <c r="C29" s="232" t="inlineStr">
+        <is>
+          <t>Settlement</t>
+        </is>
+      </c>
+      <c r="D29" s="232" t="n"/>
+      <c r="E29" s="233" t="n">
+        <v>19314.81</v>
+      </c>
+      <c r="F29" s="233">
+        <f>IFERROR(F28+D29-E29,0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="232" t="inlineStr">
+        <is>
+          <t>✅ Settled from budget</t>
+        </is>
+      </c>
+      <c r="H29" s="232" t="inlineStr">
+        <is>
+          <t>Full owner ledger balance ($19,315 rent + fronted operating items) settled against capital budget remaining with Lohith. Going forward, rent &amp; operating costs funded from allocated budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="397" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B30" s="232" t="inlineStr">
+        <is>
+          <t>Customer transfer-to-me 30-Jun</t>
+        </is>
+      </c>
+      <c r="C30" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D30" s="232" t="n"/>
+      <c r="E30" s="233" t="n">
+        <v>55</v>
+      </c>
+      <c r="F30" s="233">
+        <f>IFERROR(F29+D30-E30,0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H30" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid 55 via direct transfer to Lohith instead of restaurant card/cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="397" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B28" s="232" t="n"/>
-      <c r="C28" s="232" t="n"/>
-      <c r="D28" s="232">
-        <f>SUM(D4:D27)</f>
-        <v/>
-      </c>
-      <c r="E28" s="233">
-        <f>SUM(E4:E27)</f>
-        <v/>
-      </c>
-      <c r="F28" s="233">
-        <f>F27</f>
-        <v/>
-      </c>
-      <c r="G28" s="232">
-        <f>IF(F27&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F27,"#,##0"),IF(F27&lt;0,"Lohith holds $"&amp;TEXT(ABS(F27),"#,##0"),"Zero balance"))</f>
-        <v/>
-      </c>
-      <c r="H28" s="232" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Positive balance = restaurant owes Lohith. This sheet is the single source for the owner balance.</t>
-        </is>
-      </c>
+      <c r="B31" s="232" t="n"/>
+      <c r="C31" s="232" t="n"/>
+      <c r="D31" s="232">
+        <f>SUM(D4:D30)</f>
+        <v/>
+      </c>
+      <c r="E31" s="233">
+        <f>SUM(E4:E30)</f>
+        <v/>
+      </c>
+      <c r="F31" s="233">
+        <f>F30</f>
+        <v/>
+      </c>
+      <c r="G31" s="232">
+        <f>IF(F30&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F30,"#,##0"),IF(F30&lt;0,"Lohith holds $"&amp;TEXT(ABS(F30),"#,##0"),"Zero balance"))</f>
+        <v/>
+      </c>
+      <c r="H31" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7915,7 +8136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q372"/>
+  <dimension ref="A1:T372"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="278" min="1" max="1"/>
@@ -8112,6 +8333,19 @@
           <t>Week Profit</t>
         </is>
       </c>
+      <c r="R7" s="407" t="inlineStr">
+        <is>
+          <t>MP Comm $</t>
+        </is>
+      </c>
+      <c r="S7" s="408" t="inlineStr">
+        <is>
+          <t>MP Rate</t>
+        </is>
+      </c>
+      <c r="T7" s="409" t="n">
+        <v>0.0406</v>
+      </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" s="278">
       <c r="B8" s="229" t="n">
@@ -8156,6 +8390,10 @@
       <c r="O8" s="45" t="n"/>
       <c r="P8" s="46" t="n"/>
       <c r="Q8" s="44" t="n"/>
+      <c r="R8" s="410">
+        <f>IFERROR(D8*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" s="278">
       <c r="B9" s="229" t="n">
@@ -8200,6 +8438,10 @@
       <c r="O9" s="57" t="n"/>
       <c r="P9" s="58" t="n"/>
       <c r="Q9" s="56" t="n"/>
+      <c r="R9" s="410">
+        <f>IFERROR(D9*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" s="278">
       <c r="B10" s="229" t="n">
@@ -8244,6 +8486,10 @@
       <c r="O10" s="45" t="n"/>
       <c r="P10" s="46" t="n"/>
       <c r="Q10" s="44" t="n"/>
+      <c r="R10" s="410">
+        <f>IFERROR(D10*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="16.5" customHeight="1" s="278">
       <c r="B11" s="229" t="n">
@@ -8288,6 +8534,10 @@
       <c r="O11" s="57" t="n"/>
       <c r="P11" s="58" t="n"/>
       <c r="Q11" s="56" t="n"/>
+      <c r="R11" s="410">
+        <f>IFERROR(D11*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="278">
       <c r="B12" s="229" t="n">
@@ -8332,6 +8582,10 @@
       <c r="O12" s="45" t="n"/>
       <c r="P12" s="46" t="n"/>
       <c r="Q12" s="44" t="n"/>
+      <c r="R12" s="410">
+        <f>IFERROR(D12*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="278">
       <c r="B13" s="229" t="n">
@@ -8380,6 +8634,10 @@
       <c r="O13" s="57" t="n"/>
       <c r="P13" s="58" t="n"/>
       <c r="Q13" s="56" t="n"/>
+      <c r="R13" s="410">
+        <f>IFERROR(D13*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="278">
       <c r="B14" s="229" t="n">
@@ -8426,6 +8684,10 @@
       <c r="O14" s="45" t="n"/>
       <c r="P14" s="46" t="n"/>
       <c r="Q14" s="44" t="n"/>
+      <c r="R14" s="410">
+        <f>IFERROR(D14*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="278">
       <c r="B15" s="229" t="n">
@@ -8470,6 +8732,10 @@
       <c r="O15" s="57" t="n"/>
       <c r="P15" s="58" t="n"/>
       <c r="Q15" s="56" t="n"/>
+      <c r="R15" s="410">
+        <f>IFERROR(D15*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="278">
       <c r="B16" s="229" t="n">
@@ -8514,6 +8780,10 @@
       <c r="O16" s="45" t="n"/>
       <c r="P16" s="46" t="n"/>
       <c r="Q16" s="44" t="n"/>
+      <c r="R16" s="410">
+        <f>IFERROR(D16*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="278">
       <c r="B17" s="229" t="n">
@@ -8558,6 +8828,10 @@
       <c r="O17" s="57" t="n"/>
       <c r="P17" s="58" t="n"/>
       <c r="Q17" s="56" t="n"/>
+      <c r="R17" s="410">
+        <f>IFERROR(D17*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="278">
       <c r="B18" s="229" t="n">
@@ -8602,6 +8876,10 @@
       <c r="O18" s="45" t="n"/>
       <c r="P18" s="46" t="n"/>
       <c r="Q18" s="44" t="n"/>
+      <c r="R18" s="410">
+        <f>IFERROR(D18*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="278">
       <c r="B19" s="229" t="n">
@@ -8646,6 +8924,10 @@
       <c r="O19" s="57" t="n"/>
       <c r="P19" s="58" t="n"/>
       <c r="Q19" s="56" t="n"/>
+      <c r="R19" s="410">
+        <f>IFERROR(D19*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" s="278">
       <c r="B20" s="229" t="n">
@@ -8690,6 +8972,10 @@
       <c r="O20" s="45" t="n"/>
       <c r="P20" s="46" t="n"/>
       <c r="Q20" s="44" t="n"/>
+      <c r="R20" s="410">
+        <f>IFERROR(D20*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="278">
       <c r="B21" s="229" t="n">
@@ -8732,6 +9018,10 @@
       <c r="O21" s="57" t="n"/>
       <c r="P21" s="58" t="n"/>
       <c r="Q21" s="56" t="n"/>
+      <c r="R21" s="410">
+        <f>IFERROR(D21*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="278">
       <c r="B22" s="229" t="n">
@@ -8778,6 +9068,10 @@
       <c r="O22" s="45" t="n"/>
       <c r="P22" s="46" t="n"/>
       <c r="Q22" s="44" t="n"/>
+      <c r="R22" s="410">
+        <f>IFERROR(D22*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="278">
       <c r="B23" s="229" t="n">
@@ -8824,6 +9118,10 @@
       <c r="O23" s="57" t="n"/>
       <c r="P23" s="58" t="n"/>
       <c r="Q23" s="56" t="n"/>
+      <c r="R23" s="410">
+        <f>IFERROR(D23*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="278">
       <c r="B24" s="229" t="n">
@@ -8870,6 +9168,10 @@
       <c r="O24" s="45" t="n"/>
       <c r="P24" s="46" t="n"/>
       <c r="Q24" s="44" t="n"/>
+      <c r="R24" s="410">
+        <f>IFERROR(D24*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" s="278">
       <c r="B25" s="229" t="n">
@@ -8914,6 +9216,10 @@
       <c r="O25" s="57" t="n"/>
       <c r="P25" s="58" t="n"/>
       <c r="Q25" s="56" t="n"/>
+      <c r="R25" s="410">
+        <f>IFERROR(D25*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="16.5" customHeight="1" s="278">
       <c r="B26" s="229" t="n">
@@ -8960,6 +9266,10 @@
       <c r="O26" s="45" t="n"/>
       <c r="P26" s="46" t="n"/>
       <c r="Q26" s="44" t="n"/>
+      <c r="R26" s="410">
+        <f>IFERROR(D26*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="16.5" customHeight="1" s="278">
       <c r="B27" s="229" t="n">
@@ -9004,6 +9314,10 @@
       <c r="O27" s="57" t="n"/>
       <c r="P27" s="58" t="n"/>
       <c r="Q27" s="56" t="n"/>
+      <c r="R27" s="410">
+        <f>IFERROR(D27*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="278">
       <c r="B28" s="229" t="n">
@@ -9041,6 +9355,10 @@
       <c r="O28" s="45" t="n"/>
       <c r="P28" s="46" t="n"/>
       <c r="Q28" s="44" t="n"/>
+      <c r="R28" s="410">
+        <f>IFERROR(D28*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="16.5" customHeight="1" s="278">
       <c r="B29" s="229" t="n">
@@ -9087,6 +9405,10 @@
       <c r="O29" s="57" t="n"/>
       <c r="P29" s="58" t="n"/>
       <c r="Q29" s="56" t="n"/>
+      <c r="R29" s="410">
+        <f>IFERROR(D29*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="278">
       <c r="B30" s="229" t="n">
@@ -9131,6 +9453,10 @@
       <c r="O30" s="45" t="n"/>
       <c r="P30" s="46" t="n"/>
       <c r="Q30" s="44" t="n"/>
+      <c r="R30" s="410">
+        <f>IFERROR(D30*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="16.5" customHeight="1" s="278">
       <c r="B31" s="229" t="n">
@@ -9175,6 +9501,10 @@
       <c r="O31" s="57" t="n"/>
       <c r="P31" s="58" t="n"/>
       <c r="Q31" s="56" t="n"/>
+      <c r="R31" s="410">
+        <f>IFERROR(D31*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="16.5" customHeight="1" s="278">
       <c r="B32" s="229" t="n">
@@ -9221,6 +9551,10 @@
       <c r="O32" s="45" t="n"/>
       <c r="P32" s="46" t="n"/>
       <c r="Q32" s="44" t="n"/>
+      <c r="R32" s="410">
+        <f>IFERROR(D32*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="278">
       <c r="B33" s="229" t="n">
@@ -9267,6 +9601,10 @@
       <c r="O33" s="57" t="n"/>
       <c r="P33" s="58" t="n"/>
       <c r="Q33" s="56" t="n"/>
+      <c r="R33" s="410">
+        <f>IFERROR(D33*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="278">
       <c r="B34" s="229" t="n">
@@ -9313,6 +9651,10 @@
       <c r="O34" s="45" t="n"/>
       <c r="P34" s="46" t="n"/>
       <c r="Q34" s="44" t="n"/>
+      <c r="R34" s="410">
+        <f>IFERROR(D34*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="278">
       <c r="B35" s="229" t="n">
@@ -9359,6 +9701,10 @@
       <c r="O35" s="57" t="n"/>
       <c r="P35" s="58" t="n"/>
       <c r="Q35" s="56" t="n"/>
+      <c r="R35" s="410">
+        <f>IFERROR(D35*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="278">
       <c r="B36" s="229" t="n">
@@ -9405,6 +9751,10 @@
       <c r="O36" s="45" t="n"/>
       <c r="P36" s="46" t="n"/>
       <c r="Q36" s="44" t="n"/>
+      <c r="R36" s="410">
+        <f>IFERROR(D36*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="278">
       <c r="B37" s="229" t="n">
@@ -9451,6 +9801,10 @@
       <c r="O37" s="57" t="n"/>
       <c r="P37" s="58" t="n"/>
       <c r="Q37" s="56" t="n"/>
+      <c r="R37" s="410">
+        <f>IFERROR(D37*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="278">
       <c r="B38" s="229" t="n">
@@ -9497,6 +9851,10 @@
       <c r="O38" s="45" t="n"/>
       <c r="P38" s="46" t="n"/>
       <c r="Q38" s="44" t="n"/>
+      <c r="R38" s="410">
+        <f>IFERROR(D38*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" s="278">
       <c r="B39" s="229" t="n">
@@ -9543,6 +9901,10 @@
       <c r="O39" s="57" t="n"/>
       <c r="P39" s="58" t="n"/>
       <c r="Q39" s="56" t="n"/>
+      <c r="R39" s="410">
+        <f>IFERROR(D39*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="40" ht="16.5" customHeight="1" s="278">
       <c r="B40" s="229" t="n">
@@ -9589,6 +9951,10 @@
       <c r="O40" s="45" t="n"/>
       <c r="P40" s="46" t="n"/>
       <c r="Q40" s="44" t="n"/>
+      <c r="R40" s="410">
+        <f>IFERROR(D40*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" s="278">
       <c r="B41" s="229" t="n">
@@ -9635,6 +10001,10 @@
       <c r="O41" s="57" t="n"/>
       <c r="P41" s="58" t="n"/>
       <c r="Q41" s="56" t="n"/>
+      <c r="R41" s="410">
+        <f>IFERROR(D41*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="278">
       <c r="B42" s="385" t="n">
@@ -9681,6 +10051,10 @@
       <c r="O42" s="45" t="n"/>
       <c r="P42" s="46" t="n"/>
       <c r="Q42" s="44" t="n"/>
+      <c r="R42" s="410">
+        <f>IFERROR(D42*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="278">
       <c r="B43" s="385" t="n">
@@ -9727,6 +10101,10 @@
       <c r="O43" s="57" t="n"/>
       <c r="P43" s="58" t="n"/>
       <c r="Q43" s="56" t="n"/>
+      <c r="R43" s="410">
+        <f>IFERROR(D43*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" s="278">
       <c r="B44" s="385" t="n">
@@ -9773,6 +10151,10 @@
       <c r="O44" s="45" t="n"/>
       <c r="P44" s="46" t="n"/>
       <c r="Q44" s="44" t="n"/>
+      <c r="R44" s="410">
+        <f>IFERROR(D44*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" s="278">
       <c r="B45" s="385" t="n">
@@ -9819,6 +10201,10 @@
       <c r="O45" s="57" t="n"/>
       <c r="P45" s="58" t="n"/>
       <c r="Q45" s="56" t="n"/>
+      <c r="R45" s="410">
+        <f>IFERROR(D45*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="278">
       <c r="B46" s="385" t="n">
@@ -9865,6 +10251,10 @@
       <c r="O46" s="45" t="n"/>
       <c r="P46" s="46" t="n"/>
       <c r="Q46" s="44" t="n"/>
+      <c r="R46" s="410">
+        <f>IFERROR(D46*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="278">
       <c r="B47" s="385" t="n">
@@ -9911,6 +10301,10 @@
       <c r="O47" s="57" t="n"/>
       <c r="P47" s="58" t="n"/>
       <c r="Q47" s="56" t="n"/>
+      <c r="R47" s="410">
+        <f>IFERROR(D47*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="48" ht="16.5" customHeight="1" s="278">
       <c r="B48" s="385" t="n">
@@ -9957,6 +10351,10 @@
       <c r="O48" s="45" t="n"/>
       <c r="P48" s="46" t="n"/>
       <c r="Q48" s="44" t="n"/>
+      <c r="R48" s="410">
+        <f>IFERROR(D48*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="278">
       <c r="B49" s="385" t="n">
@@ -10003,6 +10401,10 @@
       <c r="O49" s="57" t="n"/>
       <c r="P49" s="58" t="n"/>
       <c r="Q49" s="56" t="n"/>
+      <c r="R49" s="410">
+        <f>IFERROR(D49*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" s="278">
       <c r="B50" s="385" t="n">
@@ -10049,24 +10451,60 @@
       <c r="O50" s="45" t="n"/>
       <c r="P50" s="46" t="n"/>
       <c r="Q50" s="44" t="n"/>
+      <c r="R50" s="410">
+        <f>IFERROR(D50*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="51" ht="16.5" customHeight="1" s="278">
-      <c r="B51" s="34" t="n"/>
-      <c r="C51" s="47" t="n"/>
-      <c r="D51" s="48" t="n"/>
-      <c r="E51" s="49" t="n"/>
-      <c r="F51" s="50" t="n"/>
-      <c r="G51" s="51" t="n"/>
-      <c r="H51" s="52" t="n"/>
-      <c r="I51" s="53" t="n"/>
-      <c r="J51" s="54" t="n"/>
-      <c r="K51" s="55" t="n"/>
-      <c r="L51" s="18" t="n"/>
+      <c r="B51" s="385" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C51" s="256" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D51" s="257" t="n">
+        <v>2408</v>
+      </c>
+      <c r="E51" s="49" t="n">
+        <v>1670</v>
+      </c>
+      <c r="F51" s="50">
+        <f>IFERROR(D51+E51+G51,0)</f>
+        <v/>
+      </c>
+      <c r="G51" s="258" t="n">
+        <v>55</v>
+      </c>
+      <c r="H51" s="259">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B51,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B51+1))</f>
+        <v/>
+      </c>
+      <c r="I51" s="260">
+        <f>IFERROR(F51-H51,0)</f>
+        <v/>
+      </c>
+      <c r="J51" s="261">
+        <f>IFERROR(I51/F51,0)</f>
+        <v/>
+      </c>
+      <c r="K51" s="255" t="n"/>
+      <c r="L51" s="262" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
       <c r="M51" s="21" t="n"/>
       <c r="N51" s="56" t="n"/>
       <c r="O51" s="57" t="n"/>
       <c r="P51" s="58" t="n"/>
       <c r="Q51" s="56" t="n"/>
+      <c r="R51" s="410">
+        <f>IFERROR(D51*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="52" ht="16.5" customHeight="1" s="278">
       <c r="B52" s="34" t="n"/>
@@ -32150,64 +32588,262 @@
       </c>
     </row>
     <row r="391">
-      <c r="B391" s="64" t="n"/>
-      <c r="C391" s="65" t="n"/>
-      <c r="D391" s="66" t="n"/>
-      <c r="E391" s="65" t="n"/>
-      <c r="F391" s="67" t="n"/>
-      <c r="G391" s="14" t="n"/>
-      <c r="H391" s="14" t="n"/>
-      <c r="I391" s="43" t="n"/>
+      <c r="B391" s="382" t="n">
+        <v>46173</v>
+      </c>
+      <c r="C391" s="248" t="inlineStr">
+        <is>
+          <t>Renta media mensualidad Mayo 2026 (duenos anteriores)</t>
+        </is>
+      </c>
+      <c r="D391" s="249" t="inlineStr">
+        <is>
+          <t>Previous Owners (landlord)</t>
+        </is>
+      </c>
+      <c r="E391" s="248" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="F391" s="67" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G391" s="250" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H391" s="250" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="I391" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J391" s="383" t="inlineStr">
+        <is>
+          <t>May half-month rent (partial first month); transferred by Lohith to previous owners; reimbursable</t>
+        </is>
+      </c>
     </row>
     <row r="392">
-      <c r="B392" s="64" t="n"/>
-      <c r="C392" s="69" t="n"/>
-      <c r="D392" s="68" t="n"/>
-      <c r="E392" s="69" t="n"/>
-      <c r="F392" s="70" t="n"/>
-      <c r="G392" s="23" t="n"/>
-      <c r="H392" s="23" t="n"/>
-      <c r="I392" s="55" t="n"/>
+      <c r="B392" s="382" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C392" s="252" t="inlineStr">
+        <is>
+          <t>Pan Dulces (no bill receipt)</t>
+        </is>
+      </c>
+      <c r="D392" s="253" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E392" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F392" s="70" t="n">
+        <v>96</v>
+      </c>
+      <c r="G392" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H392" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I392" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J392" s="383" t="inlineStr">
+        <is>
+          <t>No receipt available; cash purchase</t>
+        </is>
+      </c>
     </row>
     <row r="393">
-      <c r="B393" s="64" t="n"/>
-      <c r="C393" s="65" t="n"/>
-      <c r="D393" s="66" t="n"/>
-      <c r="E393" s="65" t="n"/>
-      <c r="F393" s="67" t="n"/>
-      <c r="G393" s="14" t="n"/>
-      <c r="H393" s="14" t="n"/>
-      <c r="I393" s="43" t="n"/>
+      <c r="B393" s="382" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C393" s="248" t="inlineStr">
+        <is>
+          <t>Tortillas blancas 2.055kg + Bolillo x6</t>
+        </is>
+      </c>
+      <c r="D393" s="249" t="inlineStr">
+        <is>
+          <t>Chedraui Paseo</t>
+        </is>
+      </c>
+      <c r="E393" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F393" s="67" t="n">
+        <v>43.17</v>
+      </c>
+      <c r="G393" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H393" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I393" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J393" s="383" t="inlineStr">
+        <is>
+          <t>Debito BBVA; ticket 30-Jun 08:38</t>
+        </is>
+      </c>
     </row>
     <row r="394">
-      <c r="B394" s="64" t="n"/>
-      <c r="C394" s="69" t="n"/>
-      <c r="D394" s="68" t="n"/>
-      <c r="E394" s="69" t="n"/>
-      <c r="F394" s="70" t="n"/>
-      <c r="G394" s="23" t="n"/>
-      <c r="H394" s="23" t="n"/>
-      <c r="I394" s="55" t="n"/>
+      <c r="B394" s="382" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C394" s="252" t="inlineStr">
+        <is>
+          <t>Pan hamburguesa ajonjoli x24, pan caja arandano 900g x4, chapata x24</t>
+        </is>
+      </c>
+      <c r="D394" s="253" t="inlineStr">
+        <is>
+          <t>Productos Real La Cruz</t>
+        </is>
+      </c>
+      <c r="E394" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F394" s="70" t="n">
+        <v>728</v>
+      </c>
+      <c r="G394" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H394" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I394" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J394" s="383" t="inlineStr">
+        <is>
+          <t>Tarjeta debito; base $740 - $12 desc = $728; folio 4423</t>
+        </is>
+      </c>
     </row>
     <row r="395">
-      <c r="B395" s="64" t="n"/>
-      <c r="C395" s="65" t="n"/>
-      <c r="D395" s="66" t="n"/>
-      <c r="E395" s="65" t="n"/>
-      <c r="F395" s="67" t="n"/>
-      <c r="G395" s="14" t="n"/>
-      <c r="H395" s="14" t="n"/>
-      <c r="I395" s="43" t="n"/>
+      <c r="B395" s="382" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C395" s="248" t="inlineStr">
+        <is>
+          <t>Queso Gouda Menona 2.06kg @ $135/kg</t>
+        </is>
+      </c>
+      <c r="D395" s="249" t="inlineStr">
+        <is>
+          <t>La Bodega del Buen Queso</t>
+        </is>
+      </c>
+      <c r="E395" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Dairy</t>
+        </is>
+      </c>
+      <c r="F395" s="67" t="n">
+        <v>278.1</v>
+      </c>
+      <c r="G395" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H395" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I395" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J395" s="383" t="inlineStr">
+        <is>
+          <t>Efectivo; nota 0032709</t>
+        </is>
+      </c>
     </row>
     <row r="396">
-      <c r="B396" s="64" t="n"/>
-      <c r="C396" s="69" t="n"/>
-      <c r="D396" s="68" t="n"/>
-      <c r="E396" s="69" t="n"/>
-      <c r="F396" s="70" t="n"/>
-      <c r="G396" s="23" t="n"/>
-      <c r="H396" s="23" t="n"/>
-      <c r="I396" s="55" t="n"/>
+      <c r="B396" s="382" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C396" s="252" t="inlineStr">
+        <is>
+          <t>Miscelanea LC remision (2 lineas manuscritas ilegibles)</t>
+        </is>
+      </c>
+      <c r="D396" s="253" t="inlineStr">
+        <is>
+          <t>Miscelanea LC La Cruz</t>
+        </is>
+      </c>
+      <c r="E396" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Other</t>
+        </is>
+      </c>
+      <c r="F396" s="70" t="n">
+        <v>436</v>
+      </c>
+      <c r="G396" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H396" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I396" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J396" s="383" t="inlineStr">
+        <is>
+          <t>Getnet $436 autoritativo (Aut 785588, 11:38); lineas ~$197 + 'CH Alto' ~$239 ilegibles - confirmar articulos</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="B397" s="64" t="n"/>
@@ -43135,7 +43771,7 @@
     <row r="26">
       <c r="A26" s="380" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Ingredients - Bread</t>
         </is>
       </c>
       <c r="B26" s="378">
@@ -43159,7 +43795,7 @@
     <row r="27">
       <c r="A27" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Bread</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B27" s="378">
@@ -43255,7 +43891,7 @@
     <row r="31">
       <c r="A31" s="380" t="inlineStr">
         <is>
-          <t>Software / Subscription</t>
+          <t>Ingredients - Other</t>
         </is>
       </c>
       <c r="B31" s="378">
@@ -43279,7 +43915,7 @@
     <row r="32">
       <c r="A32" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Other</t>
+          <t>Software / Subscription</t>
         </is>
       </c>
       <c r="B32" s="378">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -10507,22 +10507,54 @@
       </c>
     </row>
     <row r="52" ht="16.5" customHeight="1" s="278">
-      <c r="B52" s="34" t="n"/>
-      <c r="C52" s="35" t="n"/>
-      <c r="D52" s="36" t="n"/>
-      <c r="E52" s="37" t="n"/>
-      <c r="F52" s="38" t="n"/>
-      <c r="G52" s="39" t="n"/>
-      <c r="H52" s="40" t="n"/>
-      <c r="I52" s="41" t="n"/>
-      <c r="J52" s="42" t="n"/>
-      <c r="K52" s="43" t="n"/>
-      <c r="L52" s="9" t="n"/>
+      <c r="B52" s="385" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C52" s="386" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D52" s="387" t="n">
+        <v>2498</v>
+      </c>
+      <c r="E52" s="37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F52" s="38">
+        <f>IFERROR(D52+E52+G52,0)</f>
+        <v/>
+      </c>
+      <c r="G52" s="388" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="389">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B52,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B52+1))</f>
+        <v/>
+      </c>
+      <c r="I52" s="390">
+        <f>IFERROR(F52-H52,0)</f>
+        <v/>
+      </c>
+      <c r="J52" s="391">
+        <f>IFERROR(I52/F52,0)</f>
+        <v/>
+      </c>
+      <c r="K52" s="251" t="n"/>
+      <c r="L52" s="392" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
       <c r="M52" s="12" t="n"/>
       <c r="N52" s="44" t="n"/>
       <c r="O52" s="45" t="n"/>
       <c r="P52" s="46" t="n"/>
       <c r="Q52" s="44" t="n"/>
+      <c r="R52" s="410">
+        <f>IFERROR(D52*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="53" ht="16.5" customHeight="1" s="278">
       <c r="B53" s="34" t="n"/>
@@ -16286,9 +16318,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -32846,124 +32878,520 @@
       </c>
     </row>
     <row r="397">
-      <c r="B397" s="64" t="n"/>
-      <c r="C397" s="65" t="n"/>
-      <c r="D397" s="66" t="n"/>
-      <c r="E397" s="65" t="n"/>
-      <c r="F397" s="67" t="n"/>
-      <c r="G397" s="14" t="n"/>
-      <c r="H397" s="14" t="n"/>
-      <c r="I397" s="43" t="n"/>
+      <c r="B397" s="382" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C397" s="248" t="inlineStr">
+        <is>
+          <t>Aceite La Posada 800 x2</t>
+        </is>
+      </c>
+      <c r="D397" s="249" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E397" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F397" s="67" t="n">
+        <v>56</v>
+      </c>
+      <c r="G397" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H397" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I397" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J397" s="383" t="inlineStr">
+        <is>
+          <t>OXXO 09:14; cooking oil</t>
+        </is>
+      </c>
     </row>
     <row r="398">
-      <c r="B398" s="64" t="n"/>
-      <c r="C398" s="69" t="n"/>
-      <c r="D398" s="68" t="n"/>
-      <c r="E398" s="69" t="n"/>
-      <c r="F398" s="70" t="n"/>
-      <c r="G398" s="23" t="n"/>
-      <c r="H398" s="23" t="n"/>
-      <c r="I398" s="55" t="n"/>
+      <c r="B398" s="382" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C398" s="252" t="inlineStr">
+        <is>
+          <t>Horchata/Jamaica/Limonada 1L x6 c/u (18 pzas)</t>
+        </is>
+      </c>
+      <c r="D398" s="253" t="inlineStr">
+        <is>
+          <t>Casa Reca</t>
+        </is>
+      </c>
+      <c r="E398" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F398" s="70" t="n">
+        <v>450</v>
+      </c>
+      <c r="G398" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H398" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I398" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J398" s="383" t="inlineStr">
+        <is>
+          <t>Nota venta ruta preventa Casa Reca; facturado a 'CAFE OH LELE' = nombre anterior de LOKA (OK); efectivo confirmado</t>
+        </is>
+      </c>
     </row>
     <row r="399">
-      <c r="B399" s="64" t="n"/>
-      <c r="C399" s="65" t="n"/>
-      <c r="D399" s="66" t="n"/>
-      <c r="E399" s="65" t="n"/>
-      <c r="F399" s="67" t="n"/>
-      <c r="G399" s="14" t="n"/>
-      <c r="H399" s="14" t="n"/>
-      <c r="I399" s="43" t="n"/>
+      <c r="B399" s="382" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C399" s="248" t="inlineStr">
+        <is>
+          <t>Salchicha nortena p/asar 1kg</t>
+        </is>
+      </c>
+      <c r="D399" s="249" t="inlineStr">
+        <is>
+          <t>San Juan Salchichonerias</t>
+        </is>
+      </c>
+      <c r="E399" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F399" s="67" t="n">
+        <v>73</v>
+      </c>
+      <c r="G399" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H399" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I399" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J399" s="383" t="inlineStr">
+        <is>
+          <t>Ticket 0255365 La Cruz 14:49; tarjeta Banregio</t>
+        </is>
+      </c>
     </row>
     <row r="400">
-      <c r="B400" s="64" t="n"/>
-      <c r="C400" s="69" t="n"/>
-      <c r="D400" s="68" t="n"/>
-      <c r="E400" s="69" t="n"/>
-      <c r="F400" s="70" t="n"/>
-      <c r="G400" s="23" t="n"/>
-      <c r="H400" s="23" t="n"/>
-      <c r="I400" s="55" t="n"/>
+      <c r="B400" s="382" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C400" s="252" t="inlineStr">
+        <is>
+          <t>Tortillas blancas x2</t>
+        </is>
+      </c>
+      <c r="D400" s="253" t="inlineStr">
+        <is>
+          <t>Chedraui Paseo</t>
+        </is>
+      </c>
+      <c r="E400" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F400" s="70" t="n">
+        <v>55.93</v>
+      </c>
+      <c r="G400" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H400" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I400" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J400" s="383" t="inlineStr">
+        <is>
+          <t>Debito BBVA; 08:55</t>
+        </is>
+      </c>
     </row>
     <row r="401">
-      <c r="B401" s="64" t="n"/>
-      <c r="C401" s="65" t="n"/>
-      <c r="D401" s="66" t="n"/>
-      <c r="E401" s="65" t="n"/>
-      <c r="F401" s="67" t="n"/>
-      <c r="G401" s="14" t="n"/>
-      <c r="H401" s="14" t="n"/>
-      <c r="I401" s="43" t="n"/>
+      <c r="B401" s="382" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C401" s="248" t="inlineStr">
+        <is>
+          <t>Muslo (pollo) 5.23kg @ $50/kg</t>
+        </is>
+      </c>
+      <c r="D401" s="249" t="inlineStr">
+        <is>
+          <t>Remision Loka Cafe</t>
+        </is>
+      </c>
+      <c r="E401" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F401" s="67" t="n">
+        <v>262</v>
+      </c>
+      <c r="G401" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H401" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I401" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J401" s="383" t="inlineStr">
+        <is>
+          <t>Nota remision manuscrita; 5.23x50=261.50, total escrito $262; metodo no confirmado</t>
+        </is>
+      </c>
     </row>
     <row r="402">
-      <c r="B402" s="64" t="n"/>
-      <c r="C402" s="69" t="n"/>
-      <c r="D402" s="68" t="n"/>
-      <c r="E402" s="69" t="n"/>
-      <c r="F402" s="70" t="n"/>
-      <c r="G402" s="23" t="n"/>
-      <c r="H402" s="23" t="n"/>
-      <c r="I402" s="55" t="n"/>
+      <c r="B402" s="382" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C402" s="252" t="inlineStr">
+        <is>
+          <t>Rosca chocolate base + salchicha p/asar 800 x2</t>
+        </is>
+      </c>
+      <c r="D402" s="253" t="inlineStr">
+        <is>
+          <t>H-E-B</t>
+        </is>
+      </c>
+      <c r="E402" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Other</t>
+        </is>
+      </c>
+      <c r="F402" s="70" t="n">
+        <v>246.8</v>
+      </c>
+      <c r="G402" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H402" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I402" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J402" s="383" t="inlineStr">
+        <is>
+          <t>Cuenta tarjeta ***3982; rosca $105 + salchicha $141.80; incl IEPS</t>
+        </is>
+      </c>
     </row>
     <row r="403">
-      <c r="B403" s="64" t="n"/>
-      <c r="C403" s="65" t="n"/>
-      <c r="D403" s="66" t="n"/>
-      <c r="E403" s="65" t="n"/>
-      <c r="F403" s="67" t="n"/>
-      <c r="G403" s="14" t="n"/>
-      <c r="H403" s="14" t="n"/>
-      <c r="I403" s="43" t="n"/>
+      <c r="B403" s="382" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C403" s="248" t="inlineStr">
+        <is>
+          <t>Aceite La Posada 800 x12</t>
+        </is>
+      </c>
+      <c r="D403" s="249" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E403" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F403" s="67" t="n">
+        <v>336</v>
+      </c>
+      <c r="G403" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H403" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I403" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J403" s="383" t="inlineStr">
+        <is>
+          <t>BBVA debito ML ***3982 AUT 922070; 18:35; cooking oil</t>
+        </is>
+      </c>
     </row>
     <row r="404">
-      <c r="B404" s="64" t="n"/>
-      <c r="C404" s="69" t="n"/>
-      <c r="D404" s="68" t="n"/>
-      <c r="E404" s="69" t="n"/>
-      <c r="F404" s="70" t="n"/>
-      <c r="G404" s="23" t="n"/>
-      <c r="H404" s="23" t="n"/>
-      <c r="I404" s="55" t="n"/>
+      <c r="B404" s="382" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C404" s="252" t="inlineStr">
+        <is>
+          <t>Pork Belly</t>
+        </is>
+      </c>
+      <c r="D404" s="253" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E404" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F404" s="70" t="n">
+        <v>355</v>
+      </c>
+      <c r="G404" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H404" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I404" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J404" s="383" t="inlineStr">
+        <is>
+          <t>No receipt; cash purchase</t>
+        </is>
+      </c>
     </row>
     <row r="405">
-      <c r="B405" s="64" t="n"/>
-      <c r="C405" s="65" t="n"/>
-      <c r="D405" s="66" t="n"/>
-      <c r="E405" s="65" t="n"/>
-      <c r="F405" s="67" t="n"/>
-      <c r="G405" s="14" t="n"/>
-      <c r="H405" s="14" t="n"/>
-      <c r="I405" s="43" t="n"/>
+      <c r="B405" s="382" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C405" s="248" t="inlineStr">
+        <is>
+          <t>Carne molida</t>
+        </is>
+      </c>
+      <c r="D405" s="249" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E405" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F405" s="67" t="n">
+        <v>271</v>
+      </c>
+      <c r="G405" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H405" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I405" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J405" s="383" t="inlineStr">
+        <is>
+          <t>No receipt; cash purchase</t>
+        </is>
+      </c>
     </row>
     <row r="406">
-      <c r="B406" s="64" t="n"/>
-      <c r="C406" s="69" t="n"/>
-      <c r="D406" s="68" t="n"/>
-      <c r="E406" s="69" t="n"/>
-      <c r="F406" s="70" t="n"/>
-      <c r="G406" s="23" t="n"/>
-      <c r="H406" s="23" t="n"/>
-      <c r="I406" s="55" t="n"/>
+      <c r="B406" s="382" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C406" s="252" t="inlineStr">
+        <is>
+          <t>Agua Ciel</t>
+        </is>
+      </c>
+      <c r="D406" s="253" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E406" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F406" s="70" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="G406" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H406" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I406" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J406" s="383" t="inlineStr">
+        <is>
+          <t>No receipt; cash purchase</t>
+        </is>
+      </c>
     </row>
     <row r="407">
-      <c r="B407" s="64" t="n"/>
-      <c r="C407" s="65" t="n"/>
-      <c r="D407" s="66" t="n"/>
-      <c r="E407" s="65" t="n"/>
-      <c r="F407" s="67" t="n"/>
-      <c r="G407" s="14" t="n"/>
-      <c r="H407" s="14" t="n"/>
-      <c r="I407" s="43" t="n"/>
+      <c r="B407" s="382" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C407" s="248" t="inlineStr">
+        <is>
+          <t>Agua natural</t>
+        </is>
+      </c>
+      <c r="D407" s="249" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E407" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F407" s="67" t="n">
+        <v>36</v>
+      </c>
+      <c r="G407" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H407" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I407" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J407" s="383" t="inlineStr">
+        <is>
+          <t>No receipt; cash purchase</t>
+        </is>
+      </c>
     </row>
     <row r="408">
-      <c r="B408" s="64" t="n"/>
-      <c r="C408" s="69" t="n"/>
-      <c r="D408" s="68" t="n"/>
-      <c r="E408" s="69" t="n"/>
-      <c r="F408" s="70" t="n"/>
-      <c r="G408" s="23" t="n"/>
-      <c r="H408" s="23" t="n"/>
-      <c r="I408" s="55" t="n"/>
+      <c r="B408" s="382" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C408" s="252" t="inlineStr">
+        <is>
+          <t>Hielos</t>
+        </is>
+      </c>
+      <c r="D408" s="253" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E408" s="252" t="inlineStr">
+        <is>
+          <t>Kitchen Supplies</t>
+        </is>
+      </c>
+      <c r="F408" s="70" t="n">
+        <v>150</v>
+      </c>
+      <c r="G408" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H408" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I408" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J408" s="383" t="inlineStr">
+        <is>
+          <t>No receipt; cash purchase</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="B409" s="64" t="n"/>
@@ -43185,7 +43613,7 @@
     <col width="34" bestFit="1" customWidth="1" style="278" min="1" max="1"/>
     <col width="15" bestFit="1" customWidth="1" style="278" min="2" max="3"/>
     <col width="15" customWidth="1" style="278" min="3" max="3"/>
-    <col width="9" customWidth="1" style="278" min="4" max="14"/>
+    <col width="15" customWidth="1" style="278" min="4" max="14"/>
     <col width="9" customWidth="1" style="278" min="5" max="5"/>
     <col width="9" customWidth="1" style="278" min="6" max="6"/>
     <col width="9" customWidth="1" style="278" min="7" max="7"/>
@@ -43199,14 +43627,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="278">
-      <c r="A1" s="372" t="inlineStr">
+      <c r="A1" s="384" t="inlineStr">
         <is>
           <t>LOKA — MONTHLY P&amp;L   (live formulas — auto-updates from Daily Log &amp; Expenses)</t>
         </is>
       </c>
-      <c r="B1" s="373" t="n"/>
-      <c r="C1" s="373" t="n"/>
-      <c r="D1" s="374" t="n"/>
+      <c r="B1" s="383" t="n"/>
+      <c r="C1" s="383" t="n"/>
+      <c r="D1" s="383" t="n"/>
       <c r="E1" s="374" t="n"/>
       <c r="F1" s="374" t="n"/>
       <c r="G1" s="374" t="n"/>
@@ -43246,7 +43674,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="D3" s="374" t="n"/>
+      <c r="D3" s="376" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
       <c r="E3" s="374" t="n"/>
       <c r="F3" s="374" t="n"/>
       <c r="G3" s="374" t="n"/>
@@ -43270,7 +43702,10 @@
         <f>SUMIFS('📅 Daily Log'!$F$8:$F$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D4" s="374" t="n"/>
+      <c r="D4" s="378">
+        <f>SUMIFS('📅 Daily Log'!$F$8:$F$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E4" s="374" t="n"/>
       <c r="F4" s="374" t="n"/>
       <c r="G4" s="374" t="n"/>
@@ -43294,7 +43729,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D5" s="374" t="n"/>
+      <c r="D5" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E5" s="374" t="n"/>
       <c r="F5" s="374" t="n"/>
       <c r="G5" s="374" t="n"/>
@@ -43318,7 +43756,10 @@
         <f>C4-C5</f>
         <v/>
       </c>
-      <c r="D6" s="374" t="n"/>
+      <c r="D6" s="379">
+        <f>D4-D5</f>
+        <v/>
+      </c>
       <c r="E6" s="374" t="n"/>
       <c r="F6" s="374" t="n"/>
       <c r="G6" s="374" t="n"/>
@@ -43342,7 +43783,10 @@
         <f>COUNTIFS('📅 Daily Log'!$F$8:$F$500,"&gt;0",'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D7" s="374" t="n"/>
+      <c r="D7" s="381">
+        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$500,"&gt;0",'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E7" s="374" t="n"/>
       <c r="F7" s="374" t="n"/>
       <c r="G7" s="374" t="n"/>
@@ -43366,7 +43810,10 @@
         <f>IFERROR(C4/C7,0)</f>
         <v/>
       </c>
-      <c r="D8" s="374" t="n"/>
+      <c r="D8" s="378">
+        <f>IFERROR(D4/D7,0)</f>
+        <v/>
+      </c>
       <c r="E8" s="374" t="n"/>
       <c r="F8" s="374" t="n"/>
       <c r="G8" s="374" t="n"/>
@@ -43406,7 +43853,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="D10" s="374" t="n"/>
+      <c r="D10" s="376" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
       <c r="E10" s="374" t="n"/>
       <c r="F10" s="374" t="n"/>
       <c r="G10" s="374" t="n"/>
@@ -43430,7 +43881,10 @@
         <f>SUMIFS('📅 Daily Log'!$D$8:$D$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D11" s="374" t="n"/>
+      <c r="D11" s="378">
+        <f>SUMIFS('📅 Daily Log'!$D$8:$D$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E11" s="374" t="n"/>
       <c r="F11" s="374" t="n"/>
       <c r="G11" s="374" t="n"/>
@@ -43454,7 +43908,10 @@
         <f>SUMIFS('📅 Daily Log'!$E$8:$E$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D12" s="374" t="n"/>
+      <c r="D12" s="378">
+        <f>SUMIFS('📅 Daily Log'!$E$8:$E$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E12" s="374" t="n"/>
       <c r="F12" s="374" t="n"/>
       <c r="G12" s="374" t="n"/>
@@ -43478,7 +43935,10 @@
         <f>SUMIFS('📅 Daily Log'!$G$8:$G$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D13" s="374" t="n"/>
+      <c r="D13" s="378">
+        <f>SUMIFS('📅 Daily Log'!$G$8:$G$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E13" s="374" t="n"/>
       <c r="F13" s="374" t="n"/>
       <c r="G13" s="374" t="n"/>
@@ -43502,7 +43962,10 @@
         <f>C11+C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="374" t="n"/>
+      <c r="D14" s="379">
+        <f>D11+D12+D13</f>
+        <v/>
+      </c>
       <c r="E14" s="374" t="n"/>
       <c r="F14" s="374" t="n"/>
       <c r="G14" s="374" t="n"/>
@@ -43542,7 +44005,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="D16" s="374" t="n"/>
+      <c r="D16" s="376" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
       <c r="E16" s="374" t="n"/>
       <c r="F16" s="374" t="n"/>
       <c r="G16" s="374" t="n"/>
@@ -43566,7 +44033,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A17,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D17" s="374" t="n"/>
+      <c r="D17" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A17,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E17" s="374" t="n"/>
       <c r="F17" s="374" t="n"/>
       <c r="G17" s="374" t="n"/>
@@ -43590,7 +44060,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A18,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D18" s="374" t="n"/>
+      <c r="D18" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A18,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E18" s="374" t="n"/>
       <c r="F18" s="374" t="n"/>
       <c r="G18" s="374" t="n"/>
@@ -43614,7 +44087,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A19,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D19" s="374" t="n"/>
+      <c r="D19" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A19,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E19" s="374" t="n"/>
       <c r="F19" s="374" t="n"/>
       <c r="G19" s="374" t="n"/>
@@ -43627,7 +44103,7 @@
     <row r="20">
       <c r="A20" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Vegetables</t>
+          <t>Ingredients - Pantry</t>
         </is>
       </c>
       <c r="B20" s="378">
@@ -43638,7 +44114,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A20,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D20" s="374" t="n"/>
+      <c r="D20" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A20,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E20" s="374" t="n"/>
       <c r="F20" s="374" t="n"/>
       <c r="G20" s="374" t="n"/>
@@ -43651,7 +44130,7 @@
     <row r="21">
       <c r="A21" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Pantry</t>
+          <t>Ingredients - Vegetables</t>
         </is>
       </c>
       <c r="B21" s="378">
@@ -43662,7 +44141,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A21,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D21" s="374" t="n"/>
+      <c r="D21" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A21,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E21" s="374" t="n"/>
       <c r="F21" s="374" t="n"/>
       <c r="G21" s="374" t="n"/>
@@ -43686,7 +44168,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A22,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D22" s="374" t="n"/>
+      <c r="D22" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A22,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E22" s="374" t="n"/>
       <c r="F22" s="374" t="n"/>
       <c r="G22" s="374" t="n"/>
@@ -43710,7 +44195,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A23,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D23" s="374" t="n"/>
+      <c r="D23" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A23,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E23" s="374" t="n"/>
       <c r="F23" s="374" t="n"/>
       <c r="G23" s="374" t="n"/>
@@ -43734,7 +44222,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A24,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D24" s="374" t="n"/>
+      <c r="D24" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A24,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E24" s="374" t="n"/>
       <c r="F24" s="374" t="n"/>
       <c r="G24" s="374" t="n"/>
@@ -43758,7 +44249,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A25,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D25" s="374" t="n"/>
+      <c r="D25" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A25,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E25" s="374" t="n"/>
       <c r="F25" s="374" t="n"/>
       <c r="G25" s="374" t="n"/>
@@ -43782,7 +44276,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A26,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D26" s="374" t="n"/>
+      <c r="D26" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A26,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E26" s="374" t="n"/>
       <c r="F26" s="374" t="n"/>
       <c r="G26" s="374" t="n"/>
@@ -43806,7 +44303,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A27,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D27" s="374" t="n"/>
+      <c r="D27" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A27,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E27" s="374" t="n"/>
       <c r="F27" s="374" t="n"/>
       <c r="G27" s="374" t="n"/>
@@ -43830,7 +44330,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A28,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D28" s="374" t="n"/>
+      <c r="D28" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A28,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E28" s="374" t="n"/>
       <c r="F28" s="374" t="n"/>
       <c r="G28" s="374" t="n"/>
@@ -43854,7 +44357,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A29,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D29" s="374" t="n"/>
+      <c r="D29" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A29,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E29" s="374" t="n"/>
       <c r="F29" s="374" t="n"/>
       <c r="G29" s="374" t="n"/>
@@ -43878,7 +44384,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A30,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D30" s="374" t="n"/>
+      <c r="D30" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A30,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E30" s="374" t="n"/>
       <c r="F30" s="374" t="n"/>
       <c r="G30" s="374" t="n"/>
@@ -43902,7 +44411,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A31,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D31" s="374" t="n"/>
+      <c r="D31" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A31,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E31" s="374" t="n"/>
       <c r="F31" s="374" t="n"/>
       <c r="G31" s="374" t="n"/>
@@ -43926,7 +44438,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A32,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D32" s="374" t="n"/>
+      <c r="D32" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A32,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E32" s="374" t="n"/>
       <c r="F32" s="374" t="n"/>
       <c r="G32" s="374" t="n"/>
@@ -43939,7 +44454,7 @@
     <row r="33">
       <c r="A33" s="380" t="inlineStr">
         <is>
-          <t>Staff - Advance</t>
+          <t>Kitchen Supplies</t>
         </is>
       </c>
       <c r="B33" s="378">
@@ -43950,7 +44465,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A33,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D33" s="374" t="n"/>
+      <c r="D33" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A33,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E33" s="374" t="n"/>
       <c r="F33" s="374" t="n"/>
       <c r="G33" s="374" t="n"/>
@@ -43963,7 +44481,7 @@
     <row r="34">
       <c r="A34" s="380" t="inlineStr">
         <is>
-          <t>Kitchen Supplies</t>
+          <t>Staff - Advance</t>
         </is>
       </c>
       <c r="B34" s="378">
@@ -43974,7 +44492,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A34,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D34" s="374" t="n"/>
+      <c r="D34" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A34,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E34" s="374" t="n"/>
       <c r="F34" s="374" t="n"/>
       <c r="G34" s="374" t="n"/>
@@ -43998,7 +44519,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A35,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D35" s="374" t="n"/>
+      <c r="D35" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A35,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E35" s="374" t="n"/>
       <c r="F35" s="374" t="n"/>
       <c r="G35" s="374" t="n"/>
@@ -44022,7 +44546,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A36,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D36" s="374" t="n"/>
+      <c r="D36" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A36,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E36" s="374" t="n"/>
       <c r="F36" s="374" t="n"/>
       <c r="G36" s="374" t="n"/>
@@ -44046,7 +44573,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A37,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D37" s="374" t="n"/>
+      <c r="D37" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A37,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E37" s="374" t="n"/>
       <c r="F37" s="374" t="n"/>
       <c r="G37" s="374" t="n"/>
@@ -44070,7 +44600,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A38,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D38" s="374" t="n"/>
+      <c r="D38" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A38,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E38" s="374" t="n"/>
       <c r="F38" s="374" t="n"/>
       <c r="G38" s="374" t="n"/>
@@ -44094,7 +44627,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A39,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D39" s="374" t="n"/>
+      <c r="D39" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A39,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E39" s="374" t="n"/>
       <c r="F39" s="374" t="n"/>
       <c r="G39" s="374" t="n"/>
@@ -44118,7 +44654,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A40,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D40" s="374" t="n"/>
+      <c r="D40" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A40,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E40" s="374" t="n"/>
       <c r="F40" s="374" t="n"/>
       <c r="G40" s="374" t="n"/>
@@ -44142,7 +44681,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A41,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D41" s="374" t="n"/>
+      <c r="D41" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A41,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E41" s="374" t="n"/>
       <c r="F41" s="374" t="n"/>
       <c r="G41" s="374" t="n"/>
@@ -44166,7 +44708,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D42" s="374" t="n"/>
+      <c r="D42" s="379">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
       <c r="E42" s="374" t="n"/>
       <c r="F42" s="374" t="n"/>
       <c r="G42" s="374" t="n"/>
@@ -44190,7 +44735,10 @@
         <f>C4-C42</f>
         <v/>
       </c>
-      <c r="D43" s="374" t="n"/>
+      <c r="D43" s="379">
+        <f>D4-D42</f>
+        <v/>
+      </c>
       <c r="E43" s="374" t="n"/>
       <c r="F43" s="374" t="n"/>
       <c r="G43" s="374" t="n"/>
@@ -44440,7 +44988,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -10557,22 +10557,58 @@
       </c>
     </row>
     <row r="53" ht="16.5" customHeight="1" s="278">
-      <c r="B53" s="34" t="n"/>
-      <c r="C53" s="47" t="n"/>
-      <c r="D53" s="48" t="n"/>
-      <c r="E53" s="49" t="n"/>
-      <c r="F53" s="50" t="n"/>
-      <c r="G53" s="51" t="n"/>
-      <c r="H53" s="52" t="n"/>
-      <c r="I53" s="53" t="n"/>
-      <c r="J53" s="54" t="n"/>
-      <c r="K53" s="55" t="n"/>
-      <c r="L53" s="18" t="n"/>
+      <c r="B53" s="385" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C53" s="256" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D53" s="257" t="n">
+        <v>1859</v>
+      </c>
+      <c r="E53" s="49" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F53" s="50">
+        <f>IFERROR(D53+E53+G53,0)</f>
+        <v/>
+      </c>
+      <c r="G53" s="258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="259">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B53,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B53+1))</f>
+        <v/>
+      </c>
+      <c r="I53" s="260">
+        <f>IFERROR(F53-H53,0)</f>
+        <v/>
+      </c>
+      <c r="J53" s="261">
+        <f>IFERROR(I53/F53,0)</f>
+        <v/>
+      </c>
+      <c r="K53" s="255" t="inlineStr">
+        <is>
+          <t>incl +$120 additional card income (added 02-Jul)</t>
+        </is>
+      </c>
+      <c r="L53" s="262" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
       <c r="M53" s="21" t="n"/>
       <c r="N53" s="56" t="n"/>
       <c r="O53" s="57" t="n"/>
       <c r="P53" s="58" t="n"/>
       <c r="Q53" s="56" t="n"/>
+      <c r="R53" s="410">
+        <f>IFERROR(D53*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="54" ht="16.5" customHeight="1" s="278">
       <c r="B54" s="34" t="n"/>
@@ -16318,9 +16354,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -33394,24 +33430,90 @@
       </c>
     </row>
     <row r="409">
-      <c r="B409" s="64" t="n"/>
-      <c r="C409" s="65" t="n"/>
-      <c r="D409" s="66" t="n"/>
-      <c r="E409" s="65" t="n"/>
-      <c r="F409" s="67" t="n"/>
-      <c r="G409" s="14" t="n"/>
-      <c r="H409" s="14" t="n"/>
-      <c r="I409" s="43" t="n"/>
+      <c r="B409" s="382" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C409" s="248" t="inlineStr">
+        <is>
+          <t>Tomatoes</t>
+        </is>
+      </c>
+      <c r="D409" s="249" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E409" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F409" s="67" t="n">
+        <v>31</v>
+      </c>
+      <c r="G409" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H409" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I409" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J409" s="383" t="inlineStr">
+        <is>
+          <t>No receipt; cash purchase</t>
+        </is>
+      </c>
     </row>
     <row r="410">
-      <c r="B410" s="64" t="n"/>
-      <c r="C410" s="69" t="n"/>
-      <c r="D410" s="68" t="n"/>
-      <c r="E410" s="69" t="n"/>
-      <c r="F410" s="70" t="n"/>
-      <c r="G410" s="23" t="n"/>
-      <c r="H410" s="23" t="n"/>
-      <c r="I410" s="55" t="n"/>
+      <c r="B410" s="382" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C410" s="252" t="inlineStr">
+        <is>
+          <t>Bistec puerco (pork steak)</t>
+        </is>
+      </c>
+      <c r="D410" s="253" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E410" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F410" s="70" t="n">
+        <v>287</v>
+      </c>
+      <c r="G410" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H410" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I410" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J410" s="383" t="inlineStr">
+        <is>
+          <t>No receipt; cash purchase</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="B411" s="64" t="n"/>
@@ -43627,14 +43729,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="278">
-      <c r="A1" s="384" t="inlineStr">
+      <c r="A1" s="372" t="inlineStr">
         <is>
           <t>LOKA — MONTHLY P&amp;L   (live formulas — auto-updates from Daily Log &amp; Expenses)</t>
         </is>
       </c>
-      <c r="B1" s="383" t="n"/>
-      <c r="C1" s="383" t="n"/>
-      <c r="D1" s="383" t="n"/>
+      <c r="B1" s="373" t="n"/>
+      <c r="C1" s="373" t="n"/>
+      <c r="D1" s="373" t="n"/>
       <c r="E1" s="374" t="n"/>
       <c r="F1" s="374" t="n"/>
       <c r="G1" s="374" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -10611,22 +10611,54 @@
       </c>
     </row>
     <row r="54" ht="16.5" customHeight="1" s="278">
-      <c r="B54" s="34" t="n"/>
-      <c r="C54" s="35" t="n"/>
-      <c r="D54" s="36" t="n"/>
-      <c r="E54" s="37" t="n"/>
-      <c r="F54" s="38" t="n"/>
-      <c r="G54" s="39" t="n"/>
-      <c r="H54" s="40" t="n"/>
-      <c r="I54" s="41" t="n"/>
-      <c r="J54" s="42" t="n"/>
-      <c r="K54" s="43" t="n"/>
-      <c r="L54" s="9" t="n"/>
+      <c r="B54" s="385" t="n">
+        <v>46206</v>
+      </c>
+      <c r="C54" s="386" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D54" s="387" t="n">
+        <v>3702</v>
+      </c>
+      <c r="E54" s="37" t="n">
+        <v>2265</v>
+      </c>
+      <c r="F54" s="38">
+        <f>IFERROR(D54+E54+G54,0)</f>
+        <v/>
+      </c>
+      <c r="G54" s="388" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="389">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B54,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B54+1))</f>
+        <v/>
+      </c>
+      <c r="I54" s="390">
+        <f>IFERROR(F54-H54,0)</f>
+        <v/>
+      </c>
+      <c r="J54" s="391">
+        <f>IFERROR(I54/F54,0)</f>
+        <v/>
+      </c>
+      <c r="K54" s="251" t="n"/>
+      <c r="L54" s="392" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
       <c r="M54" s="12" t="n"/>
       <c r="N54" s="44" t="n"/>
       <c r="O54" s="45" t="n"/>
       <c r="P54" s="46" t="n"/>
       <c r="Q54" s="44" t="n"/>
+      <c r="R54" s="410">
+        <f>IFERROR(D54*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="55" ht="16.5" customHeight="1" s="278">
       <c r="B55" s="34" t="n"/>
@@ -33516,64 +33548,262 @@
       </c>
     </row>
     <row r="411">
-      <c r="B411" s="64" t="n"/>
-      <c r="C411" s="65" t="n"/>
-      <c r="D411" s="66" t="n"/>
-      <c r="E411" s="65" t="n"/>
-      <c r="F411" s="67" t="n"/>
-      <c r="G411" s="14" t="n"/>
-      <c r="H411" s="14" t="n"/>
-      <c r="I411" s="43" t="n"/>
+      <c r="B411" s="382" t="n">
+        <v>46206</v>
+      </c>
+      <c r="C411" s="248" t="inlineStr">
+        <is>
+          <t>Muslo (pollo) 3.79kg @ $50/kg</t>
+        </is>
+      </c>
+      <c r="D411" s="249" t="inlineStr">
+        <is>
+          <t>Remision Loka Cafe</t>
+        </is>
+      </c>
+      <c r="E411" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F411" s="67" t="n">
+        <v>190</v>
+      </c>
+      <c r="G411" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H411" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I411" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J411" s="383" t="inlineStr">
+        <is>
+          <t>Nota remision manuscrita; 3.79x50; efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="412">
-      <c r="B412" s="64" t="n"/>
-      <c r="C412" s="69" t="n"/>
-      <c r="D412" s="68" t="n"/>
-      <c r="E412" s="69" t="n"/>
-      <c r="F412" s="70" t="n"/>
-      <c r="G412" s="23" t="n"/>
-      <c r="H412" s="23" t="n"/>
-      <c r="I412" s="55" t="n"/>
+      <c r="B412" s="382" t="n">
+        <v>46206</v>
+      </c>
+      <c r="C412" s="252" t="inlineStr">
+        <is>
+          <t>Muslo (pollo) 2.30kg @ $50/kg</t>
+        </is>
+      </c>
+      <c r="D412" s="253" t="inlineStr">
+        <is>
+          <t>Remision</t>
+        </is>
+      </c>
+      <c r="E412" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F412" s="70" t="n">
+        <v>115</v>
+      </c>
+      <c r="G412" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H412" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I412" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J412" s="383" t="inlineStr">
+        <is>
+          <t>Nota remision manuscrita; 2.30x50=115; efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="413">
-      <c r="B413" s="64" t="n"/>
-      <c r="C413" s="65" t="n"/>
-      <c r="D413" s="66" t="n"/>
-      <c r="E413" s="65" t="n"/>
-      <c r="F413" s="67" t="n"/>
-      <c r="G413" s="14" t="n"/>
-      <c r="H413" s="14" t="n"/>
-      <c r="I413" s="43" t="n"/>
+      <c r="B413" s="382" t="n">
+        <v>46206</v>
+      </c>
+      <c r="C413" s="248" t="inlineStr">
+        <is>
+          <t>Mayo Real x2 + Leche entera (Sam's Club)</t>
+        </is>
+      </c>
+      <c r="D413" s="249" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="E413" s="248" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F413" s="67" t="n">
+        <v>810</v>
+      </c>
+      <c r="G413" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H413" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I413" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J413" s="383" t="inlineStr">
+        <is>
+          <t>Debito Mastercard Bancomer AUT 733600; mayo $544.24 + leche $284.39 - desc $18.63 = 810</t>
+        </is>
+      </c>
     </row>
     <row r="414">
-      <c r="B414" s="64" t="n"/>
-      <c r="C414" s="69" t="n"/>
-      <c r="D414" s="68" t="n"/>
-      <c r="E414" s="69" t="n"/>
-      <c r="F414" s="70" t="n"/>
-      <c r="G414" s="23" t="n"/>
-      <c r="H414" s="23" t="n"/>
-      <c r="I414" s="55" t="n"/>
+      <c r="B414" s="382" t="n">
+        <v>46206</v>
+      </c>
+      <c r="C414" s="252" t="inlineStr">
+        <is>
+          <t>Filete mojarra de mar 3.14kg @ $140/kg</t>
+        </is>
+      </c>
+      <c r="D414" s="253" t="inlineStr">
+        <is>
+          <t>Brisa del Mar</t>
+        </is>
+      </c>
+      <c r="E414" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat &amp; Fish</t>
+        </is>
+      </c>
+      <c r="F414" s="70" t="n">
+        <v>439.6</v>
+      </c>
+      <c r="G414" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H414" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I414" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J414" s="383" t="inlineStr">
+        <is>
+          <t>Pescados y mariscos 08:44; metodo no impreso (asumido efectivo)</t>
+        </is>
+      </c>
     </row>
     <row r="415">
-      <c r="B415" s="64" t="n"/>
-      <c r="C415" s="65" t="n"/>
-      <c r="D415" s="66" t="n"/>
-      <c r="E415" s="65" t="n"/>
-      <c r="F415" s="67" t="n"/>
-      <c r="G415" s="14" t="n"/>
-      <c r="H415" s="14" t="n"/>
-      <c r="I415" s="43" t="n"/>
+      <c r="B415" s="382" t="n">
+        <v>46206</v>
+      </c>
+      <c r="C415" s="248" t="inlineStr">
+        <is>
+          <t>Vegetales</t>
+        </is>
+      </c>
+      <c r="D415" s="249" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E415" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F415" s="67" t="n">
+        <v>55</v>
+      </c>
+      <c r="G415" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H415" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I415" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J415" s="383" t="inlineStr">
+        <is>
+          <t>No receipt; cash purchase</t>
+        </is>
+      </c>
     </row>
     <row r="416">
-      <c r="B416" s="64" t="n"/>
-      <c r="C416" s="69" t="n"/>
-      <c r="D416" s="68" t="n"/>
-      <c r="E416" s="69" t="n"/>
-      <c r="F416" s="70" t="n"/>
-      <c r="G416" s="23" t="n"/>
-      <c r="H416" s="23" t="n"/>
-      <c r="I416" s="55" t="n"/>
+      <c r="B416" s="382" t="n">
+        <v>46206</v>
+      </c>
+      <c r="C416" s="252" t="inlineStr">
+        <is>
+          <t>Samu — Ayudante Week 7</t>
+        </is>
+      </c>
+      <c r="D416" s="253" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E416" s="252" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F416" s="70" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G416" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H416" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I416" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J416" s="383" t="inlineStr">
+        <is>
+          <t>Week 7 salary, paid Friday 03 Jul ($800 base + $400 mesero top-up)</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="B417" s="64" t="n"/>
@@ -44556,7 +44786,7 @@
     <row r="33">
       <c r="A33" s="380" t="inlineStr">
         <is>
-          <t>Kitchen Supplies</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="B33" s="378">
@@ -44583,7 +44813,7 @@
     <row r="34">
       <c r="A34" s="380" t="inlineStr">
         <is>
-          <t>Staff - Advance</t>
+          <t>Kitchen Supplies</t>
         </is>
       </c>
       <c r="B34" s="378">
@@ -44610,7 +44840,7 @@
     <row r="35">
       <c r="A35" s="380" t="inlineStr">
         <is>
-          <t>Utilities / Internet</t>
+          <t>Staff - Advance</t>
         </is>
       </c>
       <c r="B35" s="378">
@@ -44637,7 +44867,7 @@
     <row r="36">
       <c r="A36" s="380" t="inlineStr">
         <is>
-          <t>Packaging / Disposables</t>
+          <t>Utilities / Internet</t>
         </is>
       </c>
       <c r="B36" s="378">
@@ -44664,7 +44894,7 @@
     <row r="37">
       <c r="A37" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Desserts</t>
+          <t>Packaging / Disposables</t>
         </is>
       </c>
       <c r="B37" s="378">
@@ -44691,7 +44921,7 @@
     <row r="38">
       <c r="A38" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Eggs</t>
+          <t>Ingredients - Desserts</t>
         </is>
       </c>
       <c r="B38" s="378">
@@ -44718,7 +44948,7 @@
     <row r="39">
       <c r="A39" s="380" t="inlineStr">
         <is>
-          <t>Staff - Propinas</t>
+          <t>Ingredients - Eggs</t>
         </is>
       </c>
       <c r="B39" s="378">
@@ -44745,7 +44975,7 @@
     <row r="40">
       <c r="A40" s="380" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Staff - Propinas</t>
         </is>
       </c>
       <c r="B40" s="378">
@@ -44772,7 +45002,7 @@
     <row r="41">
       <c r="A41" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Produce</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="B41" s="378">
@@ -44797,21 +45027,21 @@
       <c r="L41" s="374" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="377" t="inlineStr">
-        <is>
-          <t>TOTAL EXPENSES</t>
-        </is>
-      </c>
-      <c r="B42" s="379">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
-        <v/>
-      </c>
-      <c r="C42" s="379">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
-        <v/>
-      </c>
-      <c r="D42" s="379">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+      <c r="A42" s="380" t="inlineStr">
+        <is>
+          <t>Ingredients - Produce</t>
+        </is>
+      </c>
+      <c r="B42" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A42,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <v/>
+      </c>
+      <c r="C42" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A42,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <v/>
+      </c>
+      <c r="D42" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A42,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E42" s="374" t="n"/>
@@ -44826,19 +45056,19 @@
     <row r="43">
       <c r="A43" s="377" t="inlineStr">
         <is>
-          <t>NET PROFIT / LOSS</t>
+          <t>TOTAL EXPENSES</t>
         </is>
       </c>
       <c r="B43" s="379">
-        <f>B4-B42</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C43" s="379">
-        <f>C4-C42</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D43" s="379">
-        <f>D4-D42</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E43" s="374" t="n"/>
@@ -44851,10 +45081,23 @@
       <c r="L43" s="374" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="374" t="n"/>
-      <c r="B44" s="374" t="n"/>
-      <c r="C44" s="374" t="n"/>
-      <c r="D44" s="374" t="n"/>
+      <c r="A44" s="377" t="inlineStr">
+        <is>
+          <t>NET PROFIT / LOSS</t>
+        </is>
+      </c>
+      <c r="B44" s="379">
+        <f>B4-B43</f>
+        <v/>
+      </c>
+      <c r="C44" s="379">
+        <f>C4-C43</f>
+        <v/>
+      </c>
+      <c r="D44" s="379">
+        <f>D4-D43</f>
+        <v/>
+      </c>
       <c r="E44" s="374" t="n"/>
       <c r="F44" s="374" t="n"/>
       <c r="G44" s="374" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -10623,7 +10623,7 @@
         <v>3702</v>
       </c>
       <c r="E54" s="37" t="n">
-        <v>2265</v>
+        <v>2375</v>
       </c>
       <c r="F54" s="38">
         <f>IFERROR(D54+E54+G54,0)</f>
@@ -10644,7 +10644,11 @@
         <f>IFERROR(I54/F54,0)</f>
         <v/>
       </c>
-      <c r="K54" s="251" t="n"/>
+      <c r="K54" s="251" t="inlineStr">
+        <is>
+          <t>incl +$110 additional cash income (added 04-Jul)</t>
+        </is>
+      </c>
       <c r="L54" s="392" t="inlineStr">
         <is>
           <t>Cierre via loka.py</t>
@@ -10661,22 +10665,54 @@
       </c>
     </row>
     <row r="55" ht="16.5" customHeight="1" s="278">
-      <c r="B55" s="34" t="n"/>
-      <c r="C55" s="47" t="n"/>
-      <c r="D55" s="48" t="n"/>
-      <c r="E55" s="49" t="n"/>
-      <c r="F55" s="50" t="n"/>
-      <c r="G55" s="51" t="n"/>
-      <c r="H55" s="52" t="n"/>
-      <c r="I55" s="53" t="n"/>
-      <c r="J55" s="54" t="n"/>
-      <c r="K55" s="55" t="n"/>
-      <c r="L55" s="18" t="n"/>
+      <c r="B55" s="385" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C55" s="256" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D55" s="257" t="n">
+        <v>1739</v>
+      </c>
+      <c r="E55" s="49" t="n">
+        <v>895</v>
+      </c>
+      <c r="F55" s="50">
+        <f>IFERROR(D55+E55+G55,0)</f>
+        <v/>
+      </c>
+      <c r="G55" s="258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="259">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B55,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B55+1))</f>
+        <v/>
+      </c>
+      <c r="I55" s="260">
+        <f>IFERROR(F55-H55,0)</f>
+        <v/>
+      </c>
+      <c r="J55" s="261">
+        <f>IFERROR(I55/F55,0)</f>
+        <v/>
+      </c>
+      <c r="K55" s="255" t="n"/>
+      <c r="L55" s="262" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
       <c r="M55" s="21" t="n"/>
       <c r="N55" s="56" t="n"/>
       <c r="O55" s="57" t="n"/>
       <c r="P55" s="58" t="n"/>
       <c r="Q55" s="56" t="n"/>
+      <c r="R55" s="410">
+        <f>IFERROR(D55*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="56" ht="16.5" customHeight="1" s="278">
       <c r="B56" s="34" t="n"/>
@@ -16386,9 +16422,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -33806,164 +33842,692 @@
       </c>
     </row>
     <row r="417">
-      <c r="B417" s="64" t="n"/>
-      <c r="C417" s="65" t="n"/>
-      <c r="D417" s="66" t="n"/>
-      <c r="E417" s="65" t="n"/>
-      <c r="F417" s="67" t="n"/>
-      <c r="G417" s="14" t="n"/>
-      <c r="H417" s="14" t="n"/>
-      <c r="I417" s="43" t="n"/>
+      <c r="B417" s="382" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C417" s="248" t="inlineStr">
+        <is>
+          <t>Zanahoria 3kg, Limon 3kg, Cebolla 3kg</t>
+        </is>
+      </c>
+      <c r="D417" s="249" t="inlineStr">
+        <is>
+          <t>Mi Joven</t>
+        </is>
+      </c>
+      <c r="E417" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F417" s="67" t="n">
+        <v>147</v>
+      </c>
+      <c r="G417" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H417" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I417" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J417" s="383" t="inlineStr">
+        <is>
+          <t>Mercado de Abastos folio 21212; efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="418">
-      <c r="B418" s="64" t="n"/>
-      <c r="C418" s="69" t="n"/>
-      <c r="D418" s="68" t="n"/>
-      <c r="E418" s="69" t="n"/>
-      <c r="F418" s="70" t="n"/>
-      <c r="G418" s="23" t="n"/>
-      <c r="H418" s="23" t="n"/>
-      <c r="I418" s="55" t="n"/>
+      <c r="B418" s="382" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C418" s="252" t="inlineStr">
+        <is>
+          <t>Papas 6 x $35</t>
+        </is>
+      </c>
+      <c r="D418" s="253" t="inlineStr">
+        <is>
+          <t>Papas San Miguel</t>
+        </is>
+      </c>
+      <c r="E418" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F418" s="70" t="n">
+        <v>210</v>
+      </c>
+      <c r="G418" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H418" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I418" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J418" s="383" t="inlineStr">
+        <is>
+          <t>6x35=210; efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="419">
-      <c r="B419" s="64" t="n"/>
-      <c r="C419" s="65" t="n"/>
-      <c r="D419" s="66" t="n"/>
-      <c r="E419" s="65" t="n"/>
-      <c r="F419" s="67" t="n"/>
-      <c r="G419" s="14" t="n"/>
-      <c r="H419" s="14" t="n"/>
-      <c r="I419" s="43" t="n"/>
+      <c r="B419" s="382" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C419" s="248" t="inlineStr">
+        <is>
+          <t>Verduras/hierbas mixtas (col, espinacas, hierbabuena, champinones, betabeles, lechugas, jengibre)</t>
+        </is>
+      </c>
+      <c r="D419" s="249" t="inlineStr">
+        <is>
+          <t>Hnos. Labra</t>
+        </is>
+      </c>
+      <c r="E419" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F419" s="67" t="n">
+        <v>339</v>
+      </c>
+      <c r="G419" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H419" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I419" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J419" s="383" t="inlineStr">
+        <is>
+          <t>Suma lineas=339; efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="420">
-      <c r="B420" s="64" t="n"/>
-      <c r="C420" s="69" t="n"/>
-      <c r="D420" s="68" t="n"/>
-      <c r="E420" s="69" t="n"/>
-      <c r="F420" s="70" t="n"/>
-      <c r="G420" s="23" t="n"/>
-      <c r="H420" s="23" t="n"/>
-      <c r="I420" s="55" t="n"/>
+      <c r="B420" s="382" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C420" s="252" t="inlineStr">
+        <is>
+          <t>Guayaba (1 primera)</t>
+        </is>
+      </c>
+      <c r="D420" s="253" t="inlineStr">
+        <is>
+          <t>Guayabas Aviles Hernandez</t>
+        </is>
+      </c>
+      <c r="E420" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Fruit</t>
+        </is>
+      </c>
+      <c r="F420" s="70" t="n">
+        <v>150</v>
+      </c>
+      <c r="G420" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H420" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I420" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J420" s="383" t="inlineStr">
+        <is>
+          <t>Total ~$150; efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="421">
-      <c r="B421" s="64" t="n"/>
-      <c r="C421" s="65" t="n"/>
-      <c r="D421" s="66" t="n"/>
-      <c r="E421" s="65" t="n"/>
-      <c r="F421" s="67" t="n"/>
-      <c r="G421" s="14" t="n"/>
-      <c r="H421" s="14" t="n"/>
-      <c r="I421" s="43" t="n"/>
+      <c r="B421" s="382" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C421" s="248" t="inlineStr">
+        <is>
+          <t>Pepino</t>
+        </is>
+      </c>
+      <c r="D421" s="249" t="inlineStr">
+        <is>
+          <t>Citricos Sanchez</t>
+        </is>
+      </c>
+      <c r="E421" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F421" s="67" t="n">
+        <v>49</v>
+      </c>
+      <c r="G421" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H421" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I421" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J421" s="383" t="inlineStr">
+        <is>
+          <t>Folio 7244; total $49 (detalle de linea poco legible)</t>
+        </is>
+      </c>
     </row>
     <row r="422">
-      <c r="B422" s="64" t="n"/>
-      <c r="C422" s="69" t="n"/>
-      <c r="D422" s="68" t="n"/>
-      <c r="E422" s="69" t="n"/>
-      <c r="F422" s="70" t="n"/>
-      <c r="G422" s="23" t="n"/>
-      <c r="H422" s="23" t="n"/>
-      <c r="I422" s="55" t="n"/>
+      <c r="B422" s="382" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C422" s="252" t="inlineStr">
+        <is>
+          <t>Cubiertos soperos desechables (tenedor/cuchara/cuchillo)</t>
+        </is>
+      </c>
+      <c r="D422" s="253" t="inlineStr">
+        <is>
+          <t>Guimar Polietilenos</t>
+        </is>
+      </c>
+      <c r="E422" s="252" t="inlineStr">
+        <is>
+          <t>Packaging/Disposables</t>
+        </is>
+      </c>
+      <c r="F422" s="70" t="n">
+        <v>139.8</v>
+      </c>
+      <c r="G422" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H422" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I422" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J422" s="383" t="inlineStr">
+        <is>
+          <t>Folio AK90544; tarjeta de credito</t>
+        </is>
+      </c>
     </row>
     <row r="423">
-      <c r="B423" s="64" t="n"/>
-      <c r="C423" s="65" t="n"/>
-      <c r="D423" s="66" t="n"/>
-      <c r="E423" s="65" t="n"/>
-      <c r="F423" s="67" t="n"/>
-      <c r="G423" s="14" t="n"/>
-      <c r="H423" s="14" t="n"/>
-      <c r="I423" s="43" t="n"/>
+      <c r="B423" s="382" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C423" s="248" t="inlineStr">
+        <is>
+          <t>Melon</t>
+        </is>
+      </c>
+      <c r="D423" s="249" t="inlineStr">
+        <is>
+          <t>Frutas de Temporada Jose</t>
+        </is>
+      </c>
+      <c r="E423" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Fruit</t>
+        </is>
+      </c>
+      <c r="F423" s="67" t="n">
+        <v>30</v>
+      </c>
+      <c r="G423" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H423" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I423" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J423" s="383" t="inlineStr">
+        <is>
+          <t>Solo melon $30; sin total impreso</t>
+        </is>
+      </c>
     </row>
     <row r="424">
-      <c r="B424" s="64" t="n"/>
-      <c r="C424" s="69" t="n"/>
-      <c r="D424" s="68" t="n"/>
-      <c r="E424" s="69" t="n"/>
-      <c r="F424" s="70" t="n"/>
-      <c r="G424" s="23" t="n"/>
-      <c r="H424" s="23" t="n"/>
-      <c r="I424" s="55" t="n"/>
+      <c r="B424" s="382" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C424" s="252" t="inlineStr">
+        <is>
+          <t>Morron surtido</t>
+        </is>
+      </c>
+      <c r="D424" s="253" t="inlineStr">
+        <is>
+          <t>Verduras Selectas Oscar</t>
+        </is>
+      </c>
+      <c r="E424" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F424" s="70" t="n">
+        <v>20</v>
+      </c>
+      <c r="G424" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H424" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I424" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J424" s="383" t="inlineStr">
+        <is>
+          <t>Morron $20; sin total impreso</t>
+        </is>
+      </c>
     </row>
     <row r="425">
-      <c r="B425" s="64" t="n"/>
-      <c r="C425" s="65" t="n"/>
-      <c r="D425" s="66" t="n"/>
-      <c r="E425" s="65" t="n"/>
-      <c r="F425" s="67" t="n"/>
-      <c r="G425" s="14" t="n"/>
-      <c r="H425" s="14" t="n"/>
-      <c r="I425" s="43" t="n"/>
+      <c r="B425" s="382" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C425" s="248" t="inlineStr">
+        <is>
+          <t>Fresa 0.775kg @ $65/kg</t>
+        </is>
+      </c>
+      <c r="D425" s="249" t="inlineStr">
+        <is>
+          <t>Nota manuscrita</t>
+        </is>
+      </c>
+      <c r="E425" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Fruit</t>
+        </is>
+      </c>
+      <c r="F425" s="67" t="n">
+        <v>50</v>
+      </c>
+      <c r="G425" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H425" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I425" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J425" s="383" t="inlineStr">
+        <is>
+          <t>.775x65=50; efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="426">
-      <c r="B426" s="64" t="n"/>
-      <c r="C426" s="69" t="n"/>
-      <c r="D426" s="68" t="n"/>
-      <c r="E426" s="69" t="n"/>
-      <c r="F426" s="70" t="n"/>
-      <c r="G426" s="23" t="n"/>
-      <c r="H426" s="23" t="n"/>
-      <c r="I426" s="55" t="n"/>
+      <c r="B426" s="382" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C426" s="252" t="inlineStr">
+        <is>
+          <t>Gelatinas, hot cakes, jarabe, verduras congeladas</t>
+        </is>
+      </c>
+      <c r="D426" s="253" t="inlineStr">
+        <is>
+          <t>Basicos</t>
+        </is>
+      </c>
+      <c r="E426" s="252" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F426" s="70" t="n">
+        <v>354.5</v>
+      </c>
+      <c r="G426" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H426" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I426" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J426" s="383" t="inlineStr">
+        <is>
+          <t>Total $358 - desc $3.50 = $354.50; tarjeta</t>
+        </is>
+      </c>
     </row>
     <row r="427">
-      <c r="B427" s="64" t="n"/>
-      <c r="C427" s="65" t="n"/>
-      <c r="D427" s="66" t="n"/>
-      <c r="E427" s="65" t="n"/>
-      <c r="F427" s="67" t="n"/>
-      <c r="G427" s="14" t="n"/>
-      <c r="H427" s="14" t="n"/>
-      <c r="I427" s="43" t="n"/>
+      <c r="B427" s="382" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C427" s="248" t="inlineStr">
+        <is>
+          <t>Melocoton 2.5kg + Platano</t>
+        </is>
+      </c>
+      <c r="D427" s="249" t="inlineStr">
+        <is>
+          <t>Remision</t>
+        </is>
+      </c>
+      <c r="E427" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Fruit</t>
+        </is>
+      </c>
+      <c r="F427" s="67" t="n">
+        <v>68</v>
+      </c>
+      <c r="G427" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H427" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I427" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J427" s="383" t="inlineStr">
+        <is>
+          <t>Melocoton $50 + platano $18 = $68; efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="428">
-      <c r="B428" s="64" t="n"/>
-      <c r="C428" s="69" t="n"/>
-      <c r="D428" s="68" t="n"/>
-      <c r="E428" s="69" t="n"/>
-      <c r="F428" s="70" t="n"/>
-      <c r="G428" s="23" t="n"/>
-      <c r="H428" s="23" t="n"/>
-      <c r="I428" s="55" t="n"/>
+      <c r="B428" s="382" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C428" s="252" t="inlineStr">
+        <is>
+          <t>Papaya</t>
+        </is>
+      </c>
+      <c r="D428" s="253" t="inlineStr">
+        <is>
+          <t>Remision</t>
+        </is>
+      </c>
+      <c r="E428" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Fruit</t>
+        </is>
+      </c>
+      <c r="F428" s="70" t="n">
+        <v>36</v>
+      </c>
+      <c r="G428" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H428" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I428" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J428" s="383" t="inlineStr">
+        <is>
+          <t>Papaya total $36; efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="429">
-      <c r="B429" s="64" t="n"/>
-      <c r="C429" s="65" t="n"/>
-      <c r="D429" s="66" t="n"/>
-      <c r="E429" s="65" t="n"/>
-      <c r="F429" s="67" t="n"/>
-      <c r="G429" s="14" t="n"/>
-      <c r="H429" s="14" t="n"/>
-      <c r="I429" s="43" t="n"/>
+      <c r="B429" s="382" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C429" s="248" t="inlineStr">
+        <is>
+          <t>Granola 400g + Tortillas blancas 4.435kg</t>
+        </is>
+      </c>
+      <c r="D429" s="249" t="inlineStr">
+        <is>
+          <t>Chedraui Selecto</t>
+        </is>
+      </c>
+      <c r="E429" s="248" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F429" s="67" t="n">
+        <v>108.43</v>
+      </c>
+      <c r="G429" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H429" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I429" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J429" s="383" t="inlineStr">
+        <is>
+          <t>Granola $53 + tortillas $55.43; debito ***0311</t>
+        </is>
+      </c>
     </row>
     <row r="430">
-      <c r="B430" s="64" t="n"/>
-      <c r="C430" s="69" t="n"/>
-      <c r="D430" s="68" t="n"/>
-      <c r="E430" s="69" t="n"/>
-      <c r="F430" s="70" t="n"/>
-      <c r="G430" s="23" t="n"/>
-      <c r="H430" s="23" t="n"/>
-      <c r="I430" s="55" t="n"/>
+      <c r="B430" s="382" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C430" s="252" t="inlineStr">
+        <is>
+          <t>Jitomate 8.3kg + Aguacate Hass</t>
+        </is>
+      </c>
+      <c r="D430" s="253" t="inlineStr">
+        <is>
+          <t>Frutas Finas Ana Pao</t>
+        </is>
+      </c>
+      <c r="E430" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F430" s="70" t="n">
+        <v>126</v>
+      </c>
+      <c r="G430" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H430" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I430" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J430" s="383" t="inlineStr">
+        <is>
+          <t>Jitomate $100 + hass $26 = $126; sin total impreso</t>
+        </is>
+      </c>
     </row>
     <row r="431">
-      <c r="B431" s="64" t="n"/>
-      <c r="C431" s="65" t="n"/>
-      <c r="D431" s="66" t="n"/>
-      <c r="E431" s="65" t="n"/>
-      <c r="F431" s="67" t="n"/>
-      <c r="G431" s="14" t="n"/>
-      <c r="H431" s="14" t="n"/>
-      <c r="I431" s="43" t="n"/>
+      <c r="B431" s="382" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C431" s="248" t="inlineStr">
+        <is>
+          <t>John — Head Chef Week 7</t>
+        </is>
+      </c>
+      <c r="D431" s="249" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E431" s="248" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F431" s="67" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G431" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H431" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I431" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J431" s="383" t="inlineStr">
+        <is>
+          <t>Week 7 salary, paid Saturday 04 Jul (usual $3,750; $50 higher this week)</t>
+        </is>
+      </c>
     </row>
     <row r="432">
-      <c r="B432" s="64" t="n"/>
-      <c r="C432" s="69" t="n"/>
-      <c r="D432" s="68" t="n"/>
-      <c r="E432" s="69" t="n"/>
-      <c r="F432" s="70" t="n"/>
-      <c r="G432" s="23" t="n"/>
-      <c r="H432" s="23" t="n"/>
-      <c r="I432" s="55" t="n"/>
+      <c r="B432" s="382" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C432" s="252" t="inlineStr">
+        <is>
+          <t>Duvi/Debi — Limpieza Week 7 (5 days)</t>
+        </is>
+      </c>
+      <c r="D432" s="253" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E432" s="252" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F432" s="70" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G432" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H432" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I432" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J432" s="383" t="inlineStr">
+        <is>
+          <t>Week 7, worked 5 days @ $250/day = $1,250, paid Saturday 04 Jul</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="B433" s="64" t="n"/>
@@ -44435,7 +44999,7 @@
     <row r="20">
       <c r="A20" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Pantry</t>
+          <t>Ingredients - Vegetables</t>
         </is>
       </c>
       <c r="B20" s="378">
@@ -44462,7 +45026,7 @@
     <row r="21">
       <c r="A21" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Vegetables</t>
+          <t>Ingredients - Pantry</t>
         </is>
       </c>
       <c r="B21" s="378">
@@ -44759,7 +45323,7 @@
     <row r="32">
       <c r="A32" s="380" t="inlineStr">
         <is>
-          <t>Software / Subscription</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="B32" s="378">
@@ -44786,7 +45350,7 @@
     <row r="33">
       <c r="A33" s="380" t="inlineStr">
         <is>
-          <t>Supermarket/General</t>
+          <t>Software / Subscription</t>
         </is>
       </c>
       <c r="B33" s="378">
@@ -44975,7 +45539,7 @@
     <row r="40">
       <c r="A40" s="380" t="inlineStr">
         <is>
-          <t>Staff - Propinas</t>
+          <t>Packaging/Disposables</t>
         </is>
       </c>
       <c r="B40" s="378">
@@ -45002,7 +45566,7 @@
     <row r="41">
       <c r="A41" s="380" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Staff - Propinas</t>
         </is>
       </c>
       <c r="B41" s="378">
@@ -45029,7 +45593,7 @@
     <row r="42">
       <c r="A42" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Produce</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="B42" s="378">
@@ -45054,21 +45618,21 @@
       <c r="L42" s="374" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="377" t="inlineStr">
-        <is>
-          <t>TOTAL EXPENSES</t>
-        </is>
-      </c>
-      <c r="B43" s="379">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
-        <v/>
-      </c>
-      <c r="C43" s="379">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
-        <v/>
-      </c>
-      <c r="D43" s="379">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+      <c r="A43" s="380" t="inlineStr">
+        <is>
+          <t>Ingredients - Produce</t>
+        </is>
+      </c>
+      <c r="B43" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A43,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <v/>
+      </c>
+      <c r="C43" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A43,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <v/>
+      </c>
+      <c r="D43" s="378">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A43,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E43" s="374" t="n"/>
@@ -45083,19 +45647,19 @@
     <row r="44">
       <c r="A44" s="377" t="inlineStr">
         <is>
-          <t>NET PROFIT / LOSS</t>
+          <t>TOTAL EXPENSES</t>
         </is>
       </c>
       <c r="B44" s="379">
-        <f>B4-B43</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C44" s="379">
-        <f>C4-C43</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D44" s="379">
-        <f>D4-D43</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E44" s="374" t="n"/>
@@ -45108,10 +45672,23 @@
       <c r="L44" s="374" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="374" t="n"/>
-      <c r="B45" s="374" t="n"/>
-      <c r="C45" s="374" t="n"/>
-      <c r="D45" s="374" t="n"/>
+      <c r="A45" s="377" t="inlineStr">
+        <is>
+          <t>NET PROFIT / LOSS</t>
+        </is>
+      </c>
+      <c r="B45" s="379">
+        <f>B4-B44</f>
+        <v/>
+      </c>
+      <c r="C45" s="379">
+        <f>C4-C44</f>
+        <v/>
+      </c>
+      <c r="D45" s="379">
+        <f>D4-D44</f>
+        <v/>
+      </c>
       <c r="E45" s="374" t="n"/>
       <c r="F45" s="374" t="n"/>
       <c r="G45" s="374" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5143,11 +5143,12 @@
     <row r="139">
       <c r="B139" s="234" t="inlineStr">
         <is>
-          <t>− Owner ledger balance settled from budget (rent + fronted items)</t>
-        </is>
-      </c>
-      <c r="D139" s="242" t="n">
-        <v>19314.81</v>
+          <t>− Operating costs funded from capital (ledger settlement + rent)</t>
+        </is>
+      </c>
+      <c r="D139" s="242">
+        <f>C147</f>
+        <v/>
       </c>
     </row>
     <row r="140">
@@ -5227,11 +5228,11 @@
         </is>
       </c>
       <c r="C147" s="379" t="n">
-        <v>19314.81</v>
+        <v>39314.81</v>
       </c>
       <c r="E147" s="405" t="inlineStr">
         <is>
-          <t>Rent + fronted operating items funded from capital budget (settled 30 Jun). Add future capital-funded operating costs here.</t>
+          <t>Operating costs funded from capital: ledger settlement 30 Jun ($19,314.81) + rent paid from capital 05 Jul ($20,000). Add future capital-funded operating costs here.</t>
         </is>
       </c>
     </row>
@@ -10715,40 +10716,104 @@
       </c>
     </row>
     <row r="56" ht="16.5" customHeight="1" s="278">
-      <c r="B56" s="34" t="n"/>
-      <c r="C56" s="35" t="n"/>
-      <c r="D56" s="36" t="n"/>
-      <c r="E56" s="37" t="n"/>
-      <c r="F56" s="38" t="n"/>
-      <c r="G56" s="39" t="n"/>
-      <c r="H56" s="40" t="n"/>
-      <c r="I56" s="41" t="n"/>
-      <c r="J56" s="42" t="n"/>
-      <c r="K56" s="43" t="n"/>
-      <c r="L56" s="9" t="n"/>
+      <c r="B56" s="385" t="n">
+        <v>46209</v>
+      </c>
+      <c r="C56" s="386" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D56" s="387" t="n">
+        <v>2190</v>
+      </c>
+      <c r="E56" s="37" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F56" s="38">
+        <f>IFERROR(D56+E56+G56,0)</f>
+        <v/>
+      </c>
+      <c r="G56" s="388" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="389">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B56,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B56+1))</f>
+        <v/>
+      </c>
+      <c r="I56" s="390">
+        <f>IFERROR(F56-H56,0)</f>
+        <v/>
+      </c>
+      <c r="J56" s="391">
+        <f>IFERROR(I56/F56,0)</f>
+        <v/>
+      </c>
+      <c r="K56" s="251" t="n"/>
+      <c r="L56" s="392" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
       <c r="M56" s="12" t="n"/>
       <c r="N56" s="44" t="n"/>
       <c r="O56" s="45" t="n"/>
       <c r="P56" s="46" t="n"/>
       <c r="Q56" s="44" t="n"/>
+      <c r="R56" s="410">
+        <f>IFERROR(D56*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="57" ht="16.5" customHeight="1" s="278">
-      <c r="B57" s="34" t="n"/>
-      <c r="C57" s="47" t="n"/>
-      <c r="D57" s="48" t="n"/>
-      <c r="E57" s="49" t="n"/>
-      <c r="F57" s="50" t="n"/>
-      <c r="G57" s="51" t="n"/>
-      <c r="H57" s="52" t="n"/>
-      <c r="I57" s="53" t="n"/>
-      <c r="J57" s="54" t="n"/>
-      <c r="K57" s="55" t="n"/>
-      <c r="L57" s="18" t="n"/>
+      <c r="B57" s="385" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C57" s="256" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D57" s="257" t="n">
+        <v>1840</v>
+      </c>
+      <c r="E57" s="49" t="n">
+        <v>1820</v>
+      </c>
+      <c r="F57" s="50">
+        <f>IFERROR(D57+E57+G57,0)</f>
+        <v/>
+      </c>
+      <c r="G57" s="258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="259">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B57,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B57+1))</f>
+        <v/>
+      </c>
+      <c r="I57" s="260">
+        <f>IFERROR(F57-H57,0)</f>
+        <v/>
+      </c>
+      <c r="J57" s="261">
+        <f>IFERROR(I57/F57,0)</f>
+        <v/>
+      </c>
+      <c r="K57" s="255" t="n"/>
+      <c r="L57" s="262" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
       <c r="M57" s="21" t="n"/>
       <c r="N57" s="56" t="n"/>
       <c r="O57" s="57" t="n"/>
       <c r="P57" s="58" t="n"/>
       <c r="Q57" s="56" t="n"/>
+      <c r="R57" s="410">
+        <f>IFERROR(D57*$T$7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="58" ht="16.5" customHeight="1" s="278">
       <c r="B58" s="34" t="n"/>
@@ -16422,9 +16487,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -34530,104 +34595,434 @@
       </c>
     </row>
     <row r="433">
-      <c r="B433" s="64" t="n"/>
-      <c r="C433" s="65" t="n"/>
-      <c r="D433" s="66" t="n"/>
-      <c r="E433" s="65" t="n"/>
-      <c r="F433" s="67" t="n"/>
-      <c r="G433" s="14" t="n"/>
-      <c r="H433" s="14" t="n"/>
-      <c r="I433" s="43" t="n"/>
+      <c r="B433" s="382" t="n">
+        <v>46208</v>
+      </c>
+      <c r="C433" s="248" t="inlineStr">
+        <is>
+          <t>Renta mensual (pagada con capital)</t>
+        </is>
+      </c>
+      <c r="D433" s="249" t="inlineStr">
+        <is>
+          <t>Arrendador</t>
+        </is>
+      </c>
+      <c r="E433" s="248" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="F433" s="67" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G433" s="250" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H433" s="250" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="I433" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J433" s="383" t="inlineStr">
+        <is>
+          <t>Renta pagada con dinero de CAPITAL (no de caja operativa). Es gasto operativo (P&amp;L) y operaciones deben este monto al capital. Excluida del roll de efectivo por paid=Capital.</t>
+        </is>
+      </c>
     </row>
     <row r="434">
-      <c r="B434" s="64" t="n"/>
-      <c r="C434" s="69" t="n"/>
-      <c r="D434" s="68" t="n"/>
-      <c r="E434" s="69" t="n"/>
-      <c r="F434" s="70" t="n"/>
-      <c r="G434" s="23" t="n"/>
-      <c r="H434" s="23" t="n"/>
-      <c r="I434" s="55" t="n"/>
+      <c r="B434" s="382" t="n">
+        <v>46209</v>
+      </c>
+      <c r="C434" s="252" t="inlineStr">
+        <is>
+          <t>Miscelanea LC remision (lineas ilegibles)</t>
+        </is>
+      </c>
+      <c r="D434" s="253" t="inlineStr">
+        <is>
+          <t>Miscelanea LC La Cruz</t>
+        </is>
+      </c>
+      <c r="E434" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F434" s="70" t="n">
+        <v>974</v>
+      </c>
+      <c r="G434" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H434" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I434" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J434" s="383" t="inlineStr">
+        <is>
+          <t>Getnet $974 autoritativo (Aut 6B6666, 15:52); carniceria/meat shop; lineas manuscritas ilegibles</t>
+        </is>
+      </c>
     </row>
     <row r="435">
-      <c r="B435" s="64" t="n"/>
-      <c r="C435" s="65" t="n"/>
-      <c r="D435" s="66" t="n"/>
-      <c r="E435" s="65" t="n"/>
-      <c r="F435" s="67" t="n"/>
-      <c r="G435" s="14" t="n"/>
-      <c r="H435" s="14" t="n"/>
-      <c r="I435" s="43" t="n"/>
+      <c r="B435" s="382" t="n">
+        <v>46209</v>
+      </c>
+      <c r="C435" s="248" t="inlineStr">
+        <is>
+          <t>Miscelanea LC remision (lineas ilegibles)</t>
+        </is>
+      </c>
+      <c r="D435" s="249" t="inlineStr">
+        <is>
+          <t>Miscelanea LC La Cruz</t>
+        </is>
+      </c>
+      <c r="E435" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F435" s="67" t="n">
+        <v>289</v>
+      </c>
+      <c r="G435" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H435" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I435" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J435" s="383" t="inlineStr">
+        <is>
+          <t>Getnet $289 autoritativo (Aut 722687, 09:45); carniceria/meat shop; lineas manuscritas ilegibles</t>
+        </is>
+      </c>
     </row>
     <row r="436">
-      <c r="B436" s="64" t="n"/>
-      <c r="C436" s="69" t="n"/>
-      <c r="D436" s="68" t="n"/>
-      <c r="E436" s="69" t="n"/>
-      <c r="F436" s="70" t="n"/>
-      <c r="G436" s="23" t="n"/>
-      <c r="H436" s="23" t="n"/>
-      <c r="I436" s="55" t="n"/>
+      <c r="B436" s="382" t="n">
+        <v>46209</v>
+      </c>
+      <c r="C436" s="252" t="inlineStr">
+        <is>
+          <t>Pasta seca (codo, caracol, spaguetti, estrella)</t>
+        </is>
+      </c>
+      <c r="D436" s="253" t="inlineStr">
+        <is>
+          <t>Tres B</t>
+        </is>
+      </c>
+      <c r="E436" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F436" s="70" t="n">
+        <v>245</v>
+      </c>
+      <c r="G436" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H436" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I436" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J436" s="383" t="inlineStr">
+        <is>
+          <t>Ticket 31 08:50; tarjeta ML ***3982</t>
+        </is>
+      </c>
     </row>
     <row r="437">
-      <c r="B437" s="64" t="n"/>
-      <c r="C437" s="65" t="n"/>
-      <c r="D437" s="66" t="n"/>
-      <c r="E437" s="65" t="n"/>
-      <c r="F437" s="67" t="n"/>
-      <c r="G437" s="14" t="n"/>
-      <c r="H437" s="14" t="n"/>
-      <c r="I437" s="43" t="n"/>
+      <c r="B437" s="382" t="n">
+        <v>46209</v>
+      </c>
+      <c r="C437" s="248" t="inlineStr">
+        <is>
+          <t>Coca-Cola 600ml x2 + Crema acida x2</t>
+        </is>
+      </c>
+      <c r="D437" s="249" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="E437" s="248" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F437" s="67" t="n">
+        <v>1420</v>
+      </c>
+      <c r="G437" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H437" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I437" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J437" s="383" t="inlineStr">
+        <is>
+          <t>Coca 2x485.92 + crema 2x240.40 - desc 32.64; debito ***82; 11:01</t>
+        </is>
+      </c>
     </row>
     <row r="438">
-      <c r="B438" s="64" t="n"/>
-      <c r="C438" s="69" t="n"/>
-      <c r="D438" s="68" t="n"/>
-      <c r="E438" s="69" t="n"/>
-      <c r="F438" s="70" t="n"/>
-      <c r="G438" s="23" t="n"/>
-      <c r="H438" s="23" t="n"/>
-      <c r="I438" s="55" t="n"/>
+      <c r="B438" s="382" t="n">
+        <v>46209</v>
+      </c>
+      <c r="C438" s="252" t="inlineStr">
+        <is>
+          <t>Queso x2</t>
+        </is>
+      </c>
+      <c r="D438" s="253" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="E438" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Dairy</t>
+        </is>
+      </c>
+      <c r="F438" s="70" t="n">
+        <v>74</v>
+      </c>
+      <c r="G438" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H438" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I438" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J438" s="383" t="inlineStr">
+        <is>
+          <t>GV QSO 37x2; debito ***82; 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="439">
-      <c r="B439" s="64" t="n"/>
-      <c r="C439" s="65" t="n"/>
-      <c r="D439" s="66" t="n"/>
-      <c r="E439" s="65" t="n"/>
-      <c r="F439" s="67" t="n"/>
-      <c r="G439" s="14" t="n"/>
-      <c r="H439" s="14" t="n"/>
-      <c r="I439" s="43" t="n"/>
+      <c r="B439" s="382" t="n">
+        <v>46209</v>
+      </c>
+      <c r="C439" s="248" t="inlineStr">
+        <is>
+          <t>Milanesa 1.53kg + Muslo 10.18kg + Pechuga 3.69kg</t>
+        </is>
+      </c>
+      <c r="D439" s="249" t="inlineStr">
+        <is>
+          <t>Remision Loka Cafe</t>
+        </is>
+      </c>
+      <c r="E439" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F439" s="67" t="n">
+        <v>1133</v>
+      </c>
+      <c r="G439" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H439" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I439" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J439" s="383" t="inlineStr">
+        <is>
+          <t>Milanesa $199 + muslo $509 + pechuga $425 = $1133; efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="440">
-      <c r="B440" s="64" t="n"/>
-      <c r="C440" s="69" t="n"/>
-      <c r="D440" s="68" t="n"/>
-      <c r="E440" s="69" t="n"/>
-      <c r="F440" s="70" t="n"/>
-      <c r="G440" s="23" t="n"/>
-      <c r="H440" s="23" t="n"/>
-      <c r="I440" s="55" t="n"/>
+      <c r="B440" s="382" t="n">
+        <v>46209</v>
+      </c>
+      <c r="C440" s="252" t="inlineStr">
+        <is>
+          <t>Cilantro</t>
+        </is>
+      </c>
+      <c r="D440" s="253" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E440" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F440" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="G440" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H440" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I440" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J440" s="383" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
     </row>
     <row r="441">
-      <c r="B441" s="64" t="n"/>
-      <c r="C441" s="65" t="n"/>
-      <c r="D441" s="66" t="n"/>
-      <c r="E441" s="65" t="n"/>
-      <c r="F441" s="67" t="n"/>
-      <c r="G441" s="14" t="n"/>
-      <c r="H441" s="14" t="n"/>
-      <c r="I441" s="43" t="n"/>
+      <c r="B441" s="382" t="n">
+        <v>46209</v>
+      </c>
+      <c r="C441" s="248" t="inlineStr">
+        <is>
+          <t>Agua natural</t>
+        </is>
+      </c>
+      <c r="D441" s="249" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E441" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F441" s="67" t="n">
+        <v>60</v>
+      </c>
+      <c r="G441" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H441" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I441" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J441" s="383" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
     </row>
     <row r="442">
-      <c r="B442" s="64" t="n"/>
-      <c r="C442" s="69" t="n"/>
-      <c r="D442" s="68" t="n"/>
-      <c r="E442" s="69" t="n"/>
-      <c r="F442" s="70" t="n"/>
-      <c r="G442" s="23" t="n"/>
-      <c r="H442" s="23" t="n"/>
-      <c r="I442" s="55" t="n"/>
+      <c r="B442" s="382" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C442" s="252" t="inlineStr">
+        <is>
+          <t>Tortillas</t>
+        </is>
+      </c>
+      <c r="D442" s="253" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E442" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F442" s="70" t="n">
+        <v>49</v>
+      </c>
+      <c r="G442" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H442" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I442" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J442" s="383" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="B443" s="64" t="n"/>
@@ -44918,7 +45313,7 @@
     <row r="17">
       <c r="A17" s="380" t="inlineStr">
         <is>
-          <t>Staff - Salary</t>
+          <t>Rent</t>
         </is>
       </c>
       <c r="B17" s="378">
@@ -44945,7 +45340,7 @@
     <row r="18">
       <c r="A18" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Meat</t>
+          <t>Staff - Salary</t>
         </is>
       </c>
       <c r="B18" s="378">
@@ -44972,7 +45367,7 @@
     <row r="19">
       <c r="A19" s="380" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Ingredients - Meat</t>
         </is>
       </c>
       <c r="B19" s="378">
@@ -45269,7 +45664,7 @@
     <row r="30">
       <c r="A30" s="380" t="inlineStr">
         <is>
-          <t>Utilities / Gas</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="B30" s="378">
@@ -45296,7 +45691,7 @@
     <row r="31">
       <c r="A31" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Other</t>
+          <t>Utilities / Gas</t>
         </is>
       </c>
       <c r="B31" s="378">
@@ -45323,7 +45718,7 @@
     <row r="32">
       <c r="A32" s="380" t="inlineStr">
         <is>
-          <t>Supermarket/General</t>
+          <t>Ingredients - Other</t>
         </is>
       </c>
       <c r="B32" s="378">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -1306,7 +1306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19"/>
   </cellStyleXfs>
-  <cellXfs count="411">
+  <cellXfs count="420">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2354,6 +2354,29 @@
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="97" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="175" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="72" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="73" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="22" fillId="20" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="46" fillId="20" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="31" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="32" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4053,12 +4076,32 @@
       <c r="H60" s="288" t="n"/>
     </row>
     <row r="61" ht="22.05" customHeight="1" s="278">
-      <c r="B61" s="237" t="n"/>
-      <c r="C61" s="236" t="n"/>
-      <c r="D61" s="191" t="n"/>
-      <c r="E61" s="190" t="n"/>
-      <c r="F61" s="190" t="n"/>
-      <c r="G61" s="189" t="n"/>
+      <c r="B61" s="237" t="inlineStr">
+        <is>
+          <t>Reimbursement to Shashirekha (over-budget expenses)</t>
+        </is>
+      </c>
+      <c r="C61" s="411" t="n">
+        <v>46210</v>
+      </c>
+      <c r="D61" s="412" t="n">
+        <v>1034</v>
+      </c>
+      <c r="E61" s="413" t="inlineStr">
+        <is>
+          <t>Shashirekha B.</t>
+        </is>
+      </c>
+      <c r="F61" s="413" t="inlineStr">
+        <is>
+          <t>Partner Settlement</t>
+        </is>
+      </c>
+      <c r="G61" s="414" t="inlineStr">
+        <is>
+          <t>Reimbursed Shashi for spending $1,034 over her $120k budget (menu + syrup) — 7 Jul 2026</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="22.05" customHeight="1" s="278">
       <c r="B62" s="237" t="n"/>
@@ -4375,28 +4418,88 @@
       </c>
     </row>
     <row r="79" ht="19.95" customHeight="1" s="278">
-      <c r="B79" s="190" t="n"/>
-      <c r="C79" s="236" t="n"/>
-      <c r="D79" s="263" t="n"/>
-      <c r="E79" s="190" t="n"/>
-      <c r="F79" s="190" t="n"/>
-      <c r="G79" s="190" t="n"/>
+      <c r="B79" s="237" t="inlineStr">
+        <is>
+          <t>Menu printing</t>
+        </is>
+      </c>
+      <c r="C79" s="238" t="n">
+        <v>46210</v>
+      </c>
+      <c r="D79" s="239" t="n">
+        <v>1219</v>
+      </c>
+      <c r="E79" s="237" t="inlineStr">
+        <is>
+          <t>Print Shop</t>
+        </is>
+      </c>
+      <c r="F79" s="237" t="inlineStr">
+        <is>
+          <t>Branding / Printing</t>
+        </is>
+      </c>
+      <c r="G79" s="237" t="inlineStr">
+        <is>
+          <t>Printed menus — paid by Shashirekha (post-opening)</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="19.95" customHeight="1" s="278">
-      <c r="B80" s="190" t="n"/>
-      <c r="C80" s="236" t="n"/>
-      <c r="D80" s="263" t="n"/>
-      <c r="E80" s="190" t="n"/>
-      <c r="F80" s="190" t="n"/>
-      <c r="G80" s="190" t="n"/>
+      <c r="B80" s="237" t="inlineStr">
+        <is>
+          <t>Syrup bottles</t>
+        </is>
+      </c>
+      <c r="C80" s="238" t="n">
+        <v>46210</v>
+      </c>
+      <c r="D80" s="239" t="n">
+        <v>920</v>
+      </c>
+      <c r="E80" s="237" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="F80" s="237" t="inlineStr">
+        <is>
+          <t>Equipment / Supplies</t>
+        </is>
+      </c>
+      <c r="G80" s="237" t="inlineStr">
+        <is>
+          <t>Syrup bottles — paid by Shashirekha (post-opening)</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="19.95" customHeight="1" s="278">
-      <c r="B81" s="189" t="n"/>
-      <c r="C81" s="190" t="n"/>
-      <c r="D81" s="191" t="n"/>
-      <c r="E81" s="190" t="n"/>
-      <c r="F81" s="190" t="n"/>
-      <c r="G81" s="189" t="n"/>
+      <c r="B81" s="237" t="inlineStr">
+        <is>
+          <t>Reimbursement received from Lohith (over-budget)</t>
+        </is>
+      </c>
+      <c r="C81" s="238" t="n">
+        <v>46210</v>
+      </c>
+      <c r="D81" s="239" t="n">
+        <v>-1034</v>
+      </c>
+      <c r="E81" s="237" t="inlineStr">
+        <is>
+          <t>Lohith Reddy</t>
+        </is>
+      </c>
+      <c r="F81" s="237" t="inlineStr">
+        <is>
+          <t>Partner Settlement</t>
+        </is>
+      </c>
+      <c r="G81" s="237" t="inlineStr">
+        <is>
+          <t>Received $1,034 back from Lohith for over-budget spend — nets Shashi to her $120k budget</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="19.95" customHeight="1" s="278">
       <c r="B82" s="147" t="inlineStr">
@@ -5406,7 +5509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="278" min="1" max="1"/>
@@ -6359,30 +6462,162 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="397" t="inlineStr">
+      <c r="A31" s="397" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B31" s="232" t="inlineStr">
+        <is>
+          <t>HEB — Dustbin covers + Pan cutting knife</t>
+        </is>
+      </c>
+      <c r="C31" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D31" s="232" t="n">
+        <v>205</v>
+      </c>
+      <c r="E31" s="233" t="n"/>
+      <c r="F31" s="233">
+        <f>IFERROR(F30+D31-E31,0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="232" t="inlineStr">
+        <is>
+          <t>✅ Settled</t>
+        </is>
+      </c>
+      <c r="H31" s="232" t="inlineStr">
+        <is>
+          <t>Paid personally by Lohith (HEB) — dustbin covers + pan cutting knife; reimbursable</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="397" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B32" s="232" t="inlineStr">
+        <is>
+          <t>Transfer from restaurant — net settlement</t>
+        </is>
+      </c>
+      <c r="C32" s="232" t="inlineStr">
+        <is>
+          <t>Reimbursement</t>
+        </is>
+      </c>
+      <c r="D32" s="232" t="n"/>
+      <c r="E32" s="233" t="n">
+        <v>150</v>
+      </c>
+      <c r="F32" s="233">
+        <f>IFERROR(F31+D32-E32,0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="232" t="inlineStr">
+        <is>
+          <t>✅ Settled</t>
+        </is>
+      </c>
+      <c r="H32" s="232" t="inlineStr">
+        <is>
+          <t>Net $150 = $205 HEB expense − $55 Lohith owed to restaurant; balance now ZERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="397" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B33" s="232" t="inlineStr">
+        <is>
+          <t>GUIMAR — Vasos de plástico + tapas</t>
+        </is>
+      </c>
+      <c r="C33" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D33" s="232" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="E33" s="233" t="n"/>
+      <c r="F33" s="233">
+        <f>IFERROR(F32+D33-E33,0)</f>
+        <v/>
+      </c>
+      <c r="G33" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H33" s="232" t="inlineStr">
+        <is>
+          <t>Paid by Lohith (GUIMAR receipt, 08-Jul): vasos plast. $41 + reyma tapa vaso $32.50 = $73.50; reimbursable</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="397" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B34" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 08-Jul)</t>
+        </is>
+      </c>
+      <c r="C34" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D34" s="232" t="n"/>
+      <c r="E34" s="233" t="n">
+        <v>195</v>
+      </c>
+      <c r="F34" s="233">
+        <f>IFERROR(F33+D34-E34,0)</f>
+        <v/>
+      </c>
+      <c r="G34" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H34" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid $195 by transfer to Lohith (counts as 08-Jul revenue; cash went to Lohith not the till)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="397" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B31" s="232" t="n"/>
-      <c r="C31" s="232" t="n"/>
-      <c r="D31" s="232">
-        <f>SUM(D4:D30)</f>
-        <v/>
-      </c>
-      <c r="E31" s="233">
-        <f>SUM(E4:E30)</f>
-        <v/>
-      </c>
-      <c r="F31" s="233">
-        <f>F30</f>
-        <v/>
-      </c>
-      <c r="G31" s="232">
-        <f>IF(F30&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F30,"#,##0"),IF(F30&lt;0,"Lohith holds $"&amp;TEXT(ABS(F30),"#,##0"),"Zero balance"))</f>
-        <v/>
-      </c>
-      <c r="H31" s="232" t="n"/>
+      <c r="B35" s="232" t="n"/>
+      <c r="C35" s="232" t="n"/>
+      <c r="D35" s="232">
+        <f>SUM(D4:D34)</f>
+        <v/>
+      </c>
+      <c r="E35" s="233">
+        <f>SUM(E4:E34)</f>
+        <v/>
+      </c>
+      <c r="F35" s="233">
+        <f>F34</f>
+        <v/>
+      </c>
+      <c r="G35" s="232">
+        <f>IF(F34&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F34,"#,##0"),IF(F34&lt;0,"Lohith holds $"&amp;TEXT(ABS(F34),"#,##0"),"Zero balance"))</f>
+        <v/>
+      </c>
+      <c r="H35" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8137,7 +8372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T372"/>
+  <dimension ref="A1:X372"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="278" min="1" max="1"/>
@@ -8347,6 +8582,24 @@
       <c r="T7" s="409" t="n">
         <v>0.0406</v>
       </c>
+      <c r="U7" s="407" t="inlineStr">
+        <is>
+          <t>Soft Rest Card $</t>
+        </is>
+      </c>
+      <c r="V7" s="407" t="inlineStr">
+        <is>
+          <t>Soft Comm $</t>
+        </is>
+      </c>
+      <c r="W7" s="408" t="inlineStr">
+        <is>
+          <t>Soft Rate</t>
+        </is>
+      </c>
+      <c r="X7" s="409" t="n">
+        <v>0.0205</v>
+      </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" s="278">
       <c r="B8" s="229" t="n">
@@ -10816,22 +11069,65 @@
       </c>
     </row>
     <row r="58" ht="16.5" customHeight="1" s="278">
-      <c r="B58" s="34" t="n"/>
-      <c r="C58" s="35" t="n"/>
-      <c r="D58" s="36" t="n"/>
-      <c r="E58" s="37" t="n"/>
-      <c r="F58" s="38" t="n"/>
-      <c r="G58" s="39" t="n"/>
-      <c r="H58" s="40" t="n"/>
-      <c r="I58" s="41" t="n"/>
-      <c r="J58" s="42" t="n"/>
-      <c r="K58" s="43" t="n"/>
-      <c r="L58" s="9" t="n"/>
-      <c r="M58" s="12" t="n"/>
-      <c r="N58" s="44" t="n"/>
-      <c r="O58" s="45" t="n"/>
-      <c r="P58" s="46" t="n"/>
-      <c r="Q58" s="44" t="n"/>
+      <c r="B58" s="385" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C58" s="256" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D58" s="257" t="n">
+        <v>360</v>
+      </c>
+      <c r="E58" s="49" t="n">
+        <v>2055</v>
+      </c>
+      <c r="F58" s="50">
+        <f>IFERROR(D58+E58+G58+U58,0)</f>
+        <v/>
+      </c>
+      <c r="G58" s="258" t="n">
+        <v>195</v>
+      </c>
+      <c r="H58" s="259">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B58,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B58+1))</f>
+        <v/>
+      </c>
+      <c r="I58" s="260">
+        <f>IFERROR(F58-H58,0)</f>
+        <v/>
+      </c>
+      <c r="J58" s="261">
+        <f>IFERROR(I58/F58,0)</f>
+        <v/>
+      </c>
+      <c r="K58" s="255" t="n"/>
+      <c r="L58" s="262" t="inlineStr">
+        <is>
+          <t>EOD close (dual card: MP + Soft Restaurant)</t>
+        </is>
+      </c>
+      <c r="M58" s="415" t="n"/>
+      <c r="N58" s="416" t="n"/>
+      <c r="O58" s="417" t="n"/>
+      <c r="P58" s="418" t="n"/>
+      <c r="Q58" s="416" t="n"/>
+      <c r="R58" s="419">
+        <f>IFERROR(D58*$T$7,0)</f>
+        <v/>
+      </c>
+      <c r="S58" s="383" t="n"/>
+      <c r="T58" s="383" t="n"/>
+      <c r="U58" s="419" t="n">
+        <v>1078</v>
+      </c>
+      <c r="V58" s="419">
+        <f>IFERROR(U58*$X$7,0)</f>
+        <v/>
+      </c>
+      <c r="W58" s="383" t="n"/>
+      <c r="X58" s="383" t="n"/>
     </row>
     <row r="59" ht="16.5" customHeight="1" s="278">
       <c r="B59" s="34" t="n"/>
@@ -16487,9 +16783,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I2:P2"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B5:P5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:P2"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -35025,34 +35321,133 @@
       </c>
     </row>
     <row r="443">
-      <c r="B443" s="64" t="n"/>
-      <c r="C443" s="65" t="n"/>
-      <c r="D443" s="66" t="n"/>
-      <c r="E443" s="65" t="n"/>
-      <c r="F443" s="67" t="n"/>
-      <c r="G443" s="14" t="n"/>
-      <c r="H443" s="14" t="n"/>
-      <c r="I443" s="43" t="n"/>
+      <c r="B443" s="382" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C443" s="248" t="inlineStr">
+        <is>
+          <t>Tortillas blancas x2 + Rosca de nuez</t>
+        </is>
+      </c>
+      <c r="D443" s="249" t="inlineStr">
+        <is>
+          <t>Chedraui Paseo</t>
+        </is>
+      </c>
+      <c r="E443" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F443" s="67" t="n">
+        <v>139.43</v>
+      </c>
+      <c r="G443" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H443" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I443" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J443" s="383" t="inlineStr">
+        <is>
+          <t>Debito BBVA ***3982 09:31; tortillas $50.43 + rosca nuez $89</t>
+        </is>
+      </c>
     </row>
     <row r="444">
-      <c r="B444" s="64" t="n"/>
-      <c r="C444" s="69" t="n"/>
-      <c r="D444" s="68" t="n"/>
-      <c r="E444" s="69" t="n"/>
-      <c r="F444" s="70" t="n"/>
-      <c r="G444" s="23" t="n"/>
-      <c r="H444" s="23" t="n"/>
-      <c r="I444" s="55" t="n"/>
+      <c r="B444" s="382" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C444" s="252" t="inlineStr">
+        <is>
+          <t>Terminal rolls (rollos POS)</t>
+        </is>
+      </c>
+      <c r="D444" s="253" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E444" s="252" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F444" s="70" t="n">
+        <v>1076</v>
+      </c>
+      <c r="G444" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H444" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I444" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J444" s="383" t="inlineStr">
+        <is>
+          <t>No receipt; cash; amount confirmed by owner</t>
+        </is>
+      </c>
     </row>
     <row r="445">
-      <c r="B445" s="64" t="n"/>
-      <c r="C445" s="65" t="n"/>
-      <c r="D445" s="66" t="n"/>
-      <c r="E445" s="65" t="n"/>
-      <c r="F445" s="67" t="n"/>
-      <c r="G445" s="14" t="n"/>
-      <c r="H445" s="14" t="n"/>
-      <c r="I445" s="43" t="n"/>
+      <c r="B445" s="382" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C445" s="248" t="inlineStr">
+        <is>
+          <t>Lomo (cerdo)</t>
+        </is>
+      </c>
+      <c r="D445" s="249" t="inlineStr">
+        <is>
+          <t>Remision</t>
+        </is>
+      </c>
+      <c r="E445" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F445" s="67" t="n">
+        <v>200</v>
+      </c>
+      <c r="G445" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H445" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I445" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J445" s="383" t="inlineStr">
+        <is>
+          <t>Nota remision IMG_5162; lomo $200; efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="B446" s="64" t="n"/>
@@ -45745,7 +46140,7 @@
     <row r="33">
       <c r="A33" s="380" t="inlineStr">
         <is>
-          <t>Software / Subscription</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="B33" s="378">
@@ -45772,7 +46167,7 @@
     <row r="34">
       <c r="A34" s="380" t="inlineStr">
         <is>
-          <t>Kitchen Supplies</t>
+          <t>Software / Subscription</t>
         </is>
       </c>
       <c r="B34" s="378">
@@ -45799,7 +46194,7 @@
     <row r="35">
       <c r="A35" s="380" t="inlineStr">
         <is>
-          <t>Staff - Advance</t>
+          <t>Kitchen Supplies</t>
         </is>
       </c>
       <c r="B35" s="378">
@@ -45826,7 +46221,7 @@
     <row r="36">
       <c r="A36" s="380" t="inlineStr">
         <is>
-          <t>Utilities / Internet</t>
+          <t>Staff - Advance</t>
         </is>
       </c>
       <c r="B36" s="378">
@@ -45853,7 +46248,7 @@
     <row r="37">
       <c r="A37" s="380" t="inlineStr">
         <is>
-          <t>Packaging / Disposables</t>
+          <t>Utilities / Internet</t>
         </is>
       </c>
       <c r="B37" s="378">
@@ -45880,7 +46275,7 @@
     <row r="38">
       <c r="A38" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Desserts</t>
+          <t>Packaging / Disposables</t>
         </is>
       </c>
       <c r="B38" s="378">
@@ -45907,7 +46302,7 @@
     <row r="39">
       <c r="A39" s="380" t="inlineStr">
         <is>
-          <t>Ingredients - Eggs</t>
+          <t>Ingredients - Desserts</t>
         </is>
       </c>
       <c r="B39" s="378">
@@ -45934,7 +46329,7 @@
     <row r="40">
       <c r="A40" s="380" t="inlineStr">
         <is>
-          <t>Packaging/Disposables</t>
+          <t>Ingredients - Eggs</t>
         </is>
       </c>
       <c r="B40" s="378">
@@ -45961,7 +46356,7 @@
     <row r="41">
       <c r="A41" s="380" t="inlineStr">
         <is>
-          <t>Staff - Propinas</t>
+          <t>Packaging/Disposables</t>
         </is>
       </c>
       <c r="B41" s="378">
@@ -45988,7 +46383,7 @@
     <row r="42">
       <c r="A42" s="380" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Staff - Propinas</t>
         </is>
       </c>
       <c r="B42" s="378">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5509,7 +5509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="278" min="1" max="1"/>
@@ -6594,30 +6594,63 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="397" t="inlineStr">
+      <c r="A35" s="397" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B35" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 09-Jul)</t>
+        </is>
+      </c>
+      <c r="C35" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D35" s="232" t="n"/>
+      <c r="E35" s="233" t="n">
+        <v>120</v>
+      </c>
+      <c r="F35" s="233">
+        <f>IFERROR(F34+D35-E35,0)</f>
+        <v/>
+      </c>
+      <c r="G35" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H35" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid $120 by transfer to Lohith (09-Jul revenue; cash to Lohith not till)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="397" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B35" s="232" t="n"/>
-      <c r="C35" s="232" t="n"/>
-      <c r="D35" s="232">
-        <f>SUM(D4:D34)</f>
-        <v/>
-      </c>
-      <c r="E35" s="233">
-        <f>SUM(E4:E34)</f>
-        <v/>
-      </c>
-      <c r="F35" s="233">
-        <f>F34</f>
-        <v/>
-      </c>
-      <c r="G35" s="232">
-        <f>IF(F34&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F34,"#,##0"),IF(F34&lt;0,"Lohith holds $"&amp;TEXT(ABS(F34),"#,##0"),"Zero balance"))</f>
-        <v/>
-      </c>
-      <c r="H35" s="232" t="n"/>
+      <c r="B36" s="232" t="n"/>
+      <c r="C36" s="232" t="n"/>
+      <c r="D36" s="232">
+        <f>SUM(D4:D35)</f>
+        <v/>
+      </c>
+      <c r="E36" s="233">
+        <f>SUM(E4:E35)</f>
+        <v/>
+      </c>
+      <c r="F36" s="233">
+        <f>F35</f>
+        <v/>
+      </c>
+      <c r="G36" s="232">
+        <f>IF(F35&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F35,"#,##0"),IF(F35&lt;0,"Lohith holds $"&amp;TEXT(ABS(F35),"#,##0"),"Zero balance"))</f>
+        <v/>
+      </c>
+      <c r="H36" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -11122,30 +11155,71 @@
       <c r="U58" s="419" t="n">
         <v>1078</v>
       </c>
-      <c r="V58" s="419">
-        <f>IFERROR(U58*$X$7,0)</f>
-        <v/>
+      <c r="V58" s="419" t="n">
+        <v>22.1</v>
       </c>
       <c r="W58" s="383" t="n"/>
       <c r="X58" s="383" t="n"/>
     </row>
     <row r="59" ht="16.5" customHeight="1" s="278">
-      <c r="B59" s="34" t="n"/>
-      <c r="C59" s="47" t="n"/>
-      <c r="D59" s="48" t="n"/>
-      <c r="E59" s="49" t="n"/>
-      <c r="F59" s="50" t="n"/>
-      <c r="G59" s="51" t="n"/>
-      <c r="H59" s="52" t="n"/>
-      <c r="I59" s="53" t="n"/>
-      <c r="J59" s="54" t="n"/>
-      <c r="K59" s="55" t="n"/>
-      <c r="L59" s="18" t="n"/>
-      <c r="M59" s="21" t="n"/>
-      <c r="N59" s="56" t="n"/>
-      <c r="O59" s="57" t="n"/>
-      <c r="P59" s="58" t="n"/>
-      <c r="Q59" s="56" t="n"/>
+      <c r="B59" s="385" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C59" s="256" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D59" s="257" t="n">
+        <v>1940</v>
+      </c>
+      <c r="E59" s="49" t="n">
+        <v>3685</v>
+      </c>
+      <c r="F59" s="50">
+        <f>IFERROR(D59+E59+G59+U59,0)</f>
+        <v/>
+      </c>
+      <c r="G59" s="258" t="n">
+        <v>120</v>
+      </c>
+      <c r="H59" s="259">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B59,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B59+1))</f>
+        <v/>
+      </c>
+      <c r="I59" s="260">
+        <f>IFERROR(F59-H59,0)</f>
+        <v/>
+      </c>
+      <c r="J59" s="261">
+        <f>IFERROR(I59/F59,0)</f>
+        <v/>
+      </c>
+      <c r="K59" s="255" t="n"/>
+      <c r="L59" s="262" t="inlineStr">
+        <is>
+          <t>EOD close (dual card: MP + Soft Restaurant, actual comm)</t>
+        </is>
+      </c>
+      <c r="M59" s="415" t="n"/>
+      <c r="N59" s="416" t="n"/>
+      <c r="O59" s="417" t="n"/>
+      <c r="P59" s="418" t="n"/>
+      <c r="Q59" s="416" t="n"/>
+      <c r="R59" s="419">
+        <f>IFERROR(D59*$T$7,0)</f>
+        <v/>
+      </c>
+      <c r="S59" s="383" t="n"/>
+      <c r="T59" s="383" t="n"/>
+      <c r="U59" s="419" t="n">
+        <v>270</v>
+      </c>
+      <c r="V59" s="419" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="W59" s="383" t="n"/>
+      <c r="X59" s="383" t="n"/>
     </row>
     <row r="60" ht="16.5" customHeight="1" s="278">
       <c r="B60" s="34" t="n"/>
@@ -35450,64 +35524,262 @@
       </c>
     </row>
     <row r="446">
-      <c r="B446" s="64" t="n"/>
-      <c r="C446" s="69" t="n"/>
-      <c r="D446" s="68" t="n"/>
-      <c r="E446" s="69" t="n"/>
-      <c r="F446" s="70" t="n"/>
-      <c r="G446" s="23" t="n"/>
-      <c r="H446" s="23" t="n"/>
-      <c r="I446" s="55" t="n"/>
+      <c r="B446" s="382" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C446" s="252" t="inlineStr">
+        <is>
+          <t>Cebolla morada, mango, crema, tortillas</t>
+        </is>
+      </c>
+      <c r="D446" s="253" t="inlineStr">
+        <is>
+          <t>Chedraui Paseo</t>
+        </is>
+      </c>
+      <c r="E446" s="252" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F446" s="70" t="n">
+        <v>191.09</v>
+      </c>
+      <c r="G446" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H446" s="254" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I446" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J446" s="383" t="inlineStr">
+        <is>
+          <t>Debito Bancomer ***0863; 19:00</t>
+        </is>
+      </c>
     </row>
     <row r="447">
-      <c r="B447" s="64" t="n"/>
-      <c r="C447" s="65" t="n"/>
-      <c r="D447" s="66" t="n"/>
-      <c r="E447" s="65" t="n"/>
-      <c r="F447" s="67" t="n"/>
-      <c r="G447" s="14" t="n"/>
-      <c r="H447" s="14" t="n"/>
-      <c r="I447" s="43" t="n"/>
+      <c r="B447" s="382" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C447" s="248" t="inlineStr">
+        <is>
+          <t>Salsa BBQ Mr Wings + Salsa Mr Wings 3.8L + Pan caja masa madre</t>
+        </is>
+      </c>
+      <c r="D447" s="249" t="inlineStr">
+        <is>
+          <t>REAL La Cruz</t>
+        </is>
+      </c>
+      <c r="E447" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F447" s="67" t="n">
+        <v>506</v>
+      </c>
+      <c r="G447" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H447" s="250" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I447" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J447" s="383" t="inlineStr">
+        <is>
+          <t>Ticket venta folio 4518; debito; salsas $431 + pan $75</t>
+        </is>
+      </c>
     </row>
     <row r="448">
-      <c r="B448" s="64" t="n"/>
-      <c r="C448" s="69" t="n"/>
-      <c r="D448" s="68" t="n"/>
-      <c r="E448" s="69" t="n"/>
-      <c r="F448" s="70" t="n"/>
-      <c r="G448" s="23" t="n"/>
-      <c r="H448" s="23" t="n"/>
-      <c r="I448" s="55" t="n"/>
+      <c r="B448" s="382" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C448" s="252" t="inlineStr">
+        <is>
+          <t>Milaneza de cerdo 3.04kg @ $95</t>
+        </is>
+      </c>
+      <c r="D448" s="253" t="inlineStr">
+        <is>
+          <t>Carnicos Frescos (Central de Abastos)</t>
+        </is>
+      </c>
+      <c r="E448" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F448" s="70" t="n">
+        <v>288.8</v>
+      </c>
+      <c r="G448" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H448" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I448" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J448" s="383" t="inlineStr">
+        <is>
+          <t>Folio 74169; maciza/molida</t>
+        </is>
+      </c>
     </row>
     <row r="449">
-      <c r="B449" s="64" t="n"/>
-      <c r="C449" s="65" t="n"/>
-      <c r="D449" s="66" t="n"/>
-      <c r="E449" s="65" t="n"/>
-      <c r="F449" s="67" t="n"/>
-      <c r="G449" s="14" t="n"/>
-      <c r="H449" s="14" t="n"/>
-      <c r="I449" s="43" t="n"/>
+      <c r="B449" s="382" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C449" s="248" t="inlineStr">
+        <is>
+          <t>Pescado/mariscos</t>
+        </is>
+      </c>
+      <c r="D449" s="249" t="inlineStr">
+        <is>
+          <t>Brisa del Mar</t>
+        </is>
+      </c>
+      <c r="E449" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat &amp; Fish</t>
+        </is>
+      </c>
+      <c r="F449" s="67" t="n">
+        <v>288</v>
+      </c>
+      <c r="G449" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H449" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I449" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J449" s="383" t="inlineStr">
+        <is>
+          <t>Pescados y mariscos; NT 092008 12:21</t>
+        </is>
+      </c>
     </row>
     <row r="450">
-      <c r="B450" s="64" t="n"/>
-      <c r="C450" s="69" t="n"/>
-      <c r="D450" s="68" t="n"/>
-      <c r="E450" s="69" t="n"/>
-      <c r="F450" s="70" t="n"/>
-      <c r="G450" s="23" t="n"/>
-      <c r="H450" s="23" t="n"/>
-      <c r="I450" s="55" t="n"/>
+      <c r="B450" s="382" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C450" s="252" t="inlineStr">
+        <is>
+          <t>Tomatoes</t>
+        </is>
+      </c>
+      <c r="D450" s="253" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E450" s="252" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F450" s="70" t="n">
+        <v>39</v>
+      </c>
+      <c r="G450" s="254" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H450" s="254" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I450" s="255" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J450" s="383" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
     </row>
     <row r="451">
-      <c r="B451" s="64" t="n"/>
-      <c r="C451" s="65" t="n"/>
-      <c r="D451" s="66" t="n"/>
-      <c r="E451" s="65" t="n"/>
-      <c r="F451" s="67" t="n"/>
-      <c r="G451" s="14" t="n"/>
-      <c r="H451" s="14" t="n"/>
-      <c r="I451" s="43" t="n"/>
+      <c r="B451" s="382" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C451" s="248" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D451" s="249" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E451" s="248" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F451" s="67" t="n">
+        <v>508</v>
+      </c>
+      <c r="G451" s="250" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H451" s="250" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I451" s="251" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J451" s="383" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="B452" s="64" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -21085,8 +21085,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I2:P2"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:P2"/>
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
@@ -50636,14 +50636,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="313">
-      <c r="A1" s="417" t="inlineStr">
+      <c r="A1" s="407" t="inlineStr">
         <is>
           <t>LOKA — MONTHLY P&amp;L   (live formulas — auto-updates from Daily Log &amp; Expenses)</t>
         </is>
       </c>
-      <c r="B1" s="418" t="n"/>
-      <c r="C1" s="418" t="n"/>
-      <c r="D1" s="418" t="n"/>
+      <c r="B1" s="408" t="n"/>
+      <c r="C1" s="408" t="n"/>
+      <c r="D1" s="408" t="n"/>
       <c r="E1" s="409" t="n"/>
       <c r="F1" s="409" t="n"/>
       <c r="G1" s="409" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -25,7 +25,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="12">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ ddd"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
@@ -38,6 +38,7 @@
     <numFmt numFmtId="173" formatCode="#,##0;\-#,##0;\-"/>
     <numFmt numFmtId="174" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="175" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="176" formatCode="dd-mmm-yyyy"/>
   </numFmts>
   <fonts count="102">
     <font>
@@ -1346,7 +1347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22"/>
   </cellStyleXfs>
-  <cellXfs count="419">
+  <cellXfs count="423">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2424,6 +2425,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="51" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="37" fillId="19" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="46" fillId="20" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="51" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12094,33 +12107,72 @@
       <c r="AB62" s="292" t="n"/>
     </row>
     <row r="63" ht="16.5" customHeight="1" s="313">
-      <c r="B63" s="34" t="n"/>
-      <c r="C63" s="47" t="n"/>
-      <c r="D63" s="48" t="n"/>
-      <c r="E63" s="49" t="n"/>
-      <c r="F63" s="50" t="n"/>
-      <c r="G63" s="51" t="n"/>
-      <c r="H63" s="52" t="n"/>
-      <c r="I63" s="53" t="n"/>
-      <c r="J63" s="54" t="n"/>
-      <c r="K63" s="55" t="n"/>
-      <c r="L63" s="18" t="n"/>
-      <c r="M63" s="21" t="n"/>
-      <c r="N63" s="56" t="n"/>
-      <c r="O63" s="57" t="n"/>
-      <c r="P63" s="58" t="n"/>
-      <c r="Q63" s="56" t="n"/>
-      <c r="R63" s="56" t="n"/>
-      <c r="S63" s="56" t="n"/>
-      <c r="T63" s="56" t="n"/>
-      <c r="U63" s="56" t="n"/>
-      <c r="V63" s="56" t="n"/>
-      <c r="W63" s="56" t="n"/>
-      <c r="X63" s="56" t="n"/>
-      <c r="Y63" s="56" t="n"/>
-      <c r="Z63" s="56" t="n"/>
-      <c r="AA63" s="56" t="n"/>
-      <c r="AB63" s="56" t="n"/>
+      <c r="B63" s="420" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C63" s="255" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D63" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="49" t="n">
+        <v>1960</v>
+      </c>
+      <c r="F63" s="50">
+        <f>IFERROR(D63+E63+G63+U63+Y63,0)</f>
+        <v/>
+      </c>
+      <c r="G63" s="257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B63,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B63+1))</f>
+        <v/>
+      </c>
+      <c r="I63" s="259">
+        <f>IFERROR(F63-H63,0)</f>
+        <v/>
+      </c>
+      <c r="J63" s="260">
+        <f>IFERROR(I63/F63,0)</f>
+        <v/>
+      </c>
+      <c r="K63" s="254" t="n"/>
+      <c r="L63" s="261" t="inlineStr">
+        <is>
+          <t>EOD close (BBVA + cash)</t>
+        </is>
+      </c>
+      <c r="M63" s="291" t="n"/>
+      <c r="N63" s="292" t="n"/>
+      <c r="O63" s="293" t="n"/>
+      <c r="P63" s="294" t="n"/>
+      <c r="Q63" s="292" t="n"/>
+      <c r="R63" s="421">
+        <f>IFERROR(D63*$T$7,0)</f>
+        <v/>
+      </c>
+      <c r="S63" s="292" t="n"/>
+      <c r="T63" s="292" t="n"/>
+      <c r="U63" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" s="292" t="n"/>
+      <c r="X63" s="292" t="n"/>
+      <c r="Y63" s="421" t="n">
+        <v>1955</v>
+      </c>
+      <c r="Z63" s="421" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="AA63" s="292" t="n"/>
+      <c r="AB63" s="292" t="n"/>
     </row>
     <row r="64" ht="16.5" customHeight="1" s="313">
       <c r="B64" s="34" t="n"/>
@@ -21110,7 +21162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J474"/>
+  <dimension ref="A1:J476"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="313" min="1" max="1"/>
@@ -40995,6 +41047,92 @@
       <c r="J474" s="295" t="inlineStr">
         <is>
           <t>Pagado personalmente por Lohith (13-Jul); gasto operativo real, reembolsable via Owner Ledger. No salió de la caja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="B475" s="422" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C475" s="305" t="inlineStr">
+        <is>
+          <t>Clorox 3.8L + Tortillas blancas x3 + Rosca marmoleada + Bolillo x6</t>
+        </is>
+      </c>
+      <c r="D475" s="306" t="inlineStr">
+        <is>
+          <t>Chedraui Paseo</t>
+        </is>
+      </c>
+      <c r="E475" s="305" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F475" s="307" t="n">
+        <v>224.38</v>
+      </c>
+      <c r="G475" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H475" s="308" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I475" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J475" s="418" t="inlineStr">
+        <is>
+          <t>Debito BBVA ***3982 AUT 312881; 14-Jul 09:17; subtotal $228 - desc $3.62 = $224.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="B476" s="422" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C476" s="305" t="inlineStr">
+        <is>
+          <t>Mojarra (pescado)</t>
+        </is>
+      </c>
+      <c r="D476" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E476" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat &amp; Fish</t>
+        </is>
+      </c>
+      <c r="F476" s="307" t="n">
+        <v>372</v>
+      </c>
+      <c r="G476" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H476" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I476" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J476" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
         </is>
       </c>
     </row>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5569,7 +5569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="313" min="1" max="1"/>
@@ -6786,30 +6786,96 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="231" t="inlineStr">
+      <c r="A39" s="231" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B39" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 15-Jul)</t>
+        </is>
+      </c>
+      <c r="C39" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D39" s="232" t="n"/>
+      <c r="E39" s="233" t="n">
+        <v>130</v>
+      </c>
+      <c r="F39" s="233">
+        <f>IFERROR(F38+D39-E39,0)</f>
+        <v/>
+      </c>
+      <c r="G39" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H39" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid $130 by transfer to Lohith (15-Jul revenue; cash to Lohith not till)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="231" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B40" s="232" t="inlineStr">
+        <is>
+          <t>Sam's Club — Italpast 1kg x5 (paid CASH by Lohith)</t>
+        </is>
+      </c>
+      <c r="C40" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D40" s="232" t="n">
+        <v>195</v>
+      </c>
+      <c r="E40" s="233" t="n"/>
+      <c r="F40" s="233">
+        <f>IFERROR(F39+D40-E40,0)</f>
+        <v/>
+      </c>
+      <c r="G40" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H40" s="232" t="inlineStr">
+        <is>
+          <t>Lohith pago $195 EN EFECTIVO de su bolsillo (socio Shashi en ticket). En Expenses paid=Lohith; excluido de la caja via cash_adjust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="231" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B39" s="232" t="n"/>
-      <c r="C39" s="232" t="n"/>
-      <c r="D39" s="232">
-        <f>SUM(D4:D38)</f>
-        <v/>
-      </c>
-      <c r="E39" s="233">
-        <f>SUM(E4:E38)</f>
-        <v/>
-      </c>
-      <c r="F39" s="233">
-        <f>F38</f>
-        <v/>
-      </c>
-      <c r="G39" s="232">
-        <f>IF(F38&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F38,"#,##0"),IF(F38&lt;0,"Lohith holds $"&amp;TEXT(ABS(F38),"#,##0"),"Zero balance"))</f>
-        <v/>
-      </c>
-      <c r="H39" s="232" t="n"/>
+      <c r="B41" s="232" t="n"/>
+      <c r="C41" s="232" t="n"/>
+      <c r="D41" s="232">
+        <f>SUM(D4:D40)</f>
+        <v/>
+      </c>
+      <c r="E41" s="233">
+        <f>SUM(E4:E40)</f>
+        <v/>
+      </c>
+      <c r="F41" s="233">
+        <f>F40</f>
+        <v/>
+      </c>
+      <c r="G41" s="232">
+        <f>IF(F40&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F40,"#,##0"),IF(F40&lt;0,"Lohith holds $"&amp;TEXT(ABS(F40),"#,##0"),"Zero balance"))</f>
+        <v/>
+      </c>
+      <c r="H41" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -12175,33 +12241,72 @@
       <c r="AB63" s="292" t="n"/>
     </row>
     <row r="64" ht="16.5" customHeight="1" s="313">
-      <c r="B64" s="34" t="n"/>
-      <c r="C64" s="35" t="n"/>
-      <c r="D64" s="36" t="n"/>
-      <c r="E64" s="37" t="n"/>
-      <c r="F64" s="38" t="n"/>
-      <c r="G64" s="39" t="n"/>
-      <c r="H64" s="40" t="n"/>
-      <c r="I64" s="41" t="n"/>
-      <c r="J64" s="42" t="n"/>
-      <c r="K64" s="43" t="n"/>
-      <c r="L64" s="9" t="n"/>
-      <c r="M64" s="12" t="n"/>
-      <c r="N64" s="44" t="n"/>
-      <c r="O64" s="45" t="n"/>
-      <c r="P64" s="46" t="n"/>
-      <c r="Q64" s="44" t="n"/>
-      <c r="R64" s="44" t="n"/>
-      <c r="S64" s="44" t="n"/>
-      <c r="T64" s="44" t="n"/>
-      <c r="U64" s="44" t="n"/>
-      <c r="V64" s="44" t="n"/>
-      <c r="W64" s="44" t="n"/>
-      <c r="X64" s="44" t="n"/>
-      <c r="Y64" s="44" t="n"/>
-      <c r="Z64" s="44" t="n"/>
-      <c r="AA64" s="44" t="n"/>
-      <c r="AB64" s="44" t="n"/>
+      <c r="B64" s="420" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C64" s="255" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D64" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="49" t="n">
+        <v>2105</v>
+      </c>
+      <c r="F64" s="50">
+        <f>IFERROR(D64+E64+G64+U64+Y64,0)</f>
+        <v/>
+      </c>
+      <c r="G64" s="257" t="n">
+        <v>130</v>
+      </c>
+      <c r="H64" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B64,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B64+1))</f>
+        <v/>
+      </c>
+      <c r="I64" s="259">
+        <f>IFERROR(F64-H64,0)</f>
+        <v/>
+      </c>
+      <c r="J64" s="260">
+        <f>IFERROR(I64/F64,0)</f>
+        <v/>
+      </c>
+      <c r="K64" s="254" t="n"/>
+      <c r="L64" s="261" t="inlineStr">
+        <is>
+          <t>EOD close (BBVA + cash) | +$605 cash added (correction)</t>
+        </is>
+      </c>
+      <c r="M64" s="291" t="n"/>
+      <c r="N64" s="292" t="n"/>
+      <c r="O64" s="293" t="n"/>
+      <c r="P64" s="294" t="n"/>
+      <c r="Q64" s="292" t="n"/>
+      <c r="R64" s="421">
+        <f>IFERROR(D64*$T$7,0)</f>
+        <v/>
+      </c>
+      <c r="S64" s="292" t="n"/>
+      <c r="T64" s="292" t="n"/>
+      <c r="U64" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" s="292" t="n"/>
+      <c r="X64" s="292" t="n"/>
+      <c r="Y64" s="421" t="n">
+        <v>3330</v>
+      </c>
+      <c r="Z64" s="421" t="n">
+        <v>63.27</v>
+      </c>
+      <c r="AA64" s="292" t="n"/>
+      <c r="AB64" s="292" t="n"/>
     </row>
     <row r="65" ht="16.5" customHeight="1" s="313">
       <c r="B65" s="34" t="n"/>
@@ -21137,9 +21242,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -21162,7 +21267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J476"/>
+  <dimension ref="A1:J483"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="313" min="1" max="1"/>
@@ -41133,6 +41238,307 @@
       <c r="J476" s="418" t="inlineStr">
         <is>
           <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="B477" s="422" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C477" s="305" t="inlineStr">
+        <is>
+          <t>Italpast 1kg x5</t>
+        </is>
+      </c>
+      <c r="D477" s="306" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="E477" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F477" s="307" t="n">
+        <v>195</v>
+      </c>
+      <c r="G477" s="308" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H477" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I477" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J477" s="418" t="inlineStr">
+        <is>
+          <t>Sam's $195 (sub $199.50 - desc $4.50). Pagado en EFECTIVO por LOHITH (bolsillo propio, no de la caja). Reembolsable via Owner Ledger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="B478" s="422" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C478" s="305" t="inlineStr">
+        <is>
+          <t>Leche deslactosada, Unico fresco, Crutones</t>
+        </is>
+      </c>
+      <c r="D478" s="306" t="inlineStr">
+        <is>
+          <t>Costco</t>
+        </is>
+      </c>
+      <c r="E478" s="305" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F478" s="307" t="n">
+        <v>615</v>
+      </c>
+      <c r="G478" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H478" s="308" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I478" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J478" s="418" t="inlineStr">
+        <is>
+          <t>Debito ***3982 ticket 1672; total $615 (sub $629.13 - desc $14.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="B479" s="422" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C479" s="305" t="inlineStr">
+        <is>
+          <t>Snickers, Queso Philadelphia x2, tortillas, baguette</t>
+        </is>
+      </c>
+      <c r="D479" s="306" t="inlineStr">
+        <is>
+          <t>Chedraui Selecto</t>
+        </is>
+      </c>
+      <c r="E479" s="305" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F479" s="307" t="n">
+        <v>282.86</v>
+      </c>
+      <c r="G479" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H479" s="308" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I479" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J479" s="418" t="inlineStr">
+        <is>
+          <t>Debito ***3982 AUT 305923; sub $286.87 - desc $3.01 = $282.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="B480" s="422" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C480" s="305" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D480" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E480" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F480" s="307" t="n">
+        <v>581</v>
+      </c>
+      <c r="G480" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H480" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I480" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J480" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="B481" s="422" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C481" s="305" t="inlineStr">
+        <is>
+          <t>Cilantro</t>
+        </is>
+      </c>
+      <c r="D481" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E481" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F481" s="307" t="n">
+        <v>5</v>
+      </c>
+      <c r="G481" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H481" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I481" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J481" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="B482" s="422" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C482" s="305" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D482" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E482" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F482" s="307" t="n">
+        <v>579</v>
+      </c>
+      <c r="G482" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H482" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I482" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J482" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="B483" s="422" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C483" s="305" t="inlineStr">
+        <is>
+          <t>Telmex (internet/telefono)</t>
+        </is>
+      </c>
+      <c r="D483" s="306" t="inlineStr">
+        <is>
+          <t>Telmex</t>
+        </is>
+      </c>
+      <c r="E483" s="305" t="inlineStr">
+        <is>
+          <t>Utilities/Internet</t>
+        </is>
+      </c>
+      <c r="F483" s="307" t="n">
+        <v>349</v>
+      </c>
+      <c r="G483" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H483" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I483" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J483" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash; monthly internet/phone</t>
         </is>
       </c>
     </row>
@@ -51358,7 +51764,7 @@
     <row r="24">
       <c r="A24" s="415" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="B24" s="413">
@@ -51385,7 +51791,7 @@
     <row r="25">
       <c r="A25" s="415" t="inlineStr">
         <is>
-          <t>Supermarket/General</t>
+          <t>Supplies / Other</t>
         </is>
       </c>
       <c r="B25" s="413">
@@ -51736,7 +52142,7 @@
     <row r="38">
       <c r="A38" s="415" t="inlineStr">
         <is>
-          <t>Packaging / Disposables</t>
+          <t>Utilities/Internet</t>
         </is>
       </c>
       <c r="B38" s="413">
@@ -51763,7 +52169,7 @@
     <row r="39">
       <c r="A39" s="415" t="inlineStr">
         <is>
-          <t>Ingredients - Desserts</t>
+          <t>Packaging / Disposables</t>
         </is>
       </c>
       <c r="B39" s="413">
@@ -51790,7 +52196,7 @@
     <row r="40">
       <c r="A40" s="415" t="inlineStr">
         <is>
-          <t>Ingredients - Eggs</t>
+          <t>Ingredients - Desserts</t>
         </is>
       </c>
       <c r="B40" s="413">
@@ -51817,7 +52223,7 @@
     <row r="41">
       <c r="A41" s="415" t="inlineStr">
         <is>
-          <t>Packaging/Disposables</t>
+          <t>Ingredients - Eggs</t>
         </is>
       </c>
       <c r="B41" s="413">
@@ -51844,7 +52250,7 @@
     <row r="42">
       <c r="A42" s="415" t="inlineStr">
         <is>
-          <t>Staff - Propinas</t>
+          <t>Packaging/Disposables</t>
         </is>
       </c>
       <c r="B42" s="413">
@@ -51871,7 +52277,7 @@
     <row r="43">
       <c r="A43" s="415" t="inlineStr">
         <is>
-          <t>Ingredients - Produce</t>
+          <t>Staff - Propinas</t>
         </is>
       </c>
       <c r="B43" s="413">
@@ -51896,21 +52302,21 @@
       <c r="L43" s="409" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="412" t="inlineStr">
-        <is>
-          <t>TOTAL EXPENSES</t>
-        </is>
-      </c>
-      <c r="B44" s="414">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
-        <v/>
-      </c>
-      <c r="C44" s="414">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
-        <v/>
-      </c>
-      <c r="D44" s="414">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+      <c r="A44" s="415" t="inlineStr">
+        <is>
+          <t>Ingredients - Produce</t>
+        </is>
+      </c>
+      <c r="B44" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A44,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <v/>
+      </c>
+      <c r="C44" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A44,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <v/>
+      </c>
+      <c r="D44" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A44,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E44" s="409" t="n"/>
@@ -51925,19 +52331,19 @@
     <row r="45">
       <c r="A45" s="412" t="inlineStr">
         <is>
-          <t>NET PROFIT / LOSS</t>
+          <t>TOTAL EXPENSES</t>
         </is>
       </c>
       <c r="B45" s="414">
-        <f>B4-B44</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C45" s="414">
-        <f>C4-C44</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D45" s="414">
-        <f>D4-D44</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E45" s="409" t="n"/>
@@ -51950,10 +52356,23 @@
       <c r="L45" s="409" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="409" t="n"/>
-      <c r="B46" s="409" t="n"/>
-      <c r="C46" s="409" t="n"/>
-      <c r="D46" s="409" t="n"/>
+      <c r="A46" s="412" t="inlineStr">
+        <is>
+          <t>NET PROFIT / LOSS</t>
+        </is>
+      </c>
+      <c r="B46" s="414">
+        <f>B4-B45</f>
+        <v/>
+      </c>
+      <c r="C46" s="414">
+        <f>C4-C45</f>
+        <v/>
+      </c>
+      <c r="D46" s="414">
+        <f>D4-D45</f>
+        <v/>
+      </c>
       <c r="E46" s="409" t="n"/>
       <c r="F46" s="409" t="n"/>
       <c r="G46" s="409" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -19,7 +19,7 @@
     <sheet name="💰 Owner Ledger" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1347,7 +1347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22"/>
   </cellStyleXfs>
-  <cellXfs count="423">
+  <cellXfs count="432">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2437,6 +2437,21 @@
     <xf numFmtId="176" fontId="51" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="171" fontId="72" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="73" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="92" fillId="44" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="101" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="98" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2880,7 +2895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="3" customWidth="1" style="313" min="1" max="1"/>
@@ -4164,20 +4179,60 @@
       </c>
     </row>
     <row r="62" ht="22.05" customHeight="1" s="313">
-      <c r="B62" s="237" t="n"/>
-      <c r="C62" s="236" t="n"/>
-      <c r="D62" s="191" t="n"/>
-      <c r="E62" s="190" t="n"/>
-      <c r="F62" s="190" t="n"/>
-      <c r="G62" s="189" t="n"/>
+      <c r="B62" s="237" t="inlineStr">
+        <is>
+          <t>Additional License Costs</t>
+        </is>
+      </c>
+      <c r="C62" s="423" t="n">
+        <v>46223</v>
+      </c>
+      <c r="D62" s="424" t="n">
+        <v>2300</v>
+      </c>
+      <c r="E62" s="425" t="inlineStr">
+        <is>
+          <t>Gov / License</t>
+        </is>
+      </c>
+      <c r="F62" s="425" t="inlineStr">
+        <is>
+          <t>Legal / License</t>
+        </is>
+      </c>
+      <c r="G62" s="426" t="inlineStr">
+        <is>
+          <t>Additional license fees — paid by Lohith (from pooled partner capital)</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="19.95" customHeight="1" s="313">
-      <c r="B63" s="137" t="n"/>
-      <c r="C63" s="137" t="n"/>
-      <c r="D63" s="162" t="n"/>
-      <c r="E63" s="137" t="n"/>
-      <c r="F63" s="137" t="n"/>
-      <c r="G63" s="137" t="n"/>
+      <c r="B63" s="237" t="inlineStr">
+        <is>
+          <t>Coffee board + flyers, visiting cards</t>
+        </is>
+      </c>
+      <c r="C63" s="423" t="n">
+        <v>46223</v>
+      </c>
+      <c r="D63" s="424" t="n">
+        <v>2620</v>
+      </c>
+      <c r="E63" s="425" t="inlineStr">
+        <is>
+          <t>Print Shop</t>
+        </is>
+      </c>
+      <c r="F63" s="425" t="inlineStr">
+        <is>
+          <t>Branding / Printing</t>
+        </is>
+      </c>
+      <c r="G63" s="426" t="inlineStr">
+        <is>
+          <t>Coffee menu board, flyers, visiting cards — paid by Lohith (from pooled partner capital)</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="19.95" customHeight="1" s="313">
       <c r="B64" s="137" t="n"/>
@@ -4687,7 +4742,7 @@
         </is>
       </c>
       <c r="C90" s="159">
-        <f>SUM(D43:D44)</f>
+        <f>SUM(D43:D51)</f>
         <v/>
       </c>
       <c r="D90" s="167">
@@ -5272,9 +5327,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="B136" s="235">
-        <f>Total Funds In</f>
-        <v/>
+      <c r="B136" s="235" t="inlineStr">
+        <is>
+          <t>Total Funds In</t>
+        </is>
       </c>
       <c r="D136" s="241">
         <f>D133+D134+D135</f>
@@ -5315,9 +5371,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="B140">
-        <f>REMAINING WITH ME (budget left WITH Lohith)</f>
-        <v/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>REMAINING WITH ME (budget left WITH Lohith)</t>
+        </is>
       </c>
       <c r="D140">
         <f>D136-D137-D138-D139</f>
@@ -5405,6 +5462,271 @@
           <t>MP commission now auto-calculated per day in Daily Log (col R) at the rate in T7; feeds this result and Cash-on-Hand automatically.</t>
         </is>
       </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="427" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  L.  POOLED CAPITAL POSITION  (single $600k pot — reconciles fully)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="428" t="inlineStr">
+        <is>
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="C151" s="428" t="inlineStr">
+        <is>
+          <t>Amount ($)</t>
+        </is>
+      </c>
+      <c r="E151" s="428" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" s="428" t="inlineStr">
+        <is>
+          <t>POOLED COMMITTED BUDGET</t>
+        </is>
+      </c>
+      <c r="C152" s="429">
+        <f>SUM(D6:D8)</f>
+        <v/>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Lohith 300k + Kashi 180k + Shashi 120k</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" s="428" t="inlineStr">
+        <is>
+          <t>CAPITAL DEPLOYED (spent / committed out):</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Acquisition — paid to previous owners</t>
+        </is>
+      </c>
+      <c r="C154" s="431">
+        <f>SUM(D14:D30)</f>
+        <v/>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>of $390k (incl $15,530 CFE offset); incl $5k advance</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" s="430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Lohith pre-opening (excl. $5k advance)</t>
+        </is>
+      </c>
+      <c r="C155" s="431">
+        <f>D67-D56</f>
+        <v/>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Notary, poliza, licenses, branding (advance is in acq. above)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Kashigoud — direct ops</t>
+        </is>
+      </c>
+      <c r="C156" s="431">
+        <f>SUM(D43:D51)</f>
+        <v/>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Soft license + MP terminal + cameras (his card)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" s="430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Shashirekha — direct expenses</t>
+        </is>
+      </c>
+      <c r="C157" s="431">
+        <f>SUM(D72:D81)</f>
+        <v/>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Signage, Temu, menus (net of reimb.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Renovation / post-opening CapEx</t>
+        </is>
+      </c>
+      <c r="C158" s="431">
+        <f>D129</f>
+        <v/>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Section I</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" s="430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Operating costs funded from capital</t>
+        </is>
+      </c>
+      <c r="C159" s="431">
+        <f>C147</f>
+        <v/>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Rent-from-capital + owner-ledger settlement (Section K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" s="428" t="inlineStr">
+        <is>
+          <t>TOTAL CAPITAL DEPLOYED</t>
+        </is>
+      </c>
+      <c r="C160" s="429">
+        <f>SUM(C154:C159)</f>
+        <v/>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Money spent OR committed out of the pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" s="428" t="inlineStr">
+        <is>
+          <t>CAPITAL STILL AVAILABLE:</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Cash still WITH Lohith (Section J)</t>
+        </is>
+      </c>
+      <c r="C162" s="431">
+        <f>D140</f>
+        <v/>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Undeployed capital physically in Lohith’s hands</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" s="430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Kashigoud still to TRANSFER IN</t>
+        </is>
+      </c>
+      <c r="C163" s="431">
+        <f>F100</f>
+        <v/>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Committed $180k not yet fully sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" s="430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Shashirekha still to TRANSFER IN</t>
+        </is>
+      </c>
+      <c r="C164" s="431">
+        <f>F101</f>
+        <v/>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>~0 (fully deployed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" s="428" t="inlineStr">
+        <is>
+          <t>TOTAL CAPITAL AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C165" s="429">
+        <f>C162+C163+C164</f>
+        <v/>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>With Lohith + still to come in</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" s="428" t="inlineStr">
+        <is>
+          <t>CHECK: Deployed + Available</t>
+        </is>
+      </c>
+      <c r="C166" s="429">
+        <f>C160+C165</f>
+        <v/>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>MUST equal $600,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" s="428" t="n"/>
+    </row>
+    <row r="168">
+      <c r="B168" s="430" t="n"/>
+      <c r="C168" s="431" t="n"/>
+    </row>
+    <row r="169">
+      <c r="B169" s="430" t="n"/>
+      <c r="C169" s="431" t="n"/>
+    </row>
+    <row r="170">
+      <c r="B170" s="430" t="n"/>
+      <c r="C170" s="431" t="n"/>
+    </row>
+    <row r="171">
+      <c r="B171" s="428" t="n"/>
+      <c r="C171" s="429" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5569,7 +5891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="313" min="1" max="1"/>
@@ -6852,30 +7174,172 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="231" t="inlineStr">
+      <c r="A41" s="231" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B41" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 17-Jul)</t>
+        </is>
+      </c>
+      <c r="C41" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D41" s="232" t="n"/>
+      <c r="E41" s="233" t="n">
+        <v>300</v>
+      </c>
+      <c r="F41" s="233">
+        <f>IFERROR(F40+D41-E41,0)</f>
+        <v/>
+      </c>
+      <c r="G41" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H41" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid $300 by transfer to Lohith (17-Jul revenue; cash to Lohith not till)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="231" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B42" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 18-Jul)</t>
+        </is>
+      </c>
+      <c r="C42" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D42" s="232" t="n"/>
+      <c r="E42" s="233" t="n">
+        <v>290</v>
+      </c>
+      <c r="F42" s="233">
+        <f>IFERROR(F41+D42-E42,0)</f>
+        <v/>
+      </c>
+      <c r="G42" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H42" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid $290 by transfer to Lohith (18-Jul revenue; cash to Lohith not till)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="231" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B43" s="232" t="inlineStr">
+        <is>
+          <t>Pollo (paid by Lohith, 17-Jul)</t>
+        </is>
+      </c>
+      <c r="C43" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D43" s="232" t="n">
+        <v>300</v>
+      </c>
+      <c r="E43" s="233" t="n"/>
+      <c r="F43" s="233">
+        <f>IFERROR(F42+D43-E43,0)</f>
+        <v/>
+      </c>
+      <c r="G43" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H43" s="232" t="inlineStr">
+        <is>
+          <t>Lohith pago $300 de pollo de su bolsillo (17-Jul). En Expenses paid=Lohith; excluido de la caja via cash_adjust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="231" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B44" s="232" t="inlineStr">
+        <is>
+          <t>Bistec $290 + Pollo $89 + Hielo Oxxo $54 (paid by Lohith)</t>
+        </is>
+      </c>
+      <c r="C44" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D44" s="232" t="n">
+        <v>433</v>
+      </c>
+      <c r="E44" s="233" t="n"/>
+      <c r="F44" s="233">
+        <f>IFERROR(F43+D44-E44,0)</f>
+        <v/>
+      </c>
+      <c r="G44" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H44" s="232" t="inlineStr">
+        <is>
+          <t>Lohith pago $433 de su bolsillo (20-Jul). En Expenses paid=Lohith; excluido de la caja via cash_adjust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="231" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B41" s="232" t="n"/>
-      <c r="C41" s="232" t="n"/>
-      <c r="D41" s="232">
-        <f>SUM(D4:D40)</f>
-        <v/>
-      </c>
-      <c r="E41" s="233">
-        <f>SUM(E4:E40)</f>
-        <v/>
-      </c>
-      <c r="F41" s="233">
-        <f>F40</f>
-        <v/>
-      </c>
-      <c r="G41" s="232">
-        <f>IF(F40&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F40,"#,##0"),IF(F40&lt;0,"Lohith holds $"&amp;TEXT(ABS(F40),"#,##0"),"Zero balance"))</f>
-        <v/>
-      </c>
-      <c r="H41" s="232" t="n"/>
+      <c r="B45" s="232" t="n"/>
+      <c r="C45" s="232" t="n"/>
+      <c r="D45" s="232">
+        <f>SUM(D4:D44)</f>
+        <v/>
+      </c>
+      <c r="E45" s="233">
+        <f>SUM(E4:E44)</f>
+        <v/>
+      </c>
+      <c r="F45" s="233">
+        <f>F44</f>
+        <v/>
+      </c>
+      <c r="G45" s="232">
+        <f>IF(F44&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F44,"#,##0"),IF(F44&lt;0,"Lohith holds $"&amp;TEXT(ABS(F44),"#,##0"),"Zero balance"))</f>
+        <v/>
+      </c>
+      <c r="H45" s="232" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="231" t="n"/>
+      <c r="B46" s="232" t="n"/>
+      <c r="C46" s="232" t="n"/>
+      <c r="D46" s="232" t="n"/>
+      <c r="E46" s="233" t="n"/>
+      <c r="F46" s="233" t="n"/>
+      <c r="G46" s="232" t="n"/>
+      <c r="H46" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8898,7 +9362,7 @@
       </c>
       <c r="F8" s="38">
         <f>IFERROR(D8+E8+G8,0)</f>
-        <v/>
+        <v>3689.0</v>
       </c>
       <c r="G8" s="39" t="n"/>
       <c r="H8" s="40">
@@ -8907,11 +9371,11 @@
       </c>
       <c r="I8" s="41">
         <f>IFERROR(F8-H8,0)</f>
-        <v/>
+        <v>1060.0</v>
       </c>
       <c r="J8" s="42">
         <f>IFERROR(I8/F8,0)</f>
-        <v/>
+        <v>0.287341</v>
       </c>
       <c r="K8" s="43" t="n"/>
       <c r="L8" s="9" t="inlineStr">
@@ -8956,7 +9420,7 @@
       </c>
       <c r="F9" s="50">
         <f>IFERROR(D9+E9+G9,0)</f>
-        <v/>
+        <v>3854.0</v>
       </c>
       <c r="G9" s="51" t="n"/>
       <c r="H9" s="52">
@@ -8965,11 +9429,11 @@
       </c>
       <c r="I9" s="53">
         <f>IFERROR(F9-H9,0)</f>
-        <v/>
+        <v>3824.0</v>
       </c>
       <c r="J9" s="54">
         <f>IFERROR(I9/F9,0)</f>
-        <v/>
+        <v>0.992216</v>
       </c>
       <c r="K9" s="55" t="n"/>
       <c r="L9" s="18" t="inlineStr">
@@ -9014,7 +9478,7 @@
       </c>
       <c r="F10" s="38">
         <f>IFERROR(D10+E10+G10,0)</f>
-        <v/>
+        <v>4124.0</v>
       </c>
       <c r="G10" s="39" t="n"/>
       <c r="H10" s="40">
@@ -9023,11 +9487,11 @@
       </c>
       <c r="I10" s="41">
         <f>IFERROR(F10-H10,0)</f>
-        <v/>
+        <v>347.0</v>
       </c>
       <c r="J10" s="42">
         <f>IFERROR(I10/F10,0)</f>
-        <v/>
+        <v>0.084142</v>
       </c>
       <c r="K10" s="43" t="n"/>
       <c r="L10" s="9" t="inlineStr">
@@ -9072,7 +9536,7 @@
       </c>
       <c r="F11" s="50">
         <f>IFERROR(D11+E11+G11,0)</f>
-        <v/>
+        <v>4733.0</v>
       </c>
       <c r="G11" s="51" t="n"/>
       <c r="H11" s="52">
@@ -9081,11 +9545,11 @@
       </c>
       <c r="I11" s="53">
         <f>IFERROR(F11-H11,0)</f>
-        <v/>
+        <v>2299.0</v>
       </c>
       <c r="J11" s="54">
         <f>IFERROR(I11/F11,0)</f>
-        <v/>
+        <v>0.485738</v>
       </c>
       <c r="K11" s="55" t="n"/>
       <c r="L11" s="18" t="inlineStr">
@@ -9130,7 +9594,7 @@
       </c>
       <c r="F12" s="38">
         <f>IFERROR(D12+E12+G12,0)</f>
-        <v/>
+        <v>4282.0</v>
       </c>
       <c r="G12" s="39" t="n"/>
       <c r="H12" s="40">
@@ -9139,11 +9603,11 @@
       </c>
       <c r="I12" s="41">
         <f>IFERROR(F12-H12,0)</f>
-        <v/>
+        <v>2825.0</v>
       </c>
       <c r="J12" s="42">
         <f>IFERROR(I12/F12,0)</f>
-        <v/>
+        <v>0.659738</v>
       </c>
       <c r="K12" s="43" t="n"/>
       <c r="L12" s="9" t="inlineStr">
@@ -9188,7 +9652,7 @@
       </c>
       <c r="F13" s="50">
         <f>IFERROR(D13+E13+G13,0)</f>
-        <v/>
+        <v>3802.0</v>
       </c>
       <c r="G13" s="51" t="n"/>
       <c r="H13" s="52">
@@ -9197,11 +9661,11 @@
       </c>
       <c r="I13" s="53">
         <f>IFERROR(F13-H13,0)</f>
-        <v/>
+        <v>-3953.43</v>
       </c>
       <c r="J13" s="54">
         <f>IFERROR(I13/F13,0)</f>
-        <v/>
+        <v>-1.039829</v>
       </c>
       <c r="K13" s="55" t="inlineStr">
         <is>
@@ -9248,7 +9712,7 @@
       </c>
       <c r="F14" s="38">
         <f>IFERROR(D14+E14+G14,0)</f>
-        <v/>
+        <v>1198.0</v>
       </c>
       <c r="G14" s="39" t="n"/>
       <c r="H14" s="40">
@@ -9257,11 +9721,11 @@
       </c>
       <c r="I14" s="41">
         <f>IFERROR(F14-H14,0)</f>
-        <v/>
+        <v>122.0</v>
       </c>
       <c r="J14" s="42">
         <f>IFERROR(I14/F14,0)</f>
-        <v/>
+        <v>0.101836</v>
       </c>
       <c r="K14" s="43" t="inlineStr">
         <is>
@@ -9310,7 +9774,7 @@
       </c>
       <c r="F15" s="50">
         <f>IFERROR(D15+E15+G15,0)</f>
-        <v/>
+        <v>3730.0</v>
       </c>
       <c r="G15" s="51" t="n"/>
       <c r="H15" s="52">
@@ -9319,11 +9783,11 @@
       </c>
       <c r="I15" s="53">
         <f>IFERROR(F15-H15,0)</f>
-        <v/>
+        <v>708.55</v>
       </c>
       <c r="J15" s="54">
         <f>IFERROR(I15/F15,0)</f>
-        <v/>
+        <v>0.18996</v>
       </c>
       <c r="K15" s="55" t="n"/>
       <c r="L15" s="18" t="inlineStr">
@@ -9368,7 +9832,7 @@
       </c>
       <c r="F16" s="38">
         <f>IFERROR(D16+E16+G16,0)</f>
-        <v/>
+        <v>4264.0</v>
       </c>
       <c r="G16" s="39" t="n"/>
       <c r="H16" s="40">
@@ -9377,11 +9841,11 @@
       </c>
       <c r="I16" s="41">
         <f>IFERROR(F16-H16,0)</f>
-        <v/>
+        <v>3072.4</v>
       </c>
       <c r="J16" s="42">
         <f>IFERROR(I16/F16,0)</f>
-        <v/>
+        <v>0.720544</v>
       </c>
       <c r="K16" s="43" t="n"/>
       <c r="L16" s="9" t="inlineStr">
@@ -9426,7 +9890,7 @@
       </c>
       <c r="F17" s="50">
         <f>IFERROR(D17+E17+G17,0)</f>
-        <v/>
+        <v>3621.0</v>
       </c>
       <c r="G17" s="51" t="n"/>
       <c r="H17" s="52">
@@ -9435,11 +9899,11 @@
       </c>
       <c r="I17" s="53">
         <f>IFERROR(F17-H17,0)</f>
-        <v/>
+        <v>2547.78</v>
       </c>
       <c r="J17" s="54">
         <f>IFERROR(I17/F17,0)</f>
-        <v/>
+        <v>0.703612</v>
       </c>
       <c r="K17" s="55" t="n"/>
       <c r="L17" s="18" t="inlineStr">
@@ -9484,7 +9948,7 @@
       </c>
       <c r="F18" s="38">
         <f>IFERROR(D18+E18+G18,0)</f>
-        <v/>
+        <v>4070.0</v>
       </c>
       <c r="G18" s="39" t="n"/>
       <c r="H18" s="40">
@@ -9493,11 +9957,11 @@
       </c>
       <c r="I18" s="41">
         <f>IFERROR(F18-H18,0)</f>
-        <v/>
+        <v>2138.66</v>
       </c>
       <c r="J18" s="42">
         <f>IFERROR(I18/F18,0)</f>
-        <v/>
+        <v>0.525469</v>
       </c>
       <c r="K18" s="43" t="n"/>
       <c r="L18" s="9" t="inlineStr">
@@ -9542,7 +10006,7 @@
       </c>
       <c r="F19" s="50">
         <f>IFERROR(D19+E19+G19,0)</f>
-        <v/>
+        <v>6086.0</v>
       </c>
       <c r="G19" s="51" t="n"/>
       <c r="H19" s="52">
@@ -9551,11 +10015,11 @@
       </c>
       <c r="I19" s="53">
         <f>IFERROR(F19-H19,0)</f>
-        <v/>
+        <v>5828.71</v>
       </c>
       <c r="J19" s="54">
         <f>IFERROR(I19/F19,0)</f>
-        <v/>
+        <v>0.957724</v>
       </c>
       <c r="K19" s="55" t="n"/>
       <c r="L19" s="18" t="inlineStr">
@@ -9600,7 +10064,7 @@
       </c>
       <c r="F20" s="38">
         <f>IFERROR(D20+E20+G20,0)</f>
-        <v/>
+        <v>4603.0</v>
       </c>
       <c r="G20" s="39" t="n"/>
       <c r="H20" s="40">
@@ -9609,11 +10073,11 @@
       </c>
       <c r="I20" s="41">
         <f>IFERROR(F20-H20,0)</f>
-        <v/>
+        <v>-1371.3</v>
       </c>
       <c r="J20" s="42">
         <f>IFERROR(I20/F20,0)</f>
-        <v/>
+        <v>-0.297914</v>
       </c>
       <c r="K20" s="43" t="n"/>
       <c r="L20" s="9" t="inlineStr">
@@ -9656,7 +10120,7 @@
       </c>
       <c r="F21" s="50">
         <f>IFERROR(D21+E21+G21,0)</f>
-        <v/>
+        <v>893.0</v>
       </c>
       <c r="G21" s="51" t="n"/>
       <c r="H21" s="52">
@@ -9665,11 +10129,11 @@
       </c>
       <c r="I21" s="53">
         <f>IFERROR(F21-H21,0)</f>
-        <v/>
+        <v>-9419.0</v>
       </c>
       <c r="J21" s="54">
         <f>IFERROR(I21/F21,0)</f>
-        <v/>
+        <v>-10.547592</v>
       </c>
       <c r="K21" s="55" t="n"/>
       <c r="L21" s="18" t="inlineStr">
@@ -9714,22 +10178,22 @@
       </c>
       <c r="F22" s="38">
         <f>IFERROR(D22+E22+G22,0)</f>
-        <v/>
+        <v>5019.0</v>
       </c>
       <c r="G22" s="39" t="n">
         <v>310</v>
       </c>
       <c r="H22" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B22,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B22+1))</f>
-        <v/>
+        <v>5329.64</v>
       </c>
       <c r="I22" s="41">
         <f>IFERROR(F22-H22,0)</f>
-        <v/>
+        <v>-310.64</v>
       </c>
       <c r="J22" s="42">
         <f>IFERROR(I22/F22,0)</f>
-        <v/>
+        <v>-0.061893</v>
       </c>
       <c r="K22" s="43" t="n"/>
       <c r="L22" s="9" t="inlineStr">
@@ -9774,22 +10238,22 @@
       </c>
       <c r="F23" s="50">
         <f>IFERROR(D23+E23+G23,0)</f>
-        <v/>
+        <v>1843.0</v>
       </c>
       <c r="G23" s="51" t="n">
         <v>283</v>
       </c>
       <c r="H23" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B23,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B23+1))</f>
-        <v/>
+        <v>2379.11</v>
       </c>
       <c r="I23" s="53">
         <f>IFERROR(F23-H23,0)</f>
-        <v/>
+        <v>-536.11</v>
       </c>
       <c r="J23" s="54">
         <f>IFERROR(I23/F23,0)</f>
-        <v/>
+        <v>-0.29089</v>
       </c>
       <c r="K23" s="55" t="n"/>
       <c r="L23" s="18" t="inlineStr">
@@ -9834,22 +10298,22 @@
       </c>
       <c r="F24" s="38">
         <f>IFERROR(D24+E24+G24,0)</f>
-        <v/>
+        <v>3912.0</v>
       </c>
       <c r="G24" s="39" t="n">
         <v>120</v>
       </c>
       <c r="H24" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B24,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B24+1))</f>
-        <v/>
+        <v>4211.86</v>
       </c>
       <c r="I24" s="41">
         <f>IFERROR(F24-H24,0)</f>
-        <v/>
+        <v>-299.86</v>
       </c>
       <c r="J24" s="42">
         <f>IFERROR(I24/F24,0)</f>
-        <v/>
+        <v>-0.076651</v>
       </c>
       <c r="K24" s="43" t="n"/>
       <c r="L24" s="9" t="inlineStr">
@@ -9894,7 +10358,7 @@
       </c>
       <c r="F25" s="50">
         <f>IFERROR(D25+E25+G25,0)</f>
-        <v/>
+        <v>3757.0</v>
       </c>
       <c r="G25" s="51" t="n"/>
       <c r="H25" s="52">
@@ -9903,11 +10367,11 @@
       </c>
       <c r="I25" s="53">
         <f>IFERROR(F25-H25,0)</f>
-        <v/>
+        <v>-17202.96</v>
       </c>
       <c r="J25" s="54">
         <f>IFERROR(I25/F25,0)</f>
-        <v/>
+        <v>-4.578909</v>
       </c>
       <c r="K25" s="55" t="n"/>
       <c r="L25" s="18" t="inlineStr">
@@ -9952,22 +10416,22 @@
       </c>
       <c r="F26" s="38">
         <f>IFERROR(D26+E26+G26,0)</f>
-        <v/>
+        <v>4408.0</v>
       </c>
       <c r="G26" s="39" t="n">
         <v>135</v>
       </c>
       <c r="H26" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B26,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B26+1))</f>
-        <v/>
+        <v>878.06</v>
       </c>
       <c r="I26" s="41">
         <f>IFERROR(F26-H26,0)</f>
-        <v/>
+        <v>3529.94</v>
       </c>
       <c r="J26" s="42">
         <f>IFERROR(I26/F26,0)</f>
-        <v/>
+        <v>0.800803</v>
       </c>
       <c r="K26" s="43" t="n"/>
       <c r="L26" s="9" t="inlineStr">
@@ -10012,7 +10476,7 @@
       </c>
       <c r="F27" s="50">
         <f>IFERROR(D27+E27+G27,0)</f>
-        <v/>
+        <v>2334.0</v>
       </c>
       <c r="G27" s="51" t="n"/>
       <c r="H27" s="52">
@@ -10021,11 +10485,11 @@
       </c>
       <c r="I27" s="53">
         <f>IFERROR(F27-H27,0)</f>
-        <v/>
+        <v>-3080.0</v>
       </c>
       <c r="J27" s="54">
         <f>IFERROR(I27/F27,0)</f>
-        <v/>
+        <v>-1.319623</v>
       </c>
       <c r="K27" s="55" t="n"/>
       <c r="L27" s="18" t="inlineStr">
@@ -10075,7 +10539,7 @@
       </c>
       <c r="I28" s="41">
         <f>IFERROR(F28-H28,0)</f>
-        <v/>
+        <v>-1671.0</v>
       </c>
       <c r="J28" s="42" t="n"/>
       <c r="K28" s="43" t="n"/>
@@ -10121,22 +10585,22 @@
       </c>
       <c r="F29" s="50">
         <f>IFERROR(D29+E29+G29,0)</f>
-        <v/>
+        <v>3727.0</v>
       </c>
       <c r="G29" s="51" t="n">
         <v>99</v>
       </c>
       <c r="H29" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B29,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B29+1))</f>
-        <v/>
+        <v>3187.11</v>
       </c>
       <c r="I29" s="53">
         <f>IFERROR(F29-H29,0)</f>
-        <v/>
+        <v>539.89</v>
       </c>
       <c r="J29" s="54">
         <f>IFERROR(I29/F29,0)</f>
-        <v/>
+        <v>0.144859</v>
       </c>
       <c r="K29" s="55" t="n"/>
       <c r="L29" s="18" t="inlineStr">
@@ -10181,7 +10645,7 @@
       </c>
       <c r="F30" s="38">
         <f>IFERROR(D30+E30+G30,0)</f>
-        <v/>
+        <v>5410.0</v>
       </c>
       <c r="G30" s="39" t="n"/>
       <c r="H30" s="40">
@@ -10190,11 +10654,11 @@
       </c>
       <c r="I30" s="41">
         <f>IFERROR(F30-H30,0)</f>
-        <v/>
+        <v>-1213.98</v>
       </c>
       <c r="J30" s="42">
         <f>IFERROR(I30/F30,0)</f>
-        <v/>
+        <v>-0.224396</v>
       </c>
       <c r="K30" s="43" t="n"/>
       <c r="L30" s="9" t="inlineStr">
@@ -10239,7 +10703,7 @@
       </c>
       <c r="F31" s="50">
         <f>IFERROR(D31+E31+G31,0)</f>
-        <v/>
+        <v>4265.0</v>
       </c>
       <c r="G31" s="51" t="n"/>
       <c r="H31" s="52">
@@ -10248,11 +10712,11 @@
       </c>
       <c r="I31" s="53">
         <f>IFERROR(F31-H31,0)</f>
-        <v/>
+        <v>2923.19</v>
       </c>
       <c r="J31" s="54">
         <f>IFERROR(I31/F31,0)</f>
-        <v/>
+        <v>0.68539</v>
       </c>
       <c r="K31" s="55" t="n"/>
       <c r="L31" s="18" t="inlineStr">
@@ -10297,22 +10761,22 @@
       </c>
       <c r="F32" s="38">
         <f>IFERROR(D32+E32+G32,0)</f>
-        <v/>
+        <v>4166.0</v>
       </c>
       <c r="G32" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B32,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B32+1))</f>
-        <v/>
+        <v>4044.0</v>
       </c>
       <c r="I32" s="41">
         <f>IFERROR(F32-H32,0)</f>
-        <v/>
+        <v>122.0</v>
       </c>
       <c r="J32" s="42">
         <f>IFERROR(I32/F32,0)</f>
-        <v/>
+        <v>0.029285</v>
       </c>
       <c r="K32" s="43" t="n"/>
       <c r="L32" s="9" t="inlineStr">
@@ -10357,22 +10821,22 @@
       </c>
       <c r="F33" s="50">
         <f>IFERROR(D33+E33+G33,0)</f>
-        <v/>
+        <v>6070.0</v>
       </c>
       <c r="G33" s="51" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B33,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B33+1))</f>
-        <v/>
+        <v>901.8</v>
       </c>
       <c r="I33" s="53">
         <f>IFERROR(F33-H33,0)</f>
-        <v/>
+        <v>5168.2</v>
       </c>
       <c r="J33" s="54">
         <f>IFERROR(I33/F33,0)</f>
-        <v/>
+        <v>0.851433</v>
       </c>
       <c r="K33" s="55" t="n"/>
       <c r="L33" s="18" t="inlineStr">
@@ -10417,22 +10881,22 @@
       </c>
       <c r="F34" s="38">
         <f>IFERROR(D34+E34+G34,0)</f>
-        <v/>
+        <v>1811.0</v>
       </c>
       <c r="G34" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B34,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B34+1))</f>
-        <v/>
+        <v>8084.16</v>
       </c>
       <c r="I34" s="41">
         <f>IFERROR(F34-H34,0)</f>
-        <v/>
+        <v>-6273.16</v>
       </c>
       <c r="J34" s="42">
         <f>IFERROR(I34/F34,0)</f>
-        <v/>
+        <v>-3.46392</v>
       </c>
       <c r="K34" s="43" t="n"/>
       <c r="L34" s="9" t="inlineStr">
@@ -10477,22 +10941,22 @@
       </c>
       <c r="F35" s="50">
         <f>IFERROR(D35+E35+G35,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G35" s="51" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B35,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B35+1))</f>
-        <v/>
+        <v>1526.18</v>
       </c>
       <c r="I35" s="53">
         <f>IFERROR(F35-H35,0)</f>
-        <v/>
+        <v>-1526.18</v>
       </c>
       <c r="J35" s="54">
         <f>IFERROR(I35/F35,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K35" s="55" t="n"/>
       <c r="L35" s="18" t="inlineStr">
@@ -10537,22 +11001,22 @@
       </c>
       <c r="F36" s="38">
         <f>IFERROR(D36+E36+G36,0)</f>
-        <v/>
+        <v>4423.0</v>
       </c>
       <c r="G36" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B36,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B36+1))</f>
-        <v/>
+        <v>2858.08</v>
       </c>
       <c r="I36" s="41">
         <f>IFERROR(F36-H36,0)</f>
-        <v/>
+        <v>1564.92</v>
       </c>
       <c r="J36" s="42">
         <f>IFERROR(I36/F36,0)</f>
-        <v/>
+        <v>0.353814</v>
       </c>
       <c r="K36" s="43" t="n"/>
       <c r="L36" s="9" t="inlineStr">
@@ -10597,22 +11061,22 @@
       </c>
       <c r="F37" s="50">
         <f>IFERROR(D37+E37+G37,0)</f>
-        <v/>
+        <v>2786.0</v>
       </c>
       <c r="G37" s="51" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B37,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B37+1))</f>
-        <v/>
+        <v>2541.9</v>
       </c>
       <c r="I37" s="53">
         <f>IFERROR(F37-H37,0)</f>
-        <v/>
+        <v>244.1</v>
       </c>
       <c r="J37" s="54">
         <f>IFERROR(I37/F37,0)</f>
-        <v/>
+        <v>0.087617</v>
       </c>
       <c r="K37" s="55" t="n"/>
       <c r="L37" s="18" t="inlineStr">
@@ -10657,22 +11121,22 @@
       </c>
       <c r="F38" s="38">
         <f>IFERROR(D38+E38+G38,0)</f>
-        <v/>
+        <v>4404.0</v>
       </c>
       <c r="G38" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B38,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B38+1))</f>
-        <v/>
+        <v>2353.0</v>
       </c>
       <c r="I38" s="41">
         <f>IFERROR(F38-H38,0)</f>
-        <v/>
+        <v>2051.0</v>
       </c>
       <c r="J38" s="42">
         <f>IFERROR(I38/F38,0)</f>
-        <v/>
+        <v>0.465713</v>
       </c>
       <c r="K38" s="43" t="n"/>
       <c r="L38" s="9" t="inlineStr">
@@ -10717,22 +11181,22 @@
       </c>
       <c r="F39" s="50">
         <f>IFERROR(D39+E39+G39,0)</f>
-        <v/>
+        <v>4165.0</v>
       </c>
       <c r="G39" s="51" t="n">
         <v>400</v>
       </c>
       <c r="H39" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B39,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B39+1))</f>
-        <v/>
+        <v>2958.83</v>
       </c>
       <c r="I39" s="53">
         <f>IFERROR(F39-H39,0)</f>
-        <v/>
+        <v>1206.17</v>
       </c>
       <c r="J39" s="54">
         <f>IFERROR(I39/F39,0)</f>
-        <v/>
+        <v>0.289597</v>
       </c>
       <c r="K39" s="55" t="n"/>
       <c r="L39" s="18" t="inlineStr">
@@ -10777,22 +11241,22 @@
       </c>
       <c r="F40" s="38">
         <f>IFERROR(D40+E40+G40,0)</f>
-        <v/>
+        <v>6804.0</v>
       </c>
       <c r="G40" s="39" t="n">
         <v>120</v>
       </c>
       <c r="H40" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B40,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B40+1))</f>
-        <v/>
+        <v>1483.0</v>
       </c>
       <c r="I40" s="41">
         <f>IFERROR(F40-H40,0)</f>
-        <v/>
+        <v>5321.0</v>
       </c>
       <c r="J40" s="42">
         <f>IFERROR(I40/F40,0)</f>
-        <v/>
+        <v>0.78204</v>
       </c>
       <c r="K40" s="43" t="n"/>
       <c r="L40" s="9" t="inlineStr">
@@ -10837,22 +11301,22 @@
       </c>
       <c r="F41" s="50">
         <f>IFERROR(D41+E41+G41,0)</f>
-        <v/>
+        <v>2251.0</v>
       </c>
       <c r="G41" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B41,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B41+1))</f>
-        <v/>
+        <v>9320.81</v>
       </c>
       <c r="I41" s="259">
         <f>IFERROR(F41-H41,0)</f>
-        <v/>
+        <v>-7069.81</v>
       </c>
       <c r="J41" s="260">
         <f>IFERROR(I41/F41,0)</f>
-        <v/>
+        <v>-3.140742</v>
       </c>
       <c r="K41" s="254" t="n"/>
       <c r="L41" s="261" t="inlineStr">
@@ -10897,22 +11361,22 @@
       </c>
       <c r="F42" s="38">
         <f>IFERROR(D42+E42+G42,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G42" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B42,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B42+1))</f>
-        <v/>
+        <v>2065.85</v>
       </c>
       <c r="I42" s="274">
         <f>IFERROR(F42-H42,0)</f>
-        <v/>
+        <v>-2065.85</v>
       </c>
       <c r="J42" s="275">
         <f>IFERROR(I42/F42,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K42" s="250" t="n"/>
       <c r="L42" s="276" t="inlineStr">
@@ -10957,22 +11421,22 @@
       </c>
       <c r="F43" s="50">
         <f>IFERROR(D43+E43+G43,0)</f>
-        <v/>
+        <v>4259.0</v>
       </c>
       <c r="G43" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B43,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B43+1))</f>
-        <v/>
+        <v>1451.0</v>
       </c>
       <c r="I43" s="259">
         <f>IFERROR(F43-H43,0)</f>
-        <v/>
+        <v>2808.0</v>
       </c>
       <c r="J43" s="260">
         <f>IFERROR(I43/F43,0)</f>
-        <v/>
+        <v>0.65931</v>
       </c>
       <c r="K43" s="254" t="n"/>
       <c r="L43" s="261" t="inlineStr">
@@ -11017,22 +11481,22 @@
       </c>
       <c r="F44" s="38">
         <f>IFERROR(D44+E44+G44,0)</f>
-        <v/>
+        <v>2967.0</v>
       </c>
       <c r="G44" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B44,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B44+1))</f>
-        <v/>
+        <v>757.13</v>
       </c>
       <c r="I44" s="274">
         <f>IFERROR(F44-H44,0)</f>
-        <v/>
+        <v>2209.87</v>
       </c>
       <c r="J44" s="275">
         <f>IFERROR(I44/F44,0)</f>
-        <v/>
+        <v>0.744816</v>
       </c>
       <c r="K44" s="250" t="n"/>
       <c r="L44" s="276" t="inlineStr">
@@ -11077,22 +11541,22 @@
       </c>
       <c r="F45" s="50">
         <f>IFERROR(D45+E45+G45,0)</f>
-        <v/>
+        <v>3589.0</v>
       </c>
       <c r="G45" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B45,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B45+1))</f>
-        <v/>
+        <v>3781.35</v>
       </c>
       <c r="I45" s="259">
         <f>IFERROR(F45-H45,0)</f>
-        <v/>
+        <v>-192.35</v>
       </c>
       <c r="J45" s="260">
         <f>IFERROR(I45/F45,0)</f>
-        <v/>
+        <v>-0.053594</v>
       </c>
       <c r="K45" s="254" t="n"/>
       <c r="L45" s="261" t="inlineStr">
@@ -11137,22 +11601,22 @@
       </c>
       <c r="F46" s="38">
         <f>IFERROR(D46+E46+G46,0)</f>
-        <v/>
+        <v>3588.0</v>
       </c>
       <c r="G46" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B46,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B46+1))</f>
-        <v/>
+        <v>1228.0</v>
       </c>
       <c r="I46" s="274">
         <f>IFERROR(F46-H46,0)</f>
-        <v/>
+        <v>2360.0</v>
       </c>
       <c r="J46" s="275">
         <f>IFERROR(I46/F46,0)</f>
-        <v/>
+        <v>0.657748</v>
       </c>
       <c r="K46" s="250" t="n"/>
       <c r="L46" s="276" t="inlineStr">
@@ -11197,22 +11661,22 @@
       </c>
       <c r="F47" s="50">
         <f>IFERROR(D47+E47+G47,0)</f>
-        <v/>
+        <v>4477.0</v>
       </c>
       <c r="G47" s="257" t="n">
         <v>165</v>
       </c>
       <c r="H47" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B47,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B47+1))</f>
-        <v/>
+        <v>1945.53</v>
       </c>
       <c r="I47" s="259">
         <f>IFERROR(F47-H47,0)</f>
-        <v/>
+        <v>2531.47</v>
       </c>
       <c r="J47" s="260">
         <f>IFERROR(I47/F47,0)</f>
-        <v/>
+        <v>0.565439</v>
       </c>
       <c r="K47" s="254" t="n"/>
       <c r="L47" s="261" t="inlineStr">
@@ -11257,22 +11721,22 @@
       </c>
       <c r="F48" s="38">
         <f>IFERROR(D48+E48+G48,0)</f>
-        <v/>
+        <v>2029.0</v>
       </c>
       <c r="G48" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B48,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B48+1))</f>
-        <v/>
+        <v>5250.0</v>
       </c>
       <c r="I48" s="274">
         <f>IFERROR(F48-H48,0)</f>
-        <v/>
+        <v>-3221.0</v>
       </c>
       <c r="J48" s="275">
         <f>IFERROR(I48/F48,0)</f>
-        <v/>
+        <v>-1.587482</v>
       </c>
       <c r="K48" s="250" t="n"/>
       <c r="L48" s="276" t="inlineStr">
@@ -11317,22 +11781,22 @@
       </c>
       <c r="F49" s="50">
         <f>IFERROR(D49+E49+G49,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G49" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B49,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B49+1))</f>
-        <v/>
+        <v>3865.06</v>
       </c>
       <c r="I49" s="259">
         <f>IFERROR(F49-H49,0)</f>
-        <v/>
+        <v>-3865.06</v>
       </c>
       <c r="J49" s="260">
         <f>IFERROR(I49/F49,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K49" s="254" t="n"/>
       <c r="L49" s="261" t="inlineStr">
@@ -11377,22 +11841,22 @@
       </c>
       <c r="F50" s="38">
         <f>IFERROR(D50+E50+G50,0)</f>
-        <v/>
+        <v>3389.0</v>
       </c>
       <c r="G50" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B50,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B50+1))</f>
-        <v/>
+        <v>2683.27</v>
       </c>
       <c r="I50" s="274">
         <f>IFERROR(F50-H50,0)</f>
-        <v/>
+        <v>705.73</v>
       </c>
       <c r="J50" s="275">
         <f>IFERROR(I50/F50,0)</f>
-        <v/>
+        <v>0.208241</v>
       </c>
       <c r="K50" s="250" t="n"/>
       <c r="L50" s="276" t="inlineStr">
@@ -11437,22 +11901,22 @@
       </c>
       <c r="F51" s="50">
         <f>IFERROR(D51+E51+G51,0)</f>
-        <v/>
+        <v>4133.0</v>
       </c>
       <c r="G51" s="257" t="n">
         <v>55</v>
       </c>
       <c r="H51" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B51,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B51+1))</f>
-        <v/>
+        <v>1581.27</v>
       </c>
       <c r="I51" s="259">
         <f>IFERROR(F51-H51,0)</f>
-        <v/>
+        <v>2551.73</v>
       </c>
       <c r="J51" s="260">
         <f>IFERROR(I51/F51,0)</f>
-        <v/>
+        <v>0.617404</v>
       </c>
       <c r="K51" s="254" t="n"/>
       <c r="L51" s="261" t="inlineStr">
@@ -11497,22 +11961,22 @@
       </c>
       <c r="F52" s="38">
         <f>IFERROR(D52+E52+G52,0)</f>
-        <v/>
+        <v>4522.0</v>
       </c>
       <c r="G52" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B52,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B52+1))</f>
-        <v/>
+        <v>2341.23</v>
       </c>
       <c r="I52" s="274">
         <f>IFERROR(F52-H52,0)</f>
-        <v/>
+        <v>2180.77</v>
       </c>
       <c r="J52" s="275">
         <f>IFERROR(I52/F52,0)</f>
-        <v/>
+        <v>0.482258</v>
       </c>
       <c r="K52" s="250" t="n"/>
       <c r="L52" s="276" t="inlineStr">
@@ -11557,22 +12021,22 @@
       </c>
       <c r="F53" s="50">
         <f>IFERROR(D53+E53+G53,0)</f>
-        <v/>
+        <v>3108.0</v>
       </c>
       <c r="G53" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B53,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B53+1))</f>
-        <v/>
+        <v>318.0</v>
       </c>
       <c r="I53" s="259">
         <f>IFERROR(F53-H53,0)</f>
-        <v/>
+        <v>2790.0</v>
       </c>
       <c r="J53" s="260">
         <f>IFERROR(I53/F53,0)</f>
-        <v/>
+        <v>0.897683</v>
       </c>
       <c r="K53" s="254" t="inlineStr">
         <is>
@@ -11621,22 +12085,22 @@
       </c>
       <c r="F54" s="38">
         <f>IFERROR(D54+E54+G54,0)</f>
-        <v/>
+        <v>6077.0</v>
       </c>
       <c r="G54" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B54,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B54+1))</f>
-        <v/>
+        <v>2809.6</v>
       </c>
       <c r="I54" s="274">
         <f>IFERROR(F54-H54,0)</f>
-        <v/>
+        <v>3267.4</v>
       </c>
       <c r="J54" s="275">
         <f>IFERROR(I54/F54,0)</f>
-        <v/>
+        <v>0.537667</v>
       </c>
       <c r="K54" s="250" t="inlineStr">
         <is>
@@ -11685,22 +12149,22 @@
       </c>
       <c r="F55" s="50">
         <f>IFERROR(D55+E55+G55,0)</f>
-        <v/>
+        <v>2634.0</v>
       </c>
       <c r="G55" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B55,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B55+1))</f>
-        <v/>
+        <v>6877.73</v>
       </c>
       <c r="I55" s="259">
         <f>IFERROR(F55-H55,0)</f>
-        <v/>
+        <v>-4243.73</v>
       </c>
       <c r="J55" s="260">
         <f>IFERROR(I55/F55,0)</f>
-        <v/>
+        <v>-1.611135</v>
       </c>
       <c r="K55" s="254" t="n"/>
       <c r="L55" s="261" t="inlineStr">
@@ -11745,22 +12209,22 @@
       </c>
       <c r="F56" s="38">
         <f>IFERROR(D56+E56+G56,0)</f>
-        <v/>
+        <v>3690.0</v>
       </c>
       <c r="G56" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B56,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B56+1))</f>
-        <v/>
+        <v>4200.0</v>
       </c>
       <c r="I56" s="274">
         <f>IFERROR(F56-H56,0)</f>
-        <v/>
+        <v>-510.0</v>
       </c>
       <c r="J56" s="275">
         <f>IFERROR(I56/F56,0)</f>
-        <v/>
+        <v>-0.138211</v>
       </c>
       <c r="K56" s="250" t="n"/>
       <c r="L56" s="276" t="inlineStr">
@@ -11805,22 +12269,22 @@
       </c>
       <c r="F57" s="50">
         <f>IFERROR(D57+E57+G57,0)</f>
-        <v/>
+        <v>3660.0</v>
       </c>
       <c r="G57" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B57,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B57+1))</f>
-        <v/>
+        <v>49.0</v>
       </c>
       <c r="I57" s="259">
         <f>IFERROR(F57-H57,0)</f>
-        <v/>
+        <v>3611.0</v>
       </c>
       <c r="J57" s="260">
         <f>IFERROR(I57/F57,0)</f>
-        <v/>
+        <v>0.986612</v>
       </c>
       <c r="K57" s="254" t="n"/>
       <c r="L57" s="261" t="inlineStr">
@@ -11865,22 +12329,22 @@
       </c>
       <c r="F58" s="50">
         <f>IFERROR(D58+E58+G58+U58,0)</f>
-        <v/>
+        <v>3688.0</v>
       </c>
       <c r="G58" s="257" t="n">
         <v>195</v>
       </c>
       <c r="H58" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B58,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B58+1))</f>
-        <v/>
+        <v>1415.43</v>
       </c>
       <c r="I58" s="259">
         <f>IFERROR(F58-H58,0)</f>
-        <v/>
+        <v>2272.57</v>
       </c>
       <c r="J58" s="260">
         <f>IFERROR(I58/F58,0)</f>
-        <v/>
+        <v>0.616207</v>
       </c>
       <c r="K58" s="254" t="n"/>
       <c r="L58" s="261" t="inlineStr">
@@ -11929,22 +12393,22 @@
       </c>
       <c r="F59" s="50">
         <f>IFERROR(D59+E59+G59+U59,0)</f>
-        <v/>
+        <v>6015.0</v>
       </c>
       <c r="G59" s="257" t="n">
         <v>120</v>
       </c>
       <c r="H59" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B59,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B59+1))</f>
-        <v/>
+        <v>1820.89</v>
       </c>
       <c r="I59" s="259">
         <f>IFERROR(F59-H59,0)</f>
-        <v/>
+        <v>4194.11</v>
       </c>
       <c r="J59" s="260">
         <f>IFERROR(I59/F59,0)</f>
-        <v/>
+        <v>0.697275</v>
       </c>
       <c r="K59" s="254" t="n"/>
       <c r="L59" s="261" t="inlineStr">
@@ -11993,22 +12457,22 @@
       </c>
       <c r="F60" s="50">
         <f>IFERROR(D60+E60+G60+U60,0)</f>
-        <v/>
+        <v>3500.0</v>
       </c>
       <c r="G60" s="257" t="n">
         <v>70</v>
       </c>
       <c r="H60" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B60,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B60+1))</f>
-        <v/>
+        <v>2094.0</v>
       </c>
       <c r="I60" s="259">
         <f>IFERROR(F60-H60,0)</f>
-        <v/>
+        <v>1406.0</v>
       </c>
       <c r="J60" s="260">
         <f>IFERROR(I60/F60,0)</f>
-        <v/>
+        <v>0.401714</v>
       </c>
       <c r="K60" s="254" t="n"/>
       <c r="L60" s="261" t="inlineStr">
@@ -12057,22 +12521,22 @@
       </c>
       <c r="F61" s="50">
         <f>IFERROR(D61+E61+G61+U61,0)</f>
-        <v/>
+        <v>2725.0</v>
       </c>
       <c r="G61" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B61,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B61+1))</f>
-        <v/>
+        <v>10207.0</v>
       </c>
       <c r="I61" s="259">
         <f>IFERROR(F61-H61,0)</f>
-        <v/>
+        <v>-7482.0</v>
       </c>
       <c r="J61" s="260">
         <f>IFERROR(I61/F61,0)</f>
-        <v/>
+        <v>-2.745688</v>
       </c>
       <c r="K61" s="254" t="n"/>
       <c r="L61" s="261" t="inlineStr">
@@ -12121,22 +12585,22 @@
       </c>
       <c r="F62" s="50">
         <f>IFERROR(D62+E62+G62+U62+Y62,0)</f>
-        <v/>
+        <v>3990.0</v>
       </c>
       <c r="G62" s="257" t="n">
         <v>120</v>
       </c>
       <c r="H62" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B62,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B62+1))</f>
-        <v/>
+        <v>3142.0</v>
       </c>
       <c r="I62" s="259">
         <f>IFERROR(F62-H62,0)</f>
-        <v/>
+        <v>848.0</v>
       </c>
       <c r="J62" s="260">
         <f>IFERROR(I62/F62,0)</f>
-        <v/>
+        <v>0.212531</v>
       </c>
       <c r="K62" s="254" t="n"/>
       <c r="L62" s="261" t="inlineStr">
@@ -12189,22 +12653,22 @@
       </c>
       <c r="F63" s="50">
         <f>IFERROR(D63+E63+G63+U63+Y63,0)</f>
-        <v/>
+        <v>3915.0</v>
       </c>
       <c r="G63" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B63,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B63+1))</f>
-        <v/>
+        <v>596.38</v>
       </c>
       <c r="I63" s="259">
         <f>IFERROR(F63-H63,0)</f>
-        <v/>
+        <v>3318.62</v>
       </c>
       <c r="J63" s="260">
         <f>IFERROR(I63/F63,0)</f>
-        <v/>
+        <v>0.847668</v>
       </c>
       <c r="K63" s="254" t="n"/>
       <c r="L63" s="261" t="inlineStr">
@@ -12257,22 +12721,22 @@
       </c>
       <c r="F64" s="50">
         <f>IFERROR(D64+E64+G64+U64+Y64,0)</f>
-        <v/>
+        <v>5565.0</v>
       </c>
       <c r="G64" s="257" t="n">
         <v>130</v>
       </c>
       <c r="H64" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B64,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B64+1))</f>
-        <v/>
+        <v>2606.86</v>
       </c>
       <c r="I64" s="259">
         <f>IFERROR(F64-H64,0)</f>
-        <v/>
+        <v>2958.14</v>
       </c>
       <c r="J64" s="260">
         <f>IFERROR(I64/F64,0)</f>
-        <v/>
+        <v>0.531562</v>
       </c>
       <c r="K64" s="254" t="n"/>
       <c r="L64" s="261" t="inlineStr">
@@ -12309,120 +12773,276 @@
       <c r="AB64" s="292" t="n"/>
     </row>
     <row r="65" ht="16.5" customHeight="1" s="313">
-      <c r="B65" s="34" t="n"/>
-      <c r="C65" s="47" t="n"/>
-      <c r="D65" s="48" t="n"/>
-      <c r="E65" s="49" t="n"/>
-      <c r="F65" s="50" t="n"/>
-      <c r="G65" s="51" t="n"/>
-      <c r="H65" s="52" t="n"/>
-      <c r="I65" s="53" t="n"/>
-      <c r="J65" s="54" t="n"/>
-      <c r="K65" s="55" t="n"/>
-      <c r="L65" s="18" t="n"/>
-      <c r="M65" s="21" t="n"/>
-      <c r="N65" s="56" t="n"/>
-      <c r="O65" s="57" t="n"/>
-      <c r="P65" s="58" t="n"/>
-      <c r="Q65" s="56" t="n"/>
-      <c r="R65" s="56" t="n"/>
-      <c r="S65" s="56" t="n"/>
-      <c r="T65" s="56" t="n"/>
-      <c r="U65" s="56" t="n"/>
-      <c r="V65" s="56" t="n"/>
-      <c r="W65" s="56" t="n"/>
-      <c r="X65" s="56" t="n"/>
-      <c r="Y65" s="56" t="n"/>
-      <c r="Z65" s="56" t="n"/>
-      <c r="AA65" s="56" t="n"/>
-      <c r="AB65" s="56" t="n"/>
+      <c r="B65" s="420" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C65" s="255" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D65" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="49" t="n">
+        <v>4850</v>
+      </c>
+      <c r="F65" s="50">
+        <f>IFERROR(D65+E65+G65+U65+Y65,0)</f>
+        <v>12495.0</v>
+      </c>
+      <c r="G65" s="257" t="n">
+        <v>2385</v>
+      </c>
+      <c r="H65" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B65,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B65+1))</f>
+        <v>1657.0</v>
+      </c>
+      <c r="I65" s="259">
+        <f>IFERROR(F65-H65,0)</f>
+        <v>10838.0</v>
+      </c>
+      <c r="J65" s="260">
+        <f>IFERROR(I65/F65,0)</f>
+        <v>0.867387</v>
+      </c>
+      <c r="K65" s="254" t="n"/>
+      <c r="L65" s="261" t="inlineStr">
+        <is>
+          <t>EOD close (BBVA card + cash + $2,385 bank transfer to restaurant BBVA acct, no commission) | +$3,870 evening wine party (BBVA $1,150 + cash $2,720)</t>
+        </is>
+      </c>
+      <c r="M65" s="291" t="n"/>
+      <c r="N65" s="292" t="n"/>
+      <c r="O65" s="293" t="n"/>
+      <c r="P65" s="294" t="n"/>
+      <c r="Q65" s="292" t="n"/>
+      <c r="R65" s="421">
+        <f>IFERROR(D65*$T$7,0)</f>
+        <v/>
+      </c>
+      <c r="S65" s="292" t="n"/>
+      <c r="T65" s="292" t="n"/>
+      <c r="U65" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" s="292" t="n"/>
+      <c r="X65" s="292" t="n"/>
+      <c r="Y65" s="421" t="n">
+        <v>5260</v>
+      </c>
+      <c r="Z65" s="421" t="n">
+        <v>99.94</v>
+      </c>
+      <c r="AA65" s="292" t="n"/>
+      <c r="AB65" s="292" t="n"/>
     </row>
     <row r="66" ht="16.5" customHeight="1" s="313">
-      <c r="B66" s="34" t="n"/>
-      <c r="C66" s="35" t="n"/>
-      <c r="D66" s="36" t="n"/>
-      <c r="E66" s="37" t="n"/>
-      <c r="F66" s="38" t="n"/>
-      <c r="G66" s="39" t="n"/>
-      <c r="H66" s="40" t="n"/>
-      <c r="I66" s="41" t="n"/>
-      <c r="J66" s="42" t="n"/>
-      <c r="K66" s="43" t="n"/>
-      <c r="L66" s="9" t="n"/>
-      <c r="M66" s="12" t="n"/>
-      <c r="N66" s="44" t="n"/>
-      <c r="O66" s="45" t="n"/>
-      <c r="P66" s="46" t="n"/>
-      <c r="Q66" s="44" t="n"/>
-      <c r="R66" s="44" t="n"/>
-      <c r="S66" s="44" t="n"/>
-      <c r="T66" s="44" t="n"/>
-      <c r="U66" s="44" t="n"/>
-      <c r="V66" s="44" t="n"/>
-      <c r="W66" s="44" t="n"/>
-      <c r="X66" s="44" t="n"/>
-      <c r="Y66" s="44" t="n"/>
-      <c r="Z66" s="44" t="n"/>
-      <c r="AA66" s="44" t="n"/>
-      <c r="AB66" s="44" t="n"/>
+      <c r="B66" s="420" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C66" s="255" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D66" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="49" t="n">
+        <v>785</v>
+      </c>
+      <c r="F66" s="50">
+        <f>IFERROR(D66+E66+G66+U66+Y66,0)</f>
+        <v>2622.0</v>
+      </c>
+      <c r="G66" s="257" t="n">
+        <v>300</v>
+      </c>
+      <c r="H66" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B66,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B66+1))</f>
+        <v>1951.0</v>
+      </c>
+      <c r="I66" s="259">
+        <f>IFERROR(F66-H66,0)</f>
+        <v>671.0</v>
+      </c>
+      <c r="J66" s="260">
+        <f>IFERROR(I66/F66,0)</f>
+        <v>0.255912</v>
+      </c>
+      <c r="K66" s="254" t="n"/>
+      <c r="L66" s="261" t="inlineStr">
+        <is>
+          <t>EOD close (BBVA + cash)</t>
+        </is>
+      </c>
+      <c r="M66" s="291" t="n"/>
+      <c r="N66" s="292" t="n"/>
+      <c r="O66" s="293" t="n"/>
+      <c r="P66" s="294" t="n"/>
+      <c r="Q66" s="292" t="n"/>
+      <c r="R66" s="421">
+        <f>IFERROR(D66*$T$7,0)</f>
+        <v/>
+      </c>
+      <c r="S66" s="292" t="n"/>
+      <c r="T66" s="292" t="n"/>
+      <c r="U66" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" s="292" t="n"/>
+      <c r="X66" s="292" t="n"/>
+      <c r="Y66" s="421" t="n">
+        <v>1537</v>
+      </c>
+      <c r="Z66" s="421" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="AA66" s="292" t="n"/>
+      <c r="AB66" s="292" t="n"/>
     </row>
     <row r="67" ht="16.5" customHeight="1" s="313">
-      <c r="B67" s="34" t="n"/>
-      <c r="C67" s="47" t="n"/>
-      <c r="D67" s="48" t="n"/>
-      <c r="E67" s="49" t="n"/>
-      <c r="F67" s="50" t="n"/>
-      <c r="G67" s="51" t="n"/>
-      <c r="H67" s="52" t="n"/>
-      <c r="I67" s="53" t="n"/>
-      <c r="J67" s="54" t="n"/>
-      <c r="K67" s="55" t="n"/>
-      <c r="L67" s="18" t="n"/>
-      <c r="M67" s="21" t="n"/>
-      <c r="N67" s="56" t="n"/>
-      <c r="O67" s="57" t="n"/>
-      <c r="P67" s="58" t="n"/>
-      <c r="Q67" s="56" t="n"/>
-      <c r="R67" s="56" t="n"/>
-      <c r="S67" s="56" t="n"/>
-      <c r="T67" s="56" t="n"/>
-      <c r="U67" s="56" t="n"/>
-      <c r="V67" s="56" t="n"/>
-      <c r="W67" s="56" t="n"/>
-      <c r="X67" s="56" t="n"/>
-      <c r="Y67" s="56" t="n"/>
-      <c r="Z67" s="56" t="n"/>
-      <c r="AA67" s="56" t="n"/>
-      <c r="AB67" s="56" t="n"/>
+      <c r="B67" s="420" t="n">
+        <v>46221</v>
+      </c>
+      <c r="C67" s="255" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D67" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="49" t="n">
+        <v>745</v>
+      </c>
+      <c r="F67" s="50">
+        <f>IFERROR(D67+E67+G67+U67+Y67,0)</f>
+        <v>2900.0</v>
+      </c>
+      <c r="G67" s="257" t="n">
+        <v>290</v>
+      </c>
+      <c r="H67" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B67,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B67+1))</f>
+        <v>5250.0</v>
+      </c>
+      <c r="I67" s="259">
+        <f>IFERROR(F67-H67,0)</f>
+        <v>-2350.0</v>
+      </c>
+      <c r="J67" s="260">
+        <f>IFERROR(I67/F67,0)</f>
+        <v>-0.810345</v>
+      </c>
+      <c r="K67" s="254" t="n"/>
+      <c r="L67" s="261" t="inlineStr">
+        <is>
+          <t>EOD close (BBVA + cash) - expenses pending, salaries recorded</t>
+        </is>
+      </c>
+      <c r="M67" s="291" t="n"/>
+      <c r="N67" s="292" t="n"/>
+      <c r="O67" s="293" t="n"/>
+      <c r="P67" s="294" t="n"/>
+      <c r="Q67" s="292" t="n"/>
+      <c r="R67" s="421">
+        <f>IFERROR(D67*$T$7,0)</f>
+        <v/>
+      </c>
+      <c r="S67" s="292" t="n"/>
+      <c r="T67" s="292" t="n"/>
+      <c r="U67" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" s="292" t="n"/>
+      <c r="X67" s="292" t="n"/>
+      <c r="Y67" s="421" t="n">
+        <v>1865</v>
+      </c>
+      <c r="Z67" s="421" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="AA67" s="292" t="n"/>
+      <c r="AB67" s="292" t="n"/>
     </row>
     <row r="68" ht="16.5" customHeight="1" s="313">
-      <c r="B68" s="34" t="n"/>
-      <c r="C68" s="35" t="n"/>
-      <c r="D68" s="36" t="n"/>
-      <c r="E68" s="37" t="n"/>
-      <c r="F68" s="38" t="n"/>
-      <c r="G68" s="39" t="n"/>
-      <c r="H68" s="40" t="n"/>
-      <c r="I68" s="41" t="n"/>
-      <c r="J68" s="42" t="n"/>
-      <c r="K68" s="43" t="n"/>
-      <c r="L68" s="9" t="n"/>
-      <c r="M68" s="12" t="n"/>
-      <c r="N68" s="44" t="n"/>
-      <c r="O68" s="45" t="n"/>
-      <c r="P68" s="46" t="n"/>
-      <c r="Q68" s="44" t="n"/>
-      <c r="R68" s="44" t="n"/>
-      <c r="S68" s="44" t="n"/>
-      <c r="T68" s="44" t="n"/>
-      <c r="U68" s="44" t="n"/>
-      <c r="V68" s="44" t="n"/>
-      <c r="W68" s="44" t="n"/>
-      <c r="X68" s="44" t="n"/>
-      <c r="Y68" s="44" t="n"/>
-      <c r="Z68" s="44" t="n"/>
-      <c r="AA68" s="44" t="n"/>
-      <c r="AB68" s="44" t="n"/>
+      <c r="B68" s="420" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C68" s="255" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D68" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="49" t="n">
+        <v>1390</v>
+      </c>
+      <c r="F68" s="50">
+        <f>IFERROR(D68+E68+G68+U68+Y68,0)</f>
+        <v>4955.0</v>
+      </c>
+      <c r="G68" s="257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B68,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B68+1))</f>
+        <v>2459.0</v>
+      </c>
+      <c r="I68" s="259">
+        <f>IFERROR(F68-H68,0)</f>
+        <v>2496.0</v>
+      </c>
+      <c r="J68" s="260">
+        <f>IFERROR(I68/F68,0)</f>
+        <v>0.503734</v>
+      </c>
+      <c r="K68" s="254" t="n"/>
+      <c r="L68" s="261" t="inlineStr">
+        <is>
+          <t>EOD close (BBVA + Soft + cash). Note: 19-Jul not recorded (closed). | transfer-to-me corrected to $0</t>
+        </is>
+      </c>
+      <c r="M68" s="291" t="n"/>
+      <c r="N68" s="292" t="n"/>
+      <c r="O68" s="293" t="n"/>
+      <c r="P68" s="294" t="n"/>
+      <c r="Q68" s="292" t="n"/>
+      <c r="R68" s="421">
+        <f>IFERROR(D68*$T$7,0)</f>
+        <v/>
+      </c>
+      <c r="S68" s="292" t="n"/>
+      <c r="T68" s="292" t="n"/>
+      <c r="U68" s="421" t="n">
+        <v>80</v>
+      </c>
+      <c r="V68" s="421" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W68" s="292" t="n"/>
+      <c r="X68" s="292" t="n"/>
+      <c r="Y68" s="421" t="n">
+        <v>3485</v>
+      </c>
+      <c r="Z68" s="421" t="n">
+        <v>66.22</v>
+      </c>
+      <c r="AA68" s="292" t="n"/>
+      <c r="AB68" s="292" t="n"/>
     </row>
     <row r="69" ht="16.5" customHeight="1" s="313">
       <c r="B69" s="34" t="n"/>
@@ -21242,9 +21862,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -21267,7 +21887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J483"/>
+  <dimension ref="A1:J509"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="313" min="1" max="1"/>
@@ -41539,6 +42159,1124 @@
       <c r="J483" s="418" t="inlineStr">
         <is>
           <t>No receipt; cash; monthly internet/phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="B484" s="422" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C484" s="305" t="inlineStr">
+        <is>
+          <t>Vasos plastico + Reyma tapas (desechables)</t>
+        </is>
+      </c>
+      <c r="D484" s="306" t="inlineStr">
+        <is>
+          <t>Guimar Polietilenos</t>
+        </is>
+      </c>
+      <c r="E484" s="305" t="inlineStr">
+        <is>
+          <t>Packaging/Disposables</t>
+        </is>
+      </c>
+      <c r="F484" s="307" t="n">
+        <v>106</v>
+      </c>
+      <c r="G484" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H484" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I484" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J484" s="418" t="inlineStr">
+        <is>
+          <t>Folio XCC39648; disposables</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="B485" s="422" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C485" s="305" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="D485" s="306" t="inlineStr">
+        <is>
+          <t>Molino y Condimentos La Cruz</t>
+        </is>
+      </c>
+      <c r="E485" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F485" s="307" t="n">
+        <v>110</v>
+      </c>
+      <c r="G485" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H485" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I485" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J485" s="418" t="inlineStr">
+        <is>
+          <t>Molino La Cruz; jamaica (agua fresca)</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="B486" s="422" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C486" s="305" t="inlineStr">
+        <is>
+          <t>Queso</t>
+        </is>
+      </c>
+      <c r="D486" s="306" t="inlineStr">
+        <is>
+          <t>La Bodega del Buen Queso</t>
+        </is>
+      </c>
+      <c r="E486" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Dairy</t>
+        </is>
+      </c>
+      <c r="F486" s="307" t="n">
+        <v>409</v>
+      </c>
+      <c r="G486" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H486" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I486" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J486" s="418" t="inlineStr">
+        <is>
+          <t>Nota de venta 16-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="B487" s="422" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C487" s="305" t="inlineStr">
+        <is>
+          <t>Fideo La Moderna x3</t>
+        </is>
+      </c>
+      <c r="D487" s="306" t="inlineStr">
+        <is>
+          <t>Tres B</t>
+        </is>
+      </c>
+      <c r="E487" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F487" s="307" t="n">
+        <v>51</v>
+      </c>
+      <c r="G487" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H487" s="308" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I487" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J487" s="418" t="inlineStr">
+        <is>
+          <t>3x $17; Mercado Libre contactless</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="B488" s="422" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C488" s="305" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D488" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E488" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F488" s="307" t="n">
+        <v>263</v>
+      </c>
+      <c r="G488" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H488" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I488" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J488" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="B489" s="422" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C489" s="305" t="inlineStr">
+        <is>
+          <t>Wine glasses</t>
+        </is>
+      </c>
+      <c r="D489" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E489" s="305" t="inlineStr">
+        <is>
+          <t>Kitchen Supplies</t>
+        </is>
+      </c>
+      <c r="F489" s="307" t="n">
+        <v>150</v>
+      </c>
+      <c r="G489" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H489" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I489" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J489" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash; glassware</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="B490" s="422" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C490" s="305" t="inlineStr">
+        <is>
+          <t>Salvo (lavatrastes)</t>
+        </is>
+      </c>
+      <c r="D490" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E490" s="305" t="inlineStr">
+        <is>
+          <t>Kitchen Supplies</t>
+        </is>
+      </c>
+      <c r="F490" s="307" t="n">
+        <v>28</v>
+      </c>
+      <c r="G490" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H490" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I490" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J490" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash; dish soap</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="B491" s="422" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C491" s="305" t="inlineStr">
+        <is>
+          <t>Topo Chico (Oxxo)</t>
+        </is>
+      </c>
+      <c r="D491" s="306" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E491" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F491" s="307" t="n">
+        <v>40</v>
+      </c>
+      <c r="G491" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H491" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I491" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J491" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="B492" s="422" t="n">
+        <v>46214</v>
+      </c>
+      <c r="C492" s="305" t="inlineStr">
+        <is>
+          <t>Pan y salsas</t>
+        </is>
+      </c>
+      <c r="D492" s="306" t="inlineStr">
+        <is>
+          <t>Pan Reales</t>
+        </is>
+      </c>
+      <c r="E492" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F492" s="307" t="n">
+        <v>867</v>
+      </c>
+      <c r="G492" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H492" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I492" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J492" s="418" t="inlineStr">
+        <is>
+          <t>Pan + salsas; gasto de 11-Jul agregado despues (missed en el EOD original)</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="B493" s="422" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C493" s="305" t="inlineStr">
+        <is>
+          <t>John (Head Chef) — pago por quedarse tarde (wine party)</t>
+        </is>
+      </c>
+      <c r="D493" s="306" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E493" s="305" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F493" s="307" t="n">
+        <v>500</v>
+      </c>
+      <c r="G493" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H493" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I493" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J493" s="418" t="inlineStr">
+        <is>
+          <t>Pago extra al chef por trabajar tarde en el evento de vino (16-Jul). Sueldo/bono, no propina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="B494" s="422" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C494" s="305" t="inlineStr">
+        <is>
+          <t>Arroz (Oxxo)</t>
+        </is>
+      </c>
+      <c r="D494" s="306" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E494" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F494" s="307" t="n">
+        <v>52</v>
+      </c>
+      <c r="G494" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H494" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I494" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J494" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="B495" s="422" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C495" s="305" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D495" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E495" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F495" s="307" t="n">
+        <v>300</v>
+      </c>
+      <c r="G495" s="308" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H495" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I495" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J495" s="418" t="inlineStr">
+        <is>
+          <t>Pollo pagado personalmente por Lohith (17-Jul); gasto operativo real, reembolsable via Owner Ledger. No salio de la caja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="B496" s="422" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C496" s="305" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D496" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E496" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F496" s="307" t="n">
+        <v>51</v>
+      </c>
+      <c r="G496" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H496" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I496" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J496" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="B497" s="422" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C497" s="305" t="inlineStr">
+        <is>
+          <t>Lechuga</t>
+        </is>
+      </c>
+      <c r="D497" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E497" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F497" s="307" t="n">
+        <v>88</v>
+      </c>
+      <c r="G497" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H497" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I497" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J497" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="B498" s="422" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C498" s="305" t="inlineStr">
+        <is>
+          <t>Bistec</t>
+        </is>
+      </c>
+      <c r="D498" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E498" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F498" s="307" t="n">
+        <v>96</v>
+      </c>
+      <c r="G498" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H498" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I498" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J498" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="B499" s="422" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C499" s="305" t="inlineStr">
+        <is>
+          <t>Chedraui (varios)</t>
+        </is>
+      </c>
+      <c r="D499" s="306" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E499" s="305" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F499" s="307" t="n">
+        <v>164</v>
+      </c>
+      <c r="G499" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H499" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I499" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J499" s="418" t="inlineStr">
+        <is>
+          <t>No receipt provided; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="B500" s="422" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C500" s="305" t="inlineStr">
+        <is>
+          <t>Samu — Ayudante Week 9</t>
+        </is>
+      </c>
+      <c r="D500" s="306" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E500" s="305" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F500" s="307" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G500" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H500" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I500" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J500" s="418" t="inlineStr">
+        <is>
+          <t>Week 9 salary, paid Friday 17 Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="B501" s="422" t="n">
+        <v>46221</v>
+      </c>
+      <c r="C501" s="305" t="inlineStr">
+        <is>
+          <t>John — Head Chef Week 9</t>
+        </is>
+      </c>
+      <c r="D501" s="306" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E501" s="305" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F501" s="307" t="n">
+        <v>3750</v>
+      </c>
+      <c r="G501" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H501" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I501" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J501" s="418" t="inlineStr">
+        <is>
+          <t>Week 9 salary, paid Saturday 18 Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="B502" s="422" t="n">
+        <v>46221</v>
+      </c>
+      <c r="C502" s="305" t="inlineStr">
+        <is>
+          <t>Duvi/Debi — Limpieza Week 9</t>
+        </is>
+      </c>
+      <c r="D502" s="306" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E502" s="305" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F502" s="307" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G502" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H502" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I502" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J502" s="418" t="inlineStr">
+        <is>
+          <t>Week 9 salary, paid Saturday 18 Jul (full week)</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="B503" s="422" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C503" s="305" t="inlineStr">
+        <is>
+          <t>Milk (Oxxo)</t>
+        </is>
+      </c>
+      <c r="D503" s="306" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E503" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Dairy</t>
+        </is>
+      </c>
+      <c r="F503" s="307" t="n">
+        <v>36</v>
+      </c>
+      <c r="G503" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H503" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I503" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J503" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="B504" s="422" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C504" s="305" t="inlineStr">
+        <is>
+          <t>Bistec</t>
+        </is>
+      </c>
+      <c r="D504" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E504" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F504" s="307" t="n">
+        <v>290</v>
+      </c>
+      <c r="G504" s="308" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H504" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I504" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J504" s="418" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger; no de la caja</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="B505" s="422" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C505" s="305" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D505" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E505" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F505" s="307" t="n">
+        <v>89</v>
+      </c>
+      <c r="G505" s="308" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H505" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I505" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J505" s="418" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger; no de la caja</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="B506" s="422" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C506" s="305" t="inlineStr">
+        <is>
+          <t>Agua natural</t>
+        </is>
+      </c>
+      <c r="D506" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E506" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F506" s="307" t="n">
+        <v>30</v>
+      </c>
+      <c r="G506" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H506" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I506" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J506" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="B507" s="422" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C507" s="305" t="inlineStr">
+        <is>
+          <t>Hielo (Oxxo)</t>
+        </is>
+      </c>
+      <c r="D507" s="306" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E507" s="305" t="inlineStr">
+        <is>
+          <t>Kitchen Supplies</t>
+        </is>
+      </c>
+      <c r="F507" s="307" t="n">
+        <v>54</v>
+      </c>
+      <c r="G507" s="308" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H507" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I507" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J507" s="418" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger; no de la caja</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="B508" s="422" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C508" s="305" t="inlineStr">
+        <is>
+          <t>Hielos (mercado)</t>
+        </is>
+      </c>
+      <c r="D508" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E508" s="305" t="inlineStr">
+        <is>
+          <t>Kitchen Supplies</t>
+        </is>
+      </c>
+      <c r="F508" s="307" t="n">
+        <v>200</v>
+      </c>
+      <c r="G508" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H508" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I508" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J508" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="B509" s="422" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C509" s="305" t="inlineStr">
+        <is>
+          <t>Sam's Club (varios)</t>
+        </is>
+      </c>
+      <c r="D509" s="306" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="E509" s="305" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F509" s="307" t="n">
+        <v>1760</v>
+      </c>
+      <c r="G509" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H509" s="308" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I509" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J509" s="418" t="inlineStr">
+        <is>
+          <t>No receipt provided; restaurant-paid</t>
         </is>
       </c>
     </row>
@@ -51180,14 +52918,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="313">
-      <c r="A1" s="407" t="inlineStr">
+      <c r="A1" s="417" t="inlineStr">
         <is>
           <t>LOKA — MONTHLY P&amp;L   (live formulas — auto-updates from Daily Log &amp; Expenses)</t>
         </is>
       </c>
-      <c r="B1" s="408" t="n"/>
-      <c r="C1" s="408" t="n"/>
-      <c r="D1" s="408" t="n"/>
+      <c r="B1" s="418" t="n"/>
+      <c r="C1" s="418" t="n"/>
+      <c r="D1" s="418" t="n"/>
       <c r="E1" s="409" t="n"/>
       <c r="F1" s="409" t="n"/>
       <c r="G1" s="409" t="n"/>
@@ -51710,7 +53448,7 @@
     <row r="22">
       <c r="A22" s="415" t="inlineStr">
         <is>
-          <t>Ingredients - Beverages</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="B22" s="413">
@@ -51737,7 +53475,7 @@
     <row r="23">
       <c r="A23" s="415" t="inlineStr">
         <is>
-          <t>Ingredients - Dairy</t>
+          <t>Ingredients - Beverages</t>
         </is>
       </c>
       <c r="B23" s="413">
@@ -51764,7 +53502,7 @@
     <row r="24">
       <c r="A24" s="415" t="inlineStr">
         <is>
-          <t>Supermarket/General</t>
+          <t>Ingredients - Dairy</t>
         </is>
       </c>
       <c r="B24" s="413">
@@ -52034,7 +53772,7 @@
     <row r="34">
       <c r="A34" s="415" t="inlineStr">
         <is>
-          <t>Software / Subscription</t>
+          <t>Kitchen Supplies</t>
         </is>
       </c>
       <c r="B34" s="413">
@@ -52061,7 +53799,7 @@
     <row r="35">
       <c r="A35" s="415" t="inlineStr">
         <is>
-          <t>Kitchen Supplies</t>
+          <t>Software / Subscription</t>
         </is>
       </c>
       <c r="B35" s="413">
@@ -52223,7 +53961,7 @@
     <row r="41">
       <c r="A41" s="415" t="inlineStr">
         <is>
-          <t>Ingredients - Eggs</t>
+          <t>Packaging/Disposables</t>
         </is>
       </c>
       <c r="B41" s="413">
@@ -52250,7 +53988,7 @@
     <row r="42">
       <c r="A42" s="415" t="inlineStr">
         <is>
-          <t>Packaging/Disposables</t>
+          <t>Ingredients - Eggs</t>
         </is>
       </c>
       <c r="B42" s="413">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="C143" s="283">
-        <f>SUM('📅 Daily Log'!D8:D500)+SUM('📅 Daily Log'!E8:E500)+SUM('📅 Daily Log'!G8:G500)</f>
+        <f>SUM('📅 Daily Log'!D8:D5000)+SUM('📅 Daily Log'!E8:E5000)+SUM('📅 Daily Log'!G8:G5000)</f>
         <v/>
       </c>
       <c r="D143" s="191" t="n"/>
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="C144" s="283">
-        <f>SUM('💸 Expenses'!F8:F500)</f>
+        <f>SUM('💸 Expenses'!F8:F50000)</f>
         <v/>
       </c>
       <c r="D144" s="191" t="n"/>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="C145" s="268">
-        <f>SUM('📅 Daily Log'!R8:R500)</f>
+        <f>SUM('📅 Daily Log'!R8:R5000)</f>
         <v/>
       </c>
     </row>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="C17" s="333" t="n"/>
       <c r="D17" s="363">
-        <f>IFERROR(SUMPRODUCT((ISNUMBER('📅 Daily Log'!$B$8:$B$500))*('📅 Daily Log'!$B$8:$B$500&gt;=TODAY()-MOD(TODAY()-2,7))*('📅 Daily Log'!$B$8:$B$500&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER('📅 Daily Log'!$G$8:$G$500),'📅 Daily Log'!$G$8:$G$500,0)),0)</f>
+        <f>IFERROR(SUMPRODUCT((ISNUMBER('📅 Daily Log'!$B$8:$B$5000))*('📅 Daily Log'!$B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*('📅 Daily Log'!$B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER('📅 Daily Log'!$G$8:$G$5000),'📅 Daily Log'!$G$8:$G$5000,0)),0)</f>
         <v/>
       </c>
       <c r="E17" s="333" t="n"/>
@@ -9172,15 +9172,15 @@
       <c r="D6" s="28" t="n"/>
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
-        <f>SUMIFS($D$8:$D$500,$B$8:$B$500,TODAY())+SUMIFS($E$8:$E$500,$B$8:$B$500,TODAY())+SUMIFS($G$8:$G$500,$B$8:$B$500,TODAY())</f>
+        <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
         <v/>
       </c>
       <c r="G6" s="31">
-        <f>SUMIFS($G$8:$G$500,$B$8:$B$500,TODAY())</f>
+        <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
         <v/>
       </c>
       <c r="H6" s="28">
-        <f>SUMIFS($H$8:$H$500,$B$8:$B$500,TODAY())</f>
+        <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
         <v/>
       </c>
       <c r="I6" s="32">
@@ -9194,19 +9194,19 @@
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
-        <f>SUMPRODUCT((ISNUMBER($B$8:$B$500))*($B$8:$B$500&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$500&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$500),$F$8:$F$500,0))</f>
+        <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
         <v/>
       </c>
       <c r="N6" s="33">
-        <f>SUMPRODUCT((ISNUMBER($B$8:$B$500))*($B$8:$B$500&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$500&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$500),$F$8:$F$500,0))</f>
+        <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
         <v/>
       </c>
       <c r="O6" s="33">
-        <f>SUMPRODUCT((ISNUMBER($B$8:$B$500))*(MONTH($B$8:$B$500)=MONTH(TODAY()))*(YEAR($B$8:$B$500)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$500),$F$8:$F$500,0))</f>
+        <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
         <v/>
       </c>
       <c r="P6">
-        <f>SUMPRODUCT((ISNUMBER($B$8:$B$500))*($B$8:$B$500&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$500&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$500),$H$8:$H$500,0))</f>
+        <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
         <v/>
       </c>
       <c r="Q6">
@@ -9362,20 +9362,20 @@
       </c>
       <c r="F8" s="38">
         <f>IFERROR(D8+E8+G8,0)</f>
-        <v>3689.0</v>
+        <v/>
       </c>
       <c r="G8" s="39" t="n"/>
       <c r="H8" s="40">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B8,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B8+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B8,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B8+1))</f>
         <v/>
       </c>
       <c r="I8" s="41">
         <f>IFERROR(F8-H8,0)</f>
-        <v>1060.0</v>
+        <v/>
       </c>
       <c r="J8" s="42">
         <f>IFERROR(I8/F8,0)</f>
-        <v>0.287341</v>
+        <v/>
       </c>
       <c r="K8" s="43" t="n"/>
       <c r="L8" s="9" t="inlineStr">
@@ -9420,20 +9420,20 @@
       </c>
       <c r="F9" s="50">
         <f>IFERROR(D9+E9+G9,0)</f>
-        <v>3854.0</v>
+        <v/>
       </c>
       <c r="G9" s="51" t="n"/>
       <c r="H9" s="52">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B9,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B9+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B9,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B9+1))</f>
         <v/>
       </c>
       <c r="I9" s="53">
         <f>IFERROR(F9-H9,0)</f>
-        <v>3824.0</v>
+        <v/>
       </c>
       <c r="J9" s="54">
         <f>IFERROR(I9/F9,0)</f>
-        <v>0.992216</v>
+        <v/>
       </c>
       <c r="K9" s="55" t="n"/>
       <c r="L9" s="18" t="inlineStr">
@@ -9478,20 +9478,20 @@
       </c>
       <c r="F10" s="38">
         <f>IFERROR(D10+E10+G10,0)</f>
-        <v>4124.0</v>
+        <v/>
       </c>
       <c r="G10" s="39" t="n"/>
       <c r="H10" s="40">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B10,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B10+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B10,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B10+1))</f>
         <v/>
       </c>
       <c r="I10" s="41">
         <f>IFERROR(F10-H10,0)</f>
-        <v>347.0</v>
+        <v/>
       </c>
       <c r="J10" s="42">
         <f>IFERROR(I10/F10,0)</f>
-        <v>0.084142</v>
+        <v/>
       </c>
       <c r="K10" s="43" t="n"/>
       <c r="L10" s="9" t="inlineStr">
@@ -9536,20 +9536,20 @@
       </c>
       <c r="F11" s="50">
         <f>IFERROR(D11+E11+G11,0)</f>
-        <v>4733.0</v>
+        <v/>
       </c>
       <c r="G11" s="51" t="n"/>
       <c r="H11" s="52">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B11,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B11+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B11,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B11+1))</f>
         <v/>
       </c>
       <c r="I11" s="53">
         <f>IFERROR(F11-H11,0)</f>
-        <v>2299.0</v>
+        <v/>
       </c>
       <c r="J11" s="54">
         <f>IFERROR(I11/F11,0)</f>
-        <v>0.485738</v>
+        <v/>
       </c>
       <c r="K11" s="55" t="n"/>
       <c r="L11" s="18" t="inlineStr">
@@ -9594,20 +9594,20 @@
       </c>
       <c r="F12" s="38">
         <f>IFERROR(D12+E12+G12,0)</f>
-        <v>4282.0</v>
+        <v/>
       </c>
       <c r="G12" s="39" t="n"/>
       <c r="H12" s="40">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B12,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B12+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B12,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B12+1))</f>
         <v/>
       </c>
       <c r="I12" s="41">
         <f>IFERROR(F12-H12,0)</f>
-        <v>2825.0</v>
+        <v/>
       </c>
       <c r="J12" s="42">
         <f>IFERROR(I12/F12,0)</f>
-        <v>0.659738</v>
+        <v/>
       </c>
       <c r="K12" s="43" t="n"/>
       <c r="L12" s="9" t="inlineStr">
@@ -9652,20 +9652,20 @@
       </c>
       <c r="F13" s="50">
         <f>IFERROR(D13+E13+G13,0)</f>
-        <v>3802.0</v>
+        <v/>
       </c>
       <c r="G13" s="51" t="n"/>
       <c r="H13" s="52">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B13,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B13+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B13,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B13+1))</f>
         <v/>
       </c>
       <c r="I13" s="53">
         <f>IFERROR(F13-H13,0)</f>
-        <v>-3953.43</v>
+        <v/>
       </c>
       <c r="J13" s="54">
         <f>IFERROR(I13/F13,0)</f>
-        <v>-1.039829</v>
+        <v/>
       </c>
       <c r="K13" s="55" t="inlineStr">
         <is>
@@ -9712,20 +9712,20 @@
       </c>
       <c r="F14" s="38">
         <f>IFERROR(D14+E14+G14,0)</f>
-        <v>1198.0</v>
+        <v/>
       </c>
       <c r="G14" s="39" t="n"/>
       <c r="H14" s="40">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B14,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B14+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B14,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B14+1))</f>
         <v/>
       </c>
       <c r="I14" s="41">
         <f>IFERROR(F14-H14,0)</f>
-        <v>122.0</v>
+        <v/>
       </c>
       <c r="J14" s="42">
         <f>IFERROR(I14/F14,0)</f>
-        <v>0.101836</v>
+        <v/>
       </c>
       <c r="K14" s="43" t="inlineStr">
         <is>
@@ -9774,20 +9774,20 @@
       </c>
       <c r="F15" s="50">
         <f>IFERROR(D15+E15+G15,0)</f>
-        <v>3730.0</v>
+        <v/>
       </c>
       <c r="G15" s="51" t="n"/>
       <c r="H15" s="52">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B15,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B15+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B15,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B15+1))</f>
         <v/>
       </c>
       <c r="I15" s="53">
         <f>IFERROR(F15-H15,0)</f>
-        <v>708.55</v>
+        <v/>
       </c>
       <c r="J15" s="54">
         <f>IFERROR(I15/F15,0)</f>
-        <v>0.18996</v>
+        <v/>
       </c>
       <c r="K15" s="55" t="n"/>
       <c r="L15" s="18" t="inlineStr">
@@ -9832,20 +9832,20 @@
       </c>
       <c r="F16" s="38">
         <f>IFERROR(D16+E16+G16,0)</f>
-        <v>4264.0</v>
+        <v/>
       </c>
       <c r="G16" s="39" t="n"/>
       <c r="H16" s="40">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B16,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B16+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B16,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B16+1))</f>
         <v/>
       </c>
       <c r="I16" s="41">
         <f>IFERROR(F16-H16,0)</f>
-        <v>3072.4</v>
+        <v/>
       </c>
       <c r="J16" s="42">
         <f>IFERROR(I16/F16,0)</f>
-        <v>0.720544</v>
+        <v/>
       </c>
       <c r="K16" s="43" t="n"/>
       <c r="L16" s="9" t="inlineStr">
@@ -9890,20 +9890,20 @@
       </c>
       <c r="F17" s="50">
         <f>IFERROR(D17+E17+G17,0)</f>
-        <v>3621.0</v>
+        <v/>
       </c>
       <c r="G17" s="51" t="n"/>
       <c r="H17" s="52">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B17,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B17+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B17,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B17+1))</f>
         <v/>
       </c>
       <c r="I17" s="53">
         <f>IFERROR(F17-H17,0)</f>
-        <v>2547.78</v>
+        <v/>
       </c>
       <c r="J17" s="54">
         <f>IFERROR(I17/F17,0)</f>
-        <v>0.703612</v>
+        <v/>
       </c>
       <c r="K17" s="55" t="n"/>
       <c r="L17" s="18" t="inlineStr">
@@ -9948,20 +9948,20 @@
       </c>
       <c r="F18" s="38">
         <f>IFERROR(D18+E18+G18,0)</f>
-        <v>4070.0</v>
+        <v/>
       </c>
       <c r="G18" s="39" t="n"/>
       <c r="H18" s="40">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B18,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B18+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B18,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B18+1))</f>
         <v/>
       </c>
       <c r="I18" s="41">
         <f>IFERROR(F18-H18,0)</f>
-        <v>2138.66</v>
+        <v/>
       </c>
       <c r="J18" s="42">
         <f>IFERROR(I18/F18,0)</f>
-        <v>0.525469</v>
+        <v/>
       </c>
       <c r="K18" s="43" t="n"/>
       <c r="L18" s="9" t="inlineStr">
@@ -10006,20 +10006,20 @@
       </c>
       <c r="F19" s="50">
         <f>IFERROR(D19+E19+G19,0)</f>
-        <v>6086.0</v>
+        <v/>
       </c>
       <c r="G19" s="51" t="n"/>
       <c r="H19" s="52">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B19,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B19+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B19,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B19+1))</f>
         <v/>
       </c>
       <c r="I19" s="53">
         <f>IFERROR(F19-H19,0)</f>
-        <v>5828.71</v>
+        <v/>
       </c>
       <c r="J19" s="54">
         <f>IFERROR(I19/F19,0)</f>
-        <v>0.957724</v>
+        <v/>
       </c>
       <c r="K19" s="55" t="n"/>
       <c r="L19" s="18" t="inlineStr">
@@ -10064,20 +10064,20 @@
       </c>
       <c r="F20" s="38">
         <f>IFERROR(D20+E20+G20,0)</f>
-        <v>4603.0</v>
+        <v/>
       </c>
       <c r="G20" s="39" t="n"/>
       <c r="H20" s="40">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B20,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B20+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B20,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B20+1))</f>
         <v/>
       </c>
       <c r="I20" s="41">
         <f>IFERROR(F20-H20,0)</f>
-        <v>-1371.3</v>
+        <v/>
       </c>
       <c r="J20" s="42">
         <f>IFERROR(I20/F20,0)</f>
-        <v>-0.297914</v>
+        <v/>
       </c>
       <c r="K20" s="43" t="n"/>
       <c r="L20" s="9" t="inlineStr">
@@ -10120,20 +10120,20 @@
       </c>
       <c r="F21" s="50">
         <f>IFERROR(D21+E21+G21,0)</f>
-        <v>893.0</v>
+        <v/>
       </c>
       <c r="G21" s="51" t="n"/>
       <c r="H21" s="52">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B21,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B21+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B21,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B21+1))</f>
         <v/>
       </c>
       <c r="I21" s="53">
         <f>IFERROR(F21-H21,0)</f>
-        <v>-9419.0</v>
+        <v/>
       </c>
       <c r="J21" s="54">
         <f>IFERROR(I21/F21,0)</f>
-        <v>-10.547592</v>
+        <v/>
       </c>
       <c r="K21" s="55" t="n"/>
       <c r="L21" s="18" t="inlineStr">
@@ -10178,22 +10178,22 @@
       </c>
       <c r="F22" s="38">
         <f>IFERROR(D22+E22+G22,0)</f>
-        <v>5019.0</v>
+        <v/>
       </c>
       <c r="G22" s="39" t="n">
         <v>310</v>
       </c>
       <c r="H22" s="40">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B22,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B22+1))</f>
-        <v>5329.64</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B22,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B22+1))</f>
+        <v/>
       </c>
       <c r="I22" s="41">
         <f>IFERROR(F22-H22,0)</f>
-        <v>-310.64</v>
+        <v/>
       </c>
       <c r="J22" s="42">
         <f>IFERROR(I22/F22,0)</f>
-        <v>-0.061893</v>
+        <v/>
       </c>
       <c r="K22" s="43" t="n"/>
       <c r="L22" s="9" t="inlineStr">
@@ -10238,22 +10238,22 @@
       </c>
       <c r="F23" s="50">
         <f>IFERROR(D23+E23+G23,0)</f>
-        <v>1843.0</v>
+        <v/>
       </c>
       <c r="G23" s="51" t="n">
         <v>283</v>
       </c>
       <c r="H23" s="52">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B23,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B23+1))</f>
-        <v>2379.11</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B23,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B23+1))</f>
+        <v/>
       </c>
       <c r="I23" s="53">
         <f>IFERROR(F23-H23,0)</f>
-        <v>-536.11</v>
+        <v/>
       </c>
       <c r="J23" s="54">
         <f>IFERROR(I23/F23,0)</f>
-        <v>-0.29089</v>
+        <v/>
       </c>
       <c r="K23" s="55" t="n"/>
       <c r="L23" s="18" t="inlineStr">
@@ -10298,22 +10298,22 @@
       </c>
       <c r="F24" s="38">
         <f>IFERROR(D24+E24+G24,0)</f>
-        <v>3912.0</v>
+        <v/>
       </c>
       <c r="G24" s="39" t="n">
         <v>120</v>
       </c>
       <c r="H24" s="40">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B24,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B24+1))</f>
-        <v>4211.86</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B24,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B24+1))</f>
+        <v/>
       </c>
       <c r="I24" s="41">
         <f>IFERROR(F24-H24,0)</f>
-        <v>-299.86</v>
+        <v/>
       </c>
       <c r="J24" s="42">
         <f>IFERROR(I24/F24,0)</f>
-        <v>-0.076651</v>
+        <v/>
       </c>
       <c r="K24" s="43" t="n"/>
       <c r="L24" s="9" t="inlineStr">
@@ -10358,20 +10358,20 @@
       </c>
       <c r="F25" s="50">
         <f>IFERROR(D25+E25+G25,0)</f>
-        <v>3757.0</v>
+        <v/>
       </c>
       <c r="G25" s="51" t="n"/>
       <c r="H25" s="52">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B25,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B25+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B25,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B25+1))</f>
         <v/>
       </c>
       <c r="I25" s="53">
         <f>IFERROR(F25-H25,0)</f>
-        <v>-17202.96</v>
+        <v/>
       </c>
       <c r="J25" s="54">
         <f>IFERROR(I25/F25,0)</f>
-        <v>-4.578909</v>
+        <v/>
       </c>
       <c r="K25" s="55" t="n"/>
       <c r="L25" s="18" t="inlineStr">
@@ -10416,22 +10416,22 @@
       </c>
       <c r="F26" s="38">
         <f>IFERROR(D26+E26+G26,0)</f>
-        <v>4408.0</v>
+        <v/>
       </c>
       <c r="G26" s="39" t="n">
         <v>135</v>
       </c>
       <c r="H26" s="40">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B26,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B26+1))</f>
-        <v>878.06</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B26,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B26+1))</f>
+        <v/>
       </c>
       <c r="I26" s="41">
         <f>IFERROR(F26-H26,0)</f>
-        <v>3529.94</v>
+        <v/>
       </c>
       <c r="J26" s="42">
         <f>IFERROR(I26/F26,0)</f>
-        <v>0.800803</v>
+        <v/>
       </c>
       <c r="K26" s="43" t="n"/>
       <c r="L26" s="9" t="inlineStr">
@@ -10476,20 +10476,20 @@
       </c>
       <c r="F27" s="50">
         <f>IFERROR(D27+E27+G27,0)</f>
-        <v>2334.0</v>
+        <v/>
       </c>
       <c r="G27" s="51" t="n"/>
       <c r="H27" s="52">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B27,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B27+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B27,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B27+1))</f>
         <v/>
       </c>
       <c r="I27" s="53">
         <f>IFERROR(F27-H27,0)</f>
-        <v>-3080.0</v>
+        <v/>
       </c>
       <c r="J27" s="54">
         <f>IFERROR(I27/F27,0)</f>
-        <v>-1.319623</v>
+        <v/>
       </c>
       <c r="K27" s="55" t="n"/>
       <c r="L27" s="18" t="inlineStr">
@@ -10534,12 +10534,12 @@
       </c>
       <c r="G28" s="39" t="n"/>
       <c r="H28" s="40">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B28,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B28+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B28,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B28+1))</f>
         <v/>
       </c>
       <c r="I28" s="41">
         <f>IFERROR(F28-H28,0)</f>
-        <v>-1671.0</v>
+        <v/>
       </c>
       <c r="J28" s="42" t="n"/>
       <c r="K28" s="43" t="n"/>
@@ -10585,22 +10585,22 @@
       </c>
       <c r="F29" s="50">
         <f>IFERROR(D29+E29+G29,0)</f>
-        <v>3727.0</v>
+        <v/>
       </c>
       <c r="G29" s="51" t="n">
         <v>99</v>
       </c>
       <c r="H29" s="52">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B29,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B29+1))</f>
-        <v>3187.11</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B29,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B29+1))</f>
+        <v/>
       </c>
       <c r="I29" s="53">
         <f>IFERROR(F29-H29,0)</f>
-        <v>539.89</v>
+        <v/>
       </c>
       <c r="J29" s="54">
         <f>IFERROR(I29/F29,0)</f>
-        <v>0.144859</v>
+        <v/>
       </c>
       <c r="K29" s="55" t="n"/>
       <c r="L29" s="18" t="inlineStr">
@@ -10645,20 +10645,20 @@
       </c>
       <c r="F30" s="38">
         <f>IFERROR(D30+E30+G30,0)</f>
-        <v>5410.0</v>
+        <v/>
       </c>
       <c r="G30" s="39" t="n"/>
       <c r="H30" s="40">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B30,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B30+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B30,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B30+1))</f>
         <v/>
       </c>
       <c r="I30" s="41">
         <f>IFERROR(F30-H30,0)</f>
-        <v>-1213.98</v>
+        <v/>
       </c>
       <c r="J30" s="42">
         <f>IFERROR(I30/F30,0)</f>
-        <v>-0.224396</v>
+        <v/>
       </c>
       <c r="K30" s="43" t="n"/>
       <c r="L30" s="9" t="inlineStr">
@@ -10703,20 +10703,20 @@
       </c>
       <c r="F31" s="50">
         <f>IFERROR(D31+E31+G31,0)</f>
-        <v>4265.0</v>
+        <v/>
       </c>
       <c r="G31" s="51" t="n"/>
       <c r="H31" s="52">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B31,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B31+1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B31,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B31+1))</f>
         <v/>
       </c>
       <c r="I31" s="53">
         <f>IFERROR(F31-H31,0)</f>
-        <v>2923.19</v>
+        <v/>
       </c>
       <c r="J31" s="54">
         <f>IFERROR(I31/F31,0)</f>
-        <v>0.68539</v>
+        <v/>
       </c>
       <c r="K31" s="55" t="n"/>
       <c r="L31" s="18" t="inlineStr">
@@ -10761,22 +10761,22 @@
       </c>
       <c r="F32" s="38">
         <f>IFERROR(D32+E32+G32,0)</f>
-        <v>4166.0</v>
+        <v/>
       </c>
       <c r="G32" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="40">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B32,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B32+1))</f>
-        <v>4044.0</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B32,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B32+1))</f>
+        <v/>
       </c>
       <c r="I32" s="41">
         <f>IFERROR(F32-H32,0)</f>
-        <v>122.0</v>
+        <v/>
       </c>
       <c r="J32" s="42">
         <f>IFERROR(I32/F32,0)</f>
-        <v>0.029285</v>
+        <v/>
       </c>
       <c r="K32" s="43" t="n"/>
       <c r="L32" s="9" t="inlineStr">
@@ -10821,22 +10821,22 @@
       </c>
       <c r="F33" s="50">
         <f>IFERROR(D33+E33+G33,0)</f>
-        <v>6070.0</v>
+        <v/>
       </c>
       <c r="G33" s="51" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="52">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B33,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B33+1))</f>
-        <v>901.8</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B33,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B33+1))</f>
+        <v/>
       </c>
       <c r="I33" s="53">
         <f>IFERROR(F33-H33,0)</f>
-        <v>5168.2</v>
+        <v/>
       </c>
       <c r="J33" s="54">
         <f>IFERROR(I33/F33,0)</f>
-        <v>0.851433</v>
+        <v/>
       </c>
       <c r="K33" s="55" t="n"/>
       <c r="L33" s="18" t="inlineStr">
@@ -10881,22 +10881,22 @@
       </c>
       <c r="F34" s="38">
         <f>IFERROR(D34+E34+G34,0)</f>
-        <v>1811.0</v>
+        <v/>
       </c>
       <c r="G34" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="40">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B34,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B34+1))</f>
-        <v>8084.16</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B34,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B34+1))</f>
+        <v/>
       </c>
       <c r="I34" s="41">
         <f>IFERROR(F34-H34,0)</f>
-        <v>-6273.16</v>
+        <v/>
       </c>
       <c r="J34" s="42">
         <f>IFERROR(I34/F34,0)</f>
-        <v>-3.46392</v>
+        <v/>
       </c>
       <c r="K34" s="43" t="n"/>
       <c r="L34" s="9" t="inlineStr">
@@ -10941,22 +10941,22 @@
       </c>
       <c r="F35" s="50">
         <f>IFERROR(D35+E35+G35,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="G35" s="51" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="52">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B35,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B35+1))</f>
-        <v>1526.18</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B35,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B35+1))</f>
+        <v/>
       </c>
       <c r="I35" s="53">
         <f>IFERROR(F35-H35,0)</f>
-        <v>-1526.18</v>
+        <v/>
       </c>
       <c r="J35" s="54">
         <f>IFERROR(I35/F35,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K35" s="55" t="n"/>
       <c r="L35" s="18" t="inlineStr">
@@ -11001,22 +11001,22 @@
       </c>
       <c r="F36" s="38">
         <f>IFERROR(D36+E36+G36,0)</f>
-        <v>4423.0</v>
+        <v/>
       </c>
       <c r="G36" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="40">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B36,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B36+1))</f>
-        <v>2858.08</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B36,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B36+1))</f>
+        <v/>
       </c>
       <c r="I36" s="41">
         <f>IFERROR(F36-H36,0)</f>
-        <v>1564.92</v>
+        <v/>
       </c>
       <c r="J36" s="42">
         <f>IFERROR(I36/F36,0)</f>
-        <v>0.353814</v>
+        <v/>
       </c>
       <c r="K36" s="43" t="n"/>
       <c r="L36" s="9" t="inlineStr">
@@ -11061,22 +11061,22 @@
       </c>
       <c r="F37" s="50">
         <f>IFERROR(D37+E37+G37,0)</f>
-        <v>2786.0</v>
+        <v/>
       </c>
       <c r="G37" s="51" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="52">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B37,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B37+1))</f>
-        <v>2541.9</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B37,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B37+1))</f>
+        <v/>
       </c>
       <c r="I37" s="53">
         <f>IFERROR(F37-H37,0)</f>
-        <v>244.1</v>
+        <v/>
       </c>
       <c r="J37" s="54">
         <f>IFERROR(I37/F37,0)</f>
-        <v>0.087617</v>
+        <v/>
       </c>
       <c r="K37" s="55" t="n"/>
       <c r="L37" s="18" t="inlineStr">
@@ -11121,22 +11121,22 @@
       </c>
       <c r="F38" s="38">
         <f>IFERROR(D38+E38+G38,0)</f>
-        <v>4404.0</v>
+        <v/>
       </c>
       <c r="G38" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="40">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B38,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B38+1))</f>
-        <v>2353.0</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B38,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B38+1))</f>
+        <v/>
       </c>
       <c r="I38" s="41">
         <f>IFERROR(F38-H38,0)</f>
-        <v>2051.0</v>
+        <v/>
       </c>
       <c r="J38" s="42">
         <f>IFERROR(I38/F38,0)</f>
-        <v>0.465713</v>
+        <v/>
       </c>
       <c r="K38" s="43" t="n"/>
       <c r="L38" s="9" t="inlineStr">
@@ -11181,22 +11181,22 @@
       </c>
       <c r="F39" s="50">
         <f>IFERROR(D39+E39+G39,0)</f>
-        <v>4165.0</v>
+        <v/>
       </c>
       <c r="G39" s="51" t="n">
         <v>400</v>
       </c>
       <c r="H39" s="52">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B39,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B39+1))</f>
-        <v>2958.83</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B39,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B39+1))</f>
+        <v/>
       </c>
       <c r="I39" s="53">
         <f>IFERROR(F39-H39,0)</f>
-        <v>1206.17</v>
+        <v/>
       </c>
       <c r="J39" s="54">
         <f>IFERROR(I39/F39,0)</f>
-        <v>0.289597</v>
+        <v/>
       </c>
       <c r="K39" s="55" t="n"/>
       <c r="L39" s="18" t="inlineStr">
@@ -11241,22 +11241,22 @@
       </c>
       <c r="F40" s="38">
         <f>IFERROR(D40+E40+G40,0)</f>
-        <v>6804.0</v>
+        <v/>
       </c>
       <c r="G40" s="39" t="n">
         <v>120</v>
       </c>
       <c r="H40" s="40">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B40,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B40+1))</f>
-        <v>1483.0</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B40,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B40+1))</f>
+        <v/>
       </c>
       <c r="I40" s="41">
         <f>IFERROR(F40-H40,0)</f>
-        <v>5321.0</v>
+        <v/>
       </c>
       <c r="J40" s="42">
         <f>IFERROR(I40/F40,0)</f>
-        <v>0.78204</v>
+        <v/>
       </c>
       <c r="K40" s="43" t="n"/>
       <c r="L40" s="9" t="inlineStr">
@@ -11301,22 +11301,22 @@
       </c>
       <c r="F41" s="50">
         <f>IFERROR(D41+E41+G41,0)</f>
-        <v>2251.0</v>
+        <v/>
       </c>
       <c r="G41" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B41,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B41+1))</f>
-        <v>9320.81</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B41,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B41+1))</f>
+        <v/>
       </c>
       <c r="I41" s="259">
         <f>IFERROR(F41-H41,0)</f>
-        <v>-7069.81</v>
+        <v/>
       </c>
       <c r="J41" s="260">
         <f>IFERROR(I41/F41,0)</f>
-        <v>-3.140742</v>
+        <v/>
       </c>
       <c r="K41" s="254" t="n"/>
       <c r="L41" s="261" t="inlineStr">
@@ -11361,22 +11361,22 @@
       </c>
       <c r="F42" s="38">
         <f>IFERROR(D42+E42+G42,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="G42" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="273">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B42,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B42+1))</f>
-        <v>2065.85</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B42,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B42+1))</f>
+        <v/>
       </c>
       <c r="I42" s="274">
         <f>IFERROR(F42-H42,0)</f>
-        <v>-2065.85</v>
+        <v/>
       </c>
       <c r="J42" s="275">
         <f>IFERROR(I42/F42,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K42" s="250" t="n"/>
       <c r="L42" s="276" t="inlineStr">
@@ -11421,22 +11421,22 @@
       </c>
       <c r="F43" s="50">
         <f>IFERROR(D43+E43+G43,0)</f>
-        <v>4259.0</v>
+        <v/>
       </c>
       <c r="G43" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B43,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B43+1))</f>
-        <v>1451.0</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B43,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B43+1))</f>
+        <v/>
       </c>
       <c r="I43" s="259">
         <f>IFERROR(F43-H43,0)</f>
-        <v>2808.0</v>
+        <v/>
       </c>
       <c r="J43" s="260">
         <f>IFERROR(I43/F43,0)</f>
-        <v>0.65931</v>
+        <v/>
       </c>
       <c r="K43" s="254" t="n"/>
       <c r="L43" s="261" t="inlineStr">
@@ -11481,22 +11481,22 @@
       </c>
       <c r="F44" s="38">
         <f>IFERROR(D44+E44+G44,0)</f>
-        <v>2967.0</v>
+        <v/>
       </c>
       <c r="G44" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="273">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B44,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B44+1))</f>
-        <v>757.13</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B44,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B44+1))</f>
+        <v/>
       </c>
       <c r="I44" s="274">
         <f>IFERROR(F44-H44,0)</f>
-        <v>2209.87</v>
+        <v/>
       </c>
       <c r="J44" s="275">
         <f>IFERROR(I44/F44,0)</f>
-        <v>0.744816</v>
+        <v/>
       </c>
       <c r="K44" s="250" t="n"/>
       <c r="L44" s="276" t="inlineStr">
@@ -11541,22 +11541,22 @@
       </c>
       <c r="F45" s="50">
         <f>IFERROR(D45+E45+G45,0)</f>
-        <v>3589.0</v>
+        <v/>
       </c>
       <c r="G45" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B45,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B45+1))</f>
-        <v>3781.35</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B45,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B45+1))</f>
+        <v/>
       </c>
       <c r="I45" s="259">
         <f>IFERROR(F45-H45,0)</f>
-        <v>-192.35</v>
+        <v/>
       </c>
       <c r="J45" s="260">
         <f>IFERROR(I45/F45,0)</f>
-        <v>-0.053594</v>
+        <v/>
       </c>
       <c r="K45" s="254" t="n"/>
       <c r="L45" s="261" t="inlineStr">
@@ -11601,22 +11601,22 @@
       </c>
       <c r="F46" s="38">
         <f>IFERROR(D46+E46+G46,0)</f>
-        <v>3588.0</v>
+        <v/>
       </c>
       <c r="G46" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="273">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B46,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B46+1))</f>
-        <v>1228.0</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B46,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B46+1))</f>
+        <v/>
       </c>
       <c r="I46" s="274">
         <f>IFERROR(F46-H46,0)</f>
-        <v>2360.0</v>
+        <v/>
       </c>
       <c r="J46" s="275">
         <f>IFERROR(I46/F46,0)</f>
-        <v>0.657748</v>
+        <v/>
       </c>
       <c r="K46" s="250" t="n"/>
       <c r="L46" s="276" t="inlineStr">
@@ -11661,22 +11661,22 @@
       </c>
       <c r="F47" s="50">
         <f>IFERROR(D47+E47+G47,0)</f>
-        <v>4477.0</v>
+        <v/>
       </c>
       <c r="G47" s="257" t="n">
         <v>165</v>
       </c>
       <c r="H47" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B47,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B47+1))</f>
-        <v>1945.53</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B47,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B47+1))</f>
+        <v/>
       </c>
       <c r="I47" s="259">
         <f>IFERROR(F47-H47,0)</f>
-        <v>2531.47</v>
+        <v/>
       </c>
       <c r="J47" s="260">
         <f>IFERROR(I47/F47,0)</f>
-        <v>0.565439</v>
+        <v/>
       </c>
       <c r="K47" s="254" t="n"/>
       <c r="L47" s="261" t="inlineStr">
@@ -11721,22 +11721,22 @@
       </c>
       <c r="F48" s="38">
         <f>IFERROR(D48+E48+G48,0)</f>
-        <v>2029.0</v>
+        <v/>
       </c>
       <c r="G48" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="273">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B48,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B48+1))</f>
-        <v>5250.0</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B48,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B48+1))</f>
+        <v/>
       </c>
       <c r="I48" s="274">
         <f>IFERROR(F48-H48,0)</f>
-        <v>-3221.0</v>
+        <v/>
       </c>
       <c r="J48" s="275">
         <f>IFERROR(I48/F48,0)</f>
-        <v>-1.587482</v>
+        <v/>
       </c>
       <c r="K48" s="250" t="n"/>
       <c r="L48" s="276" t="inlineStr">
@@ -11781,22 +11781,22 @@
       </c>
       <c r="F49" s="50">
         <f>IFERROR(D49+E49+G49,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="G49" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B49,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B49+1))</f>
-        <v>3865.06</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B49,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B49+1))</f>
+        <v/>
       </c>
       <c r="I49" s="259">
         <f>IFERROR(F49-H49,0)</f>
-        <v>-3865.06</v>
+        <v/>
       </c>
       <c r="J49" s="260">
         <f>IFERROR(I49/F49,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K49" s="254" t="n"/>
       <c r="L49" s="261" t="inlineStr">
@@ -11841,22 +11841,22 @@
       </c>
       <c r="F50" s="38">
         <f>IFERROR(D50+E50+G50,0)</f>
-        <v>3389.0</v>
+        <v/>
       </c>
       <c r="G50" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="273">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B50,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B50+1))</f>
-        <v>2683.27</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B50,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B50+1))</f>
+        <v/>
       </c>
       <c r="I50" s="274">
         <f>IFERROR(F50-H50,0)</f>
-        <v>705.73</v>
+        <v/>
       </c>
       <c r="J50" s="275">
         <f>IFERROR(I50/F50,0)</f>
-        <v>0.208241</v>
+        <v/>
       </c>
       <c r="K50" s="250" t="n"/>
       <c r="L50" s="276" t="inlineStr">
@@ -11901,22 +11901,22 @@
       </c>
       <c r="F51" s="50">
         <f>IFERROR(D51+E51+G51,0)</f>
-        <v>4133.0</v>
+        <v/>
       </c>
       <c r="G51" s="257" t="n">
         <v>55</v>
       </c>
       <c r="H51" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B51,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B51+1))</f>
-        <v>1581.27</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B51,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B51+1))</f>
+        <v/>
       </c>
       <c r="I51" s="259">
         <f>IFERROR(F51-H51,0)</f>
-        <v>2551.73</v>
+        <v/>
       </c>
       <c r="J51" s="260">
         <f>IFERROR(I51/F51,0)</f>
-        <v>0.617404</v>
+        <v/>
       </c>
       <c r="K51" s="254" t="n"/>
       <c r="L51" s="261" t="inlineStr">
@@ -11961,22 +11961,22 @@
       </c>
       <c r="F52" s="38">
         <f>IFERROR(D52+E52+G52,0)</f>
-        <v>4522.0</v>
+        <v/>
       </c>
       <c r="G52" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="273">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B52,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B52+1))</f>
-        <v>2341.23</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B52,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B52+1))</f>
+        <v/>
       </c>
       <c r="I52" s="274">
         <f>IFERROR(F52-H52,0)</f>
-        <v>2180.77</v>
+        <v/>
       </c>
       <c r="J52" s="275">
         <f>IFERROR(I52/F52,0)</f>
-        <v>0.482258</v>
+        <v/>
       </c>
       <c r="K52" s="250" t="n"/>
       <c r="L52" s="276" t="inlineStr">
@@ -12021,22 +12021,22 @@
       </c>
       <c r="F53" s="50">
         <f>IFERROR(D53+E53+G53,0)</f>
-        <v>3108.0</v>
+        <v/>
       </c>
       <c r="G53" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B53,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B53+1))</f>
-        <v>318.0</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B53,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B53+1))</f>
+        <v/>
       </c>
       <c r="I53" s="259">
         <f>IFERROR(F53-H53,0)</f>
-        <v>2790.0</v>
+        <v/>
       </c>
       <c r="J53" s="260">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.897683</v>
+        <v/>
       </c>
       <c r="K53" s="254" t="inlineStr">
         <is>
@@ -12085,22 +12085,22 @@
       </c>
       <c r="F54" s="38">
         <f>IFERROR(D54+E54+G54,0)</f>
-        <v>6077.0</v>
+        <v/>
       </c>
       <c r="G54" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="273">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B54,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B54+1))</f>
-        <v>2809.6</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B54,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B54+1))</f>
+        <v/>
       </c>
       <c r="I54" s="274">
         <f>IFERROR(F54-H54,0)</f>
-        <v>3267.4</v>
+        <v/>
       </c>
       <c r="J54" s="275">
         <f>IFERROR(I54/F54,0)</f>
-        <v>0.537667</v>
+        <v/>
       </c>
       <c r="K54" s="250" t="inlineStr">
         <is>
@@ -12149,22 +12149,22 @@
       </c>
       <c r="F55" s="50">
         <f>IFERROR(D55+E55+G55,0)</f>
-        <v>2634.0</v>
+        <v/>
       </c>
       <c r="G55" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B55,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B55+1))</f>
-        <v>6877.73</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B55,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B55+1))</f>
+        <v/>
       </c>
       <c r="I55" s="259">
         <f>IFERROR(F55-H55,0)</f>
-        <v>-4243.73</v>
+        <v/>
       </c>
       <c r="J55" s="260">
         <f>IFERROR(I55/F55,0)</f>
-        <v>-1.611135</v>
+        <v/>
       </c>
       <c r="K55" s="254" t="n"/>
       <c r="L55" s="261" t="inlineStr">
@@ -12209,22 +12209,22 @@
       </c>
       <c r="F56" s="38">
         <f>IFERROR(D56+E56+G56,0)</f>
-        <v>3690.0</v>
+        <v/>
       </c>
       <c r="G56" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="273">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B56,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B56+1))</f>
-        <v>4200.0</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B56,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B56+1))</f>
+        <v/>
       </c>
       <c r="I56" s="274">
         <f>IFERROR(F56-H56,0)</f>
-        <v>-510.0</v>
+        <v/>
       </c>
       <c r="J56" s="275">
         <f>IFERROR(I56/F56,0)</f>
-        <v>-0.138211</v>
+        <v/>
       </c>
       <c r="K56" s="250" t="n"/>
       <c r="L56" s="276" t="inlineStr">
@@ -12269,22 +12269,22 @@
       </c>
       <c r="F57" s="50">
         <f>IFERROR(D57+E57+G57,0)</f>
-        <v>3660.0</v>
+        <v/>
       </c>
       <c r="G57" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B57,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B57+1))</f>
-        <v>49.0</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B57,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B57+1))</f>
+        <v/>
       </c>
       <c r="I57" s="259">
         <f>IFERROR(F57-H57,0)</f>
-        <v>3611.0</v>
+        <v/>
       </c>
       <c r="J57" s="260">
         <f>IFERROR(I57/F57,0)</f>
-        <v>0.986612</v>
+        <v/>
       </c>
       <c r="K57" s="254" t="n"/>
       <c r="L57" s="261" t="inlineStr">
@@ -12329,22 +12329,22 @@
       </c>
       <c r="F58" s="50">
         <f>IFERROR(D58+E58+G58+U58,0)</f>
-        <v>3688.0</v>
+        <v/>
       </c>
       <c r="G58" s="257" t="n">
         <v>195</v>
       </c>
       <c r="H58" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B58,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B58+1))</f>
-        <v>1415.43</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B58,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B58+1))</f>
+        <v/>
       </c>
       <c r="I58" s="259">
         <f>IFERROR(F58-H58,0)</f>
-        <v>2272.57</v>
+        <v/>
       </c>
       <c r="J58" s="260">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.616207</v>
+        <v/>
       </c>
       <c r="K58" s="254" t="n"/>
       <c r="L58" s="261" t="inlineStr">
@@ -12393,22 +12393,22 @@
       </c>
       <c r="F59" s="50">
         <f>IFERROR(D59+E59+G59+U59,0)</f>
-        <v>6015.0</v>
+        <v/>
       </c>
       <c r="G59" s="257" t="n">
         <v>120</v>
       </c>
       <c r="H59" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B59,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B59+1))</f>
-        <v>1820.89</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B59,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B59+1))</f>
+        <v/>
       </c>
       <c r="I59" s="259">
         <f>IFERROR(F59-H59,0)</f>
-        <v>4194.11</v>
+        <v/>
       </c>
       <c r="J59" s="260">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.697275</v>
+        <v/>
       </c>
       <c r="K59" s="254" t="n"/>
       <c r="L59" s="261" t="inlineStr">
@@ -12457,22 +12457,22 @@
       </c>
       <c r="F60" s="50">
         <f>IFERROR(D60+E60+G60+U60,0)</f>
-        <v>3500.0</v>
+        <v/>
       </c>
       <c r="G60" s="257" t="n">
         <v>70</v>
       </c>
       <c r="H60" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B60,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B60+1))</f>
-        <v>2094.0</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B60,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B60+1))</f>
+        <v/>
       </c>
       <c r="I60" s="259">
         <f>IFERROR(F60-H60,0)</f>
-        <v>1406.0</v>
+        <v/>
       </c>
       <c r="J60" s="260">
         <f>IFERROR(I60/F60,0)</f>
-        <v>0.401714</v>
+        <v/>
       </c>
       <c r="K60" s="254" t="n"/>
       <c r="L60" s="261" t="inlineStr">
@@ -12521,22 +12521,22 @@
       </c>
       <c r="F61" s="50">
         <f>IFERROR(D61+E61+G61+U61,0)</f>
-        <v>2725.0</v>
+        <v/>
       </c>
       <c r="G61" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B61,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B61+1))</f>
-        <v>10207.0</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B61,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B61+1))</f>
+        <v/>
       </c>
       <c r="I61" s="259">
         <f>IFERROR(F61-H61,0)</f>
-        <v>-7482.0</v>
+        <v/>
       </c>
       <c r="J61" s="260">
         <f>IFERROR(I61/F61,0)</f>
-        <v>-2.745688</v>
+        <v/>
       </c>
       <c r="K61" s="254" t="n"/>
       <c r="L61" s="261" t="inlineStr">
@@ -12585,22 +12585,22 @@
       </c>
       <c r="F62" s="50">
         <f>IFERROR(D62+E62+G62+U62+Y62,0)</f>
-        <v>3990.0</v>
+        <v/>
       </c>
       <c r="G62" s="257" t="n">
         <v>120</v>
       </c>
       <c r="H62" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B62,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B62+1))</f>
-        <v>3142.0</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B62,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B62+1))</f>
+        <v/>
       </c>
       <c r="I62" s="259">
         <f>IFERROR(F62-H62,0)</f>
-        <v>848.0</v>
+        <v/>
       </c>
       <c r="J62" s="260">
         <f>IFERROR(I62/F62,0)</f>
-        <v>0.212531</v>
+        <v/>
       </c>
       <c r="K62" s="254" t="n"/>
       <c r="L62" s="261" t="inlineStr">
@@ -12653,22 +12653,22 @@
       </c>
       <c r="F63" s="50">
         <f>IFERROR(D63+E63+G63+U63+Y63,0)</f>
-        <v>3915.0</v>
+        <v/>
       </c>
       <c r="G63" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B63,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B63+1))</f>
-        <v>596.38</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B63,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B63+1))</f>
+        <v/>
       </c>
       <c r="I63" s="259">
         <f>IFERROR(F63-H63,0)</f>
-        <v>3318.62</v>
+        <v/>
       </c>
       <c r="J63" s="260">
         <f>IFERROR(I63/F63,0)</f>
-        <v>0.847668</v>
+        <v/>
       </c>
       <c r="K63" s="254" t="n"/>
       <c r="L63" s="261" t="inlineStr">
@@ -12721,22 +12721,22 @@
       </c>
       <c r="F64" s="50">
         <f>IFERROR(D64+E64+G64+U64+Y64,0)</f>
-        <v>5565.0</v>
+        <v/>
       </c>
       <c r="G64" s="257" t="n">
         <v>130</v>
       </c>
       <c r="H64" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B64,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B64+1))</f>
-        <v>2606.86</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B64,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B64+1))</f>
+        <v/>
       </c>
       <c r="I64" s="259">
         <f>IFERROR(F64-H64,0)</f>
-        <v>2958.14</v>
+        <v/>
       </c>
       <c r="J64" s="260">
         <f>IFERROR(I64/F64,0)</f>
-        <v>0.531562</v>
+        <v/>
       </c>
       <c r="K64" s="254" t="n"/>
       <c r="L64" s="261" t="inlineStr">
@@ -12789,22 +12789,22 @@
       </c>
       <c r="F65" s="50">
         <f>IFERROR(D65+E65+G65+U65+Y65,0)</f>
-        <v>12495.0</v>
+        <v/>
       </c>
       <c r="G65" s="257" t="n">
         <v>2385</v>
       </c>
       <c r="H65" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B65,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B65+1))</f>
-        <v>1657.0</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B65,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B65+1))</f>
+        <v/>
       </c>
       <c r="I65" s="259">
         <f>IFERROR(F65-H65,0)</f>
-        <v>10838.0</v>
+        <v/>
       </c>
       <c r="J65" s="260">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.867387</v>
+        <v/>
       </c>
       <c r="K65" s="254" t="n"/>
       <c r="L65" s="261" t="inlineStr">
@@ -12857,22 +12857,22 @@
       </c>
       <c r="F66" s="50">
         <f>IFERROR(D66+E66+G66+U66+Y66,0)</f>
-        <v>2622.0</v>
+        <v/>
       </c>
       <c r="G66" s="257" t="n">
         <v>300</v>
       </c>
       <c r="H66" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B66,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B66+1))</f>
-        <v>1951.0</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B66,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B66+1))</f>
+        <v/>
       </c>
       <c r="I66" s="259">
         <f>IFERROR(F66-H66,0)</f>
-        <v>671.0</v>
+        <v/>
       </c>
       <c r="J66" s="260">
         <f>IFERROR(I66/F66,0)</f>
-        <v>0.255912</v>
+        <v/>
       </c>
       <c r="K66" s="254" t="n"/>
       <c r="L66" s="261" t="inlineStr">
@@ -12925,22 +12925,22 @@
       </c>
       <c r="F67" s="50">
         <f>IFERROR(D67+E67+G67+U67+Y67,0)</f>
-        <v>2900.0</v>
+        <v/>
       </c>
       <c r="G67" s="257" t="n">
         <v>290</v>
       </c>
       <c r="H67" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B67,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B67+1))</f>
-        <v>5250.0</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B67,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B67+1))</f>
+        <v/>
       </c>
       <c r="I67" s="259">
         <f>IFERROR(F67-H67,0)</f>
-        <v>-2350.0</v>
+        <v/>
       </c>
       <c r="J67" s="260">
         <f>IFERROR(I67/F67,0)</f>
-        <v>-0.810345</v>
+        <v/>
       </c>
       <c r="K67" s="254" t="n"/>
       <c r="L67" s="261" t="inlineStr">
@@ -12993,22 +12993,22 @@
       </c>
       <c r="F68" s="50">
         <f>IFERROR(D68+E68+G68+U68+Y68,0)</f>
-        <v>4955.0</v>
+        <v/>
       </c>
       <c r="G68" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H68" s="258">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;B68,'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;(B68+1))</f>
-        <v>2459.0</v>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B68,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B68+1))</f>
+        <v/>
       </c>
       <c r="I68" s="259">
         <f>IFERROR(F68-H68,0)</f>
-        <v>2496.0</v>
+        <v/>
       </c>
       <c r="J68" s="260">
         <f>IFERROR(I68/F68,0)</f>
-        <v>0.503734</v>
+        <v/>
       </c>
       <c r="K68" s="254" t="n"/>
       <c r="L68" s="261" t="inlineStr">
@@ -21862,9 +21862,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -21927,6 +21927,7 @@
     <row r="3">
       <c r="A3" s="401" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="59" t="inlineStr">
         <is>
@@ -21971,35 +21972,35 @@
     </row>
     <row r="6" ht="15.6" customHeight="1" s="313">
       <c r="B6" s="60">
-        <f>SUMIFS($F$8:$F$500,$B$8:$B$500,TODAY())</f>
+        <f>SUMIFS($F$8:$F$5000,$B$8:$B$5000,TODAY())</f>
         <v/>
       </c>
       <c r="C6" s="61">
-        <f>SUMIFS($F$8:$F$500,$B$8:$B$500,"&gt;="&amp;(TODAY()-WEEKDAY(TODAY(),2)+1),$B$8:$B$500,"&lt;="&amp;(TODAY()-WEEKDAY(TODAY(),2)+7))</f>
+        <f>SUMIFS($F$8:$F$5000,$B$8:$B$5000,"&gt;="&amp;(TODAY()-WEEKDAY(TODAY(),2)+1),$B$8:$B$5000,"&lt;="&amp;(TODAY()-WEEKDAY(TODAY(),2)+7))</f>
         <v/>
       </c>
       <c r="D6" s="62">
-        <f>SUMIFS($F$8:$F$500,$B$8:$B$500,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),$B$8:$B$500,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1))</f>
+        <f>SUMIFS($F$8:$F$5000,$B$8:$B$5000,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),$B$8:$B$5000,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1))</f>
         <v/>
       </c>
       <c r="E6" s="61">
-        <f>SUMIF($E$8:$E$500,"Ingredients*",$F$8:$F$500)</f>
+        <f>SUMIF($E$8:$E$5000,"Ingredients*",$F$8:$F$5000)</f>
         <v/>
       </c>
       <c r="F6" s="63">
-        <f>SUMIF($E$8:$E$500,"Staff*",$F$8:$F$500)</f>
+        <f>SUMIF($E$8:$E$5000,"Staff*",$F$8:$F$5000)</f>
         <v/>
       </c>
       <c r="G6" s="62">
-        <f>SUMIF($E$8:$E$500,"Supplies*",$F$8:$F$500)+SUMIF($E$8:$E$500,"Utilities*",$F$8:$F$500)</f>
+        <f>SUMIF($E$8:$E$5000,"Supplies*",$F$8:$F$5000)+SUMIF($E$8:$E$5000,"Utilities*",$F$8:$F$5000)</f>
         <v/>
       </c>
       <c r="H6" s="60">
-        <f>SUMIFS($F$8:$F$500,$B$8:$B$500,TODAY())</f>
+        <f>SUMIFS($F$8:$F$5000,$B$8:$B$5000,TODAY())</f>
         <v/>
       </c>
       <c r="I6" s="60">
-        <f>SUMIFS($F$8:$F$500,$B$8:$B$500,"&gt;="&amp;(TODAY()-WEEKDAY(TODAY(),2)+1),$B$8:$B$500,"&lt;="&amp;(TODAY()-WEEKDAY(TODAY(),2)+7))</f>
+        <f>SUMIFS($F$8:$F$5000,$B$8:$B$5000,"&gt;="&amp;(TODAY()-WEEKDAY(TODAY(),2)+1),$B$8:$B$5000,"&lt;="&amp;(TODAY()-WEEKDAY(TODAY(),2)+7))</f>
         <v/>
       </c>
     </row>
@@ -43399,23 +43400,23 @@
     </row>
     <row r="6" ht="25.5" customHeight="1" s="313">
       <c r="B6" s="79">
-        <f>COUNTA(B9:B200)</f>
+        <f>COUNTA(B9:B2000)</f>
         <v/>
       </c>
       <c r="D6" s="80">
-        <f>COUNTIF(J9:J200,"⚠️ LOW STOCK")</f>
+        <f>COUNTIF(J9:J2000,"⚠️ LOW STOCK")</f>
         <v/>
       </c>
       <c r="E6" s="80">
-        <f>COUNTIF(J9:J200,"⚠️ LOW STOCK")+COUNTIF(J9:J200,"🚫 OUT OF STOCK")</f>
+        <f>COUNTIF(J9:J2000,"⚠️ LOW STOCK")+COUNTIF(J9:J2000,"🚫 OUT OF STOCK")</f>
         <v/>
       </c>
       <c r="F6" s="81">
-        <f>COUNTIF(J9:J200,"🚫 OUT OF STOCK")</f>
+        <f>COUNTIF(J9:J2000,"🚫 OUT OF STOCK")</f>
         <v/>
       </c>
       <c r="H6" s="81">
-        <f>COUNTIF(J9:J200,"⚠️ LOW STOCK")+COUNTIF(J9:J200,"🚫 OUT OF STOCK")</f>
+        <f>COUNTIF(J9:J2000,"⚠️ LOW STOCK")+COUNTIF(J9:J2000,"🚫 OUT OF STOCK")</f>
         <v/>
       </c>
       <c r="J6" s="82">
@@ -48970,31 +48971,31 @@
     </row>
     <row r="6" ht="25.5" customHeight="1" s="313">
       <c r="B6" s="79">
-        <f>COUNTA(C9:C308)-1</f>
+        <f>COUNTA(C9:C3000)-1</f>
         <v/>
       </c>
       <c r="C6" s="121">
-        <f>COUNTIF(K9:K308,"Pending")</f>
+        <f>COUNTIF(K9:K3000,"Pending")</f>
         <v/>
       </c>
       <c r="D6" s="122">
-        <f>COUNTIF(K9:K308,"In Transit")</f>
+        <f>COUNTIF(K9:K3000,"In Transit")</f>
         <v/>
       </c>
       <c r="E6" s="123">
-        <f>COUNTIF(K9:K308,"Received")</f>
+        <f>COUNTIF(K9:K3000,"Received")</f>
         <v/>
       </c>
       <c r="F6" s="124">
-        <f>SUMIF(K9:K308,"Received",J9:J308)</f>
+        <f>SUMIF(K9:K3000,"Received",J9:J3000)</f>
         <v/>
       </c>
       <c r="G6" s="61">
-        <f>SUMIF(K9:K308,"Pending",J9:J308)</f>
+        <f>SUMIF(K9:K3000,"Pending",J9:J3000)</f>
         <v/>
       </c>
       <c r="H6" s="121">
-        <f>COUNTIF(K9:K308,"Pending")+COUNTIF(K9:K308,"In Transit")</f>
+        <f>COUNTIF(K9:K3000,"Pending")+COUNTIF(K9:K3000,"In Transit")</f>
         <v/>
       </c>
     </row>
@@ -52986,15 +52987,15 @@
         </is>
       </c>
       <c r="B4" s="413">
-        <f>SUMIFS('📅 Daily Log'!$F$8:$F$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$F$8:$F$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C4" s="413">
-        <f>SUMIFS('📅 Daily Log'!$F$8:$F$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$F$8:$F$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D4" s="413">
-        <f>SUMIFS('📅 Daily Log'!$F$8:$F$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$F$8:$F$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E4" s="409" t="n"/>
@@ -53013,15 +53014,15 @@
         </is>
       </c>
       <c r="B5" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C5" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D5" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E5" s="409" t="n"/>
@@ -53067,15 +53068,15 @@
         </is>
       </c>
       <c r="B7" s="416">
-        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$500,"&gt;0",'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$5000,"&gt;0",'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C7" s="416">
-        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$500,"&gt;0",'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$5000,"&gt;0",'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D7" s="416">
-        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$500,"&gt;0",'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$5000,"&gt;0",'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E7" s="409" t="n"/>
@@ -53165,15 +53166,15 @@
         </is>
       </c>
       <c r="B11" s="413">
-        <f>SUMIFS('📅 Daily Log'!$D$8:$D$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$D$8:$D$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C11" s="413">
-        <f>SUMIFS('📅 Daily Log'!$D$8:$D$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$D$8:$D$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D11" s="413">
-        <f>SUMIFS('📅 Daily Log'!$D$8:$D$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$D$8:$D$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E11" s="409" t="n"/>
@@ -53192,15 +53193,15 @@
         </is>
       </c>
       <c r="B12" s="413">
-        <f>SUMIFS('📅 Daily Log'!$E$8:$E$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$E$8:$E$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C12" s="413">
-        <f>SUMIFS('📅 Daily Log'!$E$8:$E$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$E$8:$E$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D12" s="413">
-        <f>SUMIFS('📅 Daily Log'!$E$8:$E$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$E$8:$E$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E12" s="409" t="n"/>
@@ -53219,15 +53220,15 @@
         </is>
       </c>
       <c r="B13" s="413">
-        <f>SUMIFS('📅 Daily Log'!$G$8:$G$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$G$8:$G$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C13" s="413">
-        <f>SUMIFS('📅 Daily Log'!$G$8:$G$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$G$8:$G$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D13" s="413">
-        <f>SUMIFS('📅 Daily Log'!$G$8:$G$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$G$8:$G$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E13" s="409" t="n"/>
@@ -53317,15 +53318,15 @@
         </is>
       </c>
       <c r="B17" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A17,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A17,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C17" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A17,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A17,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D17" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A17,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A17,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E17" s="409" t="n"/>
@@ -53344,15 +53345,15 @@
         </is>
       </c>
       <c r="B18" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A18,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A18,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C18" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A18,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A18,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D18" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A18,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A18,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E18" s="409" t="n"/>
@@ -53371,15 +53372,15 @@
         </is>
       </c>
       <c r="B19" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A19,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A19,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C19" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A19,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A19,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D19" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A19,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A19,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E19" s="409" t="n"/>
@@ -53398,15 +53399,15 @@
         </is>
       </c>
       <c r="B20" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A20,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A20,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C20" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A20,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A20,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D20" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A20,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A20,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E20" s="409" t="n"/>
@@ -53425,15 +53426,15 @@
         </is>
       </c>
       <c r="B21" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A21,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A21,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C21" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A21,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A21,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D21" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A21,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A21,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E21" s="409" t="n"/>
@@ -53452,15 +53453,15 @@
         </is>
       </c>
       <c r="B22" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A22,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A22,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C22" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A22,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A22,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D22" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A22,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A22,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E22" s="409" t="n"/>
@@ -53479,15 +53480,15 @@
         </is>
       </c>
       <c r="B23" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A23,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A23,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C23" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A23,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A23,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D23" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A23,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A23,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E23" s="409" t="n"/>
@@ -53506,15 +53507,15 @@
         </is>
       </c>
       <c r="B24" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A24,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A24,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C24" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A24,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A24,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D24" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A24,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A24,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E24" s="409" t="n"/>
@@ -53533,15 +53534,15 @@
         </is>
       </c>
       <c r="B25" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A25,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A25,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C25" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A25,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A25,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D25" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A25,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A25,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E25" s="409" t="n"/>
@@ -53560,15 +53561,15 @@
         </is>
       </c>
       <c r="B26" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A26,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A26,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C26" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A26,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A26,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D26" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A26,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A26,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E26" s="409" t="n"/>
@@ -53587,15 +53588,15 @@
         </is>
       </c>
       <c r="B27" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A27,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A27,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C27" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A27,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A27,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D27" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A27,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A27,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E27" s="409" t="n"/>
@@ -53614,15 +53615,15 @@
         </is>
       </c>
       <c r="B28" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A28,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A28,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C28" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A28,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A28,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D28" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A28,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A28,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E28" s="409" t="n"/>
@@ -53641,15 +53642,15 @@
         </is>
       </c>
       <c r="B29" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A29,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A29,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C29" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A29,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A29,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D29" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A29,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A29,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E29" s="409" t="n"/>
@@ -53668,15 +53669,15 @@
         </is>
       </c>
       <c r="B30" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A30,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A30,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C30" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A30,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A30,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D30" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A30,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A30,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E30" s="409" t="n"/>
@@ -53695,15 +53696,15 @@
         </is>
       </c>
       <c r="B31" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A31,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A31,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C31" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A31,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A31,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D31" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A31,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A31,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E31" s="409" t="n"/>
@@ -53722,15 +53723,15 @@
         </is>
       </c>
       <c r="B32" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A32,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A32,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C32" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A32,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A32,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D32" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A32,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A32,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E32" s="409" t="n"/>
@@ -53749,15 +53750,15 @@
         </is>
       </c>
       <c r="B33" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A33,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A33,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C33" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A33,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A33,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D33" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A33,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A33,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E33" s="409" t="n"/>
@@ -53776,15 +53777,15 @@
         </is>
       </c>
       <c r="B34" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A34,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A34,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C34" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A34,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A34,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D34" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A34,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A34,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E34" s="409" t="n"/>
@@ -53803,15 +53804,15 @@
         </is>
       </c>
       <c r="B35" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A35,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A35,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C35" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A35,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A35,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D35" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A35,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A35,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E35" s="409" t="n"/>
@@ -53830,15 +53831,15 @@
         </is>
       </c>
       <c r="B36" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A36,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A36,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C36" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A36,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A36,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D36" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A36,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A36,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E36" s="409" t="n"/>
@@ -53857,15 +53858,15 @@
         </is>
       </c>
       <c r="B37" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A37,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A37,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C37" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A37,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A37,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D37" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A37,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A37,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E37" s="409" t="n"/>
@@ -53884,15 +53885,15 @@
         </is>
       </c>
       <c r="B38" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A38,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A38,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C38" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A38,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A38,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D38" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A38,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A38,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E38" s="409" t="n"/>
@@ -53911,15 +53912,15 @@
         </is>
       </c>
       <c r="B39" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A39,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A39,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C39" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A39,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A39,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D39" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A39,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A39,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E39" s="409" t="n"/>
@@ -53938,15 +53939,15 @@
         </is>
       </c>
       <c r="B40" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A40,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A40,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C40" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A40,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A40,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D40" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A40,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A40,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E40" s="409" t="n"/>
@@ -53965,15 +53966,15 @@
         </is>
       </c>
       <c r="B41" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A41,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A41,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C41" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A41,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A41,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D41" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A41,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A41,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E41" s="409" t="n"/>
@@ -53992,15 +53993,15 @@
         </is>
       </c>
       <c r="B42" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A42,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A42,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C42" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A42,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A42,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D42" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A42,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A42,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E42" s="409" t="n"/>
@@ -54019,15 +54020,15 @@
         </is>
       </c>
       <c r="B43" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A43,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A43,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C43" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A43,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A43,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D43" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A43,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A43,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E43" s="409" t="n"/>
@@ -54046,15 +54047,15 @@
         </is>
       </c>
       <c r="B44" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A44,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A44,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C44" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A44,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A44,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D44" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A44,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A44,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E44" s="409" t="n"/>
@@ -54073,15 +54074,15 @@
         </is>
       </c>
       <c r="B45" s="414">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C45" s="414">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D45" s="414">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E45" s="409" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -1347,7 +1347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22"/>
   </cellStyleXfs>
-  <cellXfs count="432">
+  <cellXfs count="434">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2452,6 +2452,8 @@
     <xf numFmtId="175" fontId="101" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="175" fontId="98" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="97" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5410,7 +5412,7 @@
         </is>
       </c>
       <c r="C144" s="283">
-        <f>SUM('💸 Expenses'!F8:F50000)</f>
+        <f>SUM('💸 Expenses'!F8:F5000)</f>
         <v/>
       </c>
       <c r="D144" s="191" t="n"/>
@@ -5448,11 +5450,11 @@
         </is>
       </c>
       <c r="C147" s="268" t="n">
-        <v>39314.81</v>
+        <v>19314.81</v>
       </c>
       <c r="E147" s="286" t="inlineStr">
         <is>
-          <t>Operating costs funded from capital: ledger settlement 30 Jun ($19,314.81) + rent paid from capital 05 Jul ($20,000). Add future capital-funded operating costs here.</t>
+          <t>Ledger settlement 30-Jun ($19,314.81) + rent 05-Jul ($20,000) = $39,314.81; LESS $20,000 repaid from operating cash 21-Jul. Net advance still owed = $19,314.81.</t>
         </is>
       </c>
     </row>
@@ -5460,6 +5462,21 @@
       <c r="B148" s="398" t="inlineStr">
         <is>
           <t>MP commission now auto-calculated per day in Daily Log (col R) at the rate in T7; feeds this result and Cash-on-Hand automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" s="432" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;&gt; Repaid to Capital from operating cash (21-Jul)</t>
+        </is>
+      </c>
+      <c r="C149" s="433" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>$20,000 paid back to Capital from restaurant operating cash. Reduces advance owed and Cash-on-Hand; NOT a P&amp;L expense.</t>
         </is>
       </c>
     </row>
@@ -13045,33 +13062,72 @@
       <c r="AB68" s="292" t="n"/>
     </row>
     <row r="69" ht="16.5" customHeight="1" s="313">
-      <c r="B69" s="34" t="n"/>
-      <c r="C69" s="47" t="n"/>
-      <c r="D69" s="48" t="n"/>
-      <c r="E69" s="49" t="n"/>
-      <c r="F69" s="50" t="n"/>
-      <c r="G69" s="51" t="n"/>
-      <c r="H69" s="52" t="n"/>
-      <c r="I69" s="53" t="n"/>
-      <c r="J69" s="54" t="n"/>
-      <c r="K69" s="55" t="n"/>
-      <c r="L69" s="18" t="n"/>
-      <c r="M69" s="21" t="n"/>
-      <c r="N69" s="56" t="n"/>
-      <c r="O69" s="57" t="n"/>
-      <c r="P69" s="58" t="n"/>
-      <c r="Q69" s="56" t="n"/>
-      <c r="R69" s="56" t="n"/>
-      <c r="S69" s="56" t="n"/>
-      <c r="T69" s="56" t="n"/>
-      <c r="U69" s="56" t="n"/>
-      <c r="V69" s="56" t="n"/>
-      <c r="W69" s="56" t="n"/>
-      <c r="X69" s="56" t="n"/>
-      <c r="Y69" s="56" t="n"/>
-      <c r="Z69" s="56" t="n"/>
-      <c r="AA69" s="56" t="n"/>
-      <c r="AB69" s="56" t="n"/>
+      <c r="B69" s="420" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C69" s="255" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D69" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="49" t="n">
+        <v>3470</v>
+      </c>
+      <c r="F69" s="50">
+        <f>IFERROR(D69+E69+G69+U69+Y69,0)</f>
+        <v/>
+      </c>
+      <c r="G69" s="257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B69,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B69+1))</f>
+        <v/>
+      </c>
+      <c r="I69" s="259">
+        <f>IFERROR(F69-H69,0)</f>
+        <v/>
+      </c>
+      <c r="J69" s="260">
+        <f>IFERROR(I69/F69,0)</f>
+        <v/>
+      </c>
+      <c r="K69" s="254" t="n"/>
+      <c r="L69" s="261" t="inlineStr">
+        <is>
+          <t>EOD close (BBVA + cash). Week 10 start.</t>
+        </is>
+      </c>
+      <c r="M69" s="291" t="n"/>
+      <c r="N69" s="292" t="n"/>
+      <c r="O69" s="293" t="n"/>
+      <c r="P69" s="294" t="n"/>
+      <c r="Q69" s="292" t="n"/>
+      <c r="R69" s="421">
+        <f>IFERROR(D69*$T$7,0)</f>
+        <v/>
+      </c>
+      <c r="S69" s="292" t="n"/>
+      <c r="T69" s="292" t="n"/>
+      <c r="U69" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" s="292" t="n"/>
+      <c r="X69" s="292" t="n"/>
+      <c r="Y69" s="421" t="n">
+        <v>2010</v>
+      </c>
+      <c r="Z69" s="421" t="n">
+        <v>38.19</v>
+      </c>
+      <c r="AA69" s="292" t="n"/>
+      <c r="AB69" s="292" t="n"/>
     </row>
     <row r="70" ht="16.5" customHeight="1" s="313">
       <c r="B70" s="34" t="n"/>
@@ -21862,9 +21918,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -21887,7 +21943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J509"/>
+  <dimension ref="A1:J516"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="313" min="1" max="1"/>
@@ -21927,7 +21983,6 @@
     <row r="3">
       <c r="A3" s="401" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="59" t="inlineStr">
         <is>
@@ -43278,6 +43333,307 @@
       <c r="J509" s="418" t="inlineStr">
         <is>
           <t>No receipt provided; restaurant-paid</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="B510" s="422" t="n">
+        <v>46221</v>
+      </c>
+      <c r="C510" s="305" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D510" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E510" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F510" s="307" t="n">
+        <v>1520</v>
+      </c>
+      <c r="G510" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H510" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I510" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J510" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash; added later (Saturday expense)</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="B511" s="422" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C511" s="305" t="inlineStr">
+        <is>
+          <t>Jamon</t>
+        </is>
+      </c>
+      <c r="D511" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E511" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F511" s="307" t="n">
+        <v>174</v>
+      </c>
+      <c r="G511" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H511" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I511" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J511" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="B512" s="422" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C512" s="305" t="inlineStr">
+        <is>
+          <t>Carnes</t>
+        </is>
+      </c>
+      <c r="D512" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E512" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F512" s="307" t="n">
+        <v>562</v>
+      </c>
+      <c r="G512" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H512" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I512" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J512" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="B513" s="422" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C513" s="305" t="inlineStr">
+        <is>
+          <t>Carne de hamburguesa</t>
+        </is>
+      </c>
+      <c r="D513" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E513" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F513" s="307" t="n">
+        <v>380</v>
+      </c>
+      <c r="G513" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H513" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I513" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J513" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="B514" s="422" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C514" s="305" t="inlineStr">
+        <is>
+          <t>Arroz (Oxxo)</t>
+        </is>
+      </c>
+      <c r="D514" s="306" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E514" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F514" s="307" t="n">
+        <v>26</v>
+      </c>
+      <c r="G514" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H514" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I514" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J514" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="B515" s="422" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C515" s="305" t="inlineStr">
+        <is>
+          <t>Chedraui (varios)</t>
+        </is>
+      </c>
+      <c r="D515" s="306" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E515" s="305" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F515" s="307" t="n">
+        <v>116</v>
+      </c>
+      <c r="G515" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H515" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I515" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J515" s="418" t="inlineStr">
+        <is>
+          <t>No receipt provided; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="B516" s="422" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C516" s="305" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D516" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E516" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F516" s="307" t="n">
+        <v>939</v>
+      </c>
+      <c r="G516" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H516" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I516" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J516" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
         </is>
       </c>
     </row>
@@ -52919,14 +53275,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="313">
-      <c r="A1" s="417" t="inlineStr">
+      <c r="A1" s="407" t="inlineStr">
         <is>
           <t>LOKA — MONTHLY P&amp;L   (live formulas — auto-updates from Daily Log &amp; Expenses)</t>
         </is>
       </c>
-      <c r="B1" s="418" t="n"/>
-      <c r="C1" s="418" t="n"/>
-      <c r="D1" s="418" t="n"/>
+      <c r="B1" s="408" t="n"/>
+      <c r="C1" s="408" t="n"/>
+      <c r="D1" s="408" t="n"/>
       <c r="E1" s="409" t="n"/>
       <c r="F1" s="409" t="n"/>
       <c r="G1" s="409" t="n"/>
@@ -52987,15 +53343,15 @@
         </is>
       </c>
       <c r="B4" s="413">
-        <f>SUMIFS('📅 Daily Log'!$F$8:$F$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$F$8:$F$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C4" s="413">
-        <f>SUMIFS('📅 Daily Log'!$F$8:$F$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$F$8:$F$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D4" s="413">
-        <f>SUMIFS('📅 Daily Log'!$F$8:$F$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$F$8:$F$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E4" s="409" t="n"/>
@@ -53014,15 +53370,15 @@
         </is>
       </c>
       <c r="B5" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C5" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D5" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E5" s="409" t="n"/>
@@ -53068,15 +53424,15 @@
         </is>
       </c>
       <c r="B7" s="416">
-        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$5000,"&gt;0",'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$500,"&gt;0",'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C7" s="416">
-        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$5000,"&gt;0",'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$500,"&gt;0",'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D7" s="416">
-        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$5000,"&gt;0",'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$500,"&gt;0",'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E7" s="409" t="n"/>
@@ -53166,15 +53522,15 @@
         </is>
       </c>
       <c r="B11" s="413">
-        <f>SUMIFS('📅 Daily Log'!$D$8:$D$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$D$8:$D$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C11" s="413">
-        <f>SUMIFS('📅 Daily Log'!$D$8:$D$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$D$8:$D$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D11" s="413">
-        <f>SUMIFS('📅 Daily Log'!$D$8:$D$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$D$8:$D$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E11" s="409" t="n"/>
@@ -53193,15 +53549,15 @@
         </is>
       </c>
       <c r="B12" s="413">
-        <f>SUMIFS('📅 Daily Log'!$E$8:$E$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$E$8:$E$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C12" s="413">
-        <f>SUMIFS('📅 Daily Log'!$E$8:$E$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$E$8:$E$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D12" s="413">
-        <f>SUMIFS('📅 Daily Log'!$E$8:$E$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$E$8:$E$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E12" s="409" t="n"/>
@@ -53220,15 +53576,15 @@
         </is>
       </c>
       <c r="B13" s="413">
-        <f>SUMIFS('📅 Daily Log'!$G$8:$G$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$G$8:$G$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C13" s="413">
-        <f>SUMIFS('📅 Daily Log'!$G$8:$G$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$G$8:$G$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D13" s="413">
-        <f>SUMIFS('📅 Daily Log'!$G$8:$G$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$G$8:$G$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E13" s="409" t="n"/>
@@ -53318,15 +53674,15 @@
         </is>
       </c>
       <c r="B17" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A17,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A17,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C17" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A17,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A17,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D17" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A17,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A17,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E17" s="409" t="n"/>
@@ -53345,15 +53701,15 @@
         </is>
       </c>
       <c r="B18" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A18,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A18,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C18" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A18,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A18,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D18" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A18,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A18,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E18" s="409" t="n"/>
@@ -53372,15 +53728,15 @@
         </is>
       </c>
       <c r="B19" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A19,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A19,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C19" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A19,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A19,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D19" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A19,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A19,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E19" s="409" t="n"/>
@@ -53399,15 +53755,15 @@
         </is>
       </c>
       <c r="B20" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A20,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A20,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C20" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A20,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A20,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D20" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A20,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A20,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E20" s="409" t="n"/>
@@ -53426,15 +53782,15 @@
         </is>
       </c>
       <c r="B21" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A21,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A21,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C21" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A21,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A21,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D21" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A21,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A21,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E21" s="409" t="n"/>
@@ -53453,15 +53809,15 @@
         </is>
       </c>
       <c r="B22" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A22,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A22,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C22" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A22,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A22,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D22" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A22,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A22,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E22" s="409" t="n"/>
@@ -53480,15 +53836,15 @@
         </is>
       </c>
       <c r="B23" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A23,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A23,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C23" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A23,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A23,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D23" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A23,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A23,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E23" s="409" t="n"/>
@@ -53507,15 +53863,15 @@
         </is>
       </c>
       <c r="B24" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A24,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A24,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C24" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A24,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A24,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D24" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A24,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A24,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E24" s="409" t="n"/>
@@ -53534,15 +53890,15 @@
         </is>
       </c>
       <c r="B25" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A25,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A25,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C25" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A25,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A25,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D25" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A25,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A25,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E25" s="409" t="n"/>
@@ -53561,15 +53917,15 @@
         </is>
       </c>
       <c r="B26" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A26,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A26,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C26" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A26,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A26,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D26" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A26,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A26,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E26" s="409" t="n"/>
@@ -53588,15 +53944,15 @@
         </is>
       </c>
       <c r="B27" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A27,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A27,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C27" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A27,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A27,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D27" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A27,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A27,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E27" s="409" t="n"/>
@@ -53615,15 +53971,15 @@
         </is>
       </c>
       <c r="B28" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A28,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A28,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C28" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A28,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A28,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D28" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A28,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A28,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E28" s="409" t="n"/>
@@ -53642,15 +53998,15 @@
         </is>
       </c>
       <c r="B29" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A29,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A29,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C29" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A29,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A29,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D29" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A29,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A29,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E29" s="409" t="n"/>
@@ -53669,15 +54025,15 @@
         </is>
       </c>
       <c r="B30" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A30,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A30,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C30" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A30,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A30,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D30" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A30,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A30,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E30" s="409" t="n"/>
@@ -53696,15 +54052,15 @@
         </is>
       </c>
       <c r="B31" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A31,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A31,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C31" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A31,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A31,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D31" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A31,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A31,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E31" s="409" t="n"/>
@@ -53723,15 +54079,15 @@
         </is>
       </c>
       <c r="B32" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A32,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A32,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C32" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A32,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A32,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D32" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A32,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A32,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E32" s="409" t="n"/>
@@ -53750,15 +54106,15 @@
         </is>
       </c>
       <c r="B33" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A33,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A33,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C33" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A33,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A33,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D33" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A33,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A33,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E33" s="409" t="n"/>
@@ -53777,15 +54133,15 @@
         </is>
       </c>
       <c r="B34" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A34,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A34,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C34" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A34,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A34,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D34" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A34,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A34,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E34" s="409" t="n"/>
@@ -53804,15 +54160,15 @@
         </is>
       </c>
       <c r="B35" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A35,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A35,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C35" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A35,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A35,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D35" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A35,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A35,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E35" s="409" t="n"/>
@@ -53831,15 +54187,15 @@
         </is>
       </c>
       <c r="B36" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A36,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A36,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C36" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A36,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A36,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D36" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A36,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A36,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E36" s="409" t="n"/>
@@ -53858,15 +54214,15 @@
         </is>
       </c>
       <c r="B37" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A37,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A37,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C37" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A37,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A37,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D37" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A37,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A37,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E37" s="409" t="n"/>
@@ -53885,15 +54241,15 @@
         </is>
       </c>
       <c r="B38" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A38,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A38,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C38" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A38,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A38,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D38" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A38,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A38,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E38" s="409" t="n"/>
@@ -53912,15 +54268,15 @@
         </is>
       </c>
       <c r="B39" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A39,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A39,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C39" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A39,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A39,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D39" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A39,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A39,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E39" s="409" t="n"/>
@@ -53939,15 +54295,15 @@
         </is>
       </c>
       <c r="B40" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A40,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A40,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C40" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A40,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A40,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D40" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A40,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A40,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E40" s="409" t="n"/>
@@ -53966,15 +54322,15 @@
         </is>
       </c>
       <c r="B41" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A41,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A41,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C41" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A41,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A41,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D41" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A41,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A41,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E41" s="409" t="n"/>
@@ -53993,15 +54349,15 @@
         </is>
       </c>
       <c r="B42" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A42,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A42,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C42" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A42,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A42,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D42" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A42,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A42,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E42" s="409" t="n"/>
@@ -54020,15 +54376,15 @@
         </is>
       </c>
       <c r="B43" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A43,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A43,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C43" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A43,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A43,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D43" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A43,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A43,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E43" s="409" t="n"/>
@@ -54047,15 +54403,15 @@
         </is>
       </c>
       <c r="B44" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A44,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A44,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C44" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A44,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A44,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D44" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A44,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A44,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E44" s="409" t="n"/>
@@ -54074,15 +54430,15 @@
         </is>
       </c>
       <c r="B45" s="414">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C45" s="414">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D45" s="414">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E45" s="409" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5450,11 +5450,11 @@
         </is>
       </c>
       <c r="C147" s="268" t="n">
-        <v>19314.81</v>
+        <v>16727.81</v>
       </c>
       <c r="E147" s="286" t="inlineStr">
         <is>
-          <t>Ledger settlement 30-Jun ($19,314.81) + rent 05-Jul ($20,000) = $39,314.81; LESS $20,000 repaid from operating cash 21-Jul. Net advance still owed = $19,314.81.</t>
+          <t>Advance from capital-funded operating costs; repaid from operating cash: $20,000 (21-Jul) + $2,587 (22-Jul). Net advance still owed = $16,727.81.</t>
         </is>
       </c>
     </row>
@@ -5468,15 +5468,15 @@
     <row r="149">
       <c r="B149" s="432" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt; Repaid to Capital from operating cash (21-Jul)</t>
+          <t xml:space="preserve">  &gt;&gt; Repaid to Capital from operating cash</t>
         </is>
       </c>
       <c r="C149" s="433" t="n">
-        <v>-20000</v>
+        <v>-22587</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>$20,000 paid back to Capital from restaurant operating cash. Reduces advance owed and Cash-on-Hand; NOT a P&amp;L expense.</t>
+          <t>21-Jul $20,000 + 22-Jul $2,587 = $22,587 repaid from restaurant operating cash. Reduces advance owed &amp; Cash-on-Hand; NOT a P&amp;L expense.</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="313" min="1" max="1"/>
@@ -7323,40 +7323,96 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="231" t="inlineStr">
+      <c r="A45" s="231" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B45" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 22-Jul)</t>
+        </is>
+      </c>
+      <c r="C45" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D45" s="232" t="n"/>
+      <c r="E45" s="233" t="n">
+        <v>260</v>
+      </c>
+      <c r="F45" s="233">
+        <f>IFERROR(F44+D45-E45,0)</f>
+        <v/>
+      </c>
+      <c r="G45" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H45" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid $260 by transfer to Lohith personal acct (22-Jul revenue; not the $95 that went to restaurant bank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="231" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B46" s="232" t="inlineStr">
+        <is>
+          <t>Pollo (paid by Lohith, 22-Jul)</t>
+        </is>
+      </c>
+      <c r="C46" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D46" s="232" t="n">
+        <v>234</v>
+      </c>
+      <c r="E46" s="233" t="n"/>
+      <c r="F46" s="233">
+        <f>IFERROR(F45+D46-E46,0)</f>
+        <v/>
+      </c>
+      <c r="G46" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H46" s="232" t="inlineStr">
+        <is>
+          <t>Lohith pago $234 de pollo de su bolsillo (22-Jul). En Expenses paid=Lohith; excluido de la caja via cash_adjust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="231" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B45" s="232" t="n"/>
-      <c r="C45" s="232" t="n"/>
-      <c r="D45" s="232">
-        <f>SUM(D4:D44)</f>
-        <v/>
-      </c>
-      <c r="E45" s="233">
-        <f>SUM(E4:E44)</f>
-        <v/>
-      </c>
-      <c r="F45" s="233">
-        <f>F44</f>
-        <v/>
-      </c>
-      <c r="G45" s="232">
-        <f>IF(F44&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F44,"#,##0"),IF(F44&lt;0,"Lohith holds $"&amp;TEXT(ABS(F44),"#,##0"),"Zero balance"))</f>
-        <v/>
-      </c>
-      <c r="H45" s="232" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="231" t="n"/>
-      <c r="B46" s="232" t="n"/>
-      <c r="C46" s="232" t="n"/>
-      <c r="D46" s="232" t="n"/>
-      <c r="E46" s="233" t="n"/>
-      <c r="F46" s="233" t="n"/>
-      <c r="G46" s="232" t="n"/>
-      <c r="H46" s="232" t="n"/>
+      <c r="B47" s="232" t="n"/>
+      <c r="C47" s="232" t="n"/>
+      <c r="D47" s="232">
+        <f>SUM(D4:D46)</f>
+        <v/>
+      </c>
+      <c r="E47" s="233">
+        <f>SUM(E4:E46)</f>
+        <v/>
+      </c>
+      <c r="F47" s="233">
+        <f>F46</f>
+        <v/>
+      </c>
+      <c r="G47" s="232">
+        <f>IF(F46&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F46,"#,##0"),IF(F46&lt;0,"Lohith holds $"&amp;TEXT(ABS(F46),"#,##0"),"Zero balance"))</f>
+        <v/>
+      </c>
+      <c r="H47" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -13130,33 +13186,72 @@
       <c r="AB69" s="292" t="n"/>
     </row>
     <row r="70" ht="16.5" customHeight="1" s="313">
-      <c r="B70" s="34" t="n"/>
-      <c r="C70" s="35" t="n"/>
-      <c r="D70" s="36" t="n"/>
-      <c r="E70" s="37" t="n"/>
-      <c r="F70" s="38" t="n"/>
-      <c r="G70" s="39" t="n"/>
-      <c r="H70" s="40" t="n"/>
-      <c r="I70" s="41" t="n"/>
-      <c r="J70" s="42" t="n"/>
-      <c r="K70" s="43" t="n"/>
-      <c r="L70" s="9" t="n"/>
-      <c r="M70" s="12" t="n"/>
-      <c r="N70" s="44" t="n"/>
-      <c r="O70" s="45" t="n"/>
-      <c r="P70" s="46" t="n"/>
-      <c r="Q70" s="44" t="n"/>
-      <c r="R70" s="44" t="n"/>
-      <c r="S70" s="44" t="n"/>
-      <c r="T70" s="44" t="n"/>
-      <c r="U70" s="44" t="n"/>
-      <c r="V70" s="44" t="n"/>
-      <c r="W70" s="44" t="n"/>
-      <c r="X70" s="44" t="n"/>
-      <c r="Y70" s="44" t="n"/>
-      <c r="Z70" s="44" t="n"/>
-      <c r="AA70" s="44" t="n"/>
-      <c r="AB70" s="44" t="n"/>
+      <c r="B70" s="420" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C70" s="255" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D70" s="256" t="n">
+        <v>2310</v>
+      </c>
+      <c r="E70" s="49" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F70" s="50">
+        <f>IFERROR(D70+E70+G70+U70+Y70,0)</f>
+        <v/>
+      </c>
+      <c r="G70" s="257" t="n">
+        <v>355</v>
+      </c>
+      <c r="H70" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B70,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B70+1))</f>
+        <v/>
+      </c>
+      <c r="I70" s="259">
+        <f>IFERROR(F70-H70,0)</f>
+        <v/>
+      </c>
+      <c r="J70" s="260">
+        <f>IFERROR(I70/F70,0)</f>
+        <v/>
+      </c>
+      <c r="K70" s="254" t="n"/>
+      <c r="L70" s="261" t="inlineStr">
+        <is>
+          <t>EOD close (MP + BBVA + cash). Transfer col = $260 to-me (ledger) + $95 to restaurant BBVA bank (revenue, no comm). | +$240 additional cash income</t>
+        </is>
+      </c>
+      <c r="M70" s="291" t="n"/>
+      <c r="N70" s="292" t="n"/>
+      <c r="O70" s="293" t="n"/>
+      <c r="P70" s="294" t="n"/>
+      <c r="Q70" s="292" t="n"/>
+      <c r="R70" s="421">
+        <f>IFERROR(D70*$T$7,0)</f>
+        <v/>
+      </c>
+      <c r="S70" s="292" t="n"/>
+      <c r="T70" s="292" t="n"/>
+      <c r="U70" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" s="292" t="n"/>
+      <c r="X70" s="292" t="n"/>
+      <c r="Y70" s="421" t="n">
+        <v>810</v>
+      </c>
+      <c r="Z70" s="421" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="AA70" s="292" t="n"/>
+      <c r="AB70" s="292" t="n"/>
     </row>
     <row r="71" ht="16.5" customHeight="1" s="313">
       <c r="B71" s="34" t="n"/>
@@ -21918,9 +22013,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -21943,7 +22038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J516"/>
+  <dimension ref="A1:J524"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="313" min="1" max="1"/>
@@ -43632,6 +43727,350 @@
         </is>
       </c>
       <c r="J516" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="B517" s="422" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C517" s="305" t="inlineStr">
+        <is>
+          <t>Avia Reca (bebidas)</t>
+        </is>
+      </c>
+      <c r="D517" s="306" t="inlineStr">
+        <is>
+          <t>Reca</t>
+        </is>
+      </c>
+      <c r="E517" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F517" s="307" t="n">
+        <v>300</v>
+      </c>
+      <c r="G517" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H517" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I517" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J517" s="418" t="inlineStr">
+        <is>
+          <t>Marca de bebidas; gasto operativo recurrente de inventario de bebidas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="B518" s="422" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C518" s="305" t="inlineStr">
+        <is>
+          <t>Carnes</t>
+        </is>
+      </c>
+      <c r="D518" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E518" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F518" s="307" t="n">
+        <v>833</v>
+      </c>
+      <c r="G518" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H518" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I518" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J518" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="B519" s="422" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C519" s="305" t="inlineStr">
+        <is>
+          <t>Elote (Oxxo)</t>
+        </is>
+      </c>
+      <c r="D519" s="306" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E519" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F519" s="307" t="n">
+        <v>20</v>
+      </c>
+      <c r="G519" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H519" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I519" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J519" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="B520" s="422" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C520" s="305" t="inlineStr">
+        <is>
+          <t>Tilapia</t>
+        </is>
+      </c>
+      <c r="D520" s="306" t="inlineStr">
+        <is>
+          <t>Brisa del Mar</t>
+        </is>
+      </c>
+      <c r="E520" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat &amp; Fish</t>
+        </is>
+      </c>
+      <c r="F520" s="307" t="n">
+        <v>366</v>
+      </c>
+      <c r="G520" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H520" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I520" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J520" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash; pescado</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="B521" s="422" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C521" s="305" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D521" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E521" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F521" s="307" t="n">
+        <v>234</v>
+      </c>
+      <c r="G521" s="308" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H521" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I521" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J521" s="418" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger; no de la caja</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="B522" s="422" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C522" s="305" t="inlineStr">
+        <is>
+          <t>Soft Restaurant app subscription</t>
+        </is>
+      </c>
+      <c r="D522" s="306" t="inlineStr">
+        <is>
+          <t>Soft Restaurant</t>
+        </is>
+      </c>
+      <c r="E522" s="305" t="inlineStr">
+        <is>
+          <t>Utilities/Internet</t>
+        </is>
+      </c>
+      <c r="F522" s="307" t="n">
+        <v>810</v>
+      </c>
+      <c r="G522" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H522" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I522" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J522" s="418" t="inlineStr">
+        <is>
+          <t>Suscripcion MENSUAL recurrente del software POS Soft Restaurant. Gasto OPERATIVO (no capital) - se repite cada mes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="B523" s="422" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C523" s="305" t="inlineStr">
+        <is>
+          <t>Groceries (Tres B)</t>
+        </is>
+      </c>
+      <c r="D523" s="306" t="inlineStr">
+        <is>
+          <t>Tres B</t>
+        </is>
+      </c>
+      <c r="E523" s="305" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F523" s="307" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G523" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H523" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I523" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J523" s="418" t="inlineStr">
+        <is>
+          <t>No receipt provided; cash; abarrotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="B524" s="422" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C524" s="305" t="inlineStr">
+        <is>
+          <t>Agua natural</t>
+        </is>
+      </c>
+      <c r="D524" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E524" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F524" s="307" t="n">
+        <v>70</v>
+      </c>
+      <c r="G524" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H524" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I524" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J524" s="418" t="inlineStr">
         <is>
           <t>No receipt; cash</t>
         </is>
@@ -54129,7 +54568,7 @@
     <row r="34">
       <c r="A34" s="415" t="inlineStr">
         <is>
-          <t>Kitchen Supplies</t>
+          <t>Utilities/Internet</t>
         </is>
       </c>
       <c r="B34" s="413">
@@ -54156,7 +54595,7 @@
     <row r="35">
       <c r="A35" s="415" t="inlineStr">
         <is>
-          <t>Software / Subscription</t>
+          <t>Kitchen Supplies</t>
         </is>
       </c>
       <c r="B35" s="413">
@@ -54183,7 +54622,7 @@
     <row r="36">
       <c r="A36" s="415" t="inlineStr">
         <is>
-          <t>Staff - Advance</t>
+          <t>Software / Subscription</t>
         </is>
       </c>
       <c r="B36" s="413">
@@ -54210,7 +54649,7 @@
     <row r="37">
       <c r="A37" s="415" t="inlineStr">
         <is>
-          <t>Utilities / Internet</t>
+          <t>Staff - Advance</t>
         </is>
       </c>
       <c r="B37" s="413">
@@ -54237,7 +54676,7 @@
     <row r="38">
       <c r="A38" s="415" t="inlineStr">
         <is>
-          <t>Utilities/Internet</t>
+          <t>Utilities / Internet</t>
         </is>
       </c>
       <c r="B38" s="413">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -9254,15 +9254,15 @@
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v/>
+        <v>5348.83</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v/>
+        <v>-1273.83</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v/>
+        <v>-0.312596</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="F8" s="38">
         <f>IFERROR(D8+E8+G8,0)</f>
-        <v/>
+        <v>3689.0</v>
       </c>
       <c r="G8" s="39" t="n"/>
       <c r="H8" s="40">
@@ -9444,11 +9444,11 @@
       </c>
       <c r="I8" s="41">
         <f>IFERROR(F8-H8,0)</f>
-        <v/>
+        <v>1060.0</v>
       </c>
       <c r="J8" s="42">
         <f>IFERROR(I8/F8,0)</f>
-        <v/>
+        <v>0.287341</v>
       </c>
       <c r="K8" s="43" t="n"/>
       <c r="L8" s="9" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="F9" s="50">
         <f>IFERROR(D9+E9+G9,0)</f>
-        <v/>
+        <v>3854.0</v>
       </c>
       <c r="G9" s="51" t="n"/>
       <c r="H9" s="52">
@@ -9502,11 +9502,11 @@
       </c>
       <c r="I9" s="53">
         <f>IFERROR(F9-H9,0)</f>
-        <v/>
+        <v>3824.0</v>
       </c>
       <c r="J9" s="54">
         <f>IFERROR(I9/F9,0)</f>
-        <v/>
+        <v>0.992216</v>
       </c>
       <c r="K9" s="55" t="n"/>
       <c r="L9" s="18" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="F10" s="38">
         <f>IFERROR(D10+E10+G10,0)</f>
-        <v/>
+        <v>4124.0</v>
       </c>
       <c r="G10" s="39" t="n"/>
       <c r="H10" s="40">
@@ -9560,11 +9560,11 @@
       </c>
       <c r="I10" s="41">
         <f>IFERROR(F10-H10,0)</f>
-        <v/>
+        <v>347.0</v>
       </c>
       <c r="J10" s="42">
         <f>IFERROR(I10/F10,0)</f>
-        <v/>
+        <v>0.084142</v>
       </c>
       <c r="K10" s="43" t="n"/>
       <c r="L10" s="9" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="F11" s="50">
         <f>IFERROR(D11+E11+G11,0)</f>
-        <v/>
+        <v>4733.0</v>
       </c>
       <c r="G11" s="51" t="n"/>
       <c r="H11" s="52">
@@ -9618,11 +9618,11 @@
       </c>
       <c r="I11" s="53">
         <f>IFERROR(F11-H11,0)</f>
-        <v/>
+        <v>2299.0</v>
       </c>
       <c r="J11" s="54">
         <f>IFERROR(I11/F11,0)</f>
-        <v/>
+        <v>0.485738</v>
       </c>
       <c r="K11" s="55" t="n"/>
       <c r="L11" s="18" t="inlineStr">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="F12" s="38">
         <f>IFERROR(D12+E12+G12,0)</f>
-        <v/>
+        <v>4282.0</v>
       </c>
       <c r="G12" s="39" t="n"/>
       <c r="H12" s="40">
@@ -9676,11 +9676,11 @@
       </c>
       <c r="I12" s="41">
         <f>IFERROR(F12-H12,0)</f>
-        <v/>
+        <v>2825.0</v>
       </c>
       <c r="J12" s="42">
         <f>IFERROR(I12/F12,0)</f>
-        <v/>
+        <v>0.659738</v>
       </c>
       <c r="K12" s="43" t="n"/>
       <c r="L12" s="9" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="F13" s="50">
         <f>IFERROR(D13+E13+G13,0)</f>
-        <v/>
+        <v>3802.0</v>
       </c>
       <c r="G13" s="51" t="n"/>
       <c r="H13" s="52">
@@ -9734,11 +9734,11 @@
       </c>
       <c r="I13" s="53">
         <f>IFERROR(F13-H13,0)</f>
-        <v/>
+        <v>-3953.43</v>
       </c>
       <c r="J13" s="54">
         <f>IFERROR(I13/F13,0)</f>
-        <v/>
+        <v>-1.039829</v>
       </c>
       <c r="K13" s="55" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F14" s="38">
         <f>IFERROR(D14+E14+G14,0)</f>
-        <v/>
+        <v>1198.0</v>
       </c>
       <c r="G14" s="39" t="n"/>
       <c r="H14" s="40">
@@ -9794,11 +9794,11 @@
       </c>
       <c r="I14" s="41">
         <f>IFERROR(F14-H14,0)</f>
-        <v/>
+        <v>122.0</v>
       </c>
       <c r="J14" s="42">
         <f>IFERROR(I14/F14,0)</f>
-        <v/>
+        <v>0.101836</v>
       </c>
       <c r="K14" s="43" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
       </c>
       <c r="F15" s="50">
         <f>IFERROR(D15+E15+G15,0)</f>
-        <v/>
+        <v>3730.0</v>
       </c>
       <c r="G15" s="51" t="n"/>
       <c r="H15" s="52">
@@ -9856,11 +9856,11 @@
       </c>
       <c r="I15" s="53">
         <f>IFERROR(F15-H15,0)</f>
-        <v/>
+        <v>708.55</v>
       </c>
       <c r="J15" s="54">
         <f>IFERROR(I15/F15,0)</f>
-        <v/>
+        <v>0.18996</v>
       </c>
       <c r="K15" s="55" t="n"/>
       <c r="L15" s="18" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="F16" s="38">
         <f>IFERROR(D16+E16+G16,0)</f>
-        <v/>
+        <v>4264.0</v>
       </c>
       <c r="G16" s="39" t="n"/>
       <c r="H16" s="40">
@@ -9914,11 +9914,11 @@
       </c>
       <c r="I16" s="41">
         <f>IFERROR(F16-H16,0)</f>
-        <v/>
+        <v>3072.4</v>
       </c>
       <c r="J16" s="42">
         <f>IFERROR(I16/F16,0)</f>
-        <v/>
+        <v>0.720544</v>
       </c>
       <c r="K16" s="43" t="n"/>
       <c r="L16" s="9" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="F17" s="50">
         <f>IFERROR(D17+E17+G17,0)</f>
-        <v/>
+        <v>3621.0</v>
       </c>
       <c r="G17" s="51" t="n"/>
       <c r="H17" s="52">
@@ -9972,11 +9972,11 @@
       </c>
       <c r="I17" s="53">
         <f>IFERROR(F17-H17,0)</f>
-        <v/>
+        <v>2547.78</v>
       </c>
       <c r="J17" s="54">
         <f>IFERROR(I17/F17,0)</f>
-        <v/>
+        <v>0.703612</v>
       </c>
       <c r="K17" s="55" t="n"/>
       <c r="L17" s="18" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="F18" s="38">
         <f>IFERROR(D18+E18+G18,0)</f>
-        <v/>
+        <v>4070.0</v>
       </c>
       <c r="G18" s="39" t="n"/>
       <c r="H18" s="40">
@@ -10030,11 +10030,11 @@
       </c>
       <c r="I18" s="41">
         <f>IFERROR(F18-H18,0)</f>
-        <v/>
+        <v>2138.66</v>
       </c>
       <c r="J18" s="42">
         <f>IFERROR(I18/F18,0)</f>
-        <v/>
+        <v>0.525469</v>
       </c>
       <c r="K18" s="43" t="n"/>
       <c r="L18" s="9" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="F19" s="50">
         <f>IFERROR(D19+E19+G19,0)</f>
-        <v/>
+        <v>6086.0</v>
       </c>
       <c r="G19" s="51" t="n"/>
       <c r="H19" s="52">
@@ -10088,11 +10088,11 @@
       </c>
       <c r="I19" s="53">
         <f>IFERROR(F19-H19,0)</f>
-        <v/>
+        <v>5828.71</v>
       </c>
       <c r="J19" s="54">
         <f>IFERROR(I19/F19,0)</f>
-        <v/>
+        <v>0.957724</v>
       </c>
       <c r="K19" s="55" t="n"/>
       <c r="L19" s="18" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="F20" s="38">
         <f>IFERROR(D20+E20+G20,0)</f>
-        <v/>
+        <v>4603.0</v>
       </c>
       <c r="G20" s="39" t="n"/>
       <c r="H20" s="40">
@@ -10146,11 +10146,11 @@
       </c>
       <c r="I20" s="41">
         <f>IFERROR(F20-H20,0)</f>
-        <v/>
+        <v>-1371.3</v>
       </c>
       <c r="J20" s="42">
         <f>IFERROR(I20/F20,0)</f>
-        <v/>
+        <v>-0.297914</v>
       </c>
       <c r="K20" s="43" t="n"/>
       <c r="L20" s="9" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="F21" s="50">
         <f>IFERROR(D21+E21+G21,0)</f>
-        <v/>
+        <v>893.0</v>
       </c>
       <c r="G21" s="51" t="n"/>
       <c r="H21" s="52">
@@ -10202,11 +10202,11 @@
       </c>
       <c r="I21" s="53">
         <f>IFERROR(F21-H21,0)</f>
-        <v/>
+        <v>-9419.0</v>
       </c>
       <c r="J21" s="54">
         <f>IFERROR(I21/F21,0)</f>
-        <v/>
+        <v>-10.547592</v>
       </c>
       <c r="K21" s="55" t="n"/>
       <c r="L21" s="18" t="inlineStr">
@@ -10251,22 +10251,22 @@
       </c>
       <c r="F22" s="38">
         <f>IFERROR(D22+E22+G22,0)</f>
-        <v/>
+        <v>5019.0</v>
       </c>
       <c r="G22" s="39" t="n">
         <v>310</v>
       </c>
       <c r="H22" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B22,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B22+1))</f>
-        <v/>
+        <v>5329.64</v>
       </c>
       <c r="I22" s="41">
         <f>IFERROR(F22-H22,0)</f>
-        <v/>
+        <v>-310.64</v>
       </c>
       <c r="J22" s="42">
         <f>IFERROR(I22/F22,0)</f>
-        <v/>
+        <v>-0.061893</v>
       </c>
       <c r="K22" s="43" t="n"/>
       <c r="L22" s="9" t="inlineStr">
@@ -10311,22 +10311,22 @@
       </c>
       <c r="F23" s="50">
         <f>IFERROR(D23+E23+G23,0)</f>
-        <v/>
+        <v>1843.0</v>
       </c>
       <c r="G23" s="51" t="n">
         <v>283</v>
       </c>
       <c r="H23" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B23,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B23+1))</f>
-        <v/>
+        <v>2379.11</v>
       </c>
       <c r="I23" s="53">
         <f>IFERROR(F23-H23,0)</f>
-        <v/>
+        <v>-536.11</v>
       </c>
       <c r="J23" s="54">
         <f>IFERROR(I23/F23,0)</f>
-        <v/>
+        <v>-0.29089</v>
       </c>
       <c r="K23" s="55" t="n"/>
       <c r="L23" s="18" t="inlineStr">
@@ -10371,22 +10371,22 @@
       </c>
       <c r="F24" s="38">
         <f>IFERROR(D24+E24+G24,0)</f>
-        <v/>
+        <v>3912.0</v>
       </c>
       <c r="G24" s="39" t="n">
         <v>120</v>
       </c>
       <c r="H24" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B24,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B24+1))</f>
-        <v/>
+        <v>4211.86</v>
       </c>
       <c r="I24" s="41">
         <f>IFERROR(F24-H24,0)</f>
-        <v/>
+        <v>-299.86</v>
       </c>
       <c r="J24" s="42">
         <f>IFERROR(I24/F24,0)</f>
-        <v/>
+        <v>-0.076651</v>
       </c>
       <c r="K24" s="43" t="n"/>
       <c r="L24" s="9" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="F25" s="50">
         <f>IFERROR(D25+E25+G25,0)</f>
-        <v/>
+        <v>3757.0</v>
       </c>
       <c r="G25" s="51" t="n"/>
       <c r="H25" s="52">
@@ -10440,11 +10440,11 @@
       </c>
       <c r="I25" s="53">
         <f>IFERROR(F25-H25,0)</f>
-        <v/>
+        <v>-17202.96</v>
       </c>
       <c r="J25" s="54">
         <f>IFERROR(I25/F25,0)</f>
-        <v/>
+        <v>-4.578909</v>
       </c>
       <c r="K25" s="55" t="n"/>
       <c r="L25" s="18" t="inlineStr">
@@ -10489,22 +10489,22 @@
       </c>
       <c r="F26" s="38">
         <f>IFERROR(D26+E26+G26,0)</f>
-        <v/>
+        <v>4408.0</v>
       </c>
       <c r="G26" s="39" t="n">
         <v>135</v>
       </c>
       <c r="H26" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B26,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B26+1))</f>
-        <v/>
+        <v>878.06</v>
       </c>
       <c r="I26" s="41">
         <f>IFERROR(F26-H26,0)</f>
-        <v/>
+        <v>3529.94</v>
       </c>
       <c r="J26" s="42">
         <f>IFERROR(I26/F26,0)</f>
-        <v/>
+        <v>0.800803</v>
       </c>
       <c r="K26" s="43" t="n"/>
       <c r="L26" s="9" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="F27" s="50">
         <f>IFERROR(D27+E27+G27,0)</f>
-        <v/>
+        <v>2334.0</v>
       </c>
       <c r="G27" s="51" t="n"/>
       <c r="H27" s="52">
@@ -10558,11 +10558,11 @@
       </c>
       <c r="I27" s="53">
         <f>IFERROR(F27-H27,0)</f>
-        <v/>
+        <v>-3080.0</v>
       </c>
       <c r="J27" s="54">
         <f>IFERROR(I27/F27,0)</f>
-        <v/>
+        <v>-1.319623</v>
       </c>
       <c r="K27" s="55" t="n"/>
       <c r="L27" s="18" t="inlineStr">
@@ -10612,7 +10612,7 @@
       </c>
       <c r="I28" s="41">
         <f>IFERROR(F28-H28,0)</f>
-        <v/>
+        <v>-1671.0</v>
       </c>
       <c r="J28" s="42" t="n"/>
       <c r="K28" s="43" t="n"/>
@@ -10658,22 +10658,22 @@
       </c>
       <c r="F29" s="50">
         <f>IFERROR(D29+E29+G29,0)</f>
-        <v/>
+        <v>3727.0</v>
       </c>
       <c r="G29" s="51" t="n">
         <v>99</v>
       </c>
       <c r="H29" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B29,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B29+1))</f>
-        <v/>
+        <v>3187.11</v>
       </c>
       <c r="I29" s="53">
         <f>IFERROR(F29-H29,0)</f>
-        <v/>
+        <v>539.89</v>
       </c>
       <c r="J29" s="54">
         <f>IFERROR(I29/F29,0)</f>
-        <v/>
+        <v>0.144859</v>
       </c>
       <c r="K29" s="55" t="n"/>
       <c r="L29" s="18" t="inlineStr">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="F30" s="38">
         <f>IFERROR(D30+E30+G30,0)</f>
-        <v/>
+        <v>5410.0</v>
       </c>
       <c r="G30" s="39" t="n"/>
       <c r="H30" s="40">
@@ -10727,11 +10727,11 @@
       </c>
       <c r="I30" s="41">
         <f>IFERROR(F30-H30,0)</f>
-        <v/>
+        <v>-1213.98</v>
       </c>
       <c r="J30" s="42">
         <f>IFERROR(I30/F30,0)</f>
-        <v/>
+        <v>-0.224396</v>
       </c>
       <c r="K30" s="43" t="n"/>
       <c r="L30" s="9" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="F31" s="50">
         <f>IFERROR(D31+E31+G31,0)</f>
-        <v/>
+        <v>4265.0</v>
       </c>
       <c r="G31" s="51" t="n"/>
       <c r="H31" s="52">
@@ -10785,11 +10785,11 @@
       </c>
       <c r="I31" s="53">
         <f>IFERROR(F31-H31,0)</f>
-        <v/>
+        <v>2923.19</v>
       </c>
       <c r="J31" s="54">
         <f>IFERROR(I31/F31,0)</f>
-        <v/>
+        <v>0.68539</v>
       </c>
       <c r="K31" s="55" t="n"/>
       <c r="L31" s="18" t="inlineStr">
@@ -10834,22 +10834,22 @@
       </c>
       <c r="F32" s="38">
         <f>IFERROR(D32+E32+G32,0)</f>
-        <v/>
+        <v>4166.0</v>
       </c>
       <c r="G32" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B32,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B32+1))</f>
-        <v/>
+        <v>4044.0</v>
       </c>
       <c r="I32" s="41">
         <f>IFERROR(F32-H32,0)</f>
-        <v/>
+        <v>122.0</v>
       </c>
       <c r="J32" s="42">
         <f>IFERROR(I32/F32,0)</f>
-        <v/>
+        <v>0.029285</v>
       </c>
       <c r="K32" s="43" t="n"/>
       <c r="L32" s="9" t="inlineStr">
@@ -10894,22 +10894,22 @@
       </c>
       <c r="F33" s="50">
         <f>IFERROR(D33+E33+G33,0)</f>
-        <v/>
+        <v>6070.0</v>
       </c>
       <c r="G33" s="51" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B33,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B33+1))</f>
-        <v/>
+        <v>901.8</v>
       </c>
       <c r="I33" s="53">
         <f>IFERROR(F33-H33,0)</f>
-        <v/>
+        <v>5168.2</v>
       </c>
       <c r="J33" s="54">
         <f>IFERROR(I33/F33,0)</f>
-        <v/>
+        <v>0.851433</v>
       </c>
       <c r="K33" s="55" t="n"/>
       <c r="L33" s="18" t="inlineStr">
@@ -10954,22 +10954,22 @@
       </c>
       <c r="F34" s="38">
         <f>IFERROR(D34+E34+G34,0)</f>
-        <v/>
+        <v>1811.0</v>
       </c>
       <c r="G34" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B34,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B34+1))</f>
-        <v/>
+        <v>8084.16</v>
       </c>
       <c r="I34" s="41">
         <f>IFERROR(F34-H34,0)</f>
-        <v/>
+        <v>-6273.16</v>
       </c>
       <c r="J34" s="42">
         <f>IFERROR(I34/F34,0)</f>
-        <v/>
+        <v>-3.46392</v>
       </c>
       <c r="K34" s="43" t="n"/>
       <c r="L34" s="9" t="inlineStr">
@@ -11014,22 +11014,22 @@
       </c>
       <c r="F35" s="50">
         <f>IFERROR(D35+E35+G35,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G35" s="51" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B35,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B35+1))</f>
-        <v/>
+        <v>1526.18</v>
       </c>
       <c r="I35" s="53">
         <f>IFERROR(F35-H35,0)</f>
-        <v/>
+        <v>-1526.18</v>
       </c>
       <c r="J35" s="54">
         <f>IFERROR(I35/F35,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K35" s="55" t="n"/>
       <c r="L35" s="18" t="inlineStr">
@@ -11074,22 +11074,22 @@
       </c>
       <c r="F36" s="38">
         <f>IFERROR(D36+E36+G36,0)</f>
-        <v/>
+        <v>4423.0</v>
       </c>
       <c r="G36" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B36,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B36+1))</f>
-        <v/>
+        <v>2858.08</v>
       </c>
       <c r="I36" s="41">
         <f>IFERROR(F36-H36,0)</f>
-        <v/>
+        <v>1564.92</v>
       </c>
       <c r="J36" s="42">
         <f>IFERROR(I36/F36,0)</f>
-        <v/>
+        <v>0.353814</v>
       </c>
       <c r="K36" s="43" t="n"/>
       <c r="L36" s="9" t="inlineStr">
@@ -11134,22 +11134,22 @@
       </c>
       <c r="F37" s="50">
         <f>IFERROR(D37+E37+G37,0)</f>
-        <v/>
+        <v>2786.0</v>
       </c>
       <c r="G37" s="51" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B37,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B37+1))</f>
-        <v/>
+        <v>2541.9</v>
       </c>
       <c r="I37" s="53">
         <f>IFERROR(F37-H37,0)</f>
-        <v/>
+        <v>244.1</v>
       </c>
       <c r="J37" s="54">
         <f>IFERROR(I37/F37,0)</f>
-        <v/>
+        <v>0.087617</v>
       </c>
       <c r="K37" s="55" t="n"/>
       <c r="L37" s="18" t="inlineStr">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="F38" s="38">
         <f>IFERROR(D38+E38+G38,0)</f>
-        <v/>
+        <v>4404.0</v>
       </c>
       <c r="G38" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B38,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B38+1))</f>
-        <v/>
+        <v>2353.0</v>
       </c>
       <c r="I38" s="41">
         <f>IFERROR(F38-H38,0)</f>
-        <v/>
+        <v>2051.0</v>
       </c>
       <c r="J38" s="42">
         <f>IFERROR(I38/F38,0)</f>
-        <v/>
+        <v>0.465713</v>
       </c>
       <c r="K38" s="43" t="n"/>
       <c r="L38" s="9" t="inlineStr">
@@ -11254,22 +11254,22 @@
       </c>
       <c r="F39" s="50">
         <f>IFERROR(D39+E39+G39,0)</f>
-        <v/>
+        <v>4165.0</v>
       </c>
       <c r="G39" s="51" t="n">
         <v>400</v>
       </c>
       <c r="H39" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B39,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B39+1))</f>
-        <v/>
+        <v>2958.83</v>
       </c>
       <c r="I39" s="53">
         <f>IFERROR(F39-H39,0)</f>
-        <v/>
+        <v>1206.17</v>
       </c>
       <c r="J39" s="54">
         <f>IFERROR(I39/F39,0)</f>
-        <v/>
+        <v>0.289597</v>
       </c>
       <c r="K39" s="55" t="n"/>
       <c r="L39" s="18" t="inlineStr">
@@ -11314,22 +11314,22 @@
       </c>
       <c r="F40" s="38">
         <f>IFERROR(D40+E40+G40,0)</f>
-        <v/>
+        <v>6804.0</v>
       </c>
       <c r="G40" s="39" t="n">
         <v>120</v>
       </c>
       <c r="H40" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B40,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B40+1))</f>
-        <v/>
+        <v>1483.0</v>
       </c>
       <c r="I40" s="41">
         <f>IFERROR(F40-H40,0)</f>
-        <v/>
+        <v>5321.0</v>
       </c>
       <c r="J40" s="42">
         <f>IFERROR(I40/F40,0)</f>
-        <v/>
+        <v>0.78204</v>
       </c>
       <c r="K40" s="43" t="n"/>
       <c r="L40" s="9" t="inlineStr">
@@ -11374,22 +11374,22 @@
       </c>
       <c r="F41" s="50">
         <f>IFERROR(D41+E41+G41,0)</f>
-        <v/>
+        <v>2251.0</v>
       </c>
       <c r="G41" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B41,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B41+1))</f>
-        <v/>
+        <v>9320.81</v>
       </c>
       <c r="I41" s="259">
         <f>IFERROR(F41-H41,0)</f>
-        <v/>
+        <v>-7069.81</v>
       </c>
       <c r="J41" s="260">
         <f>IFERROR(I41/F41,0)</f>
-        <v/>
+        <v>-3.140742</v>
       </c>
       <c r="K41" s="254" t="n"/>
       <c r="L41" s="261" t="inlineStr">
@@ -11434,22 +11434,22 @@
       </c>
       <c r="F42" s="38">
         <f>IFERROR(D42+E42+G42,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G42" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B42,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B42+1))</f>
-        <v/>
+        <v>2065.85</v>
       </c>
       <c r="I42" s="274">
         <f>IFERROR(F42-H42,0)</f>
-        <v/>
+        <v>-2065.85</v>
       </c>
       <c r="J42" s="275">
         <f>IFERROR(I42/F42,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K42" s="250" t="n"/>
       <c r="L42" s="276" t="inlineStr">
@@ -11494,22 +11494,22 @@
       </c>
       <c r="F43" s="50">
         <f>IFERROR(D43+E43+G43,0)</f>
-        <v/>
+        <v>4259.0</v>
       </c>
       <c r="G43" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B43,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B43+1))</f>
-        <v/>
+        <v>1451.0</v>
       </c>
       <c r="I43" s="259">
         <f>IFERROR(F43-H43,0)</f>
-        <v/>
+        <v>2808.0</v>
       </c>
       <c r="J43" s="260">
         <f>IFERROR(I43/F43,0)</f>
-        <v/>
+        <v>0.65931</v>
       </c>
       <c r="K43" s="254" t="n"/>
       <c r="L43" s="261" t="inlineStr">
@@ -11554,22 +11554,22 @@
       </c>
       <c r="F44" s="38">
         <f>IFERROR(D44+E44+G44,0)</f>
-        <v/>
+        <v>2967.0</v>
       </c>
       <c r="G44" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B44,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B44+1))</f>
-        <v/>
+        <v>757.13</v>
       </c>
       <c r="I44" s="274">
         <f>IFERROR(F44-H44,0)</f>
-        <v/>
+        <v>2209.87</v>
       </c>
       <c r="J44" s="275">
         <f>IFERROR(I44/F44,0)</f>
-        <v/>
+        <v>0.744816</v>
       </c>
       <c r="K44" s="250" t="n"/>
       <c r="L44" s="276" t="inlineStr">
@@ -11614,22 +11614,22 @@
       </c>
       <c r="F45" s="50">
         <f>IFERROR(D45+E45+G45,0)</f>
-        <v/>
+        <v>3589.0</v>
       </c>
       <c r="G45" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B45,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B45+1))</f>
-        <v/>
+        <v>3781.35</v>
       </c>
       <c r="I45" s="259">
         <f>IFERROR(F45-H45,0)</f>
-        <v/>
+        <v>-192.35</v>
       </c>
       <c r="J45" s="260">
         <f>IFERROR(I45/F45,0)</f>
-        <v/>
+        <v>-0.053594</v>
       </c>
       <c r="K45" s="254" t="n"/>
       <c r="L45" s="261" t="inlineStr">
@@ -11674,22 +11674,22 @@
       </c>
       <c r="F46" s="38">
         <f>IFERROR(D46+E46+G46,0)</f>
-        <v/>
+        <v>3588.0</v>
       </c>
       <c r="G46" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B46,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B46+1))</f>
-        <v/>
+        <v>1228.0</v>
       </c>
       <c r="I46" s="274">
         <f>IFERROR(F46-H46,0)</f>
-        <v/>
+        <v>2360.0</v>
       </c>
       <c r="J46" s="275">
         <f>IFERROR(I46/F46,0)</f>
-        <v/>
+        <v>0.657748</v>
       </c>
       <c r="K46" s="250" t="n"/>
       <c r="L46" s="276" t="inlineStr">
@@ -11734,22 +11734,22 @@
       </c>
       <c r="F47" s="50">
         <f>IFERROR(D47+E47+G47,0)</f>
-        <v/>
+        <v>4477.0</v>
       </c>
       <c r="G47" s="257" t="n">
         <v>165</v>
       </c>
       <c r="H47" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B47,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B47+1))</f>
-        <v/>
+        <v>1945.53</v>
       </c>
       <c r="I47" s="259">
         <f>IFERROR(F47-H47,0)</f>
-        <v/>
+        <v>2531.47</v>
       </c>
       <c r="J47" s="260">
         <f>IFERROR(I47/F47,0)</f>
-        <v/>
+        <v>0.565439</v>
       </c>
       <c r="K47" s="254" t="n"/>
       <c r="L47" s="261" t="inlineStr">
@@ -11794,22 +11794,22 @@
       </c>
       <c r="F48" s="38">
         <f>IFERROR(D48+E48+G48,0)</f>
-        <v/>
+        <v>2029.0</v>
       </c>
       <c r="G48" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B48,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B48+1))</f>
-        <v/>
+        <v>5250.0</v>
       </c>
       <c r="I48" s="274">
         <f>IFERROR(F48-H48,0)</f>
-        <v/>
+        <v>-3221.0</v>
       </c>
       <c r="J48" s="275">
         <f>IFERROR(I48/F48,0)</f>
-        <v/>
+        <v>-1.587482</v>
       </c>
       <c r="K48" s="250" t="n"/>
       <c r="L48" s="276" t="inlineStr">
@@ -11854,22 +11854,22 @@
       </c>
       <c r="F49" s="50">
         <f>IFERROR(D49+E49+G49,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G49" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B49,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B49+1))</f>
-        <v/>
+        <v>3865.06</v>
       </c>
       <c r="I49" s="259">
         <f>IFERROR(F49-H49,0)</f>
-        <v/>
+        <v>-3865.06</v>
       </c>
       <c r="J49" s="260">
         <f>IFERROR(I49/F49,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K49" s="254" t="n"/>
       <c r="L49" s="261" t="inlineStr">
@@ -11914,22 +11914,22 @@
       </c>
       <c r="F50" s="38">
         <f>IFERROR(D50+E50+G50,0)</f>
-        <v/>
+        <v>3389.0</v>
       </c>
       <c r="G50" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B50,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B50+1))</f>
-        <v/>
+        <v>2683.27</v>
       </c>
       <c r="I50" s="274">
         <f>IFERROR(F50-H50,0)</f>
-        <v/>
+        <v>705.73</v>
       </c>
       <c r="J50" s="275">
         <f>IFERROR(I50/F50,0)</f>
-        <v/>
+        <v>0.208241</v>
       </c>
       <c r="K50" s="250" t="n"/>
       <c r="L50" s="276" t="inlineStr">
@@ -11974,22 +11974,22 @@
       </c>
       <c r="F51" s="50">
         <f>IFERROR(D51+E51+G51,0)</f>
-        <v/>
+        <v>4133.0</v>
       </c>
       <c r="G51" s="257" t="n">
         <v>55</v>
       </c>
       <c r="H51" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B51,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B51+1))</f>
-        <v/>
+        <v>1581.27</v>
       </c>
       <c r="I51" s="259">
         <f>IFERROR(F51-H51,0)</f>
-        <v/>
+        <v>2551.73</v>
       </c>
       <c r="J51" s="260">
         <f>IFERROR(I51/F51,0)</f>
-        <v/>
+        <v>0.617404</v>
       </c>
       <c r="K51" s="254" t="n"/>
       <c r="L51" s="261" t="inlineStr">
@@ -12034,22 +12034,22 @@
       </c>
       <c r="F52" s="38">
         <f>IFERROR(D52+E52+G52,0)</f>
-        <v/>
+        <v>4522.0</v>
       </c>
       <c r="G52" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B52,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B52+1))</f>
-        <v/>
+        <v>2341.23</v>
       </c>
       <c r="I52" s="274">
         <f>IFERROR(F52-H52,0)</f>
-        <v/>
+        <v>2180.77</v>
       </c>
       <c r="J52" s="275">
         <f>IFERROR(I52/F52,0)</f>
-        <v/>
+        <v>0.482258</v>
       </c>
       <c r="K52" s="250" t="n"/>
       <c r="L52" s="276" t="inlineStr">
@@ -12094,22 +12094,22 @@
       </c>
       <c r="F53" s="50">
         <f>IFERROR(D53+E53+G53,0)</f>
-        <v/>
+        <v>3108.0</v>
       </c>
       <c r="G53" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B53,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B53+1))</f>
-        <v/>
+        <v>318.0</v>
       </c>
       <c r="I53" s="259">
         <f>IFERROR(F53-H53,0)</f>
-        <v/>
+        <v>2790.0</v>
       </c>
       <c r="J53" s="260">
         <f>IFERROR(I53/F53,0)</f>
-        <v/>
+        <v>0.897683</v>
       </c>
       <c r="K53" s="254" t="inlineStr">
         <is>
@@ -12158,22 +12158,22 @@
       </c>
       <c r="F54" s="38">
         <f>IFERROR(D54+E54+G54,0)</f>
-        <v/>
+        <v>6077.0</v>
       </c>
       <c r="G54" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B54,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B54+1))</f>
-        <v/>
+        <v>2809.6</v>
       </c>
       <c r="I54" s="274">
         <f>IFERROR(F54-H54,0)</f>
-        <v/>
+        <v>3267.4</v>
       </c>
       <c r="J54" s="275">
         <f>IFERROR(I54/F54,0)</f>
-        <v/>
+        <v>0.537667</v>
       </c>
       <c r="K54" s="250" t="inlineStr">
         <is>
@@ -12222,22 +12222,22 @@
       </c>
       <c r="F55" s="50">
         <f>IFERROR(D55+E55+G55,0)</f>
-        <v/>
+        <v>2634.0</v>
       </c>
       <c r="G55" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B55,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B55+1))</f>
-        <v/>
+        <v>6877.73</v>
       </c>
       <c r="I55" s="259">
         <f>IFERROR(F55-H55,0)</f>
-        <v/>
+        <v>-4243.73</v>
       </c>
       <c r="J55" s="260">
         <f>IFERROR(I55/F55,0)</f>
-        <v/>
+        <v>-1.611135</v>
       </c>
       <c r="K55" s="254" t="n"/>
       <c r="L55" s="261" t="inlineStr">
@@ -12282,22 +12282,22 @@
       </c>
       <c r="F56" s="38">
         <f>IFERROR(D56+E56+G56,0)</f>
-        <v/>
+        <v>3690.0</v>
       </c>
       <c r="G56" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B56,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B56+1))</f>
-        <v/>
+        <v>4200.0</v>
       </c>
       <c r="I56" s="274">
         <f>IFERROR(F56-H56,0)</f>
-        <v/>
+        <v>-510.0</v>
       </c>
       <c r="J56" s="275">
         <f>IFERROR(I56/F56,0)</f>
-        <v/>
+        <v>-0.138211</v>
       </c>
       <c r="K56" s="250" t="n"/>
       <c r="L56" s="276" t="inlineStr">
@@ -12342,22 +12342,22 @@
       </c>
       <c r="F57" s="50">
         <f>IFERROR(D57+E57+G57,0)</f>
-        <v/>
+        <v>3660.0</v>
       </c>
       <c r="G57" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B57,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B57+1))</f>
-        <v/>
+        <v>49.0</v>
       </c>
       <c r="I57" s="259">
         <f>IFERROR(F57-H57,0)</f>
-        <v/>
+        <v>3611.0</v>
       </c>
       <c r="J57" s="260">
         <f>IFERROR(I57/F57,0)</f>
-        <v/>
+        <v>0.986612</v>
       </c>
       <c r="K57" s="254" t="n"/>
       <c r="L57" s="261" t="inlineStr">
@@ -12402,22 +12402,22 @@
       </c>
       <c r="F58" s="50">
         <f>IFERROR(D58+E58+G58+U58,0)</f>
-        <v/>
+        <v>3688.0</v>
       </c>
       <c r="G58" s="257" t="n">
         <v>195</v>
       </c>
       <c r="H58" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B58,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B58+1))</f>
-        <v/>
+        <v>1415.43</v>
       </c>
       <c r="I58" s="259">
         <f>IFERROR(F58-H58,0)</f>
-        <v/>
+        <v>2272.57</v>
       </c>
       <c r="J58" s="260">
         <f>IFERROR(I58/F58,0)</f>
-        <v/>
+        <v>0.616207</v>
       </c>
       <c r="K58" s="254" t="n"/>
       <c r="L58" s="261" t="inlineStr">
@@ -12466,22 +12466,22 @@
       </c>
       <c r="F59" s="50">
         <f>IFERROR(D59+E59+G59+U59,0)</f>
-        <v/>
+        <v>6015.0</v>
       </c>
       <c r="G59" s="257" t="n">
         <v>120</v>
       </c>
       <c r="H59" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B59,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B59+1))</f>
-        <v/>
+        <v>1820.89</v>
       </c>
       <c r="I59" s="259">
         <f>IFERROR(F59-H59,0)</f>
-        <v/>
+        <v>4194.11</v>
       </c>
       <c r="J59" s="260">
         <f>IFERROR(I59/F59,0)</f>
-        <v/>
+        <v>0.697275</v>
       </c>
       <c r="K59" s="254" t="n"/>
       <c r="L59" s="261" t="inlineStr">
@@ -12530,22 +12530,22 @@
       </c>
       <c r="F60" s="50">
         <f>IFERROR(D60+E60+G60+U60,0)</f>
-        <v/>
+        <v>3500.0</v>
       </c>
       <c r="G60" s="257" t="n">
         <v>70</v>
       </c>
       <c r="H60" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B60,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B60+1))</f>
-        <v/>
+        <v>2094.0</v>
       </c>
       <c r="I60" s="259">
         <f>IFERROR(F60-H60,0)</f>
-        <v/>
+        <v>1406.0</v>
       </c>
       <c r="J60" s="260">
         <f>IFERROR(I60/F60,0)</f>
-        <v/>
+        <v>0.401714</v>
       </c>
       <c r="K60" s="254" t="n"/>
       <c r="L60" s="261" t="inlineStr">
@@ -12594,22 +12594,22 @@
       </c>
       <c r="F61" s="50">
         <f>IFERROR(D61+E61+G61+U61,0)</f>
-        <v/>
+        <v>2725.0</v>
       </c>
       <c r="G61" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B61,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B61+1))</f>
-        <v/>
+        <v>10207.0</v>
       </c>
       <c r="I61" s="259">
         <f>IFERROR(F61-H61,0)</f>
-        <v/>
+        <v>-7482.0</v>
       </c>
       <c r="J61" s="260">
         <f>IFERROR(I61/F61,0)</f>
-        <v/>
+        <v>-2.745688</v>
       </c>
       <c r="K61" s="254" t="n"/>
       <c r="L61" s="261" t="inlineStr">
@@ -12658,22 +12658,22 @@
       </c>
       <c r="F62" s="50">
         <f>IFERROR(D62+E62+G62+U62+Y62,0)</f>
-        <v/>
+        <v>3990.0</v>
       </c>
       <c r="G62" s="257" t="n">
         <v>120</v>
       </c>
       <c r="H62" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B62,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B62+1))</f>
-        <v/>
+        <v>3142.0</v>
       </c>
       <c r="I62" s="259">
         <f>IFERROR(F62-H62,0)</f>
-        <v/>
+        <v>848.0</v>
       </c>
       <c r="J62" s="260">
         <f>IFERROR(I62/F62,0)</f>
-        <v/>
+        <v>0.212531</v>
       </c>
       <c r="K62" s="254" t="n"/>
       <c r="L62" s="261" t="inlineStr">
@@ -12726,22 +12726,22 @@
       </c>
       <c r="F63" s="50">
         <f>IFERROR(D63+E63+G63+U63+Y63,0)</f>
-        <v/>
+        <v>3915.0</v>
       </c>
       <c r="G63" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B63,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B63+1))</f>
-        <v/>
+        <v>596.38</v>
       </c>
       <c r="I63" s="259">
         <f>IFERROR(F63-H63,0)</f>
-        <v/>
+        <v>3318.62</v>
       </c>
       <c r="J63" s="260">
         <f>IFERROR(I63/F63,0)</f>
-        <v/>
+        <v>0.847668</v>
       </c>
       <c r="K63" s="254" t="n"/>
       <c r="L63" s="261" t="inlineStr">
@@ -12794,22 +12794,22 @@
       </c>
       <c r="F64" s="50">
         <f>IFERROR(D64+E64+G64+U64+Y64,0)</f>
-        <v/>
+        <v>5565.0</v>
       </c>
       <c r="G64" s="257" t="n">
         <v>130</v>
       </c>
       <c r="H64" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B64,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B64+1))</f>
-        <v/>
+        <v>2606.86</v>
       </c>
       <c r="I64" s="259">
         <f>IFERROR(F64-H64,0)</f>
-        <v/>
+        <v>2958.14</v>
       </c>
       <c r="J64" s="260">
         <f>IFERROR(I64/F64,0)</f>
-        <v/>
+        <v>0.531562</v>
       </c>
       <c r="K64" s="254" t="n"/>
       <c r="L64" s="261" t="inlineStr">
@@ -12862,22 +12862,22 @@
       </c>
       <c r="F65" s="50">
         <f>IFERROR(D65+E65+G65+U65+Y65,0)</f>
-        <v/>
+        <v>12495.0</v>
       </c>
       <c r="G65" s="257" t="n">
         <v>2385</v>
       </c>
       <c r="H65" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B65,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B65+1))</f>
-        <v/>
+        <v>1657.0</v>
       </c>
       <c r="I65" s="259">
         <f>IFERROR(F65-H65,0)</f>
-        <v/>
+        <v>10838.0</v>
       </c>
       <c r="J65" s="260">
         <f>IFERROR(I65/F65,0)</f>
-        <v/>
+        <v>0.867387</v>
       </c>
       <c r="K65" s="254" t="n"/>
       <c r="L65" s="261" t="inlineStr">
@@ -12930,22 +12930,22 @@
       </c>
       <c r="F66" s="50">
         <f>IFERROR(D66+E66+G66+U66+Y66,0)</f>
-        <v/>
+        <v>2622.0</v>
       </c>
       <c r="G66" s="257" t="n">
         <v>300</v>
       </c>
       <c r="H66" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B66,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B66+1))</f>
-        <v/>
+        <v>1951.0</v>
       </c>
       <c r="I66" s="259">
         <f>IFERROR(F66-H66,0)</f>
-        <v/>
+        <v>671.0</v>
       </c>
       <c r="J66" s="260">
         <f>IFERROR(I66/F66,0)</f>
-        <v/>
+        <v>0.255912</v>
       </c>
       <c r="K66" s="254" t="n"/>
       <c r="L66" s="261" t="inlineStr">
@@ -12998,22 +12998,22 @@
       </c>
       <c r="F67" s="50">
         <f>IFERROR(D67+E67+G67+U67+Y67,0)</f>
-        <v/>
+        <v>2900.0</v>
       </c>
       <c r="G67" s="257" t="n">
         <v>290</v>
       </c>
       <c r="H67" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B67,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B67+1))</f>
-        <v/>
+        <v>6770.0</v>
       </c>
       <c r="I67" s="259">
         <f>IFERROR(F67-H67,0)</f>
-        <v/>
+        <v>-3870.0</v>
       </c>
       <c r="J67" s="260">
         <f>IFERROR(I67/F67,0)</f>
-        <v/>
+        <v>-1.334483</v>
       </c>
       <c r="K67" s="254" t="n"/>
       <c r="L67" s="261" t="inlineStr">
@@ -13066,22 +13066,22 @@
       </c>
       <c r="F68" s="50">
         <f>IFERROR(D68+E68+G68+U68+Y68,0)</f>
-        <v/>
+        <v>4955.0</v>
       </c>
       <c r="G68" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H68" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B68,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B68+1))</f>
-        <v/>
+        <v>2459.0</v>
       </c>
       <c r="I68" s="259">
         <f>IFERROR(F68-H68,0)</f>
-        <v/>
+        <v>2496.0</v>
       </c>
       <c r="J68" s="260">
         <f>IFERROR(I68/F68,0)</f>
-        <v/>
+        <v>0.503734</v>
       </c>
       <c r="K68" s="254" t="n"/>
       <c r="L68" s="261" t="inlineStr">
@@ -13134,22 +13134,22 @@
       </c>
       <c r="F69" s="50">
         <f>IFERROR(D69+E69+G69+U69+Y69,0)</f>
-        <v/>
+        <v>5480.0</v>
       </c>
       <c r="G69" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H69" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B69,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B69+1))</f>
-        <v/>
+        <v>2197.0</v>
       </c>
       <c r="I69" s="259">
         <f>IFERROR(F69-H69,0)</f>
-        <v/>
+        <v>3283.0</v>
       </c>
       <c r="J69" s="260">
         <f>IFERROR(I69/F69,0)</f>
-        <v/>
+        <v>0.599088</v>
       </c>
       <c r="K69" s="254" t="n"/>
       <c r="L69" s="261" t="inlineStr">
@@ -13202,22 +13202,22 @@
       </c>
       <c r="F70" s="50">
         <f>IFERROR(D70+E70+G70+U70+Y70,0)</f>
-        <v/>
+        <v>5205.0</v>
       </c>
       <c r="G70" s="257" t="n">
         <v>355</v>
       </c>
       <c r="H70" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B70,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B70+1))</f>
-        <v/>
+        <v>3819.0</v>
       </c>
       <c r="I70" s="259">
         <f>IFERROR(F70-H70,0)</f>
-        <v/>
+        <v>1386.0</v>
       </c>
       <c r="J70" s="260">
         <f>IFERROR(I70/F70,0)</f>
-        <v/>
+        <v>0.266282</v>
       </c>
       <c r="K70" s="254" t="n"/>
       <c r="L70" s="261" t="inlineStr">
@@ -13254,33 +13254,72 @@
       <c r="AB70" s="292" t="n"/>
     </row>
     <row r="71" ht="16.5" customHeight="1" s="313">
-      <c r="B71" s="34" t="n"/>
-      <c r="C71" s="47" t="n"/>
-      <c r="D71" s="48" t="n"/>
-      <c r="E71" s="49" t="n"/>
-      <c r="F71" s="50" t="n"/>
-      <c r="G71" s="51" t="n"/>
-      <c r="H71" s="52" t="n"/>
-      <c r="I71" s="53" t="n"/>
-      <c r="J71" s="54" t="n"/>
-      <c r="K71" s="55" t="n"/>
-      <c r="L71" s="18" t="n"/>
-      <c r="M71" s="21" t="n"/>
-      <c r="N71" s="56" t="n"/>
-      <c r="O71" s="57" t="n"/>
-      <c r="P71" s="58" t="n"/>
-      <c r="Q71" s="56" t="n"/>
-      <c r="R71" s="56" t="n"/>
-      <c r="S71" s="56" t="n"/>
-      <c r="T71" s="56" t="n"/>
-      <c r="U71" s="56" t="n"/>
-      <c r="V71" s="56" t="n"/>
-      <c r="W71" s="56" t="n"/>
-      <c r="X71" s="56" t="n"/>
-      <c r="Y71" s="56" t="n"/>
-      <c r="Z71" s="56" t="n"/>
-      <c r="AA71" s="56" t="n"/>
-      <c r="AB71" s="56" t="n"/>
+      <c r="B71" s="420" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C71" s="255" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D71" s="256" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E71" s="49" t="n">
+        <v>2380</v>
+      </c>
+      <c r="F71" s="50">
+        <f>IFERROR(D71+E71+G71+U71+Y71,0)</f>
+        <v>4075.0</v>
+      </c>
+      <c r="G71" s="257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B71,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B71+1))</f>
+        <v>5348.83</v>
+      </c>
+      <c r="I71" s="259">
+        <f>IFERROR(F71-H71,0)</f>
+        <v>-1273.83</v>
+      </c>
+      <c r="J71" s="260">
+        <f>IFERROR(I71/F71,0)</f>
+        <v>-0.312596</v>
+      </c>
+      <c r="K71" s="254" t="n"/>
+      <c r="L71" s="261" t="inlineStr">
+        <is>
+          <t>EOD close (MP + cash; no BBVA/Soft, no transfers). Heavy Guimar packaging restock day.</t>
+        </is>
+      </c>
+      <c r="M71" s="291" t="n"/>
+      <c r="N71" s="292" t="n"/>
+      <c r="O71" s="293" t="n"/>
+      <c r="P71" s="294" t="n"/>
+      <c r="Q71" s="292" t="n"/>
+      <c r="R71" s="421">
+        <f>IFERROR(D71*$T$7,0)</f>
+        <v/>
+      </c>
+      <c r="S71" s="292" t="n"/>
+      <c r="T71" s="292" t="n"/>
+      <c r="U71" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" s="292" t="n"/>
+      <c r="X71" s="292" t="n"/>
+      <c r="Y71" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="292" t="n"/>
+      <c r="AB71" s="292" t="n"/>
     </row>
     <row r="72" ht="16.5" customHeight="1" s="313">
       <c r="B72" s="34" t="n"/>
@@ -22038,7 +22077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J524"/>
+  <dimension ref="A1:J532"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="313" min="1" max="1"/>
@@ -44071,6 +44110,350 @@
         </is>
       </c>
       <c r="J524" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="B525" s="422" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C525" s="305" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D525" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E525" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F525" s="307" t="n">
+        <v>105</v>
+      </c>
+      <c r="G525" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H525" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I525" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J525" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="B526" s="422" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C526" s="305" t="inlineStr">
+        <is>
+          <t>Carnes</t>
+        </is>
+      </c>
+      <c r="D526" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E526" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F526" s="307" t="n">
+        <v>600</v>
+      </c>
+      <c r="G526" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H526" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I526" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J526" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="B527" s="422" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C527" s="305" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D527" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E527" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F527" s="307" t="n">
+        <v>220</v>
+      </c>
+      <c r="G527" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H527" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I527" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J527" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="B528" s="422" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C528" s="305" t="inlineStr">
+        <is>
+          <t>Vasos plast. 12 + Reyma tapas + bolsa negra + stretch film</t>
+        </is>
+      </c>
+      <c r="D528" s="306" t="inlineStr">
+        <is>
+          <t>Guimar Polietilenos</t>
+        </is>
+      </c>
+      <c r="E528" s="305" t="inlineStr">
+        <is>
+          <t>Packaging/Disposables</t>
+        </is>
+      </c>
+      <c r="F528" s="307" t="n">
+        <v>1544.98</v>
+      </c>
+      <c r="G528" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H528" s="308" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I528" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J528" s="418" t="inlineStr">
+        <is>
+          <t>Folio AK93904 10:48. Pagado con tarjeta de Lohith pero YA reembolsado con dinero del restaurante -&gt; gasto del restaurante, sin entrada en Owner Ledger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="B529" s="422" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C529" s="305" t="inlineStr">
+        <is>
+          <t>Elote Herdez, agua mineral, detergente 5kg, tortillas, bolillo, rosca de nuez</t>
+        </is>
+      </c>
+      <c r="D529" s="306" t="inlineStr">
+        <is>
+          <t>Chedraui Selecto</t>
+        </is>
+      </c>
+      <c r="E529" s="305" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F529" s="307" t="n">
+        <v>515.4</v>
+      </c>
+      <c r="G529" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H529" s="308" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I529" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J529" s="418" t="inlineStr">
+        <is>
+          <t>Debito BBVA ***3982 AUT 006060; 23-Jul 11:34; 16 articulos</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="B530" s="422" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C530" s="305" t="inlineStr">
+        <is>
+          <t>Contenedor termico 8x8D + papel alimenticio + bolsa poliseda + bolsa en rollo</t>
+        </is>
+      </c>
+      <c r="D530" s="306" t="inlineStr">
+        <is>
+          <t>Guimar Polietilenos</t>
+        </is>
+      </c>
+      <c r="E530" s="305" t="inlineStr">
+        <is>
+          <t>Packaging/Disposables</t>
+        </is>
+      </c>
+      <c r="F530" s="307" t="n">
+        <v>1481.45</v>
+      </c>
+      <c r="G530" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H530" s="308" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I530" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J530" s="418" t="inlineStr">
+        <is>
+          <t>Folio AK93900 10:37. Term.8x8D 8x115.25=922 + papel alim. 275 + bolsa poliseda 2x82=164 + bolsa rollo 1.65x73=120.45. Tarjeta de Lohith, YA reembolsado con dinero del restaurante -&gt; sin entrada en Owner Ledger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="B531" s="422" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C531" s="305" t="inlineStr">
+        <is>
+          <t>Arroz (Oxxo)</t>
+        </is>
+      </c>
+      <c r="D531" s="306" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E531" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F531" s="307" t="n">
+        <v>35</v>
+      </c>
+      <c r="G531" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H531" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I531" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J531" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="B532" s="422" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C532" s="305" t="inlineStr">
+        <is>
+          <t>Pan y salsas</t>
+        </is>
+      </c>
+      <c r="D532" s="306" t="inlineStr">
+        <is>
+          <t>Pan Reales</t>
+        </is>
+      </c>
+      <c r="E532" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F532" s="307" t="n">
+        <v>847</v>
+      </c>
+      <c r="G532" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H532" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I532" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J532" s="418" t="inlineStr">
         <is>
           <t>No receipt; cash</t>
         </is>
@@ -49511,22 +49894,46 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="263" t="n"/>
-      <c r="B78" s="262" t="n"/>
+      <c r="A78" s="263" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B78" s="262" t="inlineStr">
+        <is>
+          <t>John (Week 9: 13-19 Jul)</t>
+        </is>
+      </c>
       <c r="C78" s="262" t="n"/>
-      <c r="D78" s="264" t="n"/>
+      <c r="D78" s="264" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="263" t="n"/>
-      <c r="B79" s="262" t="n"/>
+      <c r="A79" s="263" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B79" s="262" t="inlineStr">
+        <is>
+          <t>Duvi/Debi (Week 9: 13-19 Jul)</t>
+        </is>
+      </c>
       <c r="C79" s="262" t="n"/>
-      <c r="D79" s="264" t="n"/>
+      <c r="D79" s="264" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="263" t="n"/>
-      <c r="B80" s="262" t="n"/>
+      <c r="A80" s="263" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B80" s="262" t="inlineStr">
+        <is>
+          <t>Samu (Week 9: 13-19 Jul)</t>
+        </is>
+      </c>
       <c r="C80" s="262" t="n"/>
-      <c r="D80" s="264" t="n"/>
+      <c r="D80" s="264" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="263" t="n"/>
@@ -54325,7 +54732,7 @@
     <row r="25">
       <c r="A25" s="415" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Ingredients - Bread</t>
         </is>
       </c>
       <c r="B25" s="413">
@@ -54352,7 +54759,7 @@
     <row r="26">
       <c r="A26" s="415" t="inlineStr">
         <is>
-          <t>Ingredients - Bread</t>
+          <t>Supplies / Other</t>
         </is>
       </c>
       <c r="B26" s="413">
@@ -54460,7 +54867,7 @@
     <row r="30">
       <c r="A30" s="415" t="inlineStr">
         <is>
-          <t>Ingredients - Fruit</t>
+          <t>Packaging/Disposables</t>
         </is>
       </c>
       <c r="B30" s="413">
@@ -54487,7 +54894,7 @@
     <row r="31">
       <c r="A31" s="415" t="inlineStr">
         <is>
-          <t>Utilities / Gas</t>
+          <t>Ingredients - Fruit</t>
         </is>
       </c>
       <c r="B31" s="413">
@@ -54514,7 +54921,7 @@
     <row r="32">
       <c r="A32" s="415" t="inlineStr">
         <is>
-          <t>Ingredients - Other</t>
+          <t>Utilities / Gas</t>
         </is>
       </c>
       <c r="B32" s="413">
@@ -54541,7 +54948,7 @@
     <row r="33">
       <c r="A33" s="415" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Ingredients - Other</t>
         </is>
       </c>
       <c r="B33" s="413">
@@ -54568,7 +54975,7 @@
     <row r="34">
       <c r="A34" s="415" t="inlineStr">
         <is>
-          <t>Utilities/Internet</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="B34" s="413">
@@ -54595,7 +55002,7 @@
     <row r="35">
       <c r="A35" s="415" t="inlineStr">
         <is>
-          <t>Kitchen Supplies</t>
+          <t>Utilities/Internet</t>
         </is>
       </c>
       <c r="B35" s="413">
@@ -54622,7 +55029,7 @@
     <row r="36">
       <c r="A36" s="415" t="inlineStr">
         <is>
-          <t>Software / Subscription</t>
+          <t>Kitchen Supplies</t>
         </is>
       </c>
       <c r="B36" s="413">
@@ -54649,7 +55056,7 @@
     <row r="37">
       <c r="A37" s="415" t="inlineStr">
         <is>
-          <t>Staff - Advance</t>
+          <t>Software / Subscription</t>
         </is>
       </c>
       <c r="B37" s="413">
@@ -54676,7 +55083,7 @@
     <row r="38">
       <c r="A38" s="415" t="inlineStr">
         <is>
-          <t>Utilities / Internet</t>
+          <t>Staff - Advance</t>
         </is>
       </c>
       <c r="B38" s="413">
@@ -54703,7 +55110,7 @@
     <row r="39">
       <c r="A39" s="415" t="inlineStr">
         <is>
-          <t>Packaging / Disposables</t>
+          <t>Utilities / Internet</t>
         </is>
       </c>
       <c r="B39" s="413">
@@ -54730,7 +55137,7 @@
     <row r="40">
       <c r="A40" s="415" t="inlineStr">
         <is>
-          <t>Ingredients - Desserts</t>
+          <t>Packaging / Disposables</t>
         </is>
       </c>
       <c r="B40" s="413">
@@ -54757,7 +55164,7 @@
     <row r="41">
       <c r="A41" s="415" t="inlineStr">
         <is>
-          <t>Packaging/Disposables</t>
+          <t>Ingredients - Desserts</t>
         </is>
       </c>
       <c r="B41" s="413">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -1347,7 +1347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22"/>
   </cellStyleXfs>
-  <cellXfs count="434">
+  <cellXfs count="440">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2454,6 +2454,22 @@
     <xf numFmtId="175" fontId="98" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="175" fontId="97" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="22" fillId="19" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="46" fillId="19" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="14" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="17" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="46" fillId="19" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5908,7 +5924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="313" min="1" max="1"/>
@@ -7389,30 +7405,63 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="231" t="inlineStr">
+      <c r="A47" s="439" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B47" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 27-Jul)</t>
+        </is>
+      </c>
+      <c r="C47" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D47" s="232" t="n"/>
+      <c r="E47" s="233" t="n">
+        <v>700</v>
+      </c>
+      <c r="F47" s="233">
+        <f>IFERROR(F46+D47-E47,0)</f>
+        <v/>
+      </c>
+      <c r="G47" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H47" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="439" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B47" s="232" t="n"/>
-      <c r="C47" s="232" t="n"/>
-      <c r="D47" s="232">
-        <f>SUM(D4:D46)</f>
+      <c r="B48" s="232" t="n"/>
+      <c r="C48" s="232" t="n"/>
+      <c r="D48" s="232">
+        <f>SUM(D4:D47)</f>
         <v/>
       </c>
-      <c r="E47" s="233">
-        <f>SUM(E4:E46)</f>
+      <c r="E48" s="233">
+        <f>SUM(E4:E47)</f>
         <v/>
       </c>
-      <c r="F47" s="233">
-        <f>F46</f>
+      <c r="F48" s="233">
+        <f>F47</f>
         <v/>
       </c>
-      <c r="G47" s="232">
-        <f>IF(F46&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F46,"#,##0"),IF(F46&lt;0,"Lohith holds $"&amp;TEXT(ABS(F46),"#,##0"),"Zero balance"))</f>
+      <c r="G48" s="232">
+        <f>IF(F47&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F47,"#,##0"),IF(F47&lt;0,"Lohith holds $"&amp;TEXT(ABS(F47),"#,##0"),"Zero balance"))</f>
         <v/>
       </c>
-      <c r="H47" s="232" t="n"/>
+      <c r="H48" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9246,45 +9295,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v/>
+        <v>3180.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v/>
+        <v>700.0</v>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>5348.83</v>
+        <v>928.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>-1273.83</v>
+        <v>2252.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>-0.312596</v>
+        <v>0.708176</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v/>
+        <v>3180.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v/>
+        <v>3180.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v/>
+        <v>100996.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v/>
+        <v>928.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v/>
+        <v>2252.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="313">
@@ -9440,7 +9489,7 @@
       <c r="G8" s="39" t="n"/>
       <c r="H8" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B8,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B8+1))</f>
-        <v/>
+        <v>2629.0</v>
       </c>
       <c r="I8" s="41">
         <f>IFERROR(F8-H8,0)</f>
@@ -9463,7 +9512,7 @@
       <c r="Q8" s="44" t="n"/>
       <c r="R8" s="44">
         <f>IFERROR(D8*$T$7,0)</f>
-        <v/>
+        <v>90.5</v>
       </c>
       <c r="S8" s="44" t="n"/>
       <c r="T8" s="44" t="n"/>
@@ -9498,7 +9547,7 @@
       <c r="G9" s="51" t="n"/>
       <c r="H9" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B9,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B9+1))</f>
-        <v/>
+        <v>30.0</v>
       </c>
       <c r="I9" s="53">
         <f>IFERROR(F9-H9,0)</f>
@@ -9521,7 +9570,7 @@
       <c r="Q9" s="56" t="n"/>
       <c r="R9" s="56">
         <f>IFERROR(D9*$T$7,0)</f>
-        <v/>
+        <v>86.27</v>
       </c>
       <c r="S9" s="56" t="n"/>
       <c r="T9" s="56" t="n"/>
@@ -9556,7 +9605,7 @@
       <c r="G10" s="39" t="n"/>
       <c r="H10" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B10,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B10+1))</f>
-        <v/>
+        <v>3777.0</v>
       </c>
       <c r="I10" s="41">
         <f>IFERROR(F10-H10,0)</f>
@@ -9579,7 +9628,7 @@
       <c r="Q10" s="44" t="n"/>
       <c r="R10" s="44">
         <f>IFERROR(D10*$T$7,0)</f>
-        <v/>
+        <v>59.24</v>
       </c>
       <c r="S10" s="44" t="n"/>
       <c r="T10" s="44" t="n"/>
@@ -9614,7 +9663,7 @@
       <c r="G11" s="51" t="n"/>
       <c r="H11" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B11,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B11+1))</f>
-        <v/>
+        <v>2434.0</v>
       </c>
       <c r="I11" s="53">
         <f>IFERROR(F11-H11,0)</f>
@@ -9637,7 +9686,7 @@
       <c r="Q11" s="56" t="n"/>
       <c r="R11" s="56">
         <f>IFERROR(D11*$T$7,0)</f>
-        <v/>
+        <v>104.34</v>
       </c>
       <c r="S11" s="56" t="n"/>
       <c r="T11" s="56" t="n"/>
@@ -9672,7 +9721,7 @@
       <c r="G12" s="39" t="n"/>
       <c r="H12" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B12,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B12+1))</f>
-        <v/>
+        <v>1457.0</v>
       </c>
       <c r="I12" s="41">
         <f>IFERROR(F12-H12,0)</f>
@@ -9695,7 +9744,7 @@
       <c r="Q12" s="44" t="n"/>
       <c r="R12" s="44">
         <f>IFERROR(D12*$T$7,0)</f>
-        <v/>
+        <v>79.54</v>
       </c>
       <c r="S12" s="44" t="n"/>
       <c r="T12" s="44" t="n"/>
@@ -9730,7 +9779,7 @@
       <c r="G13" s="51" t="n"/>
       <c r="H13" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B13,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B13+1))</f>
-        <v/>
+        <v>7755.43</v>
       </c>
       <c r="I13" s="53">
         <f>IFERROR(F13-H13,0)</f>
@@ -9757,7 +9806,7 @@
       <c r="Q13" s="56" t="n"/>
       <c r="R13" s="56">
         <f>IFERROR(D13*$T$7,0)</f>
-        <v/>
+        <v>82.99</v>
       </c>
       <c r="S13" s="56" t="n"/>
       <c r="T13" s="56" t="n"/>
@@ -9790,7 +9839,7 @@
       <c r="G14" s="39" t="n"/>
       <c r="H14" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B14,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B14+1))</f>
-        <v/>
+        <v>1076.0</v>
       </c>
       <c r="I14" s="41">
         <f>IFERROR(F14-H14,0)</f>
@@ -9817,7 +9866,7 @@
       <c r="Q14" s="44" t="n"/>
       <c r="R14" s="44">
         <f>IFERROR(D14*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S14" s="44" t="n"/>
       <c r="T14" s="44" t="n"/>
@@ -9852,7 +9901,7 @@
       <c r="G15" s="51" t="n"/>
       <c r="H15" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B15,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B15+1))</f>
-        <v/>
+        <v>3021.45</v>
       </c>
       <c r="I15" s="53">
         <f>IFERROR(F15-H15,0)</f>
@@ -9875,7 +9924,7 @@
       <c r="Q15" s="56" t="n"/>
       <c r="R15" s="56">
         <f>IFERROR(D15*$T$7,0)</f>
-        <v/>
+        <v>85.5</v>
       </c>
       <c r="S15" s="56" t="n"/>
       <c r="T15" s="56" t="n"/>
@@ -9910,7 +9959,7 @@
       <c r="G16" s="39" t="n"/>
       <c r="H16" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B16,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B16+1))</f>
-        <v/>
+        <v>1191.6</v>
       </c>
       <c r="I16" s="41">
         <f>IFERROR(F16-H16,0)</f>
@@ -9933,7 +9982,7 @@
       <c r="Q16" s="44" t="n"/>
       <c r="R16" s="44">
         <f>IFERROR(D16*$T$7,0)</f>
-        <v/>
+        <v>77.51</v>
       </c>
       <c r="S16" s="44" t="n"/>
       <c r="T16" s="44" t="n"/>
@@ -9968,7 +10017,7 @@
       <c r="G17" s="51" t="n"/>
       <c r="H17" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B17,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B17+1))</f>
-        <v/>
+        <v>1073.22</v>
       </c>
       <c r="I17" s="53">
         <f>IFERROR(F17-H17,0)</f>
@@ -9991,7 +10040,7 @@
       <c r="Q17" s="56" t="n"/>
       <c r="R17" s="56">
         <f>IFERROR(D17*$T$7,0)</f>
-        <v/>
+        <v>79.41</v>
       </c>
       <c r="S17" s="56" t="n"/>
       <c r="T17" s="56" t="n"/>
@@ -10026,7 +10075,7 @@
       <c r="G18" s="39" t="n"/>
       <c r="H18" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B18,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B18+1))</f>
-        <v/>
+        <v>1931.34</v>
       </c>
       <c r="I18" s="41">
         <f>IFERROR(F18-H18,0)</f>
@@ -10049,7 +10098,7 @@
       <c r="Q18" s="44" t="n"/>
       <c r="R18" s="44">
         <f>IFERROR(D18*$T$7,0)</f>
-        <v/>
+        <v>60.94</v>
       </c>
       <c r="S18" s="44" t="n"/>
       <c r="T18" s="44" t="n"/>
@@ -10084,7 +10133,7 @@
       <c r="G19" s="51" t="n"/>
       <c r="H19" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B19,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B19+1))</f>
-        <v/>
+        <v>257.29</v>
       </c>
       <c r="I19" s="53">
         <f>IFERROR(F19-H19,0)</f>
@@ -10107,7 +10156,7 @@
       <c r="Q19" s="56" t="n"/>
       <c r="R19" s="56">
         <f>IFERROR(D19*$T$7,0)</f>
-        <v/>
+        <v>136.78</v>
       </c>
       <c r="S19" s="56" t="n"/>
       <c r="T19" s="56" t="n"/>
@@ -10142,7 +10191,7 @@
       <c r="G20" s="39" t="n"/>
       <c r="H20" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B20,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B20+1))</f>
-        <v/>
+        <v>5974.3</v>
       </c>
       <c r="I20" s="41">
         <f>IFERROR(F20-H20,0)</f>
@@ -10165,7 +10214,7 @@
       <c r="Q20" s="44" t="n"/>
       <c r="R20" s="44">
         <f>IFERROR(D20*$T$7,0)</f>
-        <v/>
+        <v>140.35</v>
       </c>
       <c r="S20" s="44" t="n"/>
       <c r="T20" s="44" t="n"/>
@@ -10198,7 +10247,7 @@
       <c r="G21" s="51" t="n"/>
       <c r="H21" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B21,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B21+1))</f>
-        <v/>
+        <v>10312.0</v>
       </c>
       <c r="I21" s="53">
         <f>IFERROR(F21-H21,0)</f>
@@ -10221,7 +10270,7 @@
       <c r="Q21" s="56" t="n"/>
       <c r="R21" s="56">
         <f>IFERROR(D21*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S21" s="56" t="n"/>
       <c r="T21" s="56" t="n"/>
@@ -10281,7 +10330,7 @@
       <c r="Q22" s="44" t="n"/>
       <c r="R22" s="44">
         <f>IFERROR(D22*$T$7,0)</f>
-        <v/>
+        <v>139.38</v>
       </c>
       <c r="S22" s="44" t="n"/>
       <c r="T22" s="44" t="n"/>
@@ -10341,7 +10390,7 @@
       <c r="Q23" s="56" t="n"/>
       <c r="R23" s="56">
         <f>IFERROR(D23*$T$7,0)</f>
-        <v/>
+        <v>50.34</v>
       </c>
       <c r="S23" s="56" t="n"/>
       <c r="T23" s="56" t="n"/>
@@ -10401,7 +10450,7 @@
       <c r="Q24" s="44" t="n"/>
       <c r="R24" s="44">
         <f>IFERROR(D24*$T$7,0)</f>
-        <v/>
+        <v>75.23</v>
       </c>
       <c r="S24" s="44" t="n"/>
       <c r="T24" s="44" t="n"/>
@@ -10436,7 +10485,7 @@
       <c r="G25" s="51" t="n"/>
       <c r="H25" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B25,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B25+1))</f>
-        <v/>
+        <v>20959.96</v>
       </c>
       <c r="I25" s="53">
         <f>IFERROR(F25-H25,0)</f>
@@ -10459,7 +10508,7 @@
       <c r="Q25" s="56" t="n"/>
       <c r="R25" s="56">
         <f>IFERROR(D25*$T$7,0)</f>
-        <v/>
+        <v>110.11</v>
       </c>
       <c r="S25" s="56" t="n"/>
       <c r="T25" s="56" t="n"/>
@@ -10519,7 +10568,7 @@
       <c r="Q26" s="44" t="n"/>
       <c r="R26" s="44">
         <f>IFERROR(D26*$T$7,0)</f>
-        <v/>
+        <v>101.3</v>
       </c>
       <c r="S26" s="44" t="n"/>
       <c r="T26" s="44" t="n"/>
@@ -10554,7 +10603,7 @@
       <c r="G27" s="51" t="n"/>
       <c r="H27" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B27,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B27+1))</f>
-        <v/>
+        <v>5414.0</v>
       </c>
       <c r="I27" s="53">
         <f>IFERROR(F27-H27,0)</f>
@@ -10577,7 +10626,7 @@
       <c r="Q27" s="56" t="n"/>
       <c r="R27" s="56">
         <f>IFERROR(D27*$T$7,0)</f>
-        <v/>
+        <v>23.55</v>
       </c>
       <c r="S27" s="56" t="n"/>
       <c r="T27" s="56" t="n"/>
@@ -10603,12 +10652,12 @@
       <c r="E28" s="37" t="n"/>
       <c r="F28" s="38">
         <f>IFERROR(D28+E28+G28,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G28" s="39" t="n"/>
       <c r="H28" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B28,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B28+1))</f>
-        <v/>
+        <v>1671.0</v>
       </c>
       <c r="I28" s="41">
         <f>IFERROR(F28-H28,0)</f>
@@ -10628,7 +10677,7 @@
       <c r="Q28" s="44" t="n"/>
       <c r="R28" s="44">
         <f>IFERROR(D28*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S28" s="44" t="n"/>
       <c r="T28" s="44" t="n"/>
@@ -10688,7 +10737,7 @@
       <c r="Q29" s="56" t="n"/>
       <c r="R29" s="56">
         <f>IFERROR(D29*$T$7,0)</f>
-        <v/>
+        <v>72.19</v>
       </c>
       <c r="S29" s="56" t="n"/>
       <c r="T29" s="56" t="n"/>
@@ -10723,7 +10772,7 @@
       <c r="G30" s="39" t="n"/>
       <c r="H30" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B30,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B30+1))</f>
-        <v/>
+        <v>6623.98</v>
       </c>
       <c r="I30" s="41">
         <f>IFERROR(F30-H30,0)</f>
@@ -10746,7 +10795,7 @@
       <c r="Q30" s="44" t="n"/>
       <c r="R30" s="44">
         <f>IFERROR(D30*$T$7,0)</f>
-        <v/>
+        <v>37.76</v>
       </c>
       <c r="S30" s="44" t="n"/>
       <c r="T30" s="44" t="n"/>
@@ -10781,7 +10830,7 @@
       <c r="G31" s="51" t="n"/>
       <c r="H31" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B31,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B31+1))</f>
-        <v/>
+        <v>1341.81</v>
       </c>
       <c r="I31" s="53">
         <f>IFERROR(F31-H31,0)</f>
@@ -10804,7 +10853,7 @@
       <c r="Q31" s="56" t="n"/>
       <c r="R31" s="56">
         <f>IFERROR(D31*$T$7,0)</f>
-        <v/>
+        <v>101.74</v>
       </c>
       <c r="S31" s="56" t="n"/>
       <c r="T31" s="56" t="n"/>
@@ -10864,7 +10913,7 @@
       <c r="Q32" s="44" t="n"/>
       <c r="R32" s="44">
         <f>IFERROR(D32*$T$7,0)</f>
-        <v/>
+        <v>84.24</v>
       </c>
       <c r="S32" s="44" t="n"/>
       <c r="T32" s="44" t="n"/>
@@ -10924,7 +10973,7 @@
       <c r="Q33" s="56" t="n"/>
       <c r="R33" s="56">
         <f>IFERROR(D33*$T$7,0)</f>
-        <v/>
+        <v>106.98</v>
       </c>
       <c r="S33" s="56" t="n"/>
       <c r="T33" s="56" t="n"/>
@@ -10984,7 +11033,7 @@
       <c r="Q34" s="44" t="n"/>
       <c r="R34" s="44">
         <f>IFERROR(D34*$T$7,0)</f>
-        <v/>
+        <v>40.8</v>
       </c>
       <c r="S34" s="44" t="n"/>
       <c r="T34" s="44" t="n"/>
@@ -11044,7 +11093,7 @@
       <c r="Q35" s="56" t="n"/>
       <c r="R35" s="56">
         <f>IFERROR(D35*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S35" s="56" t="n"/>
       <c r="T35" s="56" t="n"/>
@@ -11104,7 +11153,7 @@
       <c r="Q36" s="44" t="n"/>
       <c r="R36" s="44">
         <f>IFERROR(D36*$T$7,0)</f>
-        <v/>
+        <v>84.24</v>
       </c>
       <c r="S36" s="44" t="n"/>
       <c r="T36" s="44" t="n"/>
@@ -11164,7 +11213,7 @@
       <c r="Q37" s="56" t="n"/>
       <c r="R37" s="56">
         <f>IFERROR(D37*$T$7,0)</f>
-        <v/>
+        <v>74.74</v>
       </c>
       <c r="S37" s="56" t="n"/>
       <c r="T37" s="56" t="n"/>
@@ -11224,7 +11273,7 @@
       <c r="Q38" s="44" t="n"/>
       <c r="R38" s="44">
         <f>IFERROR(D38*$T$7,0)</f>
-        <v/>
+        <v>86.19</v>
       </c>
       <c r="S38" s="44" t="n"/>
       <c r="T38" s="44" t="n"/>
@@ -11284,7 +11333,7 @@
       <c r="Q39" s="56" t="n"/>
       <c r="R39" s="56">
         <f>IFERROR(D39*$T$7,0)</f>
-        <v/>
+        <v>89.77</v>
       </c>
       <c r="S39" s="56" t="n"/>
       <c r="T39" s="56" t="n"/>
@@ -11344,7 +11393,7 @@
       <c r="Q40" s="44" t="n"/>
       <c r="R40" s="44">
         <f>IFERROR(D40*$T$7,0)</f>
-        <v/>
+        <v>169.67</v>
       </c>
       <c r="S40" s="44" t="n"/>
       <c r="T40" s="44" t="n"/>
@@ -11404,7 +11453,7 @@
       <c r="Q41" s="56" t="n"/>
       <c r="R41" s="56">
         <f>IFERROR(D41*$T$7,0)</f>
-        <v/>
+        <v>47.58</v>
       </c>
       <c r="S41" s="56" t="n"/>
       <c r="T41" s="56" t="n"/>
@@ -11464,7 +11513,7 @@
       <c r="Q42" s="44" t="n"/>
       <c r="R42" s="44">
         <f>IFERROR(D42*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S42" s="44" t="n"/>
       <c r="T42" s="44" t="n"/>
@@ -11524,7 +11573,7 @@
       <c r="Q43" s="56" t="n"/>
       <c r="R43" s="56">
         <f>IFERROR(D43*$T$7,0)</f>
-        <v/>
+        <v>99.84</v>
       </c>
       <c r="S43" s="56" t="n"/>
       <c r="T43" s="56" t="n"/>
@@ -11584,7 +11633,7 @@
       <c r="Q44" s="44" t="n"/>
       <c r="R44" s="44">
         <f>IFERROR(D44*$T$7,0)</f>
-        <v/>
+        <v>58.95</v>
       </c>
       <c r="S44" s="44" t="n"/>
       <c r="T44" s="44" t="n"/>
@@ -11644,7 +11693,7 @@
       <c r="Q45" s="56" t="n"/>
       <c r="R45" s="56">
         <f>IFERROR(D45*$T$7,0)</f>
-        <v/>
+        <v>43.2</v>
       </c>
       <c r="S45" s="56" t="n"/>
       <c r="T45" s="56" t="n"/>
@@ -11704,7 +11753,7 @@
       <c r="Q46" s="44" t="n"/>
       <c r="R46" s="44">
         <f>IFERROR(D46*$T$7,0)</f>
-        <v/>
+        <v>70.44</v>
       </c>
       <c r="S46" s="44" t="n"/>
       <c r="T46" s="44" t="n"/>
@@ -11764,7 +11813,7 @@
       <c r="Q47" s="56" t="n"/>
       <c r="R47" s="56">
         <f>IFERROR(D47*$T$7,0)</f>
-        <v/>
+        <v>69.79</v>
       </c>
       <c r="S47" s="56" t="n"/>
       <c r="T47" s="56" t="n"/>
@@ -11824,7 +11873,7 @@
       <c r="Q48" s="44" t="n"/>
       <c r="R48" s="44">
         <f>IFERROR(D48*$T$7,0)</f>
-        <v/>
+        <v>7.1</v>
       </c>
       <c r="S48" s="44" t="n"/>
       <c r="T48" s="44" t="n"/>
@@ -11884,7 +11933,7 @@
       <c r="Q49" s="56" t="n"/>
       <c r="R49" s="56">
         <f>IFERROR(D49*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S49" s="56" t="n"/>
       <c r="T49" s="56" t="n"/>
@@ -11944,7 +11993,7 @@
       <c r="Q50" s="44" t="n"/>
       <c r="R50" s="44">
         <f>IFERROR(D50*$T$7,0)</f>
-        <v/>
+        <v>73.65</v>
       </c>
       <c r="S50" s="44" t="n"/>
       <c r="T50" s="44" t="n"/>
@@ -12004,7 +12053,7 @@
       <c r="Q51" s="56" t="n"/>
       <c r="R51" s="56">
         <f>IFERROR(D51*$T$7,0)</f>
-        <v/>
+        <v>97.76</v>
       </c>
       <c r="S51" s="56" t="n"/>
       <c r="T51" s="56" t="n"/>
@@ -12064,7 +12113,7 @@
       <c r="Q52" s="44" t="n"/>
       <c r="R52" s="44">
         <f>IFERROR(D52*$T$7,0)</f>
-        <v/>
+        <v>101.42</v>
       </c>
       <c r="S52" s="44" t="n"/>
       <c r="T52" s="44" t="n"/>
@@ -12128,7 +12177,7 @@
       <c r="Q53" s="56" t="n"/>
       <c r="R53" s="56">
         <f>IFERROR(D53*$T$7,0)</f>
-        <v/>
+        <v>75.48</v>
       </c>
       <c r="S53" s="56" t="n"/>
       <c r="T53" s="56" t="n"/>
@@ -12192,7 +12241,7 @@
       <c r="Q54" s="44" t="n"/>
       <c r="R54" s="44">
         <f>IFERROR(D54*$T$7,0)</f>
-        <v/>
+        <v>150.3</v>
       </c>
       <c r="S54" s="44" t="n"/>
       <c r="T54" s="44" t="n"/>
@@ -12252,7 +12301,7 @@
       <c r="Q55" s="56" t="n"/>
       <c r="R55" s="56">
         <f>IFERROR(D55*$T$7,0)</f>
-        <v/>
+        <v>70.6</v>
       </c>
       <c r="S55" s="56" t="n"/>
       <c r="T55" s="56" t="n"/>
@@ -12312,7 +12361,7 @@
       <c r="Q56" s="44" t="n"/>
       <c r="R56" s="44">
         <f>IFERROR(D56*$T$7,0)</f>
-        <v/>
+        <v>88.91</v>
       </c>
       <c r="S56" s="44" t="n"/>
       <c r="T56" s="44" t="n"/>
@@ -12372,7 +12421,7 @@
       <c r="Q57" s="56" t="n"/>
       <c r="R57" s="56">
         <f>IFERROR(D57*$T$7,0)</f>
-        <v/>
+        <v>74.7</v>
       </c>
       <c r="S57" s="56" t="n"/>
       <c r="T57" s="56" t="n"/>
@@ -12432,7 +12481,7 @@
       <c r="Q58" s="292" t="n"/>
       <c r="R58" s="292">
         <f>IFERROR(D58*$T$7,0)</f>
-        <v/>
+        <v>14.62</v>
       </c>
       <c r="S58" s="292" t="n"/>
       <c r="T58" s="292" t="n"/>
@@ -12496,7 +12545,7 @@
       <c r="Q59" s="292" t="n"/>
       <c r="R59" s="292">
         <f>IFERROR(D59*$T$7,0)</f>
-        <v/>
+        <v>78.76</v>
       </c>
       <c r="S59" s="292" t="n"/>
       <c r="T59" s="292" t="n"/>
@@ -12560,7 +12609,7 @@
       <c r="Q60" s="292" t="n"/>
       <c r="R60" s="292">
         <f>IFERROR(D60*$T$7,0)</f>
-        <v/>
+        <v>69.02</v>
       </c>
       <c r="S60" s="292" t="n"/>
       <c r="T60" s="292" t="n"/>
@@ -12624,7 +12673,7 @@
       <c r="Q61" s="292" t="n"/>
       <c r="R61" s="292">
         <f>IFERROR(D61*$T$7,0)</f>
-        <v/>
+        <v>11.37</v>
       </c>
       <c r="S61" s="292" t="n"/>
       <c r="T61" s="292" t="n"/>
@@ -12688,7 +12737,7 @@
       <c r="Q62" s="292" t="n"/>
       <c r="R62" s="292">
         <f>IFERROR(D62*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S62" s="292" t="n"/>
       <c r="T62" s="292" t="n"/>
@@ -12756,7 +12805,7 @@
       <c r="Q63" s="292" t="n"/>
       <c r="R63" s="421">
         <f>IFERROR(D63*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S63" s="292" t="n"/>
       <c r="T63" s="292" t="n"/>
@@ -12824,7 +12873,7 @@
       <c r="Q64" s="292" t="n"/>
       <c r="R64" s="421">
         <f>IFERROR(D64*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S64" s="292" t="n"/>
       <c r="T64" s="292" t="n"/>
@@ -12892,7 +12941,7 @@
       <c r="Q65" s="292" t="n"/>
       <c r="R65" s="421">
         <f>IFERROR(D65*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S65" s="292" t="n"/>
       <c r="T65" s="292" t="n"/>
@@ -12960,7 +13009,7 @@
       <c r="Q66" s="292" t="n"/>
       <c r="R66" s="421">
         <f>IFERROR(D66*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S66" s="292" t="n"/>
       <c r="T66" s="292" t="n"/>
@@ -13028,7 +13077,7 @@
       <c r="Q67" s="292" t="n"/>
       <c r="R67" s="421">
         <f>IFERROR(D67*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S67" s="292" t="n"/>
       <c r="T67" s="292" t="n"/>
@@ -13096,7 +13145,7 @@
       <c r="Q68" s="292" t="n"/>
       <c r="R68" s="421">
         <f>IFERROR(D68*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S68" s="292" t="n"/>
       <c r="T68" s="292" t="n"/>
@@ -13164,7 +13213,7 @@
       <c r="Q69" s="292" t="n"/>
       <c r="R69" s="421">
         <f>IFERROR(D69*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S69" s="292" t="n"/>
       <c r="T69" s="292" t="n"/>
@@ -13232,7 +13281,7 @@
       <c r="Q70" s="292" t="n"/>
       <c r="R70" s="421">
         <f>IFERROR(D70*$T$7,0)</f>
-        <v/>
+        <v>93.79</v>
       </c>
       <c r="S70" s="292" t="n"/>
       <c r="T70" s="292" t="n"/>
@@ -13300,7 +13349,7 @@
       <c r="Q71" s="292" t="n"/>
       <c r="R71" s="421">
         <f>IFERROR(D71*$T$7,0)</f>
-        <v/>
+        <v>68.82</v>
       </c>
       <c r="S71" s="292" t="n"/>
       <c r="T71" s="292" t="n"/>
@@ -13322,91 +13371,208 @@
       <c r="AB71" s="292" t="n"/>
     </row>
     <row r="72" ht="16.5" customHeight="1" s="313">
-      <c r="B72" s="34" t="n"/>
-      <c r="C72" s="35" t="n"/>
-      <c r="D72" s="36" t="n"/>
-      <c r="E72" s="37" t="n"/>
-      <c r="F72" s="38" t="n"/>
-      <c r="G72" s="39" t="n"/>
-      <c r="H72" s="40" t="n"/>
-      <c r="I72" s="41" t="n"/>
-      <c r="J72" s="42" t="n"/>
-      <c r="K72" s="43" t="n"/>
-      <c r="L72" s="9" t="n"/>
-      <c r="M72" s="12" t="n"/>
-      <c r="N72" s="44" t="n"/>
-      <c r="O72" s="45" t="n"/>
-      <c r="P72" s="46" t="n"/>
-      <c r="Q72" s="44" t="n"/>
-      <c r="R72" s="44" t="n"/>
-      <c r="S72" s="44" t="n"/>
-      <c r="T72" s="44" t="n"/>
-      <c r="U72" s="44" t="n"/>
-      <c r="V72" s="44" t="n"/>
-      <c r="W72" s="44" t="n"/>
-      <c r="X72" s="44" t="n"/>
-      <c r="Y72" s="44" t="n"/>
-      <c r="Z72" s="44" t="n"/>
-      <c r="AA72" s="44" t="n"/>
-      <c r="AB72" s="44" t="n"/>
+      <c r="B72" s="420" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C72" s="255" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D72" s="256" t="n">
+        <v>2455</v>
+      </c>
+      <c r="E72" s="49" t="n">
+        <v>3315</v>
+      </c>
+      <c r="F72" s="50">
+        <f>IFERROR(D72+E72+G72+U72+Y72,0)</f>
+        <v>5770.0</v>
+      </c>
+      <c r="G72" s="257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B72,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B72+1))</f>
+        <v>1886.0</v>
+      </c>
+      <c r="I72" s="259">
+        <f>IFERROR(F72-H72,0)</f>
+        <v>3884.0</v>
+      </c>
+      <c r="J72" s="260">
+        <f>IFERROR(I72/F72,0)</f>
+        <v>0.673137</v>
+      </c>
+      <c r="K72" s="254" t="n"/>
+      <c r="L72" s="261" t="inlineStr">
+        <is>
+          <t>EOD close (MP + cash). Samu Week 10 salary paid.</t>
+        </is>
+      </c>
+      <c r="M72" s="291" t="n"/>
+      <c r="N72" s="292" t="n"/>
+      <c r="O72" s="293" t="n"/>
+      <c r="P72" s="294" t="n"/>
+      <c r="Q72" s="292" t="n"/>
+      <c r="R72" s="421">
+        <f>IFERROR(D72*$T$7,0)</f>
+        <v>99.67</v>
+      </c>
+      <c r="S72" s="292" t="n"/>
+      <c r="T72" s="292" t="n"/>
+      <c r="U72" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" s="292" t="n"/>
+      <c r="X72" s="292" t="n"/>
+      <c r="Y72" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="292" t="n"/>
+      <c r="AB72" s="292" t="n"/>
     </row>
     <row r="73" ht="16.5" customHeight="1" s="313">
-      <c r="B73" s="34" t="n"/>
-      <c r="C73" s="47" t="n"/>
-      <c r="D73" s="48" t="n"/>
-      <c r="E73" s="49" t="n"/>
-      <c r="F73" s="50" t="n"/>
-      <c r="G73" s="51" t="n"/>
-      <c r="H73" s="52" t="n"/>
-      <c r="I73" s="53" t="n"/>
-      <c r="J73" s="54" t="n"/>
-      <c r="K73" s="55" t="n"/>
-      <c r="L73" s="18" t="n"/>
-      <c r="M73" s="21" t="n"/>
-      <c r="N73" s="56" t="n"/>
-      <c r="O73" s="57" t="n"/>
-      <c r="P73" s="58" t="n"/>
-      <c r="Q73" s="56" t="n"/>
-      <c r="R73" s="56" t="n"/>
-      <c r="S73" s="56" t="n"/>
-      <c r="T73" s="56" t="n"/>
-      <c r="U73" s="56" t="n"/>
-      <c r="V73" s="56" t="n"/>
-      <c r="W73" s="56" t="n"/>
-      <c r="X73" s="56" t="n"/>
-      <c r="Y73" s="56" t="n"/>
-      <c r="Z73" s="56" t="n"/>
-      <c r="AA73" s="56" t="n"/>
-      <c r="AB73" s="56" t="n"/>
+      <c r="B73" s="420" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C73" s="255" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D73" s="256" t="n">
+        <v>155</v>
+      </c>
+      <c r="E73" s="49" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F73" s="50">
+        <f>IFERROR(D73+E73+G73+U73+Y73,0)</f>
+        <v>1225.0</v>
+      </c>
+      <c r="G73" s="257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B73,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B73+1))</f>
+        <v>6613.0</v>
+      </c>
+      <c r="I73" s="259">
+        <f>IFERROR(F73-H73,0)</f>
+        <v>-5388.0</v>
+      </c>
+      <c r="J73" s="260">
+        <f>IFERROR(I73/F73,0)</f>
+        <v>-4.398367</v>
+      </c>
+      <c r="K73" s="254" t="n"/>
+      <c r="L73" s="261" t="inlineStr">
+        <is>
+          <t>EOD close (MP + cash). John + Duvi Week 10 salaries paid.</t>
+        </is>
+      </c>
+      <c r="M73" s="291" t="n"/>
+      <c r="N73" s="292" t="n"/>
+      <c r="O73" s="293" t="n"/>
+      <c r="P73" s="294" t="n"/>
+      <c r="Q73" s="292" t="n"/>
+      <c r="R73" s="421">
+        <f>IFERROR(D73*$T$7,0)</f>
+        <v>6.29</v>
+      </c>
+      <c r="S73" s="292" t="n"/>
+      <c r="T73" s="292" t="n"/>
+      <c r="U73" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" s="292" t="n"/>
+      <c r="X73" s="292" t="n"/>
+      <c r="Y73" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="292" t="n"/>
+      <c r="AB73" s="292" t="n"/>
     </row>
     <row r="74" ht="16.5" customHeight="1" s="313">
-      <c r="B74" s="34" t="n"/>
-      <c r="C74" s="35" t="n"/>
-      <c r="D74" s="36" t="n"/>
-      <c r="E74" s="37" t="n"/>
-      <c r="F74" s="38" t="n"/>
-      <c r="G74" s="39" t="n"/>
-      <c r="H74" s="40" t="n"/>
-      <c r="I74" s="41" t="n"/>
-      <c r="J74" s="42" t="n"/>
-      <c r="K74" s="43" t="n"/>
-      <c r="L74" s="9" t="n"/>
-      <c r="M74" s="12" t="n"/>
-      <c r="N74" s="44" t="n"/>
-      <c r="O74" s="45" t="n"/>
-      <c r="P74" s="46" t="n"/>
-      <c r="Q74" s="44" t="n"/>
-      <c r="R74" s="44" t="n"/>
-      <c r="S74" s="44" t="n"/>
-      <c r="T74" s="44" t="n"/>
-      <c r="U74" s="44" t="n"/>
-      <c r="V74" s="44" t="n"/>
-      <c r="W74" s="44" t="n"/>
-      <c r="X74" s="44" t="n"/>
-      <c r="Y74" s="44" t="n"/>
-      <c r="Z74" s="44" t="n"/>
-      <c r="AA74" s="44" t="n"/>
-      <c r="AB74" s="44" t="n"/>
+      <c r="B74" s="420" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C74" s="270" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D74" s="271" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E74" s="37" t="n">
+        <v>1380</v>
+      </c>
+      <c r="F74" s="38">
+        <f>IFERROR(D74+E74+G74+U74+Y74,0)</f>
+        <v>3180.0</v>
+      </c>
+      <c r="G74" s="272" t="n">
+        <v>700</v>
+      </c>
+      <c r="H74" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B74,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B74+1))</f>
+        <v>928.0</v>
+      </c>
+      <c r="I74" s="274">
+        <f>IFERROR(F74-H74,0)</f>
+        <v>2252.0</v>
+      </c>
+      <c r="J74" s="275">
+        <f>IFERROR(I74/F74,0)</f>
+        <v>0.708176</v>
+      </c>
+      <c r="K74" s="250" t="n"/>
+      <c r="L74" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M74" s="434" t="n"/>
+      <c r="N74" s="435" t="n"/>
+      <c r="O74" s="436" t="n"/>
+      <c r="P74" s="437" t="n"/>
+      <c r="Q74" s="435" t="n"/>
+      <c r="R74" s="438">
+        <f>IFERROR(D74*$T$7,0)</f>
+        <v>44.66</v>
+      </c>
+      <c r="S74" s="435" t="n"/>
+      <c r="T74" s="435" t="n"/>
+      <c r="U74" s="438" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" s="438" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" s="435" t="n"/>
+      <c r="X74" s="435" t="n"/>
+      <c r="Y74" s="438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="435" t="n"/>
+      <c r="AB74" s="435" t="n"/>
     </row>
     <row r="75" ht="16.5" customHeight="1" s="313">
       <c r="B75" s="34" t="n"/>
@@ -22052,9 +22218,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -22077,7 +22243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J532"/>
+  <dimension ref="A1:J548"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="313" min="1" max="1"/>
@@ -22370,7 +22536,7 @@
       </c>
       <c r="E11" s="65" t="inlineStr">
         <is>
-          <t>Supermarket / General</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="F11" s="67" t="n">
@@ -22826,7 +22992,7 @@
       </c>
       <c r="E23" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F23" s="67" t="n">
@@ -22940,7 +23106,7 @@
       </c>
       <c r="E26" s="72" t="inlineStr">
         <is>
-          <t>Supermarket / General</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="F26" s="70" t="n">
@@ -23320,7 +23486,7 @@
       </c>
       <c r="E36" s="69" t="inlineStr">
         <is>
-          <t>Supermarket / General</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="F36" s="70" t="n">
@@ -23358,7 +23524,7 @@
       </c>
       <c r="E37" s="74" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F37" s="76" t="n">
@@ -23624,7 +23790,7 @@
       </c>
       <c r="E44" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F44" s="67" t="n">
@@ -23700,7 +23866,7 @@
       </c>
       <c r="E46" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F46" s="67" t="n">
@@ -25684,7 +25850,7 @@
       </c>
       <c r="E94" s="69" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F94" s="70" t="n">
@@ -25942,7 +26108,7 @@
       </c>
       <c r="E100" s="69" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F100" s="70" t="n">
@@ -25985,7 +26151,7 @@
       </c>
       <c r="E101" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F101" s="67" t="n">
@@ -27893,7 +28059,7 @@
       </c>
       <c r="E147" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F147" s="67" t="n">
@@ -28022,7 +28188,7 @@
       </c>
       <c r="E150" s="69" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F150" s="70" t="n">
@@ -28065,7 +28231,7 @@
       </c>
       <c r="E151" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F151" s="67" t="n">
@@ -28108,7 +28274,7 @@
       </c>
       <c r="E152" s="69" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F152" s="70" t="n">
@@ -28323,7 +28489,7 @@
       </c>
       <c r="E157" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F157" s="67" t="n">
@@ -28366,7 +28532,7 @@
       </c>
       <c r="E158" s="69" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F158" s="70" t="n">
@@ -28409,7 +28575,7 @@
       </c>
       <c r="E159" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F159" s="67" t="n">
@@ -28753,7 +28919,7 @@
       </c>
       <c r="E167" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F167" s="67" t="n">
@@ -28796,7 +28962,7 @@
       </c>
       <c r="E168" s="69" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F168" s="70" t="n">
@@ -28839,7 +29005,7 @@
       </c>
       <c r="E169" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F169" s="67" t="n">
@@ -28882,7 +29048,7 @@
       </c>
       <c r="E170" s="69" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F170" s="70" t="n">
@@ -28925,7 +29091,7 @@
       </c>
       <c r="E171" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F171" s="67" t="n">
@@ -28968,7 +29134,7 @@
       </c>
       <c r="E172" s="69" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F172" s="70" t="n">
@@ -29613,7 +29779,7 @@
       </c>
       <c r="E187" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F187" s="67" t="n">
@@ -30000,7 +30166,7 @@
       </c>
       <c r="E196" s="69" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F196" s="70" t="n">
@@ -30645,7 +30811,7 @@
       </c>
       <c r="E211" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F211" s="67" t="n">
@@ -31075,7 +31241,7 @@
       </c>
       <c r="E221" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F221" s="67" t="n">
@@ -31505,7 +31671,7 @@
       </c>
       <c r="E231" s="65" t="inlineStr">
         <is>
-          <t>Supermarket / General</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="F231" s="67" t="n">
@@ -31548,7 +31714,7 @@
       </c>
       <c r="E232" s="69" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F232" s="70" t="n">
@@ -31892,7 +32058,7 @@
       </c>
       <c r="E240" s="69" t="inlineStr">
         <is>
-          <t>Supermarket / General</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="F240" s="70" t="n">
@@ -32064,7 +32230,7 @@
       </c>
       <c r="E244" s="69" t="inlineStr">
         <is>
-          <t>Supermarket / General</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="F244" s="70" t="n">
@@ -32107,7 +32273,7 @@
       </c>
       <c r="E245" s="65" t="inlineStr">
         <is>
-          <t>Ingredients - Produce</t>
+          <t>Ingredients - Vegetables</t>
         </is>
       </c>
       <c r="F245" s="67" t="n">
@@ -32150,7 +32316,7 @@
       </c>
       <c r="E246" s="69" t="inlineStr">
         <is>
-          <t>Supermarket / General</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="F246" s="70" t="n">
@@ -32838,7 +33004,7 @@
       </c>
       <c r="E262" s="69" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F262" s="70" t="n">
@@ -32881,7 +33047,7 @@
       </c>
       <c r="E263" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F263" s="67" t="n">
@@ -32967,7 +33133,7 @@
       </c>
       <c r="E265" s="65" t="inlineStr">
         <is>
-          <t>Supermarket / General</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="F265" s="67" t="n">
@@ -33311,7 +33477,7 @@
       </c>
       <c r="E273" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F273" s="67" t="n">
@@ -33483,7 +33649,7 @@
       </c>
       <c r="E277" s="65" t="inlineStr">
         <is>
-          <t>Supermarket / General</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="F277" s="67" t="n">
@@ -33569,7 +33735,7 @@
       </c>
       <c r="E279" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F279" s="67" t="n">
@@ -33698,7 +33864,7 @@
       </c>
       <c r="E282" s="69" t="inlineStr">
         <is>
-          <t>Supermarket / General</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="F282" s="70" t="n">
@@ -33741,7 +33907,7 @@
       </c>
       <c r="E283" s="65" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F283" s="67" t="n">
@@ -33784,7 +33950,7 @@
       </c>
       <c r="E284" s="69" t="inlineStr">
         <is>
-          <t>Supermarket / General</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="F284" s="70" t="n">
@@ -33999,7 +34165,7 @@
       </c>
       <c r="E289" s="65" t="inlineStr">
         <is>
-          <t>Utilities / Internet</t>
+          <t>Utilities/Internet</t>
         </is>
       </c>
       <c r="F289" s="67" t="n">
@@ -34429,7 +34595,7 @@
       </c>
       <c r="E299" s="247" t="inlineStr">
         <is>
-          <t>Supermarket / General</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="F299" s="67" t="n">
@@ -34816,7 +34982,7 @@
       </c>
       <c r="E308" s="251" t="inlineStr">
         <is>
-          <t>Software / Subscription</t>
+          <t>Software/Subscription</t>
         </is>
       </c>
       <c r="F308" s="70" t="n">
@@ -35320,7 +35486,7 @@
       </c>
       <c r="E320" s="251" t="inlineStr">
         <is>
-          <t>Packaging / Disposables</t>
+          <t>Packaging/Disposables</t>
         </is>
       </c>
       <c r="F320" s="70" t="n">
@@ -35746,7 +35912,7 @@
       </c>
       <c r="E330" s="251" t="inlineStr">
         <is>
-          <t>Packaging / Disposables</t>
+          <t>Packaging/Disposables</t>
         </is>
       </c>
       <c r="F330" s="70" t="n">
@@ -36219,7 +36385,7 @@
       </c>
       <c r="E341" s="247" t="inlineStr">
         <is>
-          <t>Utilities / Gas</t>
+          <t>Utilities/Gas</t>
         </is>
       </c>
       <c r="F341" s="67" t="n">
@@ -36563,7 +36729,7 @@
       </c>
       <c r="E349" s="247" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F349" s="67" t="n">
@@ -36649,7 +36815,7 @@
       </c>
       <c r="E351" s="247" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F351" s="67" t="n">
@@ -36950,7 +37116,7 @@
       </c>
       <c r="E358" s="251" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F358" s="70" t="n">
@@ -36993,7 +37159,7 @@
       </c>
       <c r="E359" s="247" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F359" s="67" t="n">
@@ -37036,7 +37202,7 @@
       </c>
       <c r="E360" s="251" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F360" s="70" t="n">
@@ -37122,7 +37288,7 @@
       </c>
       <c r="E362" s="251" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F362" s="70" t="n">
@@ -37165,7 +37331,7 @@
       </c>
       <c r="E363" s="247" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="F363" s="67" t="n">
@@ -44454,6 +44620,694 @@
         </is>
       </c>
       <c r="J532" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="B533" s="422" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C533" s="305" t="inlineStr">
+        <is>
+          <t>Pan molido</t>
+        </is>
+      </c>
+      <c r="D533" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E533" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F533" s="307" t="n">
+        <v>72</v>
+      </c>
+      <c r="G533" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H533" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I533" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J533" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash; breadcrumbs</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="B534" s="422" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C534" s="305" t="inlineStr">
+        <is>
+          <t>Azucar (Oxxo)</t>
+        </is>
+      </c>
+      <c r="D534" s="306" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E534" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F534" s="307" t="n">
+        <v>24</v>
+      </c>
+      <c r="G534" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H534" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I534" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J534" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="B535" s="422" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C535" s="305" t="inlineStr">
+        <is>
+          <t>Queso panela</t>
+        </is>
+      </c>
+      <c r="D535" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E535" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Dairy</t>
+        </is>
+      </c>
+      <c r="F535" s="307" t="n">
+        <v>590</v>
+      </c>
+      <c r="G535" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H535" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I535" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J535" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="B536" s="422" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C536" s="305" t="inlineStr">
+        <is>
+          <t>Samu — Ayudante Week 10</t>
+        </is>
+      </c>
+      <c r="D536" s="306" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E536" s="305" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F536" s="307" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G536" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H536" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I536" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J536" s="418" t="inlineStr">
+        <is>
+          <t>Week 10 salary, paid Friday 24 Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="B537" s="422" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C537" s="305" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D537" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E537" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F537" s="307" t="n">
+        <v>150</v>
+      </c>
+      <c r="G537" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H537" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I537" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J537" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="B538" s="422" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C538" s="305" t="inlineStr">
+        <is>
+          <t>Carne bistec</t>
+        </is>
+      </c>
+      <c r="D538" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E538" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F538" s="307" t="n">
+        <v>284</v>
+      </c>
+      <c r="G538" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H538" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I538" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J538" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="B539" s="422" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C539" s="305" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D539" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E539" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F539" s="307" t="n">
+        <v>905</v>
+      </c>
+      <c r="G539" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H539" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I539" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J539" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="B540" s="422" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C540" s="305" t="inlineStr">
+        <is>
+          <t>Azucar (Oxxo)</t>
+        </is>
+      </c>
+      <c r="D540" s="306" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E540" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F540" s="307" t="n">
+        <v>24</v>
+      </c>
+      <c r="G540" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H540" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I540" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J540" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="B541" s="422" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C541" s="305" t="inlineStr">
+        <is>
+          <t>John — Head Chef Week 10</t>
+        </is>
+      </c>
+      <c r="D541" s="306" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E541" s="305" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F541" s="307" t="n">
+        <v>3750</v>
+      </c>
+      <c r="G541" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H541" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I541" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J541" s="418" t="inlineStr">
+        <is>
+          <t>Week 10 salary, paid Saturday 25 Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="B542" s="422" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C542" s="305" t="inlineStr">
+        <is>
+          <t>Duvi/Debi — Limpieza Week 10</t>
+        </is>
+      </c>
+      <c r="D542" s="306" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E542" s="305" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F542" s="307" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G542" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H542" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I542" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J542" s="418" t="inlineStr">
+        <is>
+          <t>Week 10 salary, paid Saturday 25 Jul (full week)</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="B543" s="422" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C543" s="305" t="inlineStr">
+        <is>
+          <t>Vegetables (Central de Abastos)</t>
+        </is>
+      </c>
+      <c r="D543" s="306" t="inlineStr">
+        <is>
+          <t>Central de Abastos</t>
+        </is>
+      </c>
+      <c r="E543" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F543" s="307" t="n">
+        <v>1832</v>
+      </c>
+      <c r="G543" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H543" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I543" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J543" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash; compra semanal (domingo, restaurante cerrado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="B544" s="422" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C544" s="305" t="inlineStr">
+        <is>
+          <t>Arroz (Oxxo)</t>
+        </is>
+      </c>
+      <c r="D544" s="306" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E544" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F544" s="307" t="n">
+        <v>78</v>
+      </c>
+      <c r="G544" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H544" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I544" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J544" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash; domingo shopping</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="B545" s="422" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C545" s="305" t="inlineStr">
+        <is>
+          <t>Sam's Club (varios)</t>
+        </is>
+      </c>
+      <c r="D545" s="306" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="E545" s="305" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F545" s="307" t="n">
+        <v>1157</v>
+      </c>
+      <c r="G545" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H545" s="308" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="I545" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J545" s="418" t="inlineStr">
+        <is>
+          <t>No receipt provided; restaurant-paid; domingo shopping</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="B546" s="422" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C546" s="305" t="inlineStr">
+        <is>
+          <t>Agua Natural</t>
+        </is>
+      </c>
+      <c r="D546" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E546" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F546" s="307" t="n">
+        <v>60</v>
+      </c>
+      <c r="G546" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H546" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I546" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J546" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="B547" s="422" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C547" s="305" t="inlineStr">
+        <is>
+          <t>Sams Club</t>
+        </is>
+      </c>
+      <c r="D547" s="306" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="E547" s="305" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F547" s="307" t="n">
+        <v>491</v>
+      </c>
+      <c r="G547" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H547" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I547" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J547" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="B548" s="422" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C548" s="305" t="inlineStr">
+        <is>
+          <t>Chedruai</t>
+        </is>
+      </c>
+      <c r="D548" s="306" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E548" s="305" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F548" s="307" t="n">
+        <v>377</v>
+      </c>
+      <c r="G548" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H548" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I548" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J548" s="418" t="inlineStr">
         <is>
           <t>No receipt; cash</t>
         </is>
@@ -54189,15 +55043,15 @@
         </is>
       </c>
       <c r="B4" s="413">
-        <f>SUMIFS('📅 Daily Log'!$F$8:$F$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$F$8:$F$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C4" s="413">
-        <f>SUMIFS('📅 Daily Log'!$F$8:$F$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$F$8:$F$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D4" s="413">
-        <f>SUMIFS('📅 Daily Log'!$F$8:$F$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$F$8:$F$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E4" s="409" t="n"/>
@@ -54216,15 +55070,15 @@
         </is>
       </c>
       <c r="B5" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C5" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D5" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E5" s="409" t="n"/>
@@ -54270,15 +55124,15 @@
         </is>
       </c>
       <c r="B7" s="416">
-        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$500,"&gt;0",'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$5000,"&gt;0",'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C7" s="416">
-        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$500,"&gt;0",'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$5000,"&gt;0",'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D7" s="416">
-        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$500,"&gt;0",'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$5000,"&gt;0",'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E7" s="409" t="n"/>
@@ -54368,15 +55222,15 @@
         </is>
       </c>
       <c r="B11" s="413">
-        <f>SUMIFS('📅 Daily Log'!$D$8:$D$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$D$8:$D$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C11" s="413">
-        <f>SUMIFS('📅 Daily Log'!$D$8:$D$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$D$8:$D$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D11" s="413">
-        <f>SUMIFS('📅 Daily Log'!$D$8:$D$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$D$8:$D$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E11" s="409" t="n"/>
@@ -54395,15 +55249,15 @@
         </is>
       </c>
       <c r="B12" s="413">
-        <f>SUMIFS('📅 Daily Log'!$E$8:$E$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$E$8:$E$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C12" s="413">
-        <f>SUMIFS('📅 Daily Log'!$E$8:$E$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$E$8:$E$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D12" s="413">
-        <f>SUMIFS('📅 Daily Log'!$E$8:$E$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$E$8:$E$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E12" s="409" t="n"/>
@@ -54422,15 +55276,15 @@
         </is>
       </c>
       <c r="B13" s="413">
-        <f>SUMIFS('📅 Daily Log'!$G$8:$G$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$G$8:$G$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C13" s="413">
-        <f>SUMIFS('📅 Daily Log'!$G$8:$G$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$G$8:$G$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D13" s="413">
-        <f>SUMIFS('📅 Daily Log'!$G$8:$G$500,'📅 Daily Log'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('📅 Daily Log'!$G$8:$G$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E13" s="409" t="n"/>
@@ -54520,15 +55374,15 @@
         </is>
       </c>
       <c r="B17" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A17,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A17,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C17" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A17,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A17,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D17" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A17,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A17,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E17" s="409" t="n"/>
@@ -54547,15 +55401,15 @@
         </is>
       </c>
       <c r="B18" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A18,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A18,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C18" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A18,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A18,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D18" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A18,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A18,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E18" s="409" t="n"/>
@@ -54574,15 +55428,15 @@
         </is>
       </c>
       <c r="B19" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A19,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A19,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C19" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A19,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A19,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D19" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A19,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A19,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E19" s="409" t="n"/>
@@ -54597,19 +55451,19 @@
     <row r="20">
       <c r="A20" s="415" t="inlineStr">
         <is>
-          <t>Ingredients - Vegetables</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="B20" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A20,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A20,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C20" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A20,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A20,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D20" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A20,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A20,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E20" s="409" t="n"/>
@@ -54624,19 +55478,19 @@
     <row r="21">
       <c r="A21" s="415" t="inlineStr">
         <is>
-          <t>Ingredients - Pantry</t>
+          <t>Ingredients - Vegetables</t>
         </is>
       </c>
       <c r="B21" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A21,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A21,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C21" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A21,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A21,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D21" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A21,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A21,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E21" s="409" t="n"/>
@@ -54651,19 +55505,19 @@
     <row r="22">
       <c r="A22" s="415" t="inlineStr">
         <is>
-          <t>Supermarket/General</t>
+          <t>Ingredients - Pantry</t>
         </is>
       </c>
       <c r="B22" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A22,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A22,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C22" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A22,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A22,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D22" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A22,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A22,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E22" s="409" t="n"/>
@@ -54682,15 +55536,15 @@
         </is>
       </c>
       <c r="B23" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A23,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A23,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C23" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A23,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A23,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D23" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A23,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A23,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E23" s="409" t="n"/>
@@ -54709,15 +55563,15 @@
         </is>
       </c>
       <c r="B24" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A24,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A24,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C24" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A24,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A24,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D24" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A24,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A24,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E24" s="409" t="n"/>
@@ -54736,15 +55590,15 @@
         </is>
       </c>
       <c r="B25" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A25,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A25,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C25" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A25,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A25,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D25" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A25,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A25,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E25" s="409" t="n"/>
@@ -54759,19 +55613,19 @@
     <row r="26">
       <c r="A26" s="415" t="inlineStr">
         <is>
-          <t>Supplies / Other</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="B26" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A26,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A26,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C26" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A26,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A26,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D26" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A26,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A26,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E26" s="409" t="n"/>
@@ -54786,19 +55640,19 @@
     <row r="27">
       <c r="A27" s="415" t="inlineStr">
         <is>
-          <t>Supermarket / General</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B27" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A27,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A27,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C27" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A27,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A27,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D27" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A27,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A27,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E27" s="409" t="n"/>
@@ -54813,19 +55667,19 @@
     <row r="28">
       <c r="A28" s="415" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Ingredients - Meat &amp; Fish</t>
         </is>
       </c>
       <c r="B28" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A28,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A28,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C28" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A28,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A28,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D28" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A28,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A28,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E28" s="409" t="n"/>
@@ -54840,19 +55694,19 @@
     <row r="29">
       <c r="A29" s="415" t="inlineStr">
         <is>
-          <t>Ingredients - Meat &amp; Fish</t>
+          <t>Packaging/Disposables</t>
         </is>
       </c>
       <c r="B29" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A29,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A29,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C29" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A29,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A29,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D29" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A29,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A29,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E29" s="409" t="n"/>
@@ -54867,19 +55721,19 @@
     <row r="30">
       <c r="A30" s="415" t="inlineStr">
         <is>
-          <t>Packaging/Disposables</t>
+          <t>Ingredients - Fruit</t>
         </is>
       </c>
       <c r="B30" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A30,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A30,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C30" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A30,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A30,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D30" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A30,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A30,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E30" s="409" t="n"/>
@@ -54894,19 +55748,19 @@
     <row r="31">
       <c r="A31" s="415" t="inlineStr">
         <is>
-          <t>Ingredients - Fruit</t>
+          <t>Utilities/Internet</t>
         </is>
       </c>
       <c r="B31" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A31,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A31,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C31" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A31,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A31,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D31" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A31,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A31,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E31" s="409" t="n"/>
@@ -54921,19 +55775,19 @@
     <row r="32">
       <c r="A32" s="415" t="inlineStr">
         <is>
-          <t>Utilities / Gas</t>
+          <t>Utilities/Gas</t>
         </is>
       </c>
       <c r="B32" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A32,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A32,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C32" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A32,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A32,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D32" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A32,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A32,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E32" s="409" t="n"/>
@@ -54952,15 +55806,15 @@
         </is>
       </c>
       <c r="B33" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A33,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A33,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C33" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A33,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A33,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D33" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A33,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A33,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E33" s="409" t="n"/>
@@ -54979,15 +55833,15 @@
         </is>
       </c>
       <c r="B34" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A34,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A34,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C34" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A34,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A34,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D34" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A34,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A34,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E34" s="409" t="n"/>
@@ -55002,19 +55856,19 @@
     <row r="35">
       <c r="A35" s="415" t="inlineStr">
         <is>
-          <t>Utilities/Internet</t>
+          <t>Kitchen Supplies</t>
         </is>
       </c>
       <c r="B35" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A35,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A35,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C35" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A35,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A35,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D35" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A35,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A35,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E35" s="409" t="n"/>
@@ -55029,19 +55883,19 @@
     <row r="36">
       <c r="A36" s="415" t="inlineStr">
         <is>
-          <t>Kitchen Supplies</t>
+          <t>Software/Subscription</t>
         </is>
       </c>
       <c r="B36" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A36,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A36,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C36" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A36,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A36,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D36" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A36,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A36,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E36" s="409" t="n"/>
@@ -55056,19 +55910,19 @@
     <row r="37">
       <c r="A37" s="415" t="inlineStr">
         <is>
-          <t>Software / Subscription</t>
+          <t>Staff - Advance</t>
         </is>
       </c>
       <c r="B37" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A37,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A37,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C37" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A37,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A37,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D37" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A37,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A37,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E37" s="409" t="n"/>
@@ -55083,19 +55937,19 @@
     <row r="38">
       <c r="A38" s="415" t="inlineStr">
         <is>
-          <t>Staff - Advance</t>
+          <t>Ingredients - Desserts</t>
         </is>
       </c>
       <c r="B38" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A38,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A38,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C38" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A38,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A38,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D38" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A38,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A38,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E38" s="409" t="n"/>
@@ -55110,19 +55964,19 @@
     <row r="39">
       <c r="A39" s="415" t="inlineStr">
         <is>
-          <t>Utilities / Internet</t>
+          <t>Ingredients - Eggs</t>
         </is>
       </c>
       <c r="B39" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A39,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A39,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C39" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A39,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A39,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D39" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A39,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A39,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E39" s="409" t="n"/>
@@ -55137,19 +55991,19 @@
     <row r="40">
       <c r="A40" s="415" t="inlineStr">
         <is>
-          <t>Packaging / Disposables</t>
+          <t>Staff - Propinas</t>
         </is>
       </c>
       <c r="B40" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A40,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A40,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C40" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A40,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A40,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D40" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A40,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A40,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E40" s="409" t="n"/>
@@ -55162,21 +56016,21 @@
       <c r="L40" s="409" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="415" t="inlineStr">
-        <is>
-          <t>Ingredients - Desserts</t>
-        </is>
-      </c>
-      <c r="B41" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A41,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+      <c r="A41" s="412" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="B41" s="414">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
-      <c r="C41" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A41,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+      <c r="C41" s="414">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D41" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A41,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+      <c r="D41" s="414">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E41" s="409" t="n"/>
@@ -55189,21 +56043,21 @@
       <c r="L41" s="409" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="415" t="inlineStr">
-        <is>
-          <t>Ingredients - Eggs</t>
-        </is>
-      </c>
-      <c r="B42" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A42,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
+      <c r="A42" s="412" t="inlineStr">
+        <is>
+          <t>NET PROFIT / LOSS</t>
+        </is>
+      </c>
+      <c r="B42" s="414">
+        <f>B4-B41</f>
         <v/>
       </c>
-      <c r="C42" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A42,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
+      <c r="C42" s="414">
+        <f>C4-C41</f>
         <v/>
       </c>
-      <c r="D42" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A42,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
+      <c r="D42" s="414">
+        <f>D4-D41</f>
         <v/>
       </c>
       <c r="E42" s="409" t="n"/>
@@ -55216,23 +56070,10 @@
       <c r="L42" s="409" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="415" t="inlineStr">
-        <is>
-          <t>Staff - Propinas</t>
-        </is>
-      </c>
-      <c r="B43" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A43,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
-        <v/>
-      </c>
-      <c r="C43" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A43,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
-        <v/>
-      </c>
-      <c r="D43" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A43,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
-        <v/>
-      </c>
+      <c r="A43" s="409" t="n"/>
+      <c r="B43" s="409" t="n"/>
+      <c r="C43" s="409" t="n"/>
+      <c r="D43" s="409" t="n"/>
       <c r="E43" s="409" t="n"/>
       <c r="F43" s="409" t="n"/>
       <c r="G43" s="409" t="n"/>
@@ -55243,23 +56084,10 @@
       <c r="L43" s="409" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="415" t="inlineStr">
-        <is>
-          <t>Ingredients - Produce</t>
-        </is>
-      </c>
-      <c r="B44" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A44,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
-        <v/>
-      </c>
-      <c r="C44" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A44,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
-        <v/>
-      </c>
-      <c r="D44" s="413">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$E$8:$E$500,$A44,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
-        <v/>
-      </c>
+      <c r="A44" s="409" t="n"/>
+      <c r="B44" s="409" t="n"/>
+      <c r="C44" s="409" t="n"/>
+      <c r="D44" s="409" t="n"/>
       <c r="E44" s="409" t="n"/>
       <c r="F44" s="409" t="n"/>
       <c r="G44" s="409" t="n"/>
@@ -55270,23 +56098,10 @@
       <c r="L44" s="409" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="412" t="inlineStr">
-        <is>
-          <t>TOTAL EXPENSES</t>
-        </is>
-      </c>
-      <c r="B45" s="414">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,6,1))</f>
-        <v/>
-      </c>
-      <c r="C45" s="414">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,7,1))</f>
-        <v/>
-      </c>
-      <c r="D45" s="414">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$500,'💸 Expenses'!$B$8:$B$500,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$500,"&lt;"&amp;DATE(2026,8,1))</f>
-        <v/>
-      </c>
+      <c r="A45" s="409" t="n"/>
+      <c r="B45" s="409" t="n"/>
+      <c r="C45" s="409" t="n"/>
+      <c r="D45" s="409" t="n"/>
       <c r="E45" s="409" t="n"/>
       <c r="F45" s="409" t="n"/>
       <c r="G45" s="409" t="n"/>
@@ -55297,23 +56112,10 @@
       <c r="L45" s="409" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="412" t="inlineStr">
-        <is>
-          <t>NET PROFIT / LOSS</t>
-        </is>
-      </c>
-      <c r="B46" s="414">
-        <f>B4-B45</f>
-        <v/>
-      </c>
-      <c r="C46" s="414">
-        <f>C4-C45</f>
-        <v/>
-      </c>
-      <c r="D46" s="414">
-        <f>D4-D45</f>
-        <v/>
-      </c>
+      <c r="A46" s="409" t="n"/>
+      <c r="B46" s="409" t="n"/>
+      <c r="C46" s="409" t="n"/>
+      <c r="D46" s="409" t="n"/>
       <c r="E46" s="409" t="n"/>
       <c r="F46" s="409" t="n"/>
       <c r="G46" s="409" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5924,7 +5924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="313" min="1" max="1"/>
@@ -7438,30 +7438,96 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="439" t="inlineStr">
+      <c r="A48" s="439" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B48" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 28-Jul)</t>
+        </is>
+      </c>
+      <c r="C48" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D48" s="232" t="n"/>
+      <c r="E48" s="233" t="n">
+        <v>130</v>
+      </c>
+      <c r="F48" s="233">
+        <f>IFERROR(F47+D48-E48,0)</f>
+        <v/>
+      </c>
+      <c r="G48" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H48" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="439" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B49" s="232" t="inlineStr">
+        <is>
+          <t>Pollo $396 (paid by Lohith)</t>
+        </is>
+      </c>
+      <c r="C49" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D49" s="232" t="n">
+        <v>396</v>
+      </c>
+      <c r="E49" s="233" t="n"/>
+      <c r="F49" s="233">
+        <f>IFERROR(F48+D49-E49,0)</f>
+        <v/>
+      </c>
+      <c r="G49" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H49" s="232" t="inlineStr">
+        <is>
+          <t>Fronted from own pocket; excluded from till via cash_adjust</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="439" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B48" s="232" t="n"/>
-      <c r="C48" s="232" t="n"/>
-      <c r="D48" s="232">
-        <f>SUM(D4:D47)</f>
+      <c r="B50" s="232" t="n"/>
+      <c r="C50" s="232" t="n"/>
+      <c r="D50" s="232">
+        <f>SUM(D4:D49)</f>
         <v/>
       </c>
-      <c r="E48" s="233">
-        <f>SUM(E4:E47)</f>
+      <c r="E50" s="233">
+        <f>SUM(E4:E49)</f>
         <v/>
       </c>
-      <c r="F48" s="233">
-        <f>F47</f>
+      <c r="F50" s="233">
+        <f>F49</f>
         <v/>
       </c>
-      <c r="G48" s="232">
-        <f>IF(F47&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F47,"#,##0"),IF(F47&lt;0,"Lohith holds $"&amp;TEXT(ABS(F47),"#,##0"),"Zero balance"))</f>
+      <c r="G50" s="232">
+        <f>IF(F49&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F49,"#,##0"),IF(F49&lt;0,"Lohith holds $"&amp;TEXT(ABS(F49),"#,##0"),"Zero balance"))</f>
         <v/>
       </c>
-      <c r="H48" s="232" t="n"/>
+      <c r="H50" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9295,45 +9361,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>3180.0</v>
+        <v>5250.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>700.0</v>
+        <v>130.0</v>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>928.0</v>
+        <v>1504.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>2252.0</v>
+        <v>3746.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>0.708176</v>
+        <v>0.713524</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>3180.0</v>
+        <v>8430.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>3180.0</v>
+        <v>8430.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>100996.0</v>
+        <v>106246.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>928.0</v>
+        <v>2432.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>2252.0</v>
+        <v>5998.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="313">
@@ -13575,33 +13641,72 @@
       <c r="AB74" s="435" t="n"/>
     </row>
     <row r="75" ht="16.5" customHeight="1" s="313">
-      <c r="B75" s="34" t="n"/>
-      <c r="C75" s="47" t="n"/>
-      <c r="D75" s="48" t="n"/>
-      <c r="E75" s="49" t="n"/>
-      <c r="F75" s="50" t="n"/>
-      <c r="G75" s="51" t="n"/>
-      <c r="H75" s="52" t="n"/>
-      <c r="I75" s="53" t="n"/>
-      <c r="J75" s="54" t="n"/>
-      <c r="K75" s="55" t="n"/>
-      <c r="L75" s="18" t="n"/>
-      <c r="M75" s="21" t="n"/>
-      <c r="N75" s="56" t="n"/>
-      <c r="O75" s="57" t="n"/>
-      <c r="P75" s="58" t="n"/>
-      <c r="Q75" s="56" t="n"/>
-      <c r="R75" s="56" t="n"/>
-      <c r="S75" s="56" t="n"/>
-      <c r="T75" s="56" t="n"/>
-      <c r="U75" s="56" t="n"/>
-      <c r="V75" s="56" t="n"/>
-      <c r="W75" s="56" t="n"/>
-      <c r="X75" s="56" t="n"/>
-      <c r="Y75" s="56" t="n"/>
-      <c r="Z75" s="56" t="n"/>
-      <c r="AA75" s="56" t="n"/>
-      <c r="AB75" s="56" t="n"/>
+      <c r="B75" s="420" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C75" s="255" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D75" s="256" t="n">
+        <v>3205</v>
+      </c>
+      <c r="E75" s="49" t="n">
+        <v>1565</v>
+      </c>
+      <c r="F75" s="50">
+        <f>IFERROR(D75+E75+G75+U75+Y75,0)</f>
+        <v>5250.0</v>
+      </c>
+      <c r="G75" s="257" t="n">
+        <v>130</v>
+      </c>
+      <c r="H75" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B75,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B75+1))</f>
+        <v>1504.0</v>
+      </c>
+      <c r="I75" s="259">
+        <f>IFERROR(F75-H75,0)</f>
+        <v>3746.0</v>
+      </c>
+      <c r="J75" s="260">
+        <f>IFERROR(I75/F75,0)</f>
+        <v>0.713524</v>
+      </c>
+      <c r="K75" s="254" t="n"/>
+      <c r="L75" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M75" s="291" t="n"/>
+      <c r="N75" s="292" t="n"/>
+      <c r="O75" s="293" t="n"/>
+      <c r="P75" s="294" t="n"/>
+      <c r="Q75" s="292" t="n"/>
+      <c r="R75" s="421">
+        <f>IFERROR(D75*$T$7,0)</f>
+        <v>130.12</v>
+      </c>
+      <c r="S75" s="292" t="n"/>
+      <c r="T75" s="292" t="n"/>
+      <c r="U75" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" s="292" t="n"/>
+      <c r="X75" s="292" t="n"/>
+      <c r="Y75" s="421" t="n">
+        <v>350</v>
+      </c>
+      <c r="Z75" s="421" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AA75" s="292" t="n"/>
+      <c r="AB75" s="292" t="n"/>
     </row>
     <row r="76" ht="16.5" customHeight="1" s="313">
       <c r="B76" s="34" t="n"/>
@@ -22218,9 +22323,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -22243,7 +22348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J548"/>
+  <dimension ref="A1:J552"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="313" min="1" max="1"/>
@@ -45310,6 +45415,178 @@
       <c r="J548" s="418" t="inlineStr">
         <is>
           <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="B549" s="422" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C549" s="305" t="inlineStr">
+        <is>
+          <t>Utensils Sushi Kit</t>
+        </is>
+      </c>
+      <c r="D549" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E549" s="305" t="inlineStr">
+        <is>
+          <t>Kitchen Supplies</t>
+        </is>
+      </c>
+      <c r="F549" s="307" t="n">
+        <v>521</v>
+      </c>
+      <c r="G549" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H549" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I549" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J549" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="B550" s="422" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C550" s="305" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="D550" s="306" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E550" s="305" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F550" s="307" t="n">
+        <v>82</v>
+      </c>
+      <c r="G550" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H550" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I550" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J550" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="B551" s="422" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C551" s="305" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D551" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E551" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F551" s="307" t="n">
+        <v>505</v>
+      </c>
+      <c r="G551" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H551" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I551" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J551" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="B552" s="422" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C552" s="305" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D552" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E552" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F552" s="307" t="n">
+        <v>396</v>
+      </c>
+      <c r="G552" s="308" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H552" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I552" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J552" s="418" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
         </is>
       </c>
     </row>
@@ -55748,7 +56025,7 @@
     <row r="31">
       <c r="A31" s="415" t="inlineStr">
         <is>
-          <t>Utilities/Internet</t>
+          <t>Kitchen Supplies</t>
         </is>
       </c>
       <c r="B31" s="413">
@@ -55775,7 +56052,7 @@
     <row r="32">
       <c r="A32" s="415" t="inlineStr">
         <is>
-          <t>Utilities/Gas</t>
+          <t>Utilities/Internet</t>
         </is>
       </c>
       <c r="B32" s="413">
@@ -55802,7 +56079,7 @@
     <row r="33">
       <c r="A33" s="415" t="inlineStr">
         <is>
-          <t>Ingredients - Other</t>
+          <t>Utilities/Gas</t>
         </is>
       </c>
       <c r="B33" s="413">
@@ -55829,7 +56106,7 @@
     <row r="34">
       <c r="A34" s="415" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Ingredients - Other</t>
         </is>
       </c>
       <c r="B34" s="413">
@@ -55856,7 +56133,7 @@
     <row r="35">
       <c r="A35" s="415" t="inlineStr">
         <is>
-          <t>Kitchen Supplies</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="B35" s="413">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5924,7 +5924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="313" min="1" max="1"/>
@@ -7504,30 +7504,96 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="439" t="inlineStr">
+      <c r="A50" s="439" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B50" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 29-Jul)</t>
+        </is>
+      </c>
+      <c r="C50" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D50" s="232" t="n"/>
+      <c r="E50" s="233" t="n">
+        <v>205</v>
+      </c>
+      <c r="F50" s="233">
+        <f>IFERROR(F49+D50-E50,0)</f>
+        <v/>
+      </c>
+      <c r="G50" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H50" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="439" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B51" s="232" t="inlineStr">
+        <is>
+          <t>Arroz Sushi HEB $60 (paid by Lohith)</t>
+        </is>
+      </c>
+      <c r="C51" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D51" s="232" t="n">
+        <v>60</v>
+      </c>
+      <c r="E51" s="233" t="n"/>
+      <c r="F51" s="233">
+        <f>IFERROR(F50+D51-E51,0)</f>
+        <v/>
+      </c>
+      <c r="G51" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H51" s="232" t="inlineStr">
+        <is>
+          <t>Fronted from own pocket; excluded from till via cash_adjust</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="439" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B50" s="232" t="n"/>
-      <c r="C50" s="232" t="n"/>
-      <c r="D50" s="232">
-        <f>SUM(D4:D49)</f>
+      <c r="B52" s="232" t="n"/>
+      <c r="C52" s="232" t="n"/>
+      <c r="D52" s="232">
+        <f>SUM(D4:D51)</f>
         <v/>
       </c>
-      <c r="E50" s="233">
-        <f>SUM(E4:E49)</f>
+      <c r="E52" s="233">
+        <f>SUM(E4:E51)</f>
         <v/>
       </c>
-      <c r="F50" s="233">
-        <f>F49</f>
+      <c r="F52" s="233">
+        <f>F51</f>
         <v/>
       </c>
-      <c r="G50" s="232">
-        <f>IF(F49&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F49,"#,##0"),IF(F49&lt;0,"Lohith holds $"&amp;TEXT(ABS(F49),"#,##0"),"Zero balance"))</f>
+      <c r="G52" s="232">
+        <f>IF(F51&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F51,"#,##0"),IF(F51&lt;0,"Lohith holds $"&amp;TEXT(ABS(F51),"#,##0"),"Zero balance"))</f>
         <v/>
       </c>
-      <c r="H50" s="232" t="n"/>
+      <c r="H52" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9361,45 +9427,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>5250.0</v>
+        <v>4120.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>130.0</v>
+        <v>205.0</v>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>1504.0</v>
+        <v>1495.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>3746.0</v>
+        <v>2625.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>0.713524</v>
+        <v>0.637136</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>8430.0</v>
+        <v>12550.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>8430.0</v>
+        <v>12550.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>106246.0</v>
+        <v>110366.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>2432.0</v>
+        <v>3927.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>5998.0</v>
+        <v>8623.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="313">
@@ -13709,33 +13775,72 @@
       <c r="AB75" s="292" t="n"/>
     </row>
     <row r="76" ht="16.5" customHeight="1" s="313">
-      <c r="B76" s="34" t="n"/>
-      <c r="C76" s="35" t="n"/>
-      <c r="D76" s="36" t="n"/>
-      <c r="E76" s="37" t="n"/>
-      <c r="F76" s="38" t="n"/>
-      <c r="G76" s="39" t="n"/>
-      <c r="H76" s="40" t="n"/>
-      <c r="I76" s="41" t="n"/>
-      <c r="J76" s="42" t="n"/>
-      <c r="K76" s="43" t="n"/>
-      <c r="L76" s="9" t="n"/>
-      <c r="M76" s="12" t="n"/>
-      <c r="N76" s="44" t="n"/>
-      <c r="O76" s="45" t="n"/>
-      <c r="P76" s="46" t="n"/>
-      <c r="Q76" s="44" t="n"/>
-      <c r="R76" s="44" t="n"/>
-      <c r="S76" s="44" t="n"/>
-      <c r="T76" s="44" t="n"/>
-      <c r="U76" s="44" t="n"/>
-      <c r="V76" s="44" t="n"/>
-      <c r="W76" s="44" t="n"/>
-      <c r="X76" s="44" t="n"/>
-      <c r="Y76" s="44" t="n"/>
-      <c r="Z76" s="44" t="n"/>
-      <c r="AA76" s="44" t="n"/>
-      <c r="AB76" s="44" t="n"/>
+      <c r="B76" s="420" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C76" s="270" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D76" s="271" t="n">
+        <v>2455</v>
+      </c>
+      <c r="E76" s="37" t="n">
+        <v>1460</v>
+      </c>
+      <c r="F76" s="38">
+        <f>IFERROR(D76+E76+G76+U76+Y76,0)</f>
+        <v>4120.0</v>
+      </c>
+      <c r="G76" s="272" t="n">
+        <v>205</v>
+      </c>
+      <c r="H76" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B76,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B76+1))</f>
+        <v>1495.0</v>
+      </c>
+      <c r="I76" s="274">
+        <f>IFERROR(F76-H76,0)</f>
+        <v>2625.0</v>
+      </c>
+      <c r="J76" s="275">
+        <f>IFERROR(I76/F76,0)</f>
+        <v>0.637136</v>
+      </c>
+      <c r="K76" s="250" t="n"/>
+      <c r="L76" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M76" s="434" t="n"/>
+      <c r="N76" s="435" t="n"/>
+      <c r="O76" s="436" t="n"/>
+      <c r="P76" s="437" t="n"/>
+      <c r="Q76" s="435" t="n"/>
+      <c r="R76" s="438">
+        <f>IFERROR(D76*$T$7,0)</f>
+        <v>99.67</v>
+      </c>
+      <c r="S76" s="435" t="n"/>
+      <c r="T76" s="435" t="n"/>
+      <c r="U76" s="438" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="438" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" s="435" t="n"/>
+      <c r="X76" s="435" t="n"/>
+      <c r="Y76" s="438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="435" t="n"/>
+      <c r="AB76" s="435" t="n"/>
     </row>
     <row r="77" ht="16.5" customHeight="1" s="313">
       <c r="B77" s="34" t="n"/>
@@ -22323,9 +22428,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I2:P2"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B5:P5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:P2"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -22348,7 +22453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J552"/>
+  <dimension ref="A1:J558"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="313" min="1" max="1"/>
@@ -45585,6 +45690,264 @@
         </is>
       </c>
       <c r="J552" s="418" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="B553" s="422" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C553" s="305" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D553" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E553" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F553" s="307" t="n">
+        <v>101</v>
+      </c>
+      <c r="G553" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H553" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I553" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J553" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="B554" s="422" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C554" s="305" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D554" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E554" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F554" s="307" t="n">
+        <v>312</v>
+      </c>
+      <c r="G554" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H554" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I554" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J554" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="B555" s="422" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C555" s="305" t="inlineStr">
+        <is>
+          <t>Atun</t>
+        </is>
+      </c>
+      <c r="D555" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E555" s="305" t="inlineStr">
+        <is>
+          <t>Supplies/Other</t>
+        </is>
+      </c>
+      <c r="F555" s="307" t="n">
+        <v>250</v>
+      </c>
+      <c r="G555" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H555" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I555" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J555" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="B556" s="422" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C556" s="305" t="inlineStr">
+        <is>
+          <t>Pan Reales</t>
+        </is>
+      </c>
+      <c r="D556" s="306" t="inlineStr">
+        <is>
+          <t>Pan Reales</t>
+        </is>
+      </c>
+      <c r="E556" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F556" s="307" t="n">
+        <v>722</v>
+      </c>
+      <c r="G556" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H556" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I556" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J556" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="B557" s="422" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C557" s="305" t="inlineStr">
+        <is>
+          <t>Chedraui Mantequilla</t>
+        </is>
+      </c>
+      <c r="D557" s="306" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E557" s="305" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F557" s="307" t="n">
+        <v>50</v>
+      </c>
+      <c r="G557" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H557" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I557" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J557" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="B558" s="422" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C558" s="305" t="inlineStr">
+        <is>
+          <t>Arroz Sushi HEB</t>
+        </is>
+      </c>
+      <c r="D558" s="306" t="inlineStr">
+        <is>
+          <t>H-E-B</t>
+        </is>
+      </c>
+      <c r="E558" s="305" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F558" s="307" t="n">
+        <v>60</v>
+      </c>
+      <c r="G558" s="308" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H558" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I558" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J558" s="418" t="inlineStr">
         <is>
           <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
         </is>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5924,7 +5924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="313" min="1" max="1"/>
@@ -7570,30 +7570,129 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="439" t="inlineStr">
+      <c r="A52" s="439" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B52" s="232" t="inlineStr">
+        <is>
+          <t>Pollo $188 + Chedraui $80 (paid by Lohith)</t>
+        </is>
+      </c>
+      <c r="C52" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D52" s="232" t="n">
+        <v>268</v>
+      </c>
+      <c r="E52" s="233" t="n"/>
+      <c r="F52" s="233">
+        <f>IFERROR(F51+D52-E52,0)</f>
+        <v/>
+      </c>
+      <c r="G52" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H52" s="232" t="inlineStr">
+        <is>
+          <t>Fronted from own pocket; excluded from till via cash_adjust</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="439" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B53" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 31-Jul)</t>
+        </is>
+      </c>
+      <c r="C53" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D53" s="232" t="n"/>
+      <c r="E53" s="233" t="n">
+        <v>390</v>
+      </c>
+      <c r="F53" s="233">
+        <f>IFERROR(F52+D53-E53,0)</f>
+        <v/>
+      </c>
+      <c r="G53" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H53" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="439" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B54" s="232" t="inlineStr">
+        <is>
+          <t>Oxxo Arroz $78 (paid by Lohith)</t>
+        </is>
+      </c>
+      <c r="C54" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D54" s="232" t="n">
+        <v>78</v>
+      </c>
+      <c r="E54" s="233" t="n"/>
+      <c r="F54" s="233">
+        <f>IFERROR(F53+D54-E54,0)</f>
+        <v/>
+      </c>
+      <c r="G54" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H54" s="232" t="inlineStr">
+        <is>
+          <t>Fronted from own pocket; excluded from till via cash_adjust</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="439" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B52" s="232" t="n"/>
-      <c r="C52" s="232" t="n"/>
-      <c r="D52" s="232">
-        <f>SUM(D4:D51)</f>
+      <c r="B55" s="232" t="n"/>
+      <c r="C55" s="232" t="n"/>
+      <c r="D55" s="232">
+        <f>SUM(D4:D54)</f>
         <v/>
       </c>
-      <c r="E52" s="233">
-        <f>SUM(E4:E51)</f>
+      <c r="E55" s="233">
+        <f>SUM(E4:E54)</f>
         <v/>
       </c>
-      <c r="F52" s="233">
-        <f>F51</f>
+      <c r="F55" s="233">
+        <f>F54</f>
         <v/>
       </c>
-      <c r="G52" s="232">
-        <f>IF(F51&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F51,"#,##0"),IF(F51&lt;0,"Lohith holds $"&amp;TEXT(ABS(F51),"#,##0"),"Zero balance"))</f>
+      <c r="G55" s="232">
+        <f>IF(F54&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F54,"#,##0"),IF(F54&lt;0,"Lohith holds $"&amp;TEXT(ABS(F54),"#,##0"),"Zero balance"))</f>
         <v/>
       </c>
-      <c r="H52" s="232" t="n"/>
+      <c r="H55" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9427,45 +9526,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>4120.0</v>
+        <v>4705.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>205.0</v>
+        <v>390.0</v>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>1495.0</v>
+        <v>1993.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>2625.0</v>
+        <v>2712.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>0.637136</v>
+        <v>0.576408</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>12550.0</v>
+        <v>20489.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>12550.0</v>
+        <v>20489.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>110366.0</v>
+        <v>118305.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>3927.0</v>
+        <v>6188.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>8623.0</v>
+        <v>14301.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="313">
@@ -13843,62 +13942,140 @@
       <c r="AB76" s="435" t="n"/>
     </row>
     <row r="77" ht="16.5" customHeight="1" s="313">
-      <c r="B77" s="34" t="n"/>
-      <c r="C77" s="47" t="n"/>
-      <c r="D77" s="48" t="n"/>
-      <c r="E77" s="49" t="n"/>
-      <c r="F77" s="50" t="n"/>
-      <c r="G77" s="51" t="n"/>
-      <c r="H77" s="52" t="n"/>
-      <c r="I77" s="53" t="n"/>
-      <c r="J77" s="54" t="n"/>
-      <c r="K77" s="55" t="n"/>
-      <c r="L77" s="18" t="n"/>
-      <c r="M77" s="21" t="n"/>
-      <c r="N77" s="56" t="n"/>
-      <c r="O77" s="57" t="n"/>
-      <c r="P77" s="58" t="n"/>
-      <c r="Q77" s="56" t="n"/>
-      <c r="R77" s="56" t="n"/>
-      <c r="S77" s="56" t="n"/>
-      <c r="T77" s="56" t="n"/>
-      <c r="U77" s="56" t="n"/>
-      <c r="V77" s="56" t="n"/>
-      <c r="W77" s="56" t="n"/>
-      <c r="X77" s="56" t="n"/>
-      <c r="Y77" s="56" t="n"/>
-      <c r="Z77" s="56" t="n"/>
-      <c r="AA77" s="56" t="n"/>
-      <c r="AB77" s="56" t="n"/>
+      <c r="B77" s="420" t="n">
+        <v>46233</v>
+      </c>
+      <c r="C77" s="255" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D77" s="256" t="n">
+        <v>1944</v>
+      </c>
+      <c r="E77" s="49" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F77" s="50">
+        <f>IFERROR(D77+E77+G77+U77+Y77,0)</f>
+        <v>3234.0</v>
+      </c>
+      <c r="G77" s="257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B77,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B77+1))</f>
+        <v>268.0</v>
+      </c>
+      <c r="I77" s="259">
+        <f>IFERROR(F77-H77,0)</f>
+        <v>2966.0</v>
+      </c>
+      <c r="J77" s="260">
+        <f>IFERROR(I77/F77,0)</f>
+        <v>0.91713</v>
+      </c>
+      <c r="K77" s="254" t="n"/>
+      <c r="L77" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M77" s="291" t="n"/>
+      <c r="N77" s="292" t="n"/>
+      <c r="O77" s="293" t="n"/>
+      <c r="P77" s="294" t="n"/>
+      <c r="Q77" s="292" t="n"/>
+      <c r="R77" s="421">
+        <f>IFERROR(D77*$T$7,0)</f>
+        <v>78.93</v>
+      </c>
+      <c r="S77" s="292" t="n"/>
+      <c r="T77" s="292" t="n"/>
+      <c r="U77" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" s="292" t="n"/>
+      <c r="X77" s="292" t="n"/>
+      <c r="Y77" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="292" t="n"/>
+      <c r="AB77" s="292" t="n"/>
     </row>
     <row r="78" ht="16.5" customHeight="1" s="313">
-      <c r="B78" s="34" t="n"/>
-      <c r="C78" s="35" t="n"/>
-      <c r="D78" s="36" t="n"/>
-      <c r="E78" s="37" t="n"/>
-      <c r="F78" s="38" t="n"/>
-      <c r="G78" s="39" t="n"/>
-      <c r="H78" s="40" t="n"/>
-      <c r="I78" s="41" t="n"/>
-      <c r="J78" s="42" t="n"/>
-      <c r="K78" s="43" t="n"/>
-      <c r="L78" s="9" t="n"/>
-      <c r="M78" s="12" t="n"/>
-      <c r="N78" s="44" t="n"/>
-      <c r="O78" s="45" t="n"/>
-      <c r="P78" s="46" t="n"/>
-      <c r="Q78" s="44" t="n"/>
-      <c r="R78" s="44" t="n"/>
-      <c r="S78" s="44" t="n"/>
-      <c r="T78" s="44" t="n"/>
-      <c r="U78" s="44" t="n"/>
-      <c r="V78" s="44" t="n"/>
-      <c r="W78" s="44" t="n"/>
-      <c r="X78" s="44" t="n"/>
-      <c r="Y78" s="44" t="n"/>
-      <c r="Z78" s="44" t="n"/>
-      <c r="AA78" s="44" t="n"/>
-      <c r="AB78" s="44" t="n"/>
+      <c r="B78" s="420" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C78" s="270" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D78" s="271" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E78" s="37" t="n">
+        <v>1815</v>
+      </c>
+      <c r="F78" s="38">
+        <f>IFERROR(D78+E78+G78+U78+Y78,0)</f>
+        <v>4705.0</v>
+      </c>
+      <c r="G78" s="272" t="n">
+        <v>390</v>
+      </c>
+      <c r="H78" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B78,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B78+1))</f>
+        <v>1993.0</v>
+      </c>
+      <c r="I78" s="274">
+        <f>IFERROR(F78-H78,0)</f>
+        <v>2712.0</v>
+      </c>
+      <c r="J78" s="275">
+        <f>IFERROR(I78/F78,0)</f>
+        <v>0.576408</v>
+      </c>
+      <c r="K78" s="250" t="n"/>
+      <c r="L78" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M78" s="434" t="n"/>
+      <c r="N78" s="435" t="n"/>
+      <c r="O78" s="436" t="n"/>
+      <c r="P78" s="437" t="n"/>
+      <c r="Q78" s="435" t="n"/>
+      <c r="R78" s="438">
+        <f>IFERROR(D78*$T$7,0)</f>
+        <v>101.5</v>
+      </c>
+      <c r="S78" s="435" t="n"/>
+      <c r="T78" s="435" t="n"/>
+      <c r="U78" s="438" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="438" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" s="435" t="n"/>
+      <c r="X78" s="435" t="n"/>
+      <c r="Y78" s="438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="435" t="n"/>
+      <c r="AB78" s="435" t="n"/>
     </row>
     <row r="79" ht="16.5" customHeight="1" s="313">
       <c r="B79" s="34" t="n"/>
@@ -22428,8 +22605,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
@@ -22453,7 +22630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J558"/>
+  <dimension ref="A1:J568"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="313" min="1" max="1"/>
@@ -45950,6 +46127,436 @@
       <c r="J558" s="418" t="inlineStr">
         <is>
           <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="B559" s="422" t="n">
+        <v>46233</v>
+      </c>
+      <c r="C559" s="305" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D559" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E559" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F559" s="307" t="n">
+        <v>188</v>
+      </c>
+      <c r="G559" s="308" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H559" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I559" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J559" s="418" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="B560" s="422" t="n">
+        <v>46233</v>
+      </c>
+      <c r="C560" s="305" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="D560" s="306" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E560" s="305" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F560" s="307" t="n">
+        <v>80</v>
+      </c>
+      <c r="G560" s="308" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H560" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I560" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J560" s="418" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="B561" s="422" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C561" s="305" t="inlineStr">
+        <is>
+          <t>Pescado</t>
+        </is>
+      </c>
+      <c r="D561" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E561" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat &amp; Fish</t>
+        </is>
+      </c>
+      <c r="F561" s="307" t="n">
+        <v>248</v>
+      </c>
+      <c r="G561" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H561" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I561" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J561" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="B562" s="422" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C562" s="305" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="D562" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E562" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F562" s="307" t="n">
+        <v>38</v>
+      </c>
+      <c r="G562" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H562" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I562" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J562" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="B563" s="422" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C563" s="305" t="inlineStr">
+        <is>
+          <t>Clorox</t>
+        </is>
+      </c>
+      <c r="D563" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E563" s="305" t="inlineStr">
+        <is>
+          <t>Kitchen Supplies</t>
+        </is>
+      </c>
+      <c r="F563" s="307" t="n">
+        <v>68</v>
+      </c>
+      <c r="G563" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H563" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I563" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J563" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="B564" s="422" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C564" s="305" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="D564" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E564" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F564" s="307" t="n">
+        <v>79</v>
+      </c>
+      <c r="G564" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H564" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I564" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J564" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="B565" s="422" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C565" s="305" t="inlineStr">
+        <is>
+          <t>Hielo</t>
+        </is>
+      </c>
+      <c r="D565" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E565" s="305" t="inlineStr">
+        <is>
+          <t>Kitchen Supplies</t>
+        </is>
+      </c>
+      <c r="F565" s="307" t="n">
+        <v>250</v>
+      </c>
+      <c r="G565" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H565" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I565" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J565" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="B566" s="422" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C566" s="305" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="D566" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E566" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F566" s="307" t="n">
+        <v>32</v>
+      </c>
+      <c r="G566" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H566" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I566" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J566" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="B567" s="422" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C567" s="305" t="inlineStr">
+        <is>
+          <t>Oxxo Arroz</t>
+        </is>
+      </c>
+      <c r="D567" s="306" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E567" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F567" s="307" t="n">
+        <v>78</v>
+      </c>
+      <c r="G567" s="308" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H567" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I567" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J567" s="418" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="B568" s="422" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C568" s="305" t="inlineStr">
+        <is>
+          <t>Samu - salary</t>
+        </is>
+      </c>
+      <c r="D568" s="306" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E568" s="305" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F568" s="307" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G568" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H568" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I568" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J568" s="418" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
         </is>
       </c>
     </row>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5924,7 +5924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="313" min="1" max="1"/>
@@ -7669,30 +7669,63 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="439" t="inlineStr">
+      <c r="A55" s="439" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B55" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 01-Aug)</t>
+        </is>
+      </c>
+      <c r="C55" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D55" s="232" t="n"/>
+      <c r="E55" s="233" t="n">
+        <v>225</v>
+      </c>
+      <c r="F55" s="233">
+        <f>IFERROR(F54+D55-E55,0)</f>
+        <v/>
+      </c>
+      <c r="G55" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H55" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="439" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B55" s="232" t="n"/>
-      <c r="C55" s="232" t="n"/>
-      <c r="D55" s="232">
-        <f>SUM(D4:D54)</f>
-        <v/>
-      </c>
-      <c r="E55" s="233">
-        <f>SUM(E4:E54)</f>
-        <v/>
-      </c>
-      <c r="F55" s="233">
-        <f>F54</f>
-        <v/>
-      </c>
-      <c r="G55" s="232">
-        <f>IF(F54&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F54,"#,##0"),IF(F54&lt;0,"Lohith holds $"&amp;TEXT(ABS(F54),"#,##0"),"Zero balance"))</f>
-        <v/>
-      </c>
-      <c r="H55" s="232" t="n"/>
+      <c r="B56" s="232" t="n"/>
+      <c r="C56" s="232" t="n"/>
+      <c r="D56" s="232">
+        <f>SUM(D4:D55)</f>
+        <v/>
+      </c>
+      <c r="E56" s="233">
+        <f>SUM(E4:E55)</f>
+        <v/>
+      </c>
+      <c r="F56" s="233">
+        <f>F55</f>
+        <v/>
+      </c>
+      <c r="G56" s="232">
+        <f>IF(F55&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F55,"#,##0"),IF(F55&lt;0,"Lohith holds $"&amp;TEXT(ABS(F55),"#,##0"),"Zero balance"))</f>
+        <v/>
+      </c>
+      <c r="H56" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9526,45 +9559,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>4705.0</v>
+        <v>3738.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>390.0</v>
+        <v>225.0</v>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>1993.0</v>
+        <v>7208.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>2712.0</v>
+        <v>-3470.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>0.576408</v>
+        <v>-0.928304</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>20489.0</v>
+        <v>24227.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>20489.0</v>
+        <v>24227.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>118305.0</v>
+        <v>3738.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>6188.0</v>
+        <v>13396.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>14301.0</v>
+        <v>10831.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="313">
@@ -14078,33 +14111,72 @@
       <c r="AB78" s="435" t="n"/>
     </row>
     <row r="79" ht="16.5" customHeight="1" s="313">
-      <c r="B79" s="34" t="n"/>
-      <c r="C79" s="47" t="n"/>
-      <c r="D79" s="48" t="n"/>
-      <c r="E79" s="49" t="n"/>
-      <c r="F79" s="50" t="n"/>
-      <c r="G79" s="51" t="n"/>
-      <c r="H79" s="52" t="n"/>
-      <c r="I79" s="53" t="n"/>
-      <c r="J79" s="54" t="n"/>
-      <c r="K79" s="55" t="n"/>
-      <c r="L79" s="18" t="n"/>
-      <c r="M79" s="21" t="n"/>
-      <c r="N79" s="56" t="n"/>
-      <c r="O79" s="57" t="n"/>
-      <c r="P79" s="58" t="n"/>
-      <c r="Q79" s="56" t="n"/>
-      <c r="R79" s="56" t="n"/>
-      <c r="S79" s="56" t="n"/>
-      <c r="T79" s="56" t="n"/>
-      <c r="U79" s="56" t="n"/>
-      <c r="V79" s="56" t="n"/>
-      <c r="W79" s="56" t="n"/>
-      <c r="X79" s="56" t="n"/>
-      <c r="Y79" s="56" t="n"/>
-      <c r="Z79" s="56" t="n"/>
-      <c r="AA79" s="56" t="n"/>
-      <c r="AB79" s="56" t="n"/>
+      <c r="B79" s="420" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C79" s="255" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D79" s="256" t="n">
+        <v>2238</v>
+      </c>
+      <c r="E79" s="49" t="n">
+        <v>1275</v>
+      </c>
+      <c r="F79" s="50">
+        <f>IFERROR(D79+E79+G79+U79+Y79,0)</f>
+        <v>3738.0</v>
+      </c>
+      <c r="G79" s="257" t="n">
+        <v>225</v>
+      </c>
+      <c r="H79" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B79,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B79+1))</f>
+        <v>7208.0</v>
+      </c>
+      <c r="I79" s="259">
+        <f>IFERROR(F79-H79,0)</f>
+        <v>-3470.0</v>
+      </c>
+      <c r="J79" s="260">
+        <f>IFERROR(I79/F79,0)</f>
+        <v>-0.928304</v>
+      </c>
+      <c r="K79" s="254" t="n"/>
+      <c r="L79" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M79" s="291" t="n"/>
+      <c r="N79" s="292" t="n"/>
+      <c r="O79" s="293" t="n"/>
+      <c r="P79" s="294" t="n"/>
+      <c r="Q79" s="292" t="n"/>
+      <c r="R79" s="421">
+        <f>IFERROR(D79*$T$7,0)</f>
+        <v>90.86</v>
+      </c>
+      <c r="S79" s="292" t="n"/>
+      <c r="T79" s="292" t="n"/>
+      <c r="U79" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" s="292" t="n"/>
+      <c r="X79" s="292" t="n"/>
+      <c r="Y79" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="421" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="292" t="n"/>
+      <c r="AB79" s="292" t="n"/>
     </row>
     <row r="80" ht="16.5" customHeight="1" s="313">
       <c r="B80" s="34" t="n"/>
@@ -22630,7 +22702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J568"/>
+  <dimension ref="A1:J575"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="313" min="1" max="1"/>
@@ -46557,6 +46629,307 @@
       <c r="J568" s="418" t="inlineStr">
         <is>
           <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="B569" s="422" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C569" s="305" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="D569" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E569" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F569" s="307" t="n">
+        <v>160</v>
+      </c>
+      <c r="G569" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H569" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I569" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J569" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="B570" s="422" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C570" s="305" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="D570" s="306" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E570" s="305" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F570" s="307" t="n">
+        <v>148</v>
+      </c>
+      <c r="G570" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H570" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I570" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J570" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="B571" s="422" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C571" s="305" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="D571" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E571" s="305" t="inlineStr">
+        <is>
+          <t>Utilities/Gas</t>
+        </is>
+      </c>
+      <c r="F571" s="307" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G571" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H571" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I571" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J571" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="B572" s="422" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C572" s="305" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D572" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E572" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F572" s="307" t="n">
+        <v>150</v>
+      </c>
+      <c r="G572" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H572" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I572" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J572" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="B573" s="422" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C573" s="305" t="inlineStr">
+        <is>
+          <t>Duvi - salary</t>
+        </is>
+      </c>
+      <c r="D573" s="306" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E573" s="305" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F573" s="307" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G573" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H573" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I573" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J573" s="418" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="B574" s="422" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C574" s="305" t="inlineStr">
+        <is>
+          <t>Jhon - salary</t>
+        </is>
+      </c>
+      <c r="D574" s="306" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E574" s="305" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F574" s="307" t="n">
+        <v>3750</v>
+      </c>
+      <c r="G574" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H574" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I574" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J574" s="418" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="B575" s="422" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C575" s="305" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D575" s="306" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E575" s="305" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F575" s="307" t="n">
+        <v>1472</v>
+      </c>
+      <c r="G575" s="308" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H575" s="308" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I575" s="309" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J575" s="418" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
         </is>
       </c>
     </row>
@@ -56209,7 +56582,7 @@
     <col width="15" bestFit="1" customWidth="1" style="313" min="2" max="2"/>
     <col width="15" customWidth="1" style="313" min="3" max="4"/>
     <col width="15" customWidth="1" style="313" min="4" max="4"/>
-    <col width="9" customWidth="1" style="313" min="5" max="14"/>
+    <col width="15" customWidth="1" style="313" min="5" max="14"/>
     <col width="9" customWidth="1" style="313" min="6" max="6"/>
     <col width="9" customWidth="1" style="313" min="7" max="7"/>
     <col width="9" customWidth="1" style="313" min="8" max="8"/>
@@ -56230,7 +56603,7 @@
       <c r="B1" s="408" t="n"/>
       <c r="C1" s="408" t="n"/>
       <c r="D1" s="408" t="n"/>
-      <c r="E1" s="409" t="n"/>
+      <c r="E1" s="408" t="n"/>
       <c r="F1" s="409" t="n"/>
       <c r="G1" s="409" t="n"/>
       <c r="H1" s="409" t="n"/>
@@ -56274,7 +56647,11 @@
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="E3" s="409" t="n"/>
+      <c r="E3" s="411" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
       <c r="F3" s="409" t="n"/>
       <c r="G3" s="409" t="n"/>
       <c r="H3" s="409" t="n"/>
@@ -56301,7 +56678,10 @@
         <f>SUMIFS('📅 Daily Log'!$F$8:$F$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E4" s="409" t="n"/>
+      <c r="E4" s="413">
+        <f>SUMIFS('📅 Daily Log'!$F$8:$F$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F4" s="409" t="n"/>
       <c r="G4" s="409" t="n"/>
       <c r="H4" s="409" t="n"/>
@@ -56328,7 +56708,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E5" s="409" t="n"/>
+      <c r="E5" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F5" s="409" t="n"/>
       <c r="G5" s="409" t="n"/>
       <c r="H5" s="409" t="n"/>
@@ -56355,7 +56738,10 @@
         <f>D4-D5</f>
         <v/>
       </c>
-      <c r="E6" s="409" t="n"/>
+      <c r="E6" s="414">
+        <f>E4-E5</f>
+        <v/>
+      </c>
       <c r="F6" s="409" t="n"/>
       <c r="G6" s="409" t="n"/>
       <c r="H6" s="409" t="n"/>
@@ -56382,7 +56768,10 @@
         <f>COUNTIFS('📅 Daily Log'!$F$8:$F$5000,"&gt;0",'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E7" s="409" t="n"/>
+      <c r="E7" s="416">
+        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$5000,"&gt;0",'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F7" s="409" t="n"/>
       <c r="G7" s="409" t="n"/>
       <c r="H7" s="409" t="n"/>
@@ -56409,7 +56798,10 @@
         <f>IFERROR(D4/D7,0)</f>
         <v/>
       </c>
-      <c r="E8" s="409" t="n"/>
+      <c r="E8" s="413">
+        <f>IFERROR(E4/E7,0)</f>
+        <v/>
+      </c>
       <c r="F8" s="409" t="n"/>
       <c r="G8" s="409" t="n"/>
       <c r="H8" s="409" t="n"/>
@@ -56453,7 +56845,11 @@
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="E10" s="409" t="n"/>
+      <c r="E10" s="411" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
       <c r="F10" s="409" t="n"/>
       <c r="G10" s="409" t="n"/>
       <c r="H10" s="409" t="n"/>
@@ -56480,7 +56876,10 @@
         <f>SUMIFS('📅 Daily Log'!$D$8:$D$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E11" s="409" t="n"/>
+      <c r="E11" s="413">
+        <f>SUMIFS('📅 Daily Log'!$D$8:$D$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F11" s="409" t="n"/>
       <c r="G11" s="409" t="n"/>
       <c r="H11" s="409" t="n"/>
@@ -56507,7 +56906,10 @@
         <f>SUMIFS('📅 Daily Log'!$E$8:$E$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E12" s="409" t="n"/>
+      <c r="E12" s="413">
+        <f>SUMIFS('📅 Daily Log'!$E$8:$E$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F12" s="409" t="n"/>
       <c r="G12" s="409" t="n"/>
       <c r="H12" s="409" t="n"/>
@@ -56534,7 +56936,10 @@
         <f>SUMIFS('📅 Daily Log'!$G$8:$G$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E13" s="409" t="n"/>
+      <c r="E13" s="413">
+        <f>SUMIFS('📅 Daily Log'!$G$8:$G$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F13" s="409" t="n"/>
       <c r="G13" s="409" t="n"/>
       <c r="H13" s="409" t="n"/>
@@ -56561,7 +56966,10 @@
         <f>D11+D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="409" t="n"/>
+      <c r="E14" s="414">
+        <f>E11+E12+E13</f>
+        <v/>
+      </c>
       <c r="F14" s="409" t="n"/>
       <c r="G14" s="409" t="n"/>
       <c r="H14" s="409" t="n"/>
@@ -56605,7 +57013,11 @@
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="E16" s="409" t="n"/>
+      <c r="E16" s="411" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
       <c r="F16" s="409" t="n"/>
       <c r="G16" s="409" t="n"/>
       <c r="H16" s="409" t="n"/>
@@ -56632,7 +57044,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A17,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E17" s="409" t="n"/>
+      <c r="E17" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A17,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F17" s="409" t="n"/>
       <c r="G17" s="409" t="n"/>
       <c r="H17" s="409" t="n"/>
@@ -56659,7 +57074,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A18,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E18" s="409" t="n"/>
+      <c r="E18" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A18,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F18" s="409" t="n"/>
       <c r="G18" s="409" t="n"/>
       <c r="H18" s="409" t="n"/>
@@ -56686,7 +57104,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A19,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E19" s="409" t="n"/>
+      <c r="E19" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A19,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F19" s="409" t="n"/>
       <c r="G19" s="409" t="n"/>
       <c r="H19" s="409" t="n"/>
@@ -56713,7 +57134,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A20,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E20" s="409" t="n"/>
+      <c r="E20" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A20,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F20" s="409" t="n"/>
       <c r="G20" s="409" t="n"/>
       <c r="H20" s="409" t="n"/>
@@ -56740,7 +57164,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A21,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E21" s="409" t="n"/>
+      <c r="E21" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A21,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F21" s="409" t="n"/>
       <c r="G21" s="409" t="n"/>
       <c r="H21" s="409" t="n"/>
@@ -56767,7 +57194,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A22,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E22" s="409" t="n"/>
+      <c r="E22" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A22,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F22" s="409" t="n"/>
       <c r="G22" s="409" t="n"/>
       <c r="H22" s="409" t="n"/>
@@ -56794,7 +57224,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A23,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E23" s="409" t="n"/>
+      <c r="E23" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A23,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F23" s="409" t="n"/>
       <c r="G23" s="409" t="n"/>
       <c r="H23" s="409" t="n"/>
@@ -56821,7 +57254,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A24,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E24" s="409" t="n"/>
+      <c r="E24" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A24,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F24" s="409" t="n"/>
       <c r="G24" s="409" t="n"/>
       <c r="H24" s="409" t="n"/>
@@ -56848,7 +57284,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A25,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E25" s="409" t="n"/>
+      <c r="E25" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A25,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F25" s="409" t="n"/>
       <c r="G25" s="409" t="n"/>
       <c r="H25" s="409" t="n"/>
@@ -56875,7 +57314,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A26,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E26" s="409" t="n"/>
+      <c r="E26" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A26,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F26" s="409" t="n"/>
       <c r="G26" s="409" t="n"/>
       <c r="H26" s="409" t="n"/>
@@ -56902,7 +57344,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A27,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E27" s="409" t="n"/>
+      <c r="E27" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A27,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F27" s="409" t="n"/>
       <c r="G27" s="409" t="n"/>
       <c r="H27" s="409" t="n"/>
@@ -56929,7 +57374,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A28,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E28" s="409" t="n"/>
+      <c r="E28" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A28,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F28" s="409" t="n"/>
       <c r="G28" s="409" t="n"/>
       <c r="H28" s="409" t="n"/>
@@ -56956,7 +57404,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A29,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E29" s="409" t="n"/>
+      <c r="E29" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A29,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F29" s="409" t="n"/>
       <c r="G29" s="409" t="n"/>
       <c r="H29" s="409" t="n"/>
@@ -56968,7 +57419,7 @@
     <row r="30">
       <c r="A30" s="415" t="inlineStr">
         <is>
-          <t>Ingredients - Fruit</t>
+          <t>Utilities/Gas</t>
         </is>
       </c>
       <c r="B30" s="413">
@@ -56983,7 +57434,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A30,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E30" s="409" t="n"/>
+      <c r="E30" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A30,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F30" s="409" t="n"/>
       <c r="G30" s="409" t="n"/>
       <c r="H30" s="409" t="n"/>
@@ -56995,7 +57449,7 @@
     <row r="31">
       <c r="A31" s="415" t="inlineStr">
         <is>
-          <t>Kitchen Supplies</t>
+          <t>Ingredients - Fruit</t>
         </is>
       </c>
       <c r="B31" s="413">
@@ -57010,7 +57464,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A31,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E31" s="409" t="n"/>
+      <c r="E31" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A31,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F31" s="409" t="n"/>
       <c r="G31" s="409" t="n"/>
       <c r="H31" s="409" t="n"/>
@@ -57022,7 +57479,7 @@
     <row r="32">
       <c r="A32" s="415" t="inlineStr">
         <is>
-          <t>Utilities/Internet</t>
+          <t>Kitchen Supplies</t>
         </is>
       </c>
       <c r="B32" s="413">
@@ -57037,7 +57494,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A32,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E32" s="409" t="n"/>
+      <c r="E32" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A32,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F32" s="409" t="n"/>
       <c r="G32" s="409" t="n"/>
       <c r="H32" s="409" t="n"/>
@@ -57049,7 +57509,7 @@
     <row r="33">
       <c r="A33" s="415" t="inlineStr">
         <is>
-          <t>Utilities/Gas</t>
+          <t>Utilities/Internet</t>
         </is>
       </c>
       <c r="B33" s="413">
@@ -57064,7 +57524,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A33,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E33" s="409" t="n"/>
+      <c r="E33" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A33,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F33" s="409" t="n"/>
       <c r="G33" s="409" t="n"/>
       <c r="H33" s="409" t="n"/>
@@ -57091,7 +57554,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A34,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E34" s="409" t="n"/>
+      <c r="E34" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A34,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F34" s="409" t="n"/>
       <c r="G34" s="409" t="n"/>
       <c r="H34" s="409" t="n"/>
@@ -57118,7 +57584,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A35,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E35" s="409" t="n"/>
+      <c r="E35" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A35,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F35" s="409" t="n"/>
       <c r="G35" s="409" t="n"/>
       <c r="H35" s="409" t="n"/>
@@ -57145,7 +57614,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A36,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E36" s="409" t="n"/>
+      <c r="E36" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A36,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F36" s="409" t="n"/>
       <c r="G36" s="409" t="n"/>
       <c r="H36" s="409" t="n"/>
@@ -57172,7 +57644,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A37,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E37" s="409" t="n"/>
+      <c r="E37" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A37,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F37" s="409" t="n"/>
       <c r="G37" s="409" t="n"/>
       <c r="H37" s="409" t="n"/>
@@ -57199,7 +57674,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A38,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E38" s="409" t="n"/>
+      <c r="E38" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A38,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F38" s="409" t="n"/>
       <c r="G38" s="409" t="n"/>
       <c r="H38" s="409" t="n"/>
@@ -57226,7 +57704,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A39,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E39" s="409" t="n"/>
+      <c r="E39" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A39,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F39" s="409" t="n"/>
       <c r="G39" s="409" t="n"/>
       <c r="H39" s="409" t="n"/>
@@ -57253,7 +57734,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A40,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E40" s="409" t="n"/>
+      <c r="E40" s="413">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A40,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F40" s="409" t="n"/>
       <c r="G40" s="409" t="n"/>
       <c r="H40" s="409" t="n"/>
@@ -57280,7 +57764,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E41" s="409" t="n"/>
+      <c r="E41" s="414">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+        <v/>
+      </c>
       <c r="F41" s="409" t="n"/>
       <c r="G41" s="409" t="n"/>
       <c r="H41" s="409" t="n"/>
@@ -57307,7 +57794,10 @@
         <f>D4-D41</f>
         <v/>
       </c>
-      <c r="E42" s="409" t="n"/>
+      <c r="E42" s="414">
+        <f>E4-E41</f>
+        <v/>
+      </c>
       <c r="F42" s="409" t="n"/>
       <c r="G42" s="409" t="n"/>
       <c r="H42" s="409" t="n"/>
@@ -57570,7 +58060,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -19,7 +19,7 @@
     <sheet name="💰 Owner Ledger" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1008,7 +1008,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -1358,11 +1358,15 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <right/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25"/>
   </cellStyleXfs>
-  <cellXfs count="441">
+  <cellXfs count="443">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2486,6 +2490,10 @@
     <xf numFmtId="3" fontId="99" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="100" fillId="58" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5482,11 +5490,11 @@
         </is>
       </c>
       <c r="C147" s="268" t="n">
-        <v>16727.81</v>
+        <v>42716.85</v>
       </c>
       <c r="E147" s="286" t="inlineStr">
         <is>
-          <t>Advance from capital-funded operating costs; repaid from operating cash: $20,000 (21-Jul) + $2,587 (22-Jul). Net advance still owed = $16,727.81.</t>
+          <t>Operating costs funded from partner capital, net of repayments. Latest addition 04-Aug-2026 $25,989.04. Still owed by Operations: $42,716.85.</t>
         </is>
       </c>
     </row>
@@ -22765,8 +22773,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I2:P2"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:P2"/>
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
@@ -22790,7 +22798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J576"/>
+  <dimension ref="A1:J578"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -47061,6 +47069,92 @@
       <c r="J576" s="423" t="inlineStr">
         <is>
           <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="B577" s="429" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C577" s="297" t="inlineStr">
+        <is>
+          <t>Renta mensual Agosto 2026</t>
+        </is>
+      </c>
+      <c r="D577" s="298" t="inlineStr">
+        <is>
+          <t>Arrendador</t>
+        </is>
+      </c>
+      <c r="E577" s="297" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="F577" s="299" t="n">
+        <v>17200.04</v>
+      </c>
+      <c r="G577" s="300" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H577" s="300" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="I577" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J577" s="423" t="inlineStr">
+        <is>
+          <t>Renta contractual 19,066.68/mes. Jun y Jul se pagaron 20,000 c/u = sobrepago 933.32 x2 = 1,866.64, acreditado este mes: 19,066.68 - 1,866.64 = 17,200.04. Pagado con capital de socios. DESDE SEPTIEMBRE la renta mensual es 19,066.68.</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="B578" s="429" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C578" s="297" t="inlineStr">
+        <is>
+          <t>Recibo de luz CFE</t>
+        </is>
+      </c>
+      <c r="D578" s="298" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="E578" s="297" t="inlineStr">
+        <is>
+          <t>Utilities/Electricity</t>
+        </is>
+      </c>
+      <c r="F578" s="299" t="n">
+        <v>8789</v>
+      </c>
+      <c r="G578" s="300" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H578" s="300" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="I578" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J578" s="423" t="inlineStr">
+        <is>
+          <t>Recibo de luz pagado con capital de socios.</t>
         </is>
       </c>
     </row>
@@ -50977,7 +51071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="18.33203125" customWidth="1" style="331" min="1" max="1"/>
@@ -52637,61 +52731,405 @@
       <c r="D92" s="264" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="262" t="n"/>
-      <c r="B93" s="262" t="inlineStr">
-        <is>
-          <t>TOTAL TIPS PASSED THROUGH</t>
-        </is>
-      </c>
+      <c r="A93" s="263" t="n"/>
+      <c r="B93" s="262" t="n"/>
       <c r="C93" s="262" t="n"/>
-      <c r="D93" s="264">
-        <f>SUM(D63:D92)</f>
-        <v/>
-      </c>
+      <c r="D93" s="264" t="n"/>
+      <c r="E93" s="423" t="n"/>
+      <c r="F93" s="423" t="n"/>
+      <c r="G93" s="423" t="n"/>
+      <c r="H93" s="423" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="262" t="inlineStr">
-        <is>
-          <t>Customer tips collected &amp; handed to staff. Excluded from P&amp;L — nets to zero (received = paid).</t>
-        </is>
-      </c>
+      <c r="A94" s="263" t="n"/>
       <c r="B94" s="262" t="n"/>
       <c r="C94" s="262" t="n"/>
-      <c r="D94" s="262" t="n"/>
+      <c r="D94" s="264" t="n"/>
+      <c r="E94" s="423" t="n"/>
+      <c r="F94" s="423" t="n"/>
+      <c r="G94" s="423" t="n"/>
+      <c r="H94" s="423" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="263" t="n"/>
+      <c r="B95" s="262" t="n"/>
+      <c r="C95" s="262" t="n"/>
+      <c r="D95" s="264" t="n"/>
+      <c r="E95" s="423" t="n"/>
+      <c r="F95" s="423" t="n"/>
+      <c r="G95" s="423" t="n"/>
+      <c r="H95" s="423" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="263" t="n"/>
+      <c r="B96" s="262" t="n"/>
+      <c r="C96" s="262" t="n"/>
+      <c r="D96" s="264" t="n"/>
+      <c r="E96" s="423" t="n"/>
+      <c r="F96" s="423" t="n"/>
+      <c r="G96" s="423" t="n"/>
+      <c r="H96" s="423" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="263" t="n"/>
+      <c r="B97" s="262" t="n"/>
+      <c r="C97" s="262" t="n"/>
+      <c r="D97" s="264" t="n"/>
+      <c r="E97" s="423" t="n"/>
+      <c r="F97" s="423" t="n"/>
+      <c r="G97" s="423" t="n"/>
+      <c r="H97" s="423" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="263" t="n"/>
+      <c r="B98" s="262" t="n"/>
+      <c r="C98" s="262" t="n"/>
+      <c r="D98" s="264" t="n"/>
+      <c r="E98" s="423" t="n"/>
+      <c r="F98" s="423" t="n"/>
+      <c r="G98" s="423" t="n"/>
+      <c r="H98" s="423" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="263" t="n"/>
+      <c r="B99" s="262" t="n"/>
+      <c r="C99" s="262" t="n"/>
+      <c r="D99" s="264" t="n"/>
+      <c r="E99" s="423" t="n"/>
+      <c r="F99" s="423" t="n"/>
+      <c r="G99" s="423" t="n"/>
+      <c r="H99" s="423" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="263" t="n"/>
+      <c r="B100" s="262" t="n"/>
+      <c r="C100" s="262" t="n"/>
+      <c r="D100" s="264" t="n"/>
+      <c r="E100" s="423" t="n"/>
+      <c r="F100" s="423" t="n"/>
+      <c r="G100" s="423" t="n"/>
+      <c r="H100" s="423" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="263" t="n"/>
+      <c r="B101" s="262" t="n"/>
+      <c r="C101" s="262" t="n"/>
+      <c r="D101" s="264" t="n"/>
+      <c r="E101" s="423" t="n"/>
+      <c r="F101" s="423" t="n"/>
+      <c r="G101" s="423" t="n"/>
+      <c r="H101" s="423" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="263" t="n"/>
+      <c r="B102" s="262" t="n"/>
+      <c r="C102" s="262" t="n"/>
+      <c r="D102" s="264" t="n"/>
+      <c r="E102" s="423" t="n"/>
+      <c r="F102" s="423" t="n"/>
+      <c r="G102" s="423" t="n"/>
+      <c r="H102" s="423" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="263" t="n"/>
+      <c r="B103" s="262" t="n"/>
+      <c r="C103" s="262" t="n"/>
+      <c r="D103" s="264" t="n"/>
+      <c r="E103" s="423" t="n"/>
+      <c r="F103" s="423" t="n"/>
+      <c r="G103" s="423" t="n"/>
+      <c r="H103" s="423" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="263" t="n"/>
+      <c r="B104" s="262" t="n"/>
+      <c r="C104" s="262" t="n"/>
+      <c r="D104" s="264" t="n"/>
+      <c r="E104" s="423" t="n"/>
+      <c r="F104" s="423" t="n"/>
+      <c r="G104" s="423" t="n"/>
+      <c r="H104" s="423" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="263" t="n"/>
+      <c r="B105" s="262" t="n"/>
+      <c r="C105" s="262" t="n"/>
+      <c r="D105" s="264" t="n"/>
+      <c r="E105" s="423" t="n"/>
+      <c r="F105" s="423" t="n"/>
+      <c r="G105" s="423" t="n"/>
+      <c r="H105" s="423" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="263" t="n"/>
+      <c r="B106" s="262" t="n"/>
+      <c r="C106" s="262" t="n"/>
+      <c r="D106" s="264" t="n"/>
+      <c r="E106" s="423" t="n"/>
+      <c r="F106" s="423" t="n"/>
+      <c r="G106" s="423" t="n"/>
+      <c r="H106" s="423" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="263" t="n"/>
+      <c r="B107" s="262" t="n"/>
+      <c r="C107" s="262" t="n"/>
+      <c r="D107" s="264" t="n"/>
+      <c r="E107" s="423" t="n"/>
+      <c r="F107" s="423" t="n"/>
+      <c r="G107" s="423" t="n"/>
+      <c r="H107" s="423" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="263" t="n"/>
+      <c r="B108" s="262" t="n"/>
+      <c r="C108" s="262" t="n"/>
+      <c r="D108" s="264" t="n"/>
+      <c r="E108" s="423" t="n"/>
+      <c r="F108" s="423" t="n"/>
+      <c r="G108" s="423" t="n"/>
+      <c r="H108" s="423" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="263" t="n"/>
+      <c r="B109" s="262" t="n"/>
+      <c r="C109" s="262" t="n"/>
+      <c r="D109" s="264" t="n"/>
+      <c r="E109" s="423" t="n"/>
+      <c r="F109" s="423" t="n"/>
+      <c r="G109" s="423" t="n"/>
+      <c r="H109" s="423" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="263" t="n"/>
+      <c r="B110" s="262" t="n"/>
+      <c r="C110" s="262" t="n"/>
+      <c r="D110" s="264" t="n"/>
+      <c r="E110" s="423" t="n"/>
+      <c r="F110" s="423" t="n"/>
+      <c r="G110" s="423" t="n"/>
+      <c r="H110" s="423" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="263" t="n"/>
+      <c r="B111" s="262" t="n"/>
+      <c r="C111" s="262" t="n"/>
+      <c r="D111" s="264" t="n"/>
+      <c r="E111" s="423" t="n"/>
+      <c r="F111" s="423" t="n"/>
+      <c r="G111" s="423" t="n"/>
+      <c r="H111" s="423" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="263" t="n"/>
+      <c r="B112" s="262" t="n"/>
+      <c r="C112" s="262" t="n"/>
+      <c r="D112" s="264" t="n"/>
+      <c r="E112" s="423" t="n"/>
+      <c r="F112" s="423" t="n"/>
+      <c r="G112" s="423" t="n"/>
+      <c r="H112" s="423" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="263" t="n"/>
+      <c r="B113" s="262" t="n"/>
+      <c r="C113" s="262" t="n"/>
+      <c r="D113" s="264" t="n"/>
+      <c r="E113" s="423" t="n"/>
+      <c r="F113" s="423" t="n"/>
+      <c r="G113" s="423" t="n"/>
+      <c r="H113" s="423" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="263" t="n"/>
+      <c r="B114" s="262" t="n"/>
+      <c r="C114" s="262" t="n"/>
+      <c r="D114" s="264" t="n"/>
+      <c r="E114" s="423" t="n"/>
+      <c r="F114" s="423" t="n"/>
+      <c r="G114" s="423" t="n"/>
+      <c r="H114" s="423" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="263" t="n"/>
+      <c r="B115" s="262" t="n"/>
+      <c r="C115" s="262" t="n"/>
+      <c r="D115" s="264" t="n"/>
+      <c r="E115" s="423" t="n"/>
+      <c r="F115" s="423" t="n"/>
+      <c r="G115" s="423" t="n"/>
+      <c r="H115" s="423" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="263" t="n"/>
+      <c r="B116" s="262" t="n"/>
+      <c r="C116" s="262" t="n"/>
+      <c r="D116" s="264" t="n"/>
+      <c r="E116" s="423" t="n"/>
+      <c r="F116" s="423" t="n"/>
+      <c r="G116" s="423" t="n"/>
+      <c r="H116" s="423" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="263" t="n"/>
+      <c r="B117" s="262" t="n"/>
+      <c r="C117" s="262" t="n"/>
+      <c r="D117" s="264" t="n"/>
+      <c r="E117" s="423" t="n"/>
+      <c r="F117" s="423" t="n"/>
+      <c r="G117" s="423" t="n"/>
+      <c r="H117" s="423" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="263" t="n"/>
+      <c r="B118" s="262" t="n"/>
+      <c r="C118" s="262" t="n"/>
+      <c r="D118" s="264" t="n"/>
+      <c r="E118" s="423" t="n"/>
+      <c r="F118" s="423" t="n"/>
+      <c r="G118" s="423" t="n"/>
+      <c r="H118" s="423" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="263" t="n"/>
+      <c r="B119" s="262" t="n"/>
+      <c r="C119" s="262" t="n"/>
+      <c r="D119" s="264" t="n"/>
+      <c r="E119" s="423" t="n"/>
+      <c r="F119" s="423" t="n"/>
+      <c r="G119" s="423" t="n"/>
+      <c r="H119" s="423" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="263" t="n"/>
+      <c r="B120" s="262" t="n"/>
+      <c r="C120" s="262" t="n"/>
+      <c r="D120" s="264" t="n"/>
+      <c r="E120" s="423" t="n"/>
+      <c r="F120" s="423" t="n"/>
+      <c r="G120" s="423" t="n"/>
+      <c r="H120" s="423" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="263" t="n"/>
+      <c r="B121" s="262" t="n"/>
+      <c r="C121" s="262" t="n"/>
+      <c r="D121" s="264" t="n"/>
+      <c r="E121" s="423" t="n"/>
+      <c r="F121" s="423" t="n"/>
+      <c r="G121" s="423" t="n"/>
+      <c r="H121" s="423" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="263" t="n"/>
+      <c r="B122" s="262" t="n"/>
+      <c r="C122" s="262" t="n"/>
+      <c r="D122" s="264" t="n"/>
+      <c r="E122" s="423" t="n"/>
+      <c r="F122" s="423" t="n"/>
+      <c r="G122" s="423" t="n"/>
+      <c r="H122" s="423" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="262" t="n"/>
+      <c r="B123" s="262" t="inlineStr">
+        <is>
+          <t>TOTAL TIPS PASSED THROUGH</t>
+        </is>
+      </c>
+      <c r="C123" s="262" t="n"/>
+      <c r="D123" s="264">
+        <f>SUM(D63:D122)</f>
+        <v/>
+      </c>
+      <c r="E123" s="423" t="n"/>
+      <c r="F123" s="423" t="n"/>
+      <c r="G123" s="423" t="n"/>
+      <c r="H123" s="423" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="262" t="inlineStr">
+        <is>
+          <t>Customer tips collected &amp; handed to staff. Excluded from P&amp;L — nets to zero (received = paid).</t>
+        </is>
+      </c>
+      <c r="B124" s="262" t="n"/>
+      <c r="C124" s="262" t="n"/>
+      <c r="D124" s="262" t="n"/>
+      <c r="E124" s="423" t="n"/>
+      <c r="F124" s="423" t="n"/>
+      <c r="G124" s="423" t="n"/>
+      <c r="H124" s="423" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="423" t="n"/>
+      <c r="B125" s="423" t="n"/>
+      <c r="C125" s="423" t="n"/>
+      <c r="D125" s="423" t="n"/>
+      <c r="E125" s="423" t="n"/>
+      <c r="F125" s="423" t="n"/>
+      <c r="G125" s="423" t="n"/>
+      <c r="H125" s="423" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="423" t="inlineStr">
         <is>
           <t>── CASH RECONCILIATION (15 Jun 2026) ──</t>
         </is>
       </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="B126" s="423" t="n"/>
+      <c r="C126" s="423" t="n"/>
+      <c r="D126" s="423" t="n"/>
+      <c r="E126" s="423" t="n"/>
+      <c r="F126" s="423" t="n"/>
+      <c r="G126" s="423" t="n"/>
+      <c r="H126" s="423" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="423" t="inlineStr">
         <is>
           <t>Actual restaurant cash on hand</t>
         </is>
       </c>
-      <c r="D97" s="228" t="n">
+      <c r="B127" s="423" t="n"/>
+      <c r="C127" s="423" t="n"/>
+      <c r="D127" s="442" t="n">
         <v>20283</v>
       </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="E127" s="423" t="n"/>
+      <c r="F127" s="423" t="n"/>
+      <c r="G127" s="423" t="n"/>
+      <c r="H127" s="423" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="423" t="inlineStr">
         <is>
           <t>Adjustment: restaurant cash added to tips + Mercado Pago commission (vs running estimate)</t>
         </is>
       </c>
-      <c r="D98" s="228" t="n">
+      <c r="B128" s="423" t="n"/>
+      <c r="C128" s="423" t="n"/>
+      <c r="D128" s="442" t="n">
         <v>-165</v>
       </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="E128" s="423" t="n"/>
+      <c r="F128" s="423" t="n"/>
+      <c r="G128" s="423" t="n"/>
+      <c r="H128" s="423" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="423" t="inlineStr">
         <is>
           <t>Reconciled to physical count provided by Reddy. $20,283 is net of MP % deductions.</t>
         </is>
       </c>
+      <c r="B129" s="423" t="n"/>
+      <c r="C129" s="423" t="n"/>
+      <c r="D129" s="423" t="n"/>
+      <c r="E129" s="423" t="n"/>
+      <c r="F129" s="423" t="n"/>
+      <c r="G129" s="423" t="n"/>
+      <c r="H129" s="423" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -57394,7 +57832,7 @@
     <row r="24">
       <c r="A24" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Dairy</t>
+          <t>Utilities/Electricity</t>
         </is>
       </c>
       <c r="B24" s="437">
@@ -57424,7 +57862,7 @@
     <row r="25">
       <c r="A25" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Bread</t>
+          <t>Ingredients - Dairy</t>
         </is>
       </c>
       <c r="B25" s="437">
@@ -57454,7 +57892,7 @@
     <row r="26">
       <c r="A26" s="439" t="inlineStr">
         <is>
-          <t>Supplies/Other</t>
+          <t>Ingredients - Bread</t>
         </is>
       </c>
       <c r="B26" s="437">
@@ -57484,7 +57922,7 @@
     <row r="27">
       <c r="A27" s="439" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="B27" s="437">
@@ -57514,7 +57952,7 @@
     <row r="28">
       <c r="A28" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Meat &amp; Fish</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B28" s="437">
@@ -57544,7 +57982,7 @@
     <row r="29">
       <c r="A29" s="439" t="inlineStr">
         <is>
-          <t>Packaging/Disposables</t>
+          <t>Ingredients - Meat &amp; Fish</t>
         </is>
       </c>
       <c r="B29" s="437">
@@ -57574,7 +58012,7 @@
     <row r="30">
       <c r="A30" s="439" t="inlineStr">
         <is>
-          <t>Utilities/Gas</t>
+          <t>Packaging/Disposables</t>
         </is>
       </c>
       <c r="B30" s="437">
@@ -57604,7 +58042,7 @@
     <row r="31">
       <c r="A31" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Fruit</t>
+          <t>Utilities/Gas</t>
         </is>
       </c>
       <c r="B31" s="437">
@@ -57634,7 +58072,7 @@
     <row r="32">
       <c r="A32" s="439" t="inlineStr">
         <is>
-          <t>Kitchen Supplies</t>
+          <t>Ingredients - Fruit</t>
         </is>
       </c>
       <c r="B32" s="437">
@@ -57664,7 +58102,7 @@
     <row r="33">
       <c r="A33" s="439" t="inlineStr">
         <is>
-          <t>Utilities/Internet</t>
+          <t>Kitchen Supplies</t>
         </is>
       </c>
       <c r="B33" s="437">
@@ -57694,7 +58132,7 @@
     <row r="34">
       <c r="A34" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Other</t>
+          <t>Utilities/Internet</t>
         </is>
       </c>
       <c r="B34" s="437">
@@ -57724,7 +58162,7 @@
     <row r="35">
       <c r="A35" s="439" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Ingredients - Other</t>
         </is>
       </c>
       <c r="B35" s="437">
@@ -57754,7 +58192,7 @@
     <row r="36">
       <c r="A36" s="439" t="inlineStr">
         <is>
-          <t>Software/Subscription</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="B36" s="437">
@@ -57784,7 +58222,7 @@
     <row r="37">
       <c r="A37" s="439" t="inlineStr">
         <is>
-          <t>Staff - Advance</t>
+          <t>Software/Subscription</t>
         </is>
       </c>
       <c r="B37" s="437">
@@ -57814,7 +58252,7 @@
     <row r="38">
       <c r="A38" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Desserts</t>
+          <t>Staff - Advance</t>
         </is>
       </c>
       <c r="B38" s="437">
@@ -57844,7 +58282,7 @@
     <row r="39">
       <c r="A39" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Eggs</t>
+          <t>Ingredients - Desserts</t>
         </is>
       </c>
       <c r="B39" s="437">
@@ -57874,7 +58312,7 @@
     <row r="40">
       <c r="A40" s="439" t="inlineStr">
         <is>
-          <t>Staff - Propinas</t>
+          <t>Ingredients - Eggs</t>
         </is>
       </c>
       <c r="B40" s="437">
@@ -57902,25 +58340,25 @@
       <c r="L40" s="433" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="436" t="inlineStr">
-        <is>
-          <t>TOTAL EXPENSES</t>
-        </is>
-      </c>
-      <c r="B41" s="438">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
-        <v/>
-      </c>
-      <c r="C41" s="438">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
-        <v/>
-      </c>
-      <c r="D41" s="438">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
-        <v/>
-      </c>
-      <c r="E41" s="438">
-        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
+      <c r="A41" s="439" t="inlineStr">
+        <is>
+          <t>Staff - Propinas</t>
+        </is>
+      </c>
+      <c r="B41" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A41,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
+        <v/>
+      </c>
+      <c r="C41" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A41,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
+        <v/>
+      </c>
+      <c r="D41" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A41,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
+        <v/>
+      </c>
+      <c r="E41" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A41,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
       <c r="F41" s="433" t="n"/>
@@ -57934,23 +58372,23 @@
     <row r="42">
       <c r="A42" s="436" t="inlineStr">
         <is>
-          <t>NET PROFIT / LOSS</t>
+          <t>TOTAL EXPENSES</t>
         </is>
       </c>
       <c r="B42" s="438">
-        <f>B4-B41</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,5,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="C42" s="438">
-        <f>C4-C41</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,6,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D42" s="438">
-        <f>D4-D41</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,7,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E42" s="438">
-        <f>E4-E41</f>
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
       <c r="F42" s="433" t="n"/>
@@ -57962,11 +58400,27 @@
       <c r="L42" s="433" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="433" t="n"/>
-      <c r="B43" s="433" t="n"/>
-      <c r="C43" s="433" t="n"/>
-      <c r="D43" s="433" t="n"/>
-      <c r="E43" s="433" t="n"/>
+      <c r="A43" s="436" t="inlineStr">
+        <is>
+          <t>NET PROFIT / LOSS</t>
+        </is>
+      </c>
+      <c r="B43" s="438">
+        <f>B4-B42</f>
+        <v/>
+      </c>
+      <c r="C43" s="438">
+        <f>C4-C42</f>
+        <v/>
+      </c>
+      <c r="D43" s="438">
+        <f>D4-D42</f>
+        <v/>
+      </c>
+      <c r="E43" s="438">
+        <f>E4-E42</f>
+        <v/>
+      </c>
       <c r="F43" s="433" t="n"/>
       <c r="G43" s="433" t="n"/>
       <c r="H43" s="433" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -1366,7 +1366,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25"/>
   </cellStyleXfs>
-  <cellXfs count="443">
+  <cellXfs count="444">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2494,6 +2494,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="46" fillId="20" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9616,7 +9619,7 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>4360.0</v>
+        <v>3775.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
@@ -9624,37 +9627,37 @@
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>1008.0</v>
+        <v>28989.04</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>3352.0</v>
+        <v>-25214.04</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>0.768807</v>
+        <v>-6.679216</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>4360.0</v>
+        <v>8135.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>4360.0</v>
+        <v>8135.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>8098.0</v>
+        <v>11873.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>1008.0</v>
+        <v>29997.04</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>3352.0</v>
+        <v>-21862.04</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -14304,33 +14307,72 @@
       <c r="AB80" s="324" t="n"/>
     </row>
     <row r="81" ht="16.5" customHeight="1" s="331">
-      <c r="B81" s="34" t="n"/>
-      <c r="C81" s="47" t="n"/>
-      <c r="D81" s="48" t="n"/>
-      <c r="E81" s="49" t="n"/>
-      <c r="F81" s="50" t="n"/>
-      <c r="G81" s="51" t="n"/>
-      <c r="H81" s="52" t="n"/>
-      <c r="I81" s="53" t="n"/>
-      <c r="J81" s="54" t="n"/>
-      <c r="K81" s="55" t="n"/>
-      <c r="L81" s="18" t="n"/>
-      <c r="M81" s="21" t="n"/>
-      <c r="N81" s="56" t="n"/>
-      <c r="O81" s="57" t="n"/>
-      <c r="P81" s="58" t="n"/>
-      <c r="Q81" s="56" t="n"/>
-      <c r="R81" s="56" t="n"/>
-      <c r="S81" s="56" t="n"/>
-      <c r="T81" s="56" t="n"/>
-      <c r="U81" s="56" t="n"/>
-      <c r="V81" s="56" t="n"/>
-      <c r="W81" s="56" t="n"/>
-      <c r="X81" s="56" t="n"/>
-      <c r="Y81" s="56" t="n"/>
-      <c r="Z81" s="56" t="n"/>
-      <c r="AA81" s="56" t="n"/>
-      <c r="AB81" s="56" t="n"/>
+      <c r="B81" s="427" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C81" s="255" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D81" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F81" s="50">
+        <f>IFERROR(D81+E81+G81+U81+Y81,0)</f>
+        <v>3775.0</v>
+      </c>
+      <c r="G81" s="257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B81,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B81+1))</f>
+        <v>28989.04</v>
+      </c>
+      <c r="I81" s="259">
+        <f>IFERROR(F81-H81,0)</f>
+        <v>-25214.04</v>
+      </c>
+      <c r="J81" s="260">
+        <f>IFERROR(I81/F81,0)</f>
+        <v>-6.679216</v>
+      </c>
+      <c r="K81" s="254" t="n"/>
+      <c r="L81" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M81" s="291" t="n"/>
+      <c r="N81" s="292" t="n"/>
+      <c r="O81" s="293" t="n"/>
+      <c r="P81" s="294" t="n"/>
+      <c r="Q81" s="292" t="n"/>
+      <c r="R81" s="443">
+        <f>IFERROR(D81*$T$7,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="S81" s="292" t="n"/>
+      <c r="T81" s="292" t="n"/>
+      <c r="U81" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" s="292" t="n"/>
+      <c r="X81" s="292" t="n"/>
+      <c r="Y81" s="443" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Z81" s="443" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="AA81" s="292" t="n"/>
+      <c r="AB81" s="292" t="n"/>
     </row>
     <row r="82" ht="16.5" customHeight="1" s="331">
       <c r="B82" s="34" t="n"/>
@@ -22798,7 +22840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J578"/>
+  <dimension ref="A1:J586"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -47155,6 +47197,350 @@
       <c r="J578" s="423" t="inlineStr">
         <is>
           <t>Recibo de luz pagado con capital de socios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="B579" s="429" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C579" s="297" t="inlineStr">
+        <is>
+          <t>Oxxo Tortillas</t>
+        </is>
+      </c>
+      <c r="D579" s="298" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E579" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F579" s="299" t="n">
+        <v>29</v>
+      </c>
+      <c r="G579" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H579" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I579" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J579" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="B580" s="429" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C580" s="297" t="inlineStr">
+        <is>
+          <t>Oxxo Arroz</t>
+        </is>
+      </c>
+      <c r="D580" s="298" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E580" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F580" s="299" t="n">
+        <v>78</v>
+      </c>
+      <c r="G580" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H580" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I580" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J580" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="B581" s="429" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C581" s="297" t="inlineStr">
+        <is>
+          <t>Jamon</t>
+        </is>
+      </c>
+      <c r="D581" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E581" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F581" s="299" t="n">
+        <v>173</v>
+      </c>
+      <c r="G581" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H581" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I581" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J581" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="B582" s="429" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C582" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D582" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E582" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F582" s="299" t="n">
+        <v>1809</v>
+      </c>
+      <c r="G582" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H582" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I582" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J582" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="B583" s="429" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C583" s="297" t="inlineStr">
+        <is>
+          <t>Agua Natural</t>
+        </is>
+      </c>
+      <c r="D583" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E583" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F583" s="299" t="n">
+        <v>45</v>
+      </c>
+      <c r="G583" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H583" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I583" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J583" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="B584" s="429" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C584" s="297" t="inlineStr">
+        <is>
+          <t>Guimar Deschables</t>
+        </is>
+      </c>
+      <c r="D584" s="298" t="inlineStr">
+        <is>
+          <t>Guimar Polietilenos</t>
+        </is>
+      </c>
+      <c r="E584" s="297" t="inlineStr">
+        <is>
+          <t>Packaging/Disposables</t>
+        </is>
+      </c>
+      <c r="F584" s="299" t="n">
+        <v>145</v>
+      </c>
+      <c r="G584" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H584" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I584" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J584" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="B585" s="429" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C585" s="297" t="inlineStr">
+        <is>
+          <t>Queso Bodega</t>
+        </is>
+      </c>
+      <c r="D585" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E585" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F585" s="299" t="n">
+        <v>551</v>
+      </c>
+      <c r="G585" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H585" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I585" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J585" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="B586" s="429" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C586" s="297" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="D586" s="298" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E586" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F586" s="299" t="n">
+        <v>170</v>
+      </c>
+      <c r="G586" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H586" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I586" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J586" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
         </is>
       </c>
     </row>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -1366,7 +1366,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25"/>
   </cellStyleXfs>
-  <cellXfs count="444">
+  <cellXfs count="445">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2497,6 +2497,7 @@
     <xf numFmtId="176" fontId="46" fillId="20" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="94" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5493,11 +5494,11 @@
         </is>
       </c>
       <c r="C147" s="268" t="n">
-        <v>42716.85</v>
+        <v>32415.85</v>
       </c>
       <c r="E147" s="286" t="inlineStr">
         <is>
-          <t>Operating costs funded from partner capital, net of repayments. Latest addition 04-Aug-2026 $25,989.04. Still owed by Operations: $42,716.85.</t>
+          <t>Operating costs funded from partner capital, net of repayments. Funded: 20,000 (rent Jul) + 17,200.04 (rent Aug) + 8,789 (luz Aug) + 19,314.81 (liquidacion ledger) = 65,303.85. Repaid from operating cash: 20,000 (21-Jul) + 2,587 (22-Jul) + 10,301 (05-Aug) = 32,888. Still owed by Operations: 32,415.85.</t>
         </is>
       </c>
     </row>
@@ -5514,12 +5515,12 @@
           <t xml:space="preserve">  &gt;&gt; Repaid to Capital from operating cash</t>
         </is>
       </c>
-      <c r="C149" s="322" t="n">
-        <v>-22587</v>
+      <c r="C149" s="444" t="n">
+        <v>-32888</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>21-Jul $20,000 + 22-Jul $2,587 = $22,587 repaid from restaurant operating cash. Reduces advance owed &amp; Cash-on-Hand; NOT a P&amp;L expense.</t>
+          <t>Cumulative repaid from operating cash (latest 04-Aug-2026 $10,301.00). Reduces advance owed &amp; Cash-on-Hand; NOT a P&amp;L expense.</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="331" min="1" max="1"/>
@@ -7762,30 +7763,162 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="430" t="inlineStr">
+      <c r="A57" s="430" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B57" s="232" t="inlineStr">
+        <is>
+          <t>Pollo $285 (paid by Lohith)</t>
+        </is>
+      </c>
+      <c r="C57" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D57" s="232" t="n">
+        <v>285</v>
+      </c>
+      <c r="E57" s="233" t="n"/>
+      <c r="F57" s="233">
+        <f>IFERROR(F56+D57-E57,0)</f>
+        <v/>
+      </c>
+      <c r="G57" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H57" s="232" t="inlineStr">
+        <is>
+          <t>Fronted from own pocket; excluded from till via cash_adjust</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="430" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B58" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 06-Aug)</t>
+        </is>
+      </c>
+      <c r="C58" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D58" s="232" t="n"/>
+      <c r="E58" s="233" t="n">
+        <v>130</v>
+      </c>
+      <c r="F58" s="233">
+        <f>IFERROR(F57+D58-E58,0)</f>
+        <v/>
+      </c>
+      <c r="G58" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H58" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="430" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B59" s="232" t="inlineStr">
+        <is>
+          <t>Pollo $319 (paid by Lohith)</t>
+        </is>
+      </c>
+      <c r="C59" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D59" s="232" t="n">
+        <v>319</v>
+      </c>
+      <c r="E59" s="233" t="n"/>
+      <c r="F59" s="233">
+        <f>IFERROR(F58+D59-E59,0)</f>
+        <v/>
+      </c>
+      <c r="G59" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H59" s="232" t="inlineStr">
+        <is>
+          <t>Fronted from own pocket; excluded from till via cash_adjust</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="430" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B60" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 07-Aug)</t>
+        </is>
+      </c>
+      <c r="C60" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D60" s="232" t="n"/>
+      <c r="E60" s="233" t="n">
+        <v>130</v>
+      </c>
+      <c r="F60" s="233">
+        <f>IFERROR(F59+D60-E60,0)</f>
+        <v/>
+      </c>
+      <c r="G60" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H60" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="430" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B57" s="232" t="n"/>
-      <c r="C57" s="232" t="n"/>
-      <c r="D57" s="232">
-        <f>SUM(D4:D56)</f>
-        <v/>
-      </c>
-      <c r="E57" s="233">
-        <f>SUM(E4:E56)</f>
-        <v/>
-      </c>
-      <c r="F57" s="233">
-        <f>F56</f>
-        <v/>
-      </c>
-      <c r="G57" s="232">
-        <f>IF(F56&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F56,"#,##0"),IF(F56&lt;0,"Lohith holds $"&amp;TEXT(ABS(F56),"#,##0"),"Zero balance"))</f>
-        <v/>
-      </c>
-      <c r="H57" s="232" t="n"/>
+      <c r="B61" s="232" t="n"/>
+      <c r="C61" s="232" t="n"/>
+      <c r="D61" s="232">
+        <f>SUM(D4:D60)</f>
+        <v/>
+      </c>
+      <c r="E61" s="233">
+        <f>SUM(E4:E60)</f>
+        <v/>
+      </c>
+      <c r="F61" s="233">
+        <f>F60</f>
+        <v/>
+      </c>
+      <c r="G61" s="232">
+        <f>IF(F60&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F60,"#,##0"),IF(F60&lt;0,"Lohith holds $"&amp;TEXT(ABS(F60),"#,##0"),"Zero balance"))</f>
+        <v/>
+      </c>
+      <c r="H61" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9619,45 +9752,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>3775.0</v>
+        <v>6725.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>0.0</v>
+        <v>130.0</v>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>28989.04</v>
+        <v>2152.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>-25214.04</v>
+        <v>4573.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>-6.679216</v>
+        <v>0.68</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>8135.0</v>
+        <v>23790.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>8135.0</v>
+        <v>23790.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>11873.0</v>
+        <v>27528.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>29997.04</v>
+        <v>35966.04</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>-21862.04</v>
+        <v>-12176.04</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -14375,91 +14508,208 @@
       <c r="AB81" s="292" t="n"/>
     </row>
     <row r="82" ht="16.5" customHeight="1" s="331">
-      <c r="B82" s="34" t="n"/>
-      <c r="C82" s="35" t="n"/>
-      <c r="D82" s="36" t="n"/>
-      <c r="E82" s="37" t="n"/>
-      <c r="F82" s="38" t="n"/>
-      <c r="G82" s="39" t="n"/>
-      <c r="H82" s="40" t="n"/>
-      <c r="I82" s="41" t="n"/>
-      <c r="J82" s="42" t="n"/>
-      <c r="K82" s="43" t="n"/>
-      <c r="L82" s="9" t="n"/>
-      <c r="M82" s="12" t="n"/>
-      <c r="N82" s="44" t="n"/>
-      <c r="O82" s="45" t="n"/>
-      <c r="P82" s="46" t="n"/>
-      <c r="Q82" s="44" t="n"/>
-      <c r="R82" s="44" t="n"/>
-      <c r="S82" s="44" t="n"/>
-      <c r="T82" s="44" t="n"/>
-      <c r="U82" s="44" t="n"/>
-      <c r="V82" s="44" t="n"/>
-      <c r="W82" s="44" t="n"/>
-      <c r="X82" s="44" t="n"/>
-      <c r="Y82" s="44" t="n"/>
-      <c r="Z82" s="44" t="n"/>
-      <c r="AA82" s="44" t="n"/>
-      <c r="AB82" s="44" t="n"/>
+      <c r="B82" s="427" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C82" s="270" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D82" s="271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="37" t="n">
+        <v>1185</v>
+      </c>
+      <c r="F82" s="38">
+        <f>IFERROR(D82+E82+G82+U82+Y82,0)</f>
+        <v>5165.0</v>
+      </c>
+      <c r="G82" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B82,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B82+1))</f>
+        <v>1445.0</v>
+      </c>
+      <c r="I82" s="274">
+        <f>IFERROR(F82-H82,0)</f>
+        <v>3720.0</v>
+      </c>
+      <c r="J82" s="275">
+        <f>IFERROR(I82/F82,0)</f>
+        <v>0.720232</v>
+      </c>
+      <c r="K82" s="250" t="n"/>
+      <c r="L82" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M82" s="323" t="n"/>
+      <c r="N82" s="324" t="n"/>
+      <c r="O82" s="325" t="n"/>
+      <c r="P82" s="326" t="n"/>
+      <c r="Q82" s="324" t="n"/>
+      <c r="R82" s="428">
+        <f>IFERROR(D82*$T$7,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="S82" s="324" t="n"/>
+      <c r="T82" s="324" t="n"/>
+      <c r="U82" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" s="324" t="n"/>
+      <c r="X82" s="324" t="n"/>
+      <c r="Y82" s="428" t="n">
+        <v>3980</v>
+      </c>
+      <c r="Z82" s="428" t="n">
+        <v>75.62</v>
+      </c>
+      <c r="AA82" s="324" t="n"/>
+      <c r="AB82" s="324" t="n"/>
     </row>
     <row r="83" ht="16.5" customHeight="1" s="331">
-      <c r="B83" s="34" t="n"/>
-      <c r="C83" s="47" t="n"/>
-      <c r="D83" s="48" t="n"/>
-      <c r="E83" s="49" t="n"/>
-      <c r="F83" s="50" t="n"/>
-      <c r="G83" s="51" t="n"/>
-      <c r="H83" s="52" t="n"/>
-      <c r="I83" s="53" t="n"/>
-      <c r="J83" s="54" t="n"/>
-      <c r="K83" s="55" t="n"/>
-      <c r="L83" s="18" t="n"/>
-      <c r="M83" s="21" t="n"/>
-      <c r="N83" s="56" t="n"/>
-      <c r="O83" s="57" t="n"/>
-      <c r="P83" s="58" t="n"/>
-      <c r="Q83" s="56" t="n"/>
-      <c r="R83" s="56" t="n"/>
-      <c r="S83" s="56" t="n"/>
-      <c r="T83" s="56" t="n"/>
-      <c r="U83" s="56" t="n"/>
-      <c r="V83" s="56" t="n"/>
-      <c r="W83" s="56" t="n"/>
-      <c r="X83" s="56" t="n"/>
-      <c r="Y83" s="56" t="n"/>
-      <c r="Z83" s="56" t="n"/>
-      <c r="AA83" s="56" t="n"/>
-      <c r="AB83" s="56" t="n"/>
+      <c r="B83" s="427" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C83" s="255" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D83" s="256" t="n">
+        <v>130</v>
+      </c>
+      <c r="E83" s="49" t="n">
+        <v>1605</v>
+      </c>
+      <c r="F83" s="50">
+        <f>IFERROR(D83+E83+G83+U83+Y83,0)</f>
+        <v>3765.0</v>
+      </c>
+      <c r="G83" s="257" t="n">
+        <v>130</v>
+      </c>
+      <c r="H83" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B83,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B83+1))</f>
+        <v>2372.0</v>
+      </c>
+      <c r="I83" s="259">
+        <f>IFERROR(F83-H83,0)</f>
+        <v>1393.0</v>
+      </c>
+      <c r="J83" s="260">
+        <f>IFERROR(I83/F83,0)</f>
+        <v>0.369987</v>
+      </c>
+      <c r="K83" s="254" t="n"/>
+      <c r="L83" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M83" s="291" t="n"/>
+      <c r="N83" s="292" t="n"/>
+      <c r="O83" s="293" t="n"/>
+      <c r="P83" s="294" t="n"/>
+      <c r="Q83" s="292" t="n"/>
+      <c r="R83" s="443">
+        <f>IFERROR(D83*$T$7,0)</f>
+        <v>5.28</v>
+      </c>
+      <c r="S83" s="292" t="n"/>
+      <c r="T83" s="292" t="n"/>
+      <c r="U83" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" s="292" t="n"/>
+      <c r="X83" s="292" t="n"/>
+      <c r="Y83" s="443" t="n">
+        <v>1900</v>
+      </c>
+      <c r="Z83" s="443" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="AA83" s="292" t="n"/>
+      <c r="AB83" s="292" t="n"/>
     </row>
     <row r="84" ht="16.5" customHeight="1" s="331">
-      <c r="B84" s="34" t="n"/>
-      <c r="C84" s="35" t="n"/>
-      <c r="D84" s="36" t="n"/>
-      <c r="E84" s="37" t="n"/>
-      <c r="F84" s="38" t="n"/>
-      <c r="G84" s="39" t="n"/>
-      <c r="H84" s="40" t="n"/>
-      <c r="I84" s="41" t="n"/>
-      <c r="J84" s="42" t="n"/>
-      <c r="K84" s="43" t="n"/>
-      <c r="L84" s="9" t="n"/>
-      <c r="M84" s="12" t="n"/>
-      <c r="N84" s="44" t="n"/>
-      <c r="O84" s="45" t="n"/>
-      <c r="P84" s="46" t="n"/>
-      <c r="Q84" s="44" t="n"/>
-      <c r="R84" s="44" t="n"/>
-      <c r="S84" s="44" t="n"/>
-      <c r="T84" s="44" t="n"/>
-      <c r="U84" s="44" t="n"/>
-      <c r="V84" s="44" t="n"/>
-      <c r="W84" s="44" t="n"/>
-      <c r="X84" s="44" t="n"/>
-      <c r="Y84" s="44" t="n"/>
-      <c r="Z84" s="44" t="n"/>
-      <c r="AA84" s="44" t="n"/>
-      <c r="AB84" s="44" t="n"/>
+      <c r="B84" s="427" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C84" s="270" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D84" s="271" t="n">
+        <v>115</v>
+      </c>
+      <c r="E84" s="37" t="n">
+        <v>3495</v>
+      </c>
+      <c r="F84" s="38">
+        <f>IFERROR(D84+E84+G84+U84+Y84,0)</f>
+        <v>6725.0</v>
+      </c>
+      <c r="G84" s="272" t="n">
+        <v>130</v>
+      </c>
+      <c r="H84" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B84,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B84+1))</f>
+        <v>2152.0</v>
+      </c>
+      <c r="I84" s="274">
+        <f>IFERROR(F84-H84,0)</f>
+        <v>4573.0</v>
+      </c>
+      <c r="J84" s="275">
+        <f>IFERROR(I84/F84,0)</f>
+        <v>0.68</v>
+      </c>
+      <c r="K84" s="250" t="n"/>
+      <c r="L84" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M84" s="323" t="n"/>
+      <c r="N84" s="324" t="n"/>
+      <c r="O84" s="325" t="n"/>
+      <c r="P84" s="326" t="n"/>
+      <c r="Q84" s="324" t="n"/>
+      <c r="R84" s="428">
+        <f>IFERROR(D84*$T$7,0)</f>
+        <v>4.67</v>
+      </c>
+      <c r="S84" s="324" t="n"/>
+      <c r="T84" s="324" t="n"/>
+      <c r="U84" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" s="324" t="n"/>
+      <c r="X84" s="324" t="n"/>
+      <c r="Y84" s="428" t="n">
+        <v>2985</v>
+      </c>
+      <c r="Z84" s="428" t="n">
+        <v>56.72</v>
+      </c>
+      <c r="AA84" s="324" t="n"/>
+      <c r="AB84" s="324" t="n"/>
     </row>
     <row r="85" ht="16.5" customHeight="1" s="331">
       <c r="B85" s="34" t="n"/>
@@ -22815,8 +23065,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
@@ -22840,7 +23090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J586"/>
+  <dimension ref="A1:J600"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -47541,6 +47791,608 @@
       <c r="J586" s="423" t="inlineStr">
         <is>
           <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="B587" s="429" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C587" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D587" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E587" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F587" s="299" t="n">
+        <v>442</v>
+      </c>
+      <c r="G587" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H587" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I587" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J587" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="B588" s="429" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C588" s="297" t="inlineStr">
+        <is>
+          <t>Pescado</t>
+        </is>
+      </c>
+      <c r="D588" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E588" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat &amp; Fish</t>
+        </is>
+      </c>
+      <c r="F588" s="299" t="n">
+        <v>224</v>
+      </c>
+      <c r="G588" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H588" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I588" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J588" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="B589" s="429" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C589" s="297" t="inlineStr">
+        <is>
+          <t>Queso Panela</t>
+        </is>
+      </c>
+      <c r="D589" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E589" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Dairy</t>
+        </is>
+      </c>
+      <c r="F589" s="299" t="n">
+        <v>494</v>
+      </c>
+      <c r="G589" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H589" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I589" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J589" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="B590" s="429" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C590" s="297" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D590" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E590" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F590" s="299" t="n">
+        <v>285</v>
+      </c>
+      <c r="G590" s="300" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H590" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I590" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J590" s="423" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="B591" s="429" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C591" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D591" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E591" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F591" s="299" t="n">
+        <v>587</v>
+      </c>
+      <c r="G591" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H591" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I591" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J591" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="B592" s="429" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C592" s="297" t="inlineStr">
+        <is>
+          <t>Pescado</t>
+        </is>
+      </c>
+      <c r="D592" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E592" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat &amp; Fish</t>
+        </is>
+      </c>
+      <c r="F592" s="299" t="n">
+        <v>523</v>
+      </c>
+      <c r="G592" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H592" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I592" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J592" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="B593" s="429" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C593" s="297" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D593" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E593" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F593" s="299" t="n">
+        <v>107</v>
+      </c>
+      <c r="G593" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H593" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I593" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J593" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="B594" s="429" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C594" s="297" t="inlineStr">
+        <is>
+          <t>Sams Club</t>
+        </is>
+      </c>
+      <c r="D594" s="298" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="E594" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F594" s="299" t="n">
+        <v>590</v>
+      </c>
+      <c r="G594" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H594" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I594" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J594" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="B595" s="429" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C595" s="297" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="D595" s="298" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E595" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F595" s="299" t="n">
+        <v>246</v>
+      </c>
+      <c r="G595" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H595" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I595" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J595" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="B596" s="429" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C596" s="297" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D596" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E596" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F596" s="299" t="n">
+        <v>319</v>
+      </c>
+      <c r="G596" s="300" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H596" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I596" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J596" s="423" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="B597" s="429" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C597" s="297" t="inlineStr">
+        <is>
+          <t>Sams club</t>
+        </is>
+      </c>
+      <c r="D597" s="298" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="E597" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F597" s="299" t="n">
+        <v>778</v>
+      </c>
+      <c r="G597" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H597" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I597" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J597" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="B598" s="429" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C598" s="297" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D598" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E598" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F598" s="299" t="n">
+        <v>144</v>
+      </c>
+      <c r="G598" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H598" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I598" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J598" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="B599" s="429" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C599" s="297" t="inlineStr">
+        <is>
+          <t>Agua Natural</t>
+        </is>
+      </c>
+      <c r="D599" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E599" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F599" s="299" t="n">
+        <v>30</v>
+      </c>
+      <c r="G599" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H599" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I599" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J599" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="B600" s="429" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C600" s="297" t="inlineStr">
+        <is>
+          <t>Samu - salary</t>
+        </is>
+      </c>
+      <c r="D600" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E600" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F600" s="299" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G600" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H600" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I600" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J600" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
         </is>
       </c>
     </row>
@@ -58188,7 +59040,7 @@
     <row r="23">
       <c r="A23" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Beverages</t>
+          <t>Ingredients - Dairy</t>
         </is>
       </c>
       <c r="B23" s="437">
@@ -58218,7 +59070,7 @@
     <row r="24">
       <c r="A24" s="439" t="inlineStr">
         <is>
-          <t>Utilities/Electricity</t>
+          <t>Ingredients - Beverages</t>
         </is>
       </c>
       <c r="B24" s="437">
@@ -58248,7 +59100,7 @@
     <row r="25">
       <c r="A25" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Dairy</t>
+          <t>Utilities/Electricity</t>
         </is>
       </c>
       <c r="B25" s="437">
@@ -58338,7 +59190,7 @@
     <row r="28">
       <c r="A28" s="439" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Ingredients - Meat &amp; Fish</t>
         </is>
       </c>
       <c r="B28" s="437">
@@ -58368,7 +59220,7 @@
     <row r="29">
       <c r="A29" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Meat &amp; Fish</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B29" s="437">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5952,7 +5952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="331" min="1" max="1"/>
@@ -7895,30 +7895,162 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="430" t="inlineStr">
+      <c r="A61" s="430" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B61" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 08-Aug)</t>
+        </is>
+      </c>
+      <c r="C61" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D61" s="232" t="n"/>
+      <c r="E61" s="233" t="n">
+        <v>135</v>
+      </c>
+      <c r="F61" s="233">
+        <f>IFERROR(F60+D61-E61,0)</f>
+        <v/>
+      </c>
+      <c r="G61" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H61" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="430" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B62" s="232" t="inlineStr">
+        <is>
+          <t>Pollo $1,028 (paid by Lohith)</t>
+        </is>
+      </c>
+      <c r="C62" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D62" s="232" t="n">
+        <v>1028</v>
+      </c>
+      <c r="E62" s="233" t="n"/>
+      <c r="F62" s="233">
+        <f>IFERROR(F61+D62-E62,0)</f>
+        <v/>
+      </c>
+      <c r="G62" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H62" s="232" t="inlineStr">
+        <is>
+          <t>Fronted from own pocket; excluded from till via cash_adjust</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="430" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B63" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 10-Aug)</t>
+        </is>
+      </c>
+      <c r="C63" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D63" s="232" t="n"/>
+      <c r="E63" s="233" t="n">
+        <v>130</v>
+      </c>
+      <c r="F63" s="233">
+        <f>IFERROR(F62+D63-E63,0)</f>
+        <v/>
+      </c>
+      <c r="G63" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H63" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="430" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B64" s="232" t="inlineStr">
+        <is>
+          <t>3B Pasta $110 (paid by Lohith)</t>
+        </is>
+      </c>
+      <c r="C64" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D64" s="232" t="n">
+        <v>110</v>
+      </c>
+      <c r="E64" s="233" t="n"/>
+      <c r="F64" s="233">
+        <f>IFERROR(F63+D64-E64,0)</f>
+        <v/>
+      </c>
+      <c r="G64" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H64" s="232" t="inlineStr">
+        <is>
+          <t>Fronted from own pocket; excluded from till via cash_adjust</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="430" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B61" s="232" t="n"/>
-      <c r="C61" s="232" t="n"/>
-      <c r="D61" s="232">
-        <f>SUM(D4:D60)</f>
-        <v/>
-      </c>
-      <c r="E61" s="233">
-        <f>SUM(E4:E60)</f>
-        <v/>
-      </c>
-      <c r="F61" s="233">
-        <f>F60</f>
-        <v/>
-      </c>
-      <c r="G61" s="232">
-        <f>IF(F60&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F60,"#,##0"),IF(F60&lt;0,"Lohith holds $"&amp;TEXT(ABS(F60),"#,##0"),"Zero balance"))</f>
-        <v/>
-      </c>
-      <c r="H61" s="232" t="n"/>
+      <c r="B65" s="232" t="n"/>
+      <c r="C65" s="232" t="n"/>
+      <c r="D65" s="232">
+        <f>SUM(D4:D64)</f>
+        <v/>
+      </c>
+      <c r="E65" s="233">
+        <f>SUM(E4:E64)</f>
+        <v/>
+      </c>
+      <c r="F65" s="233">
+        <f>F64</f>
+        <v/>
+      </c>
+      <c r="G65" s="232">
+        <f>IF(F64&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F64,"#,##0"),IF(F64&lt;0,"Lohith holds $"&amp;TEXT(ABS(F64),"#,##0"),"Zero balance"))</f>
+        <v/>
+      </c>
+      <c r="H65" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9752,7 +9884,7 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>6725.0</v>
+        <v>6540.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
@@ -9760,37 +9892,37 @@
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>2152.0</v>
+        <v>1138.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>4573.0</v>
+        <v>5402.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>0.68</v>
+        <v>0.825994</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>23790.0</v>
+        <v>6540.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>23790.0</v>
+        <v>6540.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>27528.0</v>
+        <v>36478.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>35966.04</v>
+        <v>1138.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>-12176.04</v>
+        <v>5402.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -14712,62 +14844,140 @@
       <c r="AB84" s="324" t="n"/>
     </row>
     <row r="85" ht="16.5" customHeight="1" s="331">
-      <c r="B85" s="34" t="n"/>
-      <c r="C85" s="47" t="n"/>
-      <c r="D85" s="48" t="n"/>
-      <c r="E85" s="49" t="n"/>
-      <c r="F85" s="50" t="n"/>
-      <c r="G85" s="51" t="n"/>
-      <c r="H85" s="52" t="n"/>
-      <c r="I85" s="53" t="n"/>
-      <c r="J85" s="54" t="n"/>
-      <c r="K85" s="55" t="n"/>
-      <c r="L85" s="18" t="n"/>
-      <c r="M85" s="21" t="n"/>
-      <c r="N85" s="56" t="n"/>
-      <c r="O85" s="57" t="n"/>
-      <c r="P85" s="58" t="n"/>
-      <c r="Q85" s="56" t="n"/>
-      <c r="R85" s="56" t="n"/>
-      <c r="S85" s="56" t="n"/>
-      <c r="T85" s="56" t="n"/>
-      <c r="U85" s="56" t="n"/>
-      <c r="V85" s="56" t="n"/>
-      <c r="W85" s="56" t="n"/>
-      <c r="X85" s="56" t="n"/>
-      <c r="Y85" s="56" t="n"/>
-      <c r="Z85" s="56" t="n"/>
-      <c r="AA85" s="56" t="n"/>
-      <c r="AB85" s="56" t="n"/>
+      <c r="B85" s="427" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C85" s="255" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D85" s="256" t="n">
+        <v>420</v>
+      </c>
+      <c r="E85" s="49" t="n">
+        <v>1115</v>
+      </c>
+      <c r="F85" s="50">
+        <f>IFERROR(D85+E85+G85+U85+Y85,0)</f>
+        <v>2410.0</v>
+      </c>
+      <c r="G85" s="257" t="n">
+        <v>135</v>
+      </c>
+      <c r="H85" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B85,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B85+1))</f>
+        <v>7943.0</v>
+      </c>
+      <c r="I85" s="259">
+        <f>IFERROR(F85-H85,0)</f>
+        <v>-5533.0</v>
+      </c>
+      <c r="J85" s="260">
+        <f>IFERROR(I85/F85,0)</f>
+        <v>-2.295851</v>
+      </c>
+      <c r="K85" s="254" t="n"/>
+      <c r="L85" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M85" s="291" t="n"/>
+      <c r="N85" s="292" t="n"/>
+      <c r="O85" s="293" t="n"/>
+      <c r="P85" s="294" t="n"/>
+      <c r="Q85" s="292" t="n"/>
+      <c r="R85" s="443">
+        <f>IFERROR(D85*$T$7,0)</f>
+        <v>17.05</v>
+      </c>
+      <c r="S85" s="292" t="n"/>
+      <c r="T85" s="292" t="n"/>
+      <c r="U85" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" s="292" t="n"/>
+      <c r="X85" s="292" t="n"/>
+      <c r="Y85" s="443" t="n">
+        <v>740</v>
+      </c>
+      <c r="Z85" s="443" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="AA85" s="292" t="n"/>
+      <c r="AB85" s="292" t="n"/>
     </row>
     <row r="86" ht="16.5" customHeight="1" s="331">
-      <c r="B86" s="34" t="n"/>
-      <c r="C86" s="35" t="n"/>
-      <c r="D86" s="36" t="n"/>
-      <c r="E86" s="37" t="n"/>
-      <c r="F86" s="38" t="n"/>
-      <c r="G86" s="39" t="n"/>
-      <c r="H86" s="40" t="n"/>
-      <c r="I86" s="41" t="n"/>
-      <c r="J86" s="42" t="n"/>
-      <c r="K86" s="43" t="n"/>
-      <c r="L86" s="9" t="n"/>
-      <c r="M86" s="12" t="n"/>
-      <c r="N86" s="44" t="n"/>
-      <c r="O86" s="45" t="n"/>
-      <c r="P86" s="46" t="n"/>
-      <c r="Q86" s="44" t="n"/>
-      <c r="R86" s="44" t="n"/>
-      <c r="S86" s="44" t="n"/>
-      <c r="T86" s="44" t="n"/>
-      <c r="U86" s="44" t="n"/>
-      <c r="V86" s="44" t="n"/>
-      <c r="W86" s="44" t="n"/>
-      <c r="X86" s="44" t="n"/>
-      <c r="Y86" s="44" t="n"/>
-      <c r="Z86" s="44" t="n"/>
-      <c r="AA86" s="44" t="n"/>
-      <c r="AB86" s="44" t="n"/>
+      <c r="B86" s="427" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C86" s="270" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D86" s="271" t="n">
+        <v>65</v>
+      </c>
+      <c r="E86" s="37" t="n">
+        <v>4305</v>
+      </c>
+      <c r="F86" s="38">
+        <f>IFERROR(D86+E86+G86+U86+Y86,0)</f>
+        <v>6540.0</v>
+      </c>
+      <c r="G86" s="272" t="n">
+        <v>130</v>
+      </c>
+      <c r="H86" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B86,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B86+1))</f>
+        <v>1138.0</v>
+      </c>
+      <c r="I86" s="274">
+        <f>IFERROR(F86-H86,0)</f>
+        <v>5402.0</v>
+      </c>
+      <c r="J86" s="275">
+        <f>IFERROR(I86/F86,0)</f>
+        <v>0.825994</v>
+      </c>
+      <c r="K86" s="250" t="n"/>
+      <c r="L86" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M86" s="323" t="n"/>
+      <c r="N86" s="324" t="n"/>
+      <c r="O86" s="325" t="n"/>
+      <c r="P86" s="326" t="n"/>
+      <c r="Q86" s="324" t="n"/>
+      <c r="R86" s="428">
+        <f>IFERROR(D86*$T$7,0)</f>
+        <v>2.64</v>
+      </c>
+      <c r="S86" s="324" t="n"/>
+      <c r="T86" s="324" t="n"/>
+      <c r="U86" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" s="324" t="n"/>
+      <c r="X86" s="324" t="n"/>
+      <c r="Y86" s="428" t="n">
+        <v>2040</v>
+      </c>
+      <c r="Z86" s="428" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="AA86" s="324" t="n"/>
+      <c r="AB86" s="324" t="n"/>
     </row>
     <row r="87" ht="16.5" customHeight="1" s="331">
       <c r="B87" s="34" t="n"/>
@@ -23065,8 +23275,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I2:P2"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:P2"/>
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
@@ -23090,7 +23300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J600"/>
+  <dimension ref="A1:J613"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -48393,6 +48603,565 @@
       <c r="J600" s="423" t="inlineStr">
         <is>
           <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="B601" s="429" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C601" s="297" t="inlineStr">
+        <is>
+          <t>Bistec</t>
+        </is>
+      </c>
+      <c r="D601" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E601" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F601" s="299" t="n">
+        <v>145</v>
+      </c>
+      <c r="G601" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H601" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I601" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J601" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="B602" s="429" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C602" s="297" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D602" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E602" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F602" s="299" t="n">
+        <v>1520</v>
+      </c>
+      <c r="G602" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H602" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I602" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J602" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="B603" s="429" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C603" s="297" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D603" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E603" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F603" s="299" t="n">
+        <v>1028</v>
+      </c>
+      <c r="G603" s="300" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H603" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I603" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J603" s="423" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="B604" s="429" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C604" s="297" t="inlineStr">
+        <is>
+          <t>Jhon - salary</t>
+        </is>
+      </c>
+      <c r="D604" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E604" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F604" s="299" t="n">
+        <v>3750</v>
+      </c>
+      <c r="G604" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H604" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I604" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J604" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="B605" s="429" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C605" s="297" t="inlineStr">
+        <is>
+          <t>Duvi - salary</t>
+        </is>
+      </c>
+      <c r="D605" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E605" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F605" s="299" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G605" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H605" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I605" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J605" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="B606" s="429" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C606" s="297" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="D606" s="298" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E606" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F606" s="299" t="n">
+        <v>89</v>
+      </c>
+      <c r="G606" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H606" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I606" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J606" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="B607" s="429" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C607" s="297" t="inlineStr">
+        <is>
+          <t>Bistec</t>
+        </is>
+      </c>
+      <c r="D607" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E607" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F607" s="299" t="n">
+        <v>194</v>
+      </c>
+      <c r="G607" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H607" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I607" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J607" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="B608" s="429" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C608" s="297" t="inlineStr">
+        <is>
+          <t>Lomo</t>
+        </is>
+      </c>
+      <c r="D608" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E608" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F608" s="299" t="n">
+        <v>285</v>
+      </c>
+      <c r="G608" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H608" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I608" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J608" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="B609" s="429" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C609" s="297" t="inlineStr">
+        <is>
+          <t>Pan Dulce</t>
+        </is>
+      </c>
+      <c r="D609" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E609" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F609" s="299" t="n">
+        <v>145</v>
+      </c>
+      <c r="G609" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H609" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I609" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J609" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="B610" s="429" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C610" s="297" t="inlineStr">
+        <is>
+          <t>Tortillas</t>
+        </is>
+      </c>
+      <c r="D610" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E610" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F610" s="299" t="n">
+        <v>52</v>
+      </c>
+      <c r="G610" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H610" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I610" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J610" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="B611" s="429" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C611" s="297" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="D611" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E611" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F611" s="299" t="n">
+        <v>185</v>
+      </c>
+      <c r="G611" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H611" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I611" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J611" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="B612" s="429" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C612" s="297" t="inlineStr">
+        <is>
+          <t>Oxxo Arroz</t>
+        </is>
+      </c>
+      <c r="D612" s="298" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E612" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F612" s="299" t="n">
+        <v>78</v>
+      </c>
+      <c r="G612" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H612" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I612" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J612" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="B613" s="429" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C613" s="297" t="inlineStr">
+        <is>
+          <t>3B Pasta</t>
+        </is>
+      </c>
+      <c r="D613" s="298" t="inlineStr">
+        <is>
+          <t>Tres B</t>
+        </is>
+      </c>
+      <c r="E613" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F613" s="299" t="n">
+        <v>110</v>
+      </c>
+      <c r="G613" s="300" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H613" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I613" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J613" s="423" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
         </is>
       </c>
     </row>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -23275,9 +23275,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5952,7 +5952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="331" min="1" max="1"/>
@@ -8027,30 +8027,63 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="430" t="inlineStr">
+      <c r="A65" s="430" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B65" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 11-Aug)</t>
+        </is>
+      </c>
+      <c r="C65" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D65" s="232" t="n"/>
+      <c r="E65" s="233" t="n">
+        <v>655</v>
+      </c>
+      <c r="F65" s="233">
+        <f>IFERROR(F64+D65-E65,0)</f>
+        <v/>
+      </c>
+      <c r="G65" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H65" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="430" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B65" s="232" t="n"/>
-      <c r="C65" s="232" t="n"/>
-      <c r="D65" s="232">
-        <f>SUM(D4:D64)</f>
-        <v/>
-      </c>
-      <c r="E65" s="233">
-        <f>SUM(E4:E64)</f>
-        <v/>
-      </c>
-      <c r="F65" s="233">
-        <f>F64</f>
-        <v/>
-      </c>
-      <c r="G65" s="232">
-        <f>IF(F64&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F64,"#,##0"),IF(F64&lt;0,"Lohith holds $"&amp;TEXT(ABS(F64),"#,##0"),"Zero balance"))</f>
-        <v/>
-      </c>
-      <c r="H65" s="232" t="n"/>
+      <c r="B66" s="232" t="n"/>
+      <c r="C66" s="232" t="n"/>
+      <c r="D66" s="232">
+        <f>SUM(D4:D65)</f>
+        <v/>
+      </c>
+      <c r="E66" s="233">
+        <f>SUM(E4:E65)</f>
+        <v/>
+      </c>
+      <c r="F66" s="233">
+        <f>F65</f>
+        <v/>
+      </c>
+      <c r="G66" s="232">
+        <f>IF(F65&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F65,"#,##0"),IF(F65&lt;0,"Lohith holds $"&amp;TEXT(ABS(F65),"#,##0"),"Zero balance"))</f>
+        <v/>
+      </c>
+      <c r="H66" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9884,45 +9917,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>6540.0</v>
+        <v/>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>130.0</v>
+        <v/>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>1138.0</v>
+        <v/>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>5402.0</v>
+        <v/>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>0.825994</v>
+        <v/>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>6540.0</v>
+        <v/>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>6540.0</v>
+        <v/>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>36478.0</v>
+        <v/>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>1138.0</v>
+        <v/>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>5402.0</v>
+        <v/>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -10073,20 +10106,20 @@
       </c>
       <c r="F8" s="38">
         <f>IFERROR(D8+E8+G8,0)</f>
-        <v>3689.0</v>
+        <v/>
       </c>
       <c r="G8" s="39" t="n"/>
       <c r="H8" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B8,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B8+1))</f>
-        <v>2629.0</v>
+        <v/>
       </c>
       <c r="I8" s="41">
         <f>IFERROR(F8-H8,0)</f>
-        <v>1060.0</v>
+        <v/>
       </c>
       <c r="J8" s="42">
         <f>IFERROR(I8/F8,0)</f>
-        <v>0.287341</v>
+        <v/>
       </c>
       <c r="K8" s="43" t="n"/>
       <c r="L8" s="9" t="inlineStr">
@@ -10101,7 +10134,7 @@
       <c r="Q8" s="44" t="n"/>
       <c r="R8" s="44">
         <f>IFERROR(D8*$T$7,0)</f>
-        <v>90.5</v>
+        <v/>
       </c>
       <c r="S8" s="44" t="n"/>
       <c r="T8" s="44" t="n"/>
@@ -10131,20 +10164,20 @@
       </c>
       <c r="F9" s="50">
         <f>IFERROR(D9+E9+G9,0)</f>
-        <v>3854.0</v>
+        <v/>
       </c>
       <c r="G9" s="51" t="n"/>
       <c r="H9" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B9,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B9+1))</f>
-        <v>30.0</v>
+        <v/>
       </c>
       <c r="I9" s="53">
         <f>IFERROR(F9-H9,0)</f>
-        <v>3824.0</v>
+        <v/>
       </c>
       <c r="J9" s="54">
         <f>IFERROR(I9/F9,0)</f>
-        <v>0.992216</v>
+        <v/>
       </c>
       <c r="K9" s="55" t="n"/>
       <c r="L9" s="18" t="inlineStr">
@@ -10159,7 +10192,7 @@
       <c r="Q9" s="56" t="n"/>
       <c r="R9" s="56">
         <f>IFERROR(D9*$T$7,0)</f>
-        <v>86.27</v>
+        <v/>
       </c>
       <c r="S9" s="56" t="n"/>
       <c r="T9" s="56" t="n"/>
@@ -10189,20 +10222,20 @@
       </c>
       <c r="F10" s="38">
         <f>IFERROR(D10+E10+G10,0)</f>
-        <v>4124.0</v>
+        <v/>
       </c>
       <c r="G10" s="39" t="n"/>
       <c r="H10" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B10,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B10+1))</f>
-        <v>3777.0</v>
+        <v/>
       </c>
       <c r="I10" s="41">
         <f>IFERROR(F10-H10,0)</f>
-        <v>347.0</v>
+        <v/>
       </c>
       <c r="J10" s="42">
         <f>IFERROR(I10/F10,0)</f>
-        <v>0.084142</v>
+        <v/>
       </c>
       <c r="K10" s="43" t="n"/>
       <c r="L10" s="9" t="inlineStr">
@@ -10217,7 +10250,7 @@
       <c r="Q10" s="44" t="n"/>
       <c r="R10" s="44">
         <f>IFERROR(D10*$T$7,0)</f>
-        <v>59.24</v>
+        <v/>
       </c>
       <c r="S10" s="44" t="n"/>
       <c r="T10" s="44" t="n"/>
@@ -10247,20 +10280,20 @@
       </c>
       <c r="F11" s="50">
         <f>IFERROR(D11+E11+G11,0)</f>
-        <v>4733.0</v>
+        <v/>
       </c>
       <c r="G11" s="51" t="n"/>
       <c r="H11" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B11,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B11+1))</f>
-        <v>2434.0</v>
+        <v/>
       </c>
       <c r="I11" s="53">
         <f>IFERROR(F11-H11,0)</f>
-        <v>2299.0</v>
+        <v/>
       </c>
       <c r="J11" s="54">
         <f>IFERROR(I11/F11,0)</f>
-        <v>0.485738</v>
+        <v/>
       </c>
       <c r="K11" s="55" t="n"/>
       <c r="L11" s="18" t="inlineStr">
@@ -10275,7 +10308,7 @@
       <c r="Q11" s="56" t="n"/>
       <c r="R11" s="56">
         <f>IFERROR(D11*$T$7,0)</f>
-        <v>104.34</v>
+        <v/>
       </c>
       <c r="S11" s="56" t="n"/>
       <c r="T11" s="56" t="n"/>
@@ -10305,20 +10338,20 @@
       </c>
       <c r="F12" s="38">
         <f>IFERROR(D12+E12+G12,0)</f>
-        <v>4282.0</v>
+        <v/>
       </c>
       <c r="G12" s="39" t="n"/>
       <c r="H12" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B12,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B12+1))</f>
-        <v>1457.0</v>
+        <v/>
       </c>
       <c r="I12" s="41">
         <f>IFERROR(F12-H12,0)</f>
-        <v>2825.0</v>
+        <v/>
       </c>
       <c r="J12" s="42">
         <f>IFERROR(I12/F12,0)</f>
-        <v>0.659738</v>
+        <v/>
       </c>
       <c r="K12" s="43" t="n"/>
       <c r="L12" s="9" t="inlineStr">
@@ -10333,7 +10366,7 @@
       <c r="Q12" s="44" t="n"/>
       <c r="R12" s="44">
         <f>IFERROR(D12*$T$7,0)</f>
-        <v>79.54</v>
+        <v/>
       </c>
       <c r="S12" s="44" t="n"/>
       <c r="T12" s="44" t="n"/>
@@ -10363,20 +10396,20 @@
       </c>
       <c r="F13" s="50">
         <f>IFERROR(D13+E13+G13,0)</f>
-        <v>3802.0</v>
+        <v/>
       </c>
       <c r="G13" s="51" t="n"/>
       <c r="H13" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B13,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B13+1))</f>
-        <v>7755.43</v>
+        <v/>
       </c>
       <c r="I13" s="53">
         <f>IFERROR(F13-H13,0)</f>
-        <v>-3953.43</v>
+        <v/>
       </c>
       <c r="J13" s="54">
         <f>IFERROR(I13/F13,0)</f>
-        <v>-1.039829</v>
+        <v/>
       </c>
       <c r="K13" s="55" t="inlineStr">
         <is>
@@ -10395,7 +10428,7 @@
       <c r="Q13" s="56" t="n"/>
       <c r="R13" s="56">
         <f>IFERROR(D13*$T$7,0)</f>
-        <v>82.99</v>
+        <v/>
       </c>
       <c r="S13" s="56" t="n"/>
       <c r="T13" s="56" t="n"/>
@@ -10423,20 +10456,20 @@
       </c>
       <c r="F14" s="38">
         <f>IFERROR(D14+E14+G14,0)</f>
-        <v>1198.0</v>
+        <v/>
       </c>
       <c r="G14" s="39" t="n"/>
       <c r="H14" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B14,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B14+1))</f>
-        <v>1076.0</v>
+        <v/>
       </c>
       <c r="I14" s="41">
         <f>IFERROR(F14-H14,0)</f>
-        <v>122.0</v>
+        <v/>
       </c>
       <c r="J14" s="42">
         <f>IFERROR(I14/F14,0)</f>
-        <v>0.101836</v>
+        <v/>
       </c>
       <c r="K14" s="43" t="inlineStr">
         <is>
@@ -10455,7 +10488,7 @@
       <c r="Q14" s="44" t="n"/>
       <c r="R14" s="44">
         <f>IFERROR(D14*$T$7,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S14" s="44" t="n"/>
       <c r="T14" s="44" t="n"/>
@@ -10485,20 +10518,20 @@
       </c>
       <c r="F15" s="50">
         <f>IFERROR(D15+E15+G15,0)</f>
-        <v>3730.0</v>
+        <v/>
       </c>
       <c r="G15" s="51" t="n"/>
       <c r="H15" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B15,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B15+1))</f>
-        <v>3021.45</v>
+        <v/>
       </c>
       <c r="I15" s="53">
         <f>IFERROR(F15-H15,0)</f>
-        <v>708.55</v>
+        <v/>
       </c>
       <c r="J15" s="54">
         <f>IFERROR(I15/F15,0)</f>
-        <v>0.18996</v>
+        <v/>
       </c>
       <c r="K15" s="55" t="n"/>
       <c r="L15" s="18" t="inlineStr">
@@ -10513,7 +10546,7 @@
       <c r="Q15" s="56" t="n"/>
       <c r="R15" s="56">
         <f>IFERROR(D15*$T$7,0)</f>
-        <v>85.5</v>
+        <v/>
       </c>
       <c r="S15" s="56" t="n"/>
       <c r="T15" s="56" t="n"/>
@@ -10543,20 +10576,20 @@
       </c>
       <c r="F16" s="38">
         <f>IFERROR(D16+E16+G16,0)</f>
-        <v>4264.0</v>
+        <v/>
       </c>
       <c r="G16" s="39" t="n"/>
       <c r="H16" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B16,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B16+1))</f>
-        <v>1191.6</v>
+        <v/>
       </c>
       <c r="I16" s="41">
         <f>IFERROR(F16-H16,0)</f>
-        <v>3072.4</v>
+        <v/>
       </c>
       <c r="J16" s="42">
         <f>IFERROR(I16/F16,0)</f>
-        <v>0.720544</v>
+        <v/>
       </c>
       <c r="K16" s="43" t="n"/>
       <c r="L16" s="9" t="inlineStr">
@@ -10571,7 +10604,7 @@
       <c r="Q16" s="44" t="n"/>
       <c r="R16" s="44">
         <f>IFERROR(D16*$T$7,0)</f>
-        <v>77.51</v>
+        <v/>
       </c>
       <c r="S16" s="44" t="n"/>
       <c r="T16" s="44" t="n"/>
@@ -10601,20 +10634,20 @@
       </c>
       <c r="F17" s="50">
         <f>IFERROR(D17+E17+G17,0)</f>
-        <v>3621.0</v>
+        <v/>
       </c>
       <c r="G17" s="51" t="n"/>
       <c r="H17" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B17,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B17+1))</f>
-        <v>1073.22</v>
+        <v/>
       </c>
       <c r="I17" s="53">
         <f>IFERROR(F17-H17,0)</f>
-        <v>2547.78</v>
+        <v/>
       </c>
       <c r="J17" s="54">
         <f>IFERROR(I17/F17,0)</f>
-        <v>0.703612</v>
+        <v/>
       </c>
       <c r="K17" s="55" t="n"/>
       <c r="L17" s="18" t="inlineStr">
@@ -10629,7 +10662,7 @@
       <c r="Q17" s="56" t="n"/>
       <c r="R17" s="56">
         <f>IFERROR(D17*$T$7,0)</f>
-        <v>79.41</v>
+        <v/>
       </c>
       <c r="S17" s="56" t="n"/>
       <c r="T17" s="56" t="n"/>
@@ -10659,20 +10692,20 @@
       </c>
       <c r="F18" s="38">
         <f>IFERROR(D18+E18+G18,0)</f>
-        <v>4070.0</v>
+        <v/>
       </c>
       <c r="G18" s="39" t="n"/>
       <c r="H18" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B18,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B18+1))</f>
-        <v>1931.34</v>
+        <v/>
       </c>
       <c r="I18" s="41">
         <f>IFERROR(F18-H18,0)</f>
-        <v>2138.66</v>
+        <v/>
       </c>
       <c r="J18" s="42">
         <f>IFERROR(I18/F18,0)</f>
-        <v>0.525469</v>
+        <v/>
       </c>
       <c r="K18" s="43" t="n"/>
       <c r="L18" s="9" t="inlineStr">
@@ -10687,7 +10720,7 @@
       <c r="Q18" s="44" t="n"/>
       <c r="R18" s="44">
         <f>IFERROR(D18*$T$7,0)</f>
-        <v>60.94</v>
+        <v/>
       </c>
       <c r="S18" s="44" t="n"/>
       <c r="T18" s="44" t="n"/>
@@ -10717,20 +10750,20 @@
       </c>
       <c r="F19" s="50">
         <f>IFERROR(D19+E19+G19,0)</f>
-        <v>6086.0</v>
+        <v/>
       </c>
       <c r="G19" s="51" t="n"/>
       <c r="H19" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B19,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B19+1))</f>
-        <v>257.29</v>
+        <v/>
       </c>
       <c r="I19" s="53">
         <f>IFERROR(F19-H19,0)</f>
-        <v>5828.71</v>
+        <v/>
       </c>
       <c r="J19" s="54">
         <f>IFERROR(I19/F19,0)</f>
-        <v>0.957724</v>
+        <v/>
       </c>
       <c r="K19" s="55" t="n"/>
       <c r="L19" s="18" t="inlineStr">
@@ -10745,7 +10778,7 @@
       <c r="Q19" s="56" t="n"/>
       <c r="R19" s="56">
         <f>IFERROR(D19*$T$7,0)</f>
-        <v>136.78</v>
+        <v/>
       </c>
       <c r="S19" s="56" t="n"/>
       <c r="T19" s="56" t="n"/>
@@ -10775,20 +10808,20 @@
       </c>
       <c r="F20" s="38">
         <f>IFERROR(D20+E20+G20,0)</f>
-        <v>4603.0</v>
+        <v/>
       </c>
       <c r="G20" s="39" t="n"/>
       <c r="H20" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B20,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B20+1))</f>
-        <v>5974.3</v>
+        <v/>
       </c>
       <c r="I20" s="41">
         <f>IFERROR(F20-H20,0)</f>
-        <v>-1371.3</v>
+        <v/>
       </c>
       <c r="J20" s="42">
         <f>IFERROR(I20/F20,0)</f>
-        <v>-0.297914</v>
+        <v/>
       </c>
       <c r="K20" s="43" t="n"/>
       <c r="L20" s="9" t="inlineStr">
@@ -10803,7 +10836,7 @@
       <c r="Q20" s="44" t="n"/>
       <c r="R20" s="44">
         <f>IFERROR(D20*$T$7,0)</f>
-        <v>140.35</v>
+        <v/>
       </c>
       <c r="S20" s="44" t="n"/>
       <c r="T20" s="44" t="n"/>
@@ -10831,20 +10864,20 @@
       </c>
       <c r="F21" s="50">
         <f>IFERROR(D21+E21+G21,0)</f>
-        <v>893.0</v>
+        <v/>
       </c>
       <c r="G21" s="51" t="n"/>
       <c r="H21" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B21,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B21+1))</f>
-        <v>10312.0</v>
+        <v/>
       </c>
       <c r="I21" s="53">
         <f>IFERROR(F21-H21,0)</f>
-        <v>-9419.0</v>
+        <v/>
       </c>
       <c r="J21" s="54">
         <f>IFERROR(I21/F21,0)</f>
-        <v>-10.547592</v>
+        <v/>
       </c>
       <c r="K21" s="55" t="n"/>
       <c r="L21" s="18" t="inlineStr">
@@ -10859,7 +10892,7 @@
       <c r="Q21" s="56" t="n"/>
       <c r="R21" s="56">
         <f>IFERROR(D21*$T$7,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S21" s="56" t="n"/>
       <c r="T21" s="56" t="n"/>
@@ -10889,22 +10922,22 @@
       </c>
       <c r="F22" s="38">
         <f>IFERROR(D22+E22+G22,0)</f>
-        <v>5019.0</v>
+        <v/>
       </c>
       <c r="G22" s="39" t="n">
         <v>310</v>
       </c>
       <c r="H22" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B22,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B22+1))</f>
-        <v>5329.64</v>
+        <v/>
       </c>
       <c r="I22" s="41">
         <f>IFERROR(F22-H22,0)</f>
-        <v>-310.64</v>
+        <v/>
       </c>
       <c r="J22" s="42">
         <f>IFERROR(I22/F22,0)</f>
-        <v>-0.061893</v>
+        <v/>
       </c>
       <c r="K22" s="43" t="n"/>
       <c r="L22" s="9" t="inlineStr">
@@ -10919,7 +10952,7 @@
       <c r="Q22" s="44" t="n"/>
       <c r="R22" s="44">
         <f>IFERROR(D22*$T$7,0)</f>
-        <v>139.38</v>
+        <v/>
       </c>
       <c r="S22" s="44" t="n"/>
       <c r="T22" s="44" t="n"/>
@@ -10949,22 +10982,22 @@
       </c>
       <c r="F23" s="50">
         <f>IFERROR(D23+E23+G23,0)</f>
-        <v>1843.0</v>
+        <v/>
       </c>
       <c r="G23" s="51" t="n">
         <v>283</v>
       </c>
       <c r="H23" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B23,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B23+1))</f>
-        <v>2379.11</v>
+        <v/>
       </c>
       <c r="I23" s="53">
         <f>IFERROR(F23-H23,0)</f>
-        <v>-536.11</v>
+        <v/>
       </c>
       <c r="J23" s="54">
         <f>IFERROR(I23/F23,0)</f>
-        <v>-0.29089</v>
+        <v/>
       </c>
       <c r="K23" s="55" t="n"/>
       <c r="L23" s="18" t="inlineStr">
@@ -10979,7 +11012,7 @@
       <c r="Q23" s="56" t="n"/>
       <c r="R23" s="56">
         <f>IFERROR(D23*$T$7,0)</f>
-        <v>50.34</v>
+        <v/>
       </c>
       <c r="S23" s="56" t="n"/>
       <c r="T23" s="56" t="n"/>
@@ -11009,22 +11042,22 @@
       </c>
       <c r="F24" s="38">
         <f>IFERROR(D24+E24+G24,0)</f>
-        <v>3912.0</v>
+        <v/>
       </c>
       <c r="G24" s="39" t="n">
         <v>120</v>
       </c>
       <c r="H24" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B24,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B24+1))</f>
-        <v>4211.86</v>
+        <v/>
       </c>
       <c r="I24" s="41">
         <f>IFERROR(F24-H24,0)</f>
-        <v>-299.86</v>
+        <v/>
       </c>
       <c r="J24" s="42">
         <f>IFERROR(I24/F24,0)</f>
-        <v>-0.076651</v>
+        <v/>
       </c>
       <c r="K24" s="43" t="n"/>
       <c r="L24" s="9" t="inlineStr">
@@ -11039,7 +11072,7 @@
       <c r="Q24" s="44" t="n"/>
       <c r="R24" s="44">
         <f>IFERROR(D24*$T$7,0)</f>
-        <v>75.23</v>
+        <v/>
       </c>
       <c r="S24" s="44" t="n"/>
       <c r="T24" s="44" t="n"/>
@@ -11069,20 +11102,20 @@
       </c>
       <c r="F25" s="50">
         <f>IFERROR(D25+E25+G25,0)</f>
-        <v>3757.0</v>
+        <v/>
       </c>
       <c r="G25" s="51" t="n"/>
       <c r="H25" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B25,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B25+1))</f>
-        <v>20959.96</v>
+        <v/>
       </c>
       <c r="I25" s="53">
         <f>IFERROR(F25-H25,0)</f>
-        <v>-17202.96</v>
+        <v/>
       </c>
       <c r="J25" s="54">
         <f>IFERROR(I25/F25,0)</f>
-        <v>-4.578909</v>
+        <v/>
       </c>
       <c r="K25" s="55" t="n"/>
       <c r="L25" s="18" t="inlineStr">
@@ -11097,7 +11130,7 @@
       <c r="Q25" s="56" t="n"/>
       <c r="R25" s="56">
         <f>IFERROR(D25*$T$7,0)</f>
-        <v>110.11</v>
+        <v/>
       </c>
       <c r="S25" s="56" t="n"/>
       <c r="T25" s="56" t="n"/>
@@ -11127,22 +11160,22 @@
       </c>
       <c r="F26" s="38">
         <f>IFERROR(D26+E26+G26,0)</f>
-        <v>4408.0</v>
+        <v/>
       </c>
       <c r="G26" s="39" t="n">
         <v>135</v>
       </c>
       <c r="H26" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B26,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B26+1))</f>
-        <v>878.06</v>
+        <v/>
       </c>
       <c r="I26" s="41">
         <f>IFERROR(F26-H26,0)</f>
-        <v>3529.94</v>
+        <v/>
       </c>
       <c r="J26" s="42">
         <f>IFERROR(I26/F26,0)</f>
-        <v>0.800803</v>
+        <v/>
       </c>
       <c r="K26" s="43" t="n"/>
       <c r="L26" s="9" t="inlineStr">
@@ -11157,7 +11190,7 @@
       <c r="Q26" s="44" t="n"/>
       <c r="R26" s="44">
         <f>IFERROR(D26*$T$7,0)</f>
-        <v>101.3</v>
+        <v/>
       </c>
       <c r="S26" s="44" t="n"/>
       <c r="T26" s="44" t="n"/>
@@ -11187,20 +11220,20 @@
       </c>
       <c r="F27" s="50">
         <f>IFERROR(D27+E27+G27,0)</f>
-        <v>2334.0</v>
+        <v/>
       </c>
       <c r="G27" s="51" t="n"/>
       <c r="H27" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B27,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B27+1))</f>
-        <v>5414.0</v>
+        <v/>
       </c>
       <c r="I27" s="53">
         <f>IFERROR(F27-H27,0)</f>
-        <v>-3080.0</v>
+        <v/>
       </c>
       <c r="J27" s="54">
         <f>IFERROR(I27/F27,0)</f>
-        <v>-1.319623</v>
+        <v/>
       </c>
       <c r="K27" s="55" t="n"/>
       <c r="L27" s="18" t="inlineStr">
@@ -11215,7 +11248,7 @@
       <c r="Q27" s="56" t="n"/>
       <c r="R27" s="56">
         <f>IFERROR(D27*$T$7,0)</f>
-        <v>23.55</v>
+        <v/>
       </c>
       <c r="S27" s="56" t="n"/>
       <c r="T27" s="56" t="n"/>
@@ -11241,16 +11274,16 @@
       <c r="E28" s="37" t="n"/>
       <c r="F28" s="38">
         <f>IFERROR(D28+E28+G28,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="G28" s="39" t="n"/>
       <c r="H28" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B28,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B28+1))</f>
-        <v>1671.0</v>
+        <v/>
       </c>
       <c r="I28" s="41">
         <f>IFERROR(F28-H28,0)</f>
-        <v>-1671.0</v>
+        <v/>
       </c>
       <c r="J28" s="42" t="n"/>
       <c r="K28" s="43" t="n"/>
@@ -11266,7 +11299,7 @@
       <c r="Q28" s="44" t="n"/>
       <c r="R28" s="44">
         <f>IFERROR(D28*$T$7,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S28" s="44" t="n"/>
       <c r="T28" s="44" t="n"/>
@@ -11296,22 +11329,22 @@
       </c>
       <c r="F29" s="50">
         <f>IFERROR(D29+E29+G29,0)</f>
-        <v>3727.0</v>
+        <v/>
       </c>
       <c r="G29" s="51" t="n">
         <v>99</v>
       </c>
       <c r="H29" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B29,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B29+1))</f>
-        <v>3187.11</v>
+        <v/>
       </c>
       <c r="I29" s="53">
         <f>IFERROR(F29-H29,0)</f>
-        <v>539.89</v>
+        <v/>
       </c>
       <c r="J29" s="54">
         <f>IFERROR(I29/F29,0)</f>
-        <v>0.144859</v>
+        <v/>
       </c>
       <c r="K29" s="55" t="n"/>
       <c r="L29" s="18" t="inlineStr">
@@ -11326,7 +11359,7 @@
       <c r="Q29" s="56" t="n"/>
       <c r="R29" s="56">
         <f>IFERROR(D29*$T$7,0)</f>
-        <v>72.19</v>
+        <v/>
       </c>
       <c r="S29" s="56" t="n"/>
       <c r="T29" s="56" t="n"/>
@@ -11356,20 +11389,20 @@
       </c>
       <c r="F30" s="38">
         <f>IFERROR(D30+E30+G30,0)</f>
-        <v>5410.0</v>
+        <v/>
       </c>
       <c r="G30" s="39" t="n"/>
       <c r="H30" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B30,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B30+1))</f>
-        <v>6623.98</v>
+        <v/>
       </c>
       <c r="I30" s="41">
         <f>IFERROR(F30-H30,0)</f>
-        <v>-1213.98</v>
+        <v/>
       </c>
       <c r="J30" s="42">
         <f>IFERROR(I30/F30,0)</f>
-        <v>-0.224396</v>
+        <v/>
       </c>
       <c r="K30" s="43" t="n"/>
       <c r="L30" s="9" t="inlineStr">
@@ -11384,7 +11417,7 @@
       <c r="Q30" s="44" t="n"/>
       <c r="R30" s="44">
         <f>IFERROR(D30*$T$7,0)</f>
-        <v>37.76</v>
+        <v/>
       </c>
       <c r="S30" s="44" t="n"/>
       <c r="T30" s="44" t="n"/>
@@ -11414,20 +11447,20 @@
       </c>
       <c r="F31" s="50">
         <f>IFERROR(D31+E31+G31,0)</f>
-        <v>4265.0</v>
+        <v/>
       </c>
       <c r="G31" s="51" t="n"/>
       <c r="H31" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B31,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B31+1))</f>
-        <v>1341.81</v>
+        <v/>
       </c>
       <c r="I31" s="53">
         <f>IFERROR(F31-H31,0)</f>
-        <v>2923.19</v>
+        <v/>
       </c>
       <c r="J31" s="54">
         <f>IFERROR(I31/F31,0)</f>
-        <v>0.68539</v>
+        <v/>
       </c>
       <c r="K31" s="55" t="n"/>
       <c r="L31" s="18" t="inlineStr">
@@ -11442,7 +11475,7 @@
       <c r="Q31" s="56" t="n"/>
       <c r="R31" s="56">
         <f>IFERROR(D31*$T$7,0)</f>
-        <v>101.74</v>
+        <v/>
       </c>
       <c r="S31" s="56" t="n"/>
       <c r="T31" s="56" t="n"/>
@@ -11472,22 +11505,22 @@
       </c>
       <c r="F32" s="38">
         <f>IFERROR(D32+E32+G32,0)</f>
-        <v>4166.0</v>
+        <v/>
       </c>
       <c r="G32" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B32,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B32+1))</f>
-        <v>4044.0</v>
+        <v/>
       </c>
       <c r="I32" s="41">
         <f>IFERROR(F32-H32,0)</f>
-        <v>122.0</v>
+        <v/>
       </c>
       <c r="J32" s="42">
         <f>IFERROR(I32/F32,0)</f>
-        <v>0.029285</v>
+        <v/>
       </c>
       <c r="K32" s="43" t="n"/>
       <c r="L32" s="9" t="inlineStr">
@@ -11502,7 +11535,7 @@
       <c r="Q32" s="44" t="n"/>
       <c r="R32" s="44">
         <f>IFERROR(D32*$T$7,0)</f>
-        <v>84.24</v>
+        <v/>
       </c>
       <c r="S32" s="44" t="n"/>
       <c r="T32" s="44" t="n"/>
@@ -11532,22 +11565,22 @@
       </c>
       <c r="F33" s="50">
         <f>IFERROR(D33+E33+G33,0)</f>
-        <v>6070.0</v>
+        <v/>
       </c>
       <c r="G33" s="51" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B33,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B33+1))</f>
-        <v>901.8</v>
+        <v/>
       </c>
       <c r="I33" s="53">
         <f>IFERROR(F33-H33,0)</f>
-        <v>5168.2</v>
+        <v/>
       </c>
       <c r="J33" s="54">
         <f>IFERROR(I33/F33,0)</f>
-        <v>0.851433</v>
+        <v/>
       </c>
       <c r="K33" s="55" t="n"/>
       <c r="L33" s="18" t="inlineStr">
@@ -11562,7 +11595,7 @@
       <c r="Q33" s="56" t="n"/>
       <c r="R33" s="56">
         <f>IFERROR(D33*$T$7,0)</f>
-        <v>106.98</v>
+        <v/>
       </c>
       <c r="S33" s="56" t="n"/>
       <c r="T33" s="56" t="n"/>
@@ -11592,22 +11625,22 @@
       </c>
       <c r="F34" s="38">
         <f>IFERROR(D34+E34+G34,0)</f>
-        <v>1811.0</v>
+        <v/>
       </c>
       <c r="G34" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B34,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B34+1))</f>
-        <v>8084.16</v>
+        <v/>
       </c>
       <c r="I34" s="41">
         <f>IFERROR(F34-H34,0)</f>
-        <v>-6273.16</v>
+        <v/>
       </c>
       <c r="J34" s="42">
         <f>IFERROR(I34/F34,0)</f>
-        <v>-3.46392</v>
+        <v/>
       </c>
       <c r="K34" s="43" t="n"/>
       <c r="L34" s="9" t="inlineStr">
@@ -11622,7 +11655,7 @@
       <c r="Q34" s="44" t="n"/>
       <c r="R34" s="44">
         <f>IFERROR(D34*$T$7,0)</f>
-        <v>40.8</v>
+        <v/>
       </c>
       <c r="S34" s="44" t="n"/>
       <c r="T34" s="44" t="n"/>
@@ -11652,22 +11685,22 @@
       </c>
       <c r="F35" s="50">
         <f>IFERROR(D35+E35+G35,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="G35" s="51" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B35,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B35+1))</f>
-        <v>1526.18</v>
+        <v/>
       </c>
       <c r="I35" s="53">
         <f>IFERROR(F35-H35,0)</f>
-        <v>-1526.18</v>
+        <v/>
       </c>
       <c r="J35" s="54">
         <f>IFERROR(I35/F35,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K35" s="55" t="n"/>
       <c r="L35" s="18" t="inlineStr">
@@ -11682,7 +11715,7 @@
       <c r="Q35" s="56" t="n"/>
       <c r="R35" s="56">
         <f>IFERROR(D35*$T$7,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S35" s="56" t="n"/>
       <c r="T35" s="56" t="n"/>
@@ -11712,22 +11745,22 @@
       </c>
       <c r="F36" s="38">
         <f>IFERROR(D36+E36+G36,0)</f>
-        <v>4423.0</v>
+        <v/>
       </c>
       <c r="G36" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B36,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B36+1))</f>
-        <v>2858.08</v>
+        <v/>
       </c>
       <c r="I36" s="41">
         <f>IFERROR(F36-H36,0)</f>
-        <v>1564.92</v>
+        <v/>
       </c>
       <c r="J36" s="42">
         <f>IFERROR(I36/F36,0)</f>
-        <v>0.353814</v>
+        <v/>
       </c>
       <c r="K36" s="43" t="n"/>
       <c r="L36" s="9" t="inlineStr">
@@ -11742,7 +11775,7 @@
       <c r="Q36" s="44" t="n"/>
       <c r="R36" s="44">
         <f>IFERROR(D36*$T$7,0)</f>
-        <v>84.24</v>
+        <v/>
       </c>
       <c r="S36" s="44" t="n"/>
       <c r="T36" s="44" t="n"/>
@@ -11772,22 +11805,22 @@
       </c>
       <c r="F37" s="50">
         <f>IFERROR(D37+E37+G37,0)</f>
-        <v>2786.0</v>
+        <v/>
       </c>
       <c r="G37" s="51" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B37,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B37+1))</f>
-        <v>2541.9</v>
+        <v/>
       </c>
       <c r="I37" s="53">
         <f>IFERROR(F37-H37,0)</f>
-        <v>244.1</v>
+        <v/>
       </c>
       <c r="J37" s="54">
         <f>IFERROR(I37/F37,0)</f>
-        <v>0.087617</v>
+        <v/>
       </c>
       <c r="K37" s="55" t="n"/>
       <c r="L37" s="18" t="inlineStr">
@@ -11802,7 +11835,7 @@
       <c r="Q37" s="56" t="n"/>
       <c r="R37" s="56">
         <f>IFERROR(D37*$T$7,0)</f>
-        <v>74.74</v>
+        <v/>
       </c>
       <c r="S37" s="56" t="n"/>
       <c r="T37" s="56" t="n"/>
@@ -11832,22 +11865,22 @@
       </c>
       <c r="F38" s="38">
         <f>IFERROR(D38+E38+G38,0)</f>
-        <v>4404.0</v>
+        <v/>
       </c>
       <c r="G38" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B38,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B38+1))</f>
-        <v>2353.0</v>
+        <v/>
       </c>
       <c r="I38" s="41">
         <f>IFERROR(F38-H38,0)</f>
-        <v>2051.0</v>
+        <v/>
       </c>
       <c r="J38" s="42">
         <f>IFERROR(I38/F38,0)</f>
-        <v>0.465713</v>
+        <v/>
       </c>
       <c r="K38" s="43" t="n"/>
       <c r="L38" s="9" t="inlineStr">
@@ -11862,7 +11895,7 @@
       <c r="Q38" s="44" t="n"/>
       <c r="R38" s="44">
         <f>IFERROR(D38*$T$7,0)</f>
-        <v>86.19</v>
+        <v/>
       </c>
       <c r="S38" s="44" t="n"/>
       <c r="T38" s="44" t="n"/>
@@ -11892,22 +11925,22 @@
       </c>
       <c r="F39" s="50">
         <f>IFERROR(D39+E39+G39,0)</f>
-        <v>4165.0</v>
+        <v/>
       </c>
       <c r="G39" s="51" t="n">
         <v>400</v>
       </c>
       <c r="H39" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B39,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B39+1))</f>
-        <v>2958.83</v>
+        <v/>
       </c>
       <c r="I39" s="53">
         <f>IFERROR(F39-H39,0)</f>
-        <v>1206.17</v>
+        <v/>
       </c>
       <c r="J39" s="54">
         <f>IFERROR(I39/F39,0)</f>
-        <v>0.289597</v>
+        <v/>
       </c>
       <c r="K39" s="55" t="n"/>
       <c r="L39" s="18" t="inlineStr">
@@ -11922,7 +11955,7 @@
       <c r="Q39" s="56" t="n"/>
       <c r="R39" s="56">
         <f>IFERROR(D39*$T$7,0)</f>
-        <v>89.77</v>
+        <v/>
       </c>
       <c r="S39" s="56" t="n"/>
       <c r="T39" s="56" t="n"/>
@@ -11952,22 +11985,22 @@
       </c>
       <c r="F40" s="38">
         <f>IFERROR(D40+E40+G40,0)</f>
-        <v>6804.0</v>
+        <v/>
       </c>
       <c r="G40" s="39" t="n">
         <v>120</v>
       </c>
       <c r="H40" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B40,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B40+1))</f>
-        <v>1483.0</v>
+        <v/>
       </c>
       <c r="I40" s="41">
         <f>IFERROR(F40-H40,0)</f>
-        <v>5321.0</v>
+        <v/>
       </c>
       <c r="J40" s="42">
         <f>IFERROR(I40/F40,0)</f>
-        <v>0.78204</v>
+        <v/>
       </c>
       <c r="K40" s="43" t="n"/>
       <c r="L40" s="9" t="inlineStr">
@@ -11982,7 +12015,7 @@
       <c r="Q40" s="44" t="n"/>
       <c r="R40" s="44">
         <f>IFERROR(D40*$T$7,0)</f>
-        <v>169.67</v>
+        <v/>
       </c>
       <c r="S40" s="44" t="n"/>
       <c r="T40" s="44" t="n"/>
@@ -12012,22 +12045,22 @@
       </c>
       <c r="F41" s="50">
         <f>IFERROR(D41+E41+G41,0)</f>
-        <v>2251.0</v>
+        <v/>
       </c>
       <c r="G41" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B41,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B41+1))</f>
-        <v>9320.81</v>
+        <v/>
       </c>
       <c r="I41" s="259">
         <f>IFERROR(F41-H41,0)</f>
-        <v>-7069.81</v>
+        <v/>
       </c>
       <c r="J41" s="260">
         <f>IFERROR(I41/F41,0)</f>
-        <v>-3.140742</v>
+        <v/>
       </c>
       <c r="K41" s="254" t="n"/>
       <c r="L41" s="261" t="inlineStr">
@@ -12042,7 +12075,7 @@
       <c r="Q41" s="56" t="n"/>
       <c r="R41" s="56">
         <f>IFERROR(D41*$T$7,0)</f>
-        <v>47.58</v>
+        <v/>
       </c>
       <c r="S41" s="56" t="n"/>
       <c r="T41" s="56" t="n"/>
@@ -12072,22 +12105,22 @@
       </c>
       <c r="F42" s="38">
         <f>IFERROR(D42+E42+G42,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="G42" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B42,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B42+1))</f>
-        <v>2065.85</v>
+        <v/>
       </c>
       <c r="I42" s="274">
         <f>IFERROR(F42-H42,0)</f>
-        <v>-2065.85</v>
+        <v/>
       </c>
       <c r="J42" s="275">
         <f>IFERROR(I42/F42,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K42" s="250" t="n"/>
       <c r="L42" s="276" t="inlineStr">
@@ -12102,7 +12135,7 @@
       <c r="Q42" s="44" t="n"/>
       <c r="R42" s="44">
         <f>IFERROR(D42*$T$7,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S42" s="44" t="n"/>
       <c r="T42" s="44" t="n"/>
@@ -12132,22 +12165,22 @@
       </c>
       <c r="F43" s="50">
         <f>IFERROR(D43+E43+G43,0)</f>
-        <v>4259.0</v>
+        <v/>
       </c>
       <c r="G43" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B43,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B43+1))</f>
-        <v>1451.0</v>
+        <v/>
       </c>
       <c r="I43" s="259">
         <f>IFERROR(F43-H43,0)</f>
-        <v>2808.0</v>
+        <v/>
       </c>
       <c r="J43" s="260">
         <f>IFERROR(I43/F43,0)</f>
-        <v>0.65931</v>
+        <v/>
       </c>
       <c r="K43" s="254" t="n"/>
       <c r="L43" s="261" t="inlineStr">
@@ -12162,7 +12195,7 @@
       <c r="Q43" s="56" t="n"/>
       <c r="R43" s="56">
         <f>IFERROR(D43*$T$7,0)</f>
-        <v>99.84</v>
+        <v/>
       </c>
       <c r="S43" s="56" t="n"/>
       <c r="T43" s="56" t="n"/>
@@ -12192,22 +12225,22 @@
       </c>
       <c r="F44" s="38">
         <f>IFERROR(D44+E44+G44,0)</f>
-        <v>2967.0</v>
+        <v/>
       </c>
       <c r="G44" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B44,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B44+1))</f>
-        <v>757.13</v>
+        <v/>
       </c>
       <c r="I44" s="274">
         <f>IFERROR(F44-H44,0)</f>
-        <v>2209.87</v>
+        <v/>
       </c>
       <c r="J44" s="275">
         <f>IFERROR(I44/F44,0)</f>
-        <v>0.744816</v>
+        <v/>
       </c>
       <c r="K44" s="250" t="n"/>
       <c r="L44" s="276" t="inlineStr">
@@ -12222,7 +12255,7 @@
       <c r="Q44" s="44" t="n"/>
       <c r="R44" s="44">
         <f>IFERROR(D44*$T$7,0)</f>
-        <v>58.95</v>
+        <v/>
       </c>
       <c r="S44" s="44" t="n"/>
       <c r="T44" s="44" t="n"/>
@@ -12252,22 +12285,22 @@
       </c>
       <c r="F45" s="50">
         <f>IFERROR(D45+E45+G45,0)</f>
-        <v>3589.0</v>
+        <v/>
       </c>
       <c r="G45" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B45,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B45+1))</f>
-        <v>3781.35</v>
+        <v/>
       </c>
       <c r="I45" s="259">
         <f>IFERROR(F45-H45,0)</f>
-        <v>-192.35</v>
+        <v/>
       </c>
       <c r="J45" s="260">
         <f>IFERROR(I45/F45,0)</f>
-        <v>-0.053594</v>
+        <v/>
       </c>
       <c r="K45" s="254" t="n"/>
       <c r="L45" s="261" t="inlineStr">
@@ -12282,7 +12315,7 @@
       <c r="Q45" s="56" t="n"/>
       <c r="R45" s="56">
         <f>IFERROR(D45*$T$7,0)</f>
-        <v>43.2</v>
+        <v/>
       </c>
       <c r="S45" s="56" t="n"/>
       <c r="T45" s="56" t="n"/>
@@ -12312,22 +12345,22 @@
       </c>
       <c r="F46" s="38">
         <f>IFERROR(D46+E46+G46,0)</f>
-        <v>3588.0</v>
+        <v/>
       </c>
       <c r="G46" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B46,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B46+1))</f>
-        <v>1228.0</v>
+        <v/>
       </c>
       <c r="I46" s="274">
         <f>IFERROR(F46-H46,0)</f>
-        <v>2360.0</v>
+        <v/>
       </c>
       <c r="J46" s="275">
         <f>IFERROR(I46/F46,0)</f>
-        <v>0.657748</v>
+        <v/>
       </c>
       <c r="K46" s="250" t="n"/>
       <c r="L46" s="276" t="inlineStr">
@@ -12342,7 +12375,7 @@
       <c r="Q46" s="44" t="n"/>
       <c r="R46" s="44">
         <f>IFERROR(D46*$T$7,0)</f>
-        <v>70.44</v>
+        <v/>
       </c>
       <c r="S46" s="44" t="n"/>
       <c r="T46" s="44" t="n"/>
@@ -12372,22 +12405,22 @@
       </c>
       <c r="F47" s="50">
         <f>IFERROR(D47+E47+G47,0)</f>
-        <v>4477.0</v>
+        <v/>
       </c>
       <c r="G47" s="257" t="n">
         <v>165</v>
       </c>
       <c r="H47" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B47,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B47+1))</f>
-        <v>1945.53</v>
+        <v/>
       </c>
       <c r="I47" s="259">
         <f>IFERROR(F47-H47,0)</f>
-        <v>2531.47</v>
+        <v/>
       </c>
       <c r="J47" s="260">
         <f>IFERROR(I47/F47,0)</f>
-        <v>0.565439</v>
+        <v/>
       </c>
       <c r="K47" s="254" t="n"/>
       <c r="L47" s="261" t="inlineStr">
@@ -12402,7 +12435,7 @@
       <c r="Q47" s="56" t="n"/>
       <c r="R47" s="56">
         <f>IFERROR(D47*$T$7,0)</f>
-        <v>69.79</v>
+        <v/>
       </c>
       <c r="S47" s="56" t="n"/>
       <c r="T47" s="56" t="n"/>
@@ -12432,22 +12465,22 @@
       </c>
       <c r="F48" s="38">
         <f>IFERROR(D48+E48+G48,0)</f>
-        <v>2029.0</v>
+        <v/>
       </c>
       <c r="G48" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B48,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B48+1))</f>
-        <v>5250.0</v>
+        <v/>
       </c>
       <c r="I48" s="274">
         <f>IFERROR(F48-H48,0)</f>
-        <v>-3221.0</v>
+        <v/>
       </c>
       <c r="J48" s="275">
         <f>IFERROR(I48/F48,0)</f>
-        <v>-1.587482</v>
+        <v/>
       </c>
       <c r="K48" s="250" t="n"/>
       <c r="L48" s="276" t="inlineStr">
@@ -12462,7 +12495,7 @@
       <c r="Q48" s="44" t="n"/>
       <c r="R48" s="44">
         <f>IFERROR(D48*$T$7,0)</f>
-        <v>7.1</v>
+        <v/>
       </c>
       <c r="S48" s="44" t="n"/>
       <c r="T48" s="44" t="n"/>
@@ -12492,22 +12525,22 @@
       </c>
       <c r="F49" s="50">
         <f>IFERROR(D49+E49+G49,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="G49" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B49,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B49+1))</f>
-        <v>3865.06</v>
+        <v/>
       </c>
       <c r="I49" s="259">
         <f>IFERROR(F49-H49,0)</f>
-        <v>-3865.06</v>
+        <v/>
       </c>
       <c r="J49" s="260">
         <f>IFERROR(I49/F49,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K49" s="254" t="n"/>
       <c r="L49" s="261" t="inlineStr">
@@ -12522,7 +12555,7 @@
       <c r="Q49" s="56" t="n"/>
       <c r="R49" s="56">
         <f>IFERROR(D49*$T$7,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S49" s="56" t="n"/>
       <c r="T49" s="56" t="n"/>
@@ -12552,22 +12585,22 @@
       </c>
       <c r="F50" s="38">
         <f>IFERROR(D50+E50+G50,0)</f>
-        <v>3389.0</v>
+        <v/>
       </c>
       <c r="G50" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B50,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B50+1))</f>
-        <v>2683.27</v>
+        <v/>
       </c>
       <c r="I50" s="274">
         <f>IFERROR(F50-H50,0)</f>
-        <v>705.73</v>
+        <v/>
       </c>
       <c r="J50" s="275">
         <f>IFERROR(I50/F50,0)</f>
-        <v>0.208241</v>
+        <v/>
       </c>
       <c r="K50" s="250" t="n"/>
       <c r="L50" s="276" t="inlineStr">
@@ -12582,7 +12615,7 @@
       <c r="Q50" s="44" t="n"/>
       <c r="R50" s="44">
         <f>IFERROR(D50*$T$7,0)</f>
-        <v>73.65</v>
+        <v/>
       </c>
       <c r="S50" s="44" t="n"/>
       <c r="T50" s="44" t="n"/>
@@ -12612,22 +12645,22 @@
       </c>
       <c r="F51" s="50">
         <f>IFERROR(D51+E51+G51,0)</f>
-        <v>4133.0</v>
+        <v/>
       </c>
       <c r="G51" s="257" t="n">
         <v>55</v>
       </c>
       <c r="H51" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B51,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B51+1))</f>
-        <v>1581.27</v>
+        <v/>
       </c>
       <c r="I51" s="259">
         <f>IFERROR(F51-H51,0)</f>
-        <v>2551.73</v>
+        <v/>
       </c>
       <c r="J51" s="260">
         <f>IFERROR(I51/F51,0)</f>
-        <v>0.617404</v>
+        <v/>
       </c>
       <c r="K51" s="254" t="n"/>
       <c r="L51" s="261" t="inlineStr">
@@ -12642,7 +12675,7 @@
       <c r="Q51" s="56" t="n"/>
       <c r="R51" s="56">
         <f>IFERROR(D51*$T$7,0)</f>
-        <v>97.76</v>
+        <v/>
       </c>
       <c r="S51" s="56" t="n"/>
       <c r="T51" s="56" t="n"/>
@@ -12672,22 +12705,22 @@
       </c>
       <c r="F52" s="38">
         <f>IFERROR(D52+E52+G52,0)</f>
-        <v>4522.0</v>
+        <v/>
       </c>
       <c r="G52" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B52,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B52+1))</f>
-        <v>2341.23</v>
+        <v/>
       </c>
       <c r="I52" s="274">
         <f>IFERROR(F52-H52,0)</f>
-        <v>2180.77</v>
+        <v/>
       </c>
       <c r="J52" s="275">
         <f>IFERROR(I52/F52,0)</f>
-        <v>0.482258</v>
+        <v/>
       </c>
       <c r="K52" s="250" t="n"/>
       <c r="L52" s="276" t="inlineStr">
@@ -12702,7 +12735,7 @@
       <c r="Q52" s="44" t="n"/>
       <c r="R52" s="44">
         <f>IFERROR(D52*$T$7,0)</f>
-        <v>101.42</v>
+        <v/>
       </c>
       <c r="S52" s="44" t="n"/>
       <c r="T52" s="44" t="n"/>
@@ -12732,22 +12765,22 @@
       </c>
       <c r="F53" s="50">
         <f>IFERROR(D53+E53+G53,0)</f>
-        <v>3108.0</v>
+        <v/>
       </c>
       <c r="G53" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B53,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B53+1))</f>
-        <v>318.0</v>
+        <v/>
       </c>
       <c r="I53" s="259">
         <f>IFERROR(F53-H53,0)</f>
-        <v>2790.0</v>
+        <v/>
       </c>
       <c r="J53" s="260">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.897683</v>
+        <v/>
       </c>
       <c r="K53" s="254" t="inlineStr">
         <is>
@@ -12766,7 +12799,7 @@
       <c r="Q53" s="56" t="n"/>
       <c r="R53" s="56">
         <f>IFERROR(D53*$T$7,0)</f>
-        <v>75.48</v>
+        <v/>
       </c>
       <c r="S53" s="56" t="n"/>
       <c r="T53" s="56" t="n"/>
@@ -12796,22 +12829,22 @@
       </c>
       <c r="F54" s="38">
         <f>IFERROR(D54+E54+G54,0)</f>
-        <v>6077.0</v>
+        <v/>
       </c>
       <c r="G54" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B54,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B54+1))</f>
-        <v>2809.6</v>
+        <v/>
       </c>
       <c r="I54" s="274">
         <f>IFERROR(F54-H54,0)</f>
-        <v>3267.4</v>
+        <v/>
       </c>
       <c r="J54" s="275">
         <f>IFERROR(I54/F54,0)</f>
-        <v>0.537667</v>
+        <v/>
       </c>
       <c r="K54" s="250" t="inlineStr">
         <is>
@@ -12830,7 +12863,7 @@
       <c r="Q54" s="44" t="n"/>
       <c r="R54" s="44">
         <f>IFERROR(D54*$T$7,0)</f>
-        <v>150.3</v>
+        <v/>
       </c>
       <c r="S54" s="44" t="n"/>
       <c r="T54" s="44" t="n"/>
@@ -12860,22 +12893,22 @@
       </c>
       <c r="F55" s="50">
         <f>IFERROR(D55+E55+G55,0)</f>
-        <v>2634.0</v>
+        <v/>
       </c>
       <c r="G55" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B55,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B55+1))</f>
-        <v>6877.73</v>
+        <v/>
       </c>
       <c r="I55" s="259">
         <f>IFERROR(F55-H55,0)</f>
-        <v>-4243.73</v>
+        <v/>
       </c>
       <c r="J55" s="260">
         <f>IFERROR(I55/F55,0)</f>
-        <v>-1.611135</v>
+        <v/>
       </c>
       <c r="K55" s="254" t="n"/>
       <c r="L55" s="261" t="inlineStr">
@@ -12890,7 +12923,7 @@
       <c r="Q55" s="56" t="n"/>
       <c r="R55" s="56">
         <f>IFERROR(D55*$T$7,0)</f>
-        <v>70.6</v>
+        <v/>
       </c>
       <c r="S55" s="56" t="n"/>
       <c r="T55" s="56" t="n"/>
@@ -12920,22 +12953,22 @@
       </c>
       <c r="F56" s="38">
         <f>IFERROR(D56+E56+G56,0)</f>
-        <v>3690.0</v>
+        <v/>
       </c>
       <c r="G56" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B56,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B56+1))</f>
-        <v>4200.0</v>
+        <v/>
       </c>
       <c r="I56" s="274">
         <f>IFERROR(F56-H56,0)</f>
-        <v>-510.0</v>
+        <v/>
       </c>
       <c r="J56" s="275">
         <f>IFERROR(I56/F56,0)</f>
-        <v>-0.138211</v>
+        <v/>
       </c>
       <c r="K56" s="250" t="n"/>
       <c r="L56" s="276" t="inlineStr">
@@ -12950,7 +12983,7 @@
       <c r="Q56" s="44" t="n"/>
       <c r="R56" s="44">
         <f>IFERROR(D56*$T$7,0)</f>
-        <v>88.91</v>
+        <v/>
       </c>
       <c r="S56" s="44" t="n"/>
       <c r="T56" s="44" t="n"/>
@@ -12980,22 +13013,22 @@
       </c>
       <c r="F57" s="50">
         <f>IFERROR(D57+E57+G57,0)</f>
-        <v>3660.0</v>
+        <v/>
       </c>
       <c r="G57" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B57,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B57+1))</f>
-        <v>49.0</v>
+        <v/>
       </c>
       <c r="I57" s="259">
         <f>IFERROR(F57-H57,0)</f>
-        <v>3611.0</v>
+        <v/>
       </c>
       <c r="J57" s="260">
         <f>IFERROR(I57/F57,0)</f>
-        <v>0.986612</v>
+        <v/>
       </c>
       <c r="K57" s="254" t="n"/>
       <c r="L57" s="261" t="inlineStr">
@@ -13010,7 +13043,7 @@
       <c r="Q57" s="56" t="n"/>
       <c r="R57" s="56">
         <f>IFERROR(D57*$T$7,0)</f>
-        <v>74.7</v>
+        <v/>
       </c>
       <c r="S57" s="56" t="n"/>
       <c r="T57" s="56" t="n"/>
@@ -13040,22 +13073,22 @@
       </c>
       <c r="F58" s="50">
         <f>IFERROR(D58+E58+G58+U58,0)</f>
-        <v>3688.0</v>
+        <v/>
       </c>
       <c r="G58" s="257" t="n">
         <v>195</v>
       </c>
       <c r="H58" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B58,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B58+1))</f>
-        <v>1415.43</v>
+        <v/>
       </c>
       <c r="I58" s="259">
         <f>IFERROR(F58-H58,0)</f>
-        <v>2272.57</v>
+        <v/>
       </c>
       <c r="J58" s="260">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.616207</v>
+        <v/>
       </c>
       <c r="K58" s="254" t="n"/>
       <c r="L58" s="261" t="inlineStr">
@@ -13070,7 +13103,7 @@
       <c r="Q58" s="292" t="n"/>
       <c r="R58" s="292">
         <f>IFERROR(D58*$T$7,0)</f>
-        <v>14.62</v>
+        <v/>
       </c>
       <c r="S58" s="292" t="n"/>
       <c r="T58" s="292" t="n"/>
@@ -13104,22 +13137,22 @@
       </c>
       <c r="F59" s="50">
         <f>IFERROR(D59+E59+G59+U59,0)</f>
-        <v>6015.0</v>
+        <v/>
       </c>
       <c r="G59" s="257" t="n">
         <v>120</v>
       </c>
       <c r="H59" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B59,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B59+1))</f>
-        <v>1820.89</v>
+        <v/>
       </c>
       <c r="I59" s="259">
         <f>IFERROR(F59-H59,0)</f>
-        <v>4194.11</v>
+        <v/>
       </c>
       <c r="J59" s="260">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.697275</v>
+        <v/>
       </c>
       <c r="K59" s="254" t="n"/>
       <c r="L59" s="261" t="inlineStr">
@@ -13134,7 +13167,7 @@
       <c r="Q59" s="292" t="n"/>
       <c r="R59" s="292">
         <f>IFERROR(D59*$T$7,0)</f>
-        <v>78.76</v>
+        <v/>
       </c>
       <c r="S59" s="292" t="n"/>
       <c r="T59" s="292" t="n"/>
@@ -13168,22 +13201,22 @@
       </c>
       <c r="F60" s="50">
         <f>IFERROR(D60+E60+G60+U60,0)</f>
-        <v>3500.0</v>
+        <v/>
       </c>
       <c r="G60" s="257" t="n">
         <v>70</v>
       </c>
       <c r="H60" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B60,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B60+1))</f>
-        <v>2094.0</v>
+        <v/>
       </c>
       <c r="I60" s="259">
         <f>IFERROR(F60-H60,0)</f>
-        <v>1406.0</v>
+        <v/>
       </c>
       <c r="J60" s="260">
         <f>IFERROR(I60/F60,0)</f>
-        <v>0.401714</v>
+        <v/>
       </c>
       <c r="K60" s="254" t="n"/>
       <c r="L60" s="261" t="inlineStr">
@@ -13198,7 +13231,7 @@
       <c r="Q60" s="292" t="n"/>
       <c r="R60" s="292">
         <f>IFERROR(D60*$T$7,0)</f>
-        <v>69.02</v>
+        <v/>
       </c>
       <c r="S60" s="292" t="n"/>
       <c r="T60" s="292" t="n"/>
@@ -13232,22 +13265,22 @@
       </c>
       <c r="F61" s="50">
         <f>IFERROR(D61+E61+G61+U61,0)</f>
-        <v>2725.0</v>
+        <v/>
       </c>
       <c r="G61" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B61,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B61+1))</f>
-        <v>10207.0</v>
+        <v/>
       </c>
       <c r="I61" s="259">
         <f>IFERROR(F61-H61,0)</f>
-        <v>-7482.0</v>
+        <v/>
       </c>
       <c r="J61" s="260">
         <f>IFERROR(I61/F61,0)</f>
-        <v>-2.745688</v>
+        <v/>
       </c>
       <c r="K61" s="254" t="n"/>
       <c r="L61" s="261" t="inlineStr">
@@ -13262,7 +13295,7 @@
       <c r="Q61" s="292" t="n"/>
       <c r="R61" s="292">
         <f>IFERROR(D61*$T$7,0)</f>
-        <v>11.37</v>
+        <v/>
       </c>
       <c r="S61" s="292" t="n"/>
       <c r="T61" s="292" t="n"/>
@@ -13296,22 +13329,22 @@
       </c>
       <c r="F62" s="50">
         <f>IFERROR(D62+E62+G62+U62+Y62,0)</f>
-        <v>3990.0</v>
+        <v/>
       </c>
       <c r="G62" s="257" t="n">
         <v>120</v>
       </c>
       <c r="H62" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B62,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B62+1))</f>
-        <v>3142.0</v>
+        <v/>
       </c>
       <c r="I62" s="259">
         <f>IFERROR(F62-H62,0)</f>
-        <v>848.0</v>
+        <v/>
       </c>
       <c r="J62" s="260">
         <f>IFERROR(I62/F62,0)</f>
-        <v>0.212531</v>
+        <v/>
       </c>
       <c r="K62" s="254" t="n"/>
       <c r="L62" s="261" t="inlineStr">
@@ -13326,7 +13359,7 @@
       <c r="Q62" s="292" t="n"/>
       <c r="R62" s="292">
         <f>IFERROR(D62*$T$7,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S62" s="292" t="n"/>
       <c r="T62" s="292" t="n"/>
@@ -13364,22 +13397,22 @@
       </c>
       <c r="F63" s="50">
         <f>IFERROR(D63+E63+G63+U63+Y63,0)</f>
-        <v>3915.0</v>
+        <v/>
       </c>
       <c r="G63" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B63,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B63+1))</f>
-        <v>596.38</v>
+        <v/>
       </c>
       <c r="I63" s="259">
         <f>IFERROR(F63-H63,0)</f>
-        <v>3318.62</v>
+        <v/>
       </c>
       <c r="J63" s="260">
         <f>IFERROR(I63/F63,0)</f>
-        <v>0.847668</v>
+        <v/>
       </c>
       <c r="K63" s="254" t="n"/>
       <c r="L63" s="261" t="inlineStr">
@@ -13394,7 +13427,7 @@
       <c r="Q63" s="292" t="n"/>
       <c r="R63" s="311">
         <f>IFERROR(D63*$T$7,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S63" s="292" t="n"/>
       <c r="T63" s="292" t="n"/>
@@ -13432,22 +13465,22 @@
       </c>
       <c r="F64" s="50">
         <f>IFERROR(D64+E64+G64+U64+Y64,0)</f>
-        <v>5565.0</v>
+        <v/>
       </c>
       <c r="G64" s="257" t="n">
         <v>130</v>
       </c>
       <c r="H64" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B64,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B64+1))</f>
-        <v>2606.86</v>
+        <v/>
       </c>
       <c r="I64" s="259">
         <f>IFERROR(F64-H64,0)</f>
-        <v>2958.14</v>
+        <v/>
       </c>
       <c r="J64" s="260">
         <f>IFERROR(I64/F64,0)</f>
-        <v>0.531562</v>
+        <v/>
       </c>
       <c r="K64" s="254" t="n"/>
       <c r="L64" s="261" t="inlineStr">
@@ -13462,7 +13495,7 @@
       <c r="Q64" s="292" t="n"/>
       <c r="R64" s="311">
         <f>IFERROR(D64*$T$7,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S64" s="292" t="n"/>
       <c r="T64" s="292" t="n"/>
@@ -13500,22 +13533,22 @@
       </c>
       <c r="F65" s="50">
         <f>IFERROR(D65+E65+G65+U65+Y65,0)</f>
-        <v>12495.0</v>
+        <v/>
       </c>
       <c r="G65" s="257" t="n">
         <v>2385</v>
       </c>
       <c r="H65" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B65,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B65+1))</f>
-        <v>1657.0</v>
+        <v/>
       </c>
       <c r="I65" s="259">
         <f>IFERROR(F65-H65,0)</f>
-        <v>10838.0</v>
+        <v/>
       </c>
       <c r="J65" s="260">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.867387</v>
+        <v/>
       </c>
       <c r="K65" s="254" t="n"/>
       <c r="L65" s="261" t="inlineStr">
@@ -13530,7 +13563,7 @@
       <c r="Q65" s="292" t="n"/>
       <c r="R65" s="311">
         <f>IFERROR(D65*$T$7,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S65" s="292" t="n"/>
       <c r="T65" s="292" t="n"/>
@@ -13568,22 +13601,22 @@
       </c>
       <c r="F66" s="50">
         <f>IFERROR(D66+E66+G66+U66+Y66,0)</f>
-        <v>2622.0</v>
+        <v/>
       </c>
       <c r="G66" s="257" t="n">
         <v>300</v>
       </c>
       <c r="H66" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B66,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B66+1))</f>
-        <v>1951.0</v>
+        <v/>
       </c>
       <c r="I66" s="259">
         <f>IFERROR(F66-H66,0)</f>
-        <v>671.0</v>
+        <v/>
       </c>
       <c r="J66" s="260">
         <f>IFERROR(I66/F66,0)</f>
-        <v>0.255912</v>
+        <v/>
       </c>
       <c r="K66" s="254" t="n"/>
       <c r="L66" s="261" t="inlineStr">
@@ -13598,7 +13631,7 @@
       <c r="Q66" s="292" t="n"/>
       <c r="R66" s="311">
         <f>IFERROR(D66*$T$7,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S66" s="292" t="n"/>
       <c r="T66" s="292" t="n"/>
@@ -13636,22 +13669,22 @@
       </c>
       <c r="F67" s="50">
         <f>IFERROR(D67+E67+G67+U67+Y67,0)</f>
-        <v>2900.0</v>
+        <v/>
       </c>
       <c r="G67" s="257" t="n">
         <v>290</v>
       </c>
       <c r="H67" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B67,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B67+1))</f>
-        <v>6770.0</v>
+        <v/>
       </c>
       <c r="I67" s="259">
         <f>IFERROR(F67-H67,0)</f>
-        <v>-3870.0</v>
+        <v/>
       </c>
       <c r="J67" s="260">
         <f>IFERROR(I67/F67,0)</f>
-        <v>-1.334483</v>
+        <v/>
       </c>
       <c r="K67" s="254" t="n"/>
       <c r="L67" s="261" t="inlineStr">
@@ -13666,7 +13699,7 @@
       <c r="Q67" s="292" t="n"/>
       <c r="R67" s="311">
         <f>IFERROR(D67*$T$7,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S67" s="292" t="n"/>
       <c r="T67" s="292" t="n"/>
@@ -13704,22 +13737,22 @@
       </c>
       <c r="F68" s="50">
         <f>IFERROR(D68+E68+G68+U68+Y68,0)</f>
-        <v>4955.0</v>
+        <v/>
       </c>
       <c r="G68" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H68" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B68,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B68+1))</f>
-        <v>2459.0</v>
+        <v/>
       </c>
       <c r="I68" s="259">
         <f>IFERROR(F68-H68,0)</f>
-        <v>2496.0</v>
+        <v/>
       </c>
       <c r="J68" s="260">
         <f>IFERROR(I68/F68,0)</f>
-        <v>0.503734</v>
+        <v/>
       </c>
       <c r="K68" s="254" t="n"/>
       <c r="L68" s="261" t="inlineStr">
@@ -13734,7 +13767,7 @@
       <c r="Q68" s="292" t="n"/>
       <c r="R68" s="311">
         <f>IFERROR(D68*$T$7,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S68" s="292" t="n"/>
       <c r="T68" s="292" t="n"/>
@@ -13772,22 +13805,22 @@
       </c>
       <c r="F69" s="50">
         <f>IFERROR(D69+E69+G69+U69+Y69,0)</f>
-        <v>5480.0</v>
+        <v/>
       </c>
       <c r="G69" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H69" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B69,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B69+1))</f>
-        <v>2197.0</v>
+        <v/>
       </c>
       <c r="I69" s="259">
         <f>IFERROR(F69-H69,0)</f>
-        <v>3283.0</v>
+        <v/>
       </c>
       <c r="J69" s="260">
         <f>IFERROR(I69/F69,0)</f>
-        <v>0.599088</v>
+        <v/>
       </c>
       <c r="K69" s="254" t="n"/>
       <c r="L69" s="261" t="inlineStr">
@@ -13802,7 +13835,7 @@
       <c r="Q69" s="292" t="n"/>
       <c r="R69" s="311">
         <f>IFERROR(D69*$T$7,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S69" s="292" t="n"/>
       <c r="T69" s="292" t="n"/>
@@ -13840,22 +13873,22 @@
       </c>
       <c r="F70" s="50">
         <f>IFERROR(D70+E70+G70+U70+Y70,0)</f>
-        <v>5205.0</v>
+        <v/>
       </c>
       <c r="G70" s="257" t="n">
         <v>355</v>
       </c>
       <c r="H70" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B70,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B70+1))</f>
-        <v>3819.0</v>
+        <v/>
       </c>
       <c r="I70" s="259">
         <f>IFERROR(F70-H70,0)</f>
-        <v>1386.0</v>
+        <v/>
       </c>
       <c r="J70" s="260">
         <f>IFERROR(I70/F70,0)</f>
-        <v>0.266282</v>
+        <v/>
       </c>
       <c r="K70" s="254" t="n"/>
       <c r="L70" s="261" t="inlineStr">
@@ -13870,7 +13903,7 @@
       <c r="Q70" s="292" t="n"/>
       <c r="R70" s="311">
         <f>IFERROR(D70*$T$7,0)</f>
-        <v>93.79</v>
+        <v/>
       </c>
       <c r="S70" s="292" t="n"/>
       <c r="T70" s="292" t="n"/>
@@ -13908,22 +13941,22 @@
       </c>
       <c r="F71" s="50">
         <f>IFERROR(D71+E71+G71+U71+Y71,0)</f>
-        <v>4075.0</v>
+        <v/>
       </c>
       <c r="G71" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B71,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B71+1))</f>
-        <v>5348.83</v>
+        <v/>
       </c>
       <c r="I71" s="259">
         <f>IFERROR(F71-H71,0)</f>
-        <v>-1273.83</v>
+        <v/>
       </c>
       <c r="J71" s="260">
         <f>IFERROR(I71/F71,0)</f>
-        <v>-0.312596</v>
+        <v/>
       </c>
       <c r="K71" s="254" t="n"/>
       <c r="L71" s="261" t="inlineStr">
@@ -13938,7 +13971,7 @@
       <c r="Q71" s="292" t="n"/>
       <c r="R71" s="311">
         <f>IFERROR(D71*$T$7,0)</f>
-        <v>68.82</v>
+        <v/>
       </c>
       <c r="S71" s="292" t="n"/>
       <c r="T71" s="292" t="n"/>
@@ -13976,22 +14009,22 @@
       </c>
       <c r="F72" s="50">
         <f>IFERROR(D72+E72+G72+U72+Y72,0)</f>
-        <v>5770.0</v>
+        <v/>
       </c>
       <c r="G72" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B72,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B72+1))</f>
-        <v>1886.0</v>
+        <v/>
       </c>
       <c r="I72" s="259">
         <f>IFERROR(F72-H72,0)</f>
-        <v>3884.0</v>
+        <v/>
       </c>
       <c r="J72" s="260">
         <f>IFERROR(I72/F72,0)</f>
-        <v>0.673137</v>
+        <v/>
       </c>
       <c r="K72" s="254" t="n"/>
       <c r="L72" s="261" t="inlineStr">
@@ -14006,7 +14039,7 @@
       <c r="Q72" s="292" t="n"/>
       <c r="R72" s="311">
         <f>IFERROR(D72*$T$7,0)</f>
-        <v>99.67</v>
+        <v/>
       </c>
       <c r="S72" s="292" t="n"/>
       <c r="T72" s="292" t="n"/>
@@ -14044,22 +14077,22 @@
       </c>
       <c r="F73" s="50">
         <f>IFERROR(D73+E73+G73+U73+Y73,0)</f>
-        <v>1225.0</v>
+        <v/>
       </c>
       <c r="G73" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H73" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B73,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B73+1))</f>
-        <v>6613.0</v>
+        <v/>
       </c>
       <c r="I73" s="259">
         <f>IFERROR(F73-H73,0)</f>
-        <v>-5388.0</v>
+        <v/>
       </c>
       <c r="J73" s="260">
         <f>IFERROR(I73/F73,0)</f>
-        <v>-4.398367</v>
+        <v/>
       </c>
       <c r="K73" s="254" t="n"/>
       <c r="L73" s="261" t="inlineStr">
@@ -14074,7 +14107,7 @@
       <c r="Q73" s="292" t="n"/>
       <c r="R73" s="311">
         <f>IFERROR(D73*$T$7,0)</f>
-        <v>6.29</v>
+        <v/>
       </c>
       <c r="S73" s="292" t="n"/>
       <c r="T73" s="292" t="n"/>
@@ -14112,22 +14145,22 @@
       </c>
       <c r="F74" s="38">
         <f>IFERROR(D74+E74+G74+U74+Y74,0)</f>
-        <v>3180.0</v>
+        <v/>
       </c>
       <c r="G74" s="272" t="n">
         <v>700</v>
       </c>
       <c r="H74" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B74,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B74+1))</f>
-        <v>928.0</v>
+        <v/>
       </c>
       <c r="I74" s="274">
         <f>IFERROR(F74-H74,0)</f>
-        <v>2252.0</v>
+        <v/>
       </c>
       <c r="J74" s="275">
         <f>IFERROR(I74/F74,0)</f>
-        <v>0.708176</v>
+        <v/>
       </c>
       <c r="K74" s="250" t="n"/>
       <c r="L74" s="276" t="inlineStr">
@@ -14142,7 +14175,7 @@
       <c r="Q74" s="324" t="n"/>
       <c r="R74" s="327">
         <f>IFERROR(D74*$T$7,0)</f>
-        <v>44.66</v>
+        <v/>
       </c>
       <c r="S74" s="324" t="n"/>
       <c r="T74" s="324" t="n"/>
@@ -14180,22 +14213,22 @@
       </c>
       <c r="F75" s="50">
         <f>IFERROR(D75+E75+G75+U75+Y75,0)</f>
-        <v>5250.0</v>
+        <v/>
       </c>
       <c r="G75" s="257" t="n">
         <v>130</v>
       </c>
       <c r="H75" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B75,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B75+1))</f>
-        <v>1504.0</v>
+        <v/>
       </c>
       <c r="I75" s="259">
         <f>IFERROR(F75-H75,0)</f>
-        <v>3746.0</v>
+        <v/>
       </c>
       <c r="J75" s="260">
         <f>IFERROR(I75/F75,0)</f>
-        <v>0.713524</v>
+        <v/>
       </c>
       <c r="K75" s="254" t="n"/>
       <c r="L75" s="261" t="inlineStr">
@@ -14210,7 +14243,7 @@
       <c r="Q75" s="292" t="n"/>
       <c r="R75" s="311">
         <f>IFERROR(D75*$T$7,0)</f>
-        <v>130.12</v>
+        <v/>
       </c>
       <c r="S75" s="292" t="n"/>
       <c r="T75" s="292" t="n"/>
@@ -14248,22 +14281,22 @@
       </c>
       <c r="F76" s="38">
         <f>IFERROR(D76+E76+G76+U76+Y76,0)</f>
-        <v>4120.0</v>
+        <v/>
       </c>
       <c r="G76" s="272" t="n">
         <v>205</v>
       </c>
       <c r="H76" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B76,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B76+1))</f>
-        <v>1495.0</v>
+        <v/>
       </c>
       <c r="I76" s="274">
         <f>IFERROR(F76-H76,0)</f>
-        <v>2625.0</v>
+        <v/>
       </c>
       <c r="J76" s="275">
         <f>IFERROR(I76/F76,0)</f>
-        <v>0.637136</v>
+        <v/>
       </c>
       <c r="K76" s="250" t="n"/>
       <c r="L76" s="276" t="inlineStr">
@@ -14278,7 +14311,7 @@
       <c r="Q76" s="324" t="n"/>
       <c r="R76" s="327">
         <f>IFERROR(D76*$T$7,0)</f>
-        <v>99.67</v>
+        <v/>
       </c>
       <c r="S76" s="324" t="n"/>
       <c r="T76" s="324" t="n"/>
@@ -14316,22 +14349,22 @@
       </c>
       <c r="F77" s="50">
         <f>IFERROR(D77+E77+G77+U77+Y77,0)</f>
-        <v>3234.0</v>
+        <v/>
       </c>
       <c r="G77" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B77,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B77+1))</f>
-        <v>268.0</v>
+        <v/>
       </c>
       <c r="I77" s="259">
         <f>IFERROR(F77-H77,0)</f>
-        <v>2966.0</v>
+        <v/>
       </c>
       <c r="J77" s="260">
         <f>IFERROR(I77/F77,0)</f>
-        <v>0.91713</v>
+        <v/>
       </c>
       <c r="K77" s="254" t="n"/>
       <c r="L77" s="261" t="inlineStr">
@@ -14346,7 +14379,7 @@
       <c r="Q77" s="292" t="n"/>
       <c r="R77" s="311">
         <f>IFERROR(D77*$T$7,0)</f>
-        <v>78.93</v>
+        <v/>
       </c>
       <c r="S77" s="292" t="n"/>
       <c r="T77" s="292" t="n"/>
@@ -14384,22 +14417,22 @@
       </c>
       <c r="F78" s="38">
         <f>IFERROR(D78+E78+G78+U78+Y78,0)</f>
-        <v>4705.0</v>
+        <v/>
       </c>
       <c r="G78" s="272" t="n">
         <v>390</v>
       </c>
       <c r="H78" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B78,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B78+1))</f>
-        <v>1993.0</v>
+        <v/>
       </c>
       <c r="I78" s="274">
         <f>IFERROR(F78-H78,0)</f>
-        <v>2712.0</v>
+        <v/>
       </c>
       <c r="J78" s="275">
         <f>IFERROR(I78/F78,0)</f>
-        <v>0.576408</v>
+        <v/>
       </c>
       <c r="K78" s="250" t="n"/>
       <c r="L78" s="276" t="inlineStr">
@@ -14414,7 +14447,7 @@
       <c r="Q78" s="324" t="n"/>
       <c r="R78" s="327">
         <f>IFERROR(D78*$T$7,0)</f>
-        <v>101.5</v>
+        <v/>
       </c>
       <c r="S78" s="324" t="n"/>
       <c r="T78" s="324" t="n"/>
@@ -14452,22 +14485,22 @@
       </c>
       <c r="F79" s="50">
         <f>IFERROR(D79+E79+G79+U79+Y79,0)</f>
-        <v>3738.0</v>
+        <v/>
       </c>
       <c r="G79" s="257" t="n">
         <v>225</v>
       </c>
       <c r="H79" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B79,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B79+1))</f>
-        <v>7208.0</v>
+        <v/>
       </c>
       <c r="I79" s="259">
         <f>IFERROR(F79-H79,0)</f>
-        <v>-3470.0</v>
+        <v/>
       </c>
       <c r="J79" s="260">
         <f>IFERROR(I79/F79,0)</f>
-        <v>-0.928304</v>
+        <v/>
       </c>
       <c r="K79" s="254" t="n"/>
       <c r="L79" s="261" t="inlineStr">
@@ -14482,7 +14515,7 @@
       <c r="Q79" s="292" t="n"/>
       <c r="R79" s="311">
         <f>IFERROR(D79*$T$7,0)</f>
-        <v>90.86</v>
+        <v/>
       </c>
       <c r="S79" s="292" t="n"/>
       <c r="T79" s="292" t="n"/>
@@ -14520,22 +14553,22 @@
       </c>
       <c r="F80" s="38">
         <f>IFERROR(D80+E80+G80+U80+Y80,0)</f>
-        <v>4360.0</v>
+        <v/>
       </c>
       <c r="G80" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H80" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B80,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B80+1))</f>
-        <v>1008.0</v>
+        <v/>
       </c>
       <c r="I80" s="274">
         <f>IFERROR(F80-H80,0)</f>
-        <v>3352.0</v>
+        <v/>
       </c>
       <c r="J80" s="275">
         <f>IFERROR(I80/F80,0)</f>
-        <v>0.768807</v>
+        <v/>
       </c>
       <c r="K80" s="250" t="n"/>
       <c r="L80" s="276" t="inlineStr">
@@ -14550,7 +14583,7 @@
       <c r="Q80" s="324" t="n"/>
       <c r="R80" s="428">
         <f>IFERROR(D80*$T$7,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S80" s="324" t="n"/>
       <c r="T80" s="324" t="n"/>
@@ -14588,22 +14621,22 @@
       </c>
       <c r="F81" s="50">
         <f>IFERROR(D81+E81+G81+U81+Y81,0)</f>
-        <v>3775.0</v>
+        <v/>
       </c>
       <c r="G81" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H81" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B81,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B81+1))</f>
-        <v>28989.04</v>
+        <v/>
       </c>
       <c r="I81" s="259">
         <f>IFERROR(F81-H81,0)</f>
-        <v>-25214.04</v>
+        <v/>
       </c>
       <c r="J81" s="260">
         <f>IFERROR(I81/F81,0)</f>
-        <v>-6.679216</v>
+        <v/>
       </c>
       <c r="K81" s="254" t="n"/>
       <c r="L81" s="261" t="inlineStr">
@@ -14618,7 +14651,7 @@
       <c r="Q81" s="292" t="n"/>
       <c r="R81" s="443">
         <f>IFERROR(D81*$T$7,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S81" s="292" t="n"/>
       <c r="T81" s="292" t="n"/>
@@ -14656,22 +14689,22 @@
       </c>
       <c r="F82" s="38">
         <f>IFERROR(D82+E82+G82+U82+Y82,0)</f>
-        <v>5165.0</v>
+        <v/>
       </c>
       <c r="G82" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H82" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B82,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B82+1))</f>
-        <v>1445.0</v>
+        <v/>
       </c>
       <c r="I82" s="274">
         <f>IFERROR(F82-H82,0)</f>
-        <v>3720.0</v>
+        <v/>
       </c>
       <c r="J82" s="275">
         <f>IFERROR(I82/F82,0)</f>
-        <v>0.720232</v>
+        <v/>
       </c>
       <c r="K82" s="250" t="n"/>
       <c r="L82" s="276" t="inlineStr">
@@ -14686,7 +14719,7 @@
       <c r="Q82" s="324" t="n"/>
       <c r="R82" s="428">
         <f>IFERROR(D82*$T$7,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S82" s="324" t="n"/>
       <c r="T82" s="324" t="n"/>
@@ -14724,22 +14757,22 @@
       </c>
       <c r="F83" s="50">
         <f>IFERROR(D83+E83+G83+U83+Y83,0)</f>
-        <v>3765.0</v>
+        <v/>
       </c>
       <c r="G83" s="257" t="n">
         <v>130</v>
       </c>
       <c r="H83" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B83,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B83+1))</f>
-        <v>2372.0</v>
+        <v/>
       </c>
       <c r="I83" s="259">
         <f>IFERROR(F83-H83,0)</f>
-        <v>1393.0</v>
+        <v/>
       </c>
       <c r="J83" s="260">
         <f>IFERROR(I83/F83,0)</f>
-        <v>0.369987</v>
+        <v/>
       </c>
       <c r="K83" s="254" t="n"/>
       <c r="L83" s="261" t="inlineStr">
@@ -14754,7 +14787,7 @@
       <c r="Q83" s="292" t="n"/>
       <c r="R83" s="443">
         <f>IFERROR(D83*$T$7,0)</f>
-        <v>5.28</v>
+        <v/>
       </c>
       <c r="S83" s="292" t="n"/>
       <c r="T83" s="292" t="n"/>
@@ -14792,22 +14825,22 @@
       </c>
       <c r="F84" s="38">
         <f>IFERROR(D84+E84+G84+U84+Y84,0)</f>
-        <v>6725.0</v>
+        <v/>
       </c>
       <c r="G84" s="272" t="n">
         <v>130</v>
       </c>
       <c r="H84" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B84,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B84+1))</f>
-        <v>2152.0</v>
+        <v/>
       </c>
       <c r="I84" s="274">
         <f>IFERROR(F84-H84,0)</f>
-        <v>4573.0</v>
+        <v/>
       </c>
       <c r="J84" s="275">
         <f>IFERROR(I84/F84,0)</f>
-        <v>0.68</v>
+        <v/>
       </c>
       <c r="K84" s="250" t="n"/>
       <c r="L84" s="276" t="inlineStr">
@@ -14822,7 +14855,7 @@
       <c r="Q84" s="324" t="n"/>
       <c r="R84" s="428">
         <f>IFERROR(D84*$T$7,0)</f>
-        <v>4.67</v>
+        <v/>
       </c>
       <c r="S84" s="324" t="n"/>
       <c r="T84" s="324" t="n"/>
@@ -14860,22 +14893,22 @@
       </c>
       <c r="F85" s="50">
         <f>IFERROR(D85+E85+G85+U85+Y85,0)</f>
-        <v>2410.0</v>
+        <v/>
       </c>
       <c r="G85" s="257" t="n">
         <v>135</v>
       </c>
       <c r="H85" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B85,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B85+1))</f>
-        <v>7943.0</v>
+        <v/>
       </c>
       <c r="I85" s="259">
         <f>IFERROR(F85-H85,0)</f>
-        <v>-5533.0</v>
+        <v/>
       </c>
       <c r="J85" s="260">
         <f>IFERROR(I85/F85,0)</f>
-        <v>-2.295851</v>
+        <v/>
       </c>
       <c r="K85" s="254" t="n"/>
       <c r="L85" s="261" t="inlineStr">
@@ -14890,7 +14923,7 @@
       <c r="Q85" s="292" t="n"/>
       <c r="R85" s="443">
         <f>IFERROR(D85*$T$7,0)</f>
-        <v>17.05</v>
+        <v/>
       </c>
       <c r="S85" s="292" t="n"/>
       <c r="T85" s="292" t="n"/>
@@ -14928,22 +14961,22 @@
       </c>
       <c r="F86" s="38">
         <f>IFERROR(D86+E86+G86+U86+Y86,0)</f>
-        <v>6540.0</v>
+        <v/>
       </c>
       <c r="G86" s="272" t="n">
         <v>130</v>
       </c>
       <c r="H86" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B86,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B86+1))</f>
-        <v>1138.0</v>
+        <v/>
       </c>
       <c r="I86" s="274">
         <f>IFERROR(F86-H86,0)</f>
-        <v>5402.0</v>
+        <v/>
       </c>
       <c r="J86" s="275">
         <f>IFERROR(I86/F86,0)</f>
-        <v>0.825994</v>
+        <v/>
       </c>
       <c r="K86" s="250" t="n"/>
       <c r="L86" s="276" t="inlineStr">
@@ -14958,7 +14991,7 @@
       <c r="Q86" s="324" t="n"/>
       <c r="R86" s="428">
         <f>IFERROR(D86*$T$7,0)</f>
-        <v>2.64</v>
+        <v/>
       </c>
       <c r="S86" s="324" t="n"/>
       <c r="T86" s="324" t="n"/>
@@ -14980,33 +15013,72 @@
       <c r="AB86" s="324" t="n"/>
     </row>
     <row r="87" ht="16.5" customHeight="1" s="331">
-      <c r="B87" s="34" t="n"/>
-      <c r="C87" s="47" t="n"/>
-      <c r="D87" s="48" t="n"/>
-      <c r="E87" s="49" t="n"/>
-      <c r="F87" s="50" t="n"/>
-      <c r="G87" s="51" t="n"/>
-      <c r="H87" s="52" t="n"/>
-      <c r="I87" s="53" t="n"/>
-      <c r="J87" s="54" t="n"/>
-      <c r="K87" s="55" t="n"/>
-      <c r="L87" s="18" t="n"/>
-      <c r="M87" s="21" t="n"/>
-      <c r="N87" s="56" t="n"/>
-      <c r="O87" s="57" t="n"/>
-      <c r="P87" s="58" t="n"/>
-      <c r="Q87" s="56" t="n"/>
-      <c r="R87" s="56" t="n"/>
-      <c r="S87" s="56" t="n"/>
-      <c r="T87" s="56" t="n"/>
-      <c r="U87" s="56" t="n"/>
-      <c r="V87" s="56" t="n"/>
-      <c r="W87" s="56" t="n"/>
-      <c r="X87" s="56" t="n"/>
-      <c r="Y87" s="56" t="n"/>
-      <c r="Z87" s="56" t="n"/>
-      <c r="AA87" s="56" t="n"/>
-      <c r="AB87" s="56" t="n"/>
+      <c r="B87" s="427" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C87" s="255" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D87" s="256" t="n">
+        <v>240</v>
+      </c>
+      <c r="E87" s="49" t="n">
+        <v>2880</v>
+      </c>
+      <c r="F87" s="50">
+        <f>IFERROR(D87+E87+G87+U87+Y87,0)</f>
+        <v/>
+      </c>
+      <c r="G87" s="257" t="n">
+        <v>655</v>
+      </c>
+      <c r="H87" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B87,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B87+1))</f>
+        <v/>
+      </c>
+      <c r="I87" s="259">
+        <f>IFERROR(F87-H87,0)</f>
+        <v/>
+      </c>
+      <c r="J87" s="260">
+        <f>IFERROR(I87/F87,0)</f>
+        <v/>
+      </c>
+      <c r="K87" s="254" t="n"/>
+      <c r="L87" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M87" s="291" t="n"/>
+      <c r="N87" s="292" t="n"/>
+      <c r="O87" s="293" t="n"/>
+      <c r="P87" s="294" t="n"/>
+      <c r="Q87" s="292" t="n"/>
+      <c r="R87" s="443">
+        <f>IFERROR(D87*$T$7,0)</f>
+        <v/>
+      </c>
+      <c r="S87" s="292" t="n"/>
+      <c r="T87" s="292" t="n"/>
+      <c r="U87" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" s="292" t="n"/>
+      <c r="X87" s="292" t="n"/>
+      <c r="Y87" s="443" t="n">
+        <v>930</v>
+      </c>
+      <c r="Z87" s="443" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="AA87" s="292" t="n"/>
+      <c r="AB87" s="292" t="n"/>
     </row>
     <row r="88" ht="16.5" customHeight="1" s="331">
       <c r="B88" s="34" t="n"/>
@@ -23275,9 +23347,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I2:P2"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B5:P5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:P2"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -23300,7 +23372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J613"/>
+  <dimension ref="A1:J619"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -49162,6 +49234,264 @@
       <c r="J613" s="423" t="inlineStr">
         <is>
           <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="B614" s="429" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C614" s="297" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="D614" s="298" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E614" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F614" s="299" t="n">
+        <v>60</v>
+      </c>
+      <c r="G614" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H614" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I614" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J614" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="B615" s="429" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C615" s="297" t="inlineStr">
+        <is>
+          <t>Vegetales</t>
+        </is>
+      </c>
+      <c r="D615" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E615" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F615" s="299" t="n">
+        <v>49</v>
+      </c>
+      <c r="G615" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H615" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I615" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J615" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="B616" s="429" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C616" s="297" t="inlineStr">
+        <is>
+          <t>Pan Reales</t>
+        </is>
+      </c>
+      <c r="D616" s="298" t="inlineStr">
+        <is>
+          <t>Pan Reales</t>
+        </is>
+      </c>
+      <c r="E616" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F616" s="299" t="n">
+        <v>429</v>
+      </c>
+      <c r="G616" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H616" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I616" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J616" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="B617" s="429" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C617" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D617" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E617" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F617" s="299" t="n">
+        <v>359</v>
+      </c>
+      <c r="G617" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H617" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I617" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J617" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="B618" s="429" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C618" s="297" t="inlineStr">
+        <is>
+          <t>OXXO Aceite</t>
+        </is>
+      </c>
+      <c r="D618" s="298" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E618" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F618" s="299" t="n">
+        <v>336</v>
+      </c>
+      <c r="G618" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H618" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I618" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J618" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="B619" s="429" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C619" s="297" t="inlineStr">
+        <is>
+          <t>Guimar Cuchillos</t>
+        </is>
+      </c>
+      <c r="D619" s="298" t="inlineStr">
+        <is>
+          <t>Guimar Polietilenos</t>
+        </is>
+      </c>
+      <c r="E619" s="297" t="inlineStr">
+        <is>
+          <t>Kitchen Supplies</t>
+        </is>
+      </c>
+      <c r="F619" s="299" t="n">
+        <v>100</v>
+      </c>
+      <c r="G619" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H619" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I619" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J619" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
         </is>
       </c>
     </row>
@@ -54684,16 +55014,32 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="263" t="n"/>
-      <c r="B84" s="262" t="n"/>
+      <c r="A84" s="263" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B84" s="262" t="inlineStr">
+        <is>
+          <t>John (week 11)</t>
+        </is>
+      </c>
       <c r="C84" s="262" t="n"/>
-      <c r="D84" s="264" t="n"/>
+      <c r="D84" s="264" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="263" t="n"/>
-      <c r="B85" s="262" t="n"/>
+      <c r="A85" s="263" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B85" s="262" t="inlineStr">
+        <is>
+          <t>Samu (week 11)</t>
+        </is>
+      </c>
       <c r="C85" s="262" t="n"/>
-      <c r="D85" s="264" t="n"/>
+      <c r="D85" s="264" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="263" t="n"/>
@@ -59195,15 +59541,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="331">
-      <c r="A1" s="431" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>LOKA — MONTHLY P&amp;L   (live formulas — auto-updates from Daily Log &amp; Expenses)</t>
         </is>
       </c>
-      <c r="B1" s="432" t="n"/>
-      <c r="C1" s="432" t="n"/>
-      <c r="D1" s="432" t="n"/>
-      <c r="E1" s="432" t="n"/>
+      <c r="B1" s="423" t="n"/>
+      <c r="C1" s="423" t="n"/>
+      <c r="D1" s="423" t="n"/>
+      <c r="E1" s="423" t="n"/>
       <c r="F1" s="433" t="n"/>
       <c r="G1" s="433" t="n"/>
       <c r="H1" s="433" t="n"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="C147" s="268" t="n">
-        <v>32415.85</v>
+        <v>20911.85</v>
       </c>
       <c r="E147" s="286" t="inlineStr">
         <is>
@@ -5516,11 +5516,11 @@
         </is>
       </c>
       <c r="C149" s="444" t="n">
-        <v>-32888</v>
+        <v>-44392</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Cumulative repaid from operating cash (latest 04-Aug-2026 $10,301.00). Reduces advance owed &amp; Cash-on-Hand; NOT a P&amp;L expense.</t>
+          <t>Cumulative repaid from operating cash (latest 13-Aug-2026 $11,504.00). Reduces advance owed &amp; Cash-on-Hand; NOT a P&amp;L expense.</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="331" min="1" max="1"/>
@@ -8060,30 +8060,96 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="430" t="inlineStr">
+      <c r="A66" s="430" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B66" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 12-Aug)</t>
+        </is>
+      </c>
+      <c r="C66" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D66" s="232" t="n"/>
+      <c r="E66" s="233" t="n">
+        <v>130</v>
+      </c>
+      <c r="F66" s="233">
+        <f>IFERROR(F65+D66-E66,0)</f>
+        <v/>
+      </c>
+      <c r="G66" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H66" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="430" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B67" s="232" t="inlineStr">
+        <is>
+          <t>Pollo $639 (paid by Lohith)</t>
+        </is>
+      </c>
+      <c r="C67" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D67" s="232" t="n">
+        <v>639</v>
+      </c>
+      <c r="E67" s="233" t="n"/>
+      <c r="F67" s="233">
+        <f>IFERROR(F66+D67-E67,0)</f>
+        <v/>
+      </c>
+      <c r="G67" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H67" s="232" t="inlineStr">
+        <is>
+          <t>Fronted from own pocket; excluded from till via cash_adjust</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="430" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B66" s="232" t="n"/>
-      <c r="C66" s="232" t="n"/>
-      <c r="D66" s="232">
-        <f>SUM(D4:D65)</f>
-        <v/>
-      </c>
-      <c r="E66" s="233">
-        <f>SUM(E4:E65)</f>
-        <v/>
-      </c>
-      <c r="F66" s="233">
-        <f>F65</f>
-        <v/>
-      </c>
-      <c r="G66" s="232">
-        <f>IF(F65&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F65,"#,##0"),IF(F65&lt;0,"Lohith holds $"&amp;TEXT(ABS(F65),"#,##0"),"Zero balance"))</f>
-        <v/>
-      </c>
-      <c r="H66" s="232" t="n"/>
+      <c r="B68" s="232" t="n"/>
+      <c r="C68" s="232" t="n"/>
+      <c r="D68" s="232">
+        <f>SUM(D4:D67)</f>
+        <v/>
+      </c>
+      <c r="E68" s="233">
+        <f>SUM(E4:E67)</f>
+        <v/>
+      </c>
+      <c r="F68" s="233">
+        <f>F67</f>
+        <v/>
+      </c>
+      <c r="G68" s="232">
+        <f>IF(F67&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F67,"#,##0"),IF(F67&lt;0,"Lohith holds $"&amp;TEXT(ABS(F67),"#,##0"),"Zero balance"))</f>
+        <v/>
+      </c>
+      <c r="H68" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9917,45 +9983,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v/>
+        <v>2790.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v/>
+        <v>130.0</v>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v/>
+        <v>5043.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v/>
+        <v>-2253.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v/>
+        <v>-0.807527</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v/>
+        <v>14035.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v/>
+        <v>14035.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v/>
+        <v>43973.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v/>
+        <v>7514.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v/>
+        <v>6521.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -10106,20 +10172,20 @@
       </c>
       <c r="F8" s="38">
         <f>IFERROR(D8+E8+G8,0)</f>
-        <v/>
+        <v>3689.0</v>
       </c>
       <c r="G8" s="39" t="n"/>
       <c r="H8" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B8,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B8+1))</f>
-        <v/>
+        <v>2629.0</v>
       </c>
       <c r="I8" s="41">
         <f>IFERROR(F8-H8,0)</f>
-        <v/>
+        <v>1060.0</v>
       </c>
       <c r="J8" s="42">
         <f>IFERROR(I8/F8,0)</f>
-        <v/>
+        <v>0.287341</v>
       </c>
       <c r="K8" s="43" t="n"/>
       <c r="L8" s="9" t="inlineStr">
@@ -10134,7 +10200,7 @@
       <c r="Q8" s="44" t="n"/>
       <c r="R8" s="44">
         <f>IFERROR(D8*$T$7,0)</f>
-        <v/>
+        <v>90.5</v>
       </c>
       <c r="S8" s="44" t="n"/>
       <c r="T8" s="44" t="n"/>
@@ -10164,20 +10230,20 @@
       </c>
       <c r="F9" s="50">
         <f>IFERROR(D9+E9+G9,0)</f>
-        <v/>
+        <v>3854.0</v>
       </c>
       <c r="G9" s="51" t="n"/>
       <c r="H9" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B9,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B9+1))</f>
-        <v/>
+        <v>30.0</v>
       </c>
       <c r="I9" s="53">
         <f>IFERROR(F9-H9,0)</f>
-        <v/>
+        <v>3824.0</v>
       </c>
       <c r="J9" s="54">
         <f>IFERROR(I9/F9,0)</f>
-        <v/>
+        <v>0.992216</v>
       </c>
       <c r="K9" s="55" t="n"/>
       <c r="L9" s="18" t="inlineStr">
@@ -10192,7 +10258,7 @@
       <c r="Q9" s="56" t="n"/>
       <c r="R9" s="56">
         <f>IFERROR(D9*$T$7,0)</f>
-        <v/>
+        <v>86.27</v>
       </c>
       <c r="S9" s="56" t="n"/>
       <c r="T9" s="56" t="n"/>
@@ -10222,20 +10288,20 @@
       </c>
       <c r="F10" s="38">
         <f>IFERROR(D10+E10+G10,0)</f>
-        <v/>
+        <v>4124.0</v>
       </c>
       <c r="G10" s="39" t="n"/>
       <c r="H10" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B10,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B10+1))</f>
-        <v/>
+        <v>3777.0</v>
       </c>
       <c r="I10" s="41">
         <f>IFERROR(F10-H10,0)</f>
-        <v/>
+        <v>347.0</v>
       </c>
       <c r="J10" s="42">
         <f>IFERROR(I10/F10,0)</f>
-        <v/>
+        <v>0.084142</v>
       </c>
       <c r="K10" s="43" t="n"/>
       <c r="L10" s="9" t="inlineStr">
@@ -10250,7 +10316,7 @@
       <c r="Q10" s="44" t="n"/>
       <c r="R10" s="44">
         <f>IFERROR(D10*$T$7,0)</f>
-        <v/>
+        <v>59.24</v>
       </c>
       <c r="S10" s="44" t="n"/>
       <c r="T10" s="44" t="n"/>
@@ -10280,20 +10346,20 @@
       </c>
       <c r="F11" s="50">
         <f>IFERROR(D11+E11+G11,0)</f>
-        <v/>
+        <v>4733.0</v>
       </c>
       <c r="G11" s="51" t="n"/>
       <c r="H11" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B11,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B11+1))</f>
-        <v/>
+        <v>2434.0</v>
       </c>
       <c r="I11" s="53">
         <f>IFERROR(F11-H11,0)</f>
-        <v/>
+        <v>2299.0</v>
       </c>
       <c r="J11" s="54">
         <f>IFERROR(I11/F11,0)</f>
-        <v/>
+        <v>0.485738</v>
       </c>
       <c r="K11" s="55" t="n"/>
       <c r="L11" s="18" t="inlineStr">
@@ -10308,7 +10374,7 @@
       <c r="Q11" s="56" t="n"/>
       <c r="R11" s="56">
         <f>IFERROR(D11*$T$7,0)</f>
-        <v/>
+        <v>104.34</v>
       </c>
       <c r="S11" s="56" t="n"/>
       <c r="T11" s="56" t="n"/>
@@ -10338,20 +10404,20 @@
       </c>
       <c r="F12" s="38">
         <f>IFERROR(D12+E12+G12,0)</f>
-        <v/>
+        <v>4282.0</v>
       </c>
       <c r="G12" s="39" t="n"/>
       <c r="H12" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B12,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B12+1))</f>
-        <v/>
+        <v>1457.0</v>
       </c>
       <c r="I12" s="41">
         <f>IFERROR(F12-H12,0)</f>
-        <v/>
+        <v>2825.0</v>
       </c>
       <c r="J12" s="42">
         <f>IFERROR(I12/F12,0)</f>
-        <v/>
+        <v>0.659738</v>
       </c>
       <c r="K12" s="43" t="n"/>
       <c r="L12" s="9" t="inlineStr">
@@ -10366,7 +10432,7 @@
       <c r="Q12" s="44" t="n"/>
       <c r="R12" s="44">
         <f>IFERROR(D12*$T$7,0)</f>
-        <v/>
+        <v>79.54</v>
       </c>
       <c r="S12" s="44" t="n"/>
       <c r="T12" s="44" t="n"/>
@@ -10396,20 +10462,20 @@
       </c>
       <c r="F13" s="50">
         <f>IFERROR(D13+E13+G13,0)</f>
-        <v/>
+        <v>3802.0</v>
       </c>
       <c r="G13" s="51" t="n"/>
       <c r="H13" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B13,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B13+1))</f>
-        <v/>
+        <v>7755.43</v>
       </c>
       <c r="I13" s="53">
         <f>IFERROR(F13-H13,0)</f>
-        <v/>
+        <v>-3953.43</v>
       </c>
       <c r="J13" s="54">
         <f>IFERROR(I13/F13,0)</f>
-        <v/>
+        <v>-1.039829</v>
       </c>
       <c r="K13" s="55" t="inlineStr">
         <is>
@@ -10428,7 +10494,7 @@
       <c r="Q13" s="56" t="n"/>
       <c r="R13" s="56">
         <f>IFERROR(D13*$T$7,0)</f>
-        <v/>
+        <v>82.99</v>
       </c>
       <c r="S13" s="56" t="n"/>
       <c r="T13" s="56" t="n"/>
@@ -10456,20 +10522,20 @@
       </c>
       <c r="F14" s="38">
         <f>IFERROR(D14+E14+G14,0)</f>
-        <v/>
+        <v>1198.0</v>
       </c>
       <c r="G14" s="39" t="n"/>
       <c r="H14" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B14,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B14+1))</f>
-        <v/>
+        <v>1076.0</v>
       </c>
       <c r="I14" s="41">
         <f>IFERROR(F14-H14,0)</f>
-        <v/>
+        <v>122.0</v>
       </c>
       <c r="J14" s="42">
         <f>IFERROR(I14/F14,0)</f>
-        <v/>
+        <v>0.101836</v>
       </c>
       <c r="K14" s="43" t="inlineStr">
         <is>
@@ -10488,7 +10554,7 @@
       <c r="Q14" s="44" t="n"/>
       <c r="R14" s="44">
         <f>IFERROR(D14*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S14" s="44" t="n"/>
       <c r="T14" s="44" t="n"/>
@@ -10518,20 +10584,20 @@
       </c>
       <c r="F15" s="50">
         <f>IFERROR(D15+E15+G15,0)</f>
-        <v/>
+        <v>3730.0</v>
       </c>
       <c r="G15" s="51" t="n"/>
       <c r="H15" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B15,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B15+1))</f>
-        <v/>
+        <v>3021.45</v>
       </c>
       <c r="I15" s="53">
         <f>IFERROR(F15-H15,0)</f>
-        <v/>
+        <v>708.55</v>
       </c>
       <c r="J15" s="54">
         <f>IFERROR(I15/F15,0)</f>
-        <v/>
+        <v>0.18996</v>
       </c>
       <c r="K15" s="55" t="n"/>
       <c r="L15" s="18" t="inlineStr">
@@ -10546,7 +10612,7 @@
       <c r="Q15" s="56" t="n"/>
       <c r="R15" s="56">
         <f>IFERROR(D15*$T$7,0)</f>
-        <v/>
+        <v>85.5</v>
       </c>
       <c r="S15" s="56" t="n"/>
       <c r="T15" s="56" t="n"/>
@@ -10576,20 +10642,20 @@
       </c>
       <c r="F16" s="38">
         <f>IFERROR(D16+E16+G16,0)</f>
-        <v/>
+        <v>4264.0</v>
       </c>
       <c r="G16" s="39" t="n"/>
       <c r="H16" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B16,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B16+1))</f>
-        <v/>
+        <v>1191.6</v>
       </c>
       <c r="I16" s="41">
         <f>IFERROR(F16-H16,0)</f>
-        <v/>
+        <v>3072.4</v>
       </c>
       <c r="J16" s="42">
         <f>IFERROR(I16/F16,0)</f>
-        <v/>
+        <v>0.720544</v>
       </c>
       <c r="K16" s="43" t="n"/>
       <c r="L16" s="9" t="inlineStr">
@@ -10604,7 +10670,7 @@
       <c r="Q16" s="44" t="n"/>
       <c r="R16" s="44">
         <f>IFERROR(D16*$T$7,0)</f>
-        <v/>
+        <v>77.51</v>
       </c>
       <c r="S16" s="44" t="n"/>
       <c r="T16" s="44" t="n"/>
@@ -10634,20 +10700,20 @@
       </c>
       <c r="F17" s="50">
         <f>IFERROR(D17+E17+G17,0)</f>
-        <v/>
+        <v>3621.0</v>
       </c>
       <c r="G17" s="51" t="n"/>
       <c r="H17" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B17,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B17+1))</f>
-        <v/>
+        <v>1073.22</v>
       </c>
       <c r="I17" s="53">
         <f>IFERROR(F17-H17,0)</f>
-        <v/>
+        <v>2547.78</v>
       </c>
       <c r="J17" s="54">
         <f>IFERROR(I17/F17,0)</f>
-        <v/>
+        <v>0.703612</v>
       </c>
       <c r="K17" s="55" t="n"/>
       <c r="L17" s="18" t="inlineStr">
@@ -10662,7 +10728,7 @@
       <c r="Q17" s="56" t="n"/>
       <c r="R17" s="56">
         <f>IFERROR(D17*$T$7,0)</f>
-        <v/>
+        <v>79.41</v>
       </c>
       <c r="S17" s="56" t="n"/>
       <c r="T17" s="56" t="n"/>
@@ -10692,20 +10758,20 @@
       </c>
       <c r="F18" s="38">
         <f>IFERROR(D18+E18+G18,0)</f>
-        <v/>
+        <v>4070.0</v>
       </c>
       <c r="G18" s="39" t="n"/>
       <c r="H18" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B18,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B18+1))</f>
-        <v/>
+        <v>1931.34</v>
       </c>
       <c r="I18" s="41">
         <f>IFERROR(F18-H18,0)</f>
-        <v/>
+        <v>2138.66</v>
       </c>
       <c r="J18" s="42">
         <f>IFERROR(I18/F18,0)</f>
-        <v/>
+        <v>0.525469</v>
       </c>
       <c r="K18" s="43" t="n"/>
       <c r="L18" s="9" t="inlineStr">
@@ -10720,7 +10786,7 @@
       <c r="Q18" s="44" t="n"/>
       <c r="R18" s="44">
         <f>IFERROR(D18*$T$7,0)</f>
-        <v/>
+        <v>60.94</v>
       </c>
       <c r="S18" s="44" t="n"/>
       <c r="T18" s="44" t="n"/>
@@ -10750,20 +10816,20 @@
       </c>
       <c r="F19" s="50">
         <f>IFERROR(D19+E19+G19,0)</f>
-        <v/>
+        <v>6086.0</v>
       </c>
       <c r="G19" s="51" t="n"/>
       <c r="H19" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B19,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B19+1))</f>
-        <v/>
+        <v>257.29</v>
       </c>
       <c r="I19" s="53">
         <f>IFERROR(F19-H19,0)</f>
-        <v/>
+        <v>5828.71</v>
       </c>
       <c r="J19" s="54">
         <f>IFERROR(I19/F19,0)</f>
-        <v/>
+        <v>0.957724</v>
       </c>
       <c r="K19" s="55" t="n"/>
       <c r="L19" s="18" t="inlineStr">
@@ -10778,7 +10844,7 @@
       <c r="Q19" s="56" t="n"/>
       <c r="R19" s="56">
         <f>IFERROR(D19*$T$7,0)</f>
-        <v/>
+        <v>136.78</v>
       </c>
       <c r="S19" s="56" t="n"/>
       <c r="T19" s="56" t="n"/>
@@ -10808,20 +10874,20 @@
       </c>
       <c r="F20" s="38">
         <f>IFERROR(D20+E20+G20,0)</f>
-        <v/>
+        <v>4603.0</v>
       </c>
       <c r="G20" s="39" t="n"/>
       <c r="H20" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B20,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B20+1))</f>
-        <v/>
+        <v>5974.3</v>
       </c>
       <c r="I20" s="41">
         <f>IFERROR(F20-H20,0)</f>
-        <v/>
+        <v>-1371.3</v>
       </c>
       <c r="J20" s="42">
         <f>IFERROR(I20/F20,0)</f>
-        <v/>
+        <v>-0.297914</v>
       </c>
       <c r="K20" s="43" t="n"/>
       <c r="L20" s="9" t="inlineStr">
@@ -10836,7 +10902,7 @@
       <c r="Q20" s="44" t="n"/>
       <c r="R20" s="44">
         <f>IFERROR(D20*$T$7,0)</f>
-        <v/>
+        <v>140.35</v>
       </c>
       <c r="S20" s="44" t="n"/>
       <c r="T20" s="44" t="n"/>
@@ -10864,20 +10930,20 @@
       </c>
       <c r="F21" s="50">
         <f>IFERROR(D21+E21+G21,0)</f>
-        <v/>
+        <v>893.0</v>
       </c>
       <c r="G21" s="51" t="n"/>
       <c r="H21" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B21,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B21+1))</f>
-        <v/>
+        <v>10312.0</v>
       </c>
       <c r="I21" s="53">
         <f>IFERROR(F21-H21,0)</f>
-        <v/>
+        <v>-9419.0</v>
       </c>
       <c r="J21" s="54">
         <f>IFERROR(I21/F21,0)</f>
-        <v/>
+        <v>-10.547592</v>
       </c>
       <c r="K21" s="55" t="n"/>
       <c r="L21" s="18" t="inlineStr">
@@ -10892,7 +10958,7 @@
       <c r="Q21" s="56" t="n"/>
       <c r="R21" s="56">
         <f>IFERROR(D21*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S21" s="56" t="n"/>
       <c r="T21" s="56" t="n"/>
@@ -10922,22 +10988,22 @@
       </c>
       <c r="F22" s="38">
         <f>IFERROR(D22+E22+G22,0)</f>
-        <v/>
+        <v>5019.0</v>
       </c>
       <c r="G22" s="39" t="n">
         <v>310</v>
       </c>
       <c r="H22" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B22,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B22+1))</f>
-        <v/>
+        <v>5329.64</v>
       </c>
       <c r="I22" s="41">
         <f>IFERROR(F22-H22,0)</f>
-        <v/>
+        <v>-310.64</v>
       </c>
       <c r="J22" s="42">
         <f>IFERROR(I22/F22,0)</f>
-        <v/>
+        <v>-0.061893</v>
       </c>
       <c r="K22" s="43" t="n"/>
       <c r="L22" s="9" t="inlineStr">
@@ -10952,7 +11018,7 @@
       <c r="Q22" s="44" t="n"/>
       <c r="R22" s="44">
         <f>IFERROR(D22*$T$7,0)</f>
-        <v/>
+        <v>139.38</v>
       </c>
       <c r="S22" s="44" t="n"/>
       <c r="T22" s="44" t="n"/>
@@ -10982,22 +11048,22 @@
       </c>
       <c r="F23" s="50">
         <f>IFERROR(D23+E23+G23,0)</f>
-        <v/>
+        <v>1843.0</v>
       </c>
       <c r="G23" s="51" t="n">
         <v>283</v>
       </c>
       <c r="H23" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B23,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B23+1))</f>
-        <v/>
+        <v>2379.11</v>
       </c>
       <c r="I23" s="53">
         <f>IFERROR(F23-H23,0)</f>
-        <v/>
+        <v>-536.11</v>
       </c>
       <c r="J23" s="54">
         <f>IFERROR(I23/F23,0)</f>
-        <v/>
+        <v>-0.29089</v>
       </c>
       <c r="K23" s="55" t="n"/>
       <c r="L23" s="18" t="inlineStr">
@@ -11012,7 +11078,7 @@
       <c r="Q23" s="56" t="n"/>
       <c r="R23" s="56">
         <f>IFERROR(D23*$T$7,0)</f>
-        <v/>
+        <v>50.34</v>
       </c>
       <c r="S23" s="56" t="n"/>
       <c r="T23" s="56" t="n"/>
@@ -11042,22 +11108,22 @@
       </c>
       <c r="F24" s="38">
         <f>IFERROR(D24+E24+G24,0)</f>
-        <v/>
+        <v>3912.0</v>
       </c>
       <c r="G24" s="39" t="n">
         <v>120</v>
       </c>
       <c r="H24" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B24,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B24+1))</f>
-        <v/>
+        <v>4211.86</v>
       </c>
       <c r="I24" s="41">
         <f>IFERROR(F24-H24,0)</f>
-        <v/>
+        <v>-299.86</v>
       </c>
       <c r="J24" s="42">
         <f>IFERROR(I24/F24,0)</f>
-        <v/>
+        <v>-0.076651</v>
       </c>
       <c r="K24" s="43" t="n"/>
       <c r="L24" s="9" t="inlineStr">
@@ -11072,7 +11138,7 @@
       <c r="Q24" s="44" t="n"/>
       <c r="R24" s="44">
         <f>IFERROR(D24*$T$7,0)</f>
-        <v/>
+        <v>75.23</v>
       </c>
       <c r="S24" s="44" t="n"/>
       <c r="T24" s="44" t="n"/>
@@ -11102,20 +11168,20 @@
       </c>
       <c r="F25" s="50">
         <f>IFERROR(D25+E25+G25,0)</f>
-        <v/>
+        <v>3757.0</v>
       </c>
       <c r="G25" s="51" t="n"/>
       <c r="H25" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B25,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B25+1))</f>
-        <v/>
+        <v>20959.96</v>
       </c>
       <c r="I25" s="53">
         <f>IFERROR(F25-H25,0)</f>
-        <v/>
+        <v>-17202.96</v>
       </c>
       <c r="J25" s="54">
         <f>IFERROR(I25/F25,0)</f>
-        <v/>
+        <v>-4.578909</v>
       </c>
       <c r="K25" s="55" t="n"/>
       <c r="L25" s="18" t="inlineStr">
@@ -11130,7 +11196,7 @@
       <c r="Q25" s="56" t="n"/>
       <c r="R25" s="56">
         <f>IFERROR(D25*$T$7,0)</f>
-        <v/>
+        <v>110.11</v>
       </c>
       <c r="S25" s="56" t="n"/>
       <c r="T25" s="56" t="n"/>
@@ -11160,22 +11226,22 @@
       </c>
       <c r="F26" s="38">
         <f>IFERROR(D26+E26+G26,0)</f>
-        <v/>
+        <v>4408.0</v>
       </c>
       <c r="G26" s="39" t="n">
         <v>135</v>
       </c>
       <c r="H26" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B26,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B26+1))</f>
-        <v/>
+        <v>878.06</v>
       </c>
       <c r="I26" s="41">
         <f>IFERROR(F26-H26,0)</f>
-        <v/>
+        <v>3529.94</v>
       </c>
       <c r="J26" s="42">
         <f>IFERROR(I26/F26,0)</f>
-        <v/>
+        <v>0.800803</v>
       </c>
       <c r="K26" s="43" t="n"/>
       <c r="L26" s="9" t="inlineStr">
@@ -11190,7 +11256,7 @@
       <c r="Q26" s="44" t="n"/>
       <c r="R26" s="44">
         <f>IFERROR(D26*$T$7,0)</f>
-        <v/>
+        <v>101.3</v>
       </c>
       <c r="S26" s="44" t="n"/>
       <c r="T26" s="44" t="n"/>
@@ -11220,20 +11286,20 @@
       </c>
       <c r="F27" s="50">
         <f>IFERROR(D27+E27+G27,0)</f>
-        <v/>
+        <v>2334.0</v>
       </c>
       <c r="G27" s="51" t="n"/>
       <c r="H27" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B27,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B27+1))</f>
-        <v/>
+        <v>5414.0</v>
       </c>
       <c r="I27" s="53">
         <f>IFERROR(F27-H27,0)</f>
-        <v/>
+        <v>-3080.0</v>
       </c>
       <c r="J27" s="54">
         <f>IFERROR(I27/F27,0)</f>
-        <v/>
+        <v>-1.319623</v>
       </c>
       <c r="K27" s="55" t="n"/>
       <c r="L27" s="18" t="inlineStr">
@@ -11248,7 +11314,7 @@
       <c r="Q27" s="56" t="n"/>
       <c r="R27" s="56">
         <f>IFERROR(D27*$T$7,0)</f>
-        <v/>
+        <v>23.55</v>
       </c>
       <c r="S27" s="56" t="n"/>
       <c r="T27" s="56" t="n"/>
@@ -11274,16 +11340,16 @@
       <c r="E28" s="37" t="n"/>
       <c r="F28" s="38">
         <f>IFERROR(D28+E28+G28,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G28" s="39" t="n"/>
       <c r="H28" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B28,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B28+1))</f>
-        <v/>
+        <v>1671.0</v>
       </c>
       <c r="I28" s="41">
         <f>IFERROR(F28-H28,0)</f>
-        <v/>
+        <v>-1671.0</v>
       </c>
       <c r="J28" s="42" t="n"/>
       <c r="K28" s="43" t="n"/>
@@ -11299,7 +11365,7 @@
       <c r="Q28" s="44" t="n"/>
       <c r="R28" s="44">
         <f>IFERROR(D28*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S28" s="44" t="n"/>
       <c r="T28" s="44" t="n"/>
@@ -11329,22 +11395,22 @@
       </c>
       <c r="F29" s="50">
         <f>IFERROR(D29+E29+G29,0)</f>
-        <v/>
+        <v>3727.0</v>
       </c>
       <c r="G29" s="51" t="n">
         <v>99</v>
       </c>
       <c r="H29" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B29,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B29+1))</f>
-        <v/>
+        <v>3187.11</v>
       </c>
       <c r="I29" s="53">
         <f>IFERROR(F29-H29,0)</f>
-        <v/>
+        <v>539.89</v>
       </c>
       <c r="J29" s="54">
         <f>IFERROR(I29/F29,0)</f>
-        <v/>
+        <v>0.144859</v>
       </c>
       <c r="K29" s="55" t="n"/>
       <c r="L29" s="18" t="inlineStr">
@@ -11359,7 +11425,7 @@
       <c r="Q29" s="56" t="n"/>
       <c r="R29" s="56">
         <f>IFERROR(D29*$T$7,0)</f>
-        <v/>
+        <v>72.19</v>
       </c>
       <c r="S29" s="56" t="n"/>
       <c r="T29" s="56" t="n"/>
@@ -11389,20 +11455,20 @@
       </c>
       <c r="F30" s="38">
         <f>IFERROR(D30+E30+G30,0)</f>
-        <v/>
+        <v>5410.0</v>
       </c>
       <c r="G30" s="39" t="n"/>
       <c r="H30" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B30,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B30+1))</f>
-        <v/>
+        <v>6623.98</v>
       </c>
       <c r="I30" s="41">
         <f>IFERROR(F30-H30,0)</f>
-        <v/>
+        <v>-1213.98</v>
       </c>
       <c r="J30" s="42">
         <f>IFERROR(I30/F30,0)</f>
-        <v/>
+        <v>-0.224396</v>
       </c>
       <c r="K30" s="43" t="n"/>
       <c r="L30" s="9" t="inlineStr">
@@ -11417,7 +11483,7 @@
       <c r="Q30" s="44" t="n"/>
       <c r="R30" s="44">
         <f>IFERROR(D30*$T$7,0)</f>
-        <v/>
+        <v>37.76</v>
       </c>
       <c r="S30" s="44" t="n"/>
       <c r="T30" s="44" t="n"/>
@@ -11447,20 +11513,20 @@
       </c>
       <c r="F31" s="50">
         <f>IFERROR(D31+E31+G31,0)</f>
-        <v/>
+        <v>4265.0</v>
       </c>
       <c r="G31" s="51" t="n"/>
       <c r="H31" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B31,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B31+1))</f>
-        <v/>
+        <v>1341.81</v>
       </c>
       <c r="I31" s="53">
         <f>IFERROR(F31-H31,0)</f>
-        <v/>
+        <v>2923.19</v>
       </c>
       <c r="J31" s="54">
         <f>IFERROR(I31/F31,0)</f>
-        <v/>
+        <v>0.68539</v>
       </c>
       <c r="K31" s="55" t="n"/>
       <c r="L31" s="18" t="inlineStr">
@@ -11475,7 +11541,7 @@
       <c r="Q31" s="56" t="n"/>
       <c r="R31" s="56">
         <f>IFERROR(D31*$T$7,0)</f>
-        <v/>
+        <v>101.74</v>
       </c>
       <c r="S31" s="56" t="n"/>
       <c r="T31" s="56" t="n"/>
@@ -11505,22 +11571,22 @@
       </c>
       <c r="F32" s="38">
         <f>IFERROR(D32+E32+G32,0)</f>
-        <v/>
+        <v>4166.0</v>
       </c>
       <c r="G32" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B32,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B32+1))</f>
-        <v/>
+        <v>4044.0</v>
       </c>
       <c r="I32" s="41">
         <f>IFERROR(F32-H32,0)</f>
-        <v/>
+        <v>122.0</v>
       </c>
       <c r="J32" s="42">
         <f>IFERROR(I32/F32,0)</f>
-        <v/>
+        <v>0.029285</v>
       </c>
       <c r="K32" s="43" t="n"/>
       <c r="L32" s="9" t="inlineStr">
@@ -11535,7 +11601,7 @@
       <c r="Q32" s="44" t="n"/>
       <c r="R32" s="44">
         <f>IFERROR(D32*$T$7,0)</f>
-        <v/>
+        <v>84.24</v>
       </c>
       <c r="S32" s="44" t="n"/>
       <c r="T32" s="44" t="n"/>
@@ -11565,22 +11631,22 @@
       </c>
       <c r="F33" s="50">
         <f>IFERROR(D33+E33+G33,0)</f>
-        <v/>
+        <v>6070.0</v>
       </c>
       <c r="G33" s="51" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B33,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B33+1))</f>
-        <v/>
+        <v>901.8</v>
       </c>
       <c r="I33" s="53">
         <f>IFERROR(F33-H33,0)</f>
-        <v/>
+        <v>5168.2</v>
       </c>
       <c r="J33" s="54">
         <f>IFERROR(I33/F33,0)</f>
-        <v/>
+        <v>0.851433</v>
       </c>
       <c r="K33" s="55" t="n"/>
       <c r="L33" s="18" t="inlineStr">
@@ -11595,7 +11661,7 @@
       <c r="Q33" s="56" t="n"/>
       <c r="R33" s="56">
         <f>IFERROR(D33*$T$7,0)</f>
-        <v/>
+        <v>106.98</v>
       </c>
       <c r="S33" s="56" t="n"/>
       <c r="T33" s="56" t="n"/>
@@ -11625,22 +11691,22 @@
       </c>
       <c r="F34" s="38">
         <f>IFERROR(D34+E34+G34,0)</f>
-        <v/>
+        <v>1811.0</v>
       </c>
       <c r="G34" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B34,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B34+1))</f>
-        <v/>
+        <v>8084.16</v>
       </c>
       <c r="I34" s="41">
         <f>IFERROR(F34-H34,0)</f>
-        <v/>
+        <v>-6273.16</v>
       </c>
       <c r="J34" s="42">
         <f>IFERROR(I34/F34,0)</f>
-        <v/>
+        <v>-3.46392</v>
       </c>
       <c r="K34" s="43" t="n"/>
       <c r="L34" s="9" t="inlineStr">
@@ -11655,7 +11721,7 @@
       <c r="Q34" s="44" t="n"/>
       <c r="R34" s="44">
         <f>IFERROR(D34*$T$7,0)</f>
-        <v/>
+        <v>40.8</v>
       </c>
       <c r="S34" s="44" t="n"/>
       <c r="T34" s="44" t="n"/>
@@ -11685,22 +11751,22 @@
       </c>
       <c r="F35" s="50">
         <f>IFERROR(D35+E35+G35,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G35" s="51" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B35,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B35+1))</f>
-        <v/>
+        <v>1526.18</v>
       </c>
       <c r="I35" s="53">
         <f>IFERROR(F35-H35,0)</f>
-        <v/>
+        <v>-1526.18</v>
       </c>
       <c r="J35" s="54">
         <f>IFERROR(I35/F35,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K35" s="55" t="n"/>
       <c r="L35" s="18" t="inlineStr">
@@ -11715,7 +11781,7 @@
       <c r="Q35" s="56" t="n"/>
       <c r="R35" s="56">
         <f>IFERROR(D35*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S35" s="56" t="n"/>
       <c r="T35" s="56" t="n"/>
@@ -11745,22 +11811,22 @@
       </c>
       <c r="F36" s="38">
         <f>IFERROR(D36+E36+G36,0)</f>
-        <v/>
+        <v>4423.0</v>
       </c>
       <c r="G36" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B36,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B36+1))</f>
-        <v/>
+        <v>2858.08</v>
       </c>
       <c r="I36" s="41">
         <f>IFERROR(F36-H36,0)</f>
-        <v/>
+        <v>1564.92</v>
       </c>
       <c r="J36" s="42">
         <f>IFERROR(I36/F36,0)</f>
-        <v/>
+        <v>0.353814</v>
       </c>
       <c r="K36" s="43" t="n"/>
       <c r="L36" s="9" t="inlineStr">
@@ -11775,7 +11841,7 @@
       <c r="Q36" s="44" t="n"/>
       <c r="R36" s="44">
         <f>IFERROR(D36*$T$7,0)</f>
-        <v/>
+        <v>84.24</v>
       </c>
       <c r="S36" s="44" t="n"/>
       <c r="T36" s="44" t="n"/>
@@ -11805,22 +11871,22 @@
       </c>
       <c r="F37" s="50">
         <f>IFERROR(D37+E37+G37,0)</f>
-        <v/>
+        <v>2786.0</v>
       </c>
       <c r="G37" s="51" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B37,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B37+1))</f>
-        <v/>
+        <v>2541.9</v>
       </c>
       <c r="I37" s="53">
         <f>IFERROR(F37-H37,0)</f>
-        <v/>
+        <v>244.1</v>
       </c>
       <c r="J37" s="54">
         <f>IFERROR(I37/F37,0)</f>
-        <v/>
+        <v>0.087617</v>
       </c>
       <c r="K37" s="55" t="n"/>
       <c r="L37" s="18" t="inlineStr">
@@ -11835,7 +11901,7 @@
       <c r="Q37" s="56" t="n"/>
       <c r="R37" s="56">
         <f>IFERROR(D37*$T$7,0)</f>
-        <v/>
+        <v>74.74</v>
       </c>
       <c r="S37" s="56" t="n"/>
       <c r="T37" s="56" t="n"/>
@@ -11865,22 +11931,22 @@
       </c>
       <c r="F38" s="38">
         <f>IFERROR(D38+E38+G38,0)</f>
-        <v/>
+        <v>4404.0</v>
       </c>
       <c r="G38" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B38,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B38+1))</f>
-        <v/>
+        <v>2353.0</v>
       </c>
       <c r="I38" s="41">
         <f>IFERROR(F38-H38,0)</f>
-        <v/>
+        <v>2051.0</v>
       </c>
       <c r="J38" s="42">
         <f>IFERROR(I38/F38,0)</f>
-        <v/>
+        <v>0.465713</v>
       </c>
       <c r="K38" s="43" t="n"/>
       <c r="L38" s="9" t="inlineStr">
@@ -11895,7 +11961,7 @@
       <c r="Q38" s="44" t="n"/>
       <c r="R38" s="44">
         <f>IFERROR(D38*$T$7,0)</f>
-        <v/>
+        <v>86.19</v>
       </c>
       <c r="S38" s="44" t="n"/>
       <c r="T38" s="44" t="n"/>
@@ -11925,22 +11991,22 @@
       </c>
       <c r="F39" s="50">
         <f>IFERROR(D39+E39+G39,0)</f>
-        <v/>
+        <v>4165.0</v>
       </c>
       <c r="G39" s="51" t="n">
         <v>400</v>
       </c>
       <c r="H39" s="52">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B39,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B39+1))</f>
-        <v/>
+        <v>2958.83</v>
       </c>
       <c r="I39" s="53">
         <f>IFERROR(F39-H39,0)</f>
-        <v/>
+        <v>1206.17</v>
       </c>
       <c r="J39" s="54">
         <f>IFERROR(I39/F39,0)</f>
-        <v/>
+        <v>0.289597</v>
       </c>
       <c r="K39" s="55" t="n"/>
       <c r="L39" s="18" t="inlineStr">
@@ -11955,7 +12021,7 @@
       <c r="Q39" s="56" t="n"/>
       <c r="R39" s="56">
         <f>IFERROR(D39*$T$7,0)</f>
-        <v/>
+        <v>89.77</v>
       </c>
       <c r="S39" s="56" t="n"/>
       <c r="T39" s="56" t="n"/>
@@ -11985,22 +12051,22 @@
       </c>
       <c r="F40" s="38">
         <f>IFERROR(D40+E40+G40,0)</f>
-        <v/>
+        <v>6804.0</v>
       </c>
       <c r="G40" s="39" t="n">
         <v>120</v>
       </c>
       <c r="H40" s="40">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B40,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B40+1))</f>
-        <v/>
+        <v>1483.0</v>
       </c>
       <c r="I40" s="41">
         <f>IFERROR(F40-H40,0)</f>
-        <v/>
+        <v>5321.0</v>
       </c>
       <c r="J40" s="42">
         <f>IFERROR(I40/F40,0)</f>
-        <v/>
+        <v>0.78204</v>
       </c>
       <c r="K40" s="43" t="n"/>
       <c r="L40" s="9" t="inlineStr">
@@ -12015,7 +12081,7 @@
       <c r="Q40" s="44" t="n"/>
       <c r="R40" s="44">
         <f>IFERROR(D40*$T$7,0)</f>
-        <v/>
+        <v>169.67</v>
       </c>
       <c r="S40" s="44" t="n"/>
       <c r="T40" s="44" t="n"/>
@@ -12045,22 +12111,22 @@
       </c>
       <c r="F41" s="50">
         <f>IFERROR(D41+E41+G41,0)</f>
-        <v/>
+        <v>2251.0</v>
       </c>
       <c r="G41" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B41,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B41+1))</f>
-        <v/>
+        <v>9320.81</v>
       </c>
       <c r="I41" s="259">
         <f>IFERROR(F41-H41,0)</f>
-        <v/>
+        <v>-7069.81</v>
       </c>
       <c r="J41" s="260">
         <f>IFERROR(I41/F41,0)</f>
-        <v/>
+        <v>-3.140742</v>
       </c>
       <c r="K41" s="254" t="n"/>
       <c r="L41" s="261" t="inlineStr">
@@ -12075,7 +12141,7 @@
       <c r="Q41" s="56" t="n"/>
       <c r="R41" s="56">
         <f>IFERROR(D41*$T$7,0)</f>
-        <v/>
+        <v>47.58</v>
       </c>
       <c r="S41" s="56" t="n"/>
       <c r="T41" s="56" t="n"/>
@@ -12105,22 +12171,22 @@
       </c>
       <c r="F42" s="38">
         <f>IFERROR(D42+E42+G42,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G42" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B42,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B42+1))</f>
-        <v/>
+        <v>2065.85</v>
       </c>
       <c r="I42" s="274">
         <f>IFERROR(F42-H42,0)</f>
-        <v/>
+        <v>-2065.85</v>
       </c>
       <c r="J42" s="275">
         <f>IFERROR(I42/F42,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K42" s="250" t="n"/>
       <c r="L42" s="276" t="inlineStr">
@@ -12135,7 +12201,7 @@
       <c r="Q42" s="44" t="n"/>
       <c r="R42" s="44">
         <f>IFERROR(D42*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S42" s="44" t="n"/>
       <c r="T42" s="44" t="n"/>
@@ -12165,22 +12231,22 @@
       </c>
       <c r="F43" s="50">
         <f>IFERROR(D43+E43+G43,0)</f>
-        <v/>
+        <v>4259.0</v>
       </c>
       <c r="G43" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B43,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B43+1))</f>
-        <v/>
+        <v>1451.0</v>
       </c>
       <c r="I43" s="259">
         <f>IFERROR(F43-H43,0)</f>
-        <v/>
+        <v>2808.0</v>
       </c>
       <c r="J43" s="260">
         <f>IFERROR(I43/F43,0)</f>
-        <v/>
+        <v>0.65931</v>
       </c>
       <c r="K43" s="254" t="n"/>
       <c r="L43" s="261" t="inlineStr">
@@ -12195,7 +12261,7 @@
       <c r="Q43" s="56" t="n"/>
       <c r="R43" s="56">
         <f>IFERROR(D43*$T$7,0)</f>
-        <v/>
+        <v>99.84</v>
       </c>
       <c r="S43" s="56" t="n"/>
       <c r="T43" s="56" t="n"/>
@@ -12225,22 +12291,22 @@
       </c>
       <c r="F44" s="38">
         <f>IFERROR(D44+E44+G44,0)</f>
-        <v/>
+        <v>2967.0</v>
       </c>
       <c r="G44" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B44,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B44+1))</f>
-        <v/>
+        <v>757.13</v>
       </c>
       <c r="I44" s="274">
         <f>IFERROR(F44-H44,0)</f>
-        <v/>
+        <v>2209.87</v>
       </c>
       <c r="J44" s="275">
         <f>IFERROR(I44/F44,0)</f>
-        <v/>
+        <v>0.744816</v>
       </c>
       <c r="K44" s="250" t="n"/>
       <c r="L44" s="276" t="inlineStr">
@@ -12255,7 +12321,7 @@
       <c r="Q44" s="44" t="n"/>
       <c r="R44" s="44">
         <f>IFERROR(D44*$T$7,0)</f>
-        <v/>
+        <v>58.95</v>
       </c>
       <c r="S44" s="44" t="n"/>
       <c r="T44" s="44" t="n"/>
@@ -12285,22 +12351,22 @@
       </c>
       <c r="F45" s="50">
         <f>IFERROR(D45+E45+G45,0)</f>
-        <v/>
+        <v>3589.0</v>
       </c>
       <c r="G45" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B45,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B45+1))</f>
-        <v/>
+        <v>3781.35</v>
       </c>
       <c r="I45" s="259">
         <f>IFERROR(F45-H45,0)</f>
-        <v/>
+        <v>-192.35</v>
       </c>
       <c r="J45" s="260">
         <f>IFERROR(I45/F45,0)</f>
-        <v/>
+        <v>-0.053594</v>
       </c>
       <c r="K45" s="254" t="n"/>
       <c r="L45" s="261" t="inlineStr">
@@ -12315,7 +12381,7 @@
       <c r="Q45" s="56" t="n"/>
       <c r="R45" s="56">
         <f>IFERROR(D45*$T$7,0)</f>
-        <v/>
+        <v>43.2</v>
       </c>
       <c r="S45" s="56" t="n"/>
       <c r="T45" s="56" t="n"/>
@@ -12345,22 +12411,22 @@
       </c>
       <c r="F46" s="38">
         <f>IFERROR(D46+E46+G46,0)</f>
-        <v/>
+        <v>3588.0</v>
       </c>
       <c r="G46" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B46,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B46+1))</f>
-        <v/>
+        <v>1228.0</v>
       </c>
       <c r="I46" s="274">
         <f>IFERROR(F46-H46,0)</f>
-        <v/>
+        <v>2360.0</v>
       </c>
       <c r="J46" s="275">
         <f>IFERROR(I46/F46,0)</f>
-        <v/>
+        <v>0.657748</v>
       </c>
       <c r="K46" s="250" t="n"/>
       <c r="L46" s="276" t="inlineStr">
@@ -12375,7 +12441,7 @@
       <c r="Q46" s="44" t="n"/>
       <c r="R46" s="44">
         <f>IFERROR(D46*$T$7,0)</f>
-        <v/>
+        <v>70.44</v>
       </c>
       <c r="S46" s="44" t="n"/>
       <c r="T46" s="44" t="n"/>
@@ -12405,22 +12471,22 @@
       </c>
       <c r="F47" s="50">
         <f>IFERROR(D47+E47+G47,0)</f>
-        <v/>
+        <v>4477.0</v>
       </c>
       <c r="G47" s="257" t="n">
         <v>165</v>
       </c>
       <c r="H47" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B47,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B47+1))</f>
-        <v/>
+        <v>1945.53</v>
       </c>
       <c r="I47" s="259">
         <f>IFERROR(F47-H47,0)</f>
-        <v/>
+        <v>2531.47</v>
       </c>
       <c r="J47" s="260">
         <f>IFERROR(I47/F47,0)</f>
-        <v/>
+        <v>0.565439</v>
       </c>
       <c r="K47" s="254" t="n"/>
       <c r="L47" s="261" t="inlineStr">
@@ -12435,7 +12501,7 @@
       <c r="Q47" s="56" t="n"/>
       <c r="R47" s="56">
         <f>IFERROR(D47*$T$7,0)</f>
-        <v/>
+        <v>69.79</v>
       </c>
       <c r="S47" s="56" t="n"/>
       <c r="T47" s="56" t="n"/>
@@ -12465,22 +12531,22 @@
       </c>
       <c r="F48" s="38">
         <f>IFERROR(D48+E48+G48,0)</f>
-        <v/>
+        <v>2029.0</v>
       </c>
       <c r="G48" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B48,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B48+1))</f>
-        <v/>
+        <v>5250.0</v>
       </c>
       <c r="I48" s="274">
         <f>IFERROR(F48-H48,0)</f>
-        <v/>
+        <v>-3221.0</v>
       </c>
       <c r="J48" s="275">
         <f>IFERROR(I48/F48,0)</f>
-        <v/>
+        <v>-1.587482</v>
       </c>
       <c r="K48" s="250" t="n"/>
       <c r="L48" s="276" t="inlineStr">
@@ -12495,7 +12561,7 @@
       <c r="Q48" s="44" t="n"/>
       <c r="R48" s="44">
         <f>IFERROR(D48*$T$7,0)</f>
-        <v/>
+        <v>7.1</v>
       </c>
       <c r="S48" s="44" t="n"/>
       <c r="T48" s="44" t="n"/>
@@ -12525,22 +12591,22 @@
       </c>
       <c r="F49" s="50">
         <f>IFERROR(D49+E49+G49,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G49" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B49,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B49+1))</f>
-        <v/>
+        <v>3865.06</v>
       </c>
       <c r="I49" s="259">
         <f>IFERROR(F49-H49,0)</f>
-        <v/>
+        <v>-3865.06</v>
       </c>
       <c r="J49" s="260">
         <f>IFERROR(I49/F49,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K49" s="254" t="n"/>
       <c r="L49" s="261" t="inlineStr">
@@ -12555,7 +12621,7 @@
       <c r="Q49" s="56" t="n"/>
       <c r="R49" s="56">
         <f>IFERROR(D49*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S49" s="56" t="n"/>
       <c r="T49" s="56" t="n"/>
@@ -12585,22 +12651,22 @@
       </c>
       <c r="F50" s="38">
         <f>IFERROR(D50+E50+G50,0)</f>
-        <v/>
+        <v>3389.0</v>
       </c>
       <c r="G50" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B50,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B50+1))</f>
-        <v/>
+        <v>2683.27</v>
       </c>
       <c r="I50" s="274">
         <f>IFERROR(F50-H50,0)</f>
-        <v/>
+        <v>705.73</v>
       </c>
       <c r="J50" s="275">
         <f>IFERROR(I50/F50,0)</f>
-        <v/>
+        <v>0.208241</v>
       </c>
       <c r="K50" s="250" t="n"/>
       <c r="L50" s="276" t="inlineStr">
@@ -12615,7 +12681,7 @@
       <c r="Q50" s="44" t="n"/>
       <c r="R50" s="44">
         <f>IFERROR(D50*$T$7,0)</f>
-        <v/>
+        <v>73.65</v>
       </c>
       <c r="S50" s="44" t="n"/>
       <c r="T50" s="44" t="n"/>
@@ -12645,22 +12711,22 @@
       </c>
       <c r="F51" s="50">
         <f>IFERROR(D51+E51+G51,0)</f>
-        <v/>
+        <v>4133.0</v>
       </c>
       <c r="G51" s="257" t="n">
         <v>55</v>
       </c>
       <c r="H51" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B51,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B51+1))</f>
-        <v/>
+        <v>1581.27</v>
       </c>
       <c r="I51" s="259">
         <f>IFERROR(F51-H51,0)</f>
-        <v/>
+        <v>2551.73</v>
       </c>
       <c r="J51" s="260">
         <f>IFERROR(I51/F51,0)</f>
-        <v/>
+        <v>0.617404</v>
       </c>
       <c r="K51" s="254" t="n"/>
       <c r="L51" s="261" t="inlineStr">
@@ -12675,7 +12741,7 @@
       <c r="Q51" s="56" t="n"/>
       <c r="R51" s="56">
         <f>IFERROR(D51*$T$7,0)</f>
-        <v/>
+        <v>97.76</v>
       </c>
       <c r="S51" s="56" t="n"/>
       <c r="T51" s="56" t="n"/>
@@ -12705,22 +12771,22 @@
       </c>
       <c r="F52" s="38">
         <f>IFERROR(D52+E52+G52,0)</f>
-        <v/>
+        <v>4522.0</v>
       </c>
       <c r="G52" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B52,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B52+1))</f>
-        <v/>
+        <v>2341.23</v>
       </c>
       <c r="I52" s="274">
         <f>IFERROR(F52-H52,0)</f>
-        <v/>
+        <v>2180.77</v>
       </c>
       <c r="J52" s="275">
         <f>IFERROR(I52/F52,0)</f>
-        <v/>
+        <v>0.482258</v>
       </c>
       <c r="K52" s="250" t="n"/>
       <c r="L52" s="276" t="inlineStr">
@@ -12735,7 +12801,7 @@
       <c r="Q52" s="44" t="n"/>
       <c r="R52" s="44">
         <f>IFERROR(D52*$T$7,0)</f>
-        <v/>
+        <v>101.42</v>
       </c>
       <c r="S52" s="44" t="n"/>
       <c r="T52" s="44" t="n"/>
@@ -12765,22 +12831,22 @@
       </c>
       <c r="F53" s="50">
         <f>IFERROR(D53+E53+G53,0)</f>
-        <v/>
+        <v>3108.0</v>
       </c>
       <c r="G53" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B53,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B53+1))</f>
-        <v/>
+        <v>318.0</v>
       </c>
       <c r="I53" s="259">
         <f>IFERROR(F53-H53,0)</f>
-        <v/>
+        <v>2790.0</v>
       </c>
       <c r="J53" s="260">
         <f>IFERROR(I53/F53,0)</f>
-        <v/>
+        <v>0.897683</v>
       </c>
       <c r="K53" s="254" t="inlineStr">
         <is>
@@ -12799,7 +12865,7 @@
       <c r="Q53" s="56" t="n"/>
       <c r="R53" s="56">
         <f>IFERROR(D53*$T$7,0)</f>
-        <v/>
+        <v>75.48</v>
       </c>
       <c r="S53" s="56" t="n"/>
       <c r="T53" s="56" t="n"/>
@@ -12829,22 +12895,22 @@
       </c>
       <c r="F54" s="38">
         <f>IFERROR(D54+E54+G54,0)</f>
-        <v/>
+        <v>6077.0</v>
       </c>
       <c r="G54" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B54,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B54+1))</f>
-        <v/>
+        <v>2809.6</v>
       </c>
       <c r="I54" s="274">
         <f>IFERROR(F54-H54,0)</f>
-        <v/>
+        <v>3267.4</v>
       </c>
       <c r="J54" s="275">
         <f>IFERROR(I54/F54,0)</f>
-        <v/>
+        <v>0.537667</v>
       </c>
       <c r="K54" s="250" t="inlineStr">
         <is>
@@ -12863,7 +12929,7 @@
       <c r="Q54" s="44" t="n"/>
       <c r="R54" s="44">
         <f>IFERROR(D54*$T$7,0)</f>
-        <v/>
+        <v>150.3</v>
       </c>
       <c r="S54" s="44" t="n"/>
       <c r="T54" s="44" t="n"/>
@@ -12893,22 +12959,22 @@
       </c>
       <c r="F55" s="50">
         <f>IFERROR(D55+E55+G55,0)</f>
-        <v/>
+        <v>2634.0</v>
       </c>
       <c r="G55" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B55,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B55+1))</f>
-        <v/>
+        <v>6877.73</v>
       </c>
       <c r="I55" s="259">
         <f>IFERROR(F55-H55,0)</f>
-        <v/>
+        <v>-4243.73</v>
       </c>
       <c r="J55" s="260">
         <f>IFERROR(I55/F55,0)</f>
-        <v/>
+        <v>-1.611135</v>
       </c>
       <c r="K55" s="254" t="n"/>
       <c r="L55" s="261" t="inlineStr">
@@ -12923,7 +12989,7 @@
       <c r="Q55" s="56" t="n"/>
       <c r="R55" s="56">
         <f>IFERROR(D55*$T$7,0)</f>
-        <v/>
+        <v>70.6</v>
       </c>
       <c r="S55" s="56" t="n"/>
       <c r="T55" s="56" t="n"/>
@@ -12953,22 +13019,22 @@
       </c>
       <c r="F56" s="38">
         <f>IFERROR(D56+E56+G56,0)</f>
-        <v/>
+        <v>3690.0</v>
       </c>
       <c r="G56" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B56,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B56+1))</f>
-        <v/>
+        <v>4200.0</v>
       </c>
       <c r="I56" s="274">
         <f>IFERROR(F56-H56,0)</f>
-        <v/>
+        <v>-510.0</v>
       </c>
       <c r="J56" s="275">
         <f>IFERROR(I56/F56,0)</f>
-        <v/>
+        <v>-0.138211</v>
       </c>
       <c r="K56" s="250" t="n"/>
       <c r="L56" s="276" t="inlineStr">
@@ -12983,7 +13049,7 @@
       <c r="Q56" s="44" t="n"/>
       <c r="R56" s="44">
         <f>IFERROR(D56*$T$7,0)</f>
-        <v/>
+        <v>88.91</v>
       </c>
       <c r="S56" s="44" t="n"/>
       <c r="T56" s="44" t="n"/>
@@ -13013,22 +13079,22 @@
       </c>
       <c r="F57" s="50">
         <f>IFERROR(D57+E57+G57,0)</f>
-        <v/>
+        <v>3660.0</v>
       </c>
       <c r="G57" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B57,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B57+1))</f>
-        <v/>
+        <v>49.0</v>
       </c>
       <c r="I57" s="259">
         <f>IFERROR(F57-H57,0)</f>
-        <v/>
+        <v>3611.0</v>
       </c>
       <c r="J57" s="260">
         <f>IFERROR(I57/F57,0)</f>
-        <v/>
+        <v>0.986612</v>
       </c>
       <c r="K57" s="254" t="n"/>
       <c r="L57" s="261" t="inlineStr">
@@ -13043,7 +13109,7 @@
       <c r="Q57" s="56" t="n"/>
       <c r="R57" s="56">
         <f>IFERROR(D57*$T$7,0)</f>
-        <v/>
+        <v>74.7</v>
       </c>
       <c r="S57" s="56" t="n"/>
       <c r="T57" s="56" t="n"/>
@@ -13073,22 +13139,22 @@
       </c>
       <c r="F58" s="50">
         <f>IFERROR(D58+E58+G58+U58,0)</f>
-        <v/>
+        <v>3688.0</v>
       </c>
       <c r="G58" s="257" t="n">
         <v>195</v>
       </c>
       <c r="H58" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B58,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B58+1))</f>
-        <v/>
+        <v>1415.43</v>
       </c>
       <c r="I58" s="259">
         <f>IFERROR(F58-H58,0)</f>
-        <v/>
+        <v>2272.57</v>
       </c>
       <c r="J58" s="260">
         <f>IFERROR(I58/F58,0)</f>
-        <v/>
+        <v>0.616207</v>
       </c>
       <c r="K58" s="254" t="n"/>
       <c r="L58" s="261" t="inlineStr">
@@ -13103,7 +13169,7 @@
       <c r="Q58" s="292" t="n"/>
       <c r="R58" s="292">
         <f>IFERROR(D58*$T$7,0)</f>
-        <v/>
+        <v>14.62</v>
       </c>
       <c r="S58" s="292" t="n"/>
       <c r="T58" s="292" t="n"/>
@@ -13137,22 +13203,22 @@
       </c>
       <c r="F59" s="50">
         <f>IFERROR(D59+E59+G59+U59,0)</f>
-        <v/>
+        <v>6015.0</v>
       </c>
       <c r="G59" s="257" t="n">
         <v>120</v>
       </c>
       <c r="H59" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B59,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B59+1))</f>
-        <v/>
+        <v>1820.89</v>
       </c>
       <c r="I59" s="259">
         <f>IFERROR(F59-H59,0)</f>
-        <v/>
+        <v>4194.11</v>
       </c>
       <c r="J59" s="260">
         <f>IFERROR(I59/F59,0)</f>
-        <v/>
+        <v>0.697275</v>
       </c>
       <c r="K59" s="254" t="n"/>
       <c r="L59" s="261" t="inlineStr">
@@ -13167,7 +13233,7 @@
       <c r="Q59" s="292" t="n"/>
       <c r="R59" s="292">
         <f>IFERROR(D59*$T$7,0)</f>
-        <v/>
+        <v>78.76</v>
       </c>
       <c r="S59" s="292" t="n"/>
       <c r="T59" s="292" t="n"/>
@@ -13201,22 +13267,22 @@
       </c>
       <c r="F60" s="50">
         <f>IFERROR(D60+E60+G60+U60,0)</f>
-        <v/>
+        <v>3500.0</v>
       </c>
       <c r="G60" s="257" t="n">
         <v>70</v>
       </c>
       <c r="H60" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B60,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B60+1))</f>
-        <v/>
+        <v>2094.0</v>
       </c>
       <c r="I60" s="259">
         <f>IFERROR(F60-H60,0)</f>
-        <v/>
+        <v>1406.0</v>
       </c>
       <c r="J60" s="260">
         <f>IFERROR(I60/F60,0)</f>
-        <v/>
+        <v>0.401714</v>
       </c>
       <c r="K60" s="254" t="n"/>
       <c r="L60" s="261" t="inlineStr">
@@ -13231,7 +13297,7 @@
       <c r="Q60" s="292" t="n"/>
       <c r="R60" s="292">
         <f>IFERROR(D60*$T$7,0)</f>
-        <v/>
+        <v>69.02</v>
       </c>
       <c r="S60" s="292" t="n"/>
       <c r="T60" s="292" t="n"/>
@@ -13265,22 +13331,22 @@
       </c>
       <c r="F61" s="50">
         <f>IFERROR(D61+E61+G61+U61,0)</f>
-        <v/>
+        <v>2725.0</v>
       </c>
       <c r="G61" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B61,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B61+1))</f>
-        <v/>
+        <v>10207.0</v>
       </c>
       <c r="I61" s="259">
         <f>IFERROR(F61-H61,0)</f>
-        <v/>
+        <v>-7482.0</v>
       </c>
       <c r="J61" s="260">
         <f>IFERROR(I61/F61,0)</f>
-        <v/>
+        <v>-2.745688</v>
       </c>
       <c r="K61" s="254" t="n"/>
       <c r="L61" s="261" t="inlineStr">
@@ -13295,7 +13361,7 @@
       <c r="Q61" s="292" t="n"/>
       <c r="R61" s="292">
         <f>IFERROR(D61*$T$7,0)</f>
-        <v/>
+        <v>11.37</v>
       </c>
       <c r="S61" s="292" t="n"/>
       <c r="T61" s="292" t="n"/>
@@ -13329,22 +13395,22 @@
       </c>
       <c r="F62" s="50">
         <f>IFERROR(D62+E62+G62+U62+Y62,0)</f>
-        <v/>
+        <v>3990.0</v>
       </c>
       <c r="G62" s="257" t="n">
         <v>120</v>
       </c>
       <c r="H62" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B62,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B62+1))</f>
-        <v/>
+        <v>3142.0</v>
       </c>
       <c r="I62" s="259">
         <f>IFERROR(F62-H62,0)</f>
-        <v/>
+        <v>848.0</v>
       </c>
       <c r="J62" s="260">
         <f>IFERROR(I62/F62,0)</f>
-        <v/>
+        <v>0.212531</v>
       </c>
       <c r="K62" s="254" t="n"/>
       <c r="L62" s="261" t="inlineStr">
@@ -13359,7 +13425,7 @@
       <c r="Q62" s="292" t="n"/>
       <c r="R62" s="292">
         <f>IFERROR(D62*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S62" s="292" t="n"/>
       <c r="T62" s="292" t="n"/>
@@ -13397,22 +13463,22 @@
       </c>
       <c r="F63" s="50">
         <f>IFERROR(D63+E63+G63+U63+Y63,0)</f>
-        <v/>
+        <v>3915.0</v>
       </c>
       <c r="G63" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B63,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B63+1))</f>
-        <v/>
+        <v>596.38</v>
       </c>
       <c r="I63" s="259">
         <f>IFERROR(F63-H63,0)</f>
-        <v/>
+        <v>3318.62</v>
       </c>
       <c r="J63" s="260">
         <f>IFERROR(I63/F63,0)</f>
-        <v/>
+        <v>0.847668</v>
       </c>
       <c r="K63" s="254" t="n"/>
       <c r="L63" s="261" t="inlineStr">
@@ -13427,7 +13493,7 @@
       <c r="Q63" s="292" t="n"/>
       <c r="R63" s="311">
         <f>IFERROR(D63*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S63" s="292" t="n"/>
       <c r="T63" s="292" t="n"/>
@@ -13465,22 +13531,22 @@
       </c>
       <c r="F64" s="50">
         <f>IFERROR(D64+E64+G64+U64+Y64,0)</f>
-        <v/>
+        <v>5565.0</v>
       </c>
       <c r="G64" s="257" t="n">
         <v>130</v>
       </c>
       <c r="H64" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B64,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B64+1))</f>
-        <v/>
+        <v>2606.86</v>
       </c>
       <c r="I64" s="259">
         <f>IFERROR(F64-H64,0)</f>
-        <v/>
+        <v>2958.14</v>
       </c>
       <c r="J64" s="260">
         <f>IFERROR(I64/F64,0)</f>
-        <v/>
+        <v>0.531562</v>
       </c>
       <c r="K64" s="254" t="n"/>
       <c r="L64" s="261" t="inlineStr">
@@ -13495,7 +13561,7 @@
       <c r="Q64" s="292" t="n"/>
       <c r="R64" s="311">
         <f>IFERROR(D64*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S64" s="292" t="n"/>
       <c r="T64" s="292" t="n"/>
@@ -13533,22 +13599,22 @@
       </c>
       <c r="F65" s="50">
         <f>IFERROR(D65+E65+G65+U65+Y65,0)</f>
-        <v/>
+        <v>12495.0</v>
       </c>
       <c r="G65" s="257" t="n">
         <v>2385</v>
       </c>
       <c r="H65" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B65,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B65+1))</f>
-        <v/>
+        <v>1657.0</v>
       </c>
       <c r="I65" s="259">
         <f>IFERROR(F65-H65,0)</f>
-        <v/>
+        <v>10838.0</v>
       </c>
       <c r="J65" s="260">
         <f>IFERROR(I65/F65,0)</f>
-        <v/>
+        <v>0.867387</v>
       </c>
       <c r="K65" s="254" t="n"/>
       <c r="L65" s="261" t="inlineStr">
@@ -13563,7 +13629,7 @@
       <c r="Q65" s="292" t="n"/>
       <c r="R65" s="311">
         <f>IFERROR(D65*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S65" s="292" t="n"/>
       <c r="T65" s="292" t="n"/>
@@ -13601,22 +13667,22 @@
       </c>
       <c r="F66" s="50">
         <f>IFERROR(D66+E66+G66+U66+Y66,0)</f>
-        <v/>
+        <v>2622.0</v>
       </c>
       <c r="G66" s="257" t="n">
         <v>300</v>
       </c>
       <c r="H66" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B66,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B66+1))</f>
-        <v/>
+        <v>1951.0</v>
       </c>
       <c r="I66" s="259">
         <f>IFERROR(F66-H66,0)</f>
-        <v/>
+        <v>671.0</v>
       </c>
       <c r="J66" s="260">
         <f>IFERROR(I66/F66,0)</f>
-        <v/>
+        <v>0.255912</v>
       </c>
       <c r="K66" s="254" t="n"/>
       <c r="L66" s="261" t="inlineStr">
@@ -13631,7 +13697,7 @@
       <c r="Q66" s="292" t="n"/>
       <c r="R66" s="311">
         <f>IFERROR(D66*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S66" s="292" t="n"/>
       <c r="T66" s="292" t="n"/>
@@ -13669,22 +13735,22 @@
       </c>
       <c r="F67" s="50">
         <f>IFERROR(D67+E67+G67+U67+Y67,0)</f>
-        <v/>
+        <v>2900.0</v>
       </c>
       <c r="G67" s="257" t="n">
         <v>290</v>
       </c>
       <c r="H67" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B67,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B67+1))</f>
-        <v/>
+        <v>6770.0</v>
       </c>
       <c r="I67" s="259">
         <f>IFERROR(F67-H67,0)</f>
-        <v/>
+        <v>-3870.0</v>
       </c>
       <c r="J67" s="260">
         <f>IFERROR(I67/F67,0)</f>
-        <v/>
+        <v>-1.334483</v>
       </c>
       <c r="K67" s="254" t="n"/>
       <c r="L67" s="261" t="inlineStr">
@@ -13699,7 +13765,7 @@
       <c r="Q67" s="292" t="n"/>
       <c r="R67" s="311">
         <f>IFERROR(D67*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S67" s="292" t="n"/>
       <c r="T67" s="292" t="n"/>
@@ -13737,22 +13803,22 @@
       </c>
       <c r="F68" s="50">
         <f>IFERROR(D68+E68+G68+U68+Y68,0)</f>
-        <v/>
+        <v>4955.0</v>
       </c>
       <c r="G68" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H68" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B68,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B68+1))</f>
-        <v/>
+        <v>2459.0</v>
       </c>
       <c r="I68" s="259">
         <f>IFERROR(F68-H68,0)</f>
-        <v/>
+        <v>2496.0</v>
       </c>
       <c r="J68" s="260">
         <f>IFERROR(I68/F68,0)</f>
-        <v/>
+        <v>0.503734</v>
       </c>
       <c r="K68" s="254" t="n"/>
       <c r="L68" s="261" t="inlineStr">
@@ -13767,7 +13833,7 @@
       <c r="Q68" s="292" t="n"/>
       <c r="R68" s="311">
         <f>IFERROR(D68*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S68" s="292" t="n"/>
       <c r="T68" s="292" t="n"/>
@@ -13805,22 +13871,22 @@
       </c>
       <c r="F69" s="50">
         <f>IFERROR(D69+E69+G69+U69+Y69,0)</f>
-        <v/>
+        <v>5480.0</v>
       </c>
       <c r="G69" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H69" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B69,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B69+1))</f>
-        <v/>
+        <v>2197.0</v>
       </c>
       <c r="I69" s="259">
         <f>IFERROR(F69-H69,0)</f>
-        <v/>
+        <v>3283.0</v>
       </c>
       <c r="J69" s="260">
         <f>IFERROR(I69/F69,0)</f>
-        <v/>
+        <v>0.599088</v>
       </c>
       <c r="K69" s="254" t="n"/>
       <c r="L69" s="261" t="inlineStr">
@@ -13835,7 +13901,7 @@
       <c r="Q69" s="292" t="n"/>
       <c r="R69" s="311">
         <f>IFERROR(D69*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S69" s="292" t="n"/>
       <c r="T69" s="292" t="n"/>
@@ -13873,22 +13939,22 @@
       </c>
       <c r="F70" s="50">
         <f>IFERROR(D70+E70+G70+U70+Y70,0)</f>
-        <v/>
+        <v>5205.0</v>
       </c>
       <c r="G70" s="257" t="n">
         <v>355</v>
       </c>
       <c r="H70" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B70,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B70+1))</f>
-        <v/>
+        <v>3819.0</v>
       </c>
       <c r="I70" s="259">
         <f>IFERROR(F70-H70,0)</f>
-        <v/>
+        <v>1386.0</v>
       </c>
       <c r="J70" s="260">
         <f>IFERROR(I70/F70,0)</f>
-        <v/>
+        <v>0.266282</v>
       </c>
       <c r="K70" s="254" t="n"/>
       <c r="L70" s="261" t="inlineStr">
@@ -13903,7 +13969,7 @@
       <c r="Q70" s="292" t="n"/>
       <c r="R70" s="311">
         <f>IFERROR(D70*$T$7,0)</f>
-        <v/>
+        <v>93.79</v>
       </c>
       <c r="S70" s="292" t="n"/>
       <c r="T70" s="292" t="n"/>
@@ -13941,22 +14007,22 @@
       </c>
       <c r="F71" s="50">
         <f>IFERROR(D71+E71+G71+U71+Y71,0)</f>
-        <v/>
+        <v>4075.0</v>
       </c>
       <c r="G71" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B71,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B71+1))</f>
-        <v/>
+        <v>5348.83</v>
       </c>
       <c r="I71" s="259">
         <f>IFERROR(F71-H71,0)</f>
-        <v/>
+        <v>-1273.83</v>
       </c>
       <c r="J71" s="260">
         <f>IFERROR(I71/F71,0)</f>
-        <v/>
+        <v>-0.312596</v>
       </c>
       <c r="K71" s="254" t="n"/>
       <c r="L71" s="261" t="inlineStr">
@@ -13971,7 +14037,7 @@
       <c r="Q71" s="292" t="n"/>
       <c r="R71" s="311">
         <f>IFERROR(D71*$T$7,0)</f>
-        <v/>
+        <v>68.82</v>
       </c>
       <c r="S71" s="292" t="n"/>
       <c r="T71" s="292" t="n"/>
@@ -14009,22 +14075,22 @@
       </c>
       <c r="F72" s="50">
         <f>IFERROR(D72+E72+G72+U72+Y72,0)</f>
-        <v/>
+        <v>5770.0</v>
       </c>
       <c r="G72" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B72,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B72+1))</f>
-        <v/>
+        <v>1886.0</v>
       </c>
       <c r="I72" s="259">
         <f>IFERROR(F72-H72,0)</f>
-        <v/>
+        <v>3884.0</v>
       </c>
       <c r="J72" s="260">
         <f>IFERROR(I72/F72,0)</f>
-        <v/>
+        <v>0.673137</v>
       </c>
       <c r="K72" s="254" t="n"/>
       <c r="L72" s="261" t="inlineStr">
@@ -14039,7 +14105,7 @@
       <c r="Q72" s="292" t="n"/>
       <c r="R72" s="311">
         <f>IFERROR(D72*$T$7,0)</f>
-        <v/>
+        <v>99.67</v>
       </c>
       <c r="S72" s="292" t="n"/>
       <c r="T72" s="292" t="n"/>
@@ -14077,22 +14143,22 @@
       </c>
       <c r="F73" s="50">
         <f>IFERROR(D73+E73+G73+U73+Y73,0)</f>
-        <v/>
+        <v>1225.0</v>
       </c>
       <c r="G73" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H73" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B73,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B73+1))</f>
-        <v/>
+        <v>6613.0</v>
       </c>
       <c r="I73" s="259">
         <f>IFERROR(F73-H73,0)</f>
-        <v/>
+        <v>-5388.0</v>
       </c>
       <c r="J73" s="260">
         <f>IFERROR(I73/F73,0)</f>
-        <v/>
+        <v>-4.398367</v>
       </c>
       <c r="K73" s="254" t="n"/>
       <c r="L73" s="261" t="inlineStr">
@@ -14107,7 +14173,7 @@
       <c r="Q73" s="292" t="n"/>
       <c r="R73" s="311">
         <f>IFERROR(D73*$T$7,0)</f>
-        <v/>
+        <v>6.29</v>
       </c>
       <c r="S73" s="292" t="n"/>
       <c r="T73" s="292" t="n"/>
@@ -14145,22 +14211,22 @@
       </c>
       <c r="F74" s="38">
         <f>IFERROR(D74+E74+G74+U74+Y74,0)</f>
-        <v/>
+        <v>3180.0</v>
       </c>
       <c r="G74" s="272" t="n">
         <v>700</v>
       </c>
       <c r="H74" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B74,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B74+1))</f>
-        <v/>
+        <v>928.0</v>
       </c>
       <c r="I74" s="274">
         <f>IFERROR(F74-H74,0)</f>
-        <v/>
+        <v>2252.0</v>
       </c>
       <c r="J74" s="275">
         <f>IFERROR(I74/F74,0)</f>
-        <v/>
+        <v>0.708176</v>
       </c>
       <c r="K74" s="250" t="n"/>
       <c r="L74" s="276" t="inlineStr">
@@ -14175,7 +14241,7 @@
       <c r="Q74" s="324" t="n"/>
       <c r="R74" s="327">
         <f>IFERROR(D74*$T$7,0)</f>
-        <v/>
+        <v>44.66</v>
       </c>
       <c r="S74" s="324" t="n"/>
       <c r="T74" s="324" t="n"/>
@@ -14213,22 +14279,22 @@
       </c>
       <c r="F75" s="50">
         <f>IFERROR(D75+E75+G75+U75+Y75,0)</f>
-        <v/>
+        <v>5250.0</v>
       </c>
       <c r="G75" s="257" t="n">
         <v>130</v>
       </c>
       <c r="H75" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B75,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B75+1))</f>
-        <v/>
+        <v>1504.0</v>
       </c>
       <c r="I75" s="259">
         <f>IFERROR(F75-H75,0)</f>
-        <v/>
+        <v>3746.0</v>
       </c>
       <c r="J75" s="260">
         <f>IFERROR(I75/F75,0)</f>
-        <v/>
+        <v>0.713524</v>
       </c>
       <c r="K75" s="254" t="n"/>
       <c r="L75" s="261" t="inlineStr">
@@ -14243,7 +14309,7 @@
       <c r="Q75" s="292" t="n"/>
       <c r="R75" s="311">
         <f>IFERROR(D75*$T$7,0)</f>
-        <v/>
+        <v>130.12</v>
       </c>
       <c r="S75" s="292" t="n"/>
       <c r="T75" s="292" t="n"/>
@@ -14281,22 +14347,22 @@
       </c>
       <c r="F76" s="38">
         <f>IFERROR(D76+E76+G76+U76+Y76,0)</f>
-        <v/>
+        <v>4120.0</v>
       </c>
       <c r="G76" s="272" t="n">
         <v>205</v>
       </c>
       <c r="H76" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B76,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B76+1))</f>
-        <v/>
+        <v>1495.0</v>
       </c>
       <c r="I76" s="274">
         <f>IFERROR(F76-H76,0)</f>
-        <v/>
+        <v>2625.0</v>
       </c>
       <c r="J76" s="275">
         <f>IFERROR(I76/F76,0)</f>
-        <v/>
+        <v>0.637136</v>
       </c>
       <c r="K76" s="250" t="n"/>
       <c r="L76" s="276" t="inlineStr">
@@ -14311,7 +14377,7 @@
       <c r="Q76" s="324" t="n"/>
       <c r="R76" s="327">
         <f>IFERROR(D76*$T$7,0)</f>
-        <v/>
+        <v>99.67</v>
       </c>
       <c r="S76" s="324" t="n"/>
       <c r="T76" s="324" t="n"/>
@@ -14349,22 +14415,22 @@
       </c>
       <c r="F77" s="50">
         <f>IFERROR(D77+E77+G77+U77+Y77,0)</f>
-        <v/>
+        <v>3234.0</v>
       </c>
       <c r="G77" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B77,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B77+1))</f>
-        <v/>
+        <v>268.0</v>
       </c>
       <c r="I77" s="259">
         <f>IFERROR(F77-H77,0)</f>
-        <v/>
+        <v>2966.0</v>
       </c>
       <c r="J77" s="260">
         <f>IFERROR(I77/F77,0)</f>
-        <v/>
+        <v>0.91713</v>
       </c>
       <c r="K77" s="254" t="n"/>
       <c r="L77" s="261" t="inlineStr">
@@ -14379,7 +14445,7 @@
       <c r="Q77" s="292" t="n"/>
       <c r="R77" s="311">
         <f>IFERROR(D77*$T$7,0)</f>
-        <v/>
+        <v>78.93</v>
       </c>
       <c r="S77" s="292" t="n"/>
       <c r="T77" s="292" t="n"/>
@@ -14417,22 +14483,22 @@
       </c>
       <c r="F78" s="38">
         <f>IFERROR(D78+E78+G78+U78+Y78,0)</f>
-        <v/>
+        <v>4705.0</v>
       </c>
       <c r="G78" s="272" t="n">
         <v>390</v>
       </c>
       <c r="H78" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B78,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B78+1))</f>
-        <v/>
+        <v>1993.0</v>
       </c>
       <c r="I78" s="274">
         <f>IFERROR(F78-H78,0)</f>
-        <v/>
+        <v>2712.0</v>
       </c>
       <c r="J78" s="275">
         <f>IFERROR(I78/F78,0)</f>
-        <v/>
+        <v>0.576408</v>
       </c>
       <c r="K78" s="250" t="n"/>
       <c r="L78" s="276" t="inlineStr">
@@ -14447,7 +14513,7 @@
       <c r="Q78" s="324" t="n"/>
       <c r="R78" s="327">
         <f>IFERROR(D78*$T$7,0)</f>
-        <v/>
+        <v>101.5</v>
       </c>
       <c r="S78" s="324" t="n"/>
       <c r="T78" s="324" t="n"/>
@@ -14485,22 +14551,22 @@
       </c>
       <c r="F79" s="50">
         <f>IFERROR(D79+E79+G79+U79+Y79,0)</f>
-        <v/>
+        <v>3738.0</v>
       </c>
       <c r="G79" s="257" t="n">
         <v>225</v>
       </c>
       <c r="H79" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B79,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B79+1))</f>
-        <v/>
+        <v>7208.0</v>
       </c>
       <c r="I79" s="259">
         <f>IFERROR(F79-H79,0)</f>
-        <v/>
+        <v>-3470.0</v>
       </c>
       <c r="J79" s="260">
         <f>IFERROR(I79/F79,0)</f>
-        <v/>
+        <v>-0.928304</v>
       </c>
       <c r="K79" s="254" t="n"/>
       <c r="L79" s="261" t="inlineStr">
@@ -14515,7 +14581,7 @@
       <c r="Q79" s="292" t="n"/>
       <c r="R79" s="311">
         <f>IFERROR(D79*$T$7,0)</f>
-        <v/>
+        <v>90.86</v>
       </c>
       <c r="S79" s="292" t="n"/>
       <c r="T79" s="292" t="n"/>
@@ -14553,22 +14619,22 @@
       </c>
       <c r="F80" s="38">
         <f>IFERROR(D80+E80+G80+U80+Y80,0)</f>
-        <v/>
+        <v>4360.0</v>
       </c>
       <c r="G80" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H80" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B80,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B80+1))</f>
-        <v/>
+        <v>1008.0</v>
       </c>
       <c r="I80" s="274">
         <f>IFERROR(F80-H80,0)</f>
-        <v/>
+        <v>3352.0</v>
       </c>
       <c r="J80" s="275">
         <f>IFERROR(I80/F80,0)</f>
-        <v/>
+        <v>0.768807</v>
       </c>
       <c r="K80" s="250" t="n"/>
       <c r="L80" s="276" t="inlineStr">
@@ -14583,7 +14649,7 @@
       <c r="Q80" s="324" t="n"/>
       <c r="R80" s="428">
         <f>IFERROR(D80*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S80" s="324" t="n"/>
       <c r="T80" s="324" t="n"/>
@@ -14621,22 +14687,22 @@
       </c>
       <c r="F81" s="50">
         <f>IFERROR(D81+E81+G81+U81+Y81,0)</f>
-        <v/>
+        <v>3775.0</v>
       </c>
       <c r="G81" s="257" t="n">
         <v>0</v>
       </c>
       <c r="H81" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B81,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B81+1))</f>
-        <v/>
+        <v>28989.04</v>
       </c>
       <c r="I81" s="259">
         <f>IFERROR(F81-H81,0)</f>
-        <v/>
+        <v>-25214.04</v>
       </c>
       <c r="J81" s="260">
         <f>IFERROR(I81/F81,0)</f>
-        <v/>
+        <v>-6.679216</v>
       </c>
       <c r="K81" s="254" t="n"/>
       <c r="L81" s="261" t="inlineStr">
@@ -14651,7 +14717,7 @@
       <c r="Q81" s="292" t="n"/>
       <c r="R81" s="443">
         <f>IFERROR(D81*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S81" s="292" t="n"/>
       <c r="T81" s="292" t="n"/>
@@ -14689,22 +14755,22 @@
       </c>
       <c r="F82" s="38">
         <f>IFERROR(D82+E82+G82+U82+Y82,0)</f>
-        <v/>
+        <v>5165.0</v>
       </c>
       <c r="G82" s="272" t="n">
         <v>0</v>
       </c>
       <c r="H82" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B82,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B82+1))</f>
-        <v/>
+        <v>1445.0</v>
       </c>
       <c r="I82" s="274">
         <f>IFERROR(F82-H82,0)</f>
-        <v/>
+        <v>3720.0</v>
       </c>
       <c r="J82" s="275">
         <f>IFERROR(I82/F82,0)</f>
-        <v/>
+        <v>0.720232</v>
       </c>
       <c r="K82" s="250" t="n"/>
       <c r="L82" s="276" t="inlineStr">
@@ -14719,7 +14785,7 @@
       <c r="Q82" s="324" t="n"/>
       <c r="R82" s="428">
         <f>IFERROR(D82*$T$7,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="S82" s="324" t="n"/>
       <c r="T82" s="324" t="n"/>
@@ -14757,22 +14823,22 @@
       </c>
       <c r="F83" s="50">
         <f>IFERROR(D83+E83+G83+U83+Y83,0)</f>
-        <v/>
+        <v>3765.0</v>
       </c>
       <c r="G83" s="257" t="n">
         <v>130</v>
       </c>
       <c r="H83" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B83,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B83+1))</f>
-        <v/>
+        <v>2372.0</v>
       </c>
       <c r="I83" s="259">
         <f>IFERROR(F83-H83,0)</f>
-        <v/>
+        <v>1393.0</v>
       </c>
       <c r="J83" s="260">
         <f>IFERROR(I83/F83,0)</f>
-        <v/>
+        <v>0.369987</v>
       </c>
       <c r="K83" s="254" t="n"/>
       <c r="L83" s="261" t="inlineStr">
@@ -14787,7 +14853,7 @@
       <c r="Q83" s="292" t="n"/>
       <c r="R83" s="443">
         <f>IFERROR(D83*$T$7,0)</f>
-        <v/>
+        <v>5.28</v>
       </c>
       <c r="S83" s="292" t="n"/>
       <c r="T83" s="292" t="n"/>
@@ -14825,22 +14891,22 @@
       </c>
       <c r="F84" s="38">
         <f>IFERROR(D84+E84+G84+U84+Y84,0)</f>
-        <v/>
+        <v>6725.0</v>
       </c>
       <c r="G84" s="272" t="n">
         <v>130</v>
       </c>
       <c r="H84" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B84,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B84+1))</f>
-        <v/>
+        <v>2152.0</v>
       </c>
       <c r="I84" s="274">
         <f>IFERROR(F84-H84,0)</f>
-        <v/>
+        <v>4573.0</v>
       </c>
       <c r="J84" s="275">
         <f>IFERROR(I84/F84,0)</f>
-        <v/>
+        <v>0.68</v>
       </c>
       <c r="K84" s="250" t="n"/>
       <c r="L84" s="276" t="inlineStr">
@@ -14855,7 +14921,7 @@
       <c r="Q84" s="324" t="n"/>
       <c r="R84" s="428">
         <f>IFERROR(D84*$T$7,0)</f>
-        <v/>
+        <v>4.67</v>
       </c>
       <c r="S84" s="324" t="n"/>
       <c r="T84" s="324" t="n"/>
@@ -14893,22 +14959,22 @@
       </c>
       <c r="F85" s="50">
         <f>IFERROR(D85+E85+G85+U85+Y85,0)</f>
-        <v/>
+        <v>2410.0</v>
       </c>
       <c r="G85" s="257" t="n">
         <v>135</v>
       </c>
       <c r="H85" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B85,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B85+1))</f>
-        <v/>
+        <v>7943.0</v>
       </c>
       <c r="I85" s="259">
         <f>IFERROR(F85-H85,0)</f>
-        <v/>
+        <v>-5533.0</v>
       </c>
       <c r="J85" s="260">
         <f>IFERROR(I85/F85,0)</f>
-        <v/>
+        <v>-2.295851</v>
       </c>
       <c r="K85" s="254" t="n"/>
       <c r="L85" s="261" t="inlineStr">
@@ -14923,7 +14989,7 @@
       <c r="Q85" s="292" t="n"/>
       <c r="R85" s="443">
         <f>IFERROR(D85*$T$7,0)</f>
-        <v/>
+        <v>17.05</v>
       </c>
       <c r="S85" s="292" t="n"/>
       <c r="T85" s="292" t="n"/>
@@ -14961,22 +15027,22 @@
       </c>
       <c r="F86" s="38">
         <f>IFERROR(D86+E86+G86+U86+Y86,0)</f>
-        <v/>
+        <v>6540.0</v>
       </c>
       <c r="G86" s="272" t="n">
         <v>130</v>
       </c>
       <c r="H86" s="273">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B86,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B86+1))</f>
-        <v/>
+        <v>1138.0</v>
       </c>
       <c r="I86" s="274">
         <f>IFERROR(F86-H86,0)</f>
-        <v/>
+        <v>5402.0</v>
       </c>
       <c r="J86" s="275">
         <f>IFERROR(I86/F86,0)</f>
-        <v/>
+        <v>0.825994</v>
       </c>
       <c r="K86" s="250" t="n"/>
       <c r="L86" s="276" t="inlineStr">
@@ -14991,7 +15057,7 @@
       <c r="Q86" s="324" t="n"/>
       <c r="R86" s="428">
         <f>IFERROR(D86*$T$7,0)</f>
-        <v/>
+        <v>2.64</v>
       </c>
       <c r="S86" s="324" t="n"/>
       <c r="T86" s="324" t="n"/>
@@ -15029,22 +15095,22 @@
       </c>
       <c r="F87" s="50">
         <f>IFERROR(D87+E87+G87+U87+Y87,0)</f>
-        <v/>
+        <v>4705.0</v>
       </c>
       <c r="G87" s="257" t="n">
         <v>655</v>
       </c>
       <c r="H87" s="258">
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B87,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B87+1))</f>
-        <v/>
+        <v>1333.0</v>
       </c>
       <c r="I87" s="259">
         <f>IFERROR(F87-H87,0)</f>
-        <v/>
+        <v>3372.0</v>
       </c>
       <c r="J87" s="260">
         <f>IFERROR(I87/F87,0)</f>
-        <v/>
+        <v>0.716684</v>
       </c>
       <c r="K87" s="254" t="n"/>
       <c r="L87" s="261" t="inlineStr">
@@ -15059,7 +15125,7 @@
       <c r="Q87" s="292" t="n"/>
       <c r="R87" s="443">
         <f>IFERROR(D87*$T$7,0)</f>
-        <v/>
+        <v>9.74</v>
       </c>
       <c r="S87" s="292" t="n"/>
       <c r="T87" s="292" t="n"/>
@@ -15081,33 +15147,72 @@
       <c r="AB87" s="292" t="n"/>
     </row>
     <row r="88" ht="16.5" customHeight="1" s="331">
-      <c r="B88" s="34" t="n"/>
-      <c r="C88" s="35" t="n"/>
-      <c r="D88" s="36" t="n"/>
-      <c r="E88" s="37" t="n"/>
-      <c r="F88" s="38" t="n"/>
-      <c r="G88" s="39" t="n"/>
-      <c r="H88" s="40" t="n"/>
-      <c r="I88" s="41" t="n"/>
-      <c r="J88" s="42" t="n"/>
-      <c r="K88" s="43" t="n"/>
-      <c r="L88" s="9" t="n"/>
-      <c r="M88" s="12" t="n"/>
-      <c r="N88" s="44" t="n"/>
-      <c r="O88" s="45" t="n"/>
-      <c r="P88" s="46" t="n"/>
-      <c r="Q88" s="44" t="n"/>
-      <c r="R88" s="44" t="n"/>
-      <c r="S88" s="44" t="n"/>
-      <c r="T88" s="44" t="n"/>
-      <c r="U88" s="44" t="n"/>
-      <c r="V88" s="44" t="n"/>
-      <c r="W88" s="44" t="n"/>
-      <c r="X88" s="44" t="n"/>
-      <c r="Y88" s="44" t="n"/>
-      <c r="Z88" s="44" t="n"/>
-      <c r="AA88" s="44" t="n"/>
-      <c r="AB88" s="44" t="n"/>
+      <c r="B88" s="427" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C88" s="270" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D88" s="271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="37" t="n">
+        <v>810</v>
+      </c>
+      <c r="F88" s="38">
+        <f>IFERROR(D88+E88+G88+U88+Y88,0)</f>
+        <v>2790.0</v>
+      </c>
+      <c r="G88" s="272" t="n">
+        <v>130</v>
+      </c>
+      <c r="H88" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B88,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B88+1))</f>
+        <v>5043.0</v>
+      </c>
+      <c r="I88" s="274">
+        <f>IFERROR(F88-H88,0)</f>
+        <v>-2253.0</v>
+      </c>
+      <c r="J88" s="275">
+        <f>IFERROR(I88/F88,0)</f>
+        <v>-0.807527</v>
+      </c>
+      <c r="K88" s="250" t="n"/>
+      <c r="L88" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M88" s="323" t="n"/>
+      <c r="N88" s="324" t="n"/>
+      <c r="O88" s="325" t="n"/>
+      <c r="P88" s="326" t="n"/>
+      <c r="Q88" s="324" t="n"/>
+      <c r="R88" s="428">
+        <f>IFERROR(D88*$T$7,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="S88" s="324" t="n"/>
+      <c r="T88" s="324" t="n"/>
+      <c r="U88" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" s="324" t="n"/>
+      <c r="X88" s="324" t="n"/>
+      <c r="Y88" s="428" t="n">
+        <v>1850</v>
+      </c>
+      <c r="Z88" s="428" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="AA88" s="324" t="n"/>
+      <c r="AB88" s="324" t="n"/>
     </row>
     <row r="89" ht="16.5" customHeight="1" s="331">
       <c r="B89" s="34" t="n"/>
@@ -23347,8 +23452,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
@@ -23372,7 +23477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J619"/>
+  <dimension ref="A1:J627"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -49492,6 +49597,350 @@
       <c r="J619" s="423" t="inlineStr">
         <is>
           <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="B620" s="429" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C620" s="297" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="D620" s="298" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E620" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F620" s="299" t="n">
+        <v>112</v>
+      </c>
+      <c r="G620" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H620" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I620" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J620" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="B621" s="429" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C621" s="297" t="inlineStr">
+        <is>
+          <t>Vegetales</t>
+        </is>
+      </c>
+      <c r="D621" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E621" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F621" s="299" t="n">
+        <v>89</v>
+      </c>
+      <c r="G621" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H621" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I621" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J621" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="B622" s="429" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C622" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D622" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E622" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F622" s="299" t="n">
+        <v>743</v>
+      </c>
+      <c r="G622" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H622" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I622" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J622" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="B623" s="429" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C623" s="297" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="D623" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E623" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F623" s="299" t="n">
+        <v>2270</v>
+      </c>
+      <c r="G623" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H623" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I623" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J623" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="B624" s="429" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C624" s="297" t="inlineStr">
+        <is>
+          <t>Avia Reca</t>
+        </is>
+      </c>
+      <c r="D624" s="298" t="inlineStr">
+        <is>
+          <t>Reca</t>
+        </is>
+      </c>
+      <c r="E624" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F624" s="299" t="n">
+        <v>750</v>
+      </c>
+      <c r="G624" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H624" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I624" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J624" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="B625" s="429" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C625" s="297" t="inlineStr">
+        <is>
+          <t>Guimar deschables</t>
+        </is>
+      </c>
+      <c r="D625" s="298" t="inlineStr">
+        <is>
+          <t>Guimar Polietilenos</t>
+        </is>
+      </c>
+      <c r="E625" s="297" t="inlineStr">
+        <is>
+          <t>Packaging/Disposables</t>
+        </is>
+      </c>
+      <c r="F625" s="299" t="n">
+        <v>139</v>
+      </c>
+      <c r="G625" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H625" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I625" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J625" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="B626" s="429" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C626" s="297" t="inlineStr">
+        <is>
+          <t>Oxxo Arroz</t>
+        </is>
+      </c>
+      <c r="D626" s="298" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E626" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F626" s="299" t="n">
+        <v>301</v>
+      </c>
+      <c r="G626" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H626" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I626" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J626" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="B627" s="429" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C627" s="297" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D627" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E627" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F627" s="299" t="n">
+        <v>639</v>
+      </c>
+      <c r="G627" s="300" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H627" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I627" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J627" s="423" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
         </is>
       </c>
     </row>
@@ -59541,15 +59990,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="331">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="431" t="inlineStr">
         <is>
           <t>LOKA — MONTHLY P&amp;L   (live formulas — auto-updates from Daily Log &amp; Expenses)</t>
         </is>
       </c>
-      <c r="B1" s="423" t="n"/>
-      <c r="C1" s="423" t="n"/>
-      <c r="D1" s="423" t="n"/>
-      <c r="E1" s="423" t="n"/>
+      <c r="B1" s="432" t="n"/>
+      <c r="C1" s="432" t="n"/>
+      <c r="D1" s="432" t="n"/>
+      <c r="E1" s="432" t="n"/>
       <c r="F1" s="433" t="n"/>
       <c r="G1" s="433" t="n"/>
       <c r="H1" s="433" t="n"/>
@@ -60065,7 +60514,7 @@
     <row r="20">
       <c r="A20" s="439" t="inlineStr">
         <is>
-          <t>Supermarket/General</t>
+          <t>Ingredients - Vegetables</t>
         </is>
       </c>
       <c r="B20" s="437">
@@ -60095,7 +60544,7 @@
     <row r="21">
       <c r="A21" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Vegetables</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="B21" s="437">
@@ -60155,7 +60604,7 @@
     <row r="23">
       <c r="A23" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Dairy</t>
+          <t>Ingredients - Beverages</t>
         </is>
       </c>
       <c r="B23" s="437">
@@ -60185,7 +60634,7 @@
     <row r="24">
       <c r="A24" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Beverages</t>
+          <t>Ingredients - Dairy</t>
         </is>
       </c>
       <c r="B24" s="437">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5952,7 +5952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="331" min="1" max="1"/>
@@ -8126,30 +8126,63 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="430" t="inlineStr">
+      <c r="A68" s="430" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B68" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 13-Aug)</t>
+        </is>
+      </c>
+      <c r="C68" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D68" s="232" t="n"/>
+      <c r="E68" s="233" t="n">
+        <v>135</v>
+      </c>
+      <c r="F68" s="233">
+        <f>IFERROR(F67+D68-E68,0)</f>
+        <v/>
+      </c>
+      <c r="G68" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H68" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="430" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B68" s="232" t="n"/>
-      <c r="C68" s="232" t="n"/>
-      <c r="D68" s="232">
-        <f>SUM(D4:D67)</f>
-        <v/>
-      </c>
-      <c r="E68" s="233">
-        <f>SUM(E4:E67)</f>
-        <v/>
-      </c>
-      <c r="F68" s="233">
-        <f>F67</f>
-        <v/>
-      </c>
-      <c r="G68" s="232">
-        <f>IF(F67&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F67,"#,##0"),IF(F67&lt;0,"Lohith holds $"&amp;TEXT(ABS(F67),"#,##0"),"Zero balance"))</f>
-        <v/>
-      </c>
-      <c r="H68" s="232" t="n"/>
+      <c r="B69" s="232" t="n"/>
+      <c r="C69" s="232" t="n"/>
+      <c r="D69" s="232">
+        <f>SUM(D4:D68)</f>
+        <v/>
+      </c>
+      <c r="E69" s="233">
+        <f>SUM(E4:E68)</f>
+        <v/>
+      </c>
+      <c r="F69" s="233">
+        <f>F68</f>
+        <v/>
+      </c>
+      <c r="G69" s="232">
+        <f>IF(F68&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F68,"#,##0"),IF(F68&lt;0,"Lohith holds $"&amp;TEXT(ABS(F68),"#,##0"),"Zero balance"))</f>
+        <v/>
+      </c>
+      <c r="H69" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9983,45 +10016,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>2790.0</v>
+        <v>3440.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>130.0</v>
+        <v>135.0</v>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>5043.0</v>
+        <v>479.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>-2253.0</v>
+        <v>2961.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>-0.807527</v>
+        <v>0.860756</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>14035.0</v>
+        <v>17475.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>14035.0</v>
+        <v>17475.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>43973.0</v>
+        <v>47413.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>7514.0</v>
+        <v>7993.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>6521.0</v>
+        <v>9482.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -15215,33 +15248,72 @@
       <c r="AB88" s="324" t="n"/>
     </row>
     <row r="89" ht="16.5" customHeight="1" s="331">
-      <c r="B89" s="34" t="n"/>
-      <c r="C89" s="47" t="n"/>
-      <c r="D89" s="48" t="n"/>
-      <c r="E89" s="49" t="n"/>
-      <c r="F89" s="50" t="n"/>
-      <c r="G89" s="51" t="n"/>
-      <c r="H89" s="52" t="n"/>
-      <c r="I89" s="53" t="n"/>
-      <c r="J89" s="54" t="n"/>
-      <c r="K89" s="55" t="n"/>
-      <c r="L89" s="18" t="n"/>
-      <c r="M89" s="21" t="n"/>
-      <c r="N89" s="56" t="n"/>
-      <c r="O89" s="57" t="n"/>
-      <c r="P89" s="58" t="n"/>
-      <c r="Q89" s="56" t="n"/>
-      <c r="R89" s="56" t="n"/>
-      <c r="S89" s="56" t="n"/>
-      <c r="T89" s="56" t="n"/>
-      <c r="U89" s="56" t="n"/>
-      <c r="V89" s="56" t="n"/>
-      <c r="W89" s="56" t="n"/>
-      <c r="X89" s="56" t="n"/>
-      <c r="Y89" s="56" t="n"/>
-      <c r="Z89" s="56" t="n"/>
-      <c r="AA89" s="56" t="n"/>
-      <c r="AB89" s="56" t="n"/>
+      <c r="B89" s="427" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C89" s="255" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D89" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="49" t="n">
+        <v>1140</v>
+      </c>
+      <c r="F89" s="50">
+        <f>IFERROR(D89+E89+G89+U89+Y89,0)</f>
+        <v>3440.0</v>
+      </c>
+      <c r="G89" s="257" t="n">
+        <v>135</v>
+      </c>
+      <c r="H89" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B89,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B89+1))</f>
+        <v>479.0</v>
+      </c>
+      <c r="I89" s="259">
+        <f>IFERROR(F89-H89,0)</f>
+        <v>2961.0</v>
+      </c>
+      <c r="J89" s="260">
+        <f>IFERROR(I89/F89,0)</f>
+        <v>0.860756</v>
+      </c>
+      <c r="K89" s="254" t="n"/>
+      <c r="L89" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M89" s="291" t="n"/>
+      <c r="N89" s="292" t="n"/>
+      <c r="O89" s="293" t="n"/>
+      <c r="P89" s="294" t="n"/>
+      <c r="Q89" s="292" t="n"/>
+      <c r="R89" s="443">
+        <f>IFERROR(D89*$T$7,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="S89" s="292" t="n"/>
+      <c r="T89" s="292" t="n"/>
+      <c r="U89" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" s="292" t="n"/>
+      <c r="X89" s="292" t="n"/>
+      <c r="Y89" s="443" t="n">
+        <v>2165</v>
+      </c>
+      <c r="Z89" s="443" t="n">
+        <v>41.13</v>
+      </c>
+      <c r="AA89" s="292" t="n"/>
+      <c r="AB89" s="292" t="n"/>
     </row>
     <row r="90" ht="16.5" customHeight="1" s="331">
       <c r="B90" s="34" t="n"/>
@@ -23452,8 +23524,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I2:P2"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:P2"/>
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
@@ -23477,7 +23549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J627"/>
+  <dimension ref="A1:J632"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -49941,6 +50013,221 @@
       <c r="J627" s="423" t="inlineStr">
         <is>
           <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="B628" s="429" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C628" s="297" t="inlineStr">
+        <is>
+          <t>Pan Dulce</t>
+        </is>
+      </c>
+      <c r="D628" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E628" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F628" s="299" t="n">
+        <v>25</v>
+      </c>
+      <c r="G628" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H628" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I628" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J628" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="B629" s="429" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C629" s="297" t="inlineStr">
+        <is>
+          <t>Duplicate Keys</t>
+        </is>
+      </c>
+      <c r="D629" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E629" s="297" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F629" s="299" t="n">
+        <v>180</v>
+      </c>
+      <c r="G629" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H629" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I629" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J629" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="B630" s="429" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C630" s="297" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="D630" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E630" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F630" s="299" t="n">
+        <v>84</v>
+      </c>
+      <c r="G630" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H630" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I630" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J630" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="B631" s="429" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C631" s="297" t="inlineStr">
+        <is>
+          <t>Jamon</t>
+        </is>
+      </c>
+      <c r="D631" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E631" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F631" s="299" t="n">
+        <v>90</v>
+      </c>
+      <c r="G631" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H631" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I631" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J631" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="B632" s="429" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C632" s="297" t="inlineStr">
+        <is>
+          <t>Knife sharpening</t>
+        </is>
+      </c>
+      <c r="D632" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E632" s="297" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="F632" s="299" t="n">
+        <v>100</v>
+      </c>
+      <c r="G632" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H632" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I632" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J632" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
         </is>
       </c>
     </row>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -1366,7 +1366,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25"/>
   </cellStyleXfs>
-  <cellXfs count="445">
+  <cellXfs count="450">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2498,6 +2498,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="94" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="20" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="51" fillId="20" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="37" fillId="37" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="64" fillId="31" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5952,7 +5967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="331" min="1" max="1"/>
@@ -8159,30 +8174,63 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="430" t="inlineStr">
+      <c r="A69" s="430" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B69" s="232" t="inlineStr">
+        <is>
+          <t>Pollo $368 + Pollo $995 (paid by Lohith)</t>
+        </is>
+      </c>
+      <c r="C69" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D69" s="232" t="n">
+        <v>1363</v>
+      </c>
+      <c r="E69" s="233" t="n"/>
+      <c r="F69" s="233">
+        <f>IFERROR(F68+D69-E69,0)</f>
+        <v/>
+      </c>
+      <c r="G69" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H69" s="232" t="inlineStr">
+        <is>
+          <t>Fronted from own pocket; excluded from till via cash_adjust</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="430" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B69" s="232" t="n"/>
-      <c r="C69" s="232" t="n"/>
-      <c r="D69" s="232">
-        <f>SUM(D4:D68)</f>
+      <c r="B70" s="232" t="n"/>
+      <c r="C70" s="232" t="n"/>
+      <c r="D70" s="232">
+        <f>SUM(D4:D69)</f>
         <v/>
       </c>
-      <c r="E69" s="233">
-        <f>SUM(E4:E68)</f>
+      <c r="E70" s="233">
+        <f>SUM(E4:E69)</f>
         <v/>
       </c>
-      <c r="F69" s="233">
-        <f>F68</f>
+      <c r="F70" s="233">
+        <f>F69</f>
         <v/>
       </c>
-      <c r="G69" s="232">
-        <f>IF(F68&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F68,"#,##0"),IF(F68&lt;0,"Lohith holds $"&amp;TEXT(ABS(F68),"#,##0"),"Zero balance"))</f>
+      <c r="G70" s="232">
+        <f>IF(F69&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F69,"#,##0"),IF(F69&lt;0,"Lohith holds $"&amp;TEXT(ABS(F69),"#,##0"),"Zero balance"))</f>
         <v/>
       </c>
-      <c r="H69" s="232" t="n"/>
+      <c r="H70" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10016,45 +10064,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>3440.0</v>
+        <v>4905.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>135.0</v>
+        <v>0.0</v>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>479.0</v>
+        <v>7531.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>2961.0</v>
+        <v>-2626.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>0.860756</v>
+        <v>-0.535372</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>17475.0</v>
+        <v>28025.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>17475.0</v>
+        <v>28025.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>47413.0</v>
+        <v>57963.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>7993.0</v>
+        <v>19479.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>9482.0</v>
+        <v>8546.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -15316,62 +15364,140 @@
       <c r="AB89" s="292" t="n"/>
     </row>
     <row r="90" ht="16.5" customHeight="1" s="331">
-      <c r="B90" s="34" t="n"/>
-      <c r="C90" s="35" t="n"/>
-      <c r="D90" s="36" t="n"/>
-      <c r="E90" s="37" t="n"/>
-      <c r="F90" s="38" t="n"/>
-      <c r="G90" s="39" t="n"/>
-      <c r="H90" s="40" t="n"/>
-      <c r="I90" s="41" t="n"/>
-      <c r="J90" s="42" t="n"/>
-      <c r="K90" s="43" t="n"/>
-      <c r="L90" s="9" t="n"/>
-      <c r="M90" s="12" t="n"/>
-      <c r="N90" s="44" t="n"/>
-      <c r="O90" s="45" t="n"/>
-      <c r="P90" s="46" t="n"/>
-      <c r="Q90" s="44" t="n"/>
-      <c r="R90" s="44" t="n"/>
-      <c r="S90" s="44" t="n"/>
-      <c r="T90" s="44" t="n"/>
-      <c r="U90" s="44" t="n"/>
-      <c r="V90" s="44" t="n"/>
-      <c r="W90" s="44" t="n"/>
-      <c r="X90" s="44" t="n"/>
-      <c r="Y90" s="44" t="n"/>
-      <c r="Z90" s="44" t="n"/>
-      <c r="AA90" s="44" t="n"/>
-      <c r="AB90" s="44" t="n"/>
+      <c r="B90" s="427" t="n">
+        <v>46248</v>
+      </c>
+      <c r="C90" s="270" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D90" s="271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="37" t="n">
+        <v>1680</v>
+      </c>
+      <c r="F90" s="38">
+        <f>IFERROR(D90+E90+G90+U90+Y90,0)</f>
+        <v>5645.0</v>
+      </c>
+      <c r="G90" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B90,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B90+1))</f>
+        <v>3955.0</v>
+      </c>
+      <c r="I90" s="274">
+        <f>IFERROR(F90-H90,0)</f>
+        <v>1690.0</v>
+      </c>
+      <c r="J90" s="275">
+        <f>IFERROR(I90/F90,0)</f>
+        <v>0.29938</v>
+      </c>
+      <c r="K90" s="250" t="n"/>
+      <c r="L90" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M90" s="323" t="n"/>
+      <c r="N90" s="324" t="n"/>
+      <c r="O90" s="325" t="n"/>
+      <c r="P90" s="326" t="n"/>
+      <c r="Q90" s="324" t="n"/>
+      <c r="R90" s="428">
+        <f>IFERROR(D90*$T$7,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="S90" s="324" t="n"/>
+      <c r="T90" s="324" t="n"/>
+      <c r="U90" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" s="324" t="n"/>
+      <c r="X90" s="324" t="n"/>
+      <c r="Y90" s="428" t="n">
+        <v>3965</v>
+      </c>
+      <c r="Z90" s="428" t="n">
+        <v>75.33</v>
+      </c>
+      <c r="AA90" s="324" t="n"/>
+      <c r="AB90" s="324" t="n"/>
     </row>
     <row r="91" ht="16.5" customHeight="1" s="331">
-      <c r="B91" s="34" t="n"/>
-      <c r="C91" s="47" t="n"/>
-      <c r="D91" s="48" t="n"/>
-      <c r="E91" s="49" t="n"/>
-      <c r="F91" s="50" t="n"/>
-      <c r="G91" s="51" t="n"/>
-      <c r="H91" s="52" t="n"/>
-      <c r="I91" s="53" t="n"/>
-      <c r="J91" s="54" t="n"/>
-      <c r="K91" s="55" t="n"/>
-      <c r="L91" s="18" t="n"/>
-      <c r="M91" s="21" t="n"/>
-      <c r="N91" s="56" t="n"/>
-      <c r="O91" s="57" t="n"/>
-      <c r="P91" s="58" t="n"/>
-      <c r="Q91" s="56" t="n"/>
-      <c r="R91" s="56" t="n"/>
-      <c r="S91" s="56" t="n"/>
-      <c r="T91" s="56" t="n"/>
-      <c r="U91" s="56" t="n"/>
-      <c r="V91" s="56" t="n"/>
-      <c r="W91" s="56" t="n"/>
-      <c r="X91" s="56" t="n"/>
-      <c r="Y91" s="56" t="n"/>
-      <c r="Z91" s="56" t="n"/>
-      <c r="AA91" s="56" t="n"/>
-      <c r="AB91" s="56" t="n"/>
+      <c r="B91" s="427" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C91" s="255" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D91" s="256" t="n">
+        <v>2605</v>
+      </c>
+      <c r="E91" s="49" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F91" s="50">
+        <f>IFERROR(D91+E91+G91+U91+Y91,0)</f>
+        <v>4905.0</v>
+      </c>
+      <c r="G91" s="257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B91,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B91+1))</f>
+        <v>7531.0</v>
+      </c>
+      <c r="I91" s="259">
+        <f>IFERROR(F91-H91,0)</f>
+        <v>-2626.0</v>
+      </c>
+      <c r="J91" s="260">
+        <f>IFERROR(I91/F91,0)</f>
+        <v>-0.535372</v>
+      </c>
+      <c r="K91" s="254" t="n"/>
+      <c r="L91" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M91" s="291" t="n"/>
+      <c r="N91" s="292" t="n"/>
+      <c r="O91" s="293" t="n"/>
+      <c r="P91" s="294" t="n"/>
+      <c r="Q91" s="292" t="n"/>
+      <c r="R91" s="443">
+        <f>IFERROR(D91*$T$7,0)</f>
+        <v>105.76</v>
+      </c>
+      <c r="S91" s="292" t="n"/>
+      <c r="T91" s="292" t="n"/>
+      <c r="U91" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" s="292" t="n"/>
+      <c r="X91" s="292" t="n"/>
+      <c r="Y91" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="292" t="n"/>
+      <c r="AB91" s="292" t="n"/>
     </row>
     <row r="92" ht="16.5" customHeight="1" s="331">
       <c r="B92" s="34" t="n"/>
@@ -23524,9 +23650,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -23549,7 +23675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J632"/>
+  <dimension ref="A1:J647"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -50228,6 +50354,651 @@
       <c r="J632" s="423" t="inlineStr">
         <is>
           <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="B633" s="429" t="n">
+        <v>46248</v>
+      </c>
+      <c r="C633" s="297" t="inlineStr">
+        <is>
+          <t>Coca Cola</t>
+        </is>
+      </c>
+      <c r="D633" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E633" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F633" s="299" t="n">
+        <v>876</v>
+      </c>
+      <c r="G633" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H633" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I633" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J633" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="B634" s="429" t="n">
+        <v>46248</v>
+      </c>
+      <c r="C634" s="297" t="inlineStr">
+        <is>
+          <t>Oven Repair</t>
+        </is>
+      </c>
+      <c r="D634" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E634" s="297" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="F634" s="299" t="n">
+        <v>900</v>
+      </c>
+      <c r="G634" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H634" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I634" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J634" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="B635" s="429" t="n">
+        <v>46248</v>
+      </c>
+      <c r="C635" s="297" t="inlineStr">
+        <is>
+          <t>Oxxo Tortillas</t>
+        </is>
+      </c>
+      <c r="D635" s="298" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E635" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F635" s="299" t="n">
+        <v>29</v>
+      </c>
+      <c r="G635" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H635" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I635" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J635" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="B636" s="429" t="n">
+        <v>46248</v>
+      </c>
+      <c r="C636" s="297" t="inlineStr">
+        <is>
+          <t>cake</t>
+        </is>
+      </c>
+      <c r="D636" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E636" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Dairy</t>
+        </is>
+      </c>
+      <c r="F636" s="299" t="n">
+        <v>210</v>
+      </c>
+      <c r="G636" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H636" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I636" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J636" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="B637" s="429" t="n">
+        <v>46248</v>
+      </c>
+      <c r="C637" s="297" t="inlineStr">
+        <is>
+          <t>Samu - salary</t>
+        </is>
+      </c>
+      <c r="D637" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E637" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F637" s="299" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G637" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H637" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I637" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J637" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="B638" s="429" t="n">
+        <v>46248</v>
+      </c>
+      <c r="C638" s="297" t="inlineStr">
+        <is>
+          <t>Armando - salary</t>
+        </is>
+      </c>
+      <c r="D638" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E638" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F638" s="299" t="n">
+        <v>740</v>
+      </c>
+      <c r="G638" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H638" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I638" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J638" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="B639" s="429" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C639" s="297" t="inlineStr">
+        <is>
+          <t>Carne Bistec</t>
+        </is>
+      </c>
+      <c r="D639" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E639" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F639" s="299" t="n">
+        <v>116</v>
+      </c>
+      <c r="G639" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H639" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I639" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J639" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="B640" s="429" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C640" s="297" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D640" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E640" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F640" s="299" t="n">
+        <v>57</v>
+      </c>
+      <c r="G640" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H640" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I640" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J640" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="B641" s="429" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C641" s="297" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="D641" s="298" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E641" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F641" s="299" t="n">
+        <v>108</v>
+      </c>
+      <c r="G641" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H641" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I641" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J641" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="B642" s="429" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C642" s="297" t="inlineStr">
+        <is>
+          <t>Oxxo Panela</t>
+        </is>
+      </c>
+      <c r="D642" s="298" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E642" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Dairy</t>
+        </is>
+      </c>
+      <c r="F642" s="299" t="n">
+        <v>47</v>
+      </c>
+      <c r="G642" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H642" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I642" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J642" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="B643" s="429" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C643" s="297" t="inlineStr">
+        <is>
+          <t>Queso Panela</t>
+        </is>
+      </c>
+      <c r="D643" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E643" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Dairy</t>
+        </is>
+      </c>
+      <c r="F643" s="299" t="n">
+        <v>590</v>
+      </c>
+      <c r="G643" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H643" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I643" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J643" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="B644" s="429" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C644" s="297" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D644" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E644" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F644" s="299" t="n">
+        <v>368</v>
+      </c>
+      <c r="G644" s="300" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H644" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I644" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J644" s="423" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="B645" s="429" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C645" s="297" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D645" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E645" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F645" s="299" t="n">
+        <v>995</v>
+      </c>
+      <c r="G645" s="300" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H645" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I645" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J645" s="423" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="B646" s="429" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C646" s="297" t="inlineStr">
+        <is>
+          <t>Duvi - salary</t>
+        </is>
+      </c>
+      <c r="D646" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E646" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F646" s="299" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G646" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H646" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I646" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J646" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="B647" s="429" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C647" s="297" t="inlineStr">
+        <is>
+          <t>Jhon - salary</t>
+        </is>
+      </c>
+      <c r="D647" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E647" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F647" s="299" t="n">
+        <v>3750</v>
+      </c>
+      <c r="G647" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H647" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I647" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J647" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
         </is>
       </c>
     </row>
@@ -54559,74 +55330,116 @@
     <row r="13" ht="19.5" customHeight="1" s="331" thickBot="1">
       <c r="A13" s="97" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Samu (INACTIVE)</t>
         </is>
       </c>
       <c r="B13" s="98" t="inlineStr">
         <is>
+          <t>Ayudante / Support — left Aug 2026 · final week paid 14 Aug ($1,200)</t>
+        </is>
+      </c>
+      <c r="C13" s="99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="19.5" customHeight="1" s="331" thickBot="1">
+      <c r="A14" s="97" t="inlineStr">
+        <is>
+          <t>Armando</t>
+        </is>
+      </c>
+      <c r="B14" s="445" t="inlineStr">
+        <is>
           <t>Ayudante / Support</t>
         </is>
       </c>
-      <c r="C13" s="99" t="n">
-        <v>160</v>
-      </c>
-      <c r="D13" s="100" t="inlineStr">
+      <c r="C14" s="446" t="n">
+        <v>370</v>
+      </c>
+      <c r="D14" s="447" t="inlineStr">
         <is>
           <t>Full Day</t>
         </is>
       </c>
-      <c r="E13" s="100" t="inlineStr">
+      <c r="E14" s="447" t="inlineStr">
         <is>
           <t>Full Day</t>
         </is>
       </c>
-      <c r="F13" s="100" t="inlineStr">
+      <c r="F14" s="447" t="inlineStr">
         <is>
           <t>Full Day</t>
         </is>
       </c>
-      <c r="G13" s="100" t="inlineStr">
+      <c r="G14" s="447" t="inlineStr">
         <is>
           <t>Full Day</t>
         </is>
       </c>
-      <c r="H13" s="100" t="inlineStr">
+      <c r="H14" s="447" t="inlineStr">
         <is>
           <t>Full Day</t>
         </is>
       </c>
-      <c r="I13" s="100" t="inlineStr">
+      <c r="I14" s="447" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="J13" s="100" t="inlineStr">
+      <c r="J14" s="447" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="K13" s="101">
-        <f>COUNTIF(D13:J13,"Full Day")</f>
+      <c r="K14" s="448">
+        <f>COUNTIF(D14:J14,"Full Day")</f>
         <v/>
       </c>
-      <c r="L13" s="102">
-        <f>K13*C13</f>
+      <c r="L14" s="449">
+        <f>K14*C14</f>
         <v/>
       </c>
-    </row>
-    <row r="14" ht="19.5" customHeight="1" s="331" thickBot="1">
-      <c r="A14" s="97" t="n"/>
-      <c r="B14" s="98" t="n"/>
-      <c r="C14" s="99" t="n"/>
-      <c r="D14" s="100" t="n"/>
-      <c r="E14" s="100" t="n"/>
-      <c r="F14" s="100" t="n"/>
-      <c r="G14" s="100" t="n"/>
-      <c r="H14" s="100" t="n"/>
-      <c r="I14" s="100" t="n"/>
-      <c r="J14" s="100" t="n"/>
-      <c r="K14" s="101" t="n"/>
-      <c r="L14" s="102" t="n"/>
     </row>
     <row r="15" ht="19.5" customHeight="1" s="331" thickBot="1">
       <c r="A15" s="97" t="n"/>
@@ -55056,18 +55869,18 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cesar — Mesero Salary (RESIGNED)</t>
+          <t>Armando — Ayudante Salary</t>
         </is>
       </c>
       <c r="B37" s="199" t="n">
-        <v>0</v>
+        <v>1850</v>
       </c>
       <c r="C37" s="220" t="n">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="D37" s="221" t="inlineStr">
         <is>
-          <t>Resigned — Week 4 paid in full · removed from forward fixed costs</t>
+          <t>$370/day · 5 days Mon–Fri · Sat not available · started 13 Aug 2026 (first payment $740 = 2 days on 14 Aug). Replaces Samu.</t>
         </is>
       </c>
       <c r="E37" s="222" t="n"/>
@@ -55075,18 +55888,18 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Samu — Ayudante Salary</t>
+          <t>Samu — Ayudante Salary (INACTIVE)</t>
         </is>
       </c>
       <c r="B38" s="193" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="C38" s="223" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="D38" s="224" t="inlineStr">
         <is>
-          <t>Confirmed — $800/week | $160/day | 5 days Mon–Fri | Start 9 Jun 2026</t>
+          <t>Left Aug 2026 — final week paid 14 Aug · removed from forward fixed costs</t>
         </is>
       </c>
       <c r="E38" s="225" t="n"/>
@@ -55150,7 +55963,7 @@
     <row r="43">
       <c r="A43" s="203" t="inlineStr">
         <is>
-          <t>── MESERO STATUS — ✅ CESAR + SAMU ACTIVE FROM 9 JUN 2026 ──</t>
+          <t>── STAFF STATUS — ✅ JOHN + DEBI + ARMANDO ACTIVE (Samu left Aug 2026) ──</t>
         </is>
       </c>
       <c r="B43" s="203" t="n"/>
@@ -55182,7 +55995,7 @@
     <row r="45" ht="15.6" customHeight="1" s="331">
       <c r="A45" s="203" t="inlineStr">
         <is>
-          <t>Current roster: John + Debi + Samu (no mesero)</t>
+          <t>Current roster: John + Debi + Armando</t>
         </is>
       </c>
       <c r="B45" s="204" t="n">
@@ -55199,7 +56012,7 @@
       </c>
       <c r="F45" s="204" t="inlineStr">
         <is>
-          <t>Cesar resigned — fixed costs down $2,000/wk</t>
+          <t>Samu left Aug 2026 — replaced by Armando ($1,850/wk vs $1,200/wk)</t>
         </is>
       </c>
       <c r="G45" s="204" t="inlineStr">
@@ -61041,7 +61854,7 @@
     <row r="28">
       <c r="A28" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Meat &amp; Fish</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B28" s="437">
@@ -61071,7 +61884,7 @@
     <row r="29">
       <c r="A29" s="439" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Ingredients - Meat &amp; Fish</t>
         </is>
       </c>
       <c r="B29" s="437">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5967,7 +5967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="331" min="1" max="1"/>
@@ -8207,30 +8207,129 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="430" t="inlineStr">
+      <c r="A70" s="430" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B70" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 17-Aug)</t>
+        </is>
+      </c>
+      <c r="C70" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D70" s="232" t="n"/>
+      <c r="E70" s="233" t="n">
+        <v>130</v>
+      </c>
+      <c r="F70" s="233">
+        <f>IFERROR(F69+D70-E70,0)</f>
+        <v/>
+      </c>
+      <c r="G70" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H70" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="430" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B71" s="232" t="inlineStr">
+        <is>
+          <t>Telmex $349 (paid by Lohith)</t>
+        </is>
+      </c>
+      <c r="C71" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D71" s="232" t="n">
+        <v>349</v>
+      </c>
+      <c r="E71" s="233" t="n"/>
+      <c r="F71" s="233">
+        <f>IFERROR(F70+D71-E71,0)</f>
+        <v/>
+      </c>
+      <c r="G71" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H71" s="232" t="inlineStr">
+        <is>
+          <t>Fronted from own pocket; excluded from till via cash_adjust</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="430" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B72" s="232" t="inlineStr">
+        <is>
+          <t>Settlement - restaurant paid Lohith</t>
+        </is>
+      </c>
+      <c r="C72" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D72" s="232" t="n"/>
+      <c r="E72" s="233" t="n">
+        <v>2820</v>
+      </c>
+      <c r="F72" s="233">
+        <f>IFERROR(F71+D72-E72,0)</f>
+        <v/>
+      </c>
+      <c r="G72" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H72" s="232" t="inlineStr">
+        <is>
+          <t>Ledger settled from operating cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="430" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B70" s="232" t="n"/>
-      <c r="C70" s="232" t="n"/>
-      <c r="D70" s="232">
-        <f>SUM(D4:D69)</f>
+      <c r="B73" s="232" t="n"/>
+      <c r="C73" s="232" t="n"/>
+      <c r="D73" s="232">
+        <f>SUM(D4:D72)</f>
         <v/>
       </c>
-      <c r="E70" s="233">
-        <f>SUM(E4:E69)</f>
+      <c r="E73" s="233">
+        <f>SUM(E4:E72)</f>
         <v/>
       </c>
-      <c r="F70" s="233">
-        <f>F69</f>
+      <c r="F73" s="233">
+        <f>F72</f>
         <v/>
       </c>
-      <c r="G70" s="232">
-        <f>IF(F69&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F69,"#,##0"),IF(F69&lt;0,"Lohith holds $"&amp;TEXT(ABS(F69),"#,##0"),"Zero balance"))</f>
+      <c r="G73" s="232">
+        <f>IF(F72&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F72,"#,##0"),IF(F72&lt;0,"Lohith holds $"&amp;TEXT(ABS(F72),"#,##0"),"Zero balance"))</f>
         <v/>
       </c>
-      <c r="H70" s="232" t="n"/>
+      <c r="H73" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10064,45 +10163,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>4905.0</v>
+        <v>3305.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>0.0</v>
+        <v>130.0</v>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>7531.0</v>
+        <v>3743.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>-2626.0</v>
+        <v>-438.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>-0.535372</v>
+        <v>-0.132526</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>28025.0</v>
+        <v>3305.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>28025.0</v>
+        <v>3305.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>57963.0</v>
+        <v>61268.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>19479.0</v>
+        <v>3743.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>8546.0</v>
+        <v>-438.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -15500,33 +15599,72 @@
       <c r="AB91" s="292" t="n"/>
     </row>
     <row r="92" ht="16.5" customHeight="1" s="331">
-      <c r="B92" s="34" t="n"/>
-      <c r="C92" s="35" t="n"/>
-      <c r="D92" s="36" t="n"/>
-      <c r="E92" s="37" t="n"/>
-      <c r="F92" s="38" t="n"/>
-      <c r="G92" s="39" t="n"/>
-      <c r="H92" s="40" t="n"/>
-      <c r="I92" s="41" t="n"/>
-      <c r="J92" s="42" t="n"/>
-      <c r="K92" s="43" t="n"/>
-      <c r="L92" s="9" t="n"/>
-      <c r="M92" s="12" t="n"/>
-      <c r="N92" s="44" t="n"/>
-      <c r="O92" s="45" t="n"/>
-      <c r="P92" s="46" t="n"/>
-      <c r="Q92" s="44" t="n"/>
-      <c r="R92" s="44" t="n"/>
-      <c r="S92" s="44" t="n"/>
-      <c r="T92" s="44" t="n"/>
-      <c r="U92" s="44" t="n"/>
-      <c r="V92" s="44" t="n"/>
-      <c r="W92" s="44" t="n"/>
-      <c r="X92" s="44" t="n"/>
-      <c r="Y92" s="44" t="n"/>
-      <c r="Z92" s="44" t="n"/>
-      <c r="AA92" s="44" t="n"/>
-      <c r="AB92" s="44" t="n"/>
+      <c r="B92" s="427" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C92" s="270" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D92" s="271" t="n">
+        <v>2205</v>
+      </c>
+      <c r="E92" s="37" t="n">
+        <v>970</v>
+      </c>
+      <c r="F92" s="38">
+        <f>IFERROR(D92+E92+G92+U92+Y92,0)</f>
+        <v>3305.0</v>
+      </c>
+      <c r="G92" s="272" t="n">
+        <v>130</v>
+      </c>
+      <c r="H92" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B92,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B92+1))</f>
+        <v>3743.0</v>
+      </c>
+      <c r="I92" s="274">
+        <f>IFERROR(F92-H92,0)</f>
+        <v>-438.0</v>
+      </c>
+      <c r="J92" s="275">
+        <f>IFERROR(I92/F92,0)</f>
+        <v>-0.132526</v>
+      </c>
+      <c r="K92" s="250" t="n"/>
+      <c r="L92" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M92" s="323" t="n"/>
+      <c r="N92" s="324" t="n"/>
+      <c r="O92" s="325" t="n"/>
+      <c r="P92" s="326" t="n"/>
+      <c r="Q92" s="324" t="n"/>
+      <c r="R92" s="428">
+        <f>IFERROR(D92*$T$7,0)</f>
+        <v>89.52</v>
+      </c>
+      <c r="S92" s="324" t="n"/>
+      <c r="T92" s="324" t="n"/>
+      <c r="U92" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" s="324" t="n"/>
+      <c r="X92" s="324" t="n"/>
+      <c r="Y92" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="324" t="n"/>
+      <c r="AB92" s="324" t="n"/>
     </row>
     <row r="93" ht="16.5" customHeight="1" s="331">
       <c r="B93" s="34" t="n"/>
@@ -23650,9 +23788,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -23675,7 +23813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J647"/>
+  <dimension ref="A1:J653"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -50999,6 +51137,264 @@
       <c r="J647" s="423" t="inlineStr">
         <is>
           <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="B648" s="429" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C648" s="297" t="inlineStr">
+        <is>
+          <t>Pan Dulce</t>
+        </is>
+      </c>
+      <c r="D648" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E648" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F648" s="299" t="n">
+        <v>55</v>
+      </c>
+      <c r="G648" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H648" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I648" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J648" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="B649" s="429" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C649" s="297" t="inlineStr">
+        <is>
+          <t>Tortillas</t>
+        </is>
+      </c>
+      <c r="D649" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E649" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F649" s="299" t="n">
+        <v>26</v>
+      </c>
+      <c r="G649" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H649" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I649" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J649" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="B650" s="429" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C650" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D650" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E650" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F650" s="299" t="n">
+        <v>674</v>
+      </c>
+      <c r="G650" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H650" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I650" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J650" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="B651" s="429" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C651" s="297" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D651" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E651" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F651" s="299" t="n">
+        <v>1850</v>
+      </c>
+      <c r="G651" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H651" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I651" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J651" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="B652" s="429" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C652" s="297" t="inlineStr">
+        <is>
+          <t>Sams club</t>
+        </is>
+      </c>
+      <c r="D652" s="298" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="E652" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F652" s="299" t="n">
+        <v>789</v>
+      </c>
+      <c r="G652" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H652" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I652" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J652" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="B653" s="429" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C653" s="297" t="inlineStr">
+        <is>
+          <t>Telmex</t>
+        </is>
+      </c>
+      <c r="D653" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E653" s="297" t="inlineStr">
+        <is>
+          <t>Utilities/Internet</t>
+        </is>
+      </c>
+      <c r="F653" s="299" t="n">
+        <v>349</v>
+      </c>
+      <c r="G653" s="300" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H653" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I653" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J653" s="423" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
         </is>
       </c>
     </row>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5967,7 +5967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="331" min="1" max="1"/>
@@ -8306,30 +8306,63 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="430" t="inlineStr">
+      <c r="A73" s="430" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B73" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 18-Aug)</t>
+        </is>
+      </c>
+      <c r="C73" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D73" s="232" t="n"/>
+      <c r="E73" s="233" t="n">
+        <v>210</v>
+      </c>
+      <c r="F73" s="233">
+        <f>IFERROR(F72+D73-E73,0)</f>
+        <v/>
+      </c>
+      <c r="G73" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H73" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="430" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B73" s="232" t="n"/>
-      <c r="C73" s="232" t="n"/>
-      <c r="D73" s="232">
-        <f>SUM(D4:D72)</f>
+      <c r="B74" s="232" t="n"/>
+      <c r="C74" s="232" t="n"/>
+      <c r="D74" s="232">
+        <f>SUM(D4:D73)</f>
         <v/>
       </c>
-      <c r="E73" s="233">
-        <f>SUM(E4:E72)</f>
+      <c r="E74" s="233">
+        <f>SUM(E4:E73)</f>
         <v/>
       </c>
-      <c r="F73" s="233">
-        <f>F72</f>
+      <c r="F74" s="233">
+        <f>F73</f>
         <v/>
       </c>
-      <c r="G73" s="232">
-        <f>IF(F72&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F72,"#,##0"),IF(F72&lt;0,"Lohith holds $"&amp;TEXT(ABS(F72),"#,##0"),"Zero balance"))</f>
+      <c r="G74" s="232">
+        <f>IF(F73&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F73,"#,##0"),IF(F73&lt;0,"Lohith holds $"&amp;TEXT(ABS(F73),"#,##0"),"Zero balance"))</f>
         <v/>
       </c>
-      <c r="H73" s="232" t="n"/>
+      <c r="H74" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10163,45 +10196,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>3305.0</v>
+        <v>4630.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>130.0</v>
+        <v>210.0</v>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>3743.0</v>
+        <v>2603.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>-438.0</v>
+        <v>2027.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>-0.132526</v>
+        <v>0.437797</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>3305.0</v>
+        <v>7935.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>3305.0</v>
+        <v>7935.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>61268.0</v>
+        <v>65898.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>3743.0</v>
+        <v>6346.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>-438.0</v>
+        <v>1589.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -15667,33 +15700,72 @@
       <c r="AB92" s="324" t="n"/>
     </row>
     <row r="93" ht="16.5" customHeight="1" s="331">
-      <c r="B93" s="34" t="n"/>
-      <c r="C93" s="47" t="n"/>
-      <c r="D93" s="48" t="n"/>
-      <c r="E93" s="49" t="n"/>
-      <c r="F93" s="50" t="n"/>
-      <c r="G93" s="51" t="n"/>
-      <c r="H93" s="52" t="n"/>
-      <c r="I93" s="53" t="n"/>
-      <c r="J93" s="54" t="n"/>
-      <c r="K93" s="55" t="n"/>
-      <c r="L93" s="18" t="n"/>
-      <c r="M93" s="21" t="n"/>
-      <c r="N93" s="56" t="n"/>
-      <c r="O93" s="57" t="n"/>
-      <c r="P93" s="58" t="n"/>
-      <c r="Q93" s="56" t="n"/>
-      <c r="R93" s="56" t="n"/>
-      <c r="S93" s="56" t="n"/>
-      <c r="T93" s="56" t="n"/>
-      <c r="U93" s="56" t="n"/>
-      <c r="V93" s="56" t="n"/>
-      <c r="W93" s="56" t="n"/>
-      <c r="X93" s="56" t="n"/>
-      <c r="Y93" s="56" t="n"/>
-      <c r="Z93" s="56" t="n"/>
-      <c r="AA93" s="56" t="n"/>
-      <c r="AB93" s="56" t="n"/>
+      <c r="B93" s="427" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C93" s="255" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D93" s="256" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E93" s="49" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F93" s="50">
+        <f>IFERROR(D93+E93+G93+U93+Y93,0)</f>
+        <v>4630.0</v>
+      </c>
+      <c r="G93" s="257" t="n">
+        <v>210</v>
+      </c>
+      <c r="H93" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B93,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B93+1))</f>
+        <v>2603.0</v>
+      </c>
+      <c r="I93" s="259">
+        <f>IFERROR(F93-H93,0)</f>
+        <v>2027.0</v>
+      </c>
+      <c r="J93" s="260">
+        <f>IFERROR(I93/F93,0)</f>
+        <v>0.437797</v>
+      </c>
+      <c r="K93" s="254" t="n"/>
+      <c r="L93" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M93" s="291" t="n"/>
+      <c r="N93" s="292" t="n"/>
+      <c r="O93" s="293" t="n"/>
+      <c r="P93" s="294" t="n"/>
+      <c r="Q93" s="292" t="n"/>
+      <c r="R93" s="443">
+        <f>IFERROR(D93*$T$7,0)</f>
+        <v>81.61</v>
+      </c>
+      <c r="S93" s="292" t="n"/>
+      <c r="T93" s="292" t="n"/>
+      <c r="U93" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" s="292" t="n"/>
+      <c r="X93" s="292" t="n"/>
+      <c r="Y93" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="292" t="n"/>
+      <c r="AB93" s="292" t="n"/>
     </row>
     <row r="94" ht="16.5" customHeight="1" s="331">
       <c r="B94" s="34" t="n"/>
@@ -23788,8 +23860,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I2:P2"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:P2"/>
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
@@ -23813,7 +23885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J653"/>
+  <dimension ref="A1:J658"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -51395,6 +51467,221 @@
       <c r="J653" s="423" t="inlineStr">
         <is>
           <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="B654" s="429" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C654" s="297" t="inlineStr">
+        <is>
+          <t>pan reales</t>
+        </is>
+      </c>
+      <c r="D654" s="298" t="inlineStr">
+        <is>
+          <t>Pan Reales</t>
+        </is>
+      </c>
+      <c r="E654" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F654" s="299" t="n">
+        <v>475</v>
+      </c>
+      <c r="G654" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H654" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I654" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J654" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="B655" s="429" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C655" s="297" t="inlineStr">
+        <is>
+          <t>sams club</t>
+        </is>
+      </c>
+      <c r="D655" s="298" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="E655" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F655" s="299" t="n">
+        <v>1254</v>
+      </c>
+      <c r="G655" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H655" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I655" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J655" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="B656" s="429" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C656" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D656" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E656" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F656" s="299" t="n">
+        <v>491</v>
+      </c>
+      <c r="G656" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H656" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I656" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J656" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="B657" s="429" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C657" s="297" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="D657" s="298" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E657" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F657" s="299" t="n">
+        <v>312</v>
+      </c>
+      <c r="G657" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H657" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I657" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J657" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="B658" s="429" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C658" s="297" t="inlineStr">
+        <is>
+          <t>Oxxo Arroz</t>
+        </is>
+      </c>
+      <c r="D658" s="298" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E658" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F658" s="299" t="n">
+        <v>71</v>
+      </c>
+      <c r="G658" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H658" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I658" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J658" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
         </is>
       </c>
     </row>
@@ -62160,7 +62447,7 @@
     <row r="25">
       <c r="A25" s="439" t="inlineStr">
         <is>
-          <t>Utilities/Electricity</t>
+          <t>Ingredients - Bread</t>
         </is>
       </c>
       <c r="B25" s="437">
@@ -62190,7 +62477,7 @@
     <row r="26">
       <c r="A26" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Bread</t>
+          <t>Utilities/Electricity</t>
         </is>
       </c>
       <c r="B26" s="437">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5967,7 +5967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="331" min="1" max="1"/>
@@ -8339,30 +8339,96 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="430" t="inlineStr">
+      <c r="A74" s="430" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B74" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 19-Aug)</t>
+        </is>
+      </c>
+      <c r="C74" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D74" s="232" t="n"/>
+      <c r="E74" s="233" t="n">
+        <v>120</v>
+      </c>
+      <c r="F74" s="233">
+        <f>IFERROR(F73+D74-E74,0)</f>
+        <v/>
+      </c>
+      <c r="G74" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H74" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="430" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B75" s="232" t="inlineStr">
+        <is>
+          <t>Pollo $418 (paid by Lohith)</t>
+        </is>
+      </c>
+      <c r="C75" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D75" s="232" t="n">
+        <v>418</v>
+      </c>
+      <c r="E75" s="233" t="n"/>
+      <c r="F75" s="233">
+        <f>IFERROR(F74+D75-E75,0)</f>
+        <v/>
+      </c>
+      <c r="G75" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H75" s="232" t="inlineStr">
+        <is>
+          <t>Fronted from own pocket; excluded from till via cash_adjust</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="430" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B74" s="232" t="n"/>
-      <c r="C74" s="232" t="n"/>
-      <c r="D74" s="232">
-        <f>SUM(D4:D73)</f>
+      <c r="B76" s="232" t="n"/>
+      <c r="C76" s="232" t="n"/>
+      <c r="D76" s="232">
+        <f>SUM(D4:D75)</f>
         <v/>
       </c>
-      <c r="E74" s="233">
-        <f>SUM(E4:E73)</f>
+      <c r="E76" s="233">
+        <f>SUM(E4:E75)</f>
         <v/>
       </c>
-      <c r="F74" s="233">
-        <f>F73</f>
+      <c r="F76" s="233">
+        <f>F75</f>
         <v/>
       </c>
-      <c r="G74" s="232">
-        <f>IF(F73&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F73,"#,##0"),IF(F73&lt;0,"Lohith holds $"&amp;TEXT(ABS(F73),"#,##0"),"Zero balance"))</f>
+      <c r="G76" s="232">
+        <f>IF(F75&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F75,"#,##0"),IF(F75&lt;0,"Lohith holds $"&amp;TEXT(ABS(F75),"#,##0"),"Zero balance"))</f>
         <v/>
       </c>
-      <c r="H74" s="232" t="n"/>
+      <c r="H76" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10196,45 +10262,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>4630.0</v>
+        <v>6645.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>210.0</v>
+        <v>120.0</v>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>2603.0</v>
+        <v>2960.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>2027.0</v>
+        <v>3685.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>0.437797</v>
+        <v>0.554552</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>7935.0</v>
+        <v>14580.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>7935.0</v>
+        <v>14580.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>65898.0</v>
+        <v>72543.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>6346.0</v>
+        <v>9306.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>1589.0</v>
+        <v>5274.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -15768,33 +15834,72 @@
       <c r="AB93" s="292" t="n"/>
     </row>
     <row r="94" ht="16.5" customHeight="1" s="331">
-      <c r="B94" s="34" t="n"/>
-      <c r="C94" s="35" t="n"/>
-      <c r="D94" s="36" t="n"/>
-      <c r="E94" s="37" t="n"/>
-      <c r="F94" s="38" t="n"/>
-      <c r="G94" s="39" t="n"/>
-      <c r="H94" s="40" t="n"/>
-      <c r="I94" s="41" t="n"/>
-      <c r="J94" s="42" t="n"/>
-      <c r="K94" s="43" t="n"/>
-      <c r="L94" s="9" t="n"/>
-      <c r="M94" s="12" t="n"/>
-      <c r="N94" s="44" t="n"/>
-      <c r="O94" s="45" t="n"/>
-      <c r="P94" s="46" t="n"/>
-      <c r="Q94" s="44" t="n"/>
-      <c r="R94" s="44" t="n"/>
-      <c r="S94" s="44" t="n"/>
-      <c r="T94" s="44" t="n"/>
-      <c r="U94" s="44" t="n"/>
-      <c r="V94" s="44" t="n"/>
-      <c r="W94" s="44" t="n"/>
-      <c r="X94" s="44" t="n"/>
-      <c r="Y94" s="44" t="n"/>
-      <c r="Z94" s="44" t="n"/>
-      <c r="AA94" s="44" t="n"/>
-      <c r="AB94" s="44" t="n"/>
+      <c r="B94" s="427" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C94" s="270" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D94" s="271" t="n">
+        <v>2680</v>
+      </c>
+      <c r="E94" s="37" t="n">
+        <v>3845</v>
+      </c>
+      <c r="F94" s="38">
+        <f>IFERROR(D94+E94+G94+U94+Y94,0)</f>
+        <v>6645.0</v>
+      </c>
+      <c r="G94" s="272" t="n">
+        <v>120</v>
+      </c>
+      <c r="H94" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B94,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B94+1))</f>
+        <v>2960.0</v>
+      </c>
+      <c r="I94" s="274">
+        <f>IFERROR(F94-H94,0)</f>
+        <v>3685.0</v>
+      </c>
+      <c r="J94" s="275">
+        <f>IFERROR(I94/F94,0)</f>
+        <v>0.554552</v>
+      </c>
+      <c r="K94" s="250" t="n"/>
+      <c r="L94" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M94" s="323" t="n"/>
+      <c r="N94" s="324" t="n"/>
+      <c r="O94" s="325" t="n"/>
+      <c r="P94" s="326" t="n"/>
+      <c r="Q94" s="324" t="n"/>
+      <c r="R94" s="428">
+        <f>IFERROR(D94*$T$7,0)</f>
+        <v>108.81</v>
+      </c>
+      <c r="S94" s="324" t="n"/>
+      <c r="T94" s="324" t="n"/>
+      <c r="U94" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" s="324" t="n"/>
+      <c r="X94" s="324" t="n"/>
+      <c r="Y94" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="324" t="n"/>
+      <c r="AB94" s="324" t="n"/>
     </row>
     <row r="95" ht="16.5" customHeight="1" s="331">
       <c r="B95" s="34" t="n"/>
@@ -23860,8 +23965,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
@@ -23885,7 +23990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J658"/>
+  <dimension ref="A1:J665"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -51682,6 +51787,307 @@
       <c r="J658" s="423" t="inlineStr">
         <is>
           <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="B659" s="429" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C659" s="297" t="inlineStr">
+        <is>
+          <t>Hielo</t>
+        </is>
+      </c>
+      <c r="D659" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E659" s="297" t="inlineStr">
+        <is>
+          <t>Kitchen Supplies</t>
+        </is>
+      </c>
+      <c r="F659" s="299" t="n">
+        <v>100</v>
+      </c>
+      <c r="G659" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H659" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I659" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J659" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="B660" s="429" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C660" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D660" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E660" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F660" s="299" t="n">
+        <v>137</v>
+      </c>
+      <c r="G660" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H660" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I660" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J660" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="B661" s="429" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C661" s="297" t="inlineStr">
+        <is>
+          <t>office depot comanda</t>
+        </is>
+      </c>
+      <c r="D661" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E661" s="297" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F661" s="299" t="n">
+        <v>59</v>
+      </c>
+      <c r="G661" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H661" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I661" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J661" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="B662" s="429" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C662" s="297" t="inlineStr">
+        <is>
+          <t>sams club</t>
+        </is>
+      </c>
+      <c r="D662" s="298" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="E662" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F662" s="299" t="n">
+        <v>1911</v>
+      </c>
+      <c r="G662" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H662" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I662" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J662" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="B663" s="429" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C663" s="297" t="inlineStr">
+        <is>
+          <t>Oxxo Coca</t>
+        </is>
+      </c>
+      <c r="D663" s="298" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E663" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F663" s="299" t="n">
+        <v>55</v>
+      </c>
+      <c r="G663" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H663" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I663" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J663" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="B664" s="429" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C664" s="297" t="inlineStr">
+        <is>
+          <t>Oxxo Aceite</t>
+        </is>
+      </c>
+      <c r="D664" s="298" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E664" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F664" s="299" t="n">
+        <v>280</v>
+      </c>
+      <c r="G664" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H664" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I664" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J664" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="B665" s="429" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C665" s="297" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D665" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E665" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F665" s="299" t="n">
+        <v>418</v>
+      </c>
+      <c r="G665" s="300" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H665" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I665" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J665" s="423" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
         </is>
       </c>
     </row>
@@ -62297,7 +62703,7 @@
     <row r="20">
       <c r="A20" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Vegetables</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="B20" s="437">
@@ -62327,7 +62733,7 @@
     <row r="21">
       <c r="A21" s="439" t="inlineStr">
         <is>
-          <t>Supermarket/General</t>
+          <t>Ingredients - Vegetables</t>
         </is>
       </c>
       <c r="B21" s="437">
@@ -62747,7 +63153,7 @@
     <row r="35">
       <c r="A35" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Other</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="B35" s="437">
@@ -62777,7 +63183,7 @@
     <row r="36">
       <c r="A36" s="439" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Ingredients - Other</t>
         </is>
       </c>
       <c r="B36" s="437">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -10262,45 +10262,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>6645.0</v>
+        <v>3315.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>120.0</v>
+        <v>0.0</v>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>2960.0</v>
+        <v>3736.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>3685.0</v>
+        <v>-421.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>0.554552</v>
+        <v>-0.126998</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>14580.0</v>
+        <v>23090.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>14580.0</v>
+        <v>23090.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>72543.0</v>
+        <v>81053.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>9306.0</v>
+        <v>13382.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>5274.0</v>
+        <v>9708.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -15902,62 +15902,140 @@
       <c r="AB94" s="324" t="n"/>
     </row>
     <row r="95" ht="16.5" customHeight="1" s="331">
-      <c r="B95" s="34" t="n"/>
-      <c r="C95" s="47" t="n"/>
-      <c r="D95" s="48" t="n"/>
-      <c r="E95" s="49" t="n"/>
-      <c r="F95" s="50" t="n"/>
-      <c r="G95" s="51" t="n"/>
-      <c r="H95" s="52" t="n"/>
-      <c r="I95" s="53" t="n"/>
-      <c r="J95" s="54" t="n"/>
-      <c r="K95" s="55" t="n"/>
-      <c r="L95" s="18" t="n"/>
-      <c r="M95" s="21" t="n"/>
-      <c r="N95" s="56" t="n"/>
-      <c r="O95" s="57" t="n"/>
-      <c r="P95" s="58" t="n"/>
-      <c r="Q95" s="56" t="n"/>
-      <c r="R95" s="56" t="n"/>
-      <c r="S95" s="56" t="n"/>
-      <c r="T95" s="56" t="n"/>
-      <c r="U95" s="56" t="n"/>
-      <c r="V95" s="56" t="n"/>
-      <c r="W95" s="56" t="n"/>
-      <c r="X95" s="56" t="n"/>
-      <c r="Y95" s="56" t="n"/>
-      <c r="Z95" s="56" t="n"/>
-      <c r="AA95" s="56" t="n"/>
-      <c r="AB95" s="56" t="n"/>
+      <c r="B95" s="427" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C95" s="255" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D95" s="256" t="n">
+        <v>3140</v>
+      </c>
+      <c r="E95" s="49" t="n">
+        <v>2055</v>
+      </c>
+      <c r="F95" s="50">
+        <f>IFERROR(D95+E95+G95+U95+Y95,0)</f>
+        <v>5195.0</v>
+      </c>
+      <c r="G95" s="257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B95,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B95+1))</f>
+        <v>340.0</v>
+      </c>
+      <c r="I95" s="259">
+        <f>IFERROR(F95-H95,0)</f>
+        <v>4855.0</v>
+      </c>
+      <c r="J95" s="260">
+        <f>IFERROR(I95/F95,0)</f>
+        <v>0.934552</v>
+      </c>
+      <c r="K95" s="254" t="n"/>
+      <c r="L95" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M95" s="291" t="n"/>
+      <c r="N95" s="292" t="n"/>
+      <c r="O95" s="293" t="n"/>
+      <c r="P95" s="294" t="n"/>
+      <c r="Q95" s="292" t="n"/>
+      <c r="R95" s="443">
+        <f>IFERROR(D95*$T$7,0)</f>
+        <v>127.48</v>
+      </c>
+      <c r="S95" s="292" t="n"/>
+      <c r="T95" s="292" t="n"/>
+      <c r="U95" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" s="292" t="n"/>
+      <c r="X95" s="292" t="n"/>
+      <c r="Y95" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA95" s="292" t="n"/>
+      <c r="AB95" s="292" t="n"/>
     </row>
     <row r="96" ht="16.5" customHeight="1" s="331">
-      <c r="B96" s="34" t="n"/>
-      <c r="C96" s="35" t="n"/>
-      <c r="D96" s="36" t="n"/>
-      <c r="E96" s="37" t="n"/>
-      <c r="F96" s="38" t="n"/>
-      <c r="G96" s="39" t="n"/>
-      <c r="H96" s="40" t="n"/>
-      <c r="I96" s="41" t="n"/>
-      <c r="J96" s="42" t="n"/>
-      <c r="K96" s="43" t="n"/>
-      <c r="L96" s="9" t="n"/>
-      <c r="M96" s="12" t="n"/>
-      <c r="N96" s="44" t="n"/>
-      <c r="O96" s="45" t="n"/>
-      <c r="P96" s="46" t="n"/>
-      <c r="Q96" s="44" t="n"/>
-      <c r="R96" s="44" t="n"/>
-      <c r="S96" s="44" t="n"/>
-      <c r="T96" s="44" t="n"/>
-      <c r="U96" s="44" t="n"/>
-      <c r="V96" s="44" t="n"/>
-      <c r="W96" s="44" t="n"/>
-      <c r="X96" s="44" t="n"/>
-      <c r="Y96" s="44" t="n"/>
-      <c r="Z96" s="44" t="n"/>
-      <c r="AA96" s="44" t="n"/>
-      <c r="AB96" s="44" t="n"/>
+      <c r="B96" s="427" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C96" s="270" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D96" s="271" t="n">
+        <v>1210</v>
+      </c>
+      <c r="E96" s="37" t="n">
+        <v>2105</v>
+      </c>
+      <c r="F96" s="38">
+        <f>IFERROR(D96+E96+G96+U96+Y96,0)</f>
+        <v>3315.0</v>
+      </c>
+      <c r="G96" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B96,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B96+1))</f>
+        <v>3736.0</v>
+      </c>
+      <c r="I96" s="274">
+        <f>IFERROR(F96-H96,0)</f>
+        <v>-421.0</v>
+      </c>
+      <c r="J96" s="275">
+        <f>IFERROR(I96/F96,0)</f>
+        <v>-0.126998</v>
+      </c>
+      <c r="K96" s="250" t="n"/>
+      <c r="L96" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M96" s="323" t="n"/>
+      <c r="N96" s="324" t="n"/>
+      <c r="O96" s="325" t="n"/>
+      <c r="P96" s="326" t="n"/>
+      <c r="Q96" s="324" t="n"/>
+      <c r="R96" s="428">
+        <f>IFERROR(D96*$T$7,0)</f>
+        <v>49.13</v>
+      </c>
+      <c r="S96" s="324" t="n"/>
+      <c r="T96" s="324" t="n"/>
+      <c r="U96" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" s="324" t="n"/>
+      <c r="X96" s="324" t="n"/>
+      <c r="Y96" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="324" t="n"/>
+      <c r="AB96" s="324" t="n"/>
     </row>
     <row r="97" ht="16.5" customHeight="1" s="331">
       <c r="B97" s="34" t="n"/>
@@ -23990,7 +24068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J665"/>
+  <dimension ref="A1:J673"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -52088,6 +52166,350 @@
       <c r="J665" s="423" t="inlineStr">
         <is>
           <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="B666" s="429" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C666" s="297" t="inlineStr">
+        <is>
+          <t>Pescado</t>
+        </is>
+      </c>
+      <c r="D666" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E666" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat &amp; Fish</t>
+        </is>
+      </c>
+      <c r="F666" s="299" t="n">
+        <v>340</v>
+      </c>
+      <c r="G666" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H666" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I666" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J666" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="B667" s="429" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C667" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D667" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E667" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F667" s="299" t="n">
+        <v>1176</v>
+      </c>
+      <c r="G667" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H667" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I667" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J667" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="B668" s="429" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C668" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D668" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E668" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F668" s="299" t="n">
+        <v>340</v>
+      </c>
+      <c r="G668" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H668" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I668" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J668" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="B669" s="429" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C669" s="297" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D669" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E669" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F669" s="299" t="n">
+        <v>114</v>
+      </c>
+      <c r="G669" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H669" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I669" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J669" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="B670" s="429" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C670" s="297" t="inlineStr">
+        <is>
+          <t>Agua Natural</t>
+        </is>
+      </c>
+      <c r="D670" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E670" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F670" s="299" t="n">
+        <v>30</v>
+      </c>
+      <c r="G670" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H670" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I670" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J670" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="B671" s="429" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C671" s="297" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="D671" s="298" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E671" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F671" s="299" t="n">
+        <v>70</v>
+      </c>
+      <c r="G671" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H671" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I671" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J671" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="B672" s="429" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C672" s="297" t="inlineStr">
+        <is>
+          <t>Pan Reales</t>
+        </is>
+      </c>
+      <c r="D672" s="298" t="inlineStr">
+        <is>
+          <t>Pan Reales</t>
+        </is>
+      </c>
+      <c r="E672" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F672" s="299" t="n">
+        <v>156</v>
+      </c>
+      <c r="G672" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H672" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I672" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J672" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="B673" s="429" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C673" s="297" t="inlineStr">
+        <is>
+          <t>Armando - salary</t>
+        </is>
+      </c>
+      <c r="D673" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E673" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F673" s="299" t="n">
+        <v>1850</v>
+      </c>
+      <c r="G673" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H673" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I673" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J673" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
         </is>
       </c>
     </row>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="C147" s="268" t="n">
-        <v>20911.85</v>
+        <v>14911.85</v>
       </c>
       <c r="E147" s="286" t="inlineStr">
         <is>
@@ -5531,11 +5531,11 @@
         </is>
       </c>
       <c r="C149" s="444" t="n">
-        <v>-44392</v>
+        <v>-50392</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Cumulative repaid from operating cash (latest 13-Aug-2026 $11,504.00). Reduces advance owed &amp; Cash-on-Hand; NOT a P&amp;L expense.</t>
+          <t>Cumulative repaid from operating cash (latest 21-Aug-2026 $6,000.00). Reduces advance owed &amp; Cash-on-Hand; NOT a P&amp;L expense.</t>
         </is>
       </c>
     </row>
@@ -24043,9 +24043,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -10262,7 +10262,7 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>3315.0</v>
+        <v>2060.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
@@ -10270,37 +10270,37 @@
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>3736.0</v>
+        <v>4809.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>-421.0</v>
+        <v>-2749.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>-0.126998</v>
+        <v>-1.334466</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>23090.0</v>
+        <v>25150.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>23090.0</v>
+        <v>25150.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>81053.0</v>
+        <v>83113.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>13382.0</v>
+        <v>18191.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>9708.0</v>
+        <v>6959.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -16038,33 +16038,72 @@
       <c r="AB96" s="324" t="n"/>
     </row>
     <row r="97" ht="16.5" customHeight="1" s="331">
-      <c r="B97" s="34" t="n"/>
-      <c r="C97" s="47" t="n"/>
-      <c r="D97" s="48" t="n"/>
-      <c r="E97" s="49" t="n"/>
-      <c r="F97" s="50" t="n"/>
-      <c r="G97" s="51" t="n"/>
-      <c r="H97" s="52" t="n"/>
-      <c r="I97" s="53" t="n"/>
-      <c r="J97" s="54" t="n"/>
-      <c r="K97" s="55" t="n"/>
-      <c r="L97" s="18" t="n"/>
-      <c r="M97" s="21" t="n"/>
-      <c r="N97" s="56" t="n"/>
-      <c r="O97" s="57" t="n"/>
-      <c r="P97" s="58" t="n"/>
-      <c r="Q97" s="56" t="n"/>
-      <c r="R97" s="56" t="n"/>
-      <c r="S97" s="56" t="n"/>
-      <c r="T97" s="56" t="n"/>
-      <c r="U97" s="56" t="n"/>
-      <c r="V97" s="56" t="n"/>
-      <c r="W97" s="56" t="n"/>
-      <c r="X97" s="56" t="n"/>
-      <c r="Y97" s="56" t="n"/>
-      <c r="Z97" s="56" t="n"/>
-      <c r="AA97" s="56" t="n"/>
-      <c r="AB97" s="56" t="n"/>
+      <c r="B97" s="427" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C97" s="255" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D97" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="49" t="n">
+        <v>1015</v>
+      </c>
+      <c r="F97" s="50">
+        <f>IFERROR(D97+E97+G97+U97+Y97,0)</f>
+        <v>2060.0</v>
+      </c>
+      <c r="G97" s="257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B97,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B97+1))</f>
+        <v>4809.0</v>
+      </c>
+      <c r="I97" s="259">
+        <f>IFERROR(F97-H97,0)</f>
+        <v>-2749.0</v>
+      </c>
+      <c r="J97" s="260">
+        <f>IFERROR(I97/F97,0)</f>
+        <v>-1.334466</v>
+      </c>
+      <c r="K97" s="254" t="n"/>
+      <c r="L97" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M97" s="291" t="n"/>
+      <c r="N97" s="292" t="n"/>
+      <c r="O97" s="293" t="n"/>
+      <c r="P97" s="294" t="n"/>
+      <c r="Q97" s="292" t="n"/>
+      <c r="R97" s="443">
+        <f>IFERROR(D97*$T$7,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="S97" s="292" t="n"/>
+      <c r="T97" s="292" t="n"/>
+      <c r="U97" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" s="292" t="n"/>
+      <c r="X97" s="292" t="n"/>
+      <c r="Y97" s="443" t="n">
+        <v>1045</v>
+      </c>
+      <c r="Z97" s="443" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="AA97" s="292" t="n"/>
+      <c r="AB97" s="292" t="n"/>
     </row>
     <row r="98" ht="16.5" customHeight="1" s="331">
       <c r="B98" s="34" t="n"/>
@@ -24043,9 +24082,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I2:P2"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B5:P5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:P2"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -24068,7 +24107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J673"/>
+  <dimension ref="A1:J679"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -52510,6 +52549,264 @@
       <c r="J673" s="423" t="inlineStr">
         <is>
           <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="B674" s="429" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C674" s="297" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D674" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E674" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F674" s="299" t="n">
+        <v>109</v>
+      </c>
+      <c r="G674" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H674" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I674" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J674" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="B675" s="429" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C675" s="297" t="inlineStr">
+        <is>
+          <t>Jhon - salary</t>
+        </is>
+      </c>
+      <c r="D675" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E675" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F675" s="299" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G675" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H675" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I675" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J675" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="B676" s="429" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C676" s="297" t="inlineStr">
+        <is>
+          <t>Duvi - salary</t>
+        </is>
+      </c>
+      <c r="D676" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E676" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F676" s="299" t="n">
+        <v>500</v>
+      </c>
+      <c r="G676" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H676" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I676" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J676" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="B677" s="429" t="n">
+        <v>46257</v>
+      </c>
+      <c r="C677" s="297" t="inlineStr">
+        <is>
+          <t>Vegetables Abastos</t>
+        </is>
+      </c>
+      <c r="D677" s="298" t="inlineStr">
+        <is>
+          <t>Central de Abastos</t>
+        </is>
+      </c>
+      <c r="E677" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F677" s="299" t="n">
+        <v>2046</v>
+      </c>
+      <c r="G677" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H677" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I677" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J677" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="B678" s="429" t="n">
+        <v>46257</v>
+      </c>
+      <c r="C678" s="297" t="inlineStr">
+        <is>
+          <t>Basicos</t>
+        </is>
+      </c>
+      <c r="D678" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E678" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F678" s="299" t="n">
+        <v>1241</v>
+      </c>
+      <c r="G678" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H678" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I678" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J678" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="B679" s="429" t="n">
+        <v>46257</v>
+      </c>
+      <c r="C679" s="297" t="inlineStr">
+        <is>
+          <t>San Juan Jamon</t>
+        </is>
+      </c>
+      <c r="D679" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E679" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F679" s="299" t="n">
+        <v>188</v>
+      </c>
+      <c r="G679" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H679" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I679" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J679" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
         </is>
       </c>
     </row>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="C147" s="268" t="n">
-        <v>14911.85</v>
+        <v>3411.85</v>
       </c>
       <c r="E147" s="286" t="inlineStr">
         <is>
@@ -5531,11 +5531,11 @@
         </is>
       </c>
       <c r="C149" s="444" t="n">
-        <v>-50392</v>
+        <v>-61892</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Cumulative repaid from operating cash (latest 21-Aug-2026 $6,000.00). Reduces advance owed &amp; Cash-on-Hand; NOT a P&amp;L expense.</t>
+          <t>Cumulative repaid from operating cash (latest 31-Aug-2026 $10,000.00). Reduces advance owed &amp; Cash-on-Hand; NOT a P&amp;L expense.</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="331" min="1" max="1"/>
@@ -8405,30 +8405,195 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="430" t="inlineStr">
+      <c r="A76" s="430" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B76" s="232" t="inlineStr">
+        <is>
+          <t>Pollo $1,429 (paid by Lohith)</t>
+        </is>
+      </c>
+      <c r="C76" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D76" s="232" t="n">
+        <v>1429</v>
+      </c>
+      <c r="E76" s="233" t="n"/>
+      <c r="F76" s="233">
+        <f>IFERROR(F75+D76-E76,0)</f>
+        <v/>
+      </c>
+      <c r="G76" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H76" s="232" t="inlineStr">
+        <is>
+          <t>Fronted from own pocket; excluded from till via cash_adjust</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="430" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B77" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 25-Aug)</t>
+        </is>
+      </c>
+      <c r="C77" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D77" s="232" t="n"/>
+      <c r="E77" s="233" t="n">
+        <v>250</v>
+      </c>
+      <c r="F77" s="233">
+        <f>IFERROR(F76+D77-E77,0)</f>
+        <v/>
+      </c>
+      <c r="G77" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H77" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="430" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B78" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 27-Aug)</t>
+        </is>
+      </c>
+      <c r="C78" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D78" s="232" t="n"/>
+      <c r="E78" s="233" t="n">
+        <v>260</v>
+      </c>
+      <c r="F78" s="233">
+        <f>IFERROR(F77+D78-E78,0)</f>
+        <v/>
+      </c>
+      <c r="G78" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H78" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="430" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B79" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 28-Aug)</t>
+        </is>
+      </c>
+      <c r="C79" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D79" s="232" t="n"/>
+      <c r="E79" s="233" t="n">
+        <v>235</v>
+      </c>
+      <c r="F79" s="233">
+        <f>IFERROR(F78+D79-E79,0)</f>
+        <v/>
+      </c>
+      <c r="G79" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H79" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="430" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B80" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 31-Aug)</t>
+        </is>
+      </c>
+      <c r="C80" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D80" s="232" t="n"/>
+      <c r="E80" s="233" t="n">
+        <v>130</v>
+      </c>
+      <c r="F80" s="233">
+        <f>IFERROR(F79+D80-E80,0)</f>
+        <v/>
+      </c>
+      <c r="G80" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H80" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="430" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B76" s="232" t="n"/>
-      <c r="C76" s="232" t="n"/>
-      <c r="D76" s="232">
-        <f>SUM(D4:D75)</f>
+      <c r="B81" s="232" t="n"/>
+      <c r="C81" s="232" t="n"/>
+      <c r="D81" s="232">
+        <f>SUM(D4:D80)</f>
         <v/>
       </c>
-      <c r="E76" s="233">
-        <f>SUM(E4:E75)</f>
+      <c r="E81" s="233">
+        <f>SUM(E4:E80)</f>
         <v/>
       </c>
-      <c r="F76" s="233">
-        <f>F75</f>
+      <c r="F81" s="233">
+        <f>F80</f>
         <v/>
       </c>
-      <c r="G76" s="232">
-        <f>IF(F75&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F75,"#,##0"),IF(F75&lt;0,"Lohith holds $"&amp;TEXT(ABS(F75),"#,##0"),"Zero balance"))</f>
+      <c r="G81" s="232">
+        <f>IF(F80&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F80,"#,##0"),IF(F80&lt;0,"Lohith holds $"&amp;TEXT(ABS(F80),"#,##0"),"Zero balance"))</f>
         <v/>
       </c>
-      <c r="H76" s="232" t="n"/>
+      <c r="H81" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10262,45 +10427,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>2060.0</v>
+        <v>3755.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>0.0</v>
+        <v>130.0</v>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>4809.0</v>
+        <v>1438.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>-2749.0</v>
+        <v>2317.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>-1.334466</v>
+        <v>0.617044</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>25150.0</v>
+        <v>3755.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>25150.0</v>
+        <v>3755.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>83113.0</v>
+        <v>105258.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>18191.0</v>
+        <v>1438.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>6959.0</v>
+        <v>2317.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -16106,207 +16271,480 @@
       <c r="AB97" s="292" t="n"/>
     </row>
     <row r="98" ht="16.5" customHeight="1" s="331">
-      <c r="B98" s="34" t="n"/>
-      <c r="C98" s="35" t="n"/>
-      <c r="D98" s="36" t="n"/>
-      <c r="E98" s="37" t="n"/>
-      <c r="F98" s="38" t="n"/>
-      <c r="G98" s="39" t="n"/>
-      <c r="H98" s="40" t="n"/>
-      <c r="I98" s="41" t="n"/>
-      <c r="J98" s="42" t="n"/>
-      <c r="K98" s="43" t="n"/>
-      <c r="L98" s="9" t="n"/>
-      <c r="M98" s="12" t="n"/>
-      <c r="N98" s="44" t="n"/>
-      <c r="O98" s="45" t="n"/>
-      <c r="P98" s="46" t="n"/>
-      <c r="Q98" s="44" t="n"/>
-      <c r="R98" s="44" t="n"/>
-      <c r="S98" s="44" t="n"/>
-      <c r="T98" s="44" t="n"/>
-      <c r="U98" s="44" t="n"/>
-      <c r="V98" s="44" t="n"/>
-      <c r="W98" s="44" t="n"/>
-      <c r="X98" s="44" t="n"/>
-      <c r="Y98" s="44" t="n"/>
-      <c r="Z98" s="44" t="n"/>
-      <c r="AA98" s="44" t="n"/>
-      <c r="AB98" s="44" t="n"/>
+      <c r="B98" s="427" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C98" s="270" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D98" s="271" t="n">
+        <v>1085</v>
+      </c>
+      <c r="E98" s="37" t="n">
+        <v>1715</v>
+      </c>
+      <c r="F98" s="38">
+        <f>IFERROR(D98+E98+G98+U98+Y98,0)</f>
+        <v>2800.0</v>
+      </c>
+      <c r="G98" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B98,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B98+1))</f>
+        <v>2964.0</v>
+      </c>
+      <c r="I98" s="274">
+        <f>IFERROR(F98-H98,0)</f>
+        <v>-164.0</v>
+      </c>
+      <c r="J98" s="275">
+        <f>IFERROR(I98/F98,0)</f>
+        <v>-0.058571</v>
+      </c>
+      <c r="K98" s="250" t="n"/>
+      <c r="L98" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M98" s="323" t="n"/>
+      <c r="N98" s="324" t="n"/>
+      <c r="O98" s="325" t="n"/>
+      <c r="P98" s="326" t="n"/>
+      <c r="Q98" s="324" t="n"/>
+      <c r="R98" s="428">
+        <f>IFERROR(D98*$T$7,0)</f>
+        <v>44.05</v>
+      </c>
+      <c r="S98" s="324" t="n"/>
+      <c r="T98" s="324" t="n"/>
+      <c r="U98" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" s="324" t="n"/>
+      <c r="X98" s="324" t="n"/>
+      <c r="Y98" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="324" t="n"/>
+      <c r="AB98" s="324" t="n"/>
     </row>
     <row r="99" ht="16.5" customHeight="1" s="331">
-      <c r="B99" s="34" t="n"/>
-      <c r="C99" s="47" t="n"/>
-      <c r="D99" s="48" t="n"/>
-      <c r="E99" s="49" t="n"/>
-      <c r="F99" s="50" t="n"/>
-      <c r="G99" s="51" t="n"/>
-      <c r="H99" s="52" t="n"/>
-      <c r="I99" s="53" t="n"/>
-      <c r="J99" s="54" t="n"/>
-      <c r="K99" s="55" t="n"/>
-      <c r="L99" s="18" t="n"/>
-      <c r="M99" s="21" t="n"/>
-      <c r="N99" s="56" t="n"/>
-      <c r="O99" s="57" t="n"/>
-      <c r="P99" s="58" t="n"/>
-      <c r="Q99" s="56" t="n"/>
-      <c r="R99" s="56" t="n"/>
-      <c r="S99" s="56" t="n"/>
-      <c r="T99" s="56" t="n"/>
-      <c r="U99" s="56" t="n"/>
-      <c r="V99" s="56" t="n"/>
-      <c r="W99" s="56" t="n"/>
-      <c r="X99" s="56" t="n"/>
-      <c r="Y99" s="56" t="n"/>
-      <c r="Z99" s="56" t="n"/>
-      <c r="AA99" s="56" t="n"/>
-      <c r="AB99" s="56" t="n"/>
+      <c r="B99" s="427" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C99" s="255" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D99" s="256" t="n">
+        <v>500</v>
+      </c>
+      <c r="E99" s="49" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F99" s="50">
+        <f>IFERROR(D99+E99+G99+U99+Y99,0)</f>
+        <v>1910.0</v>
+      </c>
+      <c r="G99" s="257" t="n">
+        <v>250</v>
+      </c>
+      <c r="H99" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B99,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B99+1))</f>
+        <v>698.0</v>
+      </c>
+      <c r="I99" s="259">
+        <f>IFERROR(F99-H99,0)</f>
+        <v>1212.0</v>
+      </c>
+      <c r="J99" s="260">
+        <f>IFERROR(I99/F99,0)</f>
+        <v>0.634555</v>
+      </c>
+      <c r="K99" s="254" t="n"/>
+      <c r="L99" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M99" s="291" t="n"/>
+      <c r="N99" s="292" t="n"/>
+      <c r="O99" s="293" t="n"/>
+      <c r="P99" s="294" t="n"/>
+      <c r="Q99" s="292" t="n"/>
+      <c r="R99" s="443">
+        <f>IFERROR(D99*$T$7,0)</f>
+        <v>20.3</v>
+      </c>
+      <c r="S99" s="292" t="n"/>
+      <c r="T99" s="292" t="n"/>
+      <c r="U99" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" s="292" t="n"/>
+      <c r="X99" s="292" t="n"/>
+      <c r="Y99" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="292" t="n"/>
+      <c r="AB99" s="292" t="n"/>
     </row>
     <row r="100" ht="16.5" customHeight="1" s="331">
-      <c r="B100" s="34" t="n"/>
-      <c r="C100" s="35" t="n"/>
-      <c r="D100" s="36" t="n"/>
-      <c r="E100" s="37" t="n"/>
-      <c r="F100" s="38" t="n"/>
-      <c r="G100" s="39" t="n"/>
-      <c r="H100" s="40" t="n"/>
-      <c r="I100" s="41" t="n"/>
-      <c r="J100" s="42" t="n"/>
-      <c r="K100" s="43" t="n"/>
-      <c r="L100" s="9" t="n"/>
-      <c r="M100" s="12" t="n"/>
-      <c r="N100" s="44" t="n"/>
-      <c r="O100" s="45" t="n"/>
-      <c r="P100" s="46" t="n"/>
-      <c r="Q100" s="44" t="n"/>
-      <c r="R100" s="44" t="n"/>
-      <c r="S100" s="44" t="n"/>
-      <c r="T100" s="44" t="n"/>
-      <c r="U100" s="44" t="n"/>
-      <c r="V100" s="44" t="n"/>
-      <c r="W100" s="44" t="n"/>
-      <c r="X100" s="44" t="n"/>
-      <c r="Y100" s="44" t="n"/>
-      <c r="Z100" s="44" t="n"/>
-      <c r="AA100" s="44" t="n"/>
-      <c r="AB100" s="44" t="n"/>
+      <c r="B100" s="427" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C100" s="270" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D100" s="271" t="n">
+        <v>2910</v>
+      </c>
+      <c r="E100" s="37" t="n">
+        <v>2765</v>
+      </c>
+      <c r="F100" s="38">
+        <f>IFERROR(D100+E100+G100+U100+Y100,0)</f>
+        <v>5675.0</v>
+      </c>
+      <c r="G100" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B100,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B100+1))</f>
+        <v>0.0</v>
+      </c>
+      <c r="I100" s="274">
+        <f>IFERROR(F100-H100,0)</f>
+        <v>5675.0</v>
+      </c>
+      <c r="J100" s="275">
+        <f>IFERROR(I100/F100,0)</f>
+        <v>1.0</v>
+      </c>
+      <c r="K100" s="250" t="n"/>
+      <c r="L100" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M100" s="323" t="n"/>
+      <c r="N100" s="324" t="n"/>
+      <c r="O100" s="325" t="n"/>
+      <c r="P100" s="326" t="n"/>
+      <c r="Q100" s="324" t="n"/>
+      <c r="R100" s="428">
+        <f>IFERROR(D100*$T$7,0)</f>
+        <v>118.15</v>
+      </c>
+      <c r="S100" s="324" t="n"/>
+      <c r="T100" s="324" t="n"/>
+      <c r="U100" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" s="324" t="n"/>
+      <c r="X100" s="324" t="n"/>
+      <c r="Y100" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="324" t="n"/>
+      <c r="AB100" s="324" t="n"/>
     </row>
     <row r="101" ht="16.5" customHeight="1" s="331">
-      <c r="B101" s="34" t="n"/>
-      <c r="C101" s="47" t="n"/>
-      <c r="D101" s="48" t="n"/>
-      <c r="E101" s="49" t="n"/>
-      <c r="F101" s="50" t="n"/>
-      <c r="G101" s="51" t="n"/>
-      <c r="H101" s="52" t="n"/>
-      <c r="I101" s="53" t="n"/>
-      <c r="J101" s="54" t="n"/>
-      <c r="K101" s="55" t="n"/>
-      <c r="L101" s="18" t="n"/>
-      <c r="M101" s="21" t="n"/>
-      <c r="N101" s="56" t="n"/>
-      <c r="O101" s="57" t="n"/>
-      <c r="P101" s="58" t="n"/>
-      <c r="Q101" s="56" t="n"/>
-      <c r="R101" s="56" t="n"/>
-      <c r="S101" s="56" t="n"/>
-      <c r="T101" s="56" t="n"/>
-      <c r="U101" s="56" t="n"/>
-      <c r="V101" s="56" t="n"/>
-      <c r="W101" s="56" t="n"/>
-      <c r="X101" s="56" t="n"/>
-      <c r="Y101" s="56" t="n"/>
-      <c r="Z101" s="56" t="n"/>
-      <c r="AA101" s="56" t="n"/>
-      <c r="AB101" s="56" t="n"/>
+      <c r="B101" s="427" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C101" s="255" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D101" s="256" t="n">
+        <v>835</v>
+      </c>
+      <c r="E101" s="49" t="n">
+        <v>2815</v>
+      </c>
+      <c r="F101" s="50">
+        <f>IFERROR(D101+E101+G101+U101+Y101,0)</f>
+        <v>3910.0</v>
+      </c>
+      <c r="G101" s="257" t="n">
+        <v>260</v>
+      </c>
+      <c r="H101" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B101,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B101+1))</f>
+        <v>565.0</v>
+      </c>
+      <c r="I101" s="259">
+        <f>IFERROR(F101-H101,0)</f>
+        <v>3345.0</v>
+      </c>
+      <c r="J101" s="260">
+        <f>IFERROR(I101/F101,0)</f>
+        <v>0.855499</v>
+      </c>
+      <c r="K101" s="254" t="n"/>
+      <c r="L101" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M101" s="291" t="n"/>
+      <c r="N101" s="292" t="n"/>
+      <c r="O101" s="293" t="n"/>
+      <c r="P101" s="294" t="n"/>
+      <c r="Q101" s="292" t="n"/>
+      <c r="R101" s="443">
+        <f>IFERROR(D101*$T$7,0)</f>
+        <v>33.9</v>
+      </c>
+      <c r="S101" s="292" t="n"/>
+      <c r="T101" s="292" t="n"/>
+      <c r="U101" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" s="292" t="n"/>
+      <c r="X101" s="292" t="n"/>
+      <c r="Y101" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="292" t="n"/>
+      <c r="AB101" s="292" t="n"/>
     </row>
     <row r="102" ht="16.5" customHeight="1" s="331">
-      <c r="B102" s="34" t="n"/>
-      <c r="C102" s="35" t="n"/>
-      <c r="D102" s="36" t="n"/>
-      <c r="E102" s="37" t="n"/>
-      <c r="F102" s="38" t="n"/>
-      <c r="G102" s="39" t="n"/>
-      <c r="H102" s="40" t="n"/>
-      <c r="I102" s="41" t="n"/>
-      <c r="J102" s="42" t="n"/>
-      <c r="K102" s="43" t="n"/>
-      <c r="L102" s="9" t="n"/>
-      <c r="M102" s="12" t="n"/>
-      <c r="N102" s="44" t="n"/>
-      <c r="O102" s="45" t="n"/>
-      <c r="P102" s="46" t="n"/>
-      <c r="Q102" s="44" t="n"/>
-      <c r="R102" s="44" t="n"/>
-      <c r="S102" s="44" t="n"/>
-      <c r="T102" s="44" t="n"/>
-      <c r="U102" s="44" t="n"/>
-      <c r="V102" s="44" t="n"/>
-      <c r="W102" s="44" t="n"/>
-      <c r="X102" s="44" t="n"/>
-      <c r="Y102" s="44" t="n"/>
-      <c r="Z102" s="44" t="n"/>
-      <c r="AA102" s="44" t="n"/>
-      <c r="AB102" s="44" t="n"/>
+      <c r="B102" s="427" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C102" s="270" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D102" s="271" t="n">
+        <v>1110</v>
+      </c>
+      <c r="E102" s="37" t="n">
+        <v>590</v>
+      </c>
+      <c r="F102" s="38">
+        <f>IFERROR(D102+E102+G102+U102+Y102,0)</f>
+        <v>1935.0</v>
+      </c>
+      <c r="G102" s="272" t="n">
+        <v>235</v>
+      </c>
+      <c r="H102" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B102,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B102+1))</f>
+        <v>2071.0</v>
+      </c>
+      <c r="I102" s="274">
+        <f>IFERROR(F102-H102,0)</f>
+        <v>-136.0</v>
+      </c>
+      <c r="J102" s="275">
+        <f>IFERROR(I102/F102,0)</f>
+        <v>-0.070284</v>
+      </c>
+      <c r="K102" s="250" t="n"/>
+      <c r="L102" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M102" s="323" t="n"/>
+      <c r="N102" s="324" t="n"/>
+      <c r="O102" s="325" t="n"/>
+      <c r="P102" s="326" t="n"/>
+      <c r="Q102" s="324" t="n"/>
+      <c r="R102" s="428">
+        <f>IFERROR(D102*$T$7,0)</f>
+        <v>45.07</v>
+      </c>
+      <c r="S102" s="324" t="n"/>
+      <c r="T102" s="324" t="n"/>
+      <c r="U102" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" s="324" t="n"/>
+      <c r="X102" s="324" t="n"/>
+      <c r="Y102" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="324" t="n"/>
+      <c r="AB102" s="324" t="n"/>
     </row>
     <row r="103" ht="16.5" customHeight="1" s="331">
-      <c r="B103" s="34" t="n"/>
-      <c r="C103" s="47" t="n"/>
-      <c r="D103" s="48" t="n"/>
-      <c r="E103" s="49" t="n"/>
-      <c r="F103" s="50" t="n"/>
-      <c r="G103" s="51" t="n"/>
-      <c r="H103" s="52" t="n"/>
-      <c r="I103" s="53" t="n"/>
-      <c r="J103" s="54" t="n"/>
-      <c r="K103" s="55" t="n"/>
-      <c r="L103" s="18" t="n"/>
-      <c r="M103" s="21" t="n"/>
-      <c r="N103" s="56" t="n"/>
-      <c r="O103" s="57" t="n"/>
-      <c r="P103" s="58" t="n"/>
-      <c r="Q103" s="56" t="n"/>
-      <c r="R103" s="56" t="n"/>
-      <c r="S103" s="56" t="n"/>
-      <c r="T103" s="56" t="n"/>
-      <c r="U103" s="56" t="n"/>
-      <c r="V103" s="56" t="n"/>
-      <c r="W103" s="56" t="n"/>
-      <c r="X103" s="56" t="n"/>
-      <c r="Y103" s="56" t="n"/>
-      <c r="Z103" s="56" t="n"/>
-      <c r="AA103" s="56" t="n"/>
-      <c r="AB103" s="56" t="n"/>
+      <c r="B103" s="427" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C103" s="255" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D103" s="256" t="n">
+        <v>110</v>
+      </c>
+      <c r="E103" s="49" t="n">
+        <v>980</v>
+      </c>
+      <c r="F103" s="50">
+        <f>IFERROR(D103+E103+G103+U103+Y103,0)</f>
+        <v>2160.0</v>
+      </c>
+      <c r="G103" s="257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B103,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B103+1))</f>
+        <v>6970.0</v>
+      </c>
+      <c r="I103" s="259">
+        <f>IFERROR(F103-H103,0)</f>
+        <v>-4810.0</v>
+      </c>
+      <c r="J103" s="260">
+        <f>IFERROR(I103/F103,0)</f>
+        <v>-2.226852</v>
+      </c>
+      <c r="K103" s="254" t="n"/>
+      <c r="L103" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M103" s="291" t="n"/>
+      <c r="N103" s="292" t="n"/>
+      <c r="O103" s="293" t="n"/>
+      <c r="P103" s="294" t="n"/>
+      <c r="Q103" s="292" t="n"/>
+      <c r="R103" s="443">
+        <f>IFERROR(D103*$T$7,0)</f>
+        <v>4.47</v>
+      </c>
+      <c r="S103" s="292" t="n"/>
+      <c r="T103" s="292" t="n"/>
+      <c r="U103" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" s="292" t="n"/>
+      <c r="X103" s="292" t="n"/>
+      <c r="Y103" s="443" t="n">
+        <v>1070</v>
+      </c>
+      <c r="Z103" s="443" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="AA103" s="292" t="n"/>
+      <c r="AB103" s="292" t="n"/>
     </row>
     <row r="104" ht="16.5" customHeight="1" s="331">
-      <c r="B104" s="34" t="n"/>
-      <c r="C104" s="35" t="n"/>
-      <c r="D104" s="36" t="n"/>
-      <c r="E104" s="37" t="n"/>
-      <c r="F104" s="38" t="n"/>
-      <c r="G104" s="39" t="n"/>
-      <c r="H104" s="40" t="n"/>
-      <c r="I104" s="41" t="n"/>
-      <c r="J104" s="42" t="n"/>
-      <c r="K104" s="43" t="n"/>
-      <c r="L104" s="9" t="n"/>
-      <c r="M104" s="12" t="n"/>
-      <c r="N104" s="44" t="n"/>
-      <c r="O104" s="45" t="n"/>
-      <c r="P104" s="46" t="n"/>
-      <c r="Q104" s="44" t="n"/>
-      <c r="R104" s="44" t="n"/>
-      <c r="S104" s="44" t="n"/>
-      <c r="T104" s="44" t="n"/>
-      <c r="U104" s="44" t="n"/>
-      <c r="V104" s="44" t="n"/>
-      <c r="W104" s="44" t="n"/>
-      <c r="X104" s="44" t="n"/>
-      <c r="Y104" s="44" t="n"/>
-      <c r="Z104" s="44" t="n"/>
-      <c r="AA104" s="44" t="n"/>
-      <c r="AB104" s="44" t="n"/>
+      <c r="B104" s="427" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C104" s="270" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D104" s="271" t="n">
+        <v>875</v>
+      </c>
+      <c r="E104" s="37" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F104" s="38">
+        <f>IFERROR(D104+E104+G104+U104+Y104,0)</f>
+        <v>3755.0</v>
+      </c>
+      <c r="G104" s="272" t="n">
+        <v>130</v>
+      </c>
+      <c r="H104" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B104,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B104+1))</f>
+        <v>1438.0</v>
+      </c>
+      <c r="I104" s="274">
+        <f>IFERROR(F104-H104,0)</f>
+        <v>2317.0</v>
+      </c>
+      <c r="J104" s="275">
+        <f>IFERROR(I104/F104,0)</f>
+        <v>0.617044</v>
+      </c>
+      <c r="K104" s="250" t="n"/>
+      <c r="L104" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M104" s="323" t="n"/>
+      <c r="N104" s="324" t="n"/>
+      <c r="O104" s="325" t="n"/>
+      <c r="P104" s="326" t="n"/>
+      <c r="Q104" s="324" t="n"/>
+      <c r="R104" s="428">
+        <f>IFERROR(D104*$T$7,0)</f>
+        <v>35.52</v>
+      </c>
+      <c r="S104" s="324" t="n"/>
+      <c r="T104" s="324" t="n"/>
+      <c r="U104" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" s="324" t="n"/>
+      <c r="X104" s="324" t="n"/>
+      <c r="Y104" s="428" t="n">
+        <v>1490</v>
+      </c>
+      <c r="Z104" s="428" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="AA104" s="324" t="n"/>
+      <c r="AB104" s="324" t="n"/>
     </row>
     <row r="105" ht="16.5" customHeight="1" s="331">
       <c r="B105" s="34" t="n"/>
@@ -24082,8 +24520,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
@@ -24107,7 +24545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J679"/>
+  <dimension ref="A1:J706"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -52805,6 +53243,1167 @@
         </is>
       </c>
       <c r="J679" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="B680" s="429" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C680" s="297" t="inlineStr">
+        <is>
+          <t>Eggs</t>
+        </is>
+      </c>
+      <c r="D680" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E680" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Eggs</t>
+        </is>
+      </c>
+      <c r="F680" s="299" t="n">
+        <v>136</v>
+      </c>
+      <c r="G680" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H680" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I680" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J680" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="B681" s="429" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C681" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D681" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E681" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F681" s="299" t="n">
+        <v>212</v>
+      </c>
+      <c r="G681" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H681" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I681" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J681" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="B682" s="429" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C682" s="297" t="inlineStr">
+        <is>
+          <t>Pescado</t>
+        </is>
+      </c>
+      <c r="D682" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E682" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat &amp; Fish</t>
+        </is>
+      </c>
+      <c r="F682" s="299" t="n">
+        <v>259</v>
+      </c>
+      <c r="G682" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H682" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I682" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J682" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="B683" s="429" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C683" s="297" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="D683" s="298" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E683" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F683" s="299" t="n">
+        <v>151</v>
+      </c>
+      <c r="G683" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H683" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I683" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J683" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="B684" s="429" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C684" s="297" t="inlineStr">
+        <is>
+          <t>Pescado</t>
+        </is>
+      </c>
+      <c r="D684" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E684" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat &amp; Fish</t>
+        </is>
+      </c>
+      <c r="F684" s="299" t="n">
+        <v>452</v>
+      </c>
+      <c r="G684" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H684" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I684" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J684" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="B685" s="429" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C685" s="297" t="inlineStr">
+        <is>
+          <t>Hielo</t>
+        </is>
+      </c>
+      <c r="D685" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E685" s="297" t="inlineStr">
+        <is>
+          <t>Kitchen Supplies</t>
+        </is>
+      </c>
+      <c r="F685" s="299" t="n">
+        <v>200</v>
+      </c>
+      <c r="G685" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H685" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I685" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J685" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="B686" s="429" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C686" s="297" t="inlineStr">
+        <is>
+          <t>Agua Natural</t>
+        </is>
+      </c>
+      <c r="D686" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E686" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F686" s="299" t="n">
+        <v>45</v>
+      </c>
+      <c r="G686" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H686" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I686" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J686" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="B687" s="429" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C687" s="297" t="inlineStr">
+        <is>
+          <t>Molino</t>
+        </is>
+      </c>
+      <c r="D687" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E687" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F687" s="299" t="n">
+        <v>80</v>
+      </c>
+      <c r="G687" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H687" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I687" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J687" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="B688" s="429" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C688" s="297" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D688" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E688" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F688" s="299" t="n">
+        <v>1429</v>
+      </c>
+      <c r="G688" s="300" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H688" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I688" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J688" s="423" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="B689" s="429" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C689" s="297" t="inlineStr">
+        <is>
+          <t>Queso</t>
+        </is>
+      </c>
+      <c r="D689" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E689" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Dairy</t>
+        </is>
+      </c>
+      <c r="F689" s="299" t="n">
+        <v>558</v>
+      </c>
+      <c r="G689" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H689" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I689" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J689" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="B690" s="429" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C690" s="297" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D690" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E690" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F690" s="299" t="n">
+        <v>140</v>
+      </c>
+      <c r="G690" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H690" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I690" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J690" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="B691" s="429" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C691" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D691" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E691" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F691" s="299" t="n">
+        <v>439</v>
+      </c>
+      <c r="G691" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H691" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I691" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J691" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="B692" s="429" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C692" s="297" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="D692" s="298" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E692" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F692" s="299" t="n">
+        <v>126</v>
+      </c>
+      <c r="G692" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H692" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I692" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J692" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="B693" s="429" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C693" s="297" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D693" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E693" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F693" s="299" t="n">
+        <v>93</v>
+      </c>
+      <c r="G693" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H693" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I693" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J693" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="B694" s="429" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C694" s="297" t="inlineStr">
+        <is>
+          <t>Pan Molido</t>
+        </is>
+      </c>
+      <c r="D694" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E694" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F694" s="299" t="n">
+        <v>72</v>
+      </c>
+      <c r="G694" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H694" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I694" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J694" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="B695" s="429" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C695" s="297" t="inlineStr">
+        <is>
+          <t>Oxxo Aceite</t>
+        </is>
+      </c>
+      <c r="D695" s="298" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E695" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F695" s="299" t="n">
+        <v>56</v>
+      </c>
+      <c r="G695" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H695" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I695" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J695" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="B696" s="429" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C696" s="297" t="inlineStr">
+        <is>
+          <t>Armando - salary</t>
+        </is>
+      </c>
+      <c r="D696" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E696" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F696" s="299" t="n">
+        <v>1850</v>
+      </c>
+      <c r="G696" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H696" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I696" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J696" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="B697" s="429" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C697" s="297" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D697" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E697" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F697" s="299" t="n">
+        <v>1210</v>
+      </c>
+      <c r="G697" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H697" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I697" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J697" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="B698" s="429" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C698" s="297" t="inlineStr">
+        <is>
+          <t>Soft app license</t>
+        </is>
+      </c>
+      <c r="D698" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E698" s="297" t="inlineStr">
+        <is>
+          <t>Software/Subscription</t>
+        </is>
+      </c>
+      <c r="F698" s="299" t="n">
+        <v>810</v>
+      </c>
+      <c r="G698" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H698" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I698" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J698" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="B699" s="429" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C699" s="297" t="inlineStr">
+        <is>
+          <t>Duvi - salary</t>
+        </is>
+      </c>
+      <c r="D699" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E699" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F699" s="299" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G699" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H699" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I699" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J699" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="B700" s="429" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C700" s="297" t="inlineStr">
+        <is>
+          <t>Jhon - salary</t>
+        </is>
+      </c>
+      <c r="D700" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E700" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F700" s="299" t="n">
+        <v>3750</v>
+      </c>
+      <c r="G700" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H700" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I700" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J700" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="B701" s="429" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C701" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D701" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E701" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F701" s="299" t="n">
+        <v>276</v>
+      </c>
+      <c r="G701" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H701" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I701" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J701" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="B702" s="429" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C702" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D702" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E702" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F702" s="299" t="n">
+        <v>293</v>
+      </c>
+      <c r="G702" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H702" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I702" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J702" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="B703" s="429" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C703" s="297" t="inlineStr">
+        <is>
+          <t>Oxxo Aceite</t>
+        </is>
+      </c>
+      <c r="D703" s="298" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E703" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F703" s="299" t="n">
+        <v>112</v>
+      </c>
+      <c r="G703" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H703" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I703" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J703" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="B704" s="429" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C704" s="297" t="inlineStr">
+        <is>
+          <t>Agua Natural</t>
+        </is>
+      </c>
+      <c r="D704" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E704" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F704" s="299" t="n">
+        <v>75</v>
+      </c>
+      <c r="G704" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H704" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I704" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J704" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="B705" s="429" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C705" s="297" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="D705" s="298" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E705" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F705" s="299" t="n">
+        <v>92</v>
+      </c>
+      <c r="G705" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H705" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I705" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J705" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="B706" s="429" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C706" s="297" t="inlineStr">
+        <is>
+          <t>Queso Panela</t>
+        </is>
+      </c>
+      <c r="D706" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E706" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Dairy</t>
+        </is>
+      </c>
+      <c r="F706" s="299" t="n">
+        <v>590</v>
+      </c>
+      <c r="G706" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H706" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I706" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J706" s="423" t="inlineStr">
         <is>
           <t>No receipt; cash</t>
         </is>
@@ -63422,7 +65021,7 @@
     <row r="20">
       <c r="A20" s="439" t="inlineStr">
         <is>
-          <t>Supermarket/General</t>
+          <t>Ingredients - Vegetables</t>
         </is>
       </c>
       <c r="B20" s="437">
@@ -63452,7 +65051,7 @@
     <row r="21">
       <c r="A21" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Vegetables</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="B21" s="437">
@@ -63512,7 +65111,7 @@
     <row r="23">
       <c r="A23" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Beverages</t>
+          <t>Ingredients - Dairy</t>
         </is>
       </c>
       <c r="B23" s="437">
@@ -63542,7 +65141,7 @@
     <row r="24">
       <c r="A24" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Dairy</t>
+          <t>Ingredients - Beverages</t>
         </is>
       </c>
       <c r="B24" s="437">
@@ -63662,7 +65261,7 @@
     <row r="28">
       <c r="A28" s="439" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Ingredients - Meat &amp; Fish</t>
         </is>
       </c>
       <c r="B28" s="437">
@@ -63692,7 +65291,7 @@
     <row r="29">
       <c r="A29" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Meat &amp; Fish</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B29" s="437">
@@ -63872,7 +65471,7 @@
     <row r="35">
       <c r="A35" s="439" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Software/Subscription</t>
         </is>
       </c>
       <c r="B35" s="437">
@@ -63902,7 +65501,7 @@
     <row r="36">
       <c r="A36" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Other</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="B36" s="437">
@@ -63932,7 +65531,7 @@
     <row r="37">
       <c r="A37" s="439" t="inlineStr">
         <is>
-          <t>Software/Subscription</t>
+          <t>Ingredients - Other</t>
         </is>
       </c>
       <c r="B37" s="437">
@@ -63992,7 +65591,7 @@
     <row r="39">
       <c r="A39" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Desserts</t>
+          <t>Ingredients - Eggs</t>
         </is>
       </c>
       <c r="B39" s="437">
@@ -64022,7 +65621,7 @@
     <row r="40">
       <c r="A40" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Eggs</t>
+          <t>Ingredients - Desserts</t>
         </is>
       </c>
       <c r="B40" s="437">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -10427,45 +10427,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>3755.0</v>
+        <v>3085.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>130.0</v>
+        <v>0.0</v>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>1438.0</v>
+        <v>7777.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>2317.0</v>
+        <v>-4692.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>0.617044</v>
+        <v>-1.520908</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>3755.0</v>
+        <v>6840.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>3755.0</v>
+        <v>6840.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>105258.0</v>
+        <v>3085.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>1438.0</v>
+        <v>9215.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>2317.0</v>
+        <v>-2375.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -16747,33 +16747,72 @@
       <c r="AB104" s="324" t="n"/>
     </row>
     <row r="105" ht="16.5" customHeight="1" s="331">
-      <c r="B105" s="34" t="n"/>
-      <c r="C105" s="47" t="n"/>
-      <c r="D105" s="48" t="n"/>
-      <c r="E105" s="49" t="n"/>
-      <c r="F105" s="50" t="n"/>
-      <c r="G105" s="51" t="n"/>
-      <c r="H105" s="52" t="n"/>
-      <c r="I105" s="53" t="n"/>
-      <c r="J105" s="54" t="n"/>
-      <c r="K105" s="55" t="n"/>
-      <c r="L105" s="18" t="n"/>
-      <c r="M105" s="21" t="n"/>
-      <c r="N105" s="56" t="n"/>
-      <c r="O105" s="57" t="n"/>
-      <c r="P105" s="58" t="n"/>
-      <c r="Q105" s="56" t="n"/>
-      <c r="R105" s="56" t="n"/>
-      <c r="S105" s="56" t="n"/>
-      <c r="T105" s="56" t="n"/>
-      <c r="U105" s="56" t="n"/>
-      <c r="V105" s="56" t="n"/>
-      <c r="W105" s="56" t="n"/>
-      <c r="X105" s="56" t="n"/>
-      <c r="Y105" s="56" t="n"/>
-      <c r="Z105" s="56" t="n"/>
-      <c r="AA105" s="56" t="n"/>
-      <c r="AB105" s="56" t="n"/>
+      <c r="B105" s="427" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C105" s="255" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D105" s="256" t="n">
+        <v>120</v>
+      </c>
+      <c r="E105" s="49" t="n">
+        <v>1480</v>
+      </c>
+      <c r="F105" s="50">
+        <f>IFERROR(D105+E105+G105+U105+Y105,0)</f>
+        <v>3085.0</v>
+      </c>
+      <c r="G105" s="257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B105,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B105+1))</f>
+        <v>7777.0</v>
+      </c>
+      <c r="I105" s="259">
+        <f>IFERROR(F105-H105,0)</f>
+        <v>-4692.0</v>
+      </c>
+      <c r="J105" s="260">
+        <f>IFERROR(I105/F105,0)</f>
+        <v>-1.520908</v>
+      </c>
+      <c r="K105" s="254" t="n"/>
+      <c r="L105" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M105" s="291" t="n"/>
+      <c r="N105" s="292" t="n"/>
+      <c r="O105" s="293" t="n"/>
+      <c r="P105" s="294" t="n"/>
+      <c r="Q105" s="292" t="n"/>
+      <c r="R105" s="443">
+        <f>IFERROR(D105*$T$7,0)</f>
+        <v>4.87</v>
+      </c>
+      <c r="S105" s="292" t="n"/>
+      <c r="T105" s="292" t="n"/>
+      <c r="U105" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" s="292" t="n"/>
+      <c r="X105" s="292" t="n"/>
+      <c r="Y105" s="443" t="n">
+        <v>1485</v>
+      </c>
+      <c r="Z105" s="443" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="AA105" s="292" t="n"/>
+      <c r="AB105" s="292" t="n"/>
     </row>
     <row r="106" ht="16.5" customHeight="1" s="331">
       <c r="B106" s="34" t="n"/>
@@ -24545,7 +24584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J706"/>
+  <dimension ref="A1:J714"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -54404,6 +54443,350 @@
         </is>
       </c>
       <c r="J706" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="B707" s="429" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C707" s="297" t="inlineStr">
+        <is>
+          <t>3B Aceite</t>
+        </is>
+      </c>
+      <c r="D707" s="298" t="inlineStr">
+        <is>
+          <t>Tres B</t>
+        </is>
+      </c>
+      <c r="E707" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F707" s="299" t="n">
+        <v>628</v>
+      </c>
+      <c r="G707" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H707" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I707" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J707" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="B708" s="429" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C708" s="297" t="inlineStr">
+        <is>
+          <t>Carne Hamburguesa</t>
+        </is>
+      </c>
+      <c r="D708" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E708" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F708" s="299" t="n">
+        <v>380</v>
+      </c>
+      <c r="G708" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H708" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I708" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J708" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="B709" s="429" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C709" s="297" t="inlineStr">
+        <is>
+          <t>Mole</t>
+        </is>
+      </c>
+      <c r="D709" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E709" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F709" s="299" t="n">
+        <v>890</v>
+      </c>
+      <c r="G709" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H709" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I709" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J709" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="B710" s="429" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C710" s="297" t="inlineStr">
+        <is>
+          <t>Chile pasilla</t>
+        </is>
+      </c>
+      <c r="D710" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E710" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F710" s="299" t="n">
+        <v>115</v>
+      </c>
+      <c r="G710" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H710" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I710" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J710" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="B711" s="429" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C711" s="297" t="inlineStr">
+        <is>
+          <t>Pan Reales</t>
+        </is>
+      </c>
+      <c r="D711" s="298" t="inlineStr">
+        <is>
+          <t>Pan Reales</t>
+        </is>
+      </c>
+      <c r="E711" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F711" s="299" t="n">
+        <v>416</v>
+      </c>
+      <c r="G711" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H711" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I711" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J711" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="B712" s="429" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C712" s="297" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D712" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E712" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F712" s="299" t="n">
+        <v>1032</v>
+      </c>
+      <c r="G712" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H712" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I712" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J712" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="B713" s="429" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C713" s="297" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="D713" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E713" s="297" t="inlineStr">
+        <is>
+          <t>Utilities/Gas</t>
+        </is>
+      </c>
+      <c r="F713" s="299" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G713" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H713" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I713" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J713" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="B714" s="429" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C714" s="297" t="inlineStr">
+        <is>
+          <t>Sams Club</t>
+        </is>
+      </c>
+      <c r="D714" s="298" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="E714" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F714" s="299" t="n">
+        <v>2816</v>
+      </c>
+      <c r="G714" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H714" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I714" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J714" s="423" t="inlineStr">
         <is>
           <t>No receipt; cash</t>
         </is>
@@ -64485,7 +64868,7 @@
     <col width="15" customWidth="1" style="331" min="3" max="5"/>
     <col width="15" customWidth="1" style="331" min="4" max="4"/>
     <col width="15" customWidth="1" style="331" min="5" max="5"/>
-    <col width="9" customWidth="1" style="331" min="6" max="14"/>
+    <col width="15" customWidth="1" style="331" min="6" max="14"/>
     <col width="9" customWidth="1" style="331" min="7" max="7"/>
     <col width="9" customWidth="1" style="331" min="8" max="8"/>
     <col width="9" customWidth="1" style="331" min="9" max="9"/>
@@ -64506,7 +64889,7 @@
       <c r="C1" s="432" t="n"/>
       <c r="D1" s="432" t="n"/>
       <c r="E1" s="432" t="n"/>
-      <c r="F1" s="433" t="n"/>
+      <c r="F1" s="432" t="n"/>
       <c r="G1" s="433" t="n"/>
       <c r="H1" s="433" t="n"/>
       <c r="I1" s="433" t="n"/>
@@ -64554,7 +64937,11 @@
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F3" s="433" t="n"/>
+      <c r="F3" s="435" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
       <c r="G3" s="433" t="n"/>
       <c r="H3" s="433" t="n"/>
       <c r="I3" s="433" t="n"/>
@@ -64584,7 +64971,10 @@
         <f>SUMIFS('📅 Daily Log'!$F$8:$F$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F4" s="433" t="n"/>
+      <c r="F4" s="437">
+        <f>SUMIFS('📅 Daily Log'!$F$8:$F$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G4" s="433" t="n"/>
       <c r="H4" s="433" t="n"/>
       <c r="I4" s="433" t="n"/>
@@ -64614,7 +65004,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F5" s="433" t="n"/>
+      <c r="F5" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G5" s="433" t="n"/>
       <c r="H5" s="433" t="n"/>
       <c r="I5" s="433" t="n"/>
@@ -64644,7 +65037,10 @@
         <f>E4-E5</f>
         <v/>
       </c>
-      <c r="F6" s="433" t="n"/>
+      <c r="F6" s="438">
+        <f>F4-F5</f>
+        <v/>
+      </c>
       <c r="G6" s="433" t="n"/>
       <c r="H6" s="433" t="n"/>
       <c r="I6" s="433" t="n"/>
@@ -64674,7 +65070,10 @@
         <f>COUNTIFS('📅 Daily Log'!$F$8:$F$5000,"&gt;0",'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F7" s="433" t="n"/>
+      <c r="F7" s="440">
+        <f>COUNTIFS('📅 Daily Log'!$F$8:$F$5000,"&gt;0",'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G7" s="433" t="n"/>
       <c r="H7" s="433" t="n"/>
       <c r="I7" s="433" t="n"/>
@@ -64704,7 +65103,10 @@
         <f>IFERROR(E4/E7,0)</f>
         <v/>
       </c>
-      <c r="F8" s="433" t="n"/>
+      <c r="F8" s="437">
+        <f>IFERROR(F4/F7,0)</f>
+        <v/>
+      </c>
       <c r="G8" s="433" t="n"/>
       <c r="H8" s="433" t="n"/>
       <c r="I8" s="433" t="n"/>
@@ -64752,7 +65154,11 @@
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F10" s="433" t="n"/>
+      <c r="F10" s="435" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
       <c r="G10" s="433" t="n"/>
       <c r="H10" s="433" t="n"/>
       <c r="I10" s="433" t="n"/>
@@ -64782,7 +65188,10 @@
         <f>SUMIFS('📅 Daily Log'!$D$8:$D$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F11" s="433" t="n"/>
+      <c r="F11" s="437">
+        <f>SUMIFS('📅 Daily Log'!$D$8:$D$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G11" s="433" t="n"/>
       <c r="H11" s="433" t="n"/>
       <c r="I11" s="433" t="n"/>
@@ -64812,7 +65221,10 @@
         <f>SUMIFS('📅 Daily Log'!$E$8:$E$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F12" s="433" t="n"/>
+      <c r="F12" s="437">
+        <f>SUMIFS('📅 Daily Log'!$E$8:$E$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G12" s="433" t="n"/>
       <c r="H12" s="433" t="n"/>
       <c r="I12" s="433" t="n"/>
@@ -64842,7 +65254,10 @@
         <f>SUMIFS('📅 Daily Log'!$G$8:$G$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F13" s="433" t="n"/>
+      <c r="F13" s="437">
+        <f>SUMIFS('📅 Daily Log'!$G$8:$G$5000,'📅 Daily Log'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'📅 Daily Log'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G13" s="433" t="n"/>
       <c r="H13" s="433" t="n"/>
       <c r="I13" s="433" t="n"/>
@@ -64872,7 +65287,10 @@
         <f>E11+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="433" t="n"/>
+      <c r="F14" s="438">
+        <f>F11+F12+F13</f>
+        <v/>
+      </c>
       <c r="G14" s="433" t="n"/>
       <c r="H14" s="433" t="n"/>
       <c r="I14" s="433" t="n"/>
@@ -64920,7 +65338,11 @@
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F16" s="433" t="n"/>
+      <c r="F16" s="435" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
       <c r="G16" s="433" t="n"/>
       <c r="H16" s="433" t="n"/>
       <c r="I16" s="433" t="n"/>
@@ -64950,7 +65372,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A17,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F17" s="433" t="n"/>
+      <c r="F17" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A17,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G17" s="433" t="n"/>
       <c r="H17" s="433" t="n"/>
       <c r="I17" s="433" t="n"/>
@@ -64980,7 +65405,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A18,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F18" s="433" t="n"/>
+      <c r="F18" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A18,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G18" s="433" t="n"/>
       <c r="H18" s="433" t="n"/>
       <c r="I18" s="433" t="n"/>
@@ -65010,7 +65438,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A19,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F19" s="433" t="n"/>
+      <c r="F19" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A19,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G19" s="433" t="n"/>
       <c r="H19" s="433" t="n"/>
       <c r="I19" s="433" t="n"/>
@@ -65021,7 +65452,7 @@
     <row r="20">
       <c r="A20" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Vegetables</t>
+          <t>Supermarket/General</t>
         </is>
       </c>
       <c r="B20" s="437">
@@ -65040,7 +65471,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A20,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F20" s="433" t="n"/>
+      <c r="F20" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A20,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G20" s="433" t="n"/>
       <c r="H20" s="433" t="n"/>
       <c r="I20" s="433" t="n"/>
@@ -65051,7 +65485,7 @@
     <row r="21">
       <c r="A21" s="439" t="inlineStr">
         <is>
-          <t>Supermarket/General</t>
+          <t>Ingredients - Vegetables</t>
         </is>
       </c>
       <c r="B21" s="437">
@@ -65070,7 +65504,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A21,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F21" s="433" t="n"/>
+      <c r="F21" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A21,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G21" s="433" t="n"/>
       <c r="H21" s="433" t="n"/>
       <c r="I21" s="433" t="n"/>
@@ -65100,7 +65537,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A22,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F22" s="433" t="n"/>
+      <c r="F22" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A22,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G22" s="433" t="n"/>
       <c r="H22" s="433" t="n"/>
       <c r="I22" s="433" t="n"/>
@@ -65130,7 +65570,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A23,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F23" s="433" t="n"/>
+      <c r="F23" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A23,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G23" s="433" t="n"/>
       <c r="H23" s="433" t="n"/>
       <c r="I23" s="433" t="n"/>
@@ -65160,7 +65603,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A24,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F24" s="433" t="n"/>
+      <c r="F24" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A24,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G24" s="433" t="n"/>
       <c r="H24" s="433" t="n"/>
       <c r="I24" s="433" t="n"/>
@@ -65190,7 +65636,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A25,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F25" s="433" t="n"/>
+      <c r="F25" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A25,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G25" s="433" t="n"/>
       <c r="H25" s="433" t="n"/>
       <c r="I25" s="433" t="n"/>
@@ -65220,7 +65669,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A26,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F26" s="433" t="n"/>
+      <c r="F26" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A26,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G26" s="433" t="n"/>
       <c r="H26" s="433" t="n"/>
       <c r="I26" s="433" t="n"/>
@@ -65250,7 +65702,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A27,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F27" s="433" t="n"/>
+      <c r="F27" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A27,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G27" s="433" t="n"/>
       <c r="H27" s="433" t="n"/>
       <c r="I27" s="433" t="n"/>
@@ -65280,7 +65735,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A28,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F28" s="433" t="n"/>
+      <c r="F28" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A28,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G28" s="433" t="n"/>
       <c r="H28" s="433" t="n"/>
       <c r="I28" s="433" t="n"/>
@@ -65310,7 +65768,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A29,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F29" s="433" t="n"/>
+      <c r="F29" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A29,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G29" s="433" t="n"/>
       <c r="H29" s="433" t="n"/>
       <c r="I29" s="433" t="n"/>
@@ -65321,7 +65782,7 @@
     <row r="30">
       <c r="A30" s="439" t="inlineStr">
         <is>
-          <t>Packaging/Disposables</t>
+          <t>Utilities/Gas</t>
         </is>
       </c>
       <c r="B30" s="437">
@@ -65340,7 +65801,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A30,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F30" s="433" t="n"/>
+      <c r="F30" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A30,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G30" s="433" t="n"/>
       <c r="H30" s="433" t="n"/>
       <c r="I30" s="433" t="n"/>
@@ -65351,7 +65815,7 @@
     <row r="31">
       <c r="A31" s="439" t="inlineStr">
         <is>
-          <t>Utilities/Gas</t>
+          <t>Packaging/Disposables</t>
         </is>
       </c>
       <c r="B31" s="437">
@@ -65370,7 +65834,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A31,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F31" s="433" t="n"/>
+      <c r="F31" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A31,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G31" s="433" t="n"/>
       <c r="H31" s="433" t="n"/>
       <c r="I31" s="433" t="n"/>
@@ -65400,7 +65867,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A32,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F32" s="433" t="n"/>
+      <c r="F32" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A32,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G32" s="433" t="n"/>
       <c r="H32" s="433" t="n"/>
       <c r="I32" s="433" t="n"/>
@@ -65430,7 +65900,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A33,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F33" s="433" t="n"/>
+      <c r="F33" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A33,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G33" s="433" t="n"/>
       <c r="H33" s="433" t="n"/>
       <c r="I33" s="433" t="n"/>
@@ -65460,7 +65933,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A34,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F34" s="433" t="n"/>
+      <c r="F34" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A34,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G34" s="433" t="n"/>
       <c r="H34" s="433" t="n"/>
       <c r="I34" s="433" t="n"/>
@@ -65490,7 +65966,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A35,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F35" s="433" t="n"/>
+      <c r="F35" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A35,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G35" s="433" t="n"/>
       <c r="H35" s="433" t="n"/>
       <c r="I35" s="433" t="n"/>
@@ -65520,7 +65999,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A36,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F36" s="433" t="n"/>
+      <c r="F36" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A36,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G36" s="433" t="n"/>
       <c r="H36" s="433" t="n"/>
       <c r="I36" s="433" t="n"/>
@@ -65550,7 +66032,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A37,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F37" s="433" t="n"/>
+      <c r="F37" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A37,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G37" s="433" t="n"/>
       <c r="H37" s="433" t="n"/>
       <c r="I37" s="433" t="n"/>
@@ -65580,7 +66065,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A38,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F38" s="433" t="n"/>
+      <c r="F38" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A38,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G38" s="433" t="n"/>
       <c r="H38" s="433" t="n"/>
       <c r="I38" s="433" t="n"/>
@@ -65610,7 +66098,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A39,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F39" s="433" t="n"/>
+      <c r="F39" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A39,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G39" s="433" t="n"/>
       <c r="H39" s="433" t="n"/>
       <c r="I39" s="433" t="n"/>
@@ -65640,7 +66131,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A40,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F40" s="433" t="n"/>
+      <c r="F40" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A40,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G40" s="433" t="n"/>
       <c r="H40" s="433" t="n"/>
       <c r="I40" s="433" t="n"/>
@@ -65670,7 +66164,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A41,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F41" s="433" t="n"/>
+      <c r="F41" s="437">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$E$8:$E$5000,$A41,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G41" s="433" t="n"/>
       <c r="H41" s="433" t="n"/>
       <c r="I41" s="433" t="n"/>
@@ -65700,7 +66197,10 @@
         <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,8,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
-      <c r="F42" s="433" t="n"/>
+      <c r="F42" s="438">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;DATE(2026,9,1),'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;DATE(2026,10,1))</f>
+        <v/>
+      </c>
       <c r="G42" s="433" t="n"/>
       <c r="H42" s="433" t="n"/>
       <c r="I42" s="433" t="n"/>
@@ -65730,7 +66230,10 @@
         <f>E4-E42</f>
         <v/>
       </c>
-      <c r="F43" s="433" t="n"/>
+      <c r="F43" s="438">
+        <f>F4-F42</f>
+        <v/>
+      </c>
       <c r="G43" s="433" t="n"/>
       <c r="H43" s="433" t="n"/>
       <c r="I43" s="433" t="n"/>
@@ -65978,7 +66481,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5509,11 +5509,11 @@
         </is>
       </c>
       <c r="C147" s="268" t="n">
-        <v>3411.85</v>
+        <v>14778.53</v>
       </c>
       <c r="E147" s="286" t="inlineStr">
         <is>
-          <t>Operating costs funded from partner capital, net of repayments. Funded: 20,000 (rent Jul) + 17,200.04 (rent Aug) + 8,789 (luz Aug) + 19,314.81 (liquidacion ledger) = 65,303.85. Repaid from operating cash: 20,000 (21-Jul) + 2,587 (22-Jul) + 10,301 (05-Aug) = 32,888. Still owed by Operations: 32,415.85.</t>
+          <t>Operating costs funded from partner capital, net of repayments. Latest addition 04-Sep-2026 $19,066.68. Still owed by Operations: $22,478.53.</t>
         </is>
       </c>
     </row>
@@ -5531,11 +5531,11 @@
         </is>
       </c>
       <c r="C149" s="444" t="n">
-        <v>-61892</v>
+        <v>-69592</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Cumulative repaid from operating cash (latest 31-Aug-2026 $10,000.00). Reduces advance owed &amp; Cash-on-Hand; NOT a P&amp;L expense.</t>
+          <t>Cumulative repaid from operating cash (latest 04-Sep-2026 $7,700.00). Reduces advance owed &amp; Cash-on-Hand; NOT a P&amp;L expense.</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="331" min="1" max="1"/>
@@ -8570,30 +8570,63 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="430" t="inlineStr">
+      <c r="A81" s="430" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B81" s="232" t="inlineStr">
+        <is>
+          <t>Settlement - restaurant paid Lohith</t>
+        </is>
+      </c>
+      <c r="C81" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D81" s="232" t="n"/>
+      <c r="E81" s="233" t="n">
+        <v>650.5</v>
+      </c>
+      <c r="F81" s="233">
+        <f>IFERROR(F80+D81-E81,0)</f>
+        <v/>
+      </c>
+      <c r="G81" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H81" s="232" t="inlineStr">
+        <is>
+          <t>Ledger settled from operating cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="430" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B81" s="232" t="n"/>
-      <c r="C81" s="232" t="n"/>
-      <c r="D81" s="232">
-        <f>SUM(D4:D80)</f>
+      <c r="B82" s="232" t="n"/>
+      <c r="C82" s="232" t="n"/>
+      <c r="D82" s="232">
+        <f>SUM(D4:D81)</f>
         <v/>
       </c>
-      <c r="E81" s="233">
-        <f>SUM(E4:E80)</f>
+      <c r="E82" s="233">
+        <f>SUM(E4:E81)</f>
         <v/>
       </c>
-      <c r="F81" s="233">
-        <f>F80</f>
+      <c r="F82" s="233">
+        <f>F81</f>
         <v/>
       </c>
-      <c r="G81" s="232">
-        <f>IF(F80&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F80,"#,##0"),IF(F80&lt;0,"Lohith holds $"&amp;TEXT(ABS(F80),"#,##0"),"Zero balance"))</f>
+      <c r="G82" s="232">
+        <f>IF(F81&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F81,"#,##0"),IF(F81&lt;0,"Lohith holds $"&amp;TEXT(ABS(F81),"#,##0"),"Zero balance"))</f>
         <v/>
       </c>
-      <c r="H81" s="232" t="n"/>
+      <c r="H82" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10427,7 +10460,7 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>3085.0</v>
+        <v>10740.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
@@ -10435,37 +10468,37 @@
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>7777.0</v>
+        <v>5505.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>-4692.0</v>
+        <v>5235.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>-1.520908</v>
+        <v>0.48743</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>6840.0</v>
+        <v>21765.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>6840.0</v>
+        <v>21765.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>3085.0</v>
+        <v>18010.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>9215.0</v>
+        <v>15408.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>-2375.0</v>
+        <v>6357.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -16763,7 +16796,7 @@
       </c>
       <c r="F105" s="50">
         <f>IFERROR(D105+E105+G105+U105+Y105,0)</f>
-        <v>3085.0</v>
+        <v>3240.0</v>
       </c>
       <c r="G105" s="257" t="n">
         <v>0</v>
@@ -16774,16 +16807,16 @@
       </c>
       <c r="I105" s="259">
         <f>IFERROR(F105-H105,0)</f>
-        <v>-4692.0</v>
+        <v>-4537.0</v>
       </c>
       <c r="J105" s="260">
         <f>IFERROR(I105/F105,0)</f>
-        <v>-1.520908</v>
+        <v>-1.400309</v>
       </c>
       <c r="K105" s="254" t="n"/>
       <c r="L105" s="261" t="inlineStr">
         <is>
-          <t>Cierre via loka.py</t>
+          <t>Cierre via loka.py | updated 23:07</t>
         </is>
       </c>
       <c r="M105" s="291" t="n"/>
@@ -16806,71 +16839,149 @@
       <c r="W105" s="292" t="n"/>
       <c r="X105" s="292" t="n"/>
       <c r="Y105" s="443" t="n">
-        <v>1485</v>
+        <v>1640</v>
       </c>
       <c r="Z105" s="443" t="n">
-        <v>28.21</v>
+        <v>31.15</v>
       </c>
       <c r="AA105" s="292" t="n"/>
       <c r="AB105" s="292" t="n"/>
     </row>
     <row r="106" ht="16.5" customHeight="1" s="331">
-      <c r="B106" s="34" t="n"/>
-      <c r="C106" s="35" t="n"/>
-      <c r="D106" s="36" t="n"/>
-      <c r="E106" s="37" t="n"/>
-      <c r="F106" s="38" t="n"/>
-      <c r="G106" s="39" t="n"/>
-      <c r="H106" s="40" t="n"/>
-      <c r="I106" s="41" t="n"/>
-      <c r="J106" s="42" t="n"/>
-      <c r="K106" s="43" t="n"/>
-      <c r="L106" s="9" t="n"/>
-      <c r="M106" s="12" t="n"/>
-      <c r="N106" s="44" t="n"/>
-      <c r="O106" s="45" t="n"/>
-      <c r="P106" s="46" t="n"/>
-      <c r="Q106" s="44" t="n"/>
-      <c r="R106" s="44" t="n"/>
-      <c r="S106" s="44" t="n"/>
-      <c r="T106" s="44" t="n"/>
-      <c r="U106" s="44" t="n"/>
-      <c r="V106" s="44" t="n"/>
-      <c r="W106" s="44" t="n"/>
-      <c r="X106" s="44" t="n"/>
-      <c r="Y106" s="44" t="n"/>
-      <c r="Z106" s="44" t="n"/>
-      <c r="AA106" s="44" t="n"/>
-      <c r="AB106" s="44" t="n"/>
+      <c r="B106" s="427" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C106" s="270" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D106" s="271" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E106" s="37" t="n">
+        <v>1765</v>
+      </c>
+      <c r="F106" s="38">
+        <f>IFERROR(D106+E106+G106+U106+Y106,0)</f>
+        <v>4030.0</v>
+      </c>
+      <c r="G106" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B106,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B106+1))</f>
+        <v>688.0</v>
+      </c>
+      <c r="I106" s="274">
+        <f>IFERROR(F106-H106,0)</f>
+        <v>3342.0</v>
+      </c>
+      <c r="J106" s="275">
+        <f>IFERROR(I106/F106,0)</f>
+        <v>0.82928</v>
+      </c>
+      <c r="K106" s="250" t="n"/>
+      <c r="L106" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M106" s="323" t="n"/>
+      <c r="N106" s="324" t="n"/>
+      <c r="O106" s="325" t="n"/>
+      <c r="P106" s="326" t="n"/>
+      <c r="Q106" s="324" t="n"/>
+      <c r="R106" s="428">
+        <f>IFERROR(D106*$T$7,0)</f>
+        <v>52.78</v>
+      </c>
+      <c r="S106" s="324" t="n"/>
+      <c r="T106" s="324" t="n"/>
+      <c r="U106" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" s="324" t="n"/>
+      <c r="X106" s="324" t="n"/>
+      <c r="Y106" s="428" t="n">
+        <v>965</v>
+      </c>
+      <c r="Z106" s="428" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="AA106" s="324" t="n"/>
+      <c r="AB106" s="324" t="n"/>
     </row>
     <row r="107" ht="16.5" customHeight="1" s="331">
-      <c r="B107" s="34" t="n"/>
-      <c r="C107" s="47" t="n"/>
-      <c r="D107" s="48" t="n"/>
-      <c r="E107" s="49" t="n"/>
-      <c r="F107" s="50" t="n"/>
-      <c r="G107" s="51" t="n"/>
-      <c r="H107" s="52" t="n"/>
-      <c r="I107" s="53" t="n"/>
-      <c r="J107" s="54" t="n"/>
-      <c r="K107" s="55" t="n"/>
-      <c r="L107" s="18" t="n"/>
-      <c r="M107" s="21" t="n"/>
-      <c r="N107" s="56" t="n"/>
-      <c r="O107" s="57" t="n"/>
-      <c r="P107" s="58" t="n"/>
-      <c r="Q107" s="56" t="n"/>
-      <c r="R107" s="56" t="n"/>
-      <c r="S107" s="56" t="n"/>
-      <c r="T107" s="56" t="n"/>
-      <c r="U107" s="56" t="n"/>
-      <c r="V107" s="56" t="n"/>
-      <c r="W107" s="56" t="n"/>
-      <c r="X107" s="56" t="n"/>
-      <c r="Y107" s="56" t="n"/>
-      <c r="Z107" s="56" t="n"/>
-      <c r="AA107" s="56" t="n"/>
-      <c r="AB107" s="56" t="n"/>
+      <c r="B107" s="427" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C107" s="255" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D107" s="256" t="n">
+        <v>6620</v>
+      </c>
+      <c r="E107" s="49" t="n">
+        <v>3030</v>
+      </c>
+      <c r="F107" s="50">
+        <f>IFERROR(D107+E107+G107+U107+Y107,0)</f>
+        <v>10740.0</v>
+      </c>
+      <c r="G107" s="257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B107,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B107+1))</f>
+        <v>5505.0</v>
+      </c>
+      <c r="I107" s="259">
+        <f>IFERROR(F107-H107,0)</f>
+        <v>5235.0</v>
+      </c>
+      <c r="J107" s="260">
+        <f>IFERROR(I107/F107,0)</f>
+        <v>0.48743</v>
+      </c>
+      <c r="K107" s="254" t="n"/>
+      <c r="L107" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M107" s="291" t="n"/>
+      <c r="N107" s="292" t="n"/>
+      <c r="O107" s="293" t="n"/>
+      <c r="P107" s="294" t="n"/>
+      <c r="Q107" s="292" t="n"/>
+      <c r="R107" s="443">
+        <f>IFERROR(D107*$T$7,0)</f>
+        <v>268.77</v>
+      </c>
+      <c r="S107" s="292" t="n"/>
+      <c r="T107" s="292" t="n"/>
+      <c r="U107" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" s="292" t="n"/>
+      <c r="X107" s="292" t="n"/>
+      <c r="Y107" s="443" t="n">
+        <v>1090</v>
+      </c>
+      <c r="Z107" s="443" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="AA107" s="292" t="n"/>
+      <c r="AB107" s="292" t="n"/>
     </row>
     <row r="108" ht="16.5" customHeight="1" s="331">
       <c r="B108" s="34" t="n"/>
@@ -24559,9 +24670,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -24584,7 +24695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J714"/>
+  <dimension ref="A1:J727"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -54789,6 +54900,565 @@
       <c r="J714" s="423" t="inlineStr">
         <is>
           <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="B715" s="429" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C715" s="297" t="inlineStr">
+        <is>
+          <t>Jamon</t>
+        </is>
+      </c>
+      <c r="D715" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E715" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F715" s="299" t="n">
+        <v>89</v>
+      </c>
+      <c r="G715" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H715" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I715" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J715" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="B716" s="429" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C716" s="297" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="D716" s="298" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E716" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F716" s="299" t="n">
+        <v>149</v>
+      </c>
+      <c r="G716" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H716" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I716" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J716" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="B717" s="429" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C717" s="297" t="inlineStr">
+        <is>
+          <t>Avia</t>
+        </is>
+      </c>
+      <c r="D717" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E717" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F717" s="299" t="n">
+        <v>450</v>
+      </c>
+      <c r="G717" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H717" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I717" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J717" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="B718" s="429" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C718" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D718" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E718" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F718" s="299" t="n">
+        <v>1934</v>
+      </c>
+      <c r="G718" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H718" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I718" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J718" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="B719" s="429" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C719" s="297" t="inlineStr">
+        <is>
+          <t>Vessels</t>
+        </is>
+      </c>
+      <c r="D719" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E719" s="297" t="inlineStr">
+        <is>
+          <t>Kitchen Supplies</t>
+        </is>
+      </c>
+      <c r="F719" s="299" t="n">
+        <v>1245</v>
+      </c>
+      <c r="G719" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H719" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I719" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J719" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="B720" s="429" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C720" s="297" t="inlineStr">
+        <is>
+          <t>Pan Reales</t>
+        </is>
+      </c>
+      <c r="D720" s="298" t="inlineStr">
+        <is>
+          <t>Pan Reales</t>
+        </is>
+      </c>
+      <c r="E720" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F720" s="299" t="n">
+        <v>451</v>
+      </c>
+      <c r="G720" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H720" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I720" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J720" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="B721" s="429" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C721" s="297" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D721" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E721" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F721" s="299" t="n">
+        <v>213</v>
+      </c>
+      <c r="G721" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H721" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I721" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J721" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="B722" s="429" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C722" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D722" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E722" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F722" s="299" t="n">
+        <v>450</v>
+      </c>
+      <c r="G722" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H722" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I722" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J722" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="B723" s="429" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C723" s="297" t="inlineStr">
+        <is>
+          <t>Pescado</t>
+        </is>
+      </c>
+      <c r="D723" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E723" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat &amp; Fish</t>
+        </is>
+      </c>
+      <c r="F723" s="299" t="n">
+        <v>333</v>
+      </c>
+      <c r="G723" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H723" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I723" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J723" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="B724" s="429" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C724" s="297" t="inlineStr">
+        <is>
+          <t>Oxxo</t>
+        </is>
+      </c>
+      <c r="D724" s="298" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E724" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F724" s="299" t="n">
+        <v>79</v>
+      </c>
+      <c r="G724" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H724" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I724" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J724" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="B725" s="429" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C725" s="297" t="inlineStr">
+        <is>
+          <t>Jhon - salary</t>
+        </is>
+      </c>
+      <c r="D725" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E725" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F725" s="299" t="n">
+        <v>500</v>
+      </c>
+      <c r="G725" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H725" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I725" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J725" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="B726" s="429" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C726" s="297" t="inlineStr">
+        <is>
+          <t>Armando - salary</t>
+        </is>
+      </c>
+      <c r="D726" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E726" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F726" s="299" t="n">
+        <v>300</v>
+      </c>
+      <c r="G726" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H726" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I726" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J726" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="B727" s="429" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C727" s="297" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D727" s="298" t="inlineStr">
+        <is>
+          <t>No Bill</t>
+        </is>
+      </c>
+      <c r="E727" s="297" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="F727" s="299" t="n">
+        <v>19066.68</v>
+      </c>
+      <c r="G727" s="300" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H727" s="300" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="I727" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J727" s="423" t="inlineStr">
+        <is>
+          <t>Paid from Capital</t>
         </is>
       </c>
     </row>
@@ -65551,7 +66221,7 @@
     <row r="23">
       <c r="A23" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Dairy</t>
+          <t>Ingredients - Beverages</t>
         </is>
       </c>
       <c r="B23" s="437">
@@ -65584,7 +66254,7 @@
     <row r="24">
       <c r="A24" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Beverages</t>
+          <t>Ingredients - Dairy</t>
         </is>
       </c>
       <c r="B24" s="437">
@@ -65848,7 +66518,7 @@
     <row r="32">
       <c r="A32" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Fruit</t>
+          <t>Kitchen Supplies</t>
         </is>
       </c>
       <c r="B32" s="437">
@@ -65881,7 +66551,7 @@
     <row r="33">
       <c r="A33" s="439" t="inlineStr">
         <is>
-          <t>Kitchen Supplies</t>
+          <t>Ingredients - Fruit</t>
         </is>
       </c>
       <c r="B33" s="437">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -10460,7 +10460,7 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>10740.0</v>
+        <v>4839.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
@@ -10468,37 +10468,37 @@
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>5505.0</v>
+        <v>19881.68</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>5235.0</v>
+        <v>-15042.68</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>0.48743</v>
+        <v>-3.108634</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>21765.0</v>
+        <v>26604.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>21765.0</v>
+        <v>26604.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>18010.0</v>
+        <v>22849.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>15408.0</v>
+        <v>35289.68</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>6357.0</v>
+        <v>-8685.68</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -16984,33 +16984,72 @@
       <c r="AB107" s="292" t="n"/>
     </row>
     <row r="108" ht="16.5" customHeight="1" s="331">
-      <c r="B108" s="34" t="n"/>
-      <c r="C108" s="35" t="n"/>
-      <c r="D108" s="36" t="n"/>
-      <c r="E108" s="37" t="n"/>
-      <c r="F108" s="38" t="n"/>
-      <c r="G108" s="39" t="n"/>
-      <c r="H108" s="40" t="n"/>
-      <c r="I108" s="41" t="n"/>
-      <c r="J108" s="42" t="n"/>
-      <c r="K108" s="43" t="n"/>
-      <c r="L108" s="9" t="n"/>
-      <c r="M108" s="12" t="n"/>
-      <c r="N108" s="44" t="n"/>
-      <c r="O108" s="45" t="n"/>
-      <c r="P108" s="46" t="n"/>
-      <c r="Q108" s="44" t="n"/>
-      <c r="R108" s="44" t="n"/>
-      <c r="S108" s="44" t="n"/>
-      <c r="T108" s="44" t="n"/>
-      <c r="U108" s="44" t="n"/>
-      <c r="V108" s="44" t="n"/>
-      <c r="W108" s="44" t="n"/>
-      <c r="X108" s="44" t="n"/>
-      <c r="Y108" s="44" t="n"/>
-      <c r="Z108" s="44" t="n"/>
-      <c r="AA108" s="44" t="n"/>
-      <c r="AB108" s="44" t="n"/>
+      <c r="B108" s="427" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C108" s="270" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D108" s="271" t="n">
+        <v>825</v>
+      </c>
+      <c r="E108" s="37" t="n">
+        <v>1974</v>
+      </c>
+      <c r="F108" s="38">
+        <f>IFERROR(D108+E108+G108+U108+Y108,0)</f>
+        <v>4839.0</v>
+      </c>
+      <c r="G108" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B108,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B108+1))</f>
+        <v>19881.68</v>
+      </c>
+      <c r="I108" s="274">
+        <f>IFERROR(F108-H108,0)</f>
+        <v>-15042.68</v>
+      </c>
+      <c r="J108" s="275">
+        <f>IFERROR(I108/F108,0)</f>
+        <v>-3.108634</v>
+      </c>
+      <c r="K108" s="250" t="n"/>
+      <c r="L108" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M108" s="323" t="n"/>
+      <c r="N108" s="324" t="n"/>
+      <c r="O108" s="325" t="n"/>
+      <c r="P108" s="326" t="n"/>
+      <c r="Q108" s="324" t="n"/>
+      <c r="R108" s="428">
+        <f>IFERROR(D108*$T$7,0)</f>
+        <v>33.49</v>
+      </c>
+      <c r="S108" s="324" t="n"/>
+      <c r="T108" s="324" t="n"/>
+      <c r="U108" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" s="324" t="n"/>
+      <c r="X108" s="324" t="n"/>
+      <c r="Y108" s="428" t="n">
+        <v>2040</v>
+      </c>
+      <c r="Z108" s="428" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="AA108" s="324" t="n"/>
+      <c r="AB108" s="324" t="n"/>
     </row>
     <row r="109" ht="16.5" customHeight="1" s="331">
       <c r="B109" s="34" t="n"/>
@@ -24695,7 +24734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J727"/>
+  <dimension ref="A1:J731"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -55459,6 +55498,178 @@
       <c r="J727" s="423" t="inlineStr">
         <is>
           <t>Paid from Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="B728" s="429" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C728" s="297" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D728" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E728" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F728" s="299" t="n">
+        <v>117</v>
+      </c>
+      <c r="G728" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H728" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I728" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J728" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="B729" s="429" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C729" s="297" t="inlineStr">
+        <is>
+          <t>Mayonesa</t>
+        </is>
+      </c>
+      <c r="D729" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E729" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Other</t>
+        </is>
+      </c>
+      <c r="F729" s="299" t="n">
+        <v>227</v>
+      </c>
+      <c r="G729" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H729" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I729" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J729" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="B730" s="429" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C730" s="297" t="inlineStr">
+        <is>
+          <t>Abastos</t>
+        </is>
+      </c>
+      <c r="D730" s="298" t="inlineStr">
+        <is>
+          <t>Central de Abastos</t>
+        </is>
+      </c>
+      <c r="E730" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F730" s="299" t="n">
+        <v>125</v>
+      </c>
+      <c r="G730" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H730" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I730" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J730" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="B731" s="429" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C731" s="297" t="inlineStr">
+        <is>
+          <t>Basicos</t>
+        </is>
+      </c>
+      <c r="D731" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E731" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F731" s="299" t="n">
+        <v>346</v>
+      </c>
+      <c r="G731" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H731" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I731" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J731" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
         </is>
       </c>
     </row>
@@ -66650,7 +66861,7 @@
     <row r="36">
       <c r="A36" s="439" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Ingredients - Other</t>
         </is>
       </c>
       <c r="B36" s="437">
@@ -66683,7 +66894,7 @@
     <row r="37">
       <c r="A37" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Other</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="B37" s="437">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5967,7 +5967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="331" min="1" max="1"/>
@@ -8603,30 +8603,63 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="430" t="inlineStr">
+      <c r="A82" s="430" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B82" s="232" t="inlineStr">
+        <is>
+          <t>Wallmart $123 (paid by Lohith)</t>
+        </is>
+      </c>
+      <c r="C82" s="232" t="inlineStr">
+        <is>
+          <t>Expense - Personal</t>
+        </is>
+      </c>
+      <c r="D82" s="232" t="n">
+        <v>123</v>
+      </c>
+      <c r="E82" s="233" t="n"/>
+      <c r="F82" s="233">
+        <f>IFERROR(F81+D82-E82,0)</f>
+        <v/>
+      </c>
+      <c r="G82" s="232" t="inlineStr">
+        <is>
+          <t>⏳ Reimburse</t>
+        </is>
+      </c>
+      <c r="H82" s="232" t="inlineStr">
+        <is>
+          <t>Fronted from own pocket; excluded from till via cash_adjust</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="430" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B82" s="232" t="n"/>
-      <c r="C82" s="232" t="n"/>
-      <c r="D82" s="232">
-        <f>SUM(D4:D81)</f>
+      <c r="B83" s="232" t="n"/>
+      <c r="C83" s="232" t="n"/>
+      <c r="D83" s="232">
+        <f>SUM(D4:D82)</f>
         <v/>
       </c>
-      <c r="E82" s="233">
-        <f>SUM(E4:E81)</f>
+      <c r="E83" s="233">
+        <f>SUM(E4:E82)</f>
         <v/>
       </c>
-      <c r="F82" s="233">
-        <f>F81</f>
+      <c r="F83" s="233">
+        <f>F82</f>
         <v/>
       </c>
-      <c r="G82" s="232">
-        <f>IF(F81&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F81,"#,##0"),IF(F81&lt;0,"Lohith holds $"&amp;TEXT(ABS(F81),"#,##0"),"Zero balance"))</f>
+      <c r="G83" s="232">
+        <f>IF(F82&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F82,"#,##0"),IF(F82&lt;0,"Lohith holds $"&amp;TEXT(ABS(F82),"#,##0"),"Zero balance"))</f>
         <v/>
       </c>
-      <c r="H82" s="232" t="n"/>
+      <c r="H83" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10460,7 +10493,7 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>4839.0</v>
+        <v>3885.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
@@ -10468,37 +10501,37 @@
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>19881.68</v>
+        <v>6288.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>-15042.68</v>
+        <v>-2403.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>-3.108634</v>
+        <v>-0.618533</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>26604.0</v>
+        <v>3885.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>26604.0</v>
+        <v>3885.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>22849.0</v>
+        <v>29429.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>35289.68</v>
+        <v>6288.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>-8685.68</v>
+        <v>-2403.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -17052,62 +17085,140 @@
       <c r="AB108" s="324" t="n"/>
     </row>
     <row r="109" ht="16.5" customHeight="1" s="331">
-      <c r="B109" s="34" t="n"/>
-      <c r="C109" s="47" t="n"/>
-      <c r="D109" s="48" t="n"/>
-      <c r="E109" s="49" t="n"/>
-      <c r="F109" s="50" t="n"/>
-      <c r="G109" s="51" t="n"/>
-      <c r="H109" s="52" t="n"/>
-      <c r="I109" s="53" t="n"/>
-      <c r="J109" s="54" t="n"/>
-      <c r="K109" s="55" t="n"/>
-      <c r="L109" s="18" t="n"/>
-      <c r="M109" s="21" t="n"/>
-      <c r="N109" s="56" t="n"/>
-      <c r="O109" s="57" t="n"/>
-      <c r="P109" s="58" t="n"/>
-      <c r="Q109" s="56" t="n"/>
-      <c r="R109" s="56" t="n"/>
-      <c r="S109" s="56" t="n"/>
-      <c r="T109" s="56" t="n"/>
-      <c r="U109" s="56" t="n"/>
-      <c r="V109" s="56" t="n"/>
-      <c r="W109" s="56" t="n"/>
-      <c r="X109" s="56" t="n"/>
-      <c r="Y109" s="56" t="n"/>
-      <c r="Z109" s="56" t="n"/>
-      <c r="AA109" s="56" t="n"/>
-      <c r="AB109" s="56" t="n"/>
+      <c r="B109" s="427" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C109" s="255" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D109" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="49" t="n">
+        <v>1590</v>
+      </c>
+      <c r="F109" s="50">
+        <f>IFERROR(D109+E109+G109+U109+Y109,0)</f>
+        <v>2695.0</v>
+      </c>
+      <c r="G109" s="257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B109,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B109+1))</f>
+        <v>9182.0</v>
+      </c>
+      <c r="I109" s="259">
+        <f>IFERROR(F109-H109,0)</f>
+        <v>-6487.0</v>
+      </c>
+      <c r="J109" s="260">
+        <f>IFERROR(I109/F109,0)</f>
+        <v>-2.40705</v>
+      </c>
+      <c r="K109" s="254" t="n"/>
+      <c r="L109" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M109" s="291" t="n"/>
+      <c r="N109" s="292" t="n"/>
+      <c r="O109" s="293" t="n"/>
+      <c r="P109" s="294" t="n"/>
+      <c r="Q109" s="292" t="n"/>
+      <c r="R109" s="443">
+        <f>IFERROR(D109*$T$7,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="S109" s="292" t="n"/>
+      <c r="T109" s="292" t="n"/>
+      <c r="U109" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" s="292" t="n"/>
+      <c r="X109" s="292" t="n"/>
+      <c r="Y109" s="443" t="n">
+        <v>1105</v>
+      </c>
+      <c r="Z109" s="443" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA109" s="292" t="n"/>
+      <c r="AB109" s="292" t="n"/>
     </row>
     <row r="110" ht="16.5" customHeight="1" s="331">
-      <c r="B110" s="34" t="n"/>
-      <c r="C110" s="35" t="n"/>
-      <c r="D110" s="36" t="n"/>
-      <c r="E110" s="37" t="n"/>
-      <c r="F110" s="38" t="n"/>
-      <c r="G110" s="39" t="n"/>
-      <c r="H110" s="40" t="n"/>
-      <c r="I110" s="41" t="n"/>
-      <c r="J110" s="42" t="n"/>
-      <c r="K110" s="43" t="n"/>
-      <c r="L110" s="9" t="n"/>
-      <c r="M110" s="12" t="n"/>
-      <c r="N110" s="44" t="n"/>
-      <c r="O110" s="45" t="n"/>
-      <c r="P110" s="46" t="n"/>
-      <c r="Q110" s="44" t="n"/>
-      <c r="R110" s="44" t="n"/>
-      <c r="S110" s="44" t="n"/>
-      <c r="T110" s="44" t="n"/>
-      <c r="U110" s="44" t="n"/>
-      <c r="V110" s="44" t="n"/>
-      <c r="W110" s="44" t="n"/>
-      <c r="X110" s="44" t="n"/>
-      <c r="Y110" s="44" t="n"/>
-      <c r="Z110" s="44" t="n"/>
-      <c r="AA110" s="44" t="n"/>
-      <c r="AB110" s="44" t="n"/>
+      <c r="B110" s="427" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C110" s="270" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D110" s="271" t="n">
+        <v>1740</v>
+      </c>
+      <c r="E110" s="37" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F110" s="38">
+        <f>IFERROR(D110+E110+G110+U110+Y110,0)</f>
+        <v>3885.0</v>
+      </c>
+      <c r="G110" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B110,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B110+1))</f>
+        <v>6288.0</v>
+      </c>
+      <c r="I110" s="274">
+        <f>IFERROR(F110-H110,0)</f>
+        <v>-2403.0</v>
+      </c>
+      <c r="J110" s="275">
+        <f>IFERROR(I110/F110,0)</f>
+        <v>-0.618533</v>
+      </c>
+      <c r="K110" s="250" t="n"/>
+      <c r="L110" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M110" s="323" t="n"/>
+      <c r="N110" s="324" t="n"/>
+      <c r="O110" s="325" t="n"/>
+      <c r="P110" s="326" t="n"/>
+      <c r="Q110" s="324" t="n"/>
+      <c r="R110" s="428">
+        <f>IFERROR(D110*$T$7,0)</f>
+        <v>70.64</v>
+      </c>
+      <c r="S110" s="324" t="n"/>
+      <c r="T110" s="324" t="n"/>
+      <c r="U110" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" s="324" t="n"/>
+      <c r="X110" s="324" t="n"/>
+      <c r="Y110" s="428" t="n">
+        <v>1075</v>
+      </c>
+      <c r="Z110" s="428" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="AA110" s="324" t="n"/>
+      <c r="AB110" s="324" t="n"/>
     </row>
     <row r="111" ht="16.5" customHeight="1" s="331">
       <c r="B111" s="34" t="n"/>
@@ -24709,9 +24820,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I2:P2"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B5:P5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:P2"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -24734,7 +24845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J731"/>
+  <dimension ref="A1:J748"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -55670,6 +55781,737 @@
       <c r="J731" s="423" t="inlineStr">
         <is>
           <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="B732" s="429" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C732" s="297" t="inlineStr">
+        <is>
+          <t>Aramando - salary</t>
+        </is>
+      </c>
+      <c r="D732" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E732" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F732" s="299" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G732" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H732" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I732" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J732" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="B733" s="429" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C733" s="297" t="inlineStr">
+        <is>
+          <t>Duvi - salary</t>
+        </is>
+      </c>
+      <c r="D733" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E733" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F733" s="299" t="n">
+        <v>1460</v>
+      </c>
+      <c r="G733" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H733" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I733" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J733" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="B734" s="429" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C734" s="297" t="inlineStr">
+        <is>
+          <t>Jhon - salary</t>
+        </is>
+      </c>
+      <c r="D734" s="298" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E734" s="297" t="inlineStr">
+        <is>
+          <t>Staff - Salary</t>
+        </is>
+      </c>
+      <c r="F734" s="299" t="n">
+        <v>3750</v>
+      </c>
+      <c r="G734" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H734" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I734" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J734" s="423" t="inlineStr">
+        <is>
+          <t>Weekly salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="B735" s="429" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C735" s="297" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D735" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E735" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F735" s="299" t="n">
+        <v>1380</v>
+      </c>
+      <c r="G735" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H735" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I735" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J735" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="B736" s="429" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C736" s="297" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="D736" s="298" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E736" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F736" s="299" t="n">
+        <v>303</v>
+      </c>
+      <c r="G736" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H736" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I736" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J736" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="B737" s="429" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C737" s="297" t="inlineStr">
+        <is>
+          <t>Jamon</t>
+        </is>
+      </c>
+      <c r="D737" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E737" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F737" s="299" t="n">
+        <v>89</v>
+      </c>
+      <c r="G737" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H737" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I737" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J737" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="B738" s="429" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C738" s="297" t="inlineStr">
+        <is>
+          <t>Lechugas</t>
+        </is>
+      </c>
+      <c r="D738" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E738" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F738" s="299" t="n">
+        <v>60</v>
+      </c>
+      <c r="G738" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H738" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I738" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J738" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="B739" s="429" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C739" s="297" t="inlineStr">
+        <is>
+          <t>Vegetales</t>
+        </is>
+      </c>
+      <c r="D739" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E739" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F739" s="299" t="n">
+        <v>200</v>
+      </c>
+      <c r="G739" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H739" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I739" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J739" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="B740" s="429" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C740" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D740" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E740" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F740" s="299" t="n">
+        <v>3327</v>
+      </c>
+      <c r="G740" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H740" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I740" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J740" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="B741" s="429" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C741" s="297" t="inlineStr">
+        <is>
+          <t>Caramelo</t>
+        </is>
+      </c>
+      <c r="D741" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E741" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Other</t>
+        </is>
+      </c>
+      <c r="F741" s="299" t="n">
+        <v>95</v>
+      </c>
+      <c r="G741" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H741" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I741" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J741" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="B742" s="429" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C742" s="297" t="inlineStr">
+        <is>
+          <t>Guimar</t>
+        </is>
+      </c>
+      <c r="D742" s="298" t="inlineStr">
+        <is>
+          <t>Guimar Polietilenos</t>
+        </is>
+      </c>
+      <c r="E742" s="297" t="inlineStr">
+        <is>
+          <t>Packaging/Disposables</t>
+        </is>
+      </c>
+      <c r="F742" s="299" t="n">
+        <v>24</v>
+      </c>
+      <c r="G742" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H742" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I742" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J742" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="B743" s="429" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C743" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D743" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E743" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F743" s="299" t="n">
+        <v>498</v>
+      </c>
+      <c r="G743" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H743" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I743" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J743" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="B744" s="429" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C744" s="297" t="inlineStr">
+        <is>
+          <t>Jamon</t>
+        </is>
+      </c>
+      <c r="D744" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E744" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F744" s="299" t="n">
+        <v>176</v>
+      </c>
+      <c r="G744" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H744" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I744" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J744" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="B745" s="429" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C745" s="297" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="D745" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E745" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F745" s="299" t="n">
+        <v>925</v>
+      </c>
+      <c r="G745" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H745" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I745" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J745" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="B746" s="429" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C746" s="297" t="inlineStr">
+        <is>
+          <t>Electric Issue</t>
+        </is>
+      </c>
+      <c r="D746" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E746" s="297" t="inlineStr">
+        <is>
+          <t>Utilities/Electricity</t>
+        </is>
+      </c>
+      <c r="F746" s="299" t="n">
+        <v>600</v>
+      </c>
+      <c r="G746" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H746" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I746" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J746" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="B747" s="429" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C747" s="297" t="inlineStr">
+        <is>
+          <t>Oxxo Arroz</t>
+        </is>
+      </c>
+      <c r="D747" s="298" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E747" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F747" s="299" t="n">
+        <v>260</v>
+      </c>
+      <c r="G747" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H747" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I747" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J747" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="B748" s="429" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C748" s="297" t="inlineStr">
+        <is>
+          <t>Wallmart</t>
+        </is>
+      </c>
+      <c r="D748" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E748" s="297" t="inlineStr">
+        <is>
+          <t>Supplies/Other</t>
+        </is>
+      </c>
+      <c r="F748" s="299" t="n">
+        <v>123</v>
+      </c>
+      <c r="G748" s="300" t="inlineStr">
+        <is>
+          <t>Lohith</t>
+        </is>
+      </c>
+      <c r="H748" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I748" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J748" s="423" t="inlineStr">
+        <is>
+          <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
         </is>
       </c>
     </row>
@@ -66828,7 +67670,7 @@
     <row r="35">
       <c r="A35" s="439" t="inlineStr">
         <is>
-          <t>Software/Subscription</t>
+          <t>Ingredients - Other</t>
         </is>
       </c>
       <c r="B35" s="437">
@@ -66861,7 +67703,7 @@
     <row r="36">
       <c r="A36" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Other</t>
+          <t>Software/Subscription</t>
         </is>
       </c>
       <c r="B36" s="437">

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5967,7 +5967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="331" min="1" max="1"/>
@@ -8636,30 +8636,63 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="430" t="inlineStr">
+      <c r="A83" s="430" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B83" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 08-Sep)</t>
+        </is>
+      </c>
+      <c r="C83" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D83" s="232" t="n"/>
+      <c r="E83" s="233" t="n">
+        <v>275</v>
+      </c>
+      <c r="F83" s="233">
+        <f>IFERROR(F82+D83-E83,0)</f>
+        <v/>
+      </c>
+      <c r="G83" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H83" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="430" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B83" s="232" t="n"/>
-      <c r="C83" s="232" t="n"/>
-      <c r="D83" s="232">
-        <f>SUM(D4:D82)</f>
+      <c r="B84" s="232" t="n"/>
+      <c r="C84" s="232" t="n"/>
+      <c r="D84" s="232">
+        <f>SUM(D4:D83)</f>
         <v/>
       </c>
-      <c r="E83" s="233">
-        <f>SUM(E4:E82)</f>
+      <c r="E84" s="233">
+        <f>SUM(E4:E83)</f>
         <v/>
       </c>
-      <c r="F83" s="233">
-        <f>F82</f>
+      <c r="F84" s="233">
+        <f>F83</f>
         <v/>
       </c>
-      <c r="G83" s="232">
-        <f>IF(F82&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F82,"#,##0"),IF(F82&lt;0,"Lohith holds $"&amp;TEXT(ABS(F82),"#,##0"),"Zero balance"))</f>
+      <c r="G84" s="232">
+        <f>IF(F83&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F83,"#,##0"),IF(F83&lt;0,"Lohith holds $"&amp;TEXT(ABS(F83),"#,##0"),"Zero balance"))</f>
         <v/>
       </c>
-      <c r="H83" s="232" t="n"/>
+      <c r="H84" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10493,45 +10526,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>3885.0</v>
+        <v>2935.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>0.0</v>
+        <v>275.0</v>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>6288.0</v>
+        <v>1980.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>-2403.0</v>
+        <v>955.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>-0.618533</v>
+        <v>0.325383</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>3885.0</v>
+        <v>6820.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>3885.0</v>
+        <v>6820.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>29429.0</v>
+        <v>32364.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>6288.0</v>
+        <v>8268.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>-2403.0</v>
+        <v>-1448.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -17221,33 +17254,72 @@
       <c r="AB110" s="324" t="n"/>
     </row>
     <row r="111" ht="16.5" customHeight="1" s="331">
-      <c r="B111" s="34" t="n"/>
-      <c r="C111" s="47" t="n"/>
-      <c r="D111" s="48" t="n"/>
-      <c r="E111" s="49" t="n"/>
-      <c r="F111" s="50" t="n"/>
-      <c r="G111" s="51" t="n"/>
-      <c r="H111" s="52" t="n"/>
-      <c r="I111" s="53" t="n"/>
-      <c r="J111" s="54" t="n"/>
-      <c r="K111" s="55" t="n"/>
-      <c r="L111" s="18" t="n"/>
-      <c r="M111" s="21" t="n"/>
-      <c r="N111" s="56" t="n"/>
-      <c r="O111" s="57" t="n"/>
-      <c r="P111" s="58" t="n"/>
-      <c r="Q111" s="56" t="n"/>
-      <c r="R111" s="56" t="n"/>
-      <c r="S111" s="56" t="n"/>
-      <c r="T111" s="56" t="n"/>
-      <c r="U111" s="56" t="n"/>
-      <c r="V111" s="56" t="n"/>
-      <c r="W111" s="56" t="n"/>
-      <c r="X111" s="56" t="n"/>
-      <c r="Y111" s="56" t="n"/>
-      <c r="Z111" s="56" t="n"/>
-      <c r="AA111" s="56" t="n"/>
-      <c r="AB111" s="56" t="n"/>
+      <c r="B111" s="427" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C111" s="255" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D111" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="49" t="n">
+        <v>1745</v>
+      </c>
+      <c r="F111" s="50">
+        <f>IFERROR(D111+E111+G111+U111+Y111,0)</f>
+        <v>2935.0</v>
+      </c>
+      <c r="G111" s="257" t="n">
+        <v>275</v>
+      </c>
+      <c r="H111" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B111,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B111+1))</f>
+        <v>1980.0</v>
+      </c>
+      <c r="I111" s="259">
+        <f>IFERROR(F111-H111,0)</f>
+        <v>955.0</v>
+      </c>
+      <c r="J111" s="260">
+        <f>IFERROR(I111/F111,0)</f>
+        <v>0.325383</v>
+      </c>
+      <c r="K111" s="254" t="n"/>
+      <c r="L111" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py | updated 18:49</t>
+        </is>
+      </c>
+      <c r="M111" s="291" t="n"/>
+      <c r="N111" s="292" t="n"/>
+      <c r="O111" s="293" t="n"/>
+      <c r="P111" s="294" t="n"/>
+      <c r="Q111" s="292" t="n"/>
+      <c r="R111" s="443">
+        <f>IFERROR(D111*$T$7,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="S111" s="292" t="n"/>
+      <c r="T111" s="292" t="n"/>
+      <c r="U111" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" s="292" t="n"/>
+      <c r="X111" s="292" t="n"/>
+      <c r="Y111" s="443" t="n">
+        <v>915</v>
+      </c>
+      <c r="Z111" s="443" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="AA111" s="292" t="n"/>
+      <c r="AB111" s="292" t="n"/>
     </row>
     <row r="112" ht="16.5" customHeight="1" s="331">
       <c r="B112" s="34" t="n"/>
@@ -24845,7 +24917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J748"/>
+  <dimension ref="A1:J753"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -56512,6 +56584,221 @@
       <c r="J748" s="423" t="inlineStr">
         <is>
           <t>Pagado por Lohith (bolsillo); reembolsable via Owner Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="B749" s="429" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C749" s="297" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="D749" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E749" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F749" s="299" t="n">
+        <v>324</v>
+      </c>
+      <c r="G749" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H749" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I749" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J749" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="B750" s="429" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C750" s="297" t="inlineStr">
+        <is>
+          <t>Molino Soya</t>
+        </is>
+      </c>
+      <c r="D750" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E750" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F750" s="299" t="n">
+        <v>55</v>
+      </c>
+      <c r="G750" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H750" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I750" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J750" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="B751" s="429" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C751" s="297" t="inlineStr">
+        <is>
+          <t>La Comer</t>
+        </is>
+      </c>
+      <c r="D751" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E751" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F751" s="299" t="n">
+        <v>132</v>
+      </c>
+      <c r="G751" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H751" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I751" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J751" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="B752" s="429" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C752" s="297" t="inlineStr">
+        <is>
+          <t>Guimar</t>
+        </is>
+      </c>
+      <c r="D752" s="298" t="inlineStr">
+        <is>
+          <t>Guimar Polietilenos</t>
+        </is>
+      </c>
+      <c r="E752" s="297" t="inlineStr">
+        <is>
+          <t>Packaging/Disposables</t>
+        </is>
+      </c>
+      <c r="F752" s="299" t="n">
+        <v>429</v>
+      </c>
+      <c r="G752" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H752" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I752" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J752" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="B753" s="429" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C753" s="297" t="inlineStr">
+        <is>
+          <t>3B Jugo</t>
+        </is>
+      </c>
+      <c r="D753" s="298" t="inlineStr">
+        <is>
+          <t>Tres B</t>
+        </is>
+      </c>
+      <c r="E753" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F753" s="299" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G753" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H753" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I753" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J753" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
         </is>
       </c>
     </row>

--- a/LOKA_Restaurant_Manager.xlsx
+++ b/LOKA_Restaurant_Manager.xlsx
@@ -5967,7 +5967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="331" min="1" max="1"/>
@@ -8669,30 +8669,129 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="430" t="inlineStr">
+      <c r="A84" s="430" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B84" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 09-Sep)</t>
+        </is>
+      </c>
+      <c r="C84" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D84" s="232" t="n"/>
+      <c r="E84" s="233" t="n">
+        <v>250</v>
+      </c>
+      <c r="F84" s="233">
+        <f>IFERROR(F83+D84-E84,0)</f>
+        <v/>
+      </c>
+      <c r="G84" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H84" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="430" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B85" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 10-Sep)</t>
+        </is>
+      </c>
+      <c r="C85" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D85" s="232" t="n"/>
+      <c r="E85" s="233" t="n">
+        <v>120</v>
+      </c>
+      <c r="F85" s="233">
+        <f>IFERROR(F84+D85-E85,0)</f>
+        <v/>
+      </c>
+      <c r="G85" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H85" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="430" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B86" s="232" t="inlineStr">
+        <is>
+          <t>Transfer-to-me (customer payment 11-Sep)</t>
+        </is>
+      </c>
+      <c r="C86" s="232" t="inlineStr">
+        <is>
+          <t>Transfer Received</t>
+        </is>
+      </c>
+      <c r="D86" s="232" t="n"/>
+      <c r="E86" s="233" t="n">
+        <v>1010</v>
+      </c>
+      <c r="F86" s="233">
+        <f>IFERROR(F85+D86-E86,0)</f>
+        <v/>
+      </c>
+      <c r="G86" s="232" t="inlineStr">
+        <is>
+          <t>✅ Received</t>
+        </is>
+      </c>
+      <c r="H86" s="232" t="inlineStr">
+        <is>
+          <t>Customer paid Lohith personal acct</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="430" t="inlineStr">
         <is>
           <t>TOTALS &amp; CURRENT BALANCE</t>
         </is>
       </c>
-      <c r="B84" s="232" t="n"/>
-      <c r="C84" s="232" t="n"/>
-      <c r="D84" s="232">
-        <f>SUM(D4:D83)</f>
+      <c r="B87" s="232" t="n"/>
+      <c r="C87" s="232" t="n"/>
+      <c r="D87" s="232">
+        <f>SUM(D4:D86)</f>
         <v/>
       </c>
-      <c r="E84" s="233">
-        <f>SUM(E4:E83)</f>
+      <c r="E87" s="233">
+        <f>SUM(E4:E86)</f>
         <v/>
       </c>
-      <c r="F84" s="233">
-        <f>F83</f>
+      <c r="F87" s="233">
+        <f>F86</f>
         <v/>
       </c>
-      <c r="G84" s="232">
-        <f>IF(F83&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F83,"#,##0"),IF(F83&lt;0,"Lohith holds $"&amp;TEXT(ABS(F83),"#,##0"),"Zero balance"))</f>
+      <c r="G87" s="232">
+        <f>IF(F86&gt;0,"Restaurant owes Lohith $"&amp;TEXT(F86,"#,##0"),IF(F86&lt;0,"Lohith holds $"&amp;TEXT(ABS(F86),"#,##0"),"Zero balance"))</f>
         <v/>
       </c>
-      <c r="H84" s="232" t="n"/>
+      <c r="H87" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10526,45 +10625,45 @@
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="30">
         <f>SUMIFS($D$8:$D$5000,$B$8:$B$5000,TODAY())+SUMIFS($E$8:$E$5000,$B$8:$B$5000,TODAY())+SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>2935.0</v>
+        <v>3345.0</v>
       </c>
       <c r="G6" s="31">
         <f>SUMIFS($G$8:$G$5000,$B$8:$B$5000,TODAY())</f>
-        <v>275.0</v>
+        <v>1010.0</v>
       </c>
       <c r="H6" s="28">
         <f>SUMIFS($H$8:$H$5000,$B$8:$B$5000,TODAY())</f>
-        <v>1980.0</v>
+        <v>45.0</v>
       </c>
       <c r="I6" s="32">
         <f>F6-H6</f>
-        <v>955.0</v>
+        <v>3300.0</v>
       </c>
       <c r="J6">
         <f>IFERROR(I6/F6,0)</f>
-        <v>0.325383</v>
+        <v>0.986547</v>
       </c>
       <c r="K6" s="28" t="n"/>
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="28">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>6820.0</v>
+        <v>17130.0</v>
       </c>
       <c r="N6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>6820.0</v>
+        <v>17130.0</v>
       </c>
       <c r="O6" s="33">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*(MONTH($B$8:$B$5000)=MONTH(TODAY()))*(YEAR($B$8:$B$5000)=YEAR(TODAY()))*IF(ISNUMBER($F$8:$F$5000),$F$8:$F$5000,0))</f>
-        <v>32364.0</v>
+        <v>42674.0</v>
       </c>
       <c r="P6">
         <f>SUMPRODUCT((ISNUMBER($B$8:$B$5000))*($B$8:$B$5000&gt;=TODAY()-MOD(TODAY()-2,7))*($B$8:$B$5000&lt;TODAY()-MOD(TODAY()-2,7)+7)*IF(ISNUMBER($H$8:$H$5000),$H$8:$H$5000,0))</f>
-        <v>8268.0</v>
+        <v>11078.0</v>
       </c>
       <c r="Q6">
         <f>M6-P6</f>
-        <v>-1448.0</v>
+        <v>6052.0</v>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="331">
@@ -17322,91 +17421,208 @@
       <c r="AB111" s="292" t="n"/>
     </row>
     <row r="112" ht="16.5" customHeight="1" s="331">
-      <c r="B112" s="34" t="n"/>
-      <c r="C112" s="35" t="n"/>
-      <c r="D112" s="36" t="n"/>
-      <c r="E112" s="37" t="n"/>
-      <c r="F112" s="38" t="n"/>
-      <c r="G112" s="39" t="n"/>
-      <c r="H112" s="40" t="n"/>
-      <c r="I112" s="41" t="n"/>
-      <c r="J112" s="42" t="n"/>
-      <c r="K112" s="43" t="n"/>
-      <c r="L112" s="9" t="n"/>
-      <c r="M112" s="12" t="n"/>
-      <c r="N112" s="44" t="n"/>
-      <c r="O112" s="45" t="n"/>
-      <c r="P112" s="46" t="n"/>
-      <c r="Q112" s="44" t="n"/>
-      <c r="R112" s="44" t="n"/>
-      <c r="S112" s="44" t="n"/>
-      <c r="T112" s="44" t="n"/>
-      <c r="U112" s="44" t="n"/>
-      <c r="V112" s="44" t="n"/>
-      <c r="W112" s="44" t="n"/>
-      <c r="X112" s="44" t="n"/>
-      <c r="Y112" s="44" t="n"/>
-      <c r="Z112" s="44" t="n"/>
-      <c r="AA112" s="44" t="n"/>
-      <c r="AB112" s="44" t="n"/>
+      <c r="B112" s="427" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C112" s="270" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D112" s="271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="37" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F112" s="38">
+        <f>IFERROR(D112+E112+G112+U112+Y112,0)</f>
+        <v>3160.0</v>
+      </c>
+      <c r="G112" s="272" t="n">
+        <v>250</v>
+      </c>
+      <c r="H112" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B112,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B112+1))</f>
+        <v>1106.0</v>
+      </c>
+      <c r="I112" s="274">
+        <f>IFERROR(F112-H112,0)</f>
+        <v>2054.0</v>
+      </c>
+      <c r="J112" s="275">
+        <f>IFERROR(I112/F112,0)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K112" s="250" t="n"/>
+      <c r="L112" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py | updated 17:50 | updated 21:09</t>
+        </is>
+      </c>
+      <c r="M112" s="323" t="n"/>
+      <c r="N112" s="324" t="n"/>
+      <c r="O112" s="325" t="n"/>
+      <c r="P112" s="326" t="n"/>
+      <c r="Q112" s="324" t="n"/>
+      <c r="R112" s="428">
+        <f>IFERROR(D112*$T$7,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="S112" s="324" t="n"/>
+      <c r="T112" s="324" t="n"/>
+      <c r="U112" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" s="324" t="n"/>
+      <c r="X112" s="324" t="n"/>
+      <c r="Y112" s="428" t="n">
+        <v>1870</v>
+      </c>
+      <c r="Z112" s="428" t="n">
+        <v>35.53</v>
+      </c>
+      <c r="AA112" s="324" t="n"/>
+      <c r="AB112" s="324" t="n"/>
     </row>
     <row r="113" ht="16.5" customHeight="1" s="331">
-      <c r="B113" s="34" t="n"/>
-      <c r="C113" s="47" t="n"/>
-      <c r="D113" s="48" t="n"/>
-      <c r="E113" s="49" t="n"/>
-      <c r="F113" s="50" t="n"/>
-      <c r="G113" s="51" t="n"/>
-      <c r="H113" s="52" t="n"/>
-      <c r="I113" s="53" t="n"/>
-      <c r="J113" s="54" t="n"/>
-      <c r="K113" s="55" t="n"/>
-      <c r="L113" s="18" t="n"/>
-      <c r="M113" s="21" t="n"/>
-      <c r="N113" s="56" t="n"/>
-      <c r="O113" s="57" t="n"/>
-      <c r="P113" s="58" t="n"/>
-      <c r="Q113" s="56" t="n"/>
-      <c r="R113" s="56" t="n"/>
-      <c r="S113" s="56" t="n"/>
-      <c r="T113" s="56" t="n"/>
-      <c r="U113" s="56" t="n"/>
-      <c r="V113" s="56" t="n"/>
-      <c r="W113" s="56" t="n"/>
-      <c r="X113" s="56" t="n"/>
-      <c r="Y113" s="56" t="n"/>
-      <c r="Z113" s="56" t="n"/>
-      <c r="AA113" s="56" t="n"/>
-      <c r="AB113" s="56" t="n"/>
+      <c r="B113" s="427" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C113" s="255" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D113" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="49" t="n">
+        <v>1685</v>
+      </c>
+      <c r="F113" s="50">
+        <f>IFERROR(D113+E113+G113+U113+Y113,0)</f>
+        <v>3805.0</v>
+      </c>
+      <c r="G113" s="257" t="n">
+        <v>120</v>
+      </c>
+      <c r="H113" s="258">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B113,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B113+1))</f>
+        <v>1659.0</v>
+      </c>
+      <c r="I113" s="259">
+        <f>IFERROR(F113-H113,0)</f>
+        <v>2146.0</v>
+      </c>
+      <c r="J113" s="260">
+        <f>IFERROR(I113/F113,0)</f>
+        <v>0.563995</v>
+      </c>
+      <c r="K113" s="254" t="n"/>
+      <c r="L113" s="261" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py | updated 17:29</t>
+        </is>
+      </c>
+      <c r="M113" s="291" t="n"/>
+      <c r="N113" s="292" t="n"/>
+      <c r="O113" s="293" t="n"/>
+      <c r="P113" s="294" t="n"/>
+      <c r="Q113" s="292" t="n"/>
+      <c r="R113" s="443">
+        <f>IFERROR(D113*$T$7,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="S113" s="292" t="n"/>
+      <c r="T113" s="292" t="n"/>
+      <c r="U113" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" s="443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" s="292" t="n"/>
+      <c r="X113" s="292" t="n"/>
+      <c r="Y113" s="443" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Z113" s="443" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA113" s="292" t="n"/>
+      <c r="AB113" s="292" t="n"/>
     </row>
     <row r="114" ht="16.5" customHeight="1" s="331">
-      <c r="B114" s="34" t="n"/>
-      <c r="C114" s="35" t="n"/>
-      <c r="D114" s="36" t="n"/>
-      <c r="E114" s="37" t="n"/>
-      <c r="F114" s="38" t="n"/>
-      <c r="G114" s="39" t="n"/>
-      <c r="H114" s="40" t="n"/>
-      <c r="I114" s="41" t="n"/>
-      <c r="J114" s="42" t="n"/>
-      <c r="K114" s="43" t="n"/>
-      <c r="L114" s="9" t="n"/>
-      <c r="M114" s="12" t="n"/>
-      <c r="N114" s="44" t="n"/>
-      <c r="O114" s="45" t="n"/>
-      <c r="P114" s="46" t="n"/>
-      <c r="Q114" s="44" t="n"/>
-      <c r="R114" s="44" t="n"/>
-      <c r="S114" s="44" t="n"/>
-      <c r="T114" s="44" t="n"/>
-      <c r="U114" s="44" t="n"/>
-      <c r="V114" s="44" t="n"/>
-      <c r="W114" s="44" t="n"/>
-      <c r="X114" s="44" t="n"/>
-      <c r="Y114" s="44" t="n"/>
-      <c r="Z114" s="44" t="n"/>
-      <c r="AA114" s="44" t="n"/>
-      <c r="AB114" s="44" t="n"/>
+      <c r="B114" s="427" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C114" s="270" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D114" s="271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="37" t="n">
+        <v>820</v>
+      </c>
+      <c r="F114" s="38">
+        <f>IFERROR(D114+E114+G114+U114+Y114,0)</f>
+        <v>3345.0</v>
+      </c>
+      <c r="G114" s="272" t="n">
+        <v>1010</v>
+      </c>
+      <c r="H114" s="273">
+        <f>SUMIFS('💸 Expenses'!$F$8:$F$5000,'💸 Expenses'!$B$8:$B$5000,"&gt;="&amp;B114,'💸 Expenses'!$B$8:$B$5000,"&lt;"&amp;(B114+1))</f>
+        <v>45.0</v>
+      </c>
+      <c r="I114" s="274">
+        <f>IFERROR(F114-H114,0)</f>
+        <v>3300.0</v>
+      </c>
+      <c r="J114" s="275">
+        <f>IFERROR(I114/F114,0)</f>
+        <v>0.986547</v>
+      </c>
+      <c r="K114" s="250" t="n"/>
+      <c r="L114" s="276" t="inlineStr">
+        <is>
+          <t>Cierre via loka.py</t>
+        </is>
+      </c>
+      <c r="M114" s="323" t="n"/>
+      <c r="N114" s="324" t="n"/>
+      <c r="O114" s="325" t="n"/>
+      <c r="P114" s="326" t="n"/>
+      <c r="Q114" s="324" t="n"/>
+      <c r="R114" s="428">
+        <f>IFERROR(D114*$T$7,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="S114" s="324" t="n"/>
+      <c r="T114" s="324" t="n"/>
+      <c r="U114" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" s="428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" s="324" t="n"/>
+      <c r="X114" s="324" t="n"/>
+      <c r="Y114" s="428" t="n">
+        <v>1515</v>
+      </c>
+      <c r="Z114" s="428" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="AA114" s="324" t="n"/>
+      <c r="AB114" s="324" t="n"/>
     </row>
     <row r="115" ht="16.5" customHeight="1" s="331">
       <c r="B115" s="34" t="n"/>
@@ -24892,9 +25108,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:P5"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:P2"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I372">
@@ -24917,7 +25133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J753"/>
+  <dimension ref="A1:J764"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="4" customWidth="1" style="331" min="1" max="1"/>
@@ -56797,6 +57013,479 @@
         </is>
       </c>
       <c r="J753" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="B754" s="429" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C754" s="297" t="inlineStr">
+        <is>
+          <t>Avia</t>
+        </is>
+      </c>
+      <c r="D754" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E754" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F754" s="299" t="n">
+        <v>450</v>
+      </c>
+      <c r="G754" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H754" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I754" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J754" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="B755" s="429" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C755" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D755" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E755" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F755" s="299" t="n">
+        <v>634</v>
+      </c>
+      <c r="G755" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H755" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I755" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J755" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="B756" s="429" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C756" s="297" t="inlineStr">
+        <is>
+          <t>Oxxo</t>
+        </is>
+      </c>
+      <c r="D756" s="298" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E756" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F756" s="299" t="n">
+        <v>22</v>
+      </c>
+      <c r="G756" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H756" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I756" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J756" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="B757" s="429" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C757" s="297" t="inlineStr">
+        <is>
+          <t>Pan Reales</t>
+        </is>
+      </c>
+      <c r="D757" s="298" t="inlineStr">
+        <is>
+          <t>Pan Reales</t>
+        </is>
+      </c>
+      <c r="E757" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Bread</t>
+        </is>
+      </c>
+      <c r="F757" s="299" t="n">
+        <v>621</v>
+      </c>
+      <c r="G757" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H757" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I757" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J757" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="B758" s="429" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C758" s="297" t="inlineStr">
+        <is>
+          <t>Oxxo</t>
+        </is>
+      </c>
+      <c r="D758" s="298" t="inlineStr">
+        <is>
+          <t>OXXO</t>
+        </is>
+      </c>
+      <c r="E758" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Pantry</t>
+        </is>
+      </c>
+      <c r="F758" s="299" t="n">
+        <v>32</v>
+      </c>
+      <c r="G758" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H758" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I758" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J758" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="B759" s="429" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C759" s="297" t="inlineStr">
+        <is>
+          <t>Pescado</t>
+        </is>
+      </c>
+      <c r="D759" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E759" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat &amp; Fish</t>
+        </is>
+      </c>
+      <c r="F759" s="299" t="n">
+        <v>317</v>
+      </c>
+      <c r="G759" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H759" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I759" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J759" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="B760" s="429" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C760" s="297" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="D760" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E760" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Meat</t>
+        </is>
+      </c>
+      <c r="F760" s="299" t="n">
+        <v>495</v>
+      </c>
+      <c r="G760" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H760" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I760" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J760" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="B761" s="429" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C761" s="297" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="D761" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E761" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F761" s="299" t="n">
+        <v>60</v>
+      </c>
+      <c r="G761" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H761" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I761" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J761" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="B762" s="429" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C762" s="297" t="inlineStr">
+        <is>
+          <t>Lechuga</t>
+        </is>
+      </c>
+      <c r="D762" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E762" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Vegetables</t>
+        </is>
+      </c>
+      <c r="F762" s="299" t="n">
+        <v>50</v>
+      </c>
+      <c r="G762" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H762" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I762" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J762" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="B763" s="429" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C763" s="297" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="D763" s="298" t="inlineStr">
+        <is>
+          <t>Chedraui</t>
+        </is>
+      </c>
+      <c r="E763" s="297" t="inlineStr">
+        <is>
+          <t>Supermarket/General</t>
+        </is>
+      </c>
+      <c r="F763" s="299" t="n">
+        <v>84</v>
+      </c>
+      <c r="G763" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H763" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I763" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J763" s="423" t="inlineStr">
+        <is>
+          <t>No receipt; cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="B764" s="429" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C764" s="297" t="inlineStr">
+        <is>
+          <t>Agua Natural</t>
+        </is>
+      </c>
+      <c r="D764" s="298" t="inlineStr">
+        <is>
+          <t>No bill</t>
+        </is>
+      </c>
+      <c r="E764" s="297" t="inlineStr">
+        <is>
+          <t>Ingredients - Beverages</t>
+        </is>
+      </c>
+      <c r="F764" s="299" t="n">
+        <v>45</v>
+      </c>
+      <c r="G764" s="300" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H764" s="300" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I764" s="301" t="inlineStr">
+        <is>
+          <t>✅ Paid</t>
+        </is>
+      </c>
+      <c r="J764" s="423" t="inlineStr">
         <is>
           <t>No receipt; cash</t>
         </is>
@@ -67693,7 +68382,7 @@
     <row r="27">
       <c r="A27" s="439" t="inlineStr">
         <is>
-          <t>Supplies/Other</t>
+          <t>Ingredients - Meat &amp; Fish</t>
         </is>
       </c>
       <c r="B27" s="437">
@@ -67726,7 +68415,7 @@
     <row r="28">
       <c r="A28" s="439" t="inlineStr">
         <is>
-          <t>Ingredients - Meat &amp; Fish</t>
+          <t>Supplies/Other</t>
         </is>
       </c>
       <c r="B28" s="437">
